--- a/src/main/resources/canevas/canevas-vierge.xlsx
+++ b/src/main/resources/canevas/canevas-vierge.xlsx
@@ -556,7 +556,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
@@ -571,7 +570,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="17" t="inlineStr">
         <is>
@@ -621,7 +619,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="17" t="inlineStr">
         <is>
@@ -657,7 +654,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="17" t="inlineStr">
         <is>
@@ -700,7 +696,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28">
       <c r="A28" s="17" t="inlineStr">
         <is>
@@ -913,10 +908,10 @@
   </mergeCells>
   <dataValidations count="3">
     <dataValidation sqref="B9 B11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>Referentiels!$C$4:$C$23</formula1>
+      <formula1>Referentiels!$C$4:$C$203</formula1>
     </dataValidation>
     <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>Referentiels!$A$4:$A$23</formula1>
+      <formula1>Referentiels!$A$4:$A$203</formula1>
     </dataValidation>
     <dataValidation sqref="B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Referentiels!$E$4:$E$13</formula1>
@@ -1948,10 +1943,10 @@
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="F2:F300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>Referentiels!$A$4:$A$23</formula1>
+      <formula1>Referentiels!$A$4:$A$203</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>Referentiels!$C$4:$C$23</formula1>
+      <formula1>Referentiels!$C$4:$C$203</formula1>
     </dataValidation>
     <dataValidation sqref="H2:H300 I2:I300 J2:J300 K2:K300 L2:L300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Oui,Non"</formula1>

--- a/src/main/resources/canevas/canevas-vierge.xlsx
+++ b/src/main/resources/canevas/canevas-vierge.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4-Imprimantes" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5-Switchs et AP" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6-Scanners chèque" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Referentiels" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agents TPR" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Referentiels" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -245,6 +246,21 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>App</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Agents du poste. Pré-rempli par l'application. Ajoutez ici tout agent attributaire absent de la base ; il sera créé à l'import.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -906,15 +922,18 @@
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <dataValidations count="3">
-    <dataValidation sqref="B9 B11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>Referentiels!$C$4:$C$203</formula1>
-    </dataValidation>
+  <dataValidations count="4">
     <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Referentiels!$A$4:$A$203</formula1>
     </dataValidation>
     <dataValidation sqref="B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Referentiels!$E$4:$E$13</formula1>
+    </dataValidation>
+    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Referentiels!$C$4:$C$203</formula1>
+    </dataValidation>
+    <dataValidation sqref="B11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Referentiels!$G$4:$G$203</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1351,7 +1370,7 @@
       </c>
       <c r="G1" s="10" t="inlineStr">
         <is>
-          <t>Agent installateur *</t>
+          <t>Agent traitant *</t>
         </is>
       </c>
       <c r="H1" s="10" t="inlineStr">
@@ -1943,10 +1962,10 @@
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="F2:F300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>Referentiels!$A$4:$A$203</formula1>
+      <formula1>'Agents TPR'!$A$2:$A$203</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>Referentiels!$C$4:$C$203</formula1>
+      <formula1>Referentiels!$G$4:$G$203</formula1>
     </dataValidation>
     <dataValidation sqref="H2:H300 I2:I300 J2:J300 K2:K300 L2:L300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Oui,Non"</formula1>
@@ -2997,7 +3016,106 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>Matricule *</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>Nom *</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>Prénom *</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>Fonction</t>
+        </is>
+      </c>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>Téléphone</t>
+        </is>
+      </c>
+      <c r="F1" s="10" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AG001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>DIOP</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Awa</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Caissier</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AG002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NDIAYE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Modou</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Comptable</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3005,6 +3123,7 @@
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3037,6 +3156,11 @@
           <t>Catégories de câble</t>
         </is>
       </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>Membres de la mission (matricule — nom)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="14" t="inlineStr">
@@ -3054,6 +3178,11 @@
           <t>Cat5e</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>IN001 — SOW Cheikh</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -3069,6 +3198,11 @@
       <c r="E5" s="14" t="inlineStr">
         <is>
           <t>Cat6</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>IN002 — BA Fatou</t>
         </is>
       </c>
     </row>

--- a/src/main/resources/canevas/canevas-vierge.xlsx
+++ b/src/main/resources/canevas/canevas-vierge.xlsx
@@ -1328,8 +1328,8 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -1962,7 +1962,7 @@
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="F2:F300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Agents TPR'!$A$2:$A$203</formula1>
+      <formula1>'Agents TPR'!$H$2:$H$203</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Referentiels!$G$4:$G$203</formula1>
@@ -3016,7 +3016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:H203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3025,6 +3025,7 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
+    <col hidden="1" width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3058,6 +3059,11 @@
           <t>Email</t>
         </is>
       </c>
+      <c r="H1" s="10" t="inlineStr">
+        <is>
+          <t>Sélection (auto — ne pas modifier)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3080,6 +3086,10 @@
           <t>Caissier</t>
         </is>
       </c>
+      <c r="H2">
+        <f>IF($A2="","",$A2&amp;" — "&amp;$C2&amp;" "&amp;$B2)</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3101,6 +3111,1210 @@
         <is>
           <t>Comptable</t>
         </is>
+      </c>
+      <c r="H3">
+        <f>IF($A3="","",$A3&amp;" — "&amp;$C3&amp;" "&amp;$B3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="H4">
+        <f>IF($A4="","",$A4&amp;" — "&amp;$C4&amp;" "&amp;$B4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="H5">
+        <f>IF($A5="","",$A5&amp;" — "&amp;$C5&amp;" "&amp;$B5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="H6">
+        <f>IF($A6="","",$A6&amp;" — "&amp;$C6&amp;" "&amp;$B6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="H7">
+        <f>IF($A7="","",$A7&amp;" — "&amp;$C7&amp;" "&amp;$B7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="H8">
+        <f>IF($A8="","",$A8&amp;" — "&amp;$C8&amp;" "&amp;$B8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="H9">
+        <f>IF($A9="","",$A9&amp;" — "&amp;$C9&amp;" "&amp;$B9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="H10">
+        <f>IF($A10="","",$A10&amp;" — "&amp;$C10&amp;" "&amp;$B10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="H11">
+        <f>IF($A11="","",$A11&amp;" — "&amp;$C11&amp;" "&amp;$B11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="H12">
+        <f>IF($A12="","",$A12&amp;" — "&amp;$C12&amp;" "&amp;$B12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="H13">
+        <f>IF($A13="","",$A13&amp;" — "&amp;$C13&amp;" "&amp;$B13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="H14">
+        <f>IF($A14="","",$A14&amp;" — "&amp;$C14&amp;" "&amp;$B14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="H15">
+        <f>IF($A15="","",$A15&amp;" — "&amp;$C15&amp;" "&amp;$B15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="H16">
+        <f>IF($A16="","",$A16&amp;" — "&amp;$C16&amp;" "&amp;$B16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="H17">
+        <f>IF($A17="","",$A17&amp;" — "&amp;$C17&amp;" "&amp;$B17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="H18">
+        <f>IF($A18="","",$A18&amp;" — "&amp;$C18&amp;" "&amp;$B18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="H19">
+        <f>IF($A19="","",$A19&amp;" — "&amp;$C19&amp;" "&amp;$B19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="H20">
+        <f>IF($A20="","",$A20&amp;" — "&amp;$C20&amp;" "&amp;$B20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="H21">
+        <f>IF($A21="","",$A21&amp;" — "&amp;$C21&amp;" "&amp;$B21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="H22">
+        <f>IF($A22="","",$A22&amp;" — "&amp;$C22&amp;" "&amp;$B22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="H23">
+        <f>IF($A23="","",$A23&amp;" — "&amp;$C23&amp;" "&amp;$B23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="H24">
+        <f>IF($A24="","",$A24&amp;" — "&amp;$C24&amp;" "&amp;$B24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="H25">
+        <f>IF($A25="","",$A25&amp;" — "&amp;$C25&amp;" "&amp;$B25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="H26">
+        <f>IF($A26="","",$A26&amp;" — "&amp;$C26&amp;" "&amp;$B26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="H27">
+        <f>IF($A27="","",$A27&amp;" — "&amp;$C27&amp;" "&amp;$B27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="H28">
+        <f>IF($A28="","",$A28&amp;" — "&amp;$C28&amp;" "&amp;$B28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="H29">
+        <f>IF($A29="","",$A29&amp;" — "&amp;$C29&amp;" "&amp;$B29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="H30">
+        <f>IF($A30="","",$A30&amp;" — "&amp;$C30&amp;" "&amp;$B30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="H31">
+        <f>IF($A31="","",$A31&amp;" — "&amp;$C31&amp;" "&amp;$B31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="H32">
+        <f>IF($A32="","",$A32&amp;" — "&amp;$C32&amp;" "&amp;$B32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="H33">
+        <f>IF($A33="","",$A33&amp;" — "&amp;$C33&amp;" "&amp;$B33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="H34">
+        <f>IF($A34="","",$A34&amp;" — "&amp;$C34&amp;" "&amp;$B34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="H35">
+        <f>IF($A35="","",$A35&amp;" — "&amp;$C35&amp;" "&amp;$B35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="H36">
+        <f>IF($A36="","",$A36&amp;" — "&amp;$C36&amp;" "&amp;$B36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="H37">
+        <f>IF($A37="","",$A37&amp;" — "&amp;$C37&amp;" "&amp;$B37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="H38">
+        <f>IF($A38="","",$A38&amp;" — "&amp;$C38&amp;" "&amp;$B38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="H39">
+        <f>IF($A39="","",$A39&amp;" — "&amp;$C39&amp;" "&amp;$B39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="H40">
+        <f>IF($A40="","",$A40&amp;" — "&amp;$C40&amp;" "&amp;$B40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="H41">
+        <f>IF($A41="","",$A41&amp;" — "&amp;$C41&amp;" "&amp;$B41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="H42">
+        <f>IF($A42="","",$A42&amp;" — "&amp;$C42&amp;" "&amp;$B42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="H43">
+        <f>IF($A43="","",$A43&amp;" — "&amp;$C43&amp;" "&amp;$B43)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="H44">
+        <f>IF($A44="","",$A44&amp;" — "&amp;$C44&amp;" "&amp;$B44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="H45">
+        <f>IF($A45="","",$A45&amp;" — "&amp;$C45&amp;" "&amp;$B45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="H46">
+        <f>IF($A46="","",$A46&amp;" — "&amp;$C46&amp;" "&amp;$B46)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="H47">
+        <f>IF($A47="","",$A47&amp;" — "&amp;$C47&amp;" "&amp;$B47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="H48">
+        <f>IF($A48="","",$A48&amp;" — "&amp;$C48&amp;" "&amp;$B48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="H49">
+        <f>IF($A49="","",$A49&amp;" — "&amp;$C49&amp;" "&amp;$B49)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="H50">
+        <f>IF($A50="","",$A50&amp;" — "&amp;$C50&amp;" "&amp;$B50)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="H51">
+        <f>IF($A51="","",$A51&amp;" — "&amp;$C51&amp;" "&amp;$B51)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="H52">
+        <f>IF($A52="","",$A52&amp;" — "&amp;$C52&amp;" "&amp;$B52)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="H53">
+        <f>IF($A53="","",$A53&amp;" — "&amp;$C53&amp;" "&amp;$B53)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="H54">
+        <f>IF($A54="","",$A54&amp;" — "&amp;$C54&amp;" "&amp;$B54)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="H55">
+        <f>IF($A55="","",$A55&amp;" — "&amp;$C55&amp;" "&amp;$B55)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="H56">
+        <f>IF($A56="","",$A56&amp;" — "&amp;$C56&amp;" "&amp;$B56)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="H57">
+        <f>IF($A57="","",$A57&amp;" — "&amp;$C57&amp;" "&amp;$B57)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="H58">
+        <f>IF($A58="","",$A58&amp;" — "&amp;$C58&amp;" "&amp;$B58)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="H59">
+        <f>IF($A59="","",$A59&amp;" — "&amp;$C59&amp;" "&amp;$B59)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="H60">
+        <f>IF($A60="","",$A60&amp;" — "&amp;$C60&amp;" "&amp;$B60)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="H61">
+        <f>IF($A61="","",$A61&amp;" — "&amp;$C61&amp;" "&amp;$B61)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="H62">
+        <f>IF($A62="","",$A62&amp;" — "&amp;$C62&amp;" "&amp;$B62)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="H63">
+        <f>IF($A63="","",$A63&amp;" — "&amp;$C63&amp;" "&amp;$B63)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="H64">
+        <f>IF($A64="","",$A64&amp;" — "&amp;$C64&amp;" "&amp;$B64)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="H65">
+        <f>IF($A65="","",$A65&amp;" — "&amp;$C65&amp;" "&amp;$B65)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="H66">
+        <f>IF($A66="","",$A66&amp;" — "&amp;$C66&amp;" "&amp;$B66)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="H67">
+        <f>IF($A67="","",$A67&amp;" — "&amp;$C67&amp;" "&amp;$B67)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="H68">
+        <f>IF($A68="","",$A68&amp;" — "&amp;$C68&amp;" "&amp;$B68)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="H69">
+        <f>IF($A69="","",$A69&amp;" — "&amp;$C69&amp;" "&amp;$B69)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="H70">
+        <f>IF($A70="","",$A70&amp;" — "&amp;$C70&amp;" "&amp;$B70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="H71">
+        <f>IF($A71="","",$A71&amp;" — "&amp;$C71&amp;" "&amp;$B71)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="H72">
+        <f>IF($A72="","",$A72&amp;" — "&amp;$C72&amp;" "&amp;$B72)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="H73">
+        <f>IF($A73="","",$A73&amp;" — "&amp;$C73&amp;" "&amp;$B73)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="H74">
+        <f>IF($A74="","",$A74&amp;" — "&amp;$C74&amp;" "&amp;$B74)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="H75">
+        <f>IF($A75="","",$A75&amp;" — "&amp;$C75&amp;" "&amp;$B75)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="H76">
+        <f>IF($A76="","",$A76&amp;" — "&amp;$C76&amp;" "&amp;$B76)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="H77">
+        <f>IF($A77="","",$A77&amp;" — "&amp;$C77&amp;" "&amp;$B77)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="H78">
+        <f>IF($A78="","",$A78&amp;" — "&amp;$C78&amp;" "&amp;$B78)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="H79">
+        <f>IF($A79="","",$A79&amp;" — "&amp;$C79&amp;" "&amp;$B79)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="H80">
+        <f>IF($A80="","",$A80&amp;" — "&amp;$C80&amp;" "&amp;$B80)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="H81">
+        <f>IF($A81="","",$A81&amp;" — "&amp;$C81&amp;" "&amp;$B81)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="H82">
+        <f>IF($A82="","",$A82&amp;" — "&amp;$C82&amp;" "&amp;$B82)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="H83">
+        <f>IF($A83="","",$A83&amp;" — "&amp;$C83&amp;" "&amp;$B83)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="H84">
+        <f>IF($A84="","",$A84&amp;" — "&amp;$C84&amp;" "&amp;$B84)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="H85">
+        <f>IF($A85="","",$A85&amp;" — "&amp;$C85&amp;" "&amp;$B85)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="H86">
+        <f>IF($A86="","",$A86&amp;" — "&amp;$C86&amp;" "&amp;$B86)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="H87">
+        <f>IF($A87="","",$A87&amp;" — "&amp;$C87&amp;" "&amp;$B87)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="H88">
+        <f>IF($A88="","",$A88&amp;" — "&amp;$C88&amp;" "&amp;$B88)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="H89">
+        <f>IF($A89="","",$A89&amp;" — "&amp;$C89&amp;" "&amp;$B89)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="H90">
+        <f>IF($A90="","",$A90&amp;" — "&amp;$C90&amp;" "&amp;$B90)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="H91">
+        <f>IF($A91="","",$A91&amp;" — "&amp;$C91&amp;" "&amp;$B91)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="H92">
+        <f>IF($A92="","",$A92&amp;" — "&amp;$C92&amp;" "&amp;$B92)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="H93">
+        <f>IF($A93="","",$A93&amp;" — "&amp;$C93&amp;" "&amp;$B93)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="H94">
+        <f>IF($A94="","",$A94&amp;" — "&amp;$C94&amp;" "&amp;$B94)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="H95">
+        <f>IF($A95="","",$A95&amp;" — "&amp;$C95&amp;" "&amp;$B95)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="H96">
+        <f>IF($A96="","",$A96&amp;" — "&amp;$C96&amp;" "&amp;$B96)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="H97">
+        <f>IF($A97="","",$A97&amp;" — "&amp;$C97&amp;" "&amp;$B97)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="H98">
+        <f>IF($A98="","",$A98&amp;" — "&amp;$C98&amp;" "&amp;$B98)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="H99">
+        <f>IF($A99="","",$A99&amp;" — "&amp;$C99&amp;" "&amp;$B99)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="H100">
+        <f>IF($A100="","",$A100&amp;" — "&amp;$C100&amp;" "&amp;$B100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="H101">
+        <f>IF($A101="","",$A101&amp;" — "&amp;$C101&amp;" "&amp;$B101)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="H102">
+        <f>IF($A102="","",$A102&amp;" — "&amp;$C102&amp;" "&amp;$B102)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="H103">
+        <f>IF($A103="","",$A103&amp;" — "&amp;$C103&amp;" "&amp;$B103)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="H104">
+        <f>IF($A104="","",$A104&amp;" — "&amp;$C104&amp;" "&amp;$B104)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="H105">
+        <f>IF($A105="","",$A105&amp;" — "&amp;$C105&amp;" "&amp;$B105)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="H106">
+        <f>IF($A106="","",$A106&amp;" — "&amp;$C106&amp;" "&amp;$B106)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="H107">
+        <f>IF($A107="","",$A107&amp;" — "&amp;$C107&amp;" "&amp;$B107)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="H108">
+        <f>IF($A108="","",$A108&amp;" — "&amp;$C108&amp;" "&amp;$B108)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="H109">
+        <f>IF($A109="","",$A109&amp;" — "&amp;$C109&amp;" "&amp;$B109)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="H110">
+        <f>IF($A110="","",$A110&amp;" — "&amp;$C110&amp;" "&amp;$B110)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="H111">
+        <f>IF($A111="","",$A111&amp;" — "&amp;$C111&amp;" "&amp;$B111)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="H112">
+        <f>IF($A112="","",$A112&amp;" — "&amp;$C112&amp;" "&amp;$B112)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="H113">
+        <f>IF($A113="","",$A113&amp;" — "&amp;$C113&amp;" "&amp;$B113)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="H114">
+        <f>IF($A114="","",$A114&amp;" — "&amp;$C114&amp;" "&amp;$B114)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="H115">
+        <f>IF($A115="","",$A115&amp;" — "&amp;$C115&amp;" "&amp;$B115)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="H116">
+        <f>IF($A116="","",$A116&amp;" — "&amp;$C116&amp;" "&amp;$B116)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="H117">
+        <f>IF($A117="","",$A117&amp;" — "&amp;$C117&amp;" "&amp;$B117)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="H118">
+        <f>IF($A118="","",$A118&amp;" — "&amp;$C118&amp;" "&amp;$B118)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="H119">
+        <f>IF($A119="","",$A119&amp;" — "&amp;$C119&amp;" "&amp;$B119)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="H120">
+        <f>IF($A120="","",$A120&amp;" — "&amp;$C120&amp;" "&amp;$B120)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="H121">
+        <f>IF($A121="","",$A121&amp;" — "&amp;$C121&amp;" "&amp;$B121)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="H122">
+        <f>IF($A122="","",$A122&amp;" — "&amp;$C122&amp;" "&amp;$B122)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="H123">
+        <f>IF($A123="","",$A123&amp;" — "&amp;$C123&amp;" "&amp;$B123)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="H124">
+        <f>IF($A124="","",$A124&amp;" — "&amp;$C124&amp;" "&amp;$B124)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="H125">
+        <f>IF($A125="","",$A125&amp;" — "&amp;$C125&amp;" "&amp;$B125)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="H126">
+        <f>IF($A126="","",$A126&amp;" — "&amp;$C126&amp;" "&amp;$B126)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="H127">
+        <f>IF($A127="","",$A127&amp;" — "&amp;$C127&amp;" "&amp;$B127)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="H128">
+        <f>IF($A128="","",$A128&amp;" — "&amp;$C128&amp;" "&amp;$B128)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="H129">
+        <f>IF($A129="","",$A129&amp;" — "&amp;$C129&amp;" "&amp;$B129)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="H130">
+        <f>IF($A130="","",$A130&amp;" — "&amp;$C130&amp;" "&amp;$B130)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="H131">
+        <f>IF($A131="","",$A131&amp;" — "&amp;$C131&amp;" "&amp;$B131)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="H132">
+        <f>IF($A132="","",$A132&amp;" — "&amp;$C132&amp;" "&amp;$B132)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="H133">
+        <f>IF($A133="","",$A133&amp;" — "&amp;$C133&amp;" "&amp;$B133)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="H134">
+        <f>IF($A134="","",$A134&amp;" — "&amp;$C134&amp;" "&amp;$B134)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="H135">
+        <f>IF($A135="","",$A135&amp;" — "&amp;$C135&amp;" "&amp;$B135)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="H136">
+        <f>IF($A136="","",$A136&amp;" — "&amp;$C136&amp;" "&amp;$B136)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="H137">
+        <f>IF($A137="","",$A137&amp;" — "&amp;$C137&amp;" "&amp;$B137)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="H138">
+        <f>IF($A138="","",$A138&amp;" — "&amp;$C138&amp;" "&amp;$B138)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="H139">
+        <f>IF($A139="","",$A139&amp;" — "&amp;$C139&amp;" "&amp;$B139)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="H140">
+        <f>IF($A140="","",$A140&amp;" — "&amp;$C140&amp;" "&amp;$B140)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="H141">
+        <f>IF($A141="","",$A141&amp;" — "&amp;$C141&amp;" "&amp;$B141)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="H142">
+        <f>IF($A142="","",$A142&amp;" — "&amp;$C142&amp;" "&amp;$B142)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="H143">
+        <f>IF($A143="","",$A143&amp;" — "&amp;$C143&amp;" "&amp;$B143)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="H144">
+        <f>IF($A144="","",$A144&amp;" — "&amp;$C144&amp;" "&amp;$B144)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="H145">
+        <f>IF($A145="","",$A145&amp;" — "&amp;$C145&amp;" "&amp;$B145)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="H146">
+        <f>IF($A146="","",$A146&amp;" — "&amp;$C146&amp;" "&amp;$B146)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="H147">
+        <f>IF($A147="","",$A147&amp;" — "&amp;$C147&amp;" "&amp;$B147)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="H148">
+        <f>IF($A148="","",$A148&amp;" — "&amp;$C148&amp;" "&amp;$B148)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149">
+      <c r="H149">
+        <f>IF($A149="","",$A149&amp;" — "&amp;$C149&amp;" "&amp;$B149)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150">
+      <c r="H150">
+        <f>IF($A150="","",$A150&amp;" — "&amp;$C150&amp;" "&amp;$B150)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151">
+      <c r="H151">
+        <f>IF($A151="","",$A151&amp;" — "&amp;$C151&amp;" "&amp;$B151)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="152">
+      <c r="H152">
+        <f>IF($A152="","",$A152&amp;" — "&amp;$C152&amp;" "&amp;$B152)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="153">
+      <c r="H153">
+        <f>IF($A153="","",$A153&amp;" — "&amp;$C153&amp;" "&amp;$B153)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="154">
+      <c r="H154">
+        <f>IF($A154="","",$A154&amp;" — "&amp;$C154&amp;" "&amp;$B154)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="155">
+      <c r="H155">
+        <f>IF($A155="","",$A155&amp;" — "&amp;$C155&amp;" "&amp;$B155)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156">
+      <c r="H156">
+        <f>IF($A156="","",$A156&amp;" — "&amp;$C156&amp;" "&amp;$B156)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157">
+      <c r="H157">
+        <f>IF($A157="","",$A157&amp;" — "&amp;$C157&amp;" "&amp;$B157)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158">
+      <c r="H158">
+        <f>IF($A158="","",$A158&amp;" — "&amp;$C158&amp;" "&amp;$B158)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159">
+      <c r="H159">
+        <f>IF($A159="","",$A159&amp;" — "&amp;$C159&amp;" "&amp;$B159)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="160">
+      <c r="H160">
+        <f>IF($A160="","",$A160&amp;" — "&amp;$C160&amp;" "&amp;$B160)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="161">
+      <c r="H161">
+        <f>IF($A161="","",$A161&amp;" — "&amp;$C161&amp;" "&amp;$B161)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="162">
+      <c r="H162">
+        <f>IF($A162="","",$A162&amp;" — "&amp;$C162&amp;" "&amp;$B162)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="163">
+      <c r="H163">
+        <f>IF($A163="","",$A163&amp;" — "&amp;$C163&amp;" "&amp;$B163)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164">
+      <c r="H164">
+        <f>IF($A164="","",$A164&amp;" — "&amp;$C164&amp;" "&amp;$B164)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165">
+      <c r="H165">
+        <f>IF($A165="","",$A165&amp;" — "&amp;$C165&amp;" "&amp;$B165)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166">
+      <c r="H166">
+        <f>IF($A166="","",$A166&amp;" — "&amp;$C166&amp;" "&amp;$B166)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167">
+      <c r="H167">
+        <f>IF($A167="","",$A167&amp;" — "&amp;$C167&amp;" "&amp;$B167)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="168">
+      <c r="H168">
+        <f>IF($A168="","",$A168&amp;" — "&amp;$C168&amp;" "&amp;$B168)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169">
+      <c r="H169">
+        <f>IF($A169="","",$A169&amp;" — "&amp;$C169&amp;" "&amp;$B169)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="170">
+      <c r="H170">
+        <f>IF($A170="","",$A170&amp;" — "&amp;$C170&amp;" "&amp;$B170)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="171">
+      <c r="H171">
+        <f>IF($A171="","",$A171&amp;" — "&amp;$C171&amp;" "&amp;$B171)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="172">
+      <c r="H172">
+        <f>IF($A172="","",$A172&amp;" — "&amp;$C172&amp;" "&amp;$B172)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="173">
+      <c r="H173">
+        <f>IF($A173="","",$A173&amp;" — "&amp;$C173&amp;" "&amp;$B173)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="174">
+      <c r="H174">
+        <f>IF($A174="","",$A174&amp;" — "&amp;$C174&amp;" "&amp;$B174)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175">
+      <c r="H175">
+        <f>IF($A175="","",$A175&amp;" — "&amp;$C175&amp;" "&amp;$B175)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="176">
+      <c r="H176">
+        <f>IF($A176="","",$A176&amp;" — "&amp;$C176&amp;" "&amp;$B176)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="177">
+      <c r="H177">
+        <f>IF($A177="","",$A177&amp;" — "&amp;$C177&amp;" "&amp;$B177)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="178">
+      <c r="H178">
+        <f>IF($A178="","",$A178&amp;" — "&amp;$C178&amp;" "&amp;$B178)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="179">
+      <c r="H179">
+        <f>IF($A179="","",$A179&amp;" — "&amp;$C179&amp;" "&amp;$B179)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="180">
+      <c r="H180">
+        <f>IF($A180="","",$A180&amp;" — "&amp;$C180&amp;" "&amp;$B180)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="181">
+      <c r="H181">
+        <f>IF($A181="","",$A181&amp;" — "&amp;$C181&amp;" "&amp;$B181)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="182">
+      <c r="H182">
+        <f>IF($A182="","",$A182&amp;" — "&amp;$C182&amp;" "&amp;$B182)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="183">
+      <c r="H183">
+        <f>IF($A183="","",$A183&amp;" — "&amp;$C183&amp;" "&amp;$B183)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="184">
+      <c r="H184">
+        <f>IF($A184="","",$A184&amp;" — "&amp;$C184&amp;" "&amp;$B184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="185">
+      <c r="H185">
+        <f>IF($A185="","",$A185&amp;" — "&amp;$C185&amp;" "&amp;$B185)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="186">
+      <c r="H186">
+        <f>IF($A186="","",$A186&amp;" — "&amp;$C186&amp;" "&amp;$B186)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="187">
+      <c r="H187">
+        <f>IF($A187="","",$A187&amp;" — "&amp;$C187&amp;" "&amp;$B187)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="188">
+      <c r="H188">
+        <f>IF($A188="","",$A188&amp;" — "&amp;$C188&amp;" "&amp;$B188)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="189">
+      <c r="H189">
+        <f>IF($A189="","",$A189&amp;" — "&amp;$C189&amp;" "&amp;$B189)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="190">
+      <c r="H190">
+        <f>IF($A190="","",$A190&amp;" — "&amp;$C190&amp;" "&amp;$B190)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="191">
+      <c r="H191">
+        <f>IF($A191="","",$A191&amp;" — "&amp;$C191&amp;" "&amp;$B191)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="192">
+      <c r="H192">
+        <f>IF($A192="","",$A192&amp;" — "&amp;$C192&amp;" "&amp;$B192)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="193">
+      <c r="H193">
+        <f>IF($A193="","",$A193&amp;" — "&amp;$C193&amp;" "&amp;$B193)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="194">
+      <c r="H194">
+        <f>IF($A194="","",$A194&amp;" — "&amp;$C194&amp;" "&amp;$B194)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="195">
+      <c r="H195">
+        <f>IF($A195="","",$A195&amp;" — "&amp;$C195&amp;" "&amp;$B195)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="196">
+      <c r="H196">
+        <f>IF($A196="","",$A196&amp;" — "&amp;$C196&amp;" "&amp;$B196)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="197">
+      <c r="H197">
+        <f>IF($A197="","",$A197&amp;" — "&amp;$C197&amp;" "&amp;$B197)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="198">
+      <c r="H198">
+        <f>IF($A198="","",$A198&amp;" — "&amp;$C198&amp;" "&amp;$B198)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="199">
+      <c r="H199">
+        <f>IF($A199="","",$A199&amp;" — "&amp;$C199&amp;" "&amp;$B199)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="200">
+      <c r="H200">
+        <f>IF($A200="","",$A200&amp;" — "&amp;$C200&amp;" "&amp;$B200)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="201">
+      <c r="H201">
+        <f>IF($A201="","",$A201&amp;" — "&amp;$C201&amp;" "&amp;$B201)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="202">
+      <c r="H202">
+        <f>IF($A202="","",$A202&amp;" — "&amp;$C202&amp;" "&amp;$B202)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="203">
+      <c r="H203">
+        <f>IF($A203="","",$A203&amp;" — "&amp;$C203&amp;" "&amp;$B203)</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/canevas/canevas-vierge.xlsx
+++ b/src/main/resources/canevas/canevas-vierge.xlsx
@@ -922,18 +922,12 @@
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <dataValidations count="4">
-    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>Referentiels!$A$4:$A$203</formula1>
-    </dataValidation>
+  <dataValidations count="2">
     <dataValidation sqref="B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>Referentiels!$E$4:$E$13</formula1>
-    </dataValidation>
-    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>Referentiels!$C$4:$C$203</formula1>
+      <formula1>Referentiels!$C$4:$C$13</formula1>
     </dataValidation>
     <dataValidation sqref="B11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>Referentiels!$G$4:$G$203</formula1>
+      <formula1>Referentiels!$A$4:$A$203</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1965,7 +1959,7 @@
       <formula1>'Agents TPR'!$H$2:$H$203</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>Referentiels!$G$4:$G$203</formula1>
+      <formula1>Referentiels!$A$4:$A$203</formula1>
     </dataValidation>
     <dataValidation sqref="H2:H300 I2:I300 J2:J300 K2:K300 L2:L300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Oui,Non"</formula1>
@@ -4329,15 +4323,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:H210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="4" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4357,100 +4351,270 @@
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>Agents de poste (matricule — nom)</t>
+          <t>Membres de la mission (matricule — prénom nom)</t>
         </is>
       </c>
       <c r="C3" s="13" t="inlineStr">
         <is>
-          <t>Agents informaticiens (matricule — nom)</t>
-        </is>
-      </c>
-      <c r="E3" s="13" t="inlineStr">
-        <is>
           <t>Catégories de câble</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
-        <is>
-          <t>Membres de la mission (matricule — nom)</t>
-        </is>
-      </c>
+      <c r="E3" s="13" t="n"/>
+      <c r="G3" s="13" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="14" t="inlineStr">
         <is>
-          <t>AG001 — DIOP Awa</t>
+          <t>IN001 — Cheikh SOW</t>
         </is>
       </c>
       <c r="C4" s="14" t="inlineStr">
         <is>
-          <t>IN001 — SOW Cheikh</t>
-        </is>
-      </c>
-      <c r="E4" s="14" t="inlineStr">
-        <is>
           <t>Cat5e</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>IN001 — SOW Cheikh</t>
-        </is>
-      </c>
+      <c r="E4" s="14" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>AG002 — NDIAYE Modou</t>
+          <t>IN002 — Fatou BA</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>IN002 — BA Fatou</t>
-        </is>
-      </c>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
           <t>Cat6</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>IN002 — BA Fatou</t>
-        </is>
-      </c>
+      <c r="E5" s="14" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
-        <is>
-          <t>AG003 — FALL Aïssatou</t>
-        </is>
-      </c>
+      <c r="A6" s="14" t="n"/>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>IN003 — SECK Ousmane</t>
-        </is>
-      </c>
-      <c r="E6" s="14" t="inlineStr">
-        <is>
           <t>Cat6a</t>
         </is>
       </c>
+      <c r="E6" s="14" t="n"/>
     </row>
     <row r="7">
-      <c r="E7" s="14" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Cat7</t>
         </is>
       </c>
+      <c r="E7" s="14" t="n"/>
     </row>
     <row r="8">
-      <c r="E8" s="14" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Autre</t>
         </is>
       </c>
-    </row>
+      <c r="E8" s="14" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198"/>
+    <row r="199"/>
+    <row r="200"/>
+    <row r="201"/>
+    <row r="202"/>
+    <row r="203"/>
+    <row r="204"/>
+    <row r="205"/>
+    <row r="206"/>
+    <row r="207"/>
+    <row r="208"/>
+    <row r="209"/>
+    <row r="210"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>

--- a/src/main/resources/canevas/canevas-vierge.xlsx
+++ b/src/main/resources/canevas/canevas-vierge.xlsx
@@ -572,6 +572,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
@@ -586,6 +587,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="17" t="inlineStr">
         <is>
@@ -635,6 +637,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="17" t="inlineStr">
         <is>
@@ -670,6 +673,7 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="17" t="inlineStr">
         <is>
@@ -712,6 +716,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="17" t="inlineStr">
         <is>
@@ -766,6 +771,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
@@ -4323,7 +4329,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H210"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4342,11 +4348,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
-        <is>
-          <t>Exemples — en production, l'application remplit ces listes automatiquement pour le poste concerné.</t>
-        </is>
-      </c>
+      <c r="A2" s="12" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
@@ -4413,208 +4415,6 @@
       </c>
       <c r="E8" s="14" t="n"/>
     </row>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="207"/>
-    <row r="208"/>
-    <row r="209"/>
-    <row r="210"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>

--- a/src/main/resources/canevas/canevas-vierge.xlsx
+++ b/src/main/resources/canevas/canevas-vierge.xlsx
@@ -572,7 +572,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
@@ -587,7 +586,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="17" t="inlineStr">
         <is>
@@ -637,7 +635,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="17" t="inlineStr">
         <is>
@@ -673,7 +670,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="17" t="inlineStr">
         <is>
@@ -716,7 +712,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28">
       <c r="A28" s="17" t="inlineStr">
         <is>
@@ -771,7 +766,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
@@ -3086,9 +3080,10 @@
           <t>Caissier</t>
         </is>
       </c>
-      <c r="H2">
-        <f>IF($A2="","",$A2&amp;" — "&amp;$C2&amp;" "&amp;$B2)</f>
-        <v/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>AG001 — Awa DIOP</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -3112,9 +3107,10 @@
           <t>Comptable</t>
         </is>
       </c>
-      <c r="H3">
-        <f>IF($A3="","",$A3&amp;" — "&amp;$C3&amp;" "&amp;$B3)</f>
-        <v/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>AG002 — Modou NDIAYE</t>
+        </is>
       </c>
     </row>
     <row r="4">

--- a/src/main/resources/canevas/canevas-vierge.xlsx
+++ b/src/main/resources/canevas/canevas-vierge.xlsx
@@ -176,6 +176,19 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="009C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+          <bgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -766,6 +779,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
@@ -922,6 +936,46 @@
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
+  <conditionalFormatting sqref="B3">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
+      <formula>ISBLANK(B3)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B4">
+    <cfRule type="expression" priority="2" dxfId="0" stopIfTrue="0">
+      <formula>ISBLANK(B4)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="expression" priority="3" dxfId="0" stopIfTrue="0">
+      <formula>ISBLANK(B6)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7">
+    <cfRule type="expression" priority="4" dxfId="0" stopIfTrue="0">
+      <formula>ISBLANK(B7)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B8">
+    <cfRule type="expression" priority="5" dxfId="0" stopIfTrue="0">
+      <formula>ISBLANK(B8)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B9">
+    <cfRule type="expression" priority="6" dxfId="0" stopIfTrue="0">
+      <formula>ISBLANK(B9)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B10">
+    <cfRule type="expression" priority="7" dxfId="0" stopIfTrue="0">
+      <formula>ISBLANK(B10)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11">
+    <cfRule type="expression" priority="8" dxfId="0" stopIfTrue="0">
+      <formula>ISBLANK(B11)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation sqref="B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Referentiels!$C$4:$C$13</formula1>
@@ -1304,6 +1358,21 @@
       <c r="F41" s="11" t="n"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A2:A100">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
+      <formula>AND(ISBLANK(A2),COUNTA($A2:$F2)&gt;0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:B100">
+    <cfRule type="expression" priority="2" dxfId="0" stopIfTrue="0">
+      <formula>AND(ISBLANK(B2),COUNTA($A2:$F2)&gt;0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C100">
+    <cfRule type="expression" priority="3" dxfId="0" stopIfTrue="0">
+      <formula>AND(ISBLANK(C2),COUNTA($A2:$F2)&gt;0)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1954,6 +2023,26 @@
       <c r="L41" s="11" t="n"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:B300">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
+      <formula>AND(ISBLANK(B2),COUNTA($A2:$L2)&gt;0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D300">
+    <cfRule type="expression" priority="2" dxfId="0" stopIfTrue="0">
+      <formula>AND(ISBLANK(D2),COUNTA($A2:$L2)&gt;0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F300">
+    <cfRule type="expression" priority="3" dxfId="0" stopIfTrue="0">
+      <formula>AND(ISBLANK(F2),COUNTA($A2:$L2)&gt;0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G300">
+    <cfRule type="expression" priority="4" dxfId="0" stopIfTrue="0">
+      <formula>AND(ISBLANK(G2),COUNTA($A2:$L2)&gt;0)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation sqref="F2:F300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Agents TPR'!$H$2:$H$203</formula1>
@@ -2339,6 +2428,16 @@
       <c r="F41" s="11" t="n"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:B300">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
+      <formula>AND(ISBLANK(B2),COUNTA($A2:$F2)&gt;0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D300">
+    <cfRule type="expression" priority="2" dxfId="0" stopIfTrue="0">
+      <formula>AND(ISBLANK(D2),COUNTA($A2:$F2)&gt;0)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2713,6 +2812,21 @@
       <c r="F41" s="11" t="n"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:B300">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
+      <formula>AND(ISBLANK(B2),COUNTA($A2:$F2)&gt;0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C300">
+    <cfRule type="expression" priority="2" dxfId="0" stopIfTrue="0">
+      <formula>AND(ISBLANK(C2),COUNTA($A2:$F2)&gt;0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E300">
+    <cfRule type="expression" priority="3" dxfId="0" stopIfTrue="0">
+      <formula>AND(ISBLANK(E2),COUNTA($A2:$F2)&gt;0)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="B2:B300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Switch,Access point"</formula1>
@@ -3000,6 +3114,11 @@
       <c r="D41" s="11" t="n"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:B300">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
+      <formula>AND(ISBLANK(B2),COUNTA($A2:$D2)&gt;0)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4314,6 +4433,21 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A2:A203">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
+      <formula>AND(ISBLANK(A2),COUNTA($A2:$F2)&gt;0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:B203">
+    <cfRule type="expression" priority="2" dxfId="0" stopIfTrue="0">
+      <formula>AND(ISBLANK(B2),COUNTA($A2:$F2)&gt;0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C203">
+    <cfRule type="expression" priority="3" dxfId="0" stopIfTrue="0">
+      <formula>AND(ISBLANK(C2),COUNTA($A2:$F2)&gt;0)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>

--- a/src/main/resources/canevas/canevas-vierge.xlsx
+++ b/src/main/resources/canevas/canevas-vierge.xlsx
@@ -17,7 +17,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agents TPR" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Referentiels" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="ListeAttributaires">OFFSET('Agents TPR'!$H$2,0,0,MAX(1,COUNTA('Agents TPR'!$A$2:$A$203)),1)</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -183,7 +185,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="009C0006"/>
@@ -216,6 +218,17 @@
         <patternFill patternType="solid">
           <fgColor rgb="00FFC7CE"/>
           <bgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="009C6500"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFEB9C"/>
+          <bgColor rgb="00FFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4322,6 +4335,9 @@
     <cfRule type="expression" priority="2" dxfId="0" stopIfTrue="0">
       <formula>AND(ISBLANK(D2),COUNTA($A2:$L2)&gt;0)</formula>
     </cfRule>
+    <cfRule type="expression" priority="5" dxfId="3" stopIfTrue="0">
+      <formula>AND($D2&lt;&gt;"",OR(LEN($D2)&lt;&gt;17,LEN($D2)-LEN(SUBSTITUTE($D2,":",""))&lt;&gt;5))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F300">
     <cfRule type="expression" priority="3" dxfId="0" stopIfTrue="0">
@@ -4333,9 +4349,14 @@
       <formula>AND(ISBLANK(G2),COUNTA($A2:$L2)&gt;0)</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E300">
+    <cfRule type="expression" priority="6" dxfId="3" stopIfTrue="0">
+      <formula>AND($E2&lt;&gt;"",OR(LEN($E2)&lt;&gt;17,LEN($E2)-LEN(SUBSTITUTE($E2,":",""))&lt;&gt;5))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation sqref="F2:F300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Agents TPR'!$H$2:$H$203</formula1>
+      <formula1>ListeAttributaires</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Referentiels!$A$4:$A$203</formula1>
@@ -6447,6 +6468,14 @@
     <cfRule type="expression" priority="2" dxfId="0" stopIfTrue="0">
       <formula>AND(ISBLANK(D2),COUNTA($A2:$F2)&gt;0)</formula>
     </cfRule>
+    <cfRule type="expression" priority="3" dxfId="3" stopIfTrue="0">
+      <formula>AND($D2&lt;&gt;"",OR(LEN($D2)&lt;&gt;17,LEN($D2)-LEN(SUBSTITUTE($D2,":",""))&lt;&gt;5))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E300">
+    <cfRule type="expression" priority="4" dxfId="3" stopIfTrue="0">
+      <formula>AND($E2&lt;&gt;"",OR(LEN($E2)&lt;&gt;17,LEN($E2)-LEN(SUBSTITUTE($E2,":",""))&lt;&gt;5))</formula>
+    </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8555,6 +8584,9 @@
   <conditionalFormatting sqref="E2:E300">
     <cfRule type="expression" priority="3" dxfId="0" stopIfTrue="0">
       <formula>AND(ISBLANK(E2),COUNTA($A2:$F2)&gt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="3" stopIfTrue="0">
+      <formula>AND($E2&lt;&gt;"",OR(LEN($E2)&lt;&gt;17,LEN($E2)-LEN(SUBSTITUTE($E2,":",""))&lt;&gt;5))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">

--- a/src/main/resources/canevas/canevas-vierge.xlsx
+++ b/src/main/resources/canevas/canevas-vierge.xlsx
@@ -4354,7 +4354,7 @@
       <formula>AND($E2&lt;&gt;"",OR(LEN($E2)&lt;&gt;17,LEN($E2)-LEN(SUBSTITUTE($E2,":",""))&lt;&gt;5))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="3">
+  <dataValidations count="5">
     <dataValidation sqref="F2:F300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>ListeAttributaires</formula1>
     </dataValidation>
@@ -4363,6 +4363,12 @@
     </dataValidation>
     <dataValidation sqref="H2:H300 I2:I300 J2:J300 K2:K300 L2:L300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Oui,Non"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D300" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Adresse MAC invalide" error="Format attendu : AA:BB:CC:DD:EE:FF — 6 paires hexadécimales (0-9, A-F) séparées par « : »." promptTitle="Format adresse MAC" prompt="6 paires hexadécimales séparées par « : », ex. 00:1A:2B:3C:4D:5E" type="custom" errorStyle="stop">
+      <formula1>AND(LEN(D2)=17,LEN(SUBSTITUTE(D2,":",""))=12,MID(D2,3,1)=":",MID(D2,6,1)=":",MID(D2,9,1)=":",MID(D2,12,1)=":",MID(D2,15,1)=":",ISNUMBER(HEX2DEC(LEFT(SUBSTITUTE(D2,":",""),6))),ISNUMBER(HEX2DEC(MID(SUBSTITUTE(D2,":",""),7,6))))</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E300" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Adresse MAC invalide" error="Format attendu : AA:BB:CC:DD:EE:FF — 6 paires hexadécimales (0-9, A-F) séparées par « : »." promptTitle="Format adresse MAC" prompt="6 paires hexadécimales séparées par « : », ex. 00:1A:2B:3C:4D:5E" type="custom" errorStyle="stop">
+      <formula1>AND(LEN(E2)=17,LEN(SUBSTITUTE(E2,":",""))=12,MID(E2,3,1)=":",MID(E2,6,1)=":",MID(E2,9,1)=":",MID(E2,12,1)=":",MID(E2,15,1)=":",ISNUMBER(HEX2DEC(LEFT(SUBSTITUTE(E2,":",""),6))),ISNUMBER(HEX2DEC(MID(SUBSTITUTE(E2,":",""),7,6))))</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6477,6 +6483,14 @@
       <formula>AND($E2&lt;&gt;"",OR(LEN($E2)&lt;&gt;17,LEN($E2)-LEN(SUBSTITUTE($E2,":",""))&lt;&gt;5))</formula>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation sqref="D2:D300" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Adresse MAC invalide" error="Format attendu : AA:BB:CC:DD:EE:FF — 6 paires hexadécimales (0-9, A-F) séparées par « : »." promptTitle="Format adresse MAC" prompt="6 paires hexadécimales séparées par « : », ex. 00:1A:2B:3C:4D:5E" type="custom" errorStyle="stop">
+      <formula1>AND(LEN(D2)=17,LEN(SUBSTITUTE(D2,":",""))=12,MID(D2,3,1)=":",MID(D2,6,1)=":",MID(D2,9,1)=":",MID(D2,12,1)=":",MID(D2,15,1)=":",ISNUMBER(HEX2DEC(LEFT(SUBSTITUTE(D2,":",""),6))),ISNUMBER(HEX2DEC(MID(SUBSTITUTE(D2,":",""),7,6))))</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E300" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Adresse MAC invalide" error="Format attendu : AA:BB:CC:DD:EE:FF — 6 paires hexadécimales (0-9, A-F) séparées par « : »." promptTitle="Format adresse MAC" prompt="6 paires hexadécimales séparées par « : », ex. 00:1A:2B:3C:4D:5E" type="custom" errorStyle="stop">
+      <formula1>AND(LEN(E2)=17,LEN(SUBSTITUTE(E2,":",""))=12,MID(E2,3,1)=":",MID(E2,6,1)=":",MID(E2,9,1)=":",MID(E2,12,1)=":",MID(E2,15,1)=":",ISNUMBER(HEX2DEC(LEFT(SUBSTITUTE(E2,":",""),6))),ISNUMBER(HEX2DEC(MID(SUBSTITUTE(E2,":",""),7,6))))</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8589,9 +8603,12 @@
       <formula>AND($E2&lt;&gt;"",OR(LEN($E2)&lt;&gt;17,LEN($E2)-LEN(SUBSTITUTE($E2,":",""))&lt;&gt;5))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="B2:B300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Switch,Access point"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E300" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Adresse MAC invalide" error="Format attendu : AA:BB:CC:DD:EE:FF — 6 paires hexadécimales (0-9, A-F) séparées par « : »." promptTitle="Format adresse MAC" prompt="6 paires hexadécimales séparées par « : », ex. 00:1A:2B:3C:4D:5E" type="custom" errorStyle="stop">
+      <formula1>AND(LEN(E2)=17,LEN(SUBSTITUTE(E2,":",""))=12,MID(E2,3,1)=":",MID(E2,6,1)=":",MID(E2,9,1)=":",MID(E2,12,1)=":",MID(E2,15,1)=":",ISNUMBER(HEX2DEC(LEFT(SUBSTITUTE(E2,":",""),6))),ISNUMBER(HEX2DEC(MID(SUBSTITUTE(E2,":",""),7,6))))</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/src/main/resources/canevas/canevas-vierge.xlsx
+++ b/src/main/resources/canevas/canevas-vierge.xlsx
@@ -10684,30 +10684,9 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>AG001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>DIOP</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Awa</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Caissier</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>AG001 — Awa DIOP</t>
-        </is>
+      <c r="H2">
+        <f>IF($A2="","",$A2&amp;" — "&amp;$C2&amp;" "&amp;$B2)</f>
+        <v/>
       </c>
       <c r="J2">
         <f>IF(COUNTA($A2:$F2)=0,0,IF(OR($A2="",$B2="",$C2=""),1,0))</f>
@@ -10715,30 +10694,9 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>AG002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>NDIAYE</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Modou</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Comptable</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>AG002 — Modou NDIAYE</t>
-        </is>
+      <c r="H3">
+        <f>IF($A3="","",$A3&amp;" — "&amp;$C3&amp;" "&amp;$B3)</f>
+        <v/>
       </c>
       <c r="J3">
         <f>IF(COUNTA($A3:$F3)=0,0,IF(OR($A3="",$B3="",$C3=""),1,0))</f>
@@ -12808,11 +12766,7 @@
       <c r="G3" s="13" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
-        <is>
-          <t>IN001 — Cheikh SOW</t>
-        </is>
-      </c>
+      <c r="A4" s="14" t="n"/>
       <c r="C4" s="14" t="inlineStr">
         <is>
           <t>Cat5e</t>
@@ -12821,11 +12775,7 @@
       <c r="E4" s="14" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>IN002 — Fatou BA</t>
-        </is>
-      </c>
+      <c r="A5" s="14" t="n"/>
       <c r="C5" s="14" t="inlineStr">
         <is>
           <t>Cat6</t>

--- a/src/main/resources/canevas/canevas-vierge.xlsx
+++ b/src/main/resources/canevas/canevas-vierge.xlsx
@@ -185,7 +185,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="7">
     <dxf>
       <font>
         <color rgb="009C0006"/>
@@ -229,6 +229,39 @@
         <patternFill patternType="solid">
           <fgColor rgb="00FFEB9C"/>
           <bgColor rgb="00FFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C6500"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -982,7 +1015,7 @@
         </is>
       </c>
       <c r="B16" s="21">
-        <f>IF(AND($B$3&lt;&gt;"",$B$4&lt;&gt;"",$B$6&lt;&gt;"",$B$7&lt;&gt;"",$B$8&lt;&gt;"",$B$9&lt;&gt;"",$B$10&lt;&gt;"",$B$11&lt;&gt;"",SUM('2-Membres mission'!$H$2:$H$100)=0,SUM('3-Ordinateurs'!$N$2:$N$300)=0,SUM('4-Imprimantes'!$H$2:$H$300)=0,SUM('5-Switchs et AP'!$H$2:$H$300)=0,SUM('6-Scanners chèque'!$F$2:$F$300)=0,SUM('Agents TPR'!$J$2:$J$203)=0),"CANEVAS CONFORME","CANEVAS INCOMPLET - champ(s) obligatoire(s) manquant(s)")</f>
+        <f>IF(AND($B$3&lt;&gt;"",$B$4&lt;&gt;"",$B$6&lt;&gt;"",$B$7&lt;&gt;"",$B$8&lt;&gt;"",$B$9&lt;&gt;"",$B$10&lt;&gt;"",$B$11&lt;&gt;"",SUM('2-Membres mission'!$H$2:$H$100)=0,SUM('3-Ordinateurs'!$N$2:$N$300)=0,SUM('4-Imprimantes'!$H$2:$H$300)=0,SUM('5-Switchs et AP'!$H$2:$H$300)=0,SUM('6-Scanners chèque'!$F$2:$F$300)=0,SUM('Agents TPR'!$J$2:$J$203)=0),IF(AND(SUM('3-Ordinateurs'!$O$2:$O$300)=0,SUM('4-Imprimantes'!$I$2:$I$300)=0,SUM('5-Switchs et AP'!$I$2:$I$300)=0),"CANEVAS CONFORME","CANEVAS NON CONFORME - un ou plusieurs champs ont un format invalide (ex. MAC)"),"CANEVAS INCOMPLET - un ou plusieurs champs obligatoires manquent")</f>
         <v/>
       </c>
     </row>
@@ -1032,11 +1065,14 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16">
-    <cfRule type="expression" priority="9" dxfId="1">
-      <formula>ISNUMBER(SEARCH("CONFORME",$B$16))</formula>
+    <cfRule type="expression" priority="9" dxfId="4">
+      <formula>AND(ISNUMBER(SEARCH("CONFORME",$B$16)),ISERROR(SEARCH("NON CONFORME",$B$16)))</formula>
     </cfRule>
-    <cfRule type="expression" priority="10" dxfId="2">
+    <cfRule type="expression" priority="10" dxfId="5">
       <formula>ISNUMBER(SEARCH("INCOMPLET",$B$16))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="11" dxfId="6">
+      <formula>ISNUMBER(SEARCH("NON CONFORME",$B$16))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
@@ -1966,7 +2002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N300"/>
+  <dimension ref="A1:O300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1982,6 +2018,7 @@
     <col width="8" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col hidden="1" width="13" customWidth="1" min="14" max="14"/>
+    <col hidden="1" width="13" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2048,6 +2085,11 @@
       <c r="N1" t="inlineStr">
         <is>
           <t>ctrl</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>ctrlfmt</t>
         </is>
       </c>
     </row>
@@ -2068,6 +2110,10 @@
         <f>IF(COUNTA($A2:$L2)=0,0,IF(OR($B2="",$D2="",$F2="",$G2=""),1,0))</f>
         <v/>
       </c>
+      <c r="O2">
+        <f>IF(OR(AND($D2&lt;&gt;"",OR(LEN($D2)&lt;&gt;17,LEN($D2)-LEN(SUBSTITUTE($D2,":",""))&lt;&gt;5)),AND($E2&lt;&gt;"",OR(LEN($E2)&lt;&gt;17,LEN($E2)-LEN(SUBSTITUTE($E2,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n"/>
@@ -2086,6 +2132,10 @@
         <f>IF(COUNTA($A3:$L3)=0,0,IF(OR($B3="",$D3="",$F3="",$G3=""),1,0))</f>
         <v/>
       </c>
+      <c r="O3">
+        <f>IF(OR(AND($D3&lt;&gt;"",OR(LEN($D3)&lt;&gt;17,LEN($D3)-LEN(SUBSTITUTE($D3,":",""))&lt;&gt;5)),AND($E3&lt;&gt;"",OR(LEN($E3)&lt;&gt;17,LEN($E3)-LEN(SUBSTITUTE($E3,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n"/>
@@ -2104,6 +2154,10 @@
         <f>IF(COUNTA($A4:$L4)=0,0,IF(OR($B4="",$D4="",$F4="",$G4=""),1,0))</f>
         <v/>
       </c>
+      <c r="O4">
+        <f>IF(OR(AND($D4&lt;&gt;"",OR(LEN($D4)&lt;&gt;17,LEN($D4)-LEN(SUBSTITUTE($D4,":",""))&lt;&gt;5)),AND($E4&lt;&gt;"",OR(LEN($E4)&lt;&gt;17,LEN($E4)-LEN(SUBSTITUTE($E4,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n"/>
@@ -2122,6 +2176,10 @@
         <f>IF(COUNTA($A5:$L5)=0,0,IF(OR($B5="",$D5="",$F5="",$G5=""),1,0))</f>
         <v/>
       </c>
+      <c r="O5">
+        <f>IF(OR(AND($D5&lt;&gt;"",OR(LEN($D5)&lt;&gt;17,LEN($D5)-LEN(SUBSTITUTE($D5,":",""))&lt;&gt;5)),AND($E5&lt;&gt;"",OR(LEN($E5)&lt;&gt;17,LEN($E5)-LEN(SUBSTITUTE($E5,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n"/>
@@ -2140,6 +2198,10 @@
         <f>IF(COUNTA($A6:$L6)=0,0,IF(OR($B6="",$D6="",$F6="",$G6=""),1,0))</f>
         <v/>
       </c>
+      <c r="O6">
+        <f>IF(OR(AND($D6&lt;&gt;"",OR(LEN($D6)&lt;&gt;17,LEN($D6)-LEN(SUBSTITUTE($D6,":",""))&lt;&gt;5)),AND($E6&lt;&gt;"",OR(LEN($E6)&lt;&gt;17,LEN($E6)-LEN(SUBSTITUTE($E6,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n"/>
@@ -2158,6 +2220,10 @@
         <f>IF(COUNTA($A7:$L7)=0,0,IF(OR($B7="",$D7="",$F7="",$G7=""),1,0))</f>
         <v/>
       </c>
+      <c r="O7">
+        <f>IF(OR(AND($D7&lt;&gt;"",OR(LEN($D7)&lt;&gt;17,LEN($D7)-LEN(SUBSTITUTE($D7,":",""))&lt;&gt;5)),AND($E7&lt;&gt;"",OR(LEN($E7)&lt;&gt;17,LEN($E7)-LEN(SUBSTITUTE($E7,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="n"/>
@@ -2176,6 +2242,10 @@
         <f>IF(COUNTA($A8:$L8)=0,0,IF(OR($B8="",$D8="",$F8="",$G8=""),1,0))</f>
         <v/>
       </c>
+      <c r="O8">
+        <f>IF(OR(AND($D8&lt;&gt;"",OR(LEN($D8)&lt;&gt;17,LEN($D8)-LEN(SUBSTITUTE($D8,":",""))&lt;&gt;5)),AND($E8&lt;&gt;"",OR(LEN($E8)&lt;&gt;17,LEN($E8)-LEN(SUBSTITUTE($E8,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="n"/>
@@ -2194,6 +2264,10 @@
         <f>IF(COUNTA($A9:$L9)=0,0,IF(OR($B9="",$D9="",$F9="",$G9=""),1,0))</f>
         <v/>
       </c>
+      <c r="O9">
+        <f>IF(OR(AND($D9&lt;&gt;"",OR(LEN($D9)&lt;&gt;17,LEN($D9)-LEN(SUBSTITUTE($D9,":",""))&lt;&gt;5)),AND($E9&lt;&gt;"",OR(LEN($E9)&lt;&gt;17,LEN($E9)-LEN(SUBSTITUTE($E9,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="n"/>
@@ -2212,6 +2286,10 @@
         <f>IF(COUNTA($A10:$L10)=0,0,IF(OR($B10="",$D10="",$F10="",$G10=""),1,0))</f>
         <v/>
       </c>
+      <c r="O10">
+        <f>IF(OR(AND($D10&lt;&gt;"",OR(LEN($D10)&lt;&gt;17,LEN($D10)-LEN(SUBSTITUTE($D10,":",""))&lt;&gt;5)),AND($E10&lt;&gt;"",OR(LEN($E10)&lt;&gt;17,LEN($E10)-LEN(SUBSTITUTE($E10,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="n"/>
@@ -2230,6 +2308,10 @@
         <f>IF(COUNTA($A11:$L11)=0,0,IF(OR($B11="",$D11="",$F11="",$G11=""),1,0))</f>
         <v/>
       </c>
+      <c r="O11">
+        <f>IF(OR(AND($D11&lt;&gt;"",OR(LEN($D11)&lt;&gt;17,LEN($D11)-LEN(SUBSTITUTE($D11,":",""))&lt;&gt;5)),AND($E11&lt;&gt;"",OR(LEN($E11)&lt;&gt;17,LEN($E11)-LEN(SUBSTITUTE($E11,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="n"/>
@@ -2248,6 +2330,10 @@
         <f>IF(COUNTA($A12:$L12)=0,0,IF(OR($B12="",$D12="",$F12="",$G12=""),1,0))</f>
         <v/>
       </c>
+      <c r="O12">
+        <f>IF(OR(AND($D12&lt;&gt;"",OR(LEN($D12)&lt;&gt;17,LEN($D12)-LEN(SUBSTITUTE($D12,":",""))&lt;&gt;5)),AND($E12&lt;&gt;"",OR(LEN($E12)&lt;&gt;17,LEN($E12)-LEN(SUBSTITUTE($E12,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="n"/>
@@ -2266,6 +2352,10 @@
         <f>IF(COUNTA($A13:$L13)=0,0,IF(OR($B13="",$D13="",$F13="",$G13=""),1,0))</f>
         <v/>
       </c>
+      <c r="O13">
+        <f>IF(OR(AND($D13&lt;&gt;"",OR(LEN($D13)&lt;&gt;17,LEN($D13)-LEN(SUBSTITUTE($D13,":",""))&lt;&gt;5)),AND($E13&lt;&gt;"",OR(LEN($E13)&lt;&gt;17,LEN($E13)-LEN(SUBSTITUTE($E13,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="n"/>
@@ -2284,6 +2374,10 @@
         <f>IF(COUNTA($A14:$L14)=0,0,IF(OR($B14="",$D14="",$F14="",$G14=""),1,0))</f>
         <v/>
       </c>
+      <c r="O14">
+        <f>IF(OR(AND($D14&lt;&gt;"",OR(LEN($D14)&lt;&gt;17,LEN($D14)-LEN(SUBSTITUTE($D14,":",""))&lt;&gt;5)),AND($E14&lt;&gt;"",OR(LEN($E14)&lt;&gt;17,LEN($E14)-LEN(SUBSTITUTE($E14,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="n"/>
@@ -2302,6 +2396,10 @@
         <f>IF(COUNTA($A15:$L15)=0,0,IF(OR($B15="",$D15="",$F15="",$G15=""),1,0))</f>
         <v/>
       </c>
+      <c r="O15">
+        <f>IF(OR(AND($D15&lt;&gt;"",OR(LEN($D15)&lt;&gt;17,LEN($D15)-LEN(SUBSTITUTE($D15,":",""))&lt;&gt;5)),AND($E15&lt;&gt;"",OR(LEN($E15)&lt;&gt;17,LEN($E15)-LEN(SUBSTITUTE($E15,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="n"/>
@@ -2320,6 +2418,10 @@
         <f>IF(COUNTA($A16:$L16)=0,0,IF(OR($B16="",$D16="",$F16="",$G16=""),1,0))</f>
         <v/>
       </c>
+      <c r="O16">
+        <f>IF(OR(AND($D16&lt;&gt;"",OR(LEN($D16)&lt;&gt;17,LEN($D16)-LEN(SUBSTITUTE($D16,":",""))&lt;&gt;5)),AND($E16&lt;&gt;"",OR(LEN($E16)&lt;&gt;17,LEN($E16)-LEN(SUBSTITUTE($E16,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="n"/>
@@ -2338,6 +2440,10 @@
         <f>IF(COUNTA($A17:$L17)=0,0,IF(OR($B17="",$D17="",$F17="",$G17=""),1,0))</f>
         <v/>
       </c>
+      <c r="O17">
+        <f>IF(OR(AND($D17&lt;&gt;"",OR(LEN($D17)&lt;&gt;17,LEN($D17)-LEN(SUBSTITUTE($D17,":",""))&lt;&gt;5)),AND($E17&lt;&gt;"",OR(LEN($E17)&lt;&gt;17,LEN($E17)-LEN(SUBSTITUTE($E17,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="n"/>
@@ -2356,6 +2462,10 @@
         <f>IF(COUNTA($A18:$L18)=0,0,IF(OR($B18="",$D18="",$F18="",$G18=""),1,0))</f>
         <v/>
       </c>
+      <c r="O18">
+        <f>IF(OR(AND($D18&lt;&gt;"",OR(LEN($D18)&lt;&gt;17,LEN($D18)-LEN(SUBSTITUTE($D18,":",""))&lt;&gt;5)),AND($E18&lt;&gt;"",OR(LEN($E18)&lt;&gt;17,LEN($E18)-LEN(SUBSTITUTE($E18,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="n"/>
@@ -2374,6 +2484,10 @@
         <f>IF(COUNTA($A19:$L19)=0,0,IF(OR($B19="",$D19="",$F19="",$G19=""),1,0))</f>
         <v/>
       </c>
+      <c r="O19">
+        <f>IF(OR(AND($D19&lt;&gt;"",OR(LEN($D19)&lt;&gt;17,LEN($D19)-LEN(SUBSTITUTE($D19,":",""))&lt;&gt;5)),AND($E19&lt;&gt;"",OR(LEN($E19)&lt;&gt;17,LEN($E19)-LEN(SUBSTITUTE($E19,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="n"/>
@@ -2392,6 +2506,10 @@
         <f>IF(COUNTA($A20:$L20)=0,0,IF(OR($B20="",$D20="",$F20="",$G20=""),1,0))</f>
         <v/>
       </c>
+      <c r="O20">
+        <f>IF(OR(AND($D20&lt;&gt;"",OR(LEN($D20)&lt;&gt;17,LEN($D20)-LEN(SUBSTITUTE($D20,":",""))&lt;&gt;5)),AND($E20&lt;&gt;"",OR(LEN($E20)&lt;&gt;17,LEN($E20)-LEN(SUBSTITUTE($E20,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="n"/>
@@ -2410,6 +2528,10 @@
         <f>IF(COUNTA($A21:$L21)=0,0,IF(OR($B21="",$D21="",$F21="",$G21=""),1,0))</f>
         <v/>
       </c>
+      <c r="O21">
+        <f>IF(OR(AND($D21&lt;&gt;"",OR(LEN($D21)&lt;&gt;17,LEN($D21)-LEN(SUBSTITUTE($D21,":",""))&lt;&gt;5)),AND($E21&lt;&gt;"",OR(LEN($E21)&lt;&gt;17,LEN($E21)-LEN(SUBSTITUTE($E21,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="n"/>
@@ -2428,6 +2550,10 @@
         <f>IF(COUNTA($A22:$L22)=0,0,IF(OR($B22="",$D22="",$F22="",$G22=""),1,0))</f>
         <v/>
       </c>
+      <c r="O22">
+        <f>IF(OR(AND($D22&lt;&gt;"",OR(LEN($D22)&lt;&gt;17,LEN($D22)-LEN(SUBSTITUTE($D22,":",""))&lt;&gt;5)),AND($E22&lt;&gt;"",OR(LEN($E22)&lt;&gt;17,LEN($E22)-LEN(SUBSTITUTE($E22,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="n"/>
@@ -2446,6 +2572,10 @@
         <f>IF(COUNTA($A23:$L23)=0,0,IF(OR($B23="",$D23="",$F23="",$G23=""),1,0))</f>
         <v/>
       </c>
+      <c r="O23">
+        <f>IF(OR(AND($D23&lt;&gt;"",OR(LEN($D23)&lt;&gt;17,LEN($D23)-LEN(SUBSTITUTE($D23,":",""))&lt;&gt;5)),AND($E23&lt;&gt;"",OR(LEN($E23)&lt;&gt;17,LEN($E23)-LEN(SUBSTITUTE($E23,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="n"/>
@@ -2464,6 +2594,10 @@
         <f>IF(COUNTA($A24:$L24)=0,0,IF(OR($B24="",$D24="",$F24="",$G24=""),1,0))</f>
         <v/>
       </c>
+      <c r="O24">
+        <f>IF(OR(AND($D24&lt;&gt;"",OR(LEN($D24)&lt;&gt;17,LEN($D24)-LEN(SUBSTITUTE($D24,":",""))&lt;&gt;5)),AND($E24&lt;&gt;"",OR(LEN($E24)&lt;&gt;17,LEN($E24)-LEN(SUBSTITUTE($E24,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="n"/>
@@ -2482,6 +2616,10 @@
         <f>IF(COUNTA($A25:$L25)=0,0,IF(OR($B25="",$D25="",$F25="",$G25=""),1,0))</f>
         <v/>
       </c>
+      <c r="O25">
+        <f>IF(OR(AND($D25&lt;&gt;"",OR(LEN($D25)&lt;&gt;17,LEN($D25)-LEN(SUBSTITUTE($D25,":",""))&lt;&gt;5)),AND($E25&lt;&gt;"",OR(LEN($E25)&lt;&gt;17,LEN($E25)-LEN(SUBSTITUTE($E25,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="n"/>
@@ -2500,6 +2638,10 @@
         <f>IF(COUNTA($A26:$L26)=0,0,IF(OR($B26="",$D26="",$F26="",$G26=""),1,0))</f>
         <v/>
       </c>
+      <c r="O26">
+        <f>IF(OR(AND($D26&lt;&gt;"",OR(LEN($D26)&lt;&gt;17,LEN($D26)-LEN(SUBSTITUTE($D26,":",""))&lt;&gt;5)),AND($E26&lt;&gt;"",OR(LEN($E26)&lt;&gt;17,LEN($E26)-LEN(SUBSTITUTE($E26,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="n"/>
@@ -2518,6 +2660,10 @@
         <f>IF(COUNTA($A27:$L27)=0,0,IF(OR($B27="",$D27="",$F27="",$G27=""),1,0))</f>
         <v/>
       </c>
+      <c r="O27">
+        <f>IF(OR(AND($D27&lt;&gt;"",OR(LEN($D27)&lt;&gt;17,LEN($D27)-LEN(SUBSTITUTE($D27,":",""))&lt;&gt;5)),AND($E27&lt;&gt;"",OR(LEN($E27)&lt;&gt;17,LEN($E27)-LEN(SUBSTITUTE($E27,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="n"/>
@@ -2536,6 +2682,10 @@
         <f>IF(COUNTA($A28:$L28)=0,0,IF(OR($B28="",$D28="",$F28="",$G28=""),1,0))</f>
         <v/>
       </c>
+      <c r="O28">
+        <f>IF(OR(AND($D28&lt;&gt;"",OR(LEN($D28)&lt;&gt;17,LEN($D28)-LEN(SUBSTITUTE($D28,":",""))&lt;&gt;5)),AND($E28&lt;&gt;"",OR(LEN($E28)&lt;&gt;17,LEN($E28)-LEN(SUBSTITUTE($E28,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="n"/>
@@ -2554,6 +2704,10 @@
         <f>IF(COUNTA($A29:$L29)=0,0,IF(OR($B29="",$D29="",$F29="",$G29=""),1,0))</f>
         <v/>
       </c>
+      <c r="O29">
+        <f>IF(OR(AND($D29&lt;&gt;"",OR(LEN($D29)&lt;&gt;17,LEN($D29)-LEN(SUBSTITUTE($D29,":",""))&lt;&gt;5)),AND($E29&lt;&gt;"",OR(LEN($E29)&lt;&gt;17,LEN($E29)-LEN(SUBSTITUTE($E29,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="n"/>
@@ -2572,6 +2726,10 @@
         <f>IF(COUNTA($A30:$L30)=0,0,IF(OR($B30="",$D30="",$F30="",$G30=""),1,0))</f>
         <v/>
       </c>
+      <c r="O30">
+        <f>IF(OR(AND($D30&lt;&gt;"",OR(LEN($D30)&lt;&gt;17,LEN($D30)-LEN(SUBSTITUTE($D30,":",""))&lt;&gt;5)),AND($E30&lt;&gt;"",OR(LEN($E30)&lt;&gt;17,LEN($E30)-LEN(SUBSTITUTE($E30,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="n"/>
@@ -2590,6 +2748,10 @@
         <f>IF(COUNTA($A31:$L31)=0,0,IF(OR($B31="",$D31="",$F31="",$G31=""),1,0))</f>
         <v/>
       </c>
+      <c r="O31">
+        <f>IF(OR(AND($D31&lt;&gt;"",OR(LEN($D31)&lt;&gt;17,LEN($D31)-LEN(SUBSTITUTE($D31,":",""))&lt;&gt;5)),AND($E31&lt;&gt;"",OR(LEN($E31)&lt;&gt;17,LEN($E31)-LEN(SUBSTITUTE($E31,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="n"/>
@@ -2608,6 +2770,10 @@
         <f>IF(COUNTA($A32:$L32)=0,0,IF(OR($B32="",$D32="",$F32="",$G32=""),1,0))</f>
         <v/>
       </c>
+      <c r="O32">
+        <f>IF(OR(AND($D32&lt;&gt;"",OR(LEN($D32)&lt;&gt;17,LEN($D32)-LEN(SUBSTITUTE($D32,":",""))&lt;&gt;5)),AND($E32&lt;&gt;"",OR(LEN($E32)&lt;&gt;17,LEN($E32)-LEN(SUBSTITUTE($E32,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="n"/>
@@ -2626,6 +2792,10 @@
         <f>IF(COUNTA($A33:$L33)=0,0,IF(OR($B33="",$D33="",$F33="",$G33=""),1,0))</f>
         <v/>
       </c>
+      <c r="O33">
+        <f>IF(OR(AND($D33&lt;&gt;"",OR(LEN($D33)&lt;&gt;17,LEN($D33)-LEN(SUBSTITUTE($D33,":",""))&lt;&gt;5)),AND($E33&lt;&gt;"",OR(LEN($E33)&lt;&gt;17,LEN($E33)-LEN(SUBSTITUTE($E33,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="n"/>
@@ -2644,6 +2814,10 @@
         <f>IF(COUNTA($A34:$L34)=0,0,IF(OR($B34="",$D34="",$F34="",$G34=""),1,0))</f>
         <v/>
       </c>
+      <c r="O34">
+        <f>IF(OR(AND($D34&lt;&gt;"",OR(LEN($D34)&lt;&gt;17,LEN($D34)-LEN(SUBSTITUTE($D34,":",""))&lt;&gt;5)),AND($E34&lt;&gt;"",OR(LEN($E34)&lt;&gt;17,LEN($E34)-LEN(SUBSTITUTE($E34,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="n"/>
@@ -2662,6 +2836,10 @@
         <f>IF(COUNTA($A35:$L35)=0,0,IF(OR($B35="",$D35="",$F35="",$G35=""),1,0))</f>
         <v/>
       </c>
+      <c r="O35">
+        <f>IF(OR(AND($D35&lt;&gt;"",OR(LEN($D35)&lt;&gt;17,LEN($D35)-LEN(SUBSTITUTE($D35,":",""))&lt;&gt;5)),AND($E35&lt;&gt;"",OR(LEN($E35)&lt;&gt;17,LEN($E35)-LEN(SUBSTITUTE($E35,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="11" t="n"/>
@@ -2680,6 +2858,10 @@
         <f>IF(COUNTA($A36:$L36)=0,0,IF(OR($B36="",$D36="",$F36="",$G36=""),1,0))</f>
         <v/>
       </c>
+      <c r="O36">
+        <f>IF(OR(AND($D36&lt;&gt;"",OR(LEN($D36)&lt;&gt;17,LEN($D36)-LEN(SUBSTITUTE($D36,":",""))&lt;&gt;5)),AND($E36&lt;&gt;"",OR(LEN($E36)&lt;&gt;17,LEN($E36)-LEN(SUBSTITUTE($E36,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="n"/>
@@ -2698,6 +2880,10 @@
         <f>IF(COUNTA($A37:$L37)=0,0,IF(OR($B37="",$D37="",$F37="",$G37=""),1,0))</f>
         <v/>
       </c>
+      <c r="O37">
+        <f>IF(OR(AND($D37&lt;&gt;"",OR(LEN($D37)&lt;&gt;17,LEN($D37)-LEN(SUBSTITUTE($D37,":",""))&lt;&gt;5)),AND($E37&lt;&gt;"",OR(LEN($E37)&lt;&gt;17,LEN($E37)-LEN(SUBSTITUTE($E37,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="n"/>
@@ -2716,6 +2902,10 @@
         <f>IF(COUNTA($A38:$L38)=0,0,IF(OR($B38="",$D38="",$F38="",$G38=""),1,0))</f>
         <v/>
       </c>
+      <c r="O38">
+        <f>IF(OR(AND($D38&lt;&gt;"",OR(LEN($D38)&lt;&gt;17,LEN($D38)-LEN(SUBSTITUTE($D38,":",""))&lt;&gt;5)),AND($E38&lt;&gt;"",OR(LEN($E38)&lt;&gt;17,LEN($E38)-LEN(SUBSTITUTE($E38,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="11" t="n"/>
@@ -2734,6 +2924,10 @@
         <f>IF(COUNTA($A39:$L39)=0,0,IF(OR($B39="",$D39="",$F39="",$G39=""),1,0))</f>
         <v/>
       </c>
+      <c r="O39">
+        <f>IF(OR(AND($D39&lt;&gt;"",OR(LEN($D39)&lt;&gt;17,LEN($D39)-LEN(SUBSTITUTE($D39,":",""))&lt;&gt;5)),AND($E39&lt;&gt;"",OR(LEN($E39)&lt;&gt;17,LEN($E39)-LEN(SUBSTITUTE($E39,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="11" t="n"/>
@@ -2752,6 +2946,10 @@
         <f>IF(COUNTA($A40:$L40)=0,0,IF(OR($B40="",$D40="",$F40="",$G40=""),1,0))</f>
         <v/>
       </c>
+      <c r="O40">
+        <f>IF(OR(AND($D40&lt;&gt;"",OR(LEN($D40)&lt;&gt;17,LEN($D40)-LEN(SUBSTITUTE($D40,":",""))&lt;&gt;5)),AND($E40&lt;&gt;"",OR(LEN($E40)&lt;&gt;17,LEN($E40)-LEN(SUBSTITUTE($E40,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="11" t="n"/>
@@ -2770,1558 +2968,2598 @@
         <f>IF(COUNTA($A41:$L41)=0,0,IF(OR($B41="",$D41="",$F41="",$G41=""),1,0))</f>
         <v/>
       </c>
+      <c r="O41">
+        <f>IF(OR(AND($D41&lt;&gt;"",OR(LEN($D41)&lt;&gt;17,LEN($D41)-LEN(SUBSTITUTE($D41,":",""))&lt;&gt;5)),AND($E41&lt;&gt;"",OR(LEN($E41)&lt;&gt;17,LEN($E41)-LEN(SUBSTITUTE($E41,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="N42">
         <f>IF(COUNTA($A42:$L42)=0,0,IF(OR($B42="",$D42="",$F42="",$G42=""),1,0))</f>
         <v/>
       </c>
+      <c r="O42">
+        <f>IF(OR(AND($D42&lt;&gt;"",OR(LEN($D42)&lt;&gt;17,LEN($D42)-LEN(SUBSTITUTE($D42,":",""))&lt;&gt;5)),AND($E42&lt;&gt;"",OR(LEN($E42)&lt;&gt;17,LEN($E42)-LEN(SUBSTITUTE($E42,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="N43">
         <f>IF(COUNTA($A43:$L43)=0,0,IF(OR($B43="",$D43="",$F43="",$G43=""),1,0))</f>
         <v/>
       </c>
+      <c r="O43">
+        <f>IF(OR(AND($D43&lt;&gt;"",OR(LEN($D43)&lt;&gt;17,LEN($D43)-LEN(SUBSTITUTE($D43,":",""))&lt;&gt;5)),AND($E43&lt;&gt;"",OR(LEN($E43)&lt;&gt;17,LEN($E43)-LEN(SUBSTITUTE($E43,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="N44">
         <f>IF(COUNTA($A44:$L44)=0,0,IF(OR($B44="",$D44="",$F44="",$G44=""),1,0))</f>
         <v/>
       </c>
+      <c r="O44">
+        <f>IF(OR(AND($D44&lt;&gt;"",OR(LEN($D44)&lt;&gt;17,LEN($D44)-LEN(SUBSTITUTE($D44,":",""))&lt;&gt;5)),AND($E44&lt;&gt;"",OR(LEN($E44)&lt;&gt;17,LEN($E44)-LEN(SUBSTITUTE($E44,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="N45">
         <f>IF(COUNTA($A45:$L45)=0,0,IF(OR($B45="",$D45="",$F45="",$G45=""),1,0))</f>
         <v/>
       </c>
+      <c r="O45">
+        <f>IF(OR(AND($D45&lt;&gt;"",OR(LEN($D45)&lt;&gt;17,LEN($D45)-LEN(SUBSTITUTE($D45,":",""))&lt;&gt;5)),AND($E45&lt;&gt;"",OR(LEN($E45)&lt;&gt;17,LEN($E45)-LEN(SUBSTITUTE($E45,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="N46">
         <f>IF(COUNTA($A46:$L46)=0,0,IF(OR($B46="",$D46="",$F46="",$G46=""),1,0))</f>
         <v/>
       </c>
+      <c r="O46">
+        <f>IF(OR(AND($D46&lt;&gt;"",OR(LEN($D46)&lt;&gt;17,LEN($D46)-LEN(SUBSTITUTE($D46,":",""))&lt;&gt;5)),AND($E46&lt;&gt;"",OR(LEN($E46)&lt;&gt;17,LEN($E46)-LEN(SUBSTITUTE($E46,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="N47">
         <f>IF(COUNTA($A47:$L47)=0,0,IF(OR($B47="",$D47="",$F47="",$G47=""),1,0))</f>
         <v/>
       </c>
+      <c r="O47">
+        <f>IF(OR(AND($D47&lt;&gt;"",OR(LEN($D47)&lt;&gt;17,LEN($D47)-LEN(SUBSTITUTE($D47,":",""))&lt;&gt;5)),AND($E47&lt;&gt;"",OR(LEN($E47)&lt;&gt;17,LEN($E47)-LEN(SUBSTITUTE($E47,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="N48">
         <f>IF(COUNTA($A48:$L48)=0,0,IF(OR($B48="",$D48="",$F48="",$G48=""),1,0))</f>
         <v/>
       </c>
+      <c r="O48">
+        <f>IF(OR(AND($D48&lt;&gt;"",OR(LEN($D48)&lt;&gt;17,LEN($D48)-LEN(SUBSTITUTE($D48,":",""))&lt;&gt;5)),AND($E48&lt;&gt;"",OR(LEN($E48)&lt;&gt;17,LEN($E48)-LEN(SUBSTITUTE($E48,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="N49">
         <f>IF(COUNTA($A49:$L49)=0,0,IF(OR($B49="",$D49="",$F49="",$G49=""),1,0))</f>
         <v/>
       </c>
+      <c r="O49">
+        <f>IF(OR(AND($D49&lt;&gt;"",OR(LEN($D49)&lt;&gt;17,LEN($D49)-LEN(SUBSTITUTE($D49,":",""))&lt;&gt;5)),AND($E49&lt;&gt;"",OR(LEN($E49)&lt;&gt;17,LEN($E49)-LEN(SUBSTITUTE($E49,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="N50">
         <f>IF(COUNTA($A50:$L50)=0,0,IF(OR($B50="",$D50="",$F50="",$G50=""),1,0))</f>
         <v/>
       </c>
+      <c r="O50">
+        <f>IF(OR(AND($D50&lt;&gt;"",OR(LEN($D50)&lt;&gt;17,LEN($D50)-LEN(SUBSTITUTE($D50,":",""))&lt;&gt;5)),AND($E50&lt;&gt;"",OR(LEN($E50)&lt;&gt;17,LEN($E50)-LEN(SUBSTITUTE($E50,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="N51">
         <f>IF(COUNTA($A51:$L51)=0,0,IF(OR($B51="",$D51="",$F51="",$G51=""),1,0))</f>
         <v/>
       </c>
+      <c r="O51">
+        <f>IF(OR(AND($D51&lt;&gt;"",OR(LEN($D51)&lt;&gt;17,LEN($D51)-LEN(SUBSTITUTE($D51,":",""))&lt;&gt;5)),AND($E51&lt;&gt;"",OR(LEN($E51)&lt;&gt;17,LEN($E51)-LEN(SUBSTITUTE($E51,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="N52">
         <f>IF(COUNTA($A52:$L52)=0,0,IF(OR($B52="",$D52="",$F52="",$G52=""),1,0))</f>
         <v/>
       </c>
+      <c r="O52">
+        <f>IF(OR(AND($D52&lt;&gt;"",OR(LEN($D52)&lt;&gt;17,LEN($D52)-LEN(SUBSTITUTE($D52,":",""))&lt;&gt;5)),AND($E52&lt;&gt;"",OR(LEN($E52)&lt;&gt;17,LEN($E52)-LEN(SUBSTITUTE($E52,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="N53">
         <f>IF(COUNTA($A53:$L53)=0,0,IF(OR($B53="",$D53="",$F53="",$G53=""),1,0))</f>
         <v/>
       </c>
+      <c r="O53">
+        <f>IF(OR(AND($D53&lt;&gt;"",OR(LEN($D53)&lt;&gt;17,LEN($D53)-LEN(SUBSTITUTE($D53,":",""))&lt;&gt;5)),AND($E53&lt;&gt;"",OR(LEN($E53)&lt;&gt;17,LEN($E53)-LEN(SUBSTITUTE($E53,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="N54">
         <f>IF(COUNTA($A54:$L54)=0,0,IF(OR($B54="",$D54="",$F54="",$G54=""),1,0))</f>
         <v/>
       </c>
+      <c r="O54">
+        <f>IF(OR(AND($D54&lt;&gt;"",OR(LEN($D54)&lt;&gt;17,LEN($D54)-LEN(SUBSTITUTE($D54,":",""))&lt;&gt;5)),AND($E54&lt;&gt;"",OR(LEN($E54)&lt;&gt;17,LEN($E54)-LEN(SUBSTITUTE($E54,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="N55">
         <f>IF(COUNTA($A55:$L55)=0,0,IF(OR($B55="",$D55="",$F55="",$G55=""),1,0))</f>
         <v/>
       </c>
+      <c r="O55">
+        <f>IF(OR(AND($D55&lt;&gt;"",OR(LEN($D55)&lt;&gt;17,LEN($D55)-LEN(SUBSTITUTE($D55,":",""))&lt;&gt;5)),AND($E55&lt;&gt;"",OR(LEN($E55)&lt;&gt;17,LEN($E55)-LEN(SUBSTITUTE($E55,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="N56">
         <f>IF(COUNTA($A56:$L56)=0,0,IF(OR($B56="",$D56="",$F56="",$G56=""),1,0))</f>
         <v/>
       </c>
+      <c r="O56">
+        <f>IF(OR(AND($D56&lt;&gt;"",OR(LEN($D56)&lt;&gt;17,LEN($D56)-LEN(SUBSTITUTE($D56,":",""))&lt;&gt;5)),AND($E56&lt;&gt;"",OR(LEN($E56)&lt;&gt;17,LEN($E56)-LEN(SUBSTITUTE($E56,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="N57">
         <f>IF(COUNTA($A57:$L57)=0,0,IF(OR($B57="",$D57="",$F57="",$G57=""),1,0))</f>
         <v/>
       </c>
+      <c r="O57">
+        <f>IF(OR(AND($D57&lt;&gt;"",OR(LEN($D57)&lt;&gt;17,LEN($D57)-LEN(SUBSTITUTE($D57,":",""))&lt;&gt;5)),AND($E57&lt;&gt;"",OR(LEN($E57)&lt;&gt;17,LEN($E57)-LEN(SUBSTITUTE($E57,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="N58">
         <f>IF(COUNTA($A58:$L58)=0,0,IF(OR($B58="",$D58="",$F58="",$G58=""),1,0))</f>
         <v/>
       </c>
+      <c r="O58">
+        <f>IF(OR(AND($D58&lt;&gt;"",OR(LEN($D58)&lt;&gt;17,LEN($D58)-LEN(SUBSTITUTE($D58,":",""))&lt;&gt;5)),AND($E58&lt;&gt;"",OR(LEN($E58)&lt;&gt;17,LEN($E58)-LEN(SUBSTITUTE($E58,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="N59">
         <f>IF(COUNTA($A59:$L59)=0,0,IF(OR($B59="",$D59="",$F59="",$G59=""),1,0))</f>
         <v/>
       </c>
+      <c r="O59">
+        <f>IF(OR(AND($D59&lt;&gt;"",OR(LEN($D59)&lt;&gt;17,LEN($D59)-LEN(SUBSTITUTE($D59,":",""))&lt;&gt;5)),AND($E59&lt;&gt;"",OR(LEN($E59)&lt;&gt;17,LEN($E59)-LEN(SUBSTITUTE($E59,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="N60">
         <f>IF(COUNTA($A60:$L60)=0,0,IF(OR($B60="",$D60="",$F60="",$G60=""),1,0))</f>
         <v/>
       </c>
+      <c r="O60">
+        <f>IF(OR(AND($D60&lt;&gt;"",OR(LEN($D60)&lt;&gt;17,LEN($D60)-LEN(SUBSTITUTE($D60,":",""))&lt;&gt;5)),AND($E60&lt;&gt;"",OR(LEN($E60)&lt;&gt;17,LEN($E60)-LEN(SUBSTITUTE($E60,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="N61">
         <f>IF(COUNTA($A61:$L61)=0,0,IF(OR($B61="",$D61="",$F61="",$G61=""),1,0))</f>
         <v/>
       </c>
+      <c r="O61">
+        <f>IF(OR(AND($D61&lt;&gt;"",OR(LEN($D61)&lt;&gt;17,LEN($D61)-LEN(SUBSTITUTE($D61,":",""))&lt;&gt;5)),AND($E61&lt;&gt;"",OR(LEN($E61)&lt;&gt;17,LEN($E61)-LEN(SUBSTITUTE($E61,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="N62">
         <f>IF(COUNTA($A62:$L62)=0,0,IF(OR($B62="",$D62="",$F62="",$G62=""),1,0))</f>
         <v/>
       </c>
+      <c r="O62">
+        <f>IF(OR(AND($D62&lt;&gt;"",OR(LEN($D62)&lt;&gt;17,LEN($D62)-LEN(SUBSTITUTE($D62,":",""))&lt;&gt;5)),AND($E62&lt;&gt;"",OR(LEN($E62)&lt;&gt;17,LEN($E62)-LEN(SUBSTITUTE($E62,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="N63">
         <f>IF(COUNTA($A63:$L63)=0,0,IF(OR($B63="",$D63="",$F63="",$G63=""),1,0))</f>
         <v/>
       </c>
+      <c r="O63">
+        <f>IF(OR(AND($D63&lt;&gt;"",OR(LEN($D63)&lt;&gt;17,LEN($D63)-LEN(SUBSTITUTE($D63,":",""))&lt;&gt;5)),AND($E63&lt;&gt;"",OR(LEN($E63)&lt;&gt;17,LEN($E63)-LEN(SUBSTITUTE($E63,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="N64">
         <f>IF(COUNTA($A64:$L64)=0,0,IF(OR($B64="",$D64="",$F64="",$G64=""),1,0))</f>
         <v/>
       </c>
+      <c r="O64">
+        <f>IF(OR(AND($D64&lt;&gt;"",OR(LEN($D64)&lt;&gt;17,LEN($D64)-LEN(SUBSTITUTE($D64,":",""))&lt;&gt;5)),AND($E64&lt;&gt;"",OR(LEN($E64)&lt;&gt;17,LEN($E64)-LEN(SUBSTITUTE($E64,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="N65">
         <f>IF(COUNTA($A65:$L65)=0,0,IF(OR($B65="",$D65="",$F65="",$G65=""),1,0))</f>
         <v/>
       </c>
+      <c r="O65">
+        <f>IF(OR(AND($D65&lt;&gt;"",OR(LEN($D65)&lt;&gt;17,LEN($D65)-LEN(SUBSTITUTE($D65,":",""))&lt;&gt;5)),AND($E65&lt;&gt;"",OR(LEN($E65)&lt;&gt;17,LEN($E65)-LEN(SUBSTITUTE($E65,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="N66">
         <f>IF(COUNTA($A66:$L66)=0,0,IF(OR($B66="",$D66="",$F66="",$G66=""),1,0))</f>
         <v/>
       </c>
+      <c r="O66">
+        <f>IF(OR(AND($D66&lt;&gt;"",OR(LEN($D66)&lt;&gt;17,LEN($D66)-LEN(SUBSTITUTE($D66,":",""))&lt;&gt;5)),AND($E66&lt;&gt;"",OR(LEN($E66)&lt;&gt;17,LEN($E66)-LEN(SUBSTITUTE($E66,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="N67">
         <f>IF(COUNTA($A67:$L67)=0,0,IF(OR($B67="",$D67="",$F67="",$G67=""),1,0))</f>
         <v/>
       </c>
+      <c r="O67">
+        <f>IF(OR(AND($D67&lt;&gt;"",OR(LEN($D67)&lt;&gt;17,LEN($D67)-LEN(SUBSTITUTE($D67,":",""))&lt;&gt;5)),AND($E67&lt;&gt;"",OR(LEN($E67)&lt;&gt;17,LEN($E67)-LEN(SUBSTITUTE($E67,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="N68">
         <f>IF(COUNTA($A68:$L68)=0,0,IF(OR($B68="",$D68="",$F68="",$G68=""),1,0))</f>
         <v/>
       </c>
+      <c r="O68">
+        <f>IF(OR(AND($D68&lt;&gt;"",OR(LEN($D68)&lt;&gt;17,LEN($D68)-LEN(SUBSTITUTE($D68,":",""))&lt;&gt;5)),AND($E68&lt;&gt;"",OR(LEN($E68)&lt;&gt;17,LEN($E68)-LEN(SUBSTITUTE($E68,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="N69">
         <f>IF(COUNTA($A69:$L69)=0,0,IF(OR($B69="",$D69="",$F69="",$G69=""),1,0))</f>
         <v/>
       </c>
+      <c r="O69">
+        <f>IF(OR(AND($D69&lt;&gt;"",OR(LEN($D69)&lt;&gt;17,LEN($D69)-LEN(SUBSTITUTE($D69,":",""))&lt;&gt;5)),AND($E69&lt;&gt;"",OR(LEN($E69)&lt;&gt;17,LEN($E69)-LEN(SUBSTITUTE($E69,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="N70">
         <f>IF(COUNTA($A70:$L70)=0,0,IF(OR($B70="",$D70="",$F70="",$G70=""),1,0))</f>
         <v/>
       </c>
+      <c r="O70">
+        <f>IF(OR(AND($D70&lt;&gt;"",OR(LEN($D70)&lt;&gt;17,LEN($D70)-LEN(SUBSTITUTE($D70,":",""))&lt;&gt;5)),AND($E70&lt;&gt;"",OR(LEN($E70)&lt;&gt;17,LEN($E70)-LEN(SUBSTITUTE($E70,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="N71">
         <f>IF(COUNTA($A71:$L71)=0,0,IF(OR($B71="",$D71="",$F71="",$G71=""),1,0))</f>
         <v/>
       </c>
+      <c r="O71">
+        <f>IF(OR(AND($D71&lt;&gt;"",OR(LEN($D71)&lt;&gt;17,LEN($D71)-LEN(SUBSTITUTE($D71,":",""))&lt;&gt;5)),AND($E71&lt;&gt;"",OR(LEN($E71)&lt;&gt;17,LEN($E71)-LEN(SUBSTITUTE($E71,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="N72">
         <f>IF(COUNTA($A72:$L72)=0,0,IF(OR($B72="",$D72="",$F72="",$G72=""),1,0))</f>
         <v/>
       </c>
+      <c r="O72">
+        <f>IF(OR(AND($D72&lt;&gt;"",OR(LEN($D72)&lt;&gt;17,LEN($D72)-LEN(SUBSTITUTE($D72,":",""))&lt;&gt;5)),AND($E72&lt;&gt;"",OR(LEN($E72)&lt;&gt;17,LEN($E72)-LEN(SUBSTITUTE($E72,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="N73">
         <f>IF(COUNTA($A73:$L73)=0,0,IF(OR($B73="",$D73="",$F73="",$G73=""),1,0))</f>
         <v/>
       </c>
+      <c r="O73">
+        <f>IF(OR(AND($D73&lt;&gt;"",OR(LEN($D73)&lt;&gt;17,LEN($D73)-LEN(SUBSTITUTE($D73,":",""))&lt;&gt;5)),AND($E73&lt;&gt;"",OR(LEN($E73)&lt;&gt;17,LEN($E73)-LEN(SUBSTITUTE($E73,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="N74">
         <f>IF(COUNTA($A74:$L74)=0,0,IF(OR($B74="",$D74="",$F74="",$G74=""),1,0))</f>
         <v/>
       </c>
+      <c r="O74">
+        <f>IF(OR(AND($D74&lt;&gt;"",OR(LEN($D74)&lt;&gt;17,LEN($D74)-LEN(SUBSTITUTE($D74,":",""))&lt;&gt;5)),AND($E74&lt;&gt;"",OR(LEN($E74)&lt;&gt;17,LEN($E74)-LEN(SUBSTITUTE($E74,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="N75">
         <f>IF(COUNTA($A75:$L75)=0,0,IF(OR($B75="",$D75="",$F75="",$G75=""),1,0))</f>
         <v/>
       </c>
+      <c r="O75">
+        <f>IF(OR(AND($D75&lt;&gt;"",OR(LEN($D75)&lt;&gt;17,LEN($D75)-LEN(SUBSTITUTE($D75,":",""))&lt;&gt;5)),AND($E75&lt;&gt;"",OR(LEN($E75)&lt;&gt;17,LEN($E75)-LEN(SUBSTITUTE($E75,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="N76">
         <f>IF(COUNTA($A76:$L76)=0,0,IF(OR($B76="",$D76="",$F76="",$G76=""),1,0))</f>
         <v/>
       </c>
+      <c r="O76">
+        <f>IF(OR(AND($D76&lt;&gt;"",OR(LEN($D76)&lt;&gt;17,LEN($D76)-LEN(SUBSTITUTE($D76,":",""))&lt;&gt;5)),AND($E76&lt;&gt;"",OR(LEN($E76)&lt;&gt;17,LEN($E76)-LEN(SUBSTITUTE($E76,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="N77">
         <f>IF(COUNTA($A77:$L77)=0,0,IF(OR($B77="",$D77="",$F77="",$G77=""),1,0))</f>
         <v/>
       </c>
+      <c r="O77">
+        <f>IF(OR(AND($D77&lt;&gt;"",OR(LEN($D77)&lt;&gt;17,LEN($D77)-LEN(SUBSTITUTE($D77,":",""))&lt;&gt;5)),AND($E77&lt;&gt;"",OR(LEN($E77)&lt;&gt;17,LEN($E77)-LEN(SUBSTITUTE($E77,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="N78">
         <f>IF(COUNTA($A78:$L78)=0,0,IF(OR($B78="",$D78="",$F78="",$G78=""),1,0))</f>
         <v/>
       </c>
+      <c r="O78">
+        <f>IF(OR(AND($D78&lt;&gt;"",OR(LEN($D78)&lt;&gt;17,LEN($D78)-LEN(SUBSTITUTE($D78,":",""))&lt;&gt;5)),AND($E78&lt;&gt;"",OR(LEN($E78)&lt;&gt;17,LEN($E78)-LEN(SUBSTITUTE($E78,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="N79">
         <f>IF(COUNTA($A79:$L79)=0,0,IF(OR($B79="",$D79="",$F79="",$G79=""),1,0))</f>
         <v/>
       </c>
+      <c r="O79">
+        <f>IF(OR(AND($D79&lt;&gt;"",OR(LEN($D79)&lt;&gt;17,LEN($D79)-LEN(SUBSTITUTE($D79,":",""))&lt;&gt;5)),AND($E79&lt;&gt;"",OR(LEN($E79)&lt;&gt;17,LEN($E79)-LEN(SUBSTITUTE($E79,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="N80">
         <f>IF(COUNTA($A80:$L80)=0,0,IF(OR($B80="",$D80="",$F80="",$G80=""),1,0))</f>
         <v/>
       </c>
+      <c r="O80">
+        <f>IF(OR(AND($D80&lt;&gt;"",OR(LEN($D80)&lt;&gt;17,LEN($D80)-LEN(SUBSTITUTE($D80,":",""))&lt;&gt;5)),AND($E80&lt;&gt;"",OR(LEN($E80)&lt;&gt;17,LEN($E80)-LEN(SUBSTITUTE($E80,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="N81">
         <f>IF(COUNTA($A81:$L81)=0,0,IF(OR($B81="",$D81="",$F81="",$G81=""),1,0))</f>
         <v/>
       </c>
+      <c r="O81">
+        <f>IF(OR(AND($D81&lt;&gt;"",OR(LEN($D81)&lt;&gt;17,LEN($D81)-LEN(SUBSTITUTE($D81,":",""))&lt;&gt;5)),AND($E81&lt;&gt;"",OR(LEN($E81)&lt;&gt;17,LEN($E81)-LEN(SUBSTITUTE($E81,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="N82">
         <f>IF(COUNTA($A82:$L82)=0,0,IF(OR($B82="",$D82="",$F82="",$G82=""),1,0))</f>
         <v/>
       </c>
+      <c r="O82">
+        <f>IF(OR(AND($D82&lt;&gt;"",OR(LEN($D82)&lt;&gt;17,LEN($D82)-LEN(SUBSTITUTE($D82,":",""))&lt;&gt;5)),AND($E82&lt;&gt;"",OR(LEN($E82)&lt;&gt;17,LEN($E82)-LEN(SUBSTITUTE($E82,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="N83">
         <f>IF(COUNTA($A83:$L83)=0,0,IF(OR($B83="",$D83="",$F83="",$G83=""),1,0))</f>
         <v/>
       </c>
+      <c r="O83">
+        <f>IF(OR(AND($D83&lt;&gt;"",OR(LEN($D83)&lt;&gt;17,LEN($D83)-LEN(SUBSTITUTE($D83,":",""))&lt;&gt;5)),AND($E83&lt;&gt;"",OR(LEN($E83)&lt;&gt;17,LEN($E83)-LEN(SUBSTITUTE($E83,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="N84">
         <f>IF(COUNTA($A84:$L84)=0,0,IF(OR($B84="",$D84="",$F84="",$G84=""),1,0))</f>
         <v/>
       </c>
+      <c r="O84">
+        <f>IF(OR(AND($D84&lt;&gt;"",OR(LEN($D84)&lt;&gt;17,LEN($D84)-LEN(SUBSTITUTE($D84,":",""))&lt;&gt;5)),AND($E84&lt;&gt;"",OR(LEN($E84)&lt;&gt;17,LEN($E84)-LEN(SUBSTITUTE($E84,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="N85">
         <f>IF(COUNTA($A85:$L85)=0,0,IF(OR($B85="",$D85="",$F85="",$G85=""),1,0))</f>
         <v/>
       </c>
+      <c r="O85">
+        <f>IF(OR(AND($D85&lt;&gt;"",OR(LEN($D85)&lt;&gt;17,LEN($D85)-LEN(SUBSTITUTE($D85,":",""))&lt;&gt;5)),AND($E85&lt;&gt;"",OR(LEN($E85)&lt;&gt;17,LEN($E85)-LEN(SUBSTITUTE($E85,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="N86">
         <f>IF(COUNTA($A86:$L86)=0,0,IF(OR($B86="",$D86="",$F86="",$G86=""),1,0))</f>
         <v/>
       </c>
+      <c r="O86">
+        <f>IF(OR(AND($D86&lt;&gt;"",OR(LEN($D86)&lt;&gt;17,LEN($D86)-LEN(SUBSTITUTE($D86,":",""))&lt;&gt;5)),AND($E86&lt;&gt;"",OR(LEN($E86)&lt;&gt;17,LEN($E86)-LEN(SUBSTITUTE($E86,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="N87">
         <f>IF(COUNTA($A87:$L87)=0,0,IF(OR($B87="",$D87="",$F87="",$G87=""),1,0))</f>
         <v/>
       </c>
+      <c r="O87">
+        <f>IF(OR(AND($D87&lt;&gt;"",OR(LEN($D87)&lt;&gt;17,LEN($D87)-LEN(SUBSTITUTE($D87,":",""))&lt;&gt;5)),AND($E87&lt;&gt;"",OR(LEN($E87)&lt;&gt;17,LEN($E87)-LEN(SUBSTITUTE($E87,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="N88">
         <f>IF(COUNTA($A88:$L88)=0,0,IF(OR($B88="",$D88="",$F88="",$G88=""),1,0))</f>
         <v/>
       </c>
+      <c r="O88">
+        <f>IF(OR(AND($D88&lt;&gt;"",OR(LEN($D88)&lt;&gt;17,LEN($D88)-LEN(SUBSTITUTE($D88,":",""))&lt;&gt;5)),AND($E88&lt;&gt;"",OR(LEN($E88)&lt;&gt;17,LEN($E88)-LEN(SUBSTITUTE($E88,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="N89">
         <f>IF(COUNTA($A89:$L89)=0,0,IF(OR($B89="",$D89="",$F89="",$G89=""),1,0))</f>
         <v/>
       </c>
+      <c r="O89">
+        <f>IF(OR(AND($D89&lt;&gt;"",OR(LEN($D89)&lt;&gt;17,LEN($D89)-LEN(SUBSTITUTE($D89,":",""))&lt;&gt;5)),AND($E89&lt;&gt;"",OR(LEN($E89)&lt;&gt;17,LEN($E89)-LEN(SUBSTITUTE($E89,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="N90">
         <f>IF(COUNTA($A90:$L90)=0,0,IF(OR($B90="",$D90="",$F90="",$G90=""),1,0))</f>
         <v/>
       </c>
+      <c r="O90">
+        <f>IF(OR(AND($D90&lt;&gt;"",OR(LEN($D90)&lt;&gt;17,LEN($D90)-LEN(SUBSTITUTE($D90,":",""))&lt;&gt;5)),AND($E90&lt;&gt;"",OR(LEN($E90)&lt;&gt;17,LEN($E90)-LEN(SUBSTITUTE($E90,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="N91">
         <f>IF(COUNTA($A91:$L91)=0,0,IF(OR($B91="",$D91="",$F91="",$G91=""),1,0))</f>
         <v/>
       </c>
+      <c r="O91">
+        <f>IF(OR(AND($D91&lt;&gt;"",OR(LEN($D91)&lt;&gt;17,LEN($D91)-LEN(SUBSTITUTE($D91,":",""))&lt;&gt;5)),AND($E91&lt;&gt;"",OR(LEN($E91)&lt;&gt;17,LEN($E91)-LEN(SUBSTITUTE($E91,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="N92">
         <f>IF(COUNTA($A92:$L92)=0,0,IF(OR($B92="",$D92="",$F92="",$G92=""),1,0))</f>
         <v/>
       </c>
+      <c r="O92">
+        <f>IF(OR(AND($D92&lt;&gt;"",OR(LEN($D92)&lt;&gt;17,LEN($D92)-LEN(SUBSTITUTE($D92,":",""))&lt;&gt;5)),AND($E92&lt;&gt;"",OR(LEN($E92)&lt;&gt;17,LEN($E92)-LEN(SUBSTITUTE($E92,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="N93">
         <f>IF(COUNTA($A93:$L93)=0,0,IF(OR($B93="",$D93="",$F93="",$G93=""),1,0))</f>
         <v/>
       </c>
+      <c r="O93">
+        <f>IF(OR(AND($D93&lt;&gt;"",OR(LEN($D93)&lt;&gt;17,LEN($D93)-LEN(SUBSTITUTE($D93,":",""))&lt;&gt;5)),AND($E93&lt;&gt;"",OR(LEN($E93)&lt;&gt;17,LEN($E93)-LEN(SUBSTITUTE($E93,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="N94">
         <f>IF(COUNTA($A94:$L94)=0,0,IF(OR($B94="",$D94="",$F94="",$G94=""),1,0))</f>
         <v/>
       </c>
+      <c r="O94">
+        <f>IF(OR(AND($D94&lt;&gt;"",OR(LEN($D94)&lt;&gt;17,LEN($D94)-LEN(SUBSTITUTE($D94,":",""))&lt;&gt;5)),AND($E94&lt;&gt;"",OR(LEN($E94)&lt;&gt;17,LEN($E94)-LEN(SUBSTITUTE($E94,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="N95">
         <f>IF(COUNTA($A95:$L95)=0,0,IF(OR($B95="",$D95="",$F95="",$G95=""),1,0))</f>
         <v/>
       </c>
+      <c r="O95">
+        <f>IF(OR(AND($D95&lt;&gt;"",OR(LEN($D95)&lt;&gt;17,LEN($D95)-LEN(SUBSTITUTE($D95,":",""))&lt;&gt;5)),AND($E95&lt;&gt;"",OR(LEN($E95)&lt;&gt;17,LEN($E95)-LEN(SUBSTITUTE($E95,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="N96">
         <f>IF(COUNTA($A96:$L96)=0,0,IF(OR($B96="",$D96="",$F96="",$G96=""),1,0))</f>
         <v/>
       </c>
+      <c r="O96">
+        <f>IF(OR(AND($D96&lt;&gt;"",OR(LEN($D96)&lt;&gt;17,LEN($D96)-LEN(SUBSTITUTE($D96,":",""))&lt;&gt;5)),AND($E96&lt;&gt;"",OR(LEN($E96)&lt;&gt;17,LEN($E96)-LEN(SUBSTITUTE($E96,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="N97">
         <f>IF(COUNTA($A97:$L97)=0,0,IF(OR($B97="",$D97="",$F97="",$G97=""),1,0))</f>
         <v/>
       </c>
+      <c r="O97">
+        <f>IF(OR(AND($D97&lt;&gt;"",OR(LEN($D97)&lt;&gt;17,LEN($D97)-LEN(SUBSTITUTE($D97,":",""))&lt;&gt;5)),AND($E97&lt;&gt;"",OR(LEN($E97)&lt;&gt;17,LEN($E97)-LEN(SUBSTITUTE($E97,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="N98">
         <f>IF(COUNTA($A98:$L98)=0,0,IF(OR($B98="",$D98="",$F98="",$G98=""),1,0))</f>
         <v/>
       </c>
+      <c r="O98">
+        <f>IF(OR(AND($D98&lt;&gt;"",OR(LEN($D98)&lt;&gt;17,LEN($D98)-LEN(SUBSTITUTE($D98,":",""))&lt;&gt;5)),AND($E98&lt;&gt;"",OR(LEN($E98)&lt;&gt;17,LEN($E98)-LEN(SUBSTITUTE($E98,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="N99">
         <f>IF(COUNTA($A99:$L99)=0,0,IF(OR($B99="",$D99="",$F99="",$G99=""),1,0))</f>
         <v/>
       </c>
+      <c r="O99">
+        <f>IF(OR(AND($D99&lt;&gt;"",OR(LEN($D99)&lt;&gt;17,LEN($D99)-LEN(SUBSTITUTE($D99,":",""))&lt;&gt;5)),AND($E99&lt;&gt;"",OR(LEN($E99)&lt;&gt;17,LEN($E99)-LEN(SUBSTITUTE($E99,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="N100">
         <f>IF(COUNTA($A100:$L100)=0,0,IF(OR($B100="",$D100="",$F100="",$G100=""),1,0))</f>
         <v/>
       </c>
+      <c r="O100">
+        <f>IF(OR(AND($D100&lt;&gt;"",OR(LEN($D100)&lt;&gt;17,LEN($D100)-LEN(SUBSTITUTE($D100,":",""))&lt;&gt;5)),AND($E100&lt;&gt;"",OR(LEN($E100)&lt;&gt;17,LEN($E100)-LEN(SUBSTITUTE($E100,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="N101">
         <f>IF(COUNTA($A101:$L101)=0,0,IF(OR($B101="",$D101="",$F101="",$G101=""),1,0))</f>
         <v/>
       </c>
+      <c r="O101">
+        <f>IF(OR(AND($D101&lt;&gt;"",OR(LEN($D101)&lt;&gt;17,LEN($D101)-LEN(SUBSTITUTE($D101,":",""))&lt;&gt;5)),AND($E101&lt;&gt;"",OR(LEN($E101)&lt;&gt;17,LEN($E101)-LEN(SUBSTITUTE($E101,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="N102">
         <f>IF(COUNTA($A102:$L102)=0,0,IF(OR($B102="",$D102="",$F102="",$G102=""),1,0))</f>
         <v/>
       </c>
+      <c r="O102">
+        <f>IF(OR(AND($D102&lt;&gt;"",OR(LEN($D102)&lt;&gt;17,LEN($D102)-LEN(SUBSTITUTE($D102,":",""))&lt;&gt;5)),AND($E102&lt;&gt;"",OR(LEN($E102)&lt;&gt;17,LEN($E102)-LEN(SUBSTITUTE($E102,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="N103">
         <f>IF(COUNTA($A103:$L103)=0,0,IF(OR($B103="",$D103="",$F103="",$G103=""),1,0))</f>
         <v/>
       </c>
+      <c r="O103">
+        <f>IF(OR(AND($D103&lt;&gt;"",OR(LEN($D103)&lt;&gt;17,LEN($D103)-LEN(SUBSTITUTE($D103,":",""))&lt;&gt;5)),AND($E103&lt;&gt;"",OR(LEN($E103)&lt;&gt;17,LEN($E103)-LEN(SUBSTITUTE($E103,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="N104">
         <f>IF(COUNTA($A104:$L104)=0,0,IF(OR($B104="",$D104="",$F104="",$G104=""),1,0))</f>
         <v/>
       </c>
+      <c r="O104">
+        <f>IF(OR(AND($D104&lt;&gt;"",OR(LEN($D104)&lt;&gt;17,LEN($D104)-LEN(SUBSTITUTE($D104,":",""))&lt;&gt;5)),AND($E104&lt;&gt;"",OR(LEN($E104)&lt;&gt;17,LEN($E104)-LEN(SUBSTITUTE($E104,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="N105">
         <f>IF(COUNTA($A105:$L105)=0,0,IF(OR($B105="",$D105="",$F105="",$G105=""),1,0))</f>
         <v/>
       </c>
+      <c r="O105">
+        <f>IF(OR(AND($D105&lt;&gt;"",OR(LEN($D105)&lt;&gt;17,LEN($D105)-LEN(SUBSTITUTE($D105,":",""))&lt;&gt;5)),AND($E105&lt;&gt;"",OR(LEN($E105)&lt;&gt;17,LEN($E105)-LEN(SUBSTITUTE($E105,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="N106">
         <f>IF(COUNTA($A106:$L106)=0,0,IF(OR($B106="",$D106="",$F106="",$G106=""),1,0))</f>
         <v/>
       </c>
+      <c r="O106">
+        <f>IF(OR(AND($D106&lt;&gt;"",OR(LEN($D106)&lt;&gt;17,LEN($D106)-LEN(SUBSTITUTE($D106,":",""))&lt;&gt;5)),AND($E106&lt;&gt;"",OR(LEN($E106)&lt;&gt;17,LEN($E106)-LEN(SUBSTITUTE($E106,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="N107">
         <f>IF(COUNTA($A107:$L107)=0,0,IF(OR($B107="",$D107="",$F107="",$G107=""),1,0))</f>
         <v/>
       </c>
+      <c r="O107">
+        <f>IF(OR(AND($D107&lt;&gt;"",OR(LEN($D107)&lt;&gt;17,LEN($D107)-LEN(SUBSTITUTE($D107,":",""))&lt;&gt;5)),AND($E107&lt;&gt;"",OR(LEN($E107)&lt;&gt;17,LEN($E107)-LEN(SUBSTITUTE($E107,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="N108">
         <f>IF(COUNTA($A108:$L108)=0,0,IF(OR($B108="",$D108="",$F108="",$G108=""),1,0))</f>
         <v/>
       </c>
+      <c r="O108">
+        <f>IF(OR(AND($D108&lt;&gt;"",OR(LEN($D108)&lt;&gt;17,LEN($D108)-LEN(SUBSTITUTE($D108,":",""))&lt;&gt;5)),AND($E108&lt;&gt;"",OR(LEN($E108)&lt;&gt;17,LEN($E108)-LEN(SUBSTITUTE($E108,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="N109">
         <f>IF(COUNTA($A109:$L109)=0,0,IF(OR($B109="",$D109="",$F109="",$G109=""),1,0))</f>
         <v/>
       </c>
+      <c r="O109">
+        <f>IF(OR(AND($D109&lt;&gt;"",OR(LEN($D109)&lt;&gt;17,LEN($D109)-LEN(SUBSTITUTE($D109,":",""))&lt;&gt;5)),AND($E109&lt;&gt;"",OR(LEN($E109)&lt;&gt;17,LEN($E109)-LEN(SUBSTITUTE($E109,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="N110">
         <f>IF(COUNTA($A110:$L110)=0,0,IF(OR($B110="",$D110="",$F110="",$G110=""),1,0))</f>
         <v/>
       </c>
+      <c r="O110">
+        <f>IF(OR(AND($D110&lt;&gt;"",OR(LEN($D110)&lt;&gt;17,LEN($D110)-LEN(SUBSTITUTE($D110,":",""))&lt;&gt;5)),AND($E110&lt;&gt;"",OR(LEN($E110)&lt;&gt;17,LEN($E110)-LEN(SUBSTITUTE($E110,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="N111">
         <f>IF(COUNTA($A111:$L111)=0,0,IF(OR($B111="",$D111="",$F111="",$G111=""),1,0))</f>
         <v/>
       </c>
+      <c r="O111">
+        <f>IF(OR(AND($D111&lt;&gt;"",OR(LEN($D111)&lt;&gt;17,LEN($D111)-LEN(SUBSTITUTE($D111,":",""))&lt;&gt;5)),AND($E111&lt;&gt;"",OR(LEN($E111)&lt;&gt;17,LEN($E111)-LEN(SUBSTITUTE($E111,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="N112">
         <f>IF(COUNTA($A112:$L112)=0,0,IF(OR($B112="",$D112="",$F112="",$G112=""),1,0))</f>
         <v/>
       </c>
+      <c r="O112">
+        <f>IF(OR(AND($D112&lt;&gt;"",OR(LEN($D112)&lt;&gt;17,LEN($D112)-LEN(SUBSTITUTE($D112,":",""))&lt;&gt;5)),AND($E112&lt;&gt;"",OR(LEN($E112)&lt;&gt;17,LEN($E112)-LEN(SUBSTITUTE($E112,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="N113">
         <f>IF(COUNTA($A113:$L113)=0,0,IF(OR($B113="",$D113="",$F113="",$G113=""),1,0))</f>
         <v/>
       </c>
+      <c r="O113">
+        <f>IF(OR(AND($D113&lt;&gt;"",OR(LEN($D113)&lt;&gt;17,LEN($D113)-LEN(SUBSTITUTE($D113,":",""))&lt;&gt;5)),AND($E113&lt;&gt;"",OR(LEN($E113)&lt;&gt;17,LEN($E113)-LEN(SUBSTITUTE($E113,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="N114">
         <f>IF(COUNTA($A114:$L114)=0,0,IF(OR($B114="",$D114="",$F114="",$G114=""),1,0))</f>
         <v/>
       </c>
+      <c r="O114">
+        <f>IF(OR(AND($D114&lt;&gt;"",OR(LEN($D114)&lt;&gt;17,LEN($D114)-LEN(SUBSTITUTE($D114,":",""))&lt;&gt;5)),AND($E114&lt;&gt;"",OR(LEN($E114)&lt;&gt;17,LEN($E114)-LEN(SUBSTITUTE($E114,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="N115">
         <f>IF(COUNTA($A115:$L115)=0,0,IF(OR($B115="",$D115="",$F115="",$G115=""),1,0))</f>
         <v/>
       </c>
+      <c r="O115">
+        <f>IF(OR(AND($D115&lt;&gt;"",OR(LEN($D115)&lt;&gt;17,LEN($D115)-LEN(SUBSTITUTE($D115,":",""))&lt;&gt;5)),AND($E115&lt;&gt;"",OR(LEN($E115)&lt;&gt;17,LEN($E115)-LEN(SUBSTITUTE($E115,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="N116">
         <f>IF(COUNTA($A116:$L116)=0,0,IF(OR($B116="",$D116="",$F116="",$G116=""),1,0))</f>
         <v/>
       </c>
+      <c r="O116">
+        <f>IF(OR(AND($D116&lt;&gt;"",OR(LEN($D116)&lt;&gt;17,LEN($D116)-LEN(SUBSTITUTE($D116,":",""))&lt;&gt;5)),AND($E116&lt;&gt;"",OR(LEN($E116)&lt;&gt;17,LEN($E116)-LEN(SUBSTITUTE($E116,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="N117">
         <f>IF(COUNTA($A117:$L117)=0,0,IF(OR($B117="",$D117="",$F117="",$G117=""),1,0))</f>
         <v/>
       </c>
+      <c r="O117">
+        <f>IF(OR(AND($D117&lt;&gt;"",OR(LEN($D117)&lt;&gt;17,LEN($D117)-LEN(SUBSTITUTE($D117,":",""))&lt;&gt;5)),AND($E117&lt;&gt;"",OR(LEN($E117)&lt;&gt;17,LEN($E117)-LEN(SUBSTITUTE($E117,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="N118">
         <f>IF(COUNTA($A118:$L118)=0,0,IF(OR($B118="",$D118="",$F118="",$G118=""),1,0))</f>
         <v/>
       </c>
+      <c r="O118">
+        <f>IF(OR(AND($D118&lt;&gt;"",OR(LEN($D118)&lt;&gt;17,LEN($D118)-LEN(SUBSTITUTE($D118,":",""))&lt;&gt;5)),AND($E118&lt;&gt;"",OR(LEN($E118)&lt;&gt;17,LEN($E118)-LEN(SUBSTITUTE($E118,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="N119">
         <f>IF(COUNTA($A119:$L119)=0,0,IF(OR($B119="",$D119="",$F119="",$G119=""),1,0))</f>
         <v/>
       </c>
+      <c r="O119">
+        <f>IF(OR(AND($D119&lt;&gt;"",OR(LEN($D119)&lt;&gt;17,LEN($D119)-LEN(SUBSTITUTE($D119,":",""))&lt;&gt;5)),AND($E119&lt;&gt;"",OR(LEN($E119)&lt;&gt;17,LEN($E119)-LEN(SUBSTITUTE($E119,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="N120">
         <f>IF(COUNTA($A120:$L120)=0,0,IF(OR($B120="",$D120="",$F120="",$G120=""),1,0))</f>
         <v/>
       </c>
+      <c r="O120">
+        <f>IF(OR(AND($D120&lt;&gt;"",OR(LEN($D120)&lt;&gt;17,LEN($D120)-LEN(SUBSTITUTE($D120,":",""))&lt;&gt;5)),AND($E120&lt;&gt;"",OR(LEN($E120)&lt;&gt;17,LEN($E120)-LEN(SUBSTITUTE($E120,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="N121">
         <f>IF(COUNTA($A121:$L121)=0,0,IF(OR($B121="",$D121="",$F121="",$G121=""),1,0))</f>
         <v/>
       </c>
+      <c r="O121">
+        <f>IF(OR(AND($D121&lt;&gt;"",OR(LEN($D121)&lt;&gt;17,LEN($D121)-LEN(SUBSTITUTE($D121,":",""))&lt;&gt;5)),AND($E121&lt;&gt;"",OR(LEN($E121)&lt;&gt;17,LEN($E121)-LEN(SUBSTITUTE($E121,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="N122">
         <f>IF(COUNTA($A122:$L122)=0,0,IF(OR($B122="",$D122="",$F122="",$G122=""),1,0))</f>
         <v/>
       </c>
+      <c r="O122">
+        <f>IF(OR(AND($D122&lt;&gt;"",OR(LEN($D122)&lt;&gt;17,LEN($D122)-LEN(SUBSTITUTE($D122,":",""))&lt;&gt;5)),AND($E122&lt;&gt;"",OR(LEN($E122)&lt;&gt;17,LEN($E122)-LEN(SUBSTITUTE($E122,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="N123">
         <f>IF(COUNTA($A123:$L123)=0,0,IF(OR($B123="",$D123="",$F123="",$G123=""),1,0))</f>
         <v/>
       </c>
+      <c r="O123">
+        <f>IF(OR(AND($D123&lt;&gt;"",OR(LEN($D123)&lt;&gt;17,LEN($D123)-LEN(SUBSTITUTE($D123,":",""))&lt;&gt;5)),AND($E123&lt;&gt;"",OR(LEN($E123)&lt;&gt;17,LEN($E123)-LEN(SUBSTITUTE($E123,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="N124">
         <f>IF(COUNTA($A124:$L124)=0,0,IF(OR($B124="",$D124="",$F124="",$G124=""),1,0))</f>
         <v/>
       </c>
+      <c r="O124">
+        <f>IF(OR(AND($D124&lt;&gt;"",OR(LEN($D124)&lt;&gt;17,LEN($D124)-LEN(SUBSTITUTE($D124,":",""))&lt;&gt;5)),AND($E124&lt;&gt;"",OR(LEN($E124)&lt;&gt;17,LEN($E124)-LEN(SUBSTITUTE($E124,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="N125">
         <f>IF(COUNTA($A125:$L125)=0,0,IF(OR($B125="",$D125="",$F125="",$G125=""),1,0))</f>
         <v/>
       </c>
+      <c r="O125">
+        <f>IF(OR(AND($D125&lt;&gt;"",OR(LEN($D125)&lt;&gt;17,LEN($D125)-LEN(SUBSTITUTE($D125,":",""))&lt;&gt;5)),AND($E125&lt;&gt;"",OR(LEN($E125)&lt;&gt;17,LEN($E125)-LEN(SUBSTITUTE($E125,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="N126">
         <f>IF(COUNTA($A126:$L126)=0,0,IF(OR($B126="",$D126="",$F126="",$G126=""),1,0))</f>
         <v/>
       </c>
+      <c r="O126">
+        <f>IF(OR(AND($D126&lt;&gt;"",OR(LEN($D126)&lt;&gt;17,LEN($D126)-LEN(SUBSTITUTE($D126,":",""))&lt;&gt;5)),AND($E126&lt;&gt;"",OR(LEN($E126)&lt;&gt;17,LEN($E126)-LEN(SUBSTITUTE($E126,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="N127">
         <f>IF(COUNTA($A127:$L127)=0,0,IF(OR($B127="",$D127="",$F127="",$G127=""),1,0))</f>
         <v/>
       </c>
+      <c r="O127">
+        <f>IF(OR(AND($D127&lt;&gt;"",OR(LEN($D127)&lt;&gt;17,LEN($D127)-LEN(SUBSTITUTE($D127,":",""))&lt;&gt;5)),AND($E127&lt;&gt;"",OR(LEN($E127)&lt;&gt;17,LEN($E127)-LEN(SUBSTITUTE($E127,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="N128">
         <f>IF(COUNTA($A128:$L128)=0,0,IF(OR($B128="",$D128="",$F128="",$G128=""),1,0))</f>
         <v/>
       </c>
+      <c r="O128">
+        <f>IF(OR(AND($D128&lt;&gt;"",OR(LEN($D128)&lt;&gt;17,LEN($D128)-LEN(SUBSTITUTE($D128,":",""))&lt;&gt;5)),AND($E128&lt;&gt;"",OR(LEN($E128)&lt;&gt;17,LEN($E128)-LEN(SUBSTITUTE($E128,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="N129">
         <f>IF(COUNTA($A129:$L129)=0,0,IF(OR($B129="",$D129="",$F129="",$G129=""),1,0))</f>
         <v/>
       </c>
+      <c r="O129">
+        <f>IF(OR(AND($D129&lt;&gt;"",OR(LEN($D129)&lt;&gt;17,LEN($D129)-LEN(SUBSTITUTE($D129,":",""))&lt;&gt;5)),AND($E129&lt;&gt;"",OR(LEN($E129)&lt;&gt;17,LEN($E129)-LEN(SUBSTITUTE($E129,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="N130">
         <f>IF(COUNTA($A130:$L130)=0,0,IF(OR($B130="",$D130="",$F130="",$G130=""),1,0))</f>
         <v/>
       </c>
+      <c r="O130">
+        <f>IF(OR(AND($D130&lt;&gt;"",OR(LEN($D130)&lt;&gt;17,LEN($D130)-LEN(SUBSTITUTE($D130,":",""))&lt;&gt;5)),AND($E130&lt;&gt;"",OR(LEN($E130)&lt;&gt;17,LEN($E130)-LEN(SUBSTITUTE($E130,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="N131">
         <f>IF(COUNTA($A131:$L131)=0,0,IF(OR($B131="",$D131="",$F131="",$G131=""),1,0))</f>
         <v/>
       </c>
+      <c r="O131">
+        <f>IF(OR(AND($D131&lt;&gt;"",OR(LEN($D131)&lt;&gt;17,LEN($D131)-LEN(SUBSTITUTE($D131,":",""))&lt;&gt;5)),AND($E131&lt;&gt;"",OR(LEN($E131)&lt;&gt;17,LEN($E131)-LEN(SUBSTITUTE($E131,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="N132">
         <f>IF(COUNTA($A132:$L132)=0,0,IF(OR($B132="",$D132="",$F132="",$G132=""),1,0))</f>
         <v/>
       </c>
+      <c r="O132">
+        <f>IF(OR(AND($D132&lt;&gt;"",OR(LEN($D132)&lt;&gt;17,LEN($D132)-LEN(SUBSTITUTE($D132,":",""))&lt;&gt;5)),AND($E132&lt;&gt;"",OR(LEN($E132)&lt;&gt;17,LEN($E132)-LEN(SUBSTITUTE($E132,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="N133">
         <f>IF(COUNTA($A133:$L133)=0,0,IF(OR($B133="",$D133="",$F133="",$G133=""),1,0))</f>
         <v/>
       </c>
+      <c r="O133">
+        <f>IF(OR(AND($D133&lt;&gt;"",OR(LEN($D133)&lt;&gt;17,LEN($D133)-LEN(SUBSTITUTE($D133,":",""))&lt;&gt;5)),AND($E133&lt;&gt;"",OR(LEN($E133)&lt;&gt;17,LEN($E133)-LEN(SUBSTITUTE($E133,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="N134">
         <f>IF(COUNTA($A134:$L134)=0,0,IF(OR($B134="",$D134="",$F134="",$G134=""),1,0))</f>
         <v/>
       </c>
+      <c r="O134">
+        <f>IF(OR(AND($D134&lt;&gt;"",OR(LEN($D134)&lt;&gt;17,LEN($D134)-LEN(SUBSTITUTE($D134,":",""))&lt;&gt;5)),AND($E134&lt;&gt;"",OR(LEN($E134)&lt;&gt;17,LEN($E134)-LEN(SUBSTITUTE($E134,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="N135">
         <f>IF(COUNTA($A135:$L135)=0,0,IF(OR($B135="",$D135="",$F135="",$G135=""),1,0))</f>
         <v/>
       </c>
+      <c r="O135">
+        <f>IF(OR(AND($D135&lt;&gt;"",OR(LEN($D135)&lt;&gt;17,LEN($D135)-LEN(SUBSTITUTE($D135,":",""))&lt;&gt;5)),AND($E135&lt;&gt;"",OR(LEN($E135)&lt;&gt;17,LEN($E135)-LEN(SUBSTITUTE($E135,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="N136">
         <f>IF(COUNTA($A136:$L136)=0,0,IF(OR($B136="",$D136="",$F136="",$G136=""),1,0))</f>
         <v/>
       </c>
+      <c r="O136">
+        <f>IF(OR(AND($D136&lt;&gt;"",OR(LEN($D136)&lt;&gt;17,LEN($D136)-LEN(SUBSTITUTE($D136,":",""))&lt;&gt;5)),AND($E136&lt;&gt;"",OR(LEN($E136)&lt;&gt;17,LEN($E136)-LEN(SUBSTITUTE($E136,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="N137">
         <f>IF(COUNTA($A137:$L137)=0,0,IF(OR($B137="",$D137="",$F137="",$G137=""),1,0))</f>
         <v/>
       </c>
+      <c r="O137">
+        <f>IF(OR(AND($D137&lt;&gt;"",OR(LEN($D137)&lt;&gt;17,LEN($D137)-LEN(SUBSTITUTE($D137,":",""))&lt;&gt;5)),AND($E137&lt;&gt;"",OR(LEN($E137)&lt;&gt;17,LEN($E137)-LEN(SUBSTITUTE($E137,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="N138">
         <f>IF(COUNTA($A138:$L138)=0,0,IF(OR($B138="",$D138="",$F138="",$G138=""),1,0))</f>
         <v/>
       </c>
+      <c r="O138">
+        <f>IF(OR(AND($D138&lt;&gt;"",OR(LEN($D138)&lt;&gt;17,LEN($D138)-LEN(SUBSTITUTE($D138,":",""))&lt;&gt;5)),AND($E138&lt;&gt;"",OR(LEN($E138)&lt;&gt;17,LEN($E138)-LEN(SUBSTITUTE($E138,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="N139">
         <f>IF(COUNTA($A139:$L139)=0,0,IF(OR($B139="",$D139="",$F139="",$G139=""),1,0))</f>
         <v/>
       </c>
+      <c r="O139">
+        <f>IF(OR(AND($D139&lt;&gt;"",OR(LEN($D139)&lt;&gt;17,LEN($D139)-LEN(SUBSTITUTE($D139,":",""))&lt;&gt;5)),AND($E139&lt;&gt;"",OR(LEN($E139)&lt;&gt;17,LEN($E139)-LEN(SUBSTITUTE($E139,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="140">
       <c r="N140">
         <f>IF(COUNTA($A140:$L140)=0,0,IF(OR($B140="",$D140="",$F140="",$G140=""),1,0))</f>
         <v/>
       </c>
+      <c r="O140">
+        <f>IF(OR(AND($D140&lt;&gt;"",OR(LEN($D140)&lt;&gt;17,LEN($D140)-LEN(SUBSTITUTE($D140,":",""))&lt;&gt;5)),AND($E140&lt;&gt;"",OR(LEN($E140)&lt;&gt;17,LEN($E140)-LEN(SUBSTITUTE($E140,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="N141">
         <f>IF(COUNTA($A141:$L141)=0,0,IF(OR($B141="",$D141="",$F141="",$G141=""),1,0))</f>
         <v/>
       </c>
+      <c r="O141">
+        <f>IF(OR(AND($D141&lt;&gt;"",OR(LEN($D141)&lt;&gt;17,LEN($D141)-LEN(SUBSTITUTE($D141,":",""))&lt;&gt;5)),AND($E141&lt;&gt;"",OR(LEN($E141)&lt;&gt;17,LEN($E141)-LEN(SUBSTITUTE($E141,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="N142">
         <f>IF(COUNTA($A142:$L142)=0,0,IF(OR($B142="",$D142="",$F142="",$G142=""),1,0))</f>
         <v/>
       </c>
+      <c r="O142">
+        <f>IF(OR(AND($D142&lt;&gt;"",OR(LEN($D142)&lt;&gt;17,LEN($D142)-LEN(SUBSTITUTE($D142,":",""))&lt;&gt;5)),AND($E142&lt;&gt;"",OR(LEN($E142)&lt;&gt;17,LEN($E142)-LEN(SUBSTITUTE($E142,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="N143">
         <f>IF(COUNTA($A143:$L143)=0,0,IF(OR($B143="",$D143="",$F143="",$G143=""),1,0))</f>
         <v/>
       </c>
+      <c r="O143">
+        <f>IF(OR(AND($D143&lt;&gt;"",OR(LEN($D143)&lt;&gt;17,LEN($D143)-LEN(SUBSTITUTE($D143,":",""))&lt;&gt;5)),AND($E143&lt;&gt;"",OR(LEN($E143)&lt;&gt;17,LEN($E143)-LEN(SUBSTITUTE($E143,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="N144">
         <f>IF(COUNTA($A144:$L144)=0,0,IF(OR($B144="",$D144="",$F144="",$G144=""),1,0))</f>
         <v/>
       </c>
+      <c r="O144">
+        <f>IF(OR(AND($D144&lt;&gt;"",OR(LEN($D144)&lt;&gt;17,LEN($D144)-LEN(SUBSTITUTE($D144,":",""))&lt;&gt;5)),AND($E144&lt;&gt;"",OR(LEN($E144)&lt;&gt;17,LEN($E144)-LEN(SUBSTITUTE($E144,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="N145">
         <f>IF(COUNTA($A145:$L145)=0,0,IF(OR($B145="",$D145="",$F145="",$G145=""),1,0))</f>
         <v/>
       </c>
+      <c r="O145">
+        <f>IF(OR(AND($D145&lt;&gt;"",OR(LEN($D145)&lt;&gt;17,LEN($D145)-LEN(SUBSTITUTE($D145,":",""))&lt;&gt;5)),AND($E145&lt;&gt;"",OR(LEN($E145)&lt;&gt;17,LEN($E145)-LEN(SUBSTITUTE($E145,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="N146">
         <f>IF(COUNTA($A146:$L146)=0,0,IF(OR($B146="",$D146="",$F146="",$G146=""),1,0))</f>
         <v/>
       </c>
+      <c r="O146">
+        <f>IF(OR(AND($D146&lt;&gt;"",OR(LEN($D146)&lt;&gt;17,LEN($D146)-LEN(SUBSTITUTE($D146,":",""))&lt;&gt;5)),AND($E146&lt;&gt;"",OR(LEN($E146)&lt;&gt;17,LEN($E146)-LEN(SUBSTITUTE($E146,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="147">
       <c r="N147">
         <f>IF(COUNTA($A147:$L147)=0,0,IF(OR($B147="",$D147="",$F147="",$G147=""),1,0))</f>
         <v/>
       </c>
+      <c r="O147">
+        <f>IF(OR(AND($D147&lt;&gt;"",OR(LEN($D147)&lt;&gt;17,LEN($D147)-LEN(SUBSTITUTE($D147,":",""))&lt;&gt;5)),AND($E147&lt;&gt;"",OR(LEN($E147)&lt;&gt;17,LEN($E147)-LEN(SUBSTITUTE($E147,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="N148">
         <f>IF(COUNTA($A148:$L148)=0,0,IF(OR($B148="",$D148="",$F148="",$G148=""),1,0))</f>
         <v/>
       </c>
+      <c r="O148">
+        <f>IF(OR(AND($D148&lt;&gt;"",OR(LEN($D148)&lt;&gt;17,LEN($D148)-LEN(SUBSTITUTE($D148,":",""))&lt;&gt;5)),AND($E148&lt;&gt;"",OR(LEN($E148)&lt;&gt;17,LEN($E148)-LEN(SUBSTITUTE($E148,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="149">
       <c r="N149">
         <f>IF(COUNTA($A149:$L149)=0,0,IF(OR($B149="",$D149="",$F149="",$G149=""),1,0))</f>
         <v/>
       </c>
+      <c r="O149">
+        <f>IF(OR(AND($D149&lt;&gt;"",OR(LEN($D149)&lt;&gt;17,LEN($D149)-LEN(SUBSTITUTE($D149,":",""))&lt;&gt;5)),AND($E149&lt;&gt;"",OR(LEN($E149)&lt;&gt;17,LEN($E149)-LEN(SUBSTITUTE($E149,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="150">
       <c r="N150">
         <f>IF(COUNTA($A150:$L150)=0,0,IF(OR($B150="",$D150="",$F150="",$G150=""),1,0))</f>
         <v/>
       </c>
+      <c r="O150">
+        <f>IF(OR(AND($D150&lt;&gt;"",OR(LEN($D150)&lt;&gt;17,LEN($D150)-LEN(SUBSTITUTE($D150,":",""))&lt;&gt;5)),AND($E150&lt;&gt;"",OR(LEN($E150)&lt;&gt;17,LEN($E150)-LEN(SUBSTITUTE($E150,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="151">
       <c r="N151">
         <f>IF(COUNTA($A151:$L151)=0,0,IF(OR($B151="",$D151="",$F151="",$G151=""),1,0))</f>
         <v/>
       </c>
+      <c r="O151">
+        <f>IF(OR(AND($D151&lt;&gt;"",OR(LEN($D151)&lt;&gt;17,LEN($D151)-LEN(SUBSTITUTE($D151,":",""))&lt;&gt;5)),AND($E151&lt;&gt;"",OR(LEN($E151)&lt;&gt;17,LEN($E151)-LEN(SUBSTITUTE($E151,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="152">
       <c r="N152">
         <f>IF(COUNTA($A152:$L152)=0,0,IF(OR($B152="",$D152="",$F152="",$G152=""),1,0))</f>
         <v/>
       </c>
+      <c r="O152">
+        <f>IF(OR(AND($D152&lt;&gt;"",OR(LEN($D152)&lt;&gt;17,LEN($D152)-LEN(SUBSTITUTE($D152,":",""))&lt;&gt;5)),AND($E152&lt;&gt;"",OR(LEN($E152)&lt;&gt;17,LEN($E152)-LEN(SUBSTITUTE($E152,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="153">
       <c r="N153">
         <f>IF(COUNTA($A153:$L153)=0,0,IF(OR($B153="",$D153="",$F153="",$G153=""),1,0))</f>
         <v/>
       </c>
+      <c r="O153">
+        <f>IF(OR(AND($D153&lt;&gt;"",OR(LEN($D153)&lt;&gt;17,LEN($D153)-LEN(SUBSTITUTE($D153,":",""))&lt;&gt;5)),AND($E153&lt;&gt;"",OR(LEN($E153)&lt;&gt;17,LEN($E153)-LEN(SUBSTITUTE($E153,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="154">
       <c r="N154">
         <f>IF(COUNTA($A154:$L154)=0,0,IF(OR($B154="",$D154="",$F154="",$G154=""),1,0))</f>
         <v/>
       </c>
+      <c r="O154">
+        <f>IF(OR(AND($D154&lt;&gt;"",OR(LEN($D154)&lt;&gt;17,LEN($D154)-LEN(SUBSTITUTE($D154,":",""))&lt;&gt;5)),AND($E154&lt;&gt;"",OR(LEN($E154)&lt;&gt;17,LEN($E154)-LEN(SUBSTITUTE($E154,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="155">
       <c r="N155">
         <f>IF(COUNTA($A155:$L155)=0,0,IF(OR($B155="",$D155="",$F155="",$G155=""),1,0))</f>
         <v/>
       </c>
+      <c r="O155">
+        <f>IF(OR(AND($D155&lt;&gt;"",OR(LEN($D155)&lt;&gt;17,LEN($D155)-LEN(SUBSTITUTE($D155,":",""))&lt;&gt;5)),AND($E155&lt;&gt;"",OR(LEN($E155)&lt;&gt;17,LEN($E155)-LEN(SUBSTITUTE($E155,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="156">
       <c r="N156">
         <f>IF(COUNTA($A156:$L156)=0,0,IF(OR($B156="",$D156="",$F156="",$G156=""),1,0))</f>
         <v/>
       </c>
+      <c r="O156">
+        <f>IF(OR(AND($D156&lt;&gt;"",OR(LEN($D156)&lt;&gt;17,LEN($D156)-LEN(SUBSTITUTE($D156,":",""))&lt;&gt;5)),AND($E156&lt;&gt;"",OR(LEN($E156)&lt;&gt;17,LEN($E156)-LEN(SUBSTITUTE($E156,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="157">
       <c r="N157">
         <f>IF(COUNTA($A157:$L157)=0,0,IF(OR($B157="",$D157="",$F157="",$G157=""),1,0))</f>
         <v/>
       </c>
+      <c r="O157">
+        <f>IF(OR(AND($D157&lt;&gt;"",OR(LEN($D157)&lt;&gt;17,LEN($D157)-LEN(SUBSTITUTE($D157,":",""))&lt;&gt;5)),AND($E157&lt;&gt;"",OR(LEN($E157)&lt;&gt;17,LEN($E157)-LEN(SUBSTITUTE($E157,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="158">
       <c r="N158">
         <f>IF(COUNTA($A158:$L158)=0,0,IF(OR($B158="",$D158="",$F158="",$G158=""),1,0))</f>
         <v/>
       </c>
+      <c r="O158">
+        <f>IF(OR(AND($D158&lt;&gt;"",OR(LEN($D158)&lt;&gt;17,LEN($D158)-LEN(SUBSTITUTE($D158,":",""))&lt;&gt;5)),AND($E158&lt;&gt;"",OR(LEN($E158)&lt;&gt;17,LEN($E158)-LEN(SUBSTITUTE($E158,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="159">
       <c r="N159">
         <f>IF(COUNTA($A159:$L159)=0,0,IF(OR($B159="",$D159="",$F159="",$G159=""),1,0))</f>
         <v/>
       </c>
+      <c r="O159">
+        <f>IF(OR(AND($D159&lt;&gt;"",OR(LEN($D159)&lt;&gt;17,LEN($D159)-LEN(SUBSTITUTE($D159,":",""))&lt;&gt;5)),AND($E159&lt;&gt;"",OR(LEN($E159)&lt;&gt;17,LEN($E159)-LEN(SUBSTITUTE($E159,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="160">
       <c r="N160">
         <f>IF(COUNTA($A160:$L160)=0,0,IF(OR($B160="",$D160="",$F160="",$G160=""),1,0))</f>
         <v/>
       </c>
+      <c r="O160">
+        <f>IF(OR(AND($D160&lt;&gt;"",OR(LEN($D160)&lt;&gt;17,LEN($D160)-LEN(SUBSTITUTE($D160,":",""))&lt;&gt;5)),AND($E160&lt;&gt;"",OR(LEN($E160)&lt;&gt;17,LEN($E160)-LEN(SUBSTITUTE($E160,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="161">
       <c r="N161">
         <f>IF(COUNTA($A161:$L161)=0,0,IF(OR($B161="",$D161="",$F161="",$G161=""),1,0))</f>
         <v/>
       </c>
+      <c r="O161">
+        <f>IF(OR(AND($D161&lt;&gt;"",OR(LEN($D161)&lt;&gt;17,LEN($D161)-LEN(SUBSTITUTE($D161,":",""))&lt;&gt;5)),AND($E161&lt;&gt;"",OR(LEN($E161)&lt;&gt;17,LEN($E161)-LEN(SUBSTITUTE($E161,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="162">
       <c r="N162">
         <f>IF(COUNTA($A162:$L162)=0,0,IF(OR($B162="",$D162="",$F162="",$G162=""),1,0))</f>
         <v/>
       </c>
+      <c r="O162">
+        <f>IF(OR(AND($D162&lt;&gt;"",OR(LEN($D162)&lt;&gt;17,LEN($D162)-LEN(SUBSTITUTE($D162,":",""))&lt;&gt;5)),AND($E162&lt;&gt;"",OR(LEN($E162)&lt;&gt;17,LEN($E162)-LEN(SUBSTITUTE($E162,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="163">
       <c r="N163">
         <f>IF(COUNTA($A163:$L163)=0,0,IF(OR($B163="",$D163="",$F163="",$G163=""),1,0))</f>
         <v/>
       </c>
+      <c r="O163">
+        <f>IF(OR(AND($D163&lt;&gt;"",OR(LEN($D163)&lt;&gt;17,LEN($D163)-LEN(SUBSTITUTE($D163,":",""))&lt;&gt;5)),AND($E163&lt;&gt;"",OR(LEN($E163)&lt;&gt;17,LEN($E163)-LEN(SUBSTITUTE($E163,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="164">
       <c r="N164">
         <f>IF(COUNTA($A164:$L164)=0,0,IF(OR($B164="",$D164="",$F164="",$G164=""),1,0))</f>
         <v/>
       </c>
+      <c r="O164">
+        <f>IF(OR(AND($D164&lt;&gt;"",OR(LEN($D164)&lt;&gt;17,LEN($D164)-LEN(SUBSTITUTE($D164,":",""))&lt;&gt;5)),AND($E164&lt;&gt;"",OR(LEN($E164)&lt;&gt;17,LEN($E164)-LEN(SUBSTITUTE($E164,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="165">
       <c r="N165">
         <f>IF(COUNTA($A165:$L165)=0,0,IF(OR($B165="",$D165="",$F165="",$G165=""),1,0))</f>
         <v/>
       </c>
+      <c r="O165">
+        <f>IF(OR(AND($D165&lt;&gt;"",OR(LEN($D165)&lt;&gt;17,LEN($D165)-LEN(SUBSTITUTE($D165,":",""))&lt;&gt;5)),AND($E165&lt;&gt;"",OR(LEN($E165)&lt;&gt;17,LEN($E165)-LEN(SUBSTITUTE($E165,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="166">
       <c r="N166">
         <f>IF(COUNTA($A166:$L166)=0,0,IF(OR($B166="",$D166="",$F166="",$G166=""),1,0))</f>
         <v/>
       </c>
+      <c r="O166">
+        <f>IF(OR(AND($D166&lt;&gt;"",OR(LEN($D166)&lt;&gt;17,LEN($D166)-LEN(SUBSTITUTE($D166,":",""))&lt;&gt;5)),AND($E166&lt;&gt;"",OR(LEN($E166)&lt;&gt;17,LEN($E166)-LEN(SUBSTITUTE($E166,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="167">
       <c r="N167">
         <f>IF(COUNTA($A167:$L167)=0,0,IF(OR($B167="",$D167="",$F167="",$G167=""),1,0))</f>
         <v/>
       </c>
+      <c r="O167">
+        <f>IF(OR(AND($D167&lt;&gt;"",OR(LEN($D167)&lt;&gt;17,LEN($D167)-LEN(SUBSTITUTE($D167,":",""))&lt;&gt;5)),AND($E167&lt;&gt;"",OR(LEN($E167)&lt;&gt;17,LEN($E167)-LEN(SUBSTITUTE($E167,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="168">
       <c r="N168">
         <f>IF(COUNTA($A168:$L168)=0,0,IF(OR($B168="",$D168="",$F168="",$G168=""),1,0))</f>
         <v/>
       </c>
+      <c r="O168">
+        <f>IF(OR(AND($D168&lt;&gt;"",OR(LEN($D168)&lt;&gt;17,LEN($D168)-LEN(SUBSTITUTE($D168,":",""))&lt;&gt;5)),AND($E168&lt;&gt;"",OR(LEN($E168)&lt;&gt;17,LEN($E168)-LEN(SUBSTITUTE($E168,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="169">
       <c r="N169">
         <f>IF(COUNTA($A169:$L169)=0,0,IF(OR($B169="",$D169="",$F169="",$G169=""),1,0))</f>
         <v/>
       </c>
+      <c r="O169">
+        <f>IF(OR(AND($D169&lt;&gt;"",OR(LEN($D169)&lt;&gt;17,LEN($D169)-LEN(SUBSTITUTE($D169,":",""))&lt;&gt;5)),AND($E169&lt;&gt;"",OR(LEN($E169)&lt;&gt;17,LEN($E169)-LEN(SUBSTITUTE($E169,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="170">
       <c r="N170">
         <f>IF(COUNTA($A170:$L170)=0,0,IF(OR($B170="",$D170="",$F170="",$G170=""),1,0))</f>
         <v/>
       </c>
+      <c r="O170">
+        <f>IF(OR(AND($D170&lt;&gt;"",OR(LEN($D170)&lt;&gt;17,LEN($D170)-LEN(SUBSTITUTE($D170,":",""))&lt;&gt;5)),AND($E170&lt;&gt;"",OR(LEN($E170)&lt;&gt;17,LEN($E170)-LEN(SUBSTITUTE($E170,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="171">
       <c r="N171">
         <f>IF(COUNTA($A171:$L171)=0,0,IF(OR($B171="",$D171="",$F171="",$G171=""),1,0))</f>
         <v/>
       </c>
+      <c r="O171">
+        <f>IF(OR(AND($D171&lt;&gt;"",OR(LEN($D171)&lt;&gt;17,LEN($D171)-LEN(SUBSTITUTE($D171,":",""))&lt;&gt;5)),AND($E171&lt;&gt;"",OR(LEN($E171)&lt;&gt;17,LEN($E171)-LEN(SUBSTITUTE($E171,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="172">
       <c r="N172">
         <f>IF(COUNTA($A172:$L172)=0,0,IF(OR($B172="",$D172="",$F172="",$G172=""),1,0))</f>
         <v/>
       </c>
+      <c r="O172">
+        <f>IF(OR(AND($D172&lt;&gt;"",OR(LEN($D172)&lt;&gt;17,LEN($D172)-LEN(SUBSTITUTE($D172,":",""))&lt;&gt;5)),AND($E172&lt;&gt;"",OR(LEN($E172)&lt;&gt;17,LEN($E172)-LEN(SUBSTITUTE($E172,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="173">
       <c r="N173">
         <f>IF(COUNTA($A173:$L173)=0,0,IF(OR($B173="",$D173="",$F173="",$G173=""),1,0))</f>
         <v/>
       </c>
+      <c r="O173">
+        <f>IF(OR(AND($D173&lt;&gt;"",OR(LEN($D173)&lt;&gt;17,LEN($D173)-LEN(SUBSTITUTE($D173,":",""))&lt;&gt;5)),AND($E173&lt;&gt;"",OR(LEN($E173)&lt;&gt;17,LEN($E173)-LEN(SUBSTITUTE($E173,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="174">
       <c r="N174">
         <f>IF(COUNTA($A174:$L174)=0,0,IF(OR($B174="",$D174="",$F174="",$G174=""),1,0))</f>
         <v/>
       </c>
+      <c r="O174">
+        <f>IF(OR(AND($D174&lt;&gt;"",OR(LEN($D174)&lt;&gt;17,LEN($D174)-LEN(SUBSTITUTE($D174,":",""))&lt;&gt;5)),AND($E174&lt;&gt;"",OR(LEN($E174)&lt;&gt;17,LEN($E174)-LEN(SUBSTITUTE($E174,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="175">
       <c r="N175">
         <f>IF(COUNTA($A175:$L175)=0,0,IF(OR($B175="",$D175="",$F175="",$G175=""),1,0))</f>
         <v/>
       </c>
+      <c r="O175">
+        <f>IF(OR(AND($D175&lt;&gt;"",OR(LEN($D175)&lt;&gt;17,LEN($D175)-LEN(SUBSTITUTE($D175,":",""))&lt;&gt;5)),AND($E175&lt;&gt;"",OR(LEN($E175)&lt;&gt;17,LEN($E175)-LEN(SUBSTITUTE($E175,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="176">
       <c r="N176">
         <f>IF(COUNTA($A176:$L176)=0,0,IF(OR($B176="",$D176="",$F176="",$G176=""),1,0))</f>
         <v/>
       </c>
+      <c r="O176">
+        <f>IF(OR(AND($D176&lt;&gt;"",OR(LEN($D176)&lt;&gt;17,LEN($D176)-LEN(SUBSTITUTE($D176,":",""))&lt;&gt;5)),AND($E176&lt;&gt;"",OR(LEN($E176)&lt;&gt;17,LEN($E176)-LEN(SUBSTITUTE($E176,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="177">
       <c r="N177">
         <f>IF(COUNTA($A177:$L177)=0,0,IF(OR($B177="",$D177="",$F177="",$G177=""),1,0))</f>
         <v/>
       </c>
+      <c r="O177">
+        <f>IF(OR(AND($D177&lt;&gt;"",OR(LEN($D177)&lt;&gt;17,LEN($D177)-LEN(SUBSTITUTE($D177,":",""))&lt;&gt;5)),AND($E177&lt;&gt;"",OR(LEN($E177)&lt;&gt;17,LEN($E177)-LEN(SUBSTITUTE($E177,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="178">
       <c r="N178">
         <f>IF(COUNTA($A178:$L178)=0,0,IF(OR($B178="",$D178="",$F178="",$G178=""),1,0))</f>
         <v/>
       </c>
+      <c r="O178">
+        <f>IF(OR(AND($D178&lt;&gt;"",OR(LEN($D178)&lt;&gt;17,LEN($D178)-LEN(SUBSTITUTE($D178,":",""))&lt;&gt;5)),AND($E178&lt;&gt;"",OR(LEN($E178)&lt;&gt;17,LEN($E178)-LEN(SUBSTITUTE($E178,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="179">
       <c r="N179">
         <f>IF(COUNTA($A179:$L179)=0,0,IF(OR($B179="",$D179="",$F179="",$G179=""),1,0))</f>
         <v/>
       </c>
+      <c r="O179">
+        <f>IF(OR(AND($D179&lt;&gt;"",OR(LEN($D179)&lt;&gt;17,LEN($D179)-LEN(SUBSTITUTE($D179,":",""))&lt;&gt;5)),AND($E179&lt;&gt;"",OR(LEN($E179)&lt;&gt;17,LEN($E179)-LEN(SUBSTITUTE($E179,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="180">
       <c r="N180">
         <f>IF(COUNTA($A180:$L180)=0,0,IF(OR($B180="",$D180="",$F180="",$G180=""),1,0))</f>
         <v/>
       </c>
+      <c r="O180">
+        <f>IF(OR(AND($D180&lt;&gt;"",OR(LEN($D180)&lt;&gt;17,LEN($D180)-LEN(SUBSTITUTE($D180,":",""))&lt;&gt;5)),AND($E180&lt;&gt;"",OR(LEN($E180)&lt;&gt;17,LEN($E180)-LEN(SUBSTITUTE($E180,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="181">
       <c r="N181">
         <f>IF(COUNTA($A181:$L181)=0,0,IF(OR($B181="",$D181="",$F181="",$G181=""),1,0))</f>
         <v/>
       </c>
+      <c r="O181">
+        <f>IF(OR(AND($D181&lt;&gt;"",OR(LEN($D181)&lt;&gt;17,LEN($D181)-LEN(SUBSTITUTE($D181,":",""))&lt;&gt;5)),AND($E181&lt;&gt;"",OR(LEN($E181)&lt;&gt;17,LEN($E181)-LEN(SUBSTITUTE($E181,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="182">
       <c r="N182">
         <f>IF(COUNTA($A182:$L182)=0,0,IF(OR($B182="",$D182="",$F182="",$G182=""),1,0))</f>
         <v/>
       </c>
+      <c r="O182">
+        <f>IF(OR(AND($D182&lt;&gt;"",OR(LEN($D182)&lt;&gt;17,LEN($D182)-LEN(SUBSTITUTE($D182,":",""))&lt;&gt;5)),AND($E182&lt;&gt;"",OR(LEN($E182)&lt;&gt;17,LEN($E182)-LEN(SUBSTITUTE($E182,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="183">
       <c r="N183">
         <f>IF(COUNTA($A183:$L183)=0,0,IF(OR($B183="",$D183="",$F183="",$G183=""),1,0))</f>
         <v/>
       </c>
+      <c r="O183">
+        <f>IF(OR(AND($D183&lt;&gt;"",OR(LEN($D183)&lt;&gt;17,LEN($D183)-LEN(SUBSTITUTE($D183,":",""))&lt;&gt;5)),AND($E183&lt;&gt;"",OR(LEN($E183)&lt;&gt;17,LEN($E183)-LEN(SUBSTITUTE($E183,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="184">
       <c r="N184">
         <f>IF(COUNTA($A184:$L184)=0,0,IF(OR($B184="",$D184="",$F184="",$G184=""),1,0))</f>
         <v/>
       </c>
+      <c r="O184">
+        <f>IF(OR(AND($D184&lt;&gt;"",OR(LEN($D184)&lt;&gt;17,LEN($D184)-LEN(SUBSTITUTE($D184,":",""))&lt;&gt;5)),AND($E184&lt;&gt;"",OR(LEN($E184)&lt;&gt;17,LEN($E184)-LEN(SUBSTITUTE($E184,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="185">
       <c r="N185">
         <f>IF(COUNTA($A185:$L185)=0,0,IF(OR($B185="",$D185="",$F185="",$G185=""),1,0))</f>
         <v/>
       </c>
+      <c r="O185">
+        <f>IF(OR(AND($D185&lt;&gt;"",OR(LEN($D185)&lt;&gt;17,LEN($D185)-LEN(SUBSTITUTE($D185,":",""))&lt;&gt;5)),AND($E185&lt;&gt;"",OR(LEN($E185)&lt;&gt;17,LEN($E185)-LEN(SUBSTITUTE($E185,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="186">
       <c r="N186">
         <f>IF(COUNTA($A186:$L186)=0,0,IF(OR($B186="",$D186="",$F186="",$G186=""),1,0))</f>
         <v/>
       </c>
+      <c r="O186">
+        <f>IF(OR(AND($D186&lt;&gt;"",OR(LEN($D186)&lt;&gt;17,LEN($D186)-LEN(SUBSTITUTE($D186,":",""))&lt;&gt;5)),AND($E186&lt;&gt;"",OR(LEN($E186)&lt;&gt;17,LEN($E186)-LEN(SUBSTITUTE($E186,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="187">
       <c r="N187">
         <f>IF(COUNTA($A187:$L187)=0,0,IF(OR($B187="",$D187="",$F187="",$G187=""),1,0))</f>
         <v/>
       </c>
+      <c r="O187">
+        <f>IF(OR(AND($D187&lt;&gt;"",OR(LEN($D187)&lt;&gt;17,LEN($D187)-LEN(SUBSTITUTE($D187,":",""))&lt;&gt;5)),AND($E187&lt;&gt;"",OR(LEN($E187)&lt;&gt;17,LEN($E187)-LEN(SUBSTITUTE($E187,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="188">
       <c r="N188">
         <f>IF(COUNTA($A188:$L188)=0,0,IF(OR($B188="",$D188="",$F188="",$G188=""),1,0))</f>
         <v/>
       </c>
+      <c r="O188">
+        <f>IF(OR(AND($D188&lt;&gt;"",OR(LEN($D188)&lt;&gt;17,LEN($D188)-LEN(SUBSTITUTE($D188,":",""))&lt;&gt;5)),AND($E188&lt;&gt;"",OR(LEN($E188)&lt;&gt;17,LEN($E188)-LEN(SUBSTITUTE($E188,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="189">
       <c r="N189">
         <f>IF(COUNTA($A189:$L189)=0,0,IF(OR($B189="",$D189="",$F189="",$G189=""),1,0))</f>
         <v/>
       </c>
+      <c r="O189">
+        <f>IF(OR(AND($D189&lt;&gt;"",OR(LEN($D189)&lt;&gt;17,LEN($D189)-LEN(SUBSTITUTE($D189,":",""))&lt;&gt;5)),AND($E189&lt;&gt;"",OR(LEN($E189)&lt;&gt;17,LEN($E189)-LEN(SUBSTITUTE($E189,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="190">
       <c r="N190">
         <f>IF(COUNTA($A190:$L190)=0,0,IF(OR($B190="",$D190="",$F190="",$G190=""),1,0))</f>
         <v/>
       </c>
+      <c r="O190">
+        <f>IF(OR(AND($D190&lt;&gt;"",OR(LEN($D190)&lt;&gt;17,LEN($D190)-LEN(SUBSTITUTE($D190,":",""))&lt;&gt;5)),AND($E190&lt;&gt;"",OR(LEN($E190)&lt;&gt;17,LEN($E190)-LEN(SUBSTITUTE($E190,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="191">
       <c r="N191">
         <f>IF(COUNTA($A191:$L191)=0,0,IF(OR($B191="",$D191="",$F191="",$G191=""),1,0))</f>
         <v/>
       </c>
+      <c r="O191">
+        <f>IF(OR(AND($D191&lt;&gt;"",OR(LEN($D191)&lt;&gt;17,LEN($D191)-LEN(SUBSTITUTE($D191,":",""))&lt;&gt;5)),AND($E191&lt;&gt;"",OR(LEN($E191)&lt;&gt;17,LEN($E191)-LEN(SUBSTITUTE($E191,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="192">
       <c r="N192">
         <f>IF(COUNTA($A192:$L192)=0,0,IF(OR($B192="",$D192="",$F192="",$G192=""),1,0))</f>
         <v/>
       </c>
+      <c r="O192">
+        <f>IF(OR(AND($D192&lt;&gt;"",OR(LEN($D192)&lt;&gt;17,LEN($D192)-LEN(SUBSTITUTE($D192,":",""))&lt;&gt;5)),AND($E192&lt;&gt;"",OR(LEN($E192)&lt;&gt;17,LEN($E192)-LEN(SUBSTITUTE($E192,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="193">
       <c r="N193">
         <f>IF(COUNTA($A193:$L193)=0,0,IF(OR($B193="",$D193="",$F193="",$G193=""),1,0))</f>
         <v/>
       </c>
+      <c r="O193">
+        <f>IF(OR(AND($D193&lt;&gt;"",OR(LEN($D193)&lt;&gt;17,LEN($D193)-LEN(SUBSTITUTE($D193,":",""))&lt;&gt;5)),AND($E193&lt;&gt;"",OR(LEN($E193)&lt;&gt;17,LEN($E193)-LEN(SUBSTITUTE($E193,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="194">
       <c r="N194">
         <f>IF(COUNTA($A194:$L194)=0,0,IF(OR($B194="",$D194="",$F194="",$G194=""),1,0))</f>
         <v/>
       </c>
+      <c r="O194">
+        <f>IF(OR(AND($D194&lt;&gt;"",OR(LEN($D194)&lt;&gt;17,LEN($D194)-LEN(SUBSTITUTE($D194,":",""))&lt;&gt;5)),AND($E194&lt;&gt;"",OR(LEN($E194)&lt;&gt;17,LEN($E194)-LEN(SUBSTITUTE($E194,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="195">
       <c r="N195">
         <f>IF(COUNTA($A195:$L195)=0,0,IF(OR($B195="",$D195="",$F195="",$G195=""),1,0))</f>
         <v/>
       </c>
+      <c r="O195">
+        <f>IF(OR(AND($D195&lt;&gt;"",OR(LEN($D195)&lt;&gt;17,LEN($D195)-LEN(SUBSTITUTE($D195,":",""))&lt;&gt;5)),AND($E195&lt;&gt;"",OR(LEN($E195)&lt;&gt;17,LEN($E195)-LEN(SUBSTITUTE($E195,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="196">
       <c r="N196">
         <f>IF(COUNTA($A196:$L196)=0,0,IF(OR($B196="",$D196="",$F196="",$G196=""),1,0))</f>
         <v/>
       </c>
+      <c r="O196">
+        <f>IF(OR(AND($D196&lt;&gt;"",OR(LEN($D196)&lt;&gt;17,LEN($D196)-LEN(SUBSTITUTE($D196,":",""))&lt;&gt;5)),AND($E196&lt;&gt;"",OR(LEN($E196)&lt;&gt;17,LEN($E196)-LEN(SUBSTITUTE($E196,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="197">
       <c r="N197">
         <f>IF(COUNTA($A197:$L197)=0,0,IF(OR($B197="",$D197="",$F197="",$G197=""),1,0))</f>
         <v/>
       </c>
+      <c r="O197">
+        <f>IF(OR(AND($D197&lt;&gt;"",OR(LEN($D197)&lt;&gt;17,LEN($D197)-LEN(SUBSTITUTE($D197,":",""))&lt;&gt;5)),AND($E197&lt;&gt;"",OR(LEN($E197)&lt;&gt;17,LEN($E197)-LEN(SUBSTITUTE($E197,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="198">
       <c r="N198">
         <f>IF(COUNTA($A198:$L198)=0,0,IF(OR($B198="",$D198="",$F198="",$G198=""),1,0))</f>
         <v/>
       </c>
+      <c r="O198">
+        <f>IF(OR(AND($D198&lt;&gt;"",OR(LEN($D198)&lt;&gt;17,LEN($D198)-LEN(SUBSTITUTE($D198,":",""))&lt;&gt;5)),AND($E198&lt;&gt;"",OR(LEN($E198)&lt;&gt;17,LEN($E198)-LEN(SUBSTITUTE($E198,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="199">
       <c r="N199">
         <f>IF(COUNTA($A199:$L199)=0,0,IF(OR($B199="",$D199="",$F199="",$G199=""),1,0))</f>
         <v/>
       </c>
+      <c r="O199">
+        <f>IF(OR(AND($D199&lt;&gt;"",OR(LEN($D199)&lt;&gt;17,LEN($D199)-LEN(SUBSTITUTE($D199,":",""))&lt;&gt;5)),AND($E199&lt;&gt;"",OR(LEN($E199)&lt;&gt;17,LEN($E199)-LEN(SUBSTITUTE($E199,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="200">
       <c r="N200">
         <f>IF(COUNTA($A200:$L200)=0,0,IF(OR($B200="",$D200="",$F200="",$G200=""),1,0))</f>
         <v/>
       </c>
+      <c r="O200">
+        <f>IF(OR(AND($D200&lt;&gt;"",OR(LEN($D200)&lt;&gt;17,LEN($D200)-LEN(SUBSTITUTE($D200,":",""))&lt;&gt;5)),AND($E200&lt;&gt;"",OR(LEN($E200)&lt;&gt;17,LEN($E200)-LEN(SUBSTITUTE($E200,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="201">
       <c r="N201">
         <f>IF(COUNTA($A201:$L201)=0,0,IF(OR($B201="",$D201="",$F201="",$G201=""),1,0))</f>
         <v/>
       </c>
+      <c r="O201">
+        <f>IF(OR(AND($D201&lt;&gt;"",OR(LEN($D201)&lt;&gt;17,LEN($D201)-LEN(SUBSTITUTE($D201,":",""))&lt;&gt;5)),AND($E201&lt;&gt;"",OR(LEN($E201)&lt;&gt;17,LEN($E201)-LEN(SUBSTITUTE($E201,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="202">
       <c r="N202">
         <f>IF(COUNTA($A202:$L202)=0,0,IF(OR($B202="",$D202="",$F202="",$G202=""),1,0))</f>
         <v/>
       </c>
+      <c r="O202">
+        <f>IF(OR(AND($D202&lt;&gt;"",OR(LEN($D202)&lt;&gt;17,LEN($D202)-LEN(SUBSTITUTE($D202,":",""))&lt;&gt;5)),AND($E202&lt;&gt;"",OR(LEN($E202)&lt;&gt;17,LEN($E202)-LEN(SUBSTITUTE($E202,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="203">
       <c r="N203">
         <f>IF(COUNTA($A203:$L203)=0,0,IF(OR($B203="",$D203="",$F203="",$G203=""),1,0))</f>
         <v/>
       </c>
+      <c r="O203">
+        <f>IF(OR(AND($D203&lt;&gt;"",OR(LEN($D203)&lt;&gt;17,LEN($D203)-LEN(SUBSTITUTE($D203,":",""))&lt;&gt;5)),AND($E203&lt;&gt;"",OR(LEN($E203)&lt;&gt;17,LEN($E203)-LEN(SUBSTITUTE($E203,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="204">
       <c r="N204">
         <f>IF(COUNTA($A204:$L204)=0,0,IF(OR($B204="",$D204="",$F204="",$G204=""),1,0))</f>
         <v/>
       </c>
+      <c r="O204">
+        <f>IF(OR(AND($D204&lt;&gt;"",OR(LEN($D204)&lt;&gt;17,LEN($D204)-LEN(SUBSTITUTE($D204,":",""))&lt;&gt;5)),AND($E204&lt;&gt;"",OR(LEN($E204)&lt;&gt;17,LEN($E204)-LEN(SUBSTITUTE($E204,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="205">
       <c r="N205">
         <f>IF(COUNTA($A205:$L205)=0,0,IF(OR($B205="",$D205="",$F205="",$G205=""),1,0))</f>
         <v/>
       </c>
+      <c r="O205">
+        <f>IF(OR(AND($D205&lt;&gt;"",OR(LEN($D205)&lt;&gt;17,LEN($D205)-LEN(SUBSTITUTE($D205,":",""))&lt;&gt;5)),AND($E205&lt;&gt;"",OR(LEN($E205)&lt;&gt;17,LEN($E205)-LEN(SUBSTITUTE($E205,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="206">
       <c r="N206">
         <f>IF(COUNTA($A206:$L206)=0,0,IF(OR($B206="",$D206="",$F206="",$G206=""),1,0))</f>
         <v/>
       </c>
+      <c r="O206">
+        <f>IF(OR(AND($D206&lt;&gt;"",OR(LEN($D206)&lt;&gt;17,LEN($D206)-LEN(SUBSTITUTE($D206,":",""))&lt;&gt;5)),AND($E206&lt;&gt;"",OR(LEN($E206)&lt;&gt;17,LEN($E206)-LEN(SUBSTITUTE($E206,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="207">
       <c r="N207">
         <f>IF(COUNTA($A207:$L207)=0,0,IF(OR($B207="",$D207="",$F207="",$G207=""),1,0))</f>
         <v/>
       </c>
+      <c r="O207">
+        <f>IF(OR(AND($D207&lt;&gt;"",OR(LEN($D207)&lt;&gt;17,LEN($D207)-LEN(SUBSTITUTE($D207,":",""))&lt;&gt;5)),AND($E207&lt;&gt;"",OR(LEN($E207)&lt;&gt;17,LEN($E207)-LEN(SUBSTITUTE($E207,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="208">
       <c r="N208">
         <f>IF(COUNTA($A208:$L208)=0,0,IF(OR($B208="",$D208="",$F208="",$G208=""),1,0))</f>
         <v/>
       </c>
+      <c r="O208">
+        <f>IF(OR(AND($D208&lt;&gt;"",OR(LEN($D208)&lt;&gt;17,LEN($D208)-LEN(SUBSTITUTE($D208,":",""))&lt;&gt;5)),AND($E208&lt;&gt;"",OR(LEN($E208)&lt;&gt;17,LEN($E208)-LEN(SUBSTITUTE($E208,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="209">
       <c r="N209">
         <f>IF(COUNTA($A209:$L209)=0,0,IF(OR($B209="",$D209="",$F209="",$G209=""),1,0))</f>
         <v/>
       </c>
+      <c r="O209">
+        <f>IF(OR(AND($D209&lt;&gt;"",OR(LEN($D209)&lt;&gt;17,LEN($D209)-LEN(SUBSTITUTE($D209,":",""))&lt;&gt;5)),AND($E209&lt;&gt;"",OR(LEN($E209)&lt;&gt;17,LEN($E209)-LEN(SUBSTITUTE($E209,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="210">
       <c r="N210">
         <f>IF(COUNTA($A210:$L210)=0,0,IF(OR($B210="",$D210="",$F210="",$G210=""),1,0))</f>
         <v/>
       </c>
+      <c r="O210">
+        <f>IF(OR(AND($D210&lt;&gt;"",OR(LEN($D210)&lt;&gt;17,LEN($D210)-LEN(SUBSTITUTE($D210,":",""))&lt;&gt;5)),AND($E210&lt;&gt;"",OR(LEN($E210)&lt;&gt;17,LEN($E210)-LEN(SUBSTITUTE($E210,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="211">
       <c r="N211">
         <f>IF(COUNTA($A211:$L211)=0,0,IF(OR($B211="",$D211="",$F211="",$G211=""),1,0))</f>
         <v/>
       </c>
+      <c r="O211">
+        <f>IF(OR(AND($D211&lt;&gt;"",OR(LEN($D211)&lt;&gt;17,LEN($D211)-LEN(SUBSTITUTE($D211,":",""))&lt;&gt;5)),AND($E211&lt;&gt;"",OR(LEN($E211)&lt;&gt;17,LEN($E211)-LEN(SUBSTITUTE($E211,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="212">
       <c r="N212">
         <f>IF(COUNTA($A212:$L212)=0,0,IF(OR($B212="",$D212="",$F212="",$G212=""),1,0))</f>
         <v/>
       </c>
+      <c r="O212">
+        <f>IF(OR(AND($D212&lt;&gt;"",OR(LEN($D212)&lt;&gt;17,LEN($D212)-LEN(SUBSTITUTE($D212,":",""))&lt;&gt;5)),AND($E212&lt;&gt;"",OR(LEN($E212)&lt;&gt;17,LEN($E212)-LEN(SUBSTITUTE($E212,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="213">
       <c r="N213">
         <f>IF(COUNTA($A213:$L213)=0,0,IF(OR($B213="",$D213="",$F213="",$G213=""),1,0))</f>
         <v/>
       </c>
+      <c r="O213">
+        <f>IF(OR(AND($D213&lt;&gt;"",OR(LEN($D213)&lt;&gt;17,LEN($D213)-LEN(SUBSTITUTE($D213,":",""))&lt;&gt;5)),AND($E213&lt;&gt;"",OR(LEN($E213)&lt;&gt;17,LEN($E213)-LEN(SUBSTITUTE($E213,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="214">
       <c r="N214">
         <f>IF(COUNTA($A214:$L214)=0,0,IF(OR($B214="",$D214="",$F214="",$G214=""),1,0))</f>
         <v/>
       </c>
+      <c r="O214">
+        <f>IF(OR(AND($D214&lt;&gt;"",OR(LEN($D214)&lt;&gt;17,LEN($D214)-LEN(SUBSTITUTE($D214,":",""))&lt;&gt;5)),AND($E214&lt;&gt;"",OR(LEN($E214)&lt;&gt;17,LEN($E214)-LEN(SUBSTITUTE($E214,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="215">
       <c r="N215">
         <f>IF(COUNTA($A215:$L215)=0,0,IF(OR($B215="",$D215="",$F215="",$G215=""),1,0))</f>
         <v/>
       </c>
+      <c r="O215">
+        <f>IF(OR(AND($D215&lt;&gt;"",OR(LEN($D215)&lt;&gt;17,LEN($D215)-LEN(SUBSTITUTE($D215,":",""))&lt;&gt;5)),AND($E215&lt;&gt;"",OR(LEN($E215)&lt;&gt;17,LEN($E215)-LEN(SUBSTITUTE($E215,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="216">
       <c r="N216">
         <f>IF(COUNTA($A216:$L216)=0,0,IF(OR($B216="",$D216="",$F216="",$G216=""),1,0))</f>
         <v/>
       </c>
+      <c r="O216">
+        <f>IF(OR(AND($D216&lt;&gt;"",OR(LEN($D216)&lt;&gt;17,LEN($D216)-LEN(SUBSTITUTE($D216,":",""))&lt;&gt;5)),AND($E216&lt;&gt;"",OR(LEN($E216)&lt;&gt;17,LEN($E216)-LEN(SUBSTITUTE($E216,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="217">
       <c r="N217">
         <f>IF(COUNTA($A217:$L217)=0,0,IF(OR($B217="",$D217="",$F217="",$G217=""),1,0))</f>
         <v/>
       </c>
+      <c r="O217">
+        <f>IF(OR(AND($D217&lt;&gt;"",OR(LEN($D217)&lt;&gt;17,LEN($D217)-LEN(SUBSTITUTE($D217,":",""))&lt;&gt;5)),AND($E217&lt;&gt;"",OR(LEN($E217)&lt;&gt;17,LEN($E217)-LEN(SUBSTITUTE($E217,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="218">
       <c r="N218">
         <f>IF(COUNTA($A218:$L218)=0,0,IF(OR($B218="",$D218="",$F218="",$G218=""),1,0))</f>
         <v/>
       </c>
+      <c r="O218">
+        <f>IF(OR(AND($D218&lt;&gt;"",OR(LEN($D218)&lt;&gt;17,LEN($D218)-LEN(SUBSTITUTE($D218,":",""))&lt;&gt;5)),AND($E218&lt;&gt;"",OR(LEN($E218)&lt;&gt;17,LEN($E218)-LEN(SUBSTITUTE($E218,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="219">
       <c r="N219">
         <f>IF(COUNTA($A219:$L219)=0,0,IF(OR($B219="",$D219="",$F219="",$G219=""),1,0))</f>
         <v/>
       </c>
+      <c r="O219">
+        <f>IF(OR(AND($D219&lt;&gt;"",OR(LEN($D219)&lt;&gt;17,LEN($D219)-LEN(SUBSTITUTE($D219,":",""))&lt;&gt;5)),AND($E219&lt;&gt;"",OR(LEN($E219)&lt;&gt;17,LEN($E219)-LEN(SUBSTITUTE($E219,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="220">
       <c r="N220">
         <f>IF(COUNTA($A220:$L220)=0,0,IF(OR($B220="",$D220="",$F220="",$G220=""),1,0))</f>
         <v/>
       </c>
+      <c r="O220">
+        <f>IF(OR(AND($D220&lt;&gt;"",OR(LEN($D220)&lt;&gt;17,LEN($D220)-LEN(SUBSTITUTE($D220,":",""))&lt;&gt;5)),AND($E220&lt;&gt;"",OR(LEN($E220)&lt;&gt;17,LEN($E220)-LEN(SUBSTITUTE($E220,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="221">
       <c r="N221">
         <f>IF(COUNTA($A221:$L221)=0,0,IF(OR($B221="",$D221="",$F221="",$G221=""),1,0))</f>
         <v/>
       </c>
+      <c r="O221">
+        <f>IF(OR(AND($D221&lt;&gt;"",OR(LEN($D221)&lt;&gt;17,LEN($D221)-LEN(SUBSTITUTE($D221,":",""))&lt;&gt;5)),AND($E221&lt;&gt;"",OR(LEN($E221)&lt;&gt;17,LEN($E221)-LEN(SUBSTITUTE($E221,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="222">
       <c r="N222">
         <f>IF(COUNTA($A222:$L222)=0,0,IF(OR($B222="",$D222="",$F222="",$G222=""),1,0))</f>
         <v/>
       </c>
+      <c r="O222">
+        <f>IF(OR(AND($D222&lt;&gt;"",OR(LEN($D222)&lt;&gt;17,LEN($D222)-LEN(SUBSTITUTE($D222,":",""))&lt;&gt;5)),AND($E222&lt;&gt;"",OR(LEN($E222)&lt;&gt;17,LEN($E222)-LEN(SUBSTITUTE($E222,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="223">
       <c r="N223">
         <f>IF(COUNTA($A223:$L223)=0,0,IF(OR($B223="",$D223="",$F223="",$G223=""),1,0))</f>
         <v/>
       </c>
+      <c r="O223">
+        <f>IF(OR(AND($D223&lt;&gt;"",OR(LEN($D223)&lt;&gt;17,LEN($D223)-LEN(SUBSTITUTE($D223,":",""))&lt;&gt;5)),AND($E223&lt;&gt;"",OR(LEN($E223)&lt;&gt;17,LEN($E223)-LEN(SUBSTITUTE($E223,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="224">
       <c r="N224">
         <f>IF(COUNTA($A224:$L224)=0,0,IF(OR($B224="",$D224="",$F224="",$G224=""),1,0))</f>
         <v/>
       </c>
+      <c r="O224">
+        <f>IF(OR(AND($D224&lt;&gt;"",OR(LEN($D224)&lt;&gt;17,LEN($D224)-LEN(SUBSTITUTE($D224,":",""))&lt;&gt;5)),AND($E224&lt;&gt;"",OR(LEN($E224)&lt;&gt;17,LEN($E224)-LEN(SUBSTITUTE($E224,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="225">
       <c r="N225">
         <f>IF(COUNTA($A225:$L225)=0,0,IF(OR($B225="",$D225="",$F225="",$G225=""),1,0))</f>
         <v/>
       </c>
+      <c r="O225">
+        <f>IF(OR(AND($D225&lt;&gt;"",OR(LEN($D225)&lt;&gt;17,LEN($D225)-LEN(SUBSTITUTE($D225,":",""))&lt;&gt;5)),AND($E225&lt;&gt;"",OR(LEN($E225)&lt;&gt;17,LEN($E225)-LEN(SUBSTITUTE($E225,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="226">
       <c r="N226">
         <f>IF(COUNTA($A226:$L226)=0,0,IF(OR($B226="",$D226="",$F226="",$G226=""),1,0))</f>
         <v/>
       </c>
+      <c r="O226">
+        <f>IF(OR(AND($D226&lt;&gt;"",OR(LEN($D226)&lt;&gt;17,LEN($D226)-LEN(SUBSTITUTE($D226,":",""))&lt;&gt;5)),AND($E226&lt;&gt;"",OR(LEN($E226)&lt;&gt;17,LEN($E226)-LEN(SUBSTITUTE($E226,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="227">
       <c r="N227">
         <f>IF(COUNTA($A227:$L227)=0,0,IF(OR($B227="",$D227="",$F227="",$G227=""),1,0))</f>
         <v/>
       </c>
+      <c r="O227">
+        <f>IF(OR(AND($D227&lt;&gt;"",OR(LEN($D227)&lt;&gt;17,LEN($D227)-LEN(SUBSTITUTE($D227,":",""))&lt;&gt;5)),AND($E227&lt;&gt;"",OR(LEN($E227)&lt;&gt;17,LEN($E227)-LEN(SUBSTITUTE($E227,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="228">
       <c r="N228">
         <f>IF(COUNTA($A228:$L228)=0,0,IF(OR($B228="",$D228="",$F228="",$G228=""),1,0))</f>
         <v/>
       </c>
+      <c r="O228">
+        <f>IF(OR(AND($D228&lt;&gt;"",OR(LEN($D228)&lt;&gt;17,LEN($D228)-LEN(SUBSTITUTE($D228,":",""))&lt;&gt;5)),AND($E228&lt;&gt;"",OR(LEN($E228)&lt;&gt;17,LEN($E228)-LEN(SUBSTITUTE($E228,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="229">
       <c r="N229">
         <f>IF(COUNTA($A229:$L229)=0,0,IF(OR($B229="",$D229="",$F229="",$G229=""),1,0))</f>
         <v/>
       </c>
+      <c r="O229">
+        <f>IF(OR(AND($D229&lt;&gt;"",OR(LEN($D229)&lt;&gt;17,LEN($D229)-LEN(SUBSTITUTE($D229,":",""))&lt;&gt;5)),AND($E229&lt;&gt;"",OR(LEN($E229)&lt;&gt;17,LEN($E229)-LEN(SUBSTITUTE($E229,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="230">
       <c r="N230">
         <f>IF(COUNTA($A230:$L230)=0,0,IF(OR($B230="",$D230="",$F230="",$G230=""),1,0))</f>
         <v/>
       </c>
+      <c r="O230">
+        <f>IF(OR(AND($D230&lt;&gt;"",OR(LEN($D230)&lt;&gt;17,LEN($D230)-LEN(SUBSTITUTE($D230,":",""))&lt;&gt;5)),AND($E230&lt;&gt;"",OR(LEN($E230)&lt;&gt;17,LEN($E230)-LEN(SUBSTITUTE($E230,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="231">
       <c r="N231">
         <f>IF(COUNTA($A231:$L231)=0,0,IF(OR($B231="",$D231="",$F231="",$G231=""),1,0))</f>
         <v/>
       </c>
+      <c r="O231">
+        <f>IF(OR(AND($D231&lt;&gt;"",OR(LEN($D231)&lt;&gt;17,LEN($D231)-LEN(SUBSTITUTE($D231,":",""))&lt;&gt;5)),AND($E231&lt;&gt;"",OR(LEN($E231)&lt;&gt;17,LEN($E231)-LEN(SUBSTITUTE($E231,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="232">
       <c r="N232">
         <f>IF(COUNTA($A232:$L232)=0,0,IF(OR($B232="",$D232="",$F232="",$G232=""),1,0))</f>
         <v/>
       </c>
+      <c r="O232">
+        <f>IF(OR(AND($D232&lt;&gt;"",OR(LEN($D232)&lt;&gt;17,LEN($D232)-LEN(SUBSTITUTE($D232,":",""))&lt;&gt;5)),AND($E232&lt;&gt;"",OR(LEN($E232)&lt;&gt;17,LEN($E232)-LEN(SUBSTITUTE($E232,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="233">
       <c r="N233">
         <f>IF(COUNTA($A233:$L233)=0,0,IF(OR($B233="",$D233="",$F233="",$G233=""),1,0))</f>
         <v/>
       </c>
+      <c r="O233">
+        <f>IF(OR(AND($D233&lt;&gt;"",OR(LEN($D233)&lt;&gt;17,LEN($D233)-LEN(SUBSTITUTE($D233,":",""))&lt;&gt;5)),AND($E233&lt;&gt;"",OR(LEN($E233)&lt;&gt;17,LEN($E233)-LEN(SUBSTITUTE($E233,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="234">
       <c r="N234">
         <f>IF(COUNTA($A234:$L234)=0,0,IF(OR($B234="",$D234="",$F234="",$G234=""),1,0))</f>
         <v/>
       </c>
+      <c r="O234">
+        <f>IF(OR(AND($D234&lt;&gt;"",OR(LEN($D234)&lt;&gt;17,LEN($D234)-LEN(SUBSTITUTE($D234,":",""))&lt;&gt;5)),AND($E234&lt;&gt;"",OR(LEN($E234)&lt;&gt;17,LEN($E234)-LEN(SUBSTITUTE($E234,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="235">
       <c r="N235">
         <f>IF(COUNTA($A235:$L235)=0,0,IF(OR($B235="",$D235="",$F235="",$G235=""),1,0))</f>
         <v/>
       </c>
+      <c r="O235">
+        <f>IF(OR(AND($D235&lt;&gt;"",OR(LEN($D235)&lt;&gt;17,LEN($D235)-LEN(SUBSTITUTE($D235,":",""))&lt;&gt;5)),AND($E235&lt;&gt;"",OR(LEN($E235)&lt;&gt;17,LEN($E235)-LEN(SUBSTITUTE($E235,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="236">
       <c r="N236">
         <f>IF(COUNTA($A236:$L236)=0,0,IF(OR($B236="",$D236="",$F236="",$G236=""),1,0))</f>
         <v/>
       </c>
+      <c r="O236">
+        <f>IF(OR(AND($D236&lt;&gt;"",OR(LEN($D236)&lt;&gt;17,LEN($D236)-LEN(SUBSTITUTE($D236,":",""))&lt;&gt;5)),AND($E236&lt;&gt;"",OR(LEN($E236)&lt;&gt;17,LEN($E236)-LEN(SUBSTITUTE($E236,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="237">
       <c r="N237">
         <f>IF(COUNTA($A237:$L237)=0,0,IF(OR($B237="",$D237="",$F237="",$G237=""),1,0))</f>
         <v/>
       </c>
+      <c r="O237">
+        <f>IF(OR(AND($D237&lt;&gt;"",OR(LEN($D237)&lt;&gt;17,LEN($D237)-LEN(SUBSTITUTE($D237,":",""))&lt;&gt;5)),AND($E237&lt;&gt;"",OR(LEN($E237)&lt;&gt;17,LEN($E237)-LEN(SUBSTITUTE($E237,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="238">
       <c r="N238">
         <f>IF(COUNTA($A238:$L238)=0,0,IF(OR($B238="",$D238="",$F238="",$G238=""),1,0))</f>
         <v/>
       </c>
+      <c r="O238">
+        <f>IF(OR(AND($D238&lt;&gt;"",OR(LEN($D238)&lt;&gt;17,LEN($D238)-LEN(SUBSTITUTE($D238,":",""))&lt;&gt;5)),AND($E238&lt;&gt;"",OR(LEN($E238)&lt;&gt;17,LEN($E238)-LEN(SUBSTITUTE($E238,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="239">
       <c r="N239">
         <f>IF(COUNTA($A239:$L239)=0,0,IF(OR($B239="",$D239="",$F239="",$G239=""),1,0))</f>
         <v/>
       </c>
+      <c r="O239">
+        <f>IF(OR(AND($D239&lt;&gt;"",OR(LEN($D239)&lt;&gt;17,LEN($D239)-LEN(SUBSTITUTE($D239,":",""))&lt;&gt;5)),AND($E239&lt;&gt;"",OR(LEN($E239)&lt;&gt;17,LEN($E239)-LEN(SUBSTITUTE($E239,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="240">
       <c r="N240">
         <f>IF(COUNTA($A240:$L240)=0,0,IF(OR($B240="",$D240="",$F240="",$G240=""),1,0))</f>
         <v/>
       </c>
+      <c r="O240">
+        <f>IF(OR(AND($D240&lt;&gt;"",OR(LEN($D240)&lt;&gt;17,LEN($D240)-LEN(SUBSTITUTE($D240,":",""))&lt;&gt;5)),AND($E240&lt;&gt;"",OR(LEN($E240)&lt;&gt;17,LEN($E240)-LEN(SUBSTITUTE($E240,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="241">
       <c r="N241">
         <f>IF(COUNTA($A241:$L241)=0,0,IF(OR($B241="",$D241="",$F241="",$G241=""),1,0))</f>
         <v/>
       </c>
+      <c r="O241">
+        <f>IF(OR(AND($D241&lt;&gt;"",OR(LEN($D241)&lt;&gt;17,LEN($D241)-LEN(SUBSTITUTE($D241,":",""))&lt;&gt;5)),AND($E241&lt;&gt;"",OR(LEN($E241)&lt;&gt;17,LEN($E241)-LEN(SUBSTITUTE($E241,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="242">
       <c r="N242">
         <f>IF(COUNTA($A242:$L242)=0,0,IF(OR($B242="",$D242="",$F242="",$G242=""),1,0))</f>
         <v/>
       </c>
+      <c r="O242">
+        <f>IF(OR(AND($D242&lt;&gt;"",OR(LEN($D242)&lt;&gt;17,LEN($D242)-LEN(SUBSTITUTE($D242,":",""))&lt;&gt;5)),AND($E242&lt;&gt;"",OR(LEN($E242)&lt;&gt;17,LEN($E242)-LEN(SUBSTITUTE($E242,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="243">
       <c r="N243">
         <f>IF(COUNTA($A243:$L243)=0,0,IF(OR($B243="",$D243="",$F243="",$G243=""),1,0))</f>
         <v/>
       </c>
+      <c r="O243">
+        <f>IF(OR(AND($D243&lt;&gt;"",OR(LEN($D243)&lt;&gt;17,LEN($D243)-LEN(SUBSTITUTE($D243,":",""))&lt;&gt;5)),AND($E243&lt;&gt;"",OR(LEN($E243)&lt;&gt;17,LEN($E243)-LEN(SUBSTITUTE($E243,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="244">
       <c r="N244">
         <f>IF(COUNTA($A244:$L244)=0,0,IF(OR($B244="",$D244="",$F244="",$G244=""),1,0))</f>
         <v/>
       </c>
+      <c r="O244">
+        <f>IF(OR(AND($D244&lt;&gt;"",OR(LEN($D244)&lt;&gt;17,LEN($D244)-LEN(SUBSTITUTE($D244,":",""))&lt;&gt;5)),AND($E244&lt;&gt;"",OR(LEN($E244)&lt;&gt;17,LEN($E244)-LEN(SUBSTITUTE($E244,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="245">
       <c r="N245">
         <f>IF(COUNTA($A245:$L245)=0,0,IF(OR($B245="",$D245="",$F245="",$G245=""),1,0))</f>
         <v/>
       </c>
+      <c r="O245">
+        <f>IF(OR(AND($D245&lt;&gt;"",OR(LEN($D245)&lt;&gt;17,LEN($D245)-LEN(SUBSTITUTE($D245,":",""))&lt;&gt;5)),AND($E245&lt;&gt;"",OR(LEN($E245)&lt;&gt;17,LEN($E245)-LEN(SUBSTITUTE($E245,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="246">
       <c r="N246">
         <f>IF(COUNTA($A246:$L246)=0,0,IF(OR($B246="",$D246="",$F246="",$G246=""),1,0))</f>
         <v/>
       </c>
+      <c r="O246">
+        <f>IF(OR(AND($D246&lt;&gt;"",OR(LEN($D246)&lt;&gt;17,LEN($D246)-LEN(SUBSTITUTE($D246,":",""))&lt;&gt;5)),AND($E246&lt;&gt;"",OR(LEN($E246)&lt;&gt;17,LEN($E246)-LEN(SUBSTITUTE($E246,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="247">
       <c r="N247">
         <f>IF(COUNTA($A247:$L247)=0,0,IF(OR($B247="",$D247="",$F247="",$G247=""),1,0))</f>
         <v/>
       </c>
+      <c r="O247">
+        <f>IF(OR(AND($D247&lt;&gt;"",OR(LEN($D247)&lt;&gt;17,LEN($D247)-LEN(SUBSTITUTE($D247,":",""))&lt;&gt;5)),AND($E247&lt;&gt;"",OR(LEN($E247)&lt;&gt;17,LEN($E247)-LEN(SUBSTITUTE($E247,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="248">
       <c r="N248">
         <f>IF(COUNTA($A248:$L248)=0,0,IF(OR($B248="",$D248="",$F248="",$G248=""),1,0))</f>
         <v/>
       </c>
+      <c r="O248">
+        <f>IF(OR(AND($D248&lt;&gt;"",OR(LEN($D248)&lt;&gt;17,LEN($D248)-LEN(SUBSTITUTE($D248,":",""))&lt;&gt;5)),AND($E248&lt;&gt;"",OR(LEN($E248)&lt;&gt;17,LEN($E248)-LEN(SUBSTITUTE($E248,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="249">
       <c r="N249">
         <f>IF(COUNTA($A249:$L249)=0,0,IF(OR($B249="",$D249="",$F249="",$G249=""),1,0))</f>
         <v/>
       </c>
+      <c r="O249">
+        <f>IF(OR(AND($D249&lt;&gt;"",OR(LEN($D249)&lt;&gt;17,LEN($D249)-LEN(SUBSTITUTE($D249,":",""))&lt;&gt;5)),AND($E249&lt;&gt;"",OR(LEN($E249)&lt;&gt;17,LEN($E249)-LEN(SUBSTITUTE($E249,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="250">
       <c r="N250">
         <f>IF(COUNTA($A250:$L250)=0,0,IF(OR($B250="",$D250="",$F250="",$G250=""),1,0))</f>
         <v/>
       </c>
+      <c r="O250">
+        <f>IF(OR(AND($D250&lt;&gt;"",OR(LEN($D250)&lt;&gt;17,LEN($D250)-LEN(SUBSTITUTE($D250,":",""))&lt;&gt;5)),AND($E250&lt;&gt;"",OR(LEN($E250)&lt;&gt;17,LEN($E250)-LEN(SUBSTITUTE($E250,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="251">
       <c r="N251">
         <f>IF(COUNTA($A251:$L251)=0,0,IF(OR($B251="",$D251="",$F251="",$G251=""),1,0))</f>
         <v/>
       </c>
+      <c r="O251">
+        <f>IF(OR(AND($D251&lt;&gt;"",OR(LEN($D251)&lt;&gt;17,LEN($D251)-LEN(SUBSTITUTE($D251,":",""))&lt;&gt;5)),AND($E251&lt;&gt;"",OR(LEN($E251)&lt;&gt;17,LEN($E251)-LEN(SUBSTITUTE($E251,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="252">
       <c r="N252">
         <f>IF(COUNTA($A252:$L252)=0,0,IF(OR($B252="",$D252="",$F252="",$G252=""),1,0))</f>
         <v/>
       </c>
+      <c r="O252">
+        <f>IF(OR(AND($D252&lt;&gt;"",OR(LEN($D252)&lt;&gt;17,LEN($D252)-LEN(SUBSTITUTE($D252,":",""))&lt;&gt;5)),AND($E252&lt;&gt;"",OR(LEN($E252)&lt;&gt;17,LEN($E252)-LEN(SUBSTITUTE($E252,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="253">
       <c r="N253">
         <f>IF(COUNTA($A253:$L253)=0,0,IF(OR($B253="",$D253="",$F253="",$G253=""),1,0))</f>
         <v/>
       </c>
+      <c r="O253">
+        <f>IF(OR(AND($D253&lt;&gt;"",OR(LEN($D253)&lt;&gt;17,LEN($D253)-LEN(SUBSTITUTE($D253,":",""))&lt;&gt;5)),AND($E253&lt;&gt;"",OR(LEN($E253)&lt;&gt;17,LEN($E253)-LEN(SUBSTITUTE($E253,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="254">
       <c r="N254">
         <f>IF(COUNTA($A254:$L254)=0,0,IF(OR($B254="",$D254="",$F254="",$G254=""),1,0))</f>
         <v/>
       </c>
+      <c r="O254">
+        <f>IF(OR(AND($D254&lt;&gt;"",OR(LEN($D254)&lt;&gt;17,LEN($D254)-LEN(SUBSTITUTE($D254,":",""))&lt;&gt;5)),AND($E254&lt;&gt;"",OR(LEN($E254)&lt;&gt;17,LEN($E254)-LEN(SUBSTITUTE($E254,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="255">
       <c r="N255">
         <f>IF(COUNTA($A255:$L255)=0,0,IF(OR($B255="",$D255="",$F255="",$G255=""),1,0))</f>
         <v/>
       </c>
+      <c r="O255">
+        <f>IF(OR(AND($D255&lt;&gt;"",OR(LEN($D255)&lt;&gt;17,LEN($D255)-LEN(SUBSTITUTE($D255,":",""))&lt;&gt;5)),AND($E255&lt;&gt;"",OR(LEN($E255)&lt;&gt;17,LEN($E255)-LEN(SUBSTITUTE($E255,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="256">
       <c r="N256">
         <f>IF(COUNTA($A256:$L256)=0,0,IF(OR($B256="",$D256="",$F256="",$G256=""),1,0))</f>
         <v/>
       </c>
+      <c r="O256">
+        <f>IF(OR(AND($D256&lt;&gt;"",OR(LEN($D256)&lt;&gt;17,LEN($D256)-LEN(SUBSTITUTE($D256,":",""))&lt;&gt;5)),AND($E256&lt;&gt;"",OR(LEN($E256)&lt;&gt;17,LEN($E256)-LEN(SUBSTITUTE($E256,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="257">
       <c r="N257">
         <f>IF(COUNTA($A257:$L257)=0,0,IF(OR($B257="",$D257="",$F257="",$G257=""),1,0))</f>
         <v/>
       </c>
+      <c r="O257">
+        <f>IF(OR(AND($D257&lt;&gt;"",OR(LEN($D257)&lt;&gt;17,LEN($D257)-LEN(SUBSTITUTE($D257,":",""))&lt;&gt;5)),AND($E257&lt;&gt;"",OR(LEN($E257)&lt;&gt;17,LEN($E257)-LEN(SUBSTITUTE($E257,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="258">
       <c r="N258">
         <f>IF(COUNTA($A258:$L258)=0,0,IF(OR($B258="",$D258="",$F258="",$G258=""),1,0))</f>
         <v/>
       </c>
+      <c r="O258">
+        <f>IF(OR(AND($D258&lt;&gt;"",OR(LEN($D258)&lt;&gt;17,LEN($D258)-LEN(SUBSTITUTE($D258,":",""))&lt;&gt;5)),AND($E258&lt;&gt;"",OR(LEN($E258)&lt;&gt;17,LEN($E258)-LEN(SUBSTITUTE($E258,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="259">
       <c r="N259">
         <f>IF(COUNTA($A259:$L259)=0,0,IF(OR($B259="",$D259="",$F259="",$G259=""),1,0))</f>
         <v/>
       </c>
+      <c r="O259">
+        <f>IF(OR(AND($D259&lt;&gt;"",OR(LEN($D259)&lt;&gt;17,LEN($D259)-LEN(SUBSTITUTE($D259,":",""))&lt;&gt;5)),AND($E259&lt;&gt;"",OR(LEN($E259)&lt;&gt;17,LEN($E259)-LEN(SUBSTITUTE($E259,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="260">
       <c r="N260">
         <f>IF(COUNTA($A260:$L260)=0,0,IF(OR($B260="",$D260="",$F260="",$G260=""),1,0))</f>
         <v/>
       </c>
+      <c r="O260">
+        <f>IF(OR(AND($D260&lt;&gt;"",OR(LEN($D260)&lt;&gt;17,LEN($D260)-LEN(SUBSTITUTE($D260,":",""))&lt;&gt;5)),AND($E260&lt;&gt;"",OR(LEN($E260)&lt;&gt;17,LEN($E260)-LEN(SUBSTITUTE($E260,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="261">
       <c r="N261">
         <f>IF(COUNTA($A261:$L261)=0,0,IF(OR($B261="",$D261="",$F261="",$G261=""),1,0))</f>
         <v/>
       </c>
+      <c r="O261">
+        <f>IF(OR(AND($D261&lt;&gt;"",OR(LEN($D261)&lt;&gt;17,LEN($D261)-LEN(SUBSTITUTE($D261,":",""))&lt;&gt;5)),AND($E261&lt;&gt;"",OR(LEN($E261)&lt;&gt;17,LEN($E261)-LEN(SUBSTITUTE($E261,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="262">
       <c r="N262">
         <f>IF(COUNTA($A262:$L262)=0,0,IF(OR($B262="",$D262="",$F262="",$G262=""),1,0))</f>
         <v/>
       </c>
+      <c r="O262">
+        <f>IF(OR(AND($D262&lt;&gt;"",OR(LEN($D262)&lt;&gt;17,LEN($D262)-LEN(SUBSTITUTE($D262,":",""))&lt;&gt;5)),AND($E262&lt;&gt;"",OR(LEN($E262)&lt;&gt;17,LEN($E262)-LEN(SUBSTITUTE($E262,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="263">
       <c r="N263">
         <f>IF(COUNTA($A263:$L263)=0,0,IF(OR($B263="",$D263="",$F263="",$G263=""),1,0))</f>
         <v/>
       </c>
+      <c r="O263">
+        <f>IF(OR(AND($D263&lt;&gt;"",OR(LEN($D263)&lt;&gt;17,LEN($D263)-LEN(SUBSTITUTE($D263,":",""))&lt;&gt;5)),AND($E263&lt;&gt;"",OR(LEN($E263)&lt;&gt;17,LEN($E263)-LEN(SUBSTITUTE($E263,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="264">
       <c r="N264">
         <f>IF(COUNTA($A264:$L264)=0,0,IF(OR($B264="",$D264="",$F264="",$G264=""),1,0))</f>
         <v/>
       </c>
+      <c r="O264">
+        <f>IF(OR(AND($D264&lt;&gt;"",OR(LEN($D264)&lt;&gt;17,LEN($D264)-LEN(SUBSTITUTE($D264,":",""))&lt;&gt;5)),AND($E264&lt;&gt;"",OR(LEN($E264)&lt;&gt;17,LEN($E264)-LEN(SUBSTITUTE($E264,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="265">
       <c r="N265">
         <f>IF(COUNTA($A265:$L265)=0,0,IF(OR($B265="",$D265="",$F265="",$G265=""),1,0))</f>
         <v/>
       </c>
+      <c r="O265">
+        <f>IF(OR(AND($D265&lt;&gt;"",OR(LEN($D265)&lt;&gt;17,LEN($D265)-LEN(SUBSTITUTE($D265,":",""))&lt;&gt;5)),AND($E265&lt;&gt;"",OR(LEN($E265)&lt;&gt;17,LEN($E265)-LEN(SUBSTITUTE($E265,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="266">
       <c r="N266">
         <f>IF(COUNTA($A266:$L266)=0,0,IF(OR($B266="",$D266="",$F266="",$G266=""),1,0))</f>
         <v/>
       </c>
+      <c r="O266">
+        <f>IF(OR(AND($D266&lt;&gt;"",OR(LEN($D266)&lt;&gt;17,LEN($D266)-LEN(SUBSTITUTE($D266,":",""))&lt;&gt;5)),AND($E266&lt;&gt;"",OR(LEN($E266)&lt;&gt;17,LEN($E266)-LEN(SUBSTITUTE($E266,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="267">
       <c r="N267">
         <f>IF(COUNTA($A267:$L267)=0,0,IF(OR($B267="",$D267="",$F267="",$G267=""),1,0))</f>
         <v/>
       </c>
+      <c r="O267">
+        <f>IF(OR(AND($D267&lt;&gt;"",OR(LEN($D267)&lt;&gt;17,LEN($D267)-LEN(SUBSTITUTE($D267,":",""))&lt;&gt;5)),AND($E267&lt;&gt;"",OR(LEN($E267)&lt;&gt;17,LEN($E267)-LEN(SUBSTITUTE($E267,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="268">
       <c r="N268">
         <f>IF(COUNTA($A268:$L268)=0,0,IF(OR($B268="",$D268="",$F268="",$G268=""),1,0))</f>
         <v/>
       </c>
+      <c r="O268">
+        <f>IF(OR(AND($D268&lt;&gt;"",OR(LEN($D268)&lt;&gt;17,LEN($D268)-LEN(SUBSTITUTE($D268,":",""))&lt;&gt;5)),AND($E268&lt;&gt;"",OR(LEN($E268)&lt;&gt;17,LEN($E268)-LEN(SUBSTITUTE($E268,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="269">
       <c r="N269">
         <f>IF(COUNTA($A269:$L269)=0,0,IF(OR($B269="",$D269="",$F269="",$G269=""),1,0))</f>
         <v/>
       </c>
+      <c r="O269">
+        <f>IF(OR(AND($D269&lt;&gt;"",OR(LEN($D269)&lt;&gt;17,LEN($D269)-LEN(SUBSTITUTE($D269,":",""))&lt;&gt;5)),AND($E269&lt;&gt;"",OR(LEN($E269)&lt;&gt;17,LEN($E269)-LEN(SUBSTITUTE($E269,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="270">
       <c r="N270">
         <f>IF(COUNTA($A270:$L270)=0,0,IF(OR($B270="",$D270="",$F270="",$G270=""),1,0))</f>
         <v/>
       </c>
+      <c r="O270">
+        <f>IF(OR(AND($D270&lt;&gt;"",OR(LEN($D270)&lt;&gt;17,LEN($D270)-LEN(SUBSTITUTE($D270,":",""))&lt;&gt;5)),AND($E270&lt;&gt;"",OR(LEN($E270)&lt;&gt;17,LEN($E270)-LEN(SUBSTITUTE($E270,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="271">
       <c r="N271">
         <f>IF(COUNTA($A271:$L271)=0,0,IF(OR($B271="",$D271="",$F271="",$G271=""),1,0))</f>
         <v/>
       </c>
+      <c r="O271">
+        <f>IF(OR(AND($D271&lt;&gt;"",OR(LEN($D271)&lt;&gt;17,LEN($D271)-LEN(SUBSTITUTE($D271,":",""))&lt;&gt;5)),AND($E271&lt;&gt;"",OR(LEN($E271)&lt;&gt;17,LEN($E271)-LEN(SUBSTITUTE($E271,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="272">
       <c r="N272">
         <f>IF(COUNTA($A272:$L272)=0,0,IF(OR($B272="",$D272="",$F272="",$G272=""),1,0))</f>
         <v/>
       </c>
+      <c r="O272">
+        <f>IF(OR(AND($D272&lt;&gt;"",OR(LEN($D272)&lt;&gt;17,LEN($D272)-LEN(SUBSTITUTE($D272,":",""))&lt;&gt;5)),AND($E272&lt;&gt;"",OR(LEN($E272)&lt;&gt;17,LEN($E272)-LEN(SUBSTITUTE($E272,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="273">
       <c r="N273">
         <f>IF(COUNTA($A273:$L273)=0,0,IF(OR($B273="",$D273="",$F273="",$G273=""),1,0))</f>
         <v/>
       </c>
+      <c r="O273">
+        <f>IF(OR(AND($D273&lt;&gt;"",OR(LEN($D273)&lt;&gt;17,LEN($D273)-LEN(SUBSTITUTE($D273,":",""))&lt;&gt;5)),AND($E273&lt;&gt;"",OR(LEN($E273)&lt;&gt;17,LEN($E273)-LEN(SUBSTITUTE($E273,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="274">
       <c r="N274">
         <f>IF(COUNTA($A274:$L274)=0,0,IF(OR($B274="",$D274="",$F274="",$G274=""),1,0))</f>
         <v/>
       </c>
+      <c r="O274">
+        <f>IF(OR(AND($D274&lt;&gt;"",OR(LEN($D274)&lt;&gt;17,LEN($D274)-LEN(SUBSTITUTE($D274,":",""))&lt;&gt;5)),AND($E274&lt;&gt;"",OR(LEN($E274)&lt;&gt;17,LEN($E274)-LEN(SUBSTITUTE($E274,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="275">
       <c r="N275">
         <f>IF(COUNTA($A275:$L275)=0,0,IF(OR($B275="",$D275="",$F275="",$G275=""),1,0))</f>
         <v/>
       </c>
+      <c r="O275">
+        <f>IF(OR(AND($D275&lt;&gt;"",OR(LEN($D275)&lt;&gt;17,LEN($D275)-LEN(SUBSTITUTE($D275,":",""))&lt;&gt;5)),AND($E275&lt;&gt;"",OR(LEN($E275)&lt;&gt;17,LEN($E275)-LEN(SUBSTITUTE($E275,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="276">
       <c r="N276">
         <f>IF(COUNTA($A276:$L276)=0,0,IF(OR($B276="",$D276="",$F276="",$G276=""),1,0))</f>
         <v/>
       </c>
+      <c r="O276">
+        <f>IF(OR(AND($D276&lt;&gt;"",OR(LEN($D276)&lt;&gt;17,LEN($D276)-LEN(SUBSTITUTE($D276,":",""))&lt;&gt;5)),AND($E276&lt;&gt;"",OR(LEN($E276)&lt;&gt;17,LEN($E276)-LEN(SUBSTITUTE($E276,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="277">
       <c r="N277">
         <f>IF(COUNTA($A277:$L277)=0,0,IF(OR($B277="",$D277="",$F277="",$G277=""),1,0))</f>
         <v/>
       </c>
+      <c r="O277">
+        <f>IF(OR(AND($D277&lt;&gt;"",OR(LEN($D277)&lt;&gt;17,LEN($D277)-LEN(SUBSTITUTE($D277,":",""))&lt;&gt;5)),AND($E277&lt;&gt;"",OR(LEN($E277)&lt;&gt;17,LEN($E277)-LEN(SUBSTITUTE($E277,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="278">
       <c r="N278">
         <f>IF(COUNTA($A278:$L278)=0,0,IF(OR($B278="",$D278="",$F278="",$G278=""),1,0))</f>
         <v/>
       </c>
+      <c r="O278">
+        <f>IF(OR(AND($D278&lt;&gt;"",OR(LEN($D278)&lt;&gt;17,LEN($D278)-LEN(SUBSTITUTE($D278,":",""))&lt;&gt;5)),AND($E278&lt;&gt;"",OR(LEN($E278)&lt;&gt;17,LEN($E278)-LEN(SUBSTITUTE($E278,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="279">
       <c r="N279">
         <f>IF(COUNTA($A279:$L279)=0,0,IF(OR($B279="",$D279="",$F279="",$G279=""),1,0))</f>
         <v/>
       </c>
+      <c r="O279">
+        <f>IF(OR(AND($D279&lt;&gt;"",OR(LEN($D279)&lt;&gt;17,LEN($D279)-LEN(SUBSTITUTE($D279,":",""))&lt;&gt;5)),AND($E279&lt;&gt;"",OR(LEN($E279)&lt;&gt;17,LEN($E279)-LEN(SUBSTITUTE($E279,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="280">
       <c r="N280">
         <f>IF(COUNTA($A280:$L280)=0,0,IF(OR($B280="",$D280="",$F280="",$G280=""),1,0))</f>
         <v/>
       </c>
+      <c r="O280">
+        <f>IF(OR(AND($D280&lt;&gt;"",OR(LEN($D280)&lt;&gt;17,LEN($D280)-LEN(SUBSTITUTE($D280,":",""))&lt;&gt;5)),AND($E280&lt;&gt;"",OR(LEN($E280)&lt;&gt;17,LEN($E280)-LEN(SUBSTITUTE($E280,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="281">
       <c r="N281">
         <f>IF(COUNTA($A281:$L281)=0,0,IF(OR($B281="",$D281="",$F281="",$G281=""),1,0))</f>
         <v/>
       </c>
+      <c r="O281">
+        <f>IF(OR(AND($D281&lt;&gt;"",OR(LEN($D281)&lt;&gt;17,LEN($D281)-LEN(SUBSTITUTE($D281,":",""))&lt;&gt;5)),AND($E281&lt;&gt;"",OR(LEN($E281)&lt;&gt;17,LEN($E281)-LEN(SUBSTITUTE($E281,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="282">
       <c r="N282">
         <f>IF(COUNTA($A282:$L282)=0,0,IF(OR($B282="",$D282="",$F282="",$G282=""),1,0))</f>
         <v/>
       </c>
+      <c r="O282">
+        <f>IF(OR(AND($D282&lt;&gt;"",OR(LEN($D282)&lt;&gt;17,LEN($D282)-LEN(SUBSTITUTE($D282,":",""))&lt;&gt;5)),AND($E282&lt;&gt;"",OR(LEN($E282)&lt;&gt;17,LEN($E282)-LEN(SUBSTITUTE($E282,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="283">
       <c r="N283">
         <f>IF(COUNTA($A283:$L283)=0,0,IF(OR($B283="",$D283="",$F283="",$G283=""),1,0))</f>
         <v/>
       </c>
+      <c r="O283">
+        <f>IF(OR(AND($D283&lt;&gt;"",OR(LEN($D283)&lt;&gt;17,LEN($D283)-LEN(SUBSTITUTE($D283,":",""))&lt;&gt;5)),AND($E283&lt;&gt;"",OR(LEN($E283)&lt;&gt;17,LEN($E283)-LEN(SUBSTITUTE($E283,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="284">
       <c r="N284">
         <f>IF(COUNTA($A284:$L284)=0,0,IF(OR($B284="",$D284="",$F284="",$G284=""),1,0))</f>
         <v/>
       </c>
+      <c r="O284">
+        <f>IF(OR(AND($D284&lt;&gt;"",OR(LEN($D284)&lt;&gt;17,LEN($D284)-LEN(SUBSTITUTE($D284,":",""))&lt;&gt;5)),AND($E284&lt;&gt;"",OR(LEN($E284)&lt;&gt;17,LEN($E284)-LEN(SUBSTITUTE($E284,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="285">
       <c r="N285">
         <f>IF(COUNTA($A285:$L285)=0,0,IF(OR($B285="",$D285="",$F285="",$G285=""),1,0))</f>
         <v/>
       </c>
+      <c r="O285">
+        <f>IF(OR(AND($D285&lt;&gt;"",OR(LEN($D285)&lt;&gt;17,LEN($D285)-LEN(SUBSTITUTE($D285,":",""))&lt;&gt;5)),AND($E285&lt;&gt;"",OR(LEN($E285)&lt;&gt;17,LEN($E285)-LEN(SUBSTITUTE($E285,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="286">
       <c r="N286">
         <f>IF(COUNTA($A286:$L286)=0,0,IF(OR($B286="",$D286="",$F286="",$G286=""),1,0))</f>
         <v/>
       </c>
+      <c r="O286">
+        <f>IF(OR(AND($D286&lt;&gt;"",OR(LEN($D286)&lt;&gt;17,LEN($D286)-LEN(SUBSTITUTE($D286,":",""))&lt;&gt;5)),AND($E286&lt;&gt;"",OR(LEN($E286)&lt;&gt;17,LEN($E286)-LEN(SUBSTITUTE($E286,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="287">
       <c r="N287">
         <f>IF(COUNTA($A287:$L287)=0,0,IF(OR($B287="",$D287="",$F287="",$G287=""),1,0))</f>
         <v/>
       </c>
+      <c r="O287">
+        <f>IF(OR(AND($D287&lt;&gt;"",OR(LEN($D287)&lt;&gt;17,LEN($D287)-LEN(SUBSTITUTE($D287,":",""))&lt;&gt;5)),AND($E287&lt;&gt;"",OR(LEN($E287)&lt;&gt;17,LEN($E287)-LEN(SUBSTITUTE($E287,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="288">
       <c r="N288">
         <f>IF(COUNTA($A288:$L288)=0,0,IF(OR($B288="",$D288="",$F288="",$G288=""),1,0))</f>
         <v/>
       </c>
+      <c r="O288">
+        <f>IF(OR(AND($D288&lt;&gt;"",OR(LEN($D288)&lt;&gt;17,LEN($D288)-LEN(SUBSTITUTE($D288,":",""))&lt;&gt;5)),AND($E288&lt;&gt;"",OR(LEN($E288)&lt;&gt;17,LEN($E288)-LEN(SUBSTITUTE($E288,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="289">
       <c r="N289">
         <f>IF(COUNTA($A289:$L289)=0,0,IF(OR($B289="",$D289="",$F289="",$G289=""),1,0))</f>
         <v/>
       </c>
+      <c r="O289">
+        <f>IF(OR(AND($D289&lt;&gt;"",OR(LEN($D289)&lt;&gt;17,LEN($D289)-LEN(SUBSTITUTE($D289,":",""))&lt;&gt;5)),AND($E289&lt;&gt;"",OR(LEN($E289)&lt;&gt;17,LEN($E289)-LEN(SUBSTITUTE($E289,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="290">
       <c r="N290">
         <f>IF(COUNTA($A290:$L290)=0,0,IF(OR($B290="",$D290="",$F290="",$G290=""),1,0))</f>
         <v/>
       </c>
+      <c r="O290">
+        <f>IF(OR(AND($D290&lt;&gt;"",OR(LEN($D290)&lt;&gt;17,LEN($D290)-LEN(SUBSTITUTE($D290,":",""))&lt;&gt;5)),AND($E290&lt;&gt;"",OR(LEN($E290)&lt;&gt;17,LEN($E290)-LEN(SUBSTITUTE($E290,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="291">
       <c r="N291">
         <f>IF(COUNTA($A291:$L291)=0,0,IF(OR($B291="",$D291="",$F291="",$G291=""),1,0))</f>
         <v/>
       </c>
+      <c r="O291">
+        <f>IF(OR(AND($D291&lt;&gt;"",OR(LEN($D291)&lt;&gt;17,LEN($D291)-LEN(SUBSTITUTE($D291,":",""))&lt;&gt;5)),AND($E291&lt;&gt;"",OR(LEN($E291)&lt;&gt;17,LEN($E291)-LEN(SUBSTITUTE($E291,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="292">
       <c r="N292">
         <f>IF(COUNTA($A292:$L292)=0,0,IF(OR($B292="",$D292="",$F292="",$G292=""),1,0))</f>
         <v/>
       </c>
+      <c r="O292">
+        <f>IF(OR(AND($D292&lt;&gt;"",OR(LEN($D292)&lt;&gt;17,LEN($D292)-LEN(SUBSTITUTE($D292,":",""))&lt;&gt;5)),AND($E292&lt;&gt;"",OR(LEN($E292)&lt;&gt;17,LEN($E292)-LEN(SUBSTITUTE($E292,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="293">
       <c r="N293">
         <f>IF(COUNTA($A293:$L293)=0,0,IF(OR($B293="",$D293="",$F293="",$G293=""),1,0))</f>
         <v/>
       </c>
+      <c r="O293">
+        <f>IF(OR(AND($D293&lt;&gt;"",OR(LEN($D293)&lt;&gt;17,LEN($D293)-LEN(SUBSTITUTE($D293,":",""))&lt;&gt;5)),AND($E293&lt;&gt;"",OR(LEN($E293)&lt;&gt;17,LEN($E293)-LEN(SUBSTITUTE($E293,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="294">
       <c r="N294">
         <f>IF(COUNTA($A294:$L294)=0,0,IF(OR($B294="",$D294="",$F294="",$G294=""),1,0))</f>
         <v/>
       </c>
+      <c r="O294">
+        <f>IF(OR(AND($D294&lt;&gt;"",OR(LEN($D294)&lt;&gt;17,LEN($D294)-LEN(SUBSTITUTE($D294,":",""))&lt;&gt;5)),AND($E294&lt;&gt;"",OR(LEN($E294)&lt;&gt;17,LEN($E294)-LEN(SUBSTITUTE($E294,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="295">
       <c r="N295">
         <f>IF(COUNTA($A295:$L295)=0,0,IF(OR($B295="",$D295="",$F295="",$G295=""),1,0))</f>
         <v/>
       </c>
+      <c r="O295">
+        <f>IF(OR(AND($D295&lt;&gt;"",OR(LEN($D295)&lt;&gt;17,LEN($D295)-LEN(SUBSTITUTE($D295,":",""))&lt;&gt;5)),AND($E295&lt;&gt;"",OR(LEN($E295)&lt;&gt;17,LEN($E295)-LEN(SUBSTITUTE($E295,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="296">
       <c r="N296">
         <f>IF(COUNTA($A296:$L296)=0,0,IF(OR($B296="",$D296="",$F296="",$G296=""),1,0))</f>
         <v/>
       </c>
+      <c r="O296">
+        <f>IF(OR(AND($D296&lt;&gt;"",OR(LEN($D296)&lt;&gt;17,LEN($D296)-LEN(SUBSTITUTE($D296,":",""))&lt;&gt;5)),AND($E296&lt;&gt;"",OR(LEN($E296)&lt;&gt;17,LEN($E296)-LEN(SUBSTITUTE($E296,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="297">
       <c r="N297">
         <f>IF(COUNTA($A297:$L297)=0,0,IF(OR($B297="",$D297="",$F297="",$G297=""),1,0))</f>
         <v/>
       </c>
+      <c r="O297">
+        <f>IF(OR(AND($D297&lt;&gt;"",OR(LEN($D297)&lt;&gt;17,LEN($D297)-LEN(SUBSTITUTE($D297,":",""))&lt;&gt;5)),AND($E297&lt;&gt;"",OR(LEN($E297)&lt;&gt;17,LEN($E297)-LEN(SUBSTITUTE($E297,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="298">
       <c r="N298">
         <f>IF(COUNTA($A298:$L298)=0,0,IF(OR($B298="",$D298="",$F298="",$G298=""),1,0))</f>
         <v/>
       </c>
+      <c r="O298">
+        <f>IF(OR(AND($D298&lt;&gt;"",OR(LEN($D298)&lt;&gt;17,LEN($D298)-LEN(SUBSTITUTE($D298,":",""))&lt;&gt;5)),AND($E298&lt;&gt;"",OR(LEN($E298)&lt;&gt;17,LEN($E298)-LEN(SUBSTITUTE($E298,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="299">
       <c r="N299">
         <f>IF(COUNTA($A299:$L299)=0,0,IF(OR($B299="",$D299="",$F299="",$G299=""),1,0))</f>
         <v/>
       </c>
+      <c r="O299">
+        <f>IF(OR(AND($D299&lt;&gt;"",OR(LEN($D299)&lt;&gt;17,LEN($D299)-LEN(SUBSTITUTE($D299,":",""))&lt;&gt;5)),AND($E299&lt;&gt;"",OR(LEN($E299)&lt;&gt;17,LEN($E299)-LEN(SUBSTITUTE($E299,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="300">
       <c r="N300">
         <f>IF(COUNTA($A300:$L300)=0,0,IF(OR($B300="",$D300="",$F300="",$G300=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="O300">
+        <f>IF(OR(AND($D300&lt;&gt;"",OR(LEN($D300)&lt;&gt;17,LEN($D300)-LEN(SUBSTITUTE($D300,":",""))&lt;&gt;5)),AND($E300&lt;&gt;"",OR(LEN($E300)&lt;&gt;17,LEN($E300)-LEN(SUBSTITUTE($E300,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
     </row>
@@ -4381,7 +5619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H300"/>
+  <dimension ref="A1:I300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4391,6 +5629,7 @@
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col hidden="1" width="13" customWidth="1" min="8" max="8"/>
+    <col hidden="1" width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -4427,6 +5666,11 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>ctrl</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ctrlfmt</t>
         </is>
       </c>
     </row>
@@ -4441,6 +5685,10 @@
         <f>IF(COUNTA($A2:$F2)=0,0,IF(OR($B2="",$D2=""),1,0))</f>
         <v/>
       </c>
+      <c r="I2">
+        <f>IF(OR(AND($D2&lt;&gt;"",OR(LEN($D2)&lt;&gt;17,LEN($D2)-LEN(SUBSTITUTE($D2,":",""))&lt;&gt;5)),AND($E2&lt;&gt;"",OR(LEN($E2)&lt;&gt;17,LEN($E2)-LEN(SUBSTITUTE($E2,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n"/>
@@ -4453,6 +5701,10 @@
         <f>IF(COUNTA($A3:$F3)=0,0,IF(OR($B3="",$D3=""),1,0))</f>
         <v/>
       </c>
+      <c r="I3">
+        <f>IF(OR(AND($D3&lt;&gt;"",OR(LEN($D3)&lt;&gt;17,LEN($D3)-LEN(SUBSTITUTE($D3,":",""))&lt;&gt;5)),AND($E3&lt;&gt;"",OR(LEN($E3)&lt;&gt;17,LEN($E3)-LEN(SUBSTITUTE($E3,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n"/>
@@ -4465,6 +5717,10 @@
         <f>IF(COUNTA($A4:$F4)=0,0,IF(OR($B4="",$D4=""),1,0))</f>
         <v/>
       </c>
+      <c r="I4">
+        <f>IF(OR(AND($D4&lt;&gt;"",OR(LEN($D4)&lt;&gt;17,LEN($D4)-LEN(SUBSTITUTE($D4,":",""))&lt;&gt;5)),AND($E4&lt;&gt;"",OR(LEN($E4)&lt;&gt;17,LEN($E4)-LEN(SUBSTITUTE($E4,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n"/>
@@ -4477,6 +5733,10 @@
         <f>IF(COUNTA($A5:$F5)=0,0,IF(OR($B5="",$D5=""),1,0))</f>
         <v/>
       </c>
+      <c r="I5">
+        <f>IF(OR(AND($D5&lt;&gt;"",OR(LEN($D5)&lt;&gt;17,LEN($D5)-LEN(SUBSTITUTE($D5,":",""))&lt;&gt;5)),AND($E5&lt;&gt;"",OR(LEN($E5)&lt;&gt;17,LEN($E5)-LEN(SUBSTITUTE($E5,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n"/>
@@ -4489,6 +5749,10 @@
         <f>IF(COUNTA($A6:$F6)=0,0,IF(OR($B6="",$D6=""),1,0))</f>
         <v/>
       </c>
+      <c r="I6">
+        <f>IF(OR(AND($D6&lt;&gt;"",OR(LEN($D6)&lt;&gt;17,LEN($D6)-LEN(SUBSTITUTE($D6,":",""))&lt;&gt;5)),AND($E6&lt;&gt;"",OR(LEN($E6)&lt;&gt;17,LEN($E6)-LEN(SUBSTITUTE($E6,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n"/>
@@ -4501,6 +5765,10 @@
         <f>IF(COUNTA($A7:$F7)=0,0,IF(OR($B7="",$D7=""),1,0))</f>
         <v/>
       </c>
+      <c r="I7">
+        <f>IF(OR(AND($D7&lt;&gt;"",OR(LEN($D7)&lt;&gt;17,LEN($D7)-LEN(SUBSTITUTE($D7,":",""))&lt;&gt;5)),AND($E7&lt;&gt;"",OR(LEN($E7)&lt;&gt;17,LEN($E7)-LEN(SUBSTITUTE($E7,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="n"/>
@@ -4513,6 +5781,10 @@
         <f>IF(COUNTA($A8:$F8)=0,0,IF(OR($B8="",$D8=""),1,0))</f>
         <v/>
       </c>
+      <c r="I8">
+        <f>IF(OR(AND($D8&lt;&gt;"",OR(LEN($D8)&lt;&gt;17,LEN($D8)-LEN(SUBSTITUTE($D8,":",""))&lt;&gt;5)),AND($E8&lt;&gt;"",OR(LEN($E8)&lt;&gt;17,LEN($E8)-LEN(SUBSTITUTE($E8,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="n"/>
@@ -4525,6 +5797,10 @@
         <f>IF(COUNTA($A9:$F9)=0,0,IF(OR($B9="",$D9=""),1,0))</f>
         <v/>
       </c>
+      <c r="I9">
+        <f>IF(OR(AND($D9&lt;&gt;"",OR(LEN($D9)&lt;&gt;17,LEN($D9)-LEN(SUBSTITUTE($D9,":",""))&lt;&gt;5)),AND($E9&lt;&gt;"",OR(LEN($E9)&lt;&gt;17,LEN($E9)-LEN(SUBSTITUTE($E9,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="n"/>
@@ -4537,6 +5813,10 @@
         <f>IF(COUNTA($A10:$F10)=0,0,IF(OR($B10="",$D10=""),1,0))</f>
         <v/>
       </c>
+      <c r="I10">
+        <f>IF(OR(AND($D10&lt;&gt;"",OR(LEN($D10)&lt;&gt;17,LEN($D10)-LEN(SUBSTITUTE($D10,":",""))&lt;&gt;5)),AND($E10&lt;&gt;"",OR(LEN($E10)&lt;&gt;17,LEN($E10)-LEN(SUBSTITUTE($E10,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="n"/>
@@ -4549,6 +5829,10 @@
         <f>IF(COUNTA($A11:$F11)=0,0,IF(OR($B11="",$D11=""),1,0))</f>
         <v/>
       </c>
+      <c r="I11">
+        <f>IF(OR(AND($D11&lt;&gt;"",OR(LEN($D11)&lt;&gt;17,LEN($D11)-LEN(SUBSTITUTE($D11,":",""))&lt;&gt;5)),AND($E11&lt;&gt;"",OR(LEN($E11)&lt;&gt;17,LEN($E11)-LEN(SUBSTITUTE($E11,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="n"/>
@@ -4561,6 +5845,10 @@
         <f>IF(COUNTA($A12:$F12)=0,0,IF(OR($B12="",$D12=""),1,0))</f>
         <v/>
       </c>
+      <c r="I12">
+        <f>IF(OR(AND($D12&lt;&gt;"",OR(LEN($D12)&lt;&gt;17,LEN($D12)-LEN(SUBSTITUTE($D12,":",""))&lt;&gt;5)),AND($E12&lt;&gt;"",OR(LEN($E12)&lt;&gt;17,LEN($E12)-LEN(SUBSTITUTE($E12,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="n"/>
@@ -4573,6 +5861,10 @@
         <f>IF(COUNTA($A13:$F13)=0,0,IF(OR($B13="",$D13=""),1,0))</f>
         <v/>
       </c>
+      <c r="I13">
+        <f>IF(OR(AND($D13&lt;&gt;"",OR(LEN($D13)&lt;&gt;17,LEN($D13)-LEN(SUBSTITUTE($D13,":",""))&lt;&gt;5)),AND($E13&lt;&gt;"",OR(LEN($E13)&lt;&gt;17,LEN($E13)-LEN(SUBSTITUTE($E13,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="n"/>
@@ -4585,6 +5877,10 @@
         <f>IF(COUNTA($A14:$F14)=0,0,IF(OR($B14="",$D14=""),1,0))</f>
         <v/>
       </c>
+      <c r="I14">
+        <f>IF(OR(AND($D14&lt;&gt;"",OR(LEN($D14)&lt;&gt;17,LEN($D14)-LEN(SUBSTITUTE($D14,":",""))&lt;&gt;5)),AND($E14&lt;&gt;"",OR(LEN($E14)&lt;&gt;17,LEN($E14)-LEN(SUBSTITUTE($E14,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="n"/>
@@ -4597,6 +5893,10 @@
         <f>IF(COUNTA($A15:$F15)=0,0,IF(OR($B15="",$D15=""),1,0))</f>
         <v/>
       </c>
+      <c r="I15">
+        <f>IF(OR(AND($D15&lt;&gt;"",OR(LEN($D15)&lt;&gt;17,LEN($D15)-LEN(SUBSTITUTE($D15,":",""))&lt;&gt;5)),AND($E15&lt;&gt;"",OR(LEN($E15)&lt;&gt;17,LEN($E15)-LEN(SUBSTITUTE($E15,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="n"/>
@@ -4609,6 +5909,10 @@
         <f>IF(COUNTA($A16:$F16)=0,0,IF(OR($B16="",$D16=""),1,0))</f>
         <v/>
       </c>
+      <c r="I16">
+        <f>IF(OR(AND($D16&lt;&gt;"",OR(LEN($D16)&lt;&gt;17,LEN($D16)-LEN(SUBSTITUTE($D16,":",""))&lt;&gt;5)),AND($E16&lt;&gt;"",OR(LEN($E16)&lt;&gt;17,LEN($E16)-LEN(SUBSTITUTE($E16,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="n"/>
@@ -4621,6 +5925,10 @@
         <f>IF(COUNTA($A17:$F17)=0,0,IF(OR($B17="",$D17=""),1,0))</f>
         <v/>
       </c>
+      <c r="I17">
+        <f>IF(OR(AND($D17&lt;&gt;"",OR(LEN($D17)&lt;&gt;17,LEN($D17)-LEN(SUBSTITUTE($D17,":",""))&lt;&gt;5)),AND($E17&lt;&gt;"",OR(LEN($E17)&lt;&gt;17,LEN($E17)-LEN(SUBSTITUTE($E17,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="n"/>
@@ -4633,6 +5941,10 @@
         <f>IF(COUNTA($A18:$F18)=0,0,IF(OR($B18="",$D18=""),1,0))</f>
         <v/>
       </c>
+      <c r="I18">
+        <f>IF(OR(AND($D18&lt;&gt;"",OR(LEN($D18)&lt;&gt;17,LEN($D18)-LEN(SUBSTITUTE($D18,":",""))&lt;&gt;5)),AND($E18&lt;&gt;"",OR(LEN($E18)&lt;&gt;17,LEN($E18)-LEN(SUBSTITUTE($E18,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="n"/>
@@ -4645,6 +5957,10 @@
         <f>IF(COUNTA($A19:$F19)=0,0,IF(OR($B19="",$D19=""),1,0))</f>
         <v/>
       </c>
+      <c r="I19">
+        <f>IF(OR(AND($D19&lt;&gt;"",OR(LEN($D19)&lt;&gt;17,LEN($D19)-LEN(SUBSTITUTE($D19,":",""))&lt;&gt;5)),AND($E19&lt;&gt;"",OR(LEN($E19)&lt;&gt;17,LEN($E19)-LEN(SUBSTITUTE($E19,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="n"/>
@@ -4657,6 +5973,10 @@
         <f>IF(COUNTA($A20:$F20)=0,0,IF(OR($B20="",$D20=""),1,0))</f>
         <v/>
       </c>
+      <c r="I20">
+        <f>IF(OR(AND($D20&lt;&gt;"",OR(LEN($D20)&lt;&gt;17,LEN($D20)-LEN(SUBSTITUTE($D20,":",""))&lt;&gt;5)),AND($E20&lt;&gt;"",OR(LEN($E20)&lt;&gt;17,LEN($E20)-LEN(SUBSTITUTE($E20,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="n"/>
@@ -4669,6 +5989,10 @@
         <f>IF(COUNTA($A21:$F21)=0,0,IF(OR($B21="",$D21=""),1,0))</f>
         <v/>
       </c>
+      <c r="I21">
+        <f>IF(OR(AND($D21&lt;&gt;"",OR(LEN($D21)&lt;&gt;17,LEN($D21)-LEN(SUBSTITUTE($D21,":",""))&lt;&gt;5)),AND($E21&lt;&gt;"",OR(LEN($E21)&lt;&gt;17,LEN($E21)-LEN(SUBSTITUTE($E21,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="n"/>
@@ -4681,6 +6005,10 @@
         <f>IF(COUNTA($A22:$F22)=0,0,IF(OR($B22="",$D22=""),1,0))</f>
         <v/>
       </c>
+      <c r="I22">
+        <f>IF(OR(AND($D22&lt;&gt;"",OR(LEN($D22)&lt;&gt;17,LEN($D22)-LEN(SUBSTITUTE($D22,":",""))&lt;&gt;5)),AND($E22&lt;&gt;"",OR(LEN($E22)&lt;&gt;17,LEN($E22)-LEN(SUBSTITUTE($E22,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="n"/>
@@ -4693,6 +6021,10 @@
         <f>IF(COUNTA($A23:$F23)=0,0,IF(OR($B23="",$D23=""),1,0))</f>
         <v/>
       </c>
+      <c r="I23">
+        <f>IF(OR(AND($D23&lt;&gt;"",OR(LEN($D23)&lt;&gt;17,LEN($D23)-LEN(SUBSTITUTE($D23,":",""))&lt;&gt;5)),AND($E23&lt;&gt;"",OR(LEN($E23)&lt;&gt;17,LEN($E23)-LEN(SUBSTITUTE($E23,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="n"/>
@@ -4705,6 +6037,10 @@
         <f>IF(COUNTA($A24:$F24)=0,0,IF(OR($B24="",$D24=""),1,0))</f>
         <v/>
       </c>
+      <c r="I24">
+        <f>IF(OR(AND($D24&lt;&gt;"",OR(LEN($D24)&lt;&gt;17,LEN($D24)-LEN(SUBSTITUTE($D24,":",""))&lt;&gt;5)),AND($E24&lt;&gt;"",OR(LEN($E24)&lt;&gt;17,LEN($E24)-LEN(SUBSTITUTE($E24,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="n"/>
@@ -4717,6 +6053,10 @@
         <f>IF(COUNTA($A25:$F25)=0,0,IF(OR($B25="",$D25=""),1,0))</f>
         <v/>
       </c>
+      <c r="I25">
+        <f>IF(OR(AND($D25&lt;&gt;"",OR(LEN($D25)&lt;&gt;17,LEN($D25)-LEN(SUBSTITUTE($D25,":",""))&lt;&gt;5)),AND($E25&lt;&gt;"",OR(LEN($E25)&lt;&gt;17,LEN($E25)-LEN(SUBSTITUTE($E25,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="n"/>
@@ -4729,6 +6069,10 @@
         <f>IF(COUNTA($A26:$F26)=0,0,IF(OR($B26="",$D26=""),1,0))</f>
         <v/>
       </c>
+      <c r="I26">
+        <f>IF(OR(AND($D26&lt;&gt;"",OR(LEN($D26)&lt;&gt;17,LEN($D26)-LEN(SUBSTITUTE($D26,":",""))&lt;&gt;5)),AND($E26&lt;&gt;"",OR(LEN($E26)&lt;&gt;17,LEN($E26)-LEN(SUBSTITUTE($E26,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="n"/>
@@ -4741,6 +6085,10 @@
         <f>IF(COUNTA($A27:$F27)=0,0,IF(OR($B27="",$D27=""),1,0))</f>
         <v/>
       </c>
+      <c r="I27">
+        <f>IF(OR(AND($D27&lt;&gt;"",OR(LEN($D27)&lt;&gt;17,LEN($D27)-LEN(SUBSTITUTE($D27,":",""))&lt;&gt;5)),AND($E27&lt;&gt;"",OR(LEN($E27)&lt;&gt;17,LEN($E27)-LEN(SUBSTITUTE($E27,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="n"/>
@@ -4753,6 +6101,10 @@
         <f>IF(COUNTA($A28:$F28)=0,0,IF(OR($B28="",$D28=""),1,0))</f>
         <v/>
       </c>
+      <c r="I28">
+        <f>IF(OR(AND($D28&lt;&gt;"",OR(LEN($D28)&lt;&gt;17,LEN($D28)-LEN(SUBSTITUTE($D28,":",""))&lt;&gt;5)),AND($E28&lt;&gt;"",OR(LEN($E28)&lt;&gt;17,LEN($E28)-LEN(SUBSTITUTE($E28,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="n"/>
@@ -4765,6 +6117,10 @@
         <f>IF(COUNTA($A29:$F29)=0,0,IF(OR($B29="",$D29=""),1,0))</f>
         <v/>
       </c>
+      <c r="I29">
+        <f>IF(OR(AND($D29&lt;&gt;"",OR(LEN($D29)&lt;&gt;17,LEN($D29)-LEN(SUBSTITUTE($D29,":",""))&lt;&gt;5)),AND($E29&lt;&gt;"",OR(LEN($E29)&lt;&gt;17,LEN($E29)-LEN(SUBSTITUTE($E29,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="n"/>
@@ -4777,6 +6133,10 @@
         <f>IF(COUNTA($A30:$F30)=0,0,IF(OR($B30="",$D30=""),1,0))</f>
         <v/>
       </c>
+      <c r="I30">
+        <f>IF(OR(AND($D30&lt;&gt;"",OR(LEN($D30)&lt;&gt;17,LEN($D30)-LEN(SUBSTITUTE($D30,":",""))&lt;&gt;5)),AND($E30&lt;&gt;"",OR(LEN($E30)&lt;&gt;17,LEN($E30)-LEN(SUBSTITUTE($E30,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="n"/>
@@ -4789,6 +6149,10 @@
         <f>IF(COUNTA($A31:$F31)=0,0,IF(OR($B31="",$D31=""),1,0))</f>
         <v/>
       </c>
+      <c r="I31">
+        <f>IF(OR(AND($D31&lt;&gt;"",OR(LEN($D31)&lt;&gt;17,LEN($D31)-LEN(SUBSTITUTE($D31,":",""))&lt;&gt;5)),AND($E31&lt;&gt;"",OR(LEN($E31)&lt;&gt;17,LEN($E31)-LEN(SUBSTITUTE($E31,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="n"/>
@@ -4801,6 +6165,10 @@
         <f>IF(COUNTA($A32:$F32)=0,0,IF(OR($B32="",$D32=""),1,0))</f>
         <v/>
       </c>
+      <c r="I32">
+        <f>IF(OR(AND($D32&lt;&gt;"",OR(LEN($D32)&lt;&gt;17,LEN($D32)-LEN(SUBSTITUTE($D32,":",""))&lt;&gt;5)),AND($E32&lt;&gt;"",OR(LEN($E32)&lt;&gt;17,LEN($E32)-LEN(SUBSTITUTE($E32,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="n"/>
@@ -4813,6 +6181,10 @@
         <f>IF(COUNTA($A33:$F33)=0,0,IF(OR($B33="",$D33=""),1,0))</f>
         <v/>
       </c>
+      <c r="I33">
+        <f>IF(OR(AND($D33&lt;&gt;"",OR(LEN($D33)&lt;&gt;17,LEN($D33)-LEN(SUBSTITUTE($D33,":",""))&lt;&gt;5)),AND($E33&lt;&gt;"",OR(LEN($E33)&lt;&gt;17,LEN($E33)-LEN(SUBSTITUTE($E33,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="n"/>
@@ -4825,6 +6197,10 @@
         <f>IF(COUNTA($A34:$F34)=0,0,IF(OR($B34="",$D34=""),1,0))</f>
         <v/>
       </c>
+      <c r="I34">
+        <f>IF(OR(AND($D34&lt;&gt;"",OR(LEN($D34)&lt;&gt;17,LEN($D34)-LEN(SUBSTITUTE($D34,":",""))&lt;&gt;5)),AND($E34&lt;&gt;"",OR(LEN($E34)&lt;&gt;17,LEN($E34)-LEN(SUBSTITUTE($E34,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="n"/>
@@ -4837,6 +6213,10 @@
         <f>IF(COUNTA($A35:$F35)=0,0,IF(OR($B35="",$D35=""),1,0))</f>
         <v/>
       </c>
+      <c r="I35">
+        <f>IF(OR(AND($D35&lt;&gt;"",OR(LEN($D35)&lt;&gt;17,LEN($D35)-LEN(SUBSTITUTE($D35,":",""))&lt;&gt;5)),AND($E35&lt;&gt;"",OR(LEN($E35)&lt;&gt;17,LEN($E35)-LEN(SUBSTITUTE($E35,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="11" t="n"/>
@@ -4849,6 +6229,10 @@
         <f>IF(COUNTA($A36:$F36)=0,0,IF(OR($B36="",$D36=""),1,0))</f>
         <v/>
       </c>
+      <c r="I36">
+        <f>IF(OR(AND($D36&lt;&gt;"",OR(LEN($D36)&lt;&gt;17,LEN($D36)-LEN(SUBSTITUTE($D36,":",""))&lt;&gt;5)),AND($E36&lt;&gt;"",OR(LEN($E36)&lt;&gt;17,LEN($E36)-LEN(SUBSTITUTE($E36,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="n"/>
@@ -4861,6 +6245,10 @@
         <f>IF(COUNTA($A37:$F37)=0,0,IF(OR($B37="",$D37=""),1,0))</f>
         <v/>
       </c>
+      <c r="I37">
+        <f>IF(OR(AND($D37&lt;&gt;"",OR(LEN($D37)&lt;&gt;17,LEN($D37)-LEN(SUBSTITUTE($D37,":",""))&lt;&gt;5)),AND($E37&lt;&gt;"",OR(LEN($E37)&lt;&gt;17,LEN($E37)-LEN(SUBSTITUTE($E37,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="n"/>
@@ -4873,6 +6261,10 @@
         <f>IF(COUNTA($A38:$F38)=0,0,IF(OR($B38="",$D38=""),1,0))</f>
         <v/>
       </c>
+      <c r="I38">
+        <f>IF(OR(AND($D38&lt;&gt;"",OR(LEN($D38)&lt;&gt;17,LEN($D38)-LEN(SUBSTITUTE($D38,":",""))&lt;&gt;5)),AND($E38&lt;&gt;"",OR(LEN($E38)&lt;&gt;17,LEN($E38)-LEN(SUBSTITUTE($E38,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="11" t="n"/>
@@ -4885,6 +6277,10 @@
         <f>IF(COUNTA($A39:$F39)=0,0,IF(OR($B39="",$D39=""),1,0))</f>
         <v/>
       </c>
+      <c r="I39">
+        <f>IF(OR(AND($D39&lt;&gt;"",OR(LEN($D39)&lt;&gt;17,LEN($D39)-LEN(SUBSTITUTE($D39,":",""))&lt;&gt;5)),AND($E39&lt;&gt;"",OR(LEN($E39)&lt;&gt;17,LEN($E39)-LEN(SUBSTITUTE($E39,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="11" t="n"/>
@@ -4897,6 +6293,10 @@
         <f>IF(COUNTA($A40:$F40)=0,0,IF(OR($B40="",$D40=""),1,0))</f>
         <v/>
       </c>
+      <c r="I40">
+        <f>IF(OR(AND($D40&lt;&gt;"",OR(LEN($D40)&lt;&gt;17,LEN($D40)-LEN(SUBSTITUTE($D40,":",""))&lt;&gt;5)),AND($E40&lt;&gt;"",OR(LEN($E40)&lt;&gt;17,LEN($E40)-LEN(SUBSTITUTE($E40,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="11" t="n"/>
@@ -4909,1558 +6309,2598 @@
         <f>IF(COUNTA($A41:$F41)=0,0,IF(OR($B41="",$D41=""),1,0))</f>
         <v/>
       </c>
+      <c r="I41">
+        <f>IF(OR(AND($D41&lt;&gt;"",OR(LEN($D41)&lt;&gt;17,LEN($D41)-LEN(SUBSTITUTE($D41,":",""))&lt;&gt;5)),AND($E41&lt;&gt;"",OR(LEN($E41)&lt;&gt;17,LEN($E41)-LEN(SUBSTITUTE($E41,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="H42">
         <f>IF(COUNTA($A42:$F42)=0,0,IF(OR($B42="",$D42=""),1,0))</f>
         <v/>
       </c>
+      <c r="I42">
+        <f>IF(OR(AND($D42&lt;&gt;"",OR(LEN($D42)&lt;&gt;17,LEN($D42)-LEN(SUBSTITUTE($D42,":",""))&lt;&gt;5)),AND($E42&lt;&gt;"",OR(LEN($E42)&lt;&gt;17,LEN($E42)-LEN(SUBSTITUTE($E42,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="H43">
         <f>IF(COUNTA($A43:$F43)=0,0,IF(OR($B43="",$D43=""),1,0))</f>
         <v/>
       </c>
+      <c r="I43">
+        <f>IF(OR(AND($D43&lt;&gt;"",OR(LEN($D43)&lt;&gt;17,LEN($D43)-LEN(SUBSTITUTE($D43,":",""))&lt;&gt;5)),AND($E43&lt;&gt;"",OR(LEN($E43)&lt;&gt;17,LEN($E43)-LEN(SUBSTITUTE($E43,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="H44">
         <f>IF(COUNTA($A44:$F44)=0,0,IF(OR($B44="",$D44=""),1,0))</f>
         <v/>
       </c>
+      <c r="I44">
+        <f>IF(OR(AND($D44&lt;&gt;"",OR(LEN($D44)&lt;&gt;17,LEN($D44)-LEN(SUBSTITUTE($D44,":",""))&lt;&gt;5)),AND($E44&lt;&gt;"",OR(LEN($E44)&lt;&gt;17,LEN($E44)-LEN(SUBSTITUTE($E44,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="H45">
         <f>IF(COUNTA($A45:$F45)=0,0,IF(OR($B45="",$D45=""),1,0))</f>
         <v/>
       </c>
+      <c r="I45">
+        <f>IF(OR(AND($D45&lt;&gt;"",OR(LEN($D45)&lt;&gt;17,LEN($D45)-LEN(SUBSTITUTE($D45,":",""))&lt;&gt;5)),AND($E45&lt;&gt;"",OR(LEN($E45)&lt;&gt;17,LEN($E45)-LEN(SUBSTITUTE($E45,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="H46">
         <f>IF(COUNTA($A46:$F46)=0,0,IF(OR($B46="",$D46=""),1,0))</f>
         <v/>
       </c>
+      <c r="I46">
+        <f>IF(OR(AND($D46&lt;&gt;"",OR(LEN($D46)&lt;&gt;17,LEN($D46)-LEN(SUBSTITUTE($D46,":",""))&lt;&gt;5)),AND($E46&lt;&gt;"",OR(LEN($E46)&lt;&gt;17,LEN($E46)-LEN(SUBSTITUTE($E46,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="H47">
         <f>IF(COUNTA($A47:$F47)=0,0,IF(OR($B47="",$D47=""),1,0))</f>
         <v/>
       </c>
+      <c r="I47">
+        <f>IF(OR(AND($D47&lt;&gt;"",OR(LEN($D47)&lt;&gt;17,LEN($D47)-LEN(SUBSTITUTE($D47,":",""))&lt;&gt;5)),AND($E47&lt;&gt;"",OR(LEN($E47)&lt;&gt;17,LEN($E47)-LEN(SUBSTITUTE($E47,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="H48">
         <f>IF(COUNTA($A48:$F48)=0,0,IF(OR($B48="",$D48=""),1,0))</f>
         <v/>
       </c>
+      <c r="I48">
+        <f>IF(OR(AND($D48&lt;&gt;"",OR(LEN($D48)&lt;&gt;17,LEN($D48)-LEN(SUBSTITUTE($D48,":",""))&lt;&gt;5)),AND($E48&lt;&gt;"",OR(LEN($E48)&lt;&gt;17,LEN($E48)-LEN(SUBSTITUTE($E48,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="H49">
         <f>IF(COUNTA($A49:$F49)=0,0,IF(OR($B49="",$D49=""),1,0))</f>
         <v/>
       </c>
+      <c r="I49">
+        <f>IF(OR(AND($D49&lt;&gt;"",OR(LEN($D49)&lt;&gt;17,LEN($D49)-LEN(SUBSTITUTE($D49,":",""))&lt;&gt;5)),AND($E49&lt;&gt;"",OR(LEN($E49)&lt;&gt;17,LEN($E49)-LEN(SUBSTITUTE($E49,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="H50">
         <f>IF(COUNTA($A50:$F50)=0,0,IF(OR($B50="",$D50=""),1,0))</f>
         <v/>
       </c>
+      <c r="I50">
+        <f>IF(OR(AND($D50&lt;&gt;"",OR(LEN($D50)&lt;&gt;17,LEN($D50)-LEN(SUBSTITUTE($D50,":",""))&lt;&gt;5)),AND($E50&lt;&gt;"",OR(LEN($E50)&lt;&gt;17,LEN($E50)-LEN(SUBSTITUTE($E50,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="H51">
         <f>IF(COUNTA($A51:$F51)=0,0,IF(OR($B51="",$D51=""),1,0))</f>
         <v/>
       </c>
+      <c r="I51">
+        <f>IF(OR(AND($D51&lt;&gt;"",OR(LEN($D51)&lt;&gt;17,LEN($D51)-LEN(SUBSTITUTE($D51,":",""))&lt;&gt;5)),AND($E51&lt;&gt;"",OR(LEN($E51)&lt;&gt;17,LEN($E51)-LEN(SUBSTITUTE($E51,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="H52">
         <f>IF(COUNTA($A52:$F52)=0,0,IF(OR($B52="",$D52=""),1,0))</f>
         <v/>
       </c>
+      <c r="I52">
+        <f>IF(OR(AND($D52&lt;&gt;"",OR(LEN($D52)&lt;&gt;17,LEN($D52)-LEN(SUBSTITUTE($D52,":",""))&lt;&gt;5)),AND($E52&lt;&gt;"",OR(LEN($E52)&lt;&gt;17,LEN($E52)-LEN(SUBSTITUTE($E52,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="H53">
         <f>IF(COUNTA($A53:$F53)=0,0,IF(OR($B53="",$D53=""),1,0))</f>
         <v/>
       </c>
+      <c r="I53">
+        <f>IF(OR(AND($D53&lt;&gt;"",OR(LEN($D53)&lt;&gt;17,LEN($D53)-LEN(SUBSTITUTE($D53,":",""))&lt;&gt;5)),AND($E53&lt;&gt;"",OR(LEN($E53)&lt;&gt;17,LEN($E53)-LEN(SUBSTITUTE($E53,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="H54">
         <f>IF(COUNTA($A54:$F54)=0,0,IF(OR($B54="",$D54=""),1,0))</f>
         <v/>
       </c>
+      <c r="I54">
+        <f>IF(OR(AND($D54&lt;&gt;"",OR(LEN($D54)&lt;&gt;17,LEN($D54)-LEN(SUBSTITUTE($D54,":",""))&lt;&gt;5)),AND($E54&lt;&gt;"",OR(LEN($E54)&lt;&gt;17,LEN($E54)-LEN(SUBSTITUTE($E54,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="H55">
         <f>IF(COUNTA($A55:$F55)=0,0,IF(OR($B55="",$D55=""),1,0))</f>
         <v/>
       </c>
+      <c r="I55">
+        <f>IF(OR(AND($D55&lt;&gt;"",OR(LEN($D55)&lt;&gt;17,LEN($D55)-LEN(SUBSTITUTE($D55,":",""))&lt;&gt;5)),AND($E55&lt;&gt;"",OR(LEN($E55)&lt;&gt;17,LEN($E55)-LEN(SUBSTITUTE($E55,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="H56">
         <f>IF(COUNTA($A56:$F56)=0,0,IF(OR($B56="",$D56=""),1,0))</f>
         <v/>
       </c>
+      <c r="I56">
+        <f>IF(OR(AND($D56&lt;&gt;"",OR(LEN($D56)&lt;&gt;17,LEN($D56)-LEN(SUBSTITUTE($D56,":",""))&lt;&gt;5)),AND($E56&lt;&gt;"",OR(LEN($E56)&lt;&gt;17,LEN($E56)-LEN(SUBSTITUTE($E56,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="H57">
         <f>IF(COUNTA($A57:$F57)=0,0,IF(OR($B57="",$D57=""),1,0))</f>
         <v/>
       </c>
+      <c r="I57">
+        <f>IF(OR(AND($D57&lt;&gt;"",OR(LEN($D57)&lt;&gt;17,LEN($D57)-LEN(SUBSTITUTE($D57,":",""))&lt;&gt;5)),AND($E57&lt;&gt;"",OR(LEN($E57)&lt;&gt;17,LEN($E57)-LEN(SUBSTITUTE($E57,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="H58">
         <f>IF(COUNTA($A58:$F58)=0,0,IF(OR($B58="",$D58=""),1,0))</f>
         <v/>
       </c>
+      <c r="I58">
+        <f>IF(OR(AND($D58&lt;&gt;"",OR(LEN($D58)&lt;&gt;17,LEN($D58)-LEN(SUBSTITUTE($D58,":",""))&lt;&gt;5)),AND($E58&lt;&gt;"",OR(LEN($E58)&lt;&gt;17,LEN($E58)-LEN(SUBSTITUTE($E58,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="H59">
         <f>IF(COUNTA($A59:$F59)=0,0,IF(OR($B59="",$D59=""),1,0))</f>
         <v/>
       </c>
+      <c r="I59">
+        <f>IF(OR(AND($D59&lt;&gt;"",OR(LEN($D59)&lt;&gt;17,LEN($D59)-LEN(SUBSTITUTE($D59,":",""))&lt;&gt;5)),AND($E59&lt;&gt;"",OR(LEN($E59)&lt;&gt;17,LEN($E59)-LEN(SUBSTITUTE($E59,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="H60">
         <f>IF(COUNTA($A60:$F60)=0,0,IF(OR($B60="",$D60=""),1,0))</f>
         <v/>
       </c>
+      <c r="I60">
+        <f>IF(OR(AND($D60&lt;&gt;"",OR(LEN($D60)&lt;&gt;17,LEN($D60)-LEN(SUBSTITUTE($D60,":",""))&lt;&gt;5)),AND($E60&lt;&gt;"",OR(LEN($E60)&lt;&gt;17,LEN($E60)-LEN(SUBSTITUTE($E60,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="H61">
         <f>IF(COUNTA($A61:$F61)=0,0,IF(OR($B61="",$D61=""),1,0))</f>
         <v/>
       </c>
+      <c r="I61">
+        <f>IF(OR(AND($D61&lt;&gt;"",OR(LEN($D61)&lt;&gt;17,LEN($D61)-LEN(SUBSTITUTE($D61,":",""))&lt;&gt;5)),AND($E61&lt;&gt;"",OR(LEN($E61)&lt;&gt;17,LEN($E61)-LEN(SUBSTITUTE($E61,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="H62">
         <f>IF(COUNTA($A62:$F62)=0,0,IF(OR($B62="",$D62=""),1,0))</f>
         <v/>
       </c>
+      <c r="I62">
+        <f>IF(OR(AND($D62&lt;&gt;"",OR(LEN($D62)&lt;&gt;17,LEN($D62)-LEN(SUBSTITUTE($D62,":",""))&lt;&gt;5)),AND($E62&lt;&gt;"",OR(LEN($E62)&lt;&gt;17,LEN($E62)-LEN(SUBSTITUTE($E62,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="H63">
         <f>IF(COUNTA($A63:$F63)=0,0,IF(OR($B63="",$D63=""),1,0))</f>
         <v/>
       </c>
+      <c r="I63">
+        <f>IF(OR(AND($D63&lt;&gt;"",OR(LEN($D63)&lt;&gt;17,LEN($D63)-LEN(SUBSTITUTE($D63,":",""))&lt;&gt;5)),AND($E63&lt;&gt;"",OR(LEN($E63)&lt;&gt;17,LEN($E63)-LEN(SUBSTITUTE($E63,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="H64">
         <f>IF(COUNTA($A64:$F64)=0,0,IF(OR($B64="",$D64=""),1,0))</f>
         <v/>
       </c>
+      <c r="I64">
+        <f>IF(OR(AND($D64&lt;&gt;"",OR(LEN($D64)&lt;&gt;17,LEN($D64)-LEN(SUBSTITUTE($D64,":",""))&lt;&gt;5)),AND($E64&lt;&gt;"",OR(LEN($E64)&lt;&gt;17,LEN($E64)-LEN(SUBSTITUTE($E64,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="H65">
         <f>IF(COUNTA($A65:$F65)=0,0,IF(OR($B65="",$D65=""),1,0))</f>
         <v/>
       </c>
+      <c r="I65">
+        <f>IF(OR(AND($D65&lt;&gt;"",OR(LEN($D65)&lt;&gt;17,LEN($D65)-LEN(SUBSTITUTE($D65,":",""))&lt;&gt;5)),AND($E65&lt;&gt;"",OR(LEN($E65)&lt;&gt;17,LEN($E65)-LEN(SUBSTITUTE($E65,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="H66">
         <f>IF(COUNTA($A66:$F66)=0,0,IF(OR($B66="",$D66=""),1,0))</f>
         <v/>
       </c>
+      <c r="I66">
+        <f>IF(OR(AND($D66&lt;&gt;"",OR(LEN($D66)&lt;&gt;17,LEN($D66)-LEN(SUBSTITUTE($D66,":",""))&lt;&gt;5)),AND($E66&lt;&gt;"",OR(LEN($E66)&lt;&gt;17,LEN($E66)-LEN(SUBSTITUTE($E66,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="H67">
         <f>IF(COUNTA($A67:$F67)=0,0,IF(OR($B67="",$D67=""),1,0))</f>
         <v/>
       </c>
+      <c r="I67">
+        <f>IF(OR(AND($D67&lt;&gt;"",OR(LEN($D67)&lt;&gt;17,LEN($D67)-LEN(SUBSTITUTE($D67,":",""))&lt;&gt;5)),AND($E67&lt;&gt;"",OR(LEN($E67)&lt;&gt;17,LEN($E67)-LEN(SUBSTITUTE($E67,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="H68">
         <f>IF(COUNTA($A68:$F68)=0,0,IF(OR($B68="",$D68=""),1,0))</f>
         <v/>
       </c>
+      <c r="I68">
+        <f>IF(OR(AND($D68&lt;&gt;"",OR(LEN($D68)&lt;&gt;17,LEN($D68)-LEN(SUBSTITUTE($D68,":",""))&lt;&gt;5)),AND($E68&lt;&gt;"",OR(LEN($E68)&lt;&gt;17,LEN($E68)-LEN(SUBSTITUTE($E68,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="H69">
         <f>IF(COUNTA($A69:$F69)=0,0,IF(OR($B69="",$D69=""),1,0))</f>
         <v/>
       </c>
+      <c r="I69">
+        <f>IF(OR(AND($D69&lt;&gt;"",OR(LEN($D69)&lt;&gt;17,LEN($D69)-LEN(SUBSTITUTE($D69,":",""))&lt;&gt;5)),AND($E69&lt;&gt;"",OR(LEN($E69)&lt;&gt;17,LEN($E69)-LEN(SUBSTITUTE($E69,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="H70">
         <f>IF(COUNTA($A70:$F70)=0,0,IF(OR($B70="",$D70=""),1,0))</f>
         <v/>
       </c>
+      <c r="I70">
+        <f>IF(OR(AND($D70&lt;&gt;"",OR(LEN($D70)&lt;&gt;17,LEN($D70)-LEN(SUBSTITUTE($D70,":",""))&lt;&gt;5)),AND($E70&lt;&gt;"",OR(LEN($E70)&lt;&gt;17,LEN($E70)-LEN(SUBSTITUTE($E70,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="H71">
         <f>IF(COUNTA($A71:$F71)=0,0,IF(OR($B71="",$D71=""),1,0))</f>
         <v/>
       </c>
+      <c r="I71">
+        <f>IF(OR(AND($D71&lt;&gt;"",OR(LEN($D71)&lt;&gt;17,LEN($D71)-LEN(SUBSTITUTE($D71,":",""))&lt;&gt;5)),AND($E71&lt;&gt;"",OR(LEN($E71)&lt;&gt;17,LEN($E71)-LEN(SUBSTITUTE($E71,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="H72">
         <f>IF(COUNTA($A72:$F72)=0,0,IF(OR($B72="",$D72=""),1,0))</f>
         <v/>
       </c>
+      <c r="I72">
+        <f>IF(OR(AND($D72&lt;&gt;"",OR(LEN($D72)&lt;&gt;17,LEN($D72)-LEN(SUBSTITUTE($D72,":",""))&lt;&gt;5)),AND($E72&lt;&gt;"",OR(LEN($E72)&lt;&gt;17,LEN($E72)-LEN(SUBSTITUTE($E72,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="H73">
         <f>IF(COUNTA($A73:$F73)=0,0,IF(OR($B73="",$D73=""),1,0))</f>
         <v/>
       </c>
+      <c r="I73">
+        <f>IF(OR(AND($D73&lt;&gt;"",OR(LEN($D73)&lt;&gt;17,LEN($D73)-LEN(SUBSTITUTE($D73,":",""))&lt;&gt;5)),AND($E73&lt;&gt;"",OR(LEN($E73)&lt;&gt;17,LEN($E73)-LEN(SUBSTITUTE($E73,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="H74">
         <f>IF(COUNTA($A74:$F74)=0,0,IF(OR($B74="",$D74=""),1,0))</f>
         <v/>
       </c>
+      <c r="I74">
+        <f>IF(OR(AND($D74&lt;&gt;"",OR(LEN($D74)&lt;&gt;17,LEN($D74)-LEN(SUBSTITUTE($D74,":",""))&lt;&gt;5)),AND($E74&lt;&gt;"",OR(LEN($E74)&lt;&gt;17,LEN($E74)-LEN(SUBSTITUTE($E74,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="H75">
         <f>IF(COUNTA($A75:$F75)=0,0,IF(OR($B75="",$D75=""),1,0))</f>
         <v/>
       </c>
+      <c r="I75">
+        <f>IF(OR(AND($D75&lt;&gt;"",OR(LEN($D75)&lt;&gt;17,LEN($D75)-LEN(SUBSTITUTE($D75,":",""))&lt;&gt;5)),AND($E75&lt;&gt;"",OR(LEN($E75)&lt;&gt;17,LEN($E75)-LEN(SUBSTITUTE($E75,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="H76">
         <f>IF(COUNTA($A76:$F76)=0,0,IF(OR($B76="",$D76=""),1,0))</f>
         <v/>
       </c>
+      <c r="I76">
+        <f>IF(OR(AND($D76&lt;&gt;"",OR(LEN($D76)&lt;&gt;17,LEN($D76)-LEN(SUBSTITUTE($D76,":",""))&lt;&gt;5)),AND($E76&lt;&gt;"",OR(LEN($E76)&lt;&gt;17,LEN($E76)-LEN(SUBSTITUTE($E76,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="H77">
         <f>IF(COUNTA($A77:$F77)=0,0,IF(OR($B77="",$D77=""),1,0))</f>
         <v/>
       </c>
+      <c r="I77">
+        <f>IF(OR(AND($D77&lt;&gt;"",OR(LEN($D77)&lt;&gt;17,LEN($D77)-LEN(SUBSTITUTE($D77,":",""))&lt;&gt;5)),AND($E77&lt;&gt;"",OR(LEN($E77)&lt;&gt;17,LEN($E77)-LEN(SUBSTITUTE($E77,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="H78">
         <f>IF(COUNTA($A78:$F78)=0,0,IF(OR($B78="",$D78=""),1,0))</f>
         <v/>
       </c>
+      <c r="I78">
+        <f>IF(OR(AND($D78&lt;&gt;"",OR(LEN($D78)&lt;&gt;17,LEN($D78)-LEN(SUBSTITUTE($D78,":",""))&lt;&gt;5)),AND($E78&lt;&gt;"",OR(LEN($E78)&lt;&gt;17,LEN($E78)-LEN(SUBSTITUTE($E78,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="H79">
         <f>IF(COUNTA($A79:$F79)=0,0,IF(OR($B79="",$D79=""),1,0))</f>
         <v/>
       </c>
+      <c r="I79">
+        <f>IF(OR(AND($D79&lt;&gt;"",OR(LEN($D79)&lt;&gt;17,LEN($D79)-LEN(SUBSTITUTE($D79,":",""))&lt;&gt;5)),AND($E79&lt;&gt;"",OR(LEN($E79)&lt;&gt;17,LEN($E79)-LEN(SUBSTITUTE($E79,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="H80">
         <f>IF(COUNTA($A80:$F80)=0,0,IF(OR($B80="",$D80=""),1,0))</f>
         <v/>
       </c>
+      <c r="I80">
+        <f>IF(OR(AND($D80&lt;&gt;"",OR(LEN($D80)&lt;&gt;17,LEN($D80)-LEN(SUBSTITUTE($D80,":",""))&lt;&gt;5)),AND($E80&lt;&gt;"",OR(LEN($E80)&lt;&gt;17,LEN($E80)-LEN(SUBSTITUTE($E80,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="H81">
         <f>IF(COUNTA($A81:$F81)=0,0,IF(OR($B81="",$D81=""),1,0))</f>
         <v/>
       </c>
+      <c r="I81">
+        <f>IF(OR(AND($D81&lt;&gt;"",OR(LEN($D81)&lt;&gt;17,LEN($D81)-LEN(SUBSTITUTE($D81,":",""))&lt;&gt;5)),AND($E81&lt;&gt;"",OR(LEN($E81)&lt;&gt;17,LEN($E81)-LEN(SUBSTITUTE($E81,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="H82">
         <f>IF(COUNTA($A82:$F82)=0,0,IF(OR($B82="",$D82=""),1,0))</f>
         <v/>
       </c>
+      <c r="I82">
+        <f>IF(OR(AND($D82&lt;&gt;"",OR(LEN($D82)&lt;&gt;17,LEN($D82)-LEN(SUBSTITUTE($D82,":",""))&lt;&gt;5)),AND($E82&lt;&gt;"",OR(LEN($E82)&lt;&gt;17,LEN($E82)-LEN(SUBSTITUTE($E82,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="H83">
         <f>IF(COUNTA($A83:$F83)=0,0,IF(OR($B83="",$D83=""),1,0))</f>
         <v/>
       </c>
+      <c r="I83">
+        <f>IF(OR(AND($D83&lt;&gt;"",OR(LEN($D83)&lt;&gt;17,LEN($D83)-LEN(SUBSTITUTE($D83,":",""))&lt;&gt;5)),AND($E83&lt;&gt;"",OR(LEN($E83)&lt;&gt;17,LEN($E83)-LEN(SUBSTITUTE($E83,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="H84">
         <f>IF(COUNTA($A84:$F84)=0,0,IF(OR($B84="",$D84=""),1,0))</f>
         <v/>
       </c>
+      <c r="I84">
+        <f>IF(OR(AND($D84&lt;&gt;"",OR(LEN($D84)&lt;&gt;17,LEN($D84)-LEN(SUBSTITUTE($D84,":",""))&lt;&gt;5)),AND($E84&lt;&gt;"",OR(LEN($E84)&lt;&gt;17,LEN($E84)-LEN(SUBSTITUTE($E84,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="H85">
         <f>IF(COUNTA($A85:$F85)=0,0,IF(OR($B85="",$D85=""),1,0))</f>
         <v/>
       </c>
+      <c r="I85">
+        <f>IF(OR(AND($D85&lt;&gt;"",OR(LEN($D85)&lt;&gt;17,LEN($D85)-LEN(SUBSTITUTE($D85,":",""))&lt;&gt;5)),AND($E85&lt;&gt;"",OR(LEN($E85)&lt;&gt;17,LEN($E85)-LEN(SUBSTITUTE($E85,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="H86">
         <f>IF(COUNTA($A86:$F86)=0,0,IF(OR($B86="",$D86=""),1,0))</f>
         <v/>
       </c>
+      <c r="I86">
+        <f>IF(OR(AND($D86&lt;&gt;"",OR(LEN($D86)&lt;&gt;17,LEN($D86)-LEN(SUBSTITUTE($D86,":",""))&lt;&gt;5)),AND($E86&lt;&gt;"",OR(LEN($E86)&lt;&gt;17,LEN($E86)-LEN(SUBSTITUTE($E86,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="H87">
         <f>IF(COUNTA($A87:$F87)=0,0,IF(OR($B87="",$D87=""),1,0))</f>
         <v/>
       </c>
+      <c r="I87">
+        <f>IF(OR(AND($D87&lt;&gt;"",OR(LEN($D87)&lt;&gt;17,LEN($D87)-LEN(SUBSTITUTE($D87,":",""))&lt;&gt;5)),AND($E87&lt;&gt;"",OR(LEN($E87)&lt;&gt;17,LEN($E87)-LEN(SUBSTITUTE($E87,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="H88">
         <f>IF(COUNTA($A88:$F88)=0,0,IF(OR($B88="",$D88=""),1,0))</f>
         <v/>
       </c>
+      <c r="I88">
+        <f>IF(OR(AND($D88&lt;&gt;"",OR(LEN($D88)&lt;&gt;17,LEN($D88)-LEN(SUBSTITUTE($D88,":",""))&lt;&gt;5)),AND($E88&lt;&gt;"",OR(LEN($E88)&lt;&gt;17,LEN($E88)-LEN(SUBSTITUTE($E88,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="H89">
         <f>IF(COUNTA($A89:$F89)=0,0,IF(OR($B89="",$D89=""),1,0))</f>
         <v/>
       </c>
+      <c r="I89">
+        <f>IF(OR(AND($D89&lt;&gt;"",OR(LEN($D89)&lt;&gt;17,LEN($D89)-LEN(SUBSTITUTE($D89,":",""))&lt;&gt;5)),AND($E89&lt;&gt;"",OR(LEN($E89)&lt;&gt;17,LEN($E89)-LEN(SUBSTITUTE($E89,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="H90">
         <f>IF(COUNTA($A90:$F90)=0,0,IF(OR($B90="",$D90=""),1,0))</f>
         <v/>
       </c>
+      <c r="I90">
+        <f>IF(OR(AND($D90&lt;&gt;"",OR(LEN($D90)&lt;&gt;17,LEN($D90)-LEN(SUBSTITUTE($D90,":",""))&lt;&gt;5)),AND($E90&lt;&gt;"",OR(LEN($E90)&lt;&gt;17,LEN($E90)-LEN(SUBSTITUTE($E90,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="H91">
         <f>IF(COUNTA($A91:$F91)=0,0,IF(OR($B91="",$D91=""),1,0))</f>
         <v/>
       </c>
+      <c r="I91">
+        <f>IF(OR(AND($D91&lt;&gt;"",OR(LEN($D91)&lt;&gt;17,LEN($D91)-LEN(SUBSTITUTE($D91,":",""))&lt;&gt;5)),AND($E91&lt;&gt;"",OR(LEN($E91)&lt;&gt;17,LEN($E91)-LEN(SUBSTITUTE($E91,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="H92">
         <f>IF(COUNTA($A92:$F92)=0,0,IF(OR($B92="",$D92=""),1,0))</f>
         <v/>
       </c>
+      <c r="I92">
+        <f>IF(OR(AND($D92&lt;&gt;"",OR(LEN($D92)&lt;&gt;17,LEN($D92)-LEN(SUBSTITUTE($D92,":",""))&lt;&gt;5)),AND($E92&lt;&gt;"",OR(LEN($E92)&lt;&gt;17,LEN($E92)-LEN(SUBSTITUTE($E92,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="H93">
         <f>IF(COUNTA($A93:$F93)=0,0,IF(OR($B93="",$D93=""),1,0))</f>
         <v/>
       </c>
+      <c r="I93">
+        <f>IF(OR(AND($D93&lt;&gt;"",OR(LEN($D93)&lt;&gt;17,LEN($D93)-LEN(SUBSTITUTE($D93,":",""))&lt;&gt;5)),AND($E93&lt;&gt;"",OR(LEN($E93)&lt;&gt;17,LEN($E93)-LEN(SUBSTITUTE($E93,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="H94">
         <f>IF(COUNTA($A94:$F94)=0,0,IF(OR($B94="",$D94=""),1,0))</f>
         <v/>
       </c>
+      <c r="I94">
+        <f>IF(OR(AND($D94&lt;&gt;"",OR(LEN($D94)&lt;&gt;17,LEN($D94)-LEN(SUBSTITUTE($D94,":",""))&lt;&gt;5)),AND($E94&lt;&gt;"",OR(LEN($E94)&lt;&gt;17,LEN($E94)-LEN(SUBSTITUTE($E94,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="H95">
         <f>IF(COUNTA($A95:$F95)=0,0,IF(OR($B95="",$D95=""),1,0))</f>
         <v/>
       </c>
+      <c r="I95">
+        <f>IF(OR(AND($D95&lt;&gt;"",OR(LEN($D95)&lt;&gt;17,LEN($D95)-LEN(SUBSTITUTE($D95,":",""))&lt;&gt;5)),AND($E95&lt;&gt;"",OR(LEN($E95)&lt;&gt;17,LEN($E95)-LEN(SUBSTITUTE($E95,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="H96">
         <f>IF(COUNTA($A96:$F96)=0,0,IF(OR($B96="",$D96=""),1,0))</f>
         <v/>
       </c>
+      <c r="I96">
+        <f>IF(OR(AND($D96&lt;&gt;"",OR(LEN($D96)&lt;&gt;17,LEN($D96)-LEN(SUBSTITUTE($D96,":",""))&lt;&gt;5)),AND($E96&lt;&gt;"",OR(LEN($E96)&lt;&gt;17,LEN($E96)-LEN(SUBSTITUTE($E96,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="H97">
         <f>IF(COUNTA($A97:$F97)=0,0,IF(OR($B97="",$D97=""),1,0))</f>
         <v/>
       </c>
+      <c r="I97">
+        <f>IF(OR(AND($D97&lt;&gt;"",OR(LEN($D97)&lt;&gt;17,LEN($D97)-LEN(SUBSTITUTE($D97,":",""))&lt;&gt;5)),AND($E97&lt;&gt;"",OR(LEN($E97)&lt;&gt;17,LEN($E97)-LEN(SUBSTITUTE($E97,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="H98">
         <f>IF(COUNTA($A98:$F98)=0,0,IF(OR($B98="",$D98=""),1,0))</f>
         <v/>
       </c>
+      <c r="I98">
+        <f>IF(OR(AND($D98&lt;&gt;"",OR(LEN($D98)&lt;&gt;17,LEN($D98)-LEN(SUBSTITUTE($D98,":",""))&lt;&gt;5)),AND($E98&lt;&gt;"",OR(LEN($E98)&lt;&gt;17,LEN($E98)-LEN(SUBSTITUTE($E98,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="H99">
         <f>IF(COUNTA($A99:$F99)=0,0,IF(OR($B99="",$D99=""),1,0))</f>
         <v/>
       </c>
+      <c r="I99">
+        <f>IF(OR(AND($D99&lt;&gt;"",OR(LEN($D99)&lt;&gt;17,LEN($D99)-LEN(SUBSTITUTE($D99,":",""))&lt;&gt;5)),AND($E99&lt;&gt;"",OR(LEN($E99)&lt;&gt;17,LEN($E99)-LEN(SUBSTITUTE($E99,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="H100">
         <f>IF(COUNTA($A100:$F100)=0,0,IF(OR($B100="",$D100=""),1,0))</f>
         <v/>
       </c>
+      <c r="I100">
+        <f>IF(OR(AND($D100&lt;&gt;"",OR(LEN($D100)&lt;&gt;17,LEN($D100)-LEN(SUBSTITUTE($D100,":",""))&lt;&gt;5)),AND($E100&lt;&gt;"",OR(LEN($E100)&lt;&gt;17,LEN($E100)-LEN(SUBSTITUTE($E100,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="H101">
         <f>IF(COUNTA($A101:$F101)=0,0,IF(OR($B101="",$D101=""),1,0))</f>
         <v/>
       </c>
+      <c r="I101">
+        <f>IF(OR(AND($D101&lt;&gt;"",OR(LEN($D101)&lt;&gt;17,LEN($D101)-LEN(SUBSTITUTE($D101,":",""))&lt;&gt;5)),AND($E101&lt;&gt;"",OR(LEN($E101)&lt;&gt;17,LEN($E101)-LEN(SUBSTITUTE($E101,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="H102">
         <f>IF(COUNTA($A102:$F102)=0,0,IF(OR($B102="",$D102=""),1,0))</f>
         <v/>
       </c>
+      <c r="I102">
+        <f>IF(OR(AND($D102&lt;&gt;"",OR(LEN($D102)&lt;&gt;17,LEN($D102)-LEN(SUBSTITUTE($D102,":",""))&lt;&gt;5)),AND($E102&lt;&gt;"",OR(LEN($E102)&lt;&gt;17,LEN($E102)-LEN(SUBSTITUTE($E102,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="H103">
         <f>IF(COUNTA($A103:$F103)=0,0,IF(OR($B103="",$D103=""),1,0))</f>
         <v/>
       </c>
+      <c r="I103">
+        <f>IF(OR(AND($D103&lt;&gt;"",OR(LEN($D103)&lt;&gt;17,LEN($D103)-LEN(SUBSTITUTE($D103,":",""))&lt;&gt;5)),AND($E103&lt;&gt;"",OR(LEN($E103)&lt;&gt;17,LEN($E103)-LEN(SUBSTITUTE($E103,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="H104">
         <f>IF(COUNTA($A104:$F104)=0,0,IF(OR($B104="",$D104=""),1,0))</f>
         <v/>
       </c>
+      <c r="I104">
+        <f>IF(OR(AND($D104&lt;&gt;"",OR(LEN($D104)&lt;&gt;17,LEN($D104)-LEN(SUBSTITUTE($D104,":",""))&lt;&gt;5)),AND($E104&lt;&gt;"",OR(LEN($E104)&lt;&gt;17,LEN($E104)-LEN(SUBSTITUTE($E104,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="H105">
         <f>IF(COUNTA($A105:$F105)=0,0,IF(OR($B105="",$D105=""),1,0))</f>
         <v/>
       </c>
+      <c r="I105">
+        <f>IF(OR(AND($D105&lt;&gt;"",OR(LEN($D105)&lt;&gt;17,LEN($D105)-LEN(SUBSTITUTE($D105,":",""))&lt;&gt;5)),AND($E105&lt;&gt;"",OR(LEN($E105)&lt;&gt;17,LEN($E105)-LEN(SUBSTITUTE($E105,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="H106">
         <f>IF(COUNTA($A106:$F106)=0,0,IF(OR($B106="",$D106=""),1,0))</f>
         <v/>
       </c>
+      <c r="I106">
+        <f>IF(OR(AND($D106&lt;&gt;"",OR(LEN($D106)&lt;&gt;17,LEN($D106)-LEN(SUBSTITUTE($D106,":",""))&lt;&gt;5)),AND($E106&lt;&gt;"",OR(LEN($E106)&lt;&gt;17,LEN($E106)-LEN(SUBSTITUTE($E106,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="H107">
         <f>IF(COUNTA($A107:$F107)=0,0,IF(OR($B107="",$D107=""),1,0))</f>
         <v/>
       </c>
+      <c r="I107">
+        <f>IF(OR(AND($D107&lt;&gt;"",OR(LEN($D107)&lt;&gt;17,LEN($D107)-LEN(SUBSTITUTE($D107,":",""))&lt;&gt;5)),AND($E107&lt;&gt;"",OR(LEN($E107)&lt;&gt;17,LEN($E107)-LEN(SUBSTITUTE($E107,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="H108">
         <f>IF(COUNTA($A108:$F108)=0,0,IF(OR($B108="",$D108=""),1,0))</f>
         <v/>
       </c>
+      <c r="I108">
+        <f>IF(OR(AND($D108&lt;&gt;"",OR(LEN($D108)&lt;&gt;17,LEN($D108)-LEN(SUBSTITUTE($D108,":",""))&lt;&gt;5)),AND($E108&lt;&gt;"",OR(LEN($E108)&lt;&gt;17,LEN($E108)-LEN(SUBSTITUTE($E108,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="H109">
         <f>IF(COUNTA($A109:$F109)=0,0,IF(OR($B109="",$D109=""),1,0))</f>
         <v/>
       </c>
+      <c r="I109">
+        <f>IF(OR(AND($D109&lt;&gt;"",OR(LEN($D109)&lt;&gt;17,LEN($D109)-LEN(SUBSTITUTE($D109,":",""))&lt;&gt;5)),AND($E109&lt;&gt;"",OR(LEN($E109)&lt;&gt;17,LEN($E109)-LEN(SUBSTITUTE($E109,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="H110">
         <f>IF(COUNTA($A110:$F110)=0,0,IF(OR($B110="",$D110=""),1,0))</f>
         <v/>
       </c>
+      <c r="I110">
+        <f>IF(OR(AND($D110&lt;&gt;"",OR(LEN($D110)&lt;&gt;17,LEN($D110)-LEN(SUBSTITUTE($D110,":",""))&lt;&gt;5)),AND($E110&lt;&gt;"",OR(LEN($E110)&lt;&gt;17,LEN($E110)-LEN(SUBSTITUTE($E110,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="H111">
         <f>IF(COUNTA($A111:$F111)=0,0,IF(OR($B111="",$D111=""),1,0))</f>
         <v/>
       </c>
+      <c r="I111">
+        <f>IF(OR(AND($D111&lt;&gt;"",OR(LEN($D111)&lt;&gt;17,LEN($D111)-LEN(SUBSTITUTE($D111,":",""))&lt;&gt;5)),AND($E111&lt;&gt;"",OR(LEN($E111)&lt;&gt;17,LEN($E111)-LEN(SUBSTITUTE($E111,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="H112">
         <f>IF(COUNTA($A112:$F112)=0,0,IF(OR($B112="",$D112=""),1,0))</f>
         <v/>
       </c>
+      <c r="I112">
+        <f>IF(OR(AND($D112&lt;&gt;"",OR(LEN($D112)&lt;&gt;17,LEN($D112)-LEN(SUBSTITUTE($D112,":",""))&lt;&gt;5)),AND($E112&lt;&gt;"",OR(LEN($E112)&lt;&gt;17,LEN($E112)-LEN(SUBSTITUTE($E112,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="H113">
         <f>IF(COUNTA($A113:$F113)=0,0,IF(OR($B113="",$D113=""),1,0))</f>
         <v/>
       </c>
+      <c r="I113">
+        <f>IF(OR(AND($D113&lt;&gt;"",OR(LEN($D113)&lt;&gt;17,LEN($D113)-LEN(SUBSTITUTE($D113,":",""))&lt;&gt;5)),AND($E113&lt;&gt;"",OR(LEN($E113)&lt;&gt;17,LEN($E113)-LEN(SUBSTITUTE($E113,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="H114">
         <f>IF(COUNTA($A114:$F114)=0,0,IF(OR($B114="",$D114=""),1,0))</f>
         <v/>
       </c>
+      <c r="I114">
+        <f>IF(OR(AND($D114&lt;&gt;"",OR(LEN($D114)&lt;&gt;17,LEN($D114)-LEN(SUBSTITUTE($D114,":",""))&lt;&gt;5)),AND($E114&lt;&gt;"",OR(LEN($E114)&lt;&gt;17,LEN($E114)-LEN(SUBSTITUTE($E114,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="H115">
         <f>IF(COUNTA($A115:$F115)=0,0,IF(OR($B115="",$D115=""),1,0))</f>
         <v/>
       </c>
+      <c r="I115">
+        <f>IF(OR(AND($D115&lt;&gt;"",OR(LEN($D115)&lt;&gt;17,LEN($D115)-LEN(SUBSTITUTE($D115,":",""))&lt;&gt;5)),AND($E115&lt;&gt;"",OR(LEN($E115)&lt;&gt;17,LEN($E115)-LEN(SUBSTITUTE($E115,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="H116">
         <f>IF(COUNTA($A116:$F116)=0,0,IF(OR($B116="",$D116=""),1,0))</f>
         <v/>
       </c>
+      <c r="I116">
+        <f>IF(OR(AND($D116&lt;&gt;"",OR(LEN($D116)&lt;&gt;17,LEN($D116)-LEN(SUBSTITUTE($D116,":",""))&lt;&gt;5)),AND($E116&lt;&gt;"",OR(LEN($E116)&lt;&gt;17,LEN($E116)-LEN(SUBSTITUTE($E116,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="H117">
         <f>IF(COUNTA($A117:$F117)=0,0,IF(OR($B117="",$D117=""),1,0))</f>
         <v/>
       </c>
+      <c r="I117">
+        <f>IF(OR(AND($D117&lt;&gt;"",OR(LEN($D117)&lt;&gt;17,LEN($D117)-LEN(SUBSTITUTE($D117,":",""))&lt;&gt;5)),AND($E117&lt;&gt;"",OR(LEN($E117)&lt;&gt;17,LEN($E117)-LEN(SUBSTITUTE($E117,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="H118">
         <f>IF(COUNTA($A118:$F118)=0,0,IF(OR($B118="",$D118=""),1,0))</f>
         <v/>
       </c>
+      <c r="I118">
+        <f>IF(OR(AND($D118&lt;&gt;"",OR(LEN($D118)&lt;&gt;17,LEN($D118)-LEN(SUBSTITUTE($D118,":",""))&lt;&gt;5)),AND($E118&lt;&gt;"",OR(LEN($E118)&lt;&gt;17,LEN($E118)-LEN(SUBSTITUTE($E118,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="H119">
         <f>IF(COUNTA($A119:$F119)=0,0,IF(OR($B119="",$D119=""),1,0))</f>
         <v/>
       </c>
+      <c r="I119">
+        <f>IF(OR(AND($D119&lt;&gt;"",OR(LEN($D119)&lt;&gt;17,LEN($D119)-LEN(SUBSTITUTE($D119,":",""))&lt;&gt;5)),AND($E119&lt;&gt;"",OR(LEN($E119)&lt;&gt;17,LEN($E119)-LEN(SUBSTITUTE($E119,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="H120">
         <f>IF(COUNTA($A120:$F120)=0,0,IF(OR($B120="",$D120=""),1,0))</f>
         <v/>
       </c>
+      <c r="I120">
+        <f>IF(OR(AND($D120&lt;&gt;"",OR(LEN($D120)&lt;&gt;17,LEN($D120)-LEN(SUBSTITUTE($D120,":",""))&lt;&gt;5)),AND($E120&lt;&gt;"",OR(LEN($E120)&lt;&gt;17,LEN($E120)-LEN(SUBSTITUTE($E120,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="H121">
         <f>IF(COUNTA($A121:$F121)=0,0,IF(OR($B121="",$D121=""),1,0))</f>
         <v/>
       </c>
+      <c r="I121">
+        <f>IF(OR(AND($D121&lt;&gt;"",OR(LEN($D121)&lt;&gt;17,LEN($D121)-LEN(SUBSTITUTE($D121,":",""))&lt;&gt;5)),AND($E121&lt;&gt;"",OR(LEN($E121)&lt;&gt;17,LEN($E121)-LEN(SUBSTITUTE($E121,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="H122">
         <f>IF(COUNTA($A122:$F122)=0,0,IF(OR($B122="",$D122=""),1,0))</f>
         <v/>
       </c>
+      <c r="I122">
+        <f>IF(OR(AND($D122&lt;&gt;"",OR(LEN($D122)&lt;&gt;17,LEN($D122)-LEN(SUBSTITUTE($D122,":",""))&lt;&gt;5)),AND($E122&lt;&gt;"",OR(LEN($E122)&lt;&gt;17,LEN($E122)-LEN(SUBSTITUTE($E122,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="H123">
         <f>IF(COUNTA($A123:$F123)=0,0,IF(OR($B123="",$D123=""),1,0))</f>
         <v/>
       </c>
+      <c r="I123">
+        <f>IF(OR(AND($D123&lt;&gt;"",OR(LEN($D123)&lt;&gt;17,LEN($D123)-LEN(SUBSTITUTE($D123,":",""))&lt;&gt;5)),AND($E123&lt;&gt;"",OR(LEN($E123)&lt;&gt;17,LEN($E123)-LEN(SUBSTITUTE($E123,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="H124">
         <f>IF(COUNTA($A124:$F124)=0,0,IF(OR($B124="",$D124=""),1,0))</f>
         <v/>
       </c>
+      <c r="I124">
+        <f>IF(OR(AND($D124&lt;&gt;"",OR(LEN($D124)&lt;&gt;17,LEN($D124)-LEN(SUBSTITUTE($D124,":",""))&lt;&gt;5)),AND($E124&lt;&gt;"",OR(LEN($E124)&lt;&gt;17,LEN($E124)-LEN(SUBSTITUTE($E124,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="H125">
         <f>IF(COUNTA($A125:$F125)=0,0,IF(OR($B125="",$D125=""),1,0))</f>
         <v/>
       </c>
+      <c r="I125">
+        <f>IF(OR(AND($D125&lt;&gt;"",OR(LEN($D125)&lt;&gt;17,LEN($D125)-LEN(SUBSTITUTE($D125,":",""))&lt;&gt;5)),AND($E125&lt;&gt;"",OR(LEN($E125)&lt;&gt;17,LEN($E125)-LEN(SUBSTITUTE($E125,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="H126">
         <f>IF(COUNTA($A126:$F126)=0,0,IF(OR($B126="",$D126=""),1,0))</f>
         <v/>
       </c>
+      <c r="I126">
+        <f>IF(OR(AND($D126&lt;&gt;"",OR(LEN($D126)&lt;&gt;17,LEN($D126)-LEN(SUBSTITUTE($D126,":",""))&lt;&gt;5)),AND($E126&lt;&gt;"",OR(LEN($E126)&lt;&gt;17,LEN($E126)-LEN(SUBSTITUTE($E126,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="H127">
         <f>IF(COUNTA($A127:$F127)=0,0,IF(OR($B127="",$D127=""),1,0))</f>
         <v/>
       </c>
+      <c r="I127">
+        <f>IF(OR(AND($D127&lt;&gt;"",OR(LEN($D127)&lt;&gt;17,LEN($D127)-LEN(SUBSTITUTE($D127,":",""))&lt;&gt;5)),AND($E127&lt;&gt;"",OR(LEN($E127)&lt;&gt;17,LEN($E127)-LEN(SUBSTITUTE($E127,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="H128">
         <f>IF(COUNTA($A128:$F128)=0,0,IF(OR($B128="",$D128=""),1,0))</f>
         <v/>
       </c>
+      <c r="I128">
+        <f>IF(OR(AND($D128&lt;&gt;"",OR(LEN($D128)&lt;&gt;17,LEN($D128)-LEN(SUBSTITUTE($D128,":",""))&lt;&gt;5)),AND($E128&lt;&gt;"",OR(LEN($E128)&lt;&gt;17,LEN($E128)-LEN(SUBSTITUTE($E128,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="H129">
         <f>IF(COUNTA($A129:$F129)=0,0,IF(OR($B129="",$D129=""),1,0))</f>
         <v/>
       </c>
+      <c r="I129">
+        <f>IF(OR(AND($D129&lt;&gt;"",OR(LEN($D129)&lt;&gt;17,LEN($D129)-LEN(SUBSTITUTE($D129,":",""))&lt;&gt;5)),AND($E129&lt;&gt;"",OR(LEN($E129)&lt;&gt;17,LEN($E129)-LEN(SUBSTITUTE($E129,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="H130">
         <f>IF(COUNTA($A130:$F130)=0,0,IF(OR($B130="",$D130=""),1,0))</f>
         <v/>
       </c>
+      <c r="I130">
+        <f>IF(OR(AND($D130&lt;&gt;"",OR(LEN($D130)&lt;&gt;17,LEN($D130)-LEN(SUBSTITUTE($D130,":",""))&lt;&gt;5)),AND($E130&lt;&gt;"",OR(LEN($E130)&lt;&gt;17,LEN($E130)-LEN(SUBSTITUTE($E130,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="H131">
         <f>IF(COUNTA($A131:$F131)=0,0,IF(OR($B131="",$D131=""),1,0))</f>
         <v/>
       </c>
+      <c r="I131">
+        <f>IF(OR(AND($D131&lt;&gt;"",OR(LEN($D131)&lt;&gt;17,LEN($D131)-LEN(SUBSTITUTE($D131,":",""))&lt;&gt;5)),AND($E131&lt;&gt;"",OR(LEN($E131)&lt;&gt;17,LEN($E131)-LEN(SUBSTITUTE($E131,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="H132">
         <f>IF(COUNTA($A132:$F132)=0,0,IF(OR($B132="",$D132=""),1,0))</f>
         <v/>
       </c>
+      <c r="I132">
+        <f>IF(OR(AND($D132&lt;&gt;"",OR(LEN($D132)&lt;&gt;17,LEN($D132)-LEN(SUBSTITUTE($D132,":",""))&lt;&gt;5)),AND($E132&lt;&gt;"",OR(LEN($E132)&lt;&gt;17,LEN($E132)-LEN(SUBSTITUTE($E132,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="H133">
         <f>IF(COUNTA($A133:$F133)=0,0,IF(OR($B133="",$D133=""),1,0))</f>
         <v/>
       </c>
+      <c r="I133">
+        <f>IF(OR(AND($D133&lt;&gt;"",OR(LEN($D133)&lt;&gt;17,LEN($D133)-LEN(SUBSTITUTE($D133,":",""))&lt;&gt;5)),AND($E133&lt;&gt;"",OR(LEN($E133)&lt;&gt;17,LEN($E133)-LEN(SUBSTITUTE($E133,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="H134">
         <f>IF(COUNTA($A134:$F134)=0,0,IF(OR($B134="",$D134=""),1,0))</f>
         <v/>
       </c>
+      <c r="I134">
+        <f>IF(OR(AND($D134&lt;&gt;"",OR(LEN($D134)&lt;&gt;17,LEN($D134)-LEN(SUBSTITUTE($D134,":",""))&lt;&gt;5)),AND($E134&lt;&gt;"",OR(LEN($E134)&lt;&gt;17,LEN($E134)-LEN(SUBSTITUTE($E134,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="H135">
         <f>IF(COUNTA($A135:$F135)=0,0,IF(OR($B135="",$D135=""),1,0))</f>
         <v/>
       </c>
+      <c r="I135">
+        <f>IF(OR(AND($D135&lt;&gt;"",OR(LEN($D135)&lt;&gt;17,LEN($D135)-LEN(SUBSTITUTE($D135,":",""))&lt;&gt;5)),AND($E135&lt;&gt;"",OR(LEN($E135)&lt;&gt;17,LEN($E135)-LEN(SUBSTITUTE($E135,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="H136">
         <f>IF(COUNTA($A136:$F136)=0,0,IF(OR($B136="",$D136=""),1,0))</f>
         <v/>
       </c>
+      <c r="I136">
+        <f>IF(OR(AND($D136&lt;&gt;"",OR(LEN($D136)&lt;&gt;17,LEN($D136)-LEN(SUBSTITUTE($D136,":",""))&lt;&gt;5)),AND($E136&lt;&gt;"",OR(LEN($E136)&lt;&gt;17,LEN($E136)-LEN(SUBSTITUTE($E136,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="H137">
         <f>IF(COUNTA($A137:$F137)=0,0,IF(OR($B137="",$D137=""),1,0))</f>
         <v/>
       </c>
+      <c r="I137">
+        <f>IF(OR(AND($D137&lt;&gt;"",OR(LEN($D137)&lt;&gt;17,LEN($D137)-LEN(SUBSTITUTE($D137,":",""))&lt;&gt;5)),AND($E137&lt;&gt;"",OR(LEN($E137)&lt;&gt;17,LEN($E137)-LEN(SUBSTITUTE($E137,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="H138">
         <f>IF(COUNTA($A138:$F138)=0,0,IF(OR($B138="",$D138=""),1,0))</f>
         <v/>
       </c>
+      <c r="I138">
+        <f>IF(OR(AND($D138&lt;&gt;"",OR(LEN($D138)&lt;&gt;17,LEN($D138)-LEN(SUBSTITUTE($D138,":",""))&lt;&gt;5)),AND($E138&lt;&gt;"",OR(LEN($E138)&lt;&gt;17,LEN($E138)-LEN(SUBSTITUTE($E138,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="H139">
         <f>IF(COUNTA($A139:$F139)=0,0,IF(OR($B139="",$D139=""),1,0))</f>
         <v/>
       </c>
+      <c r="I139">
+        <f>IF(OR(AND($D139&lt;&gt;"",OR(LEN($D139)&lt;&gt;17,LEN($D139)-LEN(SUBSTITUTE($D139,":",""))&lt;&gt;5)),AND($E139&lt;&gt;"",OR(LEN($E139)&lt;&gt;17,LEN($E139)-LEN(SUBSTITUTE($E139,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="140">
       <c r="H140">
         <f>IF(COUNTA($A140:$F140)=0,0,IF(OR($B140="",$D140=""),1,0))</f>
         <v/>
       </c>
+      <c r="I140">
+        <f>IF(OR(AND($D140&lt;&gt;"",OR(LEN($D140)&lt;&gt;17,LEN($D140)-LEN(SUBSTITUTE($D140,":",""))&lt;&gt;5)),AND($E140&lt;&gt;"",OR(LEN($E140)&lt;&gt;17,LEN($E140)-LEN(SUBSTITUTE($E140,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="H141">
         <f>IF(COUNTA($A141:$F141)=0,0,IF(OR($B141="",$D141=""),1,0))</f>
         <v/>
       </c>
+      <c r="I141">
+        <f>IF(OR(AND($D141&lt;&gt;"",OR(LEN($D141)&lt;&gt;17,LEN($D141)-LEN(SUBSTITUTE($D141,":",""))&lt;&gt;5)),AND($E141&lt;&gt;"",OR(LEN($E141)&lt;&gt;17,LEN($E141)-LEN(SUBSTITUTE($E141,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="H142">
         <f>IF(COUNTA($A142:$F142)=0,0,IF(OR($B142="",$D142=""),1,0))</f>
         <v/>
       </c>
+      <c r="I142">
+        <f>IF(OR(AND($D142&lt;&gt;"",OR(LEN($D142)&lt;&gt;17,LEN($D142)-LEN(SUBSTITUTE($D142,":",""))&lt;&gt;5)),AND($E142&lt;&gt;"",OR(LEN($E142)&lt;&gt;17,LEN($E142)-LEN(SUBSTITUTE($E142,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="H143">
         <f>IF(COUNTA($A143:$F143)=0,0,IF(OR($B143="",$D143=""),1,0))</f>
         <v/>
       </c>
+      <c r="I143">
+        <f>IF(OR(AND($D143&lt;&gt;"",OR(LEN($D143)&lt;&gt;17,LEN($D143)-LEN(SUBSTITUTE($D143,":",""))&lt;&gt;5)),AND($E143&lt;&gt;"",OR(LEN($E143)&lt;&gt;17,LEN($E143)-LEN(SUBSTITUTE($E143,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="H144">
         <f>IF(COUNTA($A144:$F144)=0,0,IF(OR($B144="",$D144=""),1,0))</f>
         <v/>
       </c>
+      <c r="I144">
+        <f>IF(OR(AND($D144&lt;&gt;"",OR(LEN($D144)&lt;&gt;17,LEN($D144)-LEN(SUBSTITUTE($D144,":",""))&lt;&gt;5)),AND($E144&lt;&gt;"",OR(LEN($E144)&lt;&gt;17,LEN($E144)-LEN(SUBSTITUTE($E144,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="H145">
         <f>IF(COUNTA($A145:$F145)=0,0,IF(OR($B145="",$D145=""),1,0))</f>
         <v/>
       </c>
+      <c r="I145">
+        <f>IF(OR(AND($D145&lt;&gt;"",OR(LEN($D145)&lt;&gt;17,LEN($D145)-LEN(SUBSTITUTE($D145,":",""))&lt;&gt;5)),AND($E145&lt;&gt;"",OR(LEN($E145)&lt;&gt;17,LEN($E145)-LEN(SUBSTITUTE($E145,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="H146">
         <f>IF(COUNTA($A146:$F146)=0,0,IF(OR($B146="",$D146=""),1,0))</f>
         <v/>
       </c>
+      <c r="I146">
+        <f>IF(OR(AND($D146&lt;&gt;"",OR(LEN($D146)&lt;&gt;17,LEN($D146)-LEN(SUBSTITUTE($D146,":",""))&lt;&gt;5)),AND($E146&lt;&gt;"",OR(LEN($E146)&lt;&gt;17,LEN($E146)-LEN(SUBSTITUTE($E146,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="147">
       <c r="H147">
         <f>IF(COUNTA($A147:$F147)=0,0,IF(OR($B147="",$D147=""),1,0))</f>
         <v/>
       </c>
+      <c r="I147">
+        <f>IF(OR(AND($D147&lt;&gt;"",OR(LEN($D147)&lt;&gt;17,LEN($D147)-LEN(SUBSTITUTE($D147,":",""))&lt;&gt;5)),AND($E147&lt;&gt;"",OR(LEN($E147)&lt;&gt;17,LEN($E147)-LEN(SUBSTITUTE($E147,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="H148">
         <f>IF(COUNTA($A148:$F148)=0,0,IF(OR($B148="",$D148=""),1,0))</f>
         <v/>
       </c>
+      <c r="I148">
+        <f>IF(OR(AND($D148&lt;&gt;"",OR(LEN($D148)&lt;&gt;17,LEN($D148)-LEN(SUBSTITUTE($D148,":",""))&lt;&gt;5)),AND($E148&lt;&gt;"",OR(LEN($E148)&lt;&gt;17,LEN($E148)-LEN(SUBSTITUTE($E148,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="149">
       <c r="H149">
         <f>IF(COUNTA($A149:$F149)=0,0,IF(OR($B149="",$D149=""),1,0))</f>
         <v/>
       </c>
+      <c r="I149">
+        <f>IF(OR(AND($D149&lt;&gt;"",OR(LEN($D149)&lt;&gt;17,LEN($D149)-LEN(SUBSTITUTE($D149,":",""))&lt;&gt;5)),AND($E149&lt;&gt;"",OR(LEN($E149)&lt;&gt;17,LEN($E149)-LEN(SUBSTITUTE($E149,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="150">
       <c r="H150">
         <f>IF(COUNTA($A150:$F150)=0,0,IF(OR($B150="",$D150=""),1,0))</f>
         <v/>
       </c>
+      <c r="I150">
+        <f>IF(OR(AND($D150&lt;&gt;"",OR(LEN($D150)&lt;&gt;17,LEN($D150)-LEN(SUBSTITUTE($D150,":",""))&lt;&gt;5)),AND($E150&lt;&gt;"",OR(LEN($E150)&lt;&gt;17,LEN($E150)-LEN(SUBSTITUTE($E150,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="151">
       <c r="H151">
         <f>IF(COUNTA($A151:$F151)=0,0,IF(OR($B151="",$D151=""),1,0))</f>
         <v/>
       </c>
+      <c r="I151">
+        <f>IF(OR(AND($D151&lt;&gt;"",OR(LEN($D151)&lt;&gt;17,LEN($D151)-LEN(SUBSTITUTE($D151,":",""))&lt;&gt;5)),AND($E151&lt;&gt;"",OR(LEN($E151)&lt;&gt;17,LEN($E151)-LEN(SUBSTITUTE($E151,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="152">
       <c r="H152">
         <f>IF(COUNTA($A152:$F152)=0,0,IF(OR($B152="",$D152=""),1,0))</f>
         <v/>
       </c>
+      <c r="I152">
+        <f>IF(OR(AND($D152&lt;&gt;"",OR(LEN($D152)&lt;&gt;17,LEN($D152)-LEN(SUBSTITUTE($D152,":",""))&lt;&gt;5)),AND($E152&lt;&gt;"",OR(LEN($E152)&lt;&gt;17,LEN($E152)-LEN(SUBSTITUTE($E152,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="153">
       <c r="H153">
         <f>IF(COUNTA($A153:$F153)=0,0,IF(OR($B153="",$D153=""),1,0))</f>
         <v/>
       </c>
+      <c r="I153">
+        <f>IF(OR(AND($D153&lt;&gt;"",OR(LEN($D153)&lt;&gt;17,LEN($D153)-LEN(SUBSTITUTE($D153,":",""))&lt;&gt;5)),AND($E153&lt;&gt;"",OR(LEN($E153)&lt;&gt;17,LEN($E153)-LEN(SUBSTITUTE($E153,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="154">
       <c r="H154">
         <f>IF(COUNTA($A154:$F154)=0,0,IF(OR($B154="",$D154=""),1,0))</f>
         <v/>
       </c>
+      <c r="I154">
+        <f>IF(OR(AND($D154&lt;&gt;"",OR(LEN($D154)&lt;&gt;17,LEN($D154)-LEN(SUBSTITUTE($D154,":",""))&lt;&gt;5)),AND($E154&lt;&gt;"",OR(LEN($E154)&lt;&gt;17,LEN($E154)-LEN(SUBSTITUTE($E154,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="155">
       <c r="H155">
         <f>IF(COUNTA($A155:$F155)=0,0,IF(OR($B155="",$D155=""),1,0))</f>
         <v/>
       </c>
+      <c r="I155">
+        <f>IF(OR(AND($D155&lt;&gt;"",OR(LEN($D155)&lt;&gt;17,LEN($D155)-LEN(SUBSTITUTE($D155,":",""))&lt;&gt;5)),AND($E155&lt;&gt;"",OR(LEN($E155)&lt;&gt;17,LEN($E155)-LEN(SUBSTITUTE($E155,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="156">
       <c r="H156">
         <f>IF(COUNTA($A156:$F156)=0,0,IF(OR($B156="",$D156=""),1,0))</f>
         <v/>
       </c>
+      <c r="I156">
+        <f>IF(OR(AND($D156&lt;&gt;"",OR(LEN($D156)&lt;&gt;17,LEN($D156)-LEN(SUBSTITUTE($D156,":",""))&lt;&gt;5)),AND($E156&lt;&gt;"",OR(LEN($E156)&lt;&gt;17,LEN($E156)-LEN(SUBSTITUTE($E156,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="157">
       <c r="H157">
         <f>IF(COUNTA($A157:$F157)=0,0,IF(OR($B157="",$D157=""),1,0))</f>
         <v/>
       </c>
+      <c r="I157">
+        <f>IF(OR(AND($D157&lt;&gt;"",OR(LEN($D157)&lt;&gt;17,LEN($D157)-LEN(SUBSTITUTE($D157,":",""))&lt;&gt;5)),AND($E157&lt;&gt;"",OR(LEN($E157)&lt;&gt;17,LEN($E157)-LEN(SUBSTITUTE($E157,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="158">
       <c r="H158">
         <f>IF(COUNTA($A158:$F158)=0,0,IF(OR($B158="",$D158=""),1,0))</f>
         <v/>
       </c>
+      <c r="I158">
+        <f>IF(OR(AND($D158&lt;&gt;"",OR(LEN($D158)&lt;&gt;17,LEN($D158)-LEN(SUBSTITUTE($D158,":",""))&lt;&gt;5)),AND($E158&lt;&gt;"",OR(LEN($E158)&lt;&gt;17,LEN($E158)-LEN(SUBSTITUTE($E158,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="159">
       <c r="H159">
         <f>IF(COUNTA($A159:$F159)=0,0,IF(OR($B159="",$D159=""),1,0))</f>
         <v/>
       </c>
+      <c r="I159">
+        <f>IF(OR(AND($D159&lt;&gt;"",OR(LEN($D159)&lt;&gt;17,LEN($D159)-LEN(SUBSTITUTE($D159,":",""))&lt;&gt;5)),AND($E159&lt;&gt;"",OR(LEN($E159)&lt;&gt;17,LEN($E159)-LEN(SUBSTITUTE($E159,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="160">
       <c r="H160">
         <f>IF(COUNTA($A160:$F160)=0,0,IF(OR($B160="",$D160=""),1,0))</f>
         <v/>
       </c>
+      <c r="I160">
+        <f>IF(OR(AND($D160&lt;&gt;"",OR(LEN($D160)&lt;&gt;17,LEN($D160)-LEN(SUBSTITUTE($D160,":",""))&lt;&gt;5)),AND($E160&lt;&gt;"",OR(LEN($E160)&lt;&gt;17,LEN($E160)-LEN(SUBSTITUTE($E160,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="161">
       <c r="H161">
         <f>IF(COUNTA($A161:$F161)=0,0,IF(OR($B161="",$D161=""),1,0))</f>
         <v/>
       </c>
+      <c r="I161">
+        <f>IF(OR(AND($D161&lt;&gt;"",OR(LEN($D161)&lt;&gt;17,LEN($D161)-LEN(SUBSTITUTE($D161,":",""))&lt;&gt;5)),AND($E161&lt;&gt;"",OR(LEN($E161)&lt;&gt;17,LEN($E161)-LEN(SUBSTITUTE($E161,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="162">
       <c r="H162">
         <f>IF(COUNTA($A162:$F162)=0,0,IF(OR($B162="",$D162=""),1,0))</f>
         <v/>
       </c>
+      <c r="I162">
+        <f>IF(OR(AND($D162&lt;&gt;"",OR(LEN($D162)&lt;&gt;17,LEN($D162)-LEN(SUBSTITUTE($D162,":",""))&lt;&gt;5)),AND($E162&lt;&gt;"",OR(LEN($E162)&lt;&gt;17,LEN($E162)-LEN(SUBSTITUTE($E162,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="163">
       <c r="H163">
         <f>IF(COUNTA($A163:$F163)=0,0,IF(OR($B163="",$D163=""),1,0))</f>
         <v/>
       </c>
+      <c r="I163">
+        <f>IF(OR(AND($D163&lt;&gt;"",OR(LEN($D163)&lt;&gt;17,LEN($D163)-LEN(SUBSTITUTE($D163,":",""))&lt;&gt;5)),AND($E163&lt;&gt;"",OR(LEN($E163)&lt;&gt;17,LEN($E163)-LEN(SUBSTITUTE($E163,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="164">
       <c r="H164">
         <f>IF(COUNTA($A164:$F164)=0,0,IF(OR($B164="",$D164=""),1,0))</f>
         <v/>
       </c>
+      <c r="I164">
+        <f>IF(OR(AND($D164&lt;&gt;"",OR(LEN($D164)&lt;&gt;17,LEN($D164)-LEN(SUBSTITUTE($D164,":",""))&lt;&gt;5)),AND($E164&lt;&gt;"",OR(LEN($E164)&lt;&gt;17,LEN($E164)-LEN(SUBSTITUTE($E164,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="165">
       <c r="H165">
         <f>IF(COUNTA($A165:$F165)=0,0,IF(OR($B165="",$D165=""),1,0))</f>
         <v/>
       </c>
+      <c r="I165">
+        <f>IF(OR(AND($D165&lt;&gt;"",OR(LEN($D165)&lt;&gt;17,LEN($D165)-LEN(SUBSTITUTE($D165,":",""))&lt;&gt;5)),AND($E165&lt;&gt;"",OR(LEN($E165)&lt;&gt;17,LEN($E165)-LEN(SUBSTITUTE($E165,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="166">
       <c r="H166">
         <f>IF(COUNTA($A166:$F166)=0,0,IF(OR($B166="",$D166=""),1,0))</f>
         <v/>
       </c>
+      <c r="I166">
+        <f>IF(OR(AND($D166&lt;&gt;"",OR(LEN($D166)&lt;&gt;17,LEN($D166)-LEN(SUBSTITUTE($D166,":",""))&lt;&gt;5)),AND($E166&lt;&gt;"",OR(LEN($E166)&lt;&gt;17,LEN($E166)-LEN(SUBSTITUTE($E166,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="167">
       <c r="H167">
         <f>IF(COUNTA($A167:$F167)=0,0,IF(OR($B167="",$D167=""),1,0))</f>
         <v/>
       </c>
+      <c r="I167">
+        <f>IF(OR(AND($D167&lt;&gt;"",OR(LEN($D167)&lt;&gt;17,LEN($D167)-LEN(SUBSTITUTE($D167,":",""))&lt;&gt;5)),AND($E167&lt;&gt;"",OR(LEN($E167)&lt;&gt;17,LEN($E167)-LEN(SUBSTITUTE($E167,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="168">
       <c r="H168">
         <f>IF(COUNTA($A168:$F168)=0,0,IF(OR($B168="",$D168=""),1,0))</f>
         <v/>
       </c>
+      <c r="I168">
+        <f>IF(OR(AND($D168&lt;&gt;"",OR(LEN($D168)&lt;&gt;17,LEN($D168)-LEN(SUBSTITUTE($D168,":",""))&lt;&gt;5)),AND($E168&lt;&gt;"",OR(LEN($E168)&lt;&gt;17,LEN($E168)-LEN(SUBSTITUTE($E168,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="169">
       <c r="H169">
         <f>IF(COUNTA($A169:$F169)=0,0,IF(OR($B169="",$D169=""),1,0))</f>
         <v/>
       </c>
+      <c r="I169">
+        <f>IF(OR(AND($D169&lt;&gt;"",OR(LEN($D169)&lt;&gt;17,LEN($D169)-LEN(SUBSTITUTE($D169,":",""))&lt;&gt;5)),AND($E169&lt;&gt;"",OR(LEN($E169)&lt;&gt;17,LEN($E169)-LEN(SUBSTITUTE($E169,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="170">
       <c r="H170">
         <f>IF(COUNTA($A170:$F170)=0,0,IF(OR($B170="",$D170=""),1,0))</f>
         <v/>
       </c>
+      <c r="I170">
+        <f>IF(OR(AND($D170&lt;&gt;"",OR(LEN($D170)&lt;&gt;17,LEN($D170)-LEN(SUBSTITUTE($D170,":",""))&lt;&gt;5)),AND($E170&lt;&gt;"",OR(LEN($E170)&lt;&gt;17,LEN($E170)-LEN(SUBSTITUTE($E170,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="171">
       <c r="H171">
         <f>IF(COUNTA($A171:$F171)=0,0,IF(OR($B171="",$D171=""),1,0))</f>
         <v/>
       </c>
+      <c r="I171">
+        <f>IF(OR(AND($D171&lt;&gt;"",OR(LEN($D171)&lt;&gt;17,LEN($D171)-LEN(SUBSTITUTE($D171,":",""))&lt;&gt;5)),AND($E171&lt;&gt;"",OR(LEN($E171)&lt;&gt;17,LEN($E171)-LEN(SUBSTITUTE($E171,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="172">
       <c r="H172">
         <f>IF(COUNTA($A172:$F172)=0,0,IF(OR($B172="",$D172=""),1,0))</f>
         <v/>
       </c>
+      <c r="I172">
+        <f>IF(OR(AND($D172&lt;&gt;"",OR(LEN($D172)&lt;&gt;17,LEN($D172)-LEN(SUBSTITUTE($D172,":",""))&lt;&gt;5)),AND($E172&lt;&gt;"",OR(LEN($E172)&lt;&gt;17,LEN($E172)-LEN(SUBSTITUTE($E172,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="173">
       <c r="H173">
         <f>IF(COUNTA($A173:$F173)=0,0,IF(OR($B173="",$D173=""),1,0))</f>
         <v/>
       </c>
+      <c r="I173">
+        <f>IF(OR(AND($D173&lt;&gt;"",OR(LEN($D173)&lt;&gt;17,LEN($D173)-LEN(SUBSTITUTE($D173,":",""))&lt;&gt;5)),AND($E173&lt;&gt;"",OR(LEN($E173)&lt;&gt;17,LEN($E173)-LEN(SUBSTITUTE($E173,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="174">
       <c r="H174">
         <f>IF(COUNTA($A174:$F174)=0,0,IF(OR($B174="",$D174=""),1,0))</f>
         <v/>
       </c>
+      <c r="I174">
+        <f>IF(OR(AND($D174&lt;&gt;"",OR(LEN($D174)&lt;&gt;17,LEN($D174)-LEN(SUBSTITUTE($D174,":",""))&lt;&gt;5)),AND($E174&lt;&gt;"",OR(LEN($E174)&lt;&gt;17,LEN($E174)-LEN(SUBSTITUTE($E174,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="175">
       <c r="H175">
         <f>IF(COUNTA($A175:$F175)=0,0,IF(OR($B175="",$D175=""),1,0))</f>
         <v/>
       </c>
+      <c r="I175">
+        <f>IF(OR(AND($D175&lt;&gt;"",OR(LEN($D175)&lt;&gt;17,LEN($D175)-LEN(SUBSTITUTE($D175,":",""))&lt;&gt;5)),AND($E175&lt;&gt;"",OR(LEN($E175)&lt;&gt;17,LEN($E175)-LEN(SUBSTITUTE($E175,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="176">
       <c r="H176">
         <f>IF(COUNTA($A176:$F176)=0,0,IF(OR($B176="",$D176=""),1,0))</f>
         <v/>
       </c>
+      <c r="I176">
+        <f>IF(OR(AND($D176&lt;&gt;"",OR(LEN($D176)&lt;&gt;17,LEN($D176)-LEN(SUBSTITUTE($D176,":",""))&lt;&gt;5)),AND($E176&lt;&gt;"",OR(LEN($E176)&lt;&gt;17,LEN($E176)-LEN(SUBSTITUTE($E176,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="177">
       <c r="H177">
         <f>IF(COUNTA($A177:$F177)=0,0,IF(OR($B177="",$D177=""),1,0))</f>
         <v/>
       </c>
+      <c r="I177">
+        <f>IF(OR(AND($D177&lt;&gt;"",OR(LEN($D177)&lt;&gt;17,LEN($D177)-LEN(SUBSTITUTE($D177,":",""))&lt;&gt;5)),AND($E177&lt;&gt;"",OR(LEN($E177)&lt;&gt;17,LEN($E177)-LEN(SUBSTITUTE($E177,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="178">
       <c r="H178">
         <f>IF(COUNTA($A178:$F178)=0,0,IF(OR($B178="",$D178=""),1,0))</f>
         <v/>
       </c>
+      <c r="I178">
+        <f>IF(OR(AND($D178&lt;&gt;"",OR(LEN($D178)&lt;&gt;17,LEN($D178)-LEN(SUBSTITUTE($D178,":",""))&lt;&gt;5)),AND($E178&lt;&gt;"",OR(LEN($E178)&lt;&gt;17,LEN($E178)-LEN(SUBSTITUTE($E178,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="179">
       <c r="H179">
         <f>IF(COUNTA($A179:$F179)=0,0,IF(OR($B179="",$D179=""),1,0))</f>
         <v/>
       </c>
+      <c r="I179">
+        <f>IF(OR(AND($D179&lt;&gt;"",OR(LEN($D179)&lt;&gt;17,LEN($D179)-LEN(SUBSTITUTE($D179,":",""))&lt;&gt;5)),AND($E179&lt;&gt;"",OR(LEN($E179)&lt;&gt;17,LEN($E179)-LEN(SUBSTITUTE($E179,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="180">
       <c r="H180">
         <f>IF(COUNTA($A180:$F180)=0,0,IF(OR($B180="",$D180=""),1,0))</f>
         <v/>
       </c>
+      <c r="I180">
+        <f>IF(OR(AND($D180&lt;&gt;"",OR(LEN($D180)&lt;&gt;17,LEN($D180)-LEN(SUBSTITUTE($D180,":",""))&lt;&gt;5)),AND($E180&lt;&gt;"",OR(LEN($E180)&lt;&gt;17,LEN($E180)-LEN(SUBSTITUTE($E180,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="181">
       <c r="H181">
         <f>IF(COUNTA($A181:$F181)=0,0,IF(OR($B181="",$D181=""),1,0))</f>
         <v/>
       </c>
+      <c r="I181">
+        <f>IF(OR(AND($D181&lt;&gt;"",OR(LEN($D181)&lt;&gt;17,LEN($D181)-LEN(SUBSTITUTE($D181,":",""))&lt;&gt;5)),AND($E181&lt;&gt;"",OR(LEN($E181)&lt;&gt;17,LEN($E181)-LEN(SUBSTITUTE($E181,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="182">
       <c r="H182">
         <f>IF(COUNTA($A182:$F182)=0,0,IF(OR($B182="",$D182=""),1,0))</f>
         <v/>
       </c>
+      <c r="I182">
+        <f>IF(OR(AND($D182&lt;&gt;"",OR(LEN($D182)&lt;&gt;17,LEN($D182)-LEN(SUBSTITUTE($D182,":",""))&lt;&gt;5)),AND($E182&lt;&gt;"",OR(LEN($E182)&lt;&gt;17,LEN($E182)-LEN(SUBSTITUTE($E182,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="183">
       <c r="H183">
         <f>IF(COUNTA($A183:$F183)=0,0,IF(OR($B183="",$D183=""),1,0))</f>
         <v/>
       </c>
+      <c r="I183">
+        <f>IF(OR(AND($D183&lt;&gt;"",OR(LEN($D183)&lt;&gt;17,LEN($D183)-LEN(SUBSTITUTE($D183,":",""))&lt;&gt;5)),AND($E183&lt;&gt;"",OR(LEN($E183)&lt;&gt;17,LEN($E183)-LEN(SUBSTITUTE($E183,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="184">
       <c r="H184">
         <f>IF(COUNTA($A184:$F184)=0,0,IF(OR($B184="",$D184=""),1,0))</f>
         <v/>
       </c>
+      <c r="I184">
+        <f>IF(OR(AND($D184&lt;&gt;"",OR(LEN($D184)&lt;&gt;17,LEN($D184)-LEN(SUBSTITUTE($D184,":",""))&lt;&gt;5)),AND($E184&lt;&gt;"",OR(LEN($E184)&lt;&gt;17,LEN($E184)-LEN(SUBSTITUTE($E184,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="185">
       <c r="H185">
         <f>IF(COUNTA($A185:$F185)=0,0,IF(OR($B185="",$D185=""),1,0))</f>
         <v/>
       </c>
+      <c r="I185">
+        <f>IF(OR(AND($D185&lt;&gt;"",OR(LEN($D185)&lt;&gt;17,LEN($D185)-LEN(SUBSTITUTE($D185,":",""))&lt;&gt;5)),AND($E185&lt;&gt;"",OR(LEN($E185)&lt;&gt;17,LEN($E185)-LEN(SUBSTITUTE($E185,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="186">
       <c r="H186">
         <f>IF(COUNTA($A186:$F186)=0,0,IF(OR($B186="",$D186=""),1,0))</f>
         <v/>
       </c>
+      <c r="I186">
+        <f>IF(OR(AND($D186&lt;&gt;"",OR(LEN($D186)&lt;&gt;17,LEN($D186)-LEN(SUBSTITUTE($D186,":",""))&lt;&gt;5)),AND($E186&lt;&gt;"",OR(LEN($E186)&lt;&gt;17,LEN($E186)-LEN(SUBSTITUTE($E186,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="187">
       <c r="H187">
         <f>IF(COUNTA($A187:$F187)=0,0,IF(OR($B187="",$D187=""),1,0))</f>
         <v/>
       </c>
+      <c r="I187">
+        <f>IF(OR(AND($D187&lt;&gt;"",OR(LEN($D187)&lt;&gt;17,LEN($D187)-LEN(SUBSTITUTE($D187,":",""))&lt;&gt;5)),AND($E187&lt;&gt;"",OR(LEN($E187)&lt;&gt;17,LEN($E187)-LEN(SUBSTITUTE($E187,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="188">
       <c r="H188">
         <f>IF(COUNTA($A188:$F188)=0,0,IF(OR($B188="",$D188=""),1,0))</f>
         <v/>
       </c>
+      <c r="I188">
+        <f>IF(OR(AND($D188&lt;&gt;"",OR(LEN($D188)&lt;&gt;17,LEN($D188)-LEN(SUBSTITUTE($D188,":",""))&lt;&gt;5)),AND($E188&lt;&gt;"",OR(LEN($E188)&lt;&gt;17,LEN($E188)-LEN(SUBSTITUTE($E188,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="189">
       <c r="H189">
         <f>IF(COUNTA($A189:$F189)=0,0,IF(OR($B189="",$D189=""),1,0))</f>
         <v/>
       </c>
+      <c r="I189">
+        <f>IF(OR(AND($D189&lt;&gt;"",OR(LEN($D189)&lt;&gt;17,LEN($D189)-LEN(SUBSTITUTE($D189,":",""))&lt;&gt;5)),AND($E189&lt;&gt;"",OR(LEN($E189)&lt;&gt;17,LEN($E189)-LEN(SUBSTITUTE($E189,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="190">
       <c r="H190">
         <f>IF(COUNTA($A190:$F190)=0,0,IF(OR($B190="",$D190=""),1,0))</f>
         <v/>
       </c>
+      <c r="I190">
+        <f>IF(OR(AND($D190&lt;&gt;"",OR(LEN($D190)&lt;&gt;17,LEN($D190)-LEN(SUBSTITUTE($D190,":",""))&lt;&gt;5)),AND($E190&lt;&gt;"",OR(LEN($E190)&lt;&gt;17,LEN($E190)-LEN(SUBSTITUTE($E190,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="191">
       <c r="H191">
         <f>IF(COUNTA($A191:$F191)=0,0,IF(OR($B191="",$D191=""),1,0))</f>
         <v/>
       </c>
+      <c r="I191">
+        <f>IF(OR(AND($D191&lt;&gt;"",OR(LEN($D191)&lt;&gt;17,LEN($D191)-LEN(SUBSTITUTE($D191,":",""))&lt;&gt;5)),AND($E191&lt;&gt;"",OR(LEN($E191)&lt;&gt;17,LEN($E191)-LEN(SUBSTITUTE($E191,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="192">
       <c r="H192">
         <f>IF(COUNTA($A192:$F192)=0,0,IF(OR($B192="",$D192=""),1,0))</f>
         <v/>
       </c>
+      <c r="I192">
+        <f>IF(OR(AND($D192&lt;&gt;"",OR(LEN($D192)&lt;&gt;17,LEN($D192)-LEN(SUBSTITUTE($D192,":",""))&lt;&gt;5)),AND($E192&lt;&gt;"",OR(LEN($E192)&lt;&gt;17,LEN($E192)-LEN(SUBSTITUTE($E192,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="193">
       <c r="H193">
         <f>IF(COUNTA($A193:$F193)=0,0,IF(OR($B193="",$D193=""),1,0))</f>
         <v/>
       </c>
+      <c r="I193">
+        <f>IF(OR(AND($D193&lt;&gt;"",OR(LEN($D193)&lt;&gt;17,LEN($D193)-LEN(SUBSTITUTE($D193,":",""))&lt;&gt;5)),AND($E193&lt;&gt;"",OR(LEN($E193)&lt;&gt;17,LEN($E193)-LEN(SUBSTITUTE($E193,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="194">
       <c r="H194">
         <f>IF(COUNTA($A194:$F194)=0,0,IF(OR($B194="",$D194=""),1,0))</f>
         <v/>
       </c>
+      <c r="I194">
+        <f>IF(OR(AND($D194&lt;&gt;"",OR(LEN($D194)&lt;&gt;17,LEN($D194)-LEN(SUBSTITUTE($D194,":",""))&lt;&gt;5)),AND($E194&lt;&gt;"",OR(LEN($E194)&lt;&gt;17,LEN($E194)-LEN(SUBSTITUTE($E194,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="195">
       <c r="H195">
         <f>IF(COUNTA($A195:$F195)=0,0,IF(OR($B195="",$D195=""),1,0))</f>
         <v/>
       </c>
+      <c r="I195">
+        <f>IF(OR(AND($D195&lt;&gt;"",OR(LEN($D195)&lt;&gt;17,LEN($D195)-LEN(SUBSTITUTE($D195,":",""))&lt;&gt;5)),AND($E195&lt;&gt;"",OR(LEN($E195)&lt;&gt;17,LEN($E195)-LEN(SUBSTITUTE($E195,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="196">
       <c r="H196">
         <f>IF(COUNTA($A196:$F196)=0,0,IF(OR($B196="",$D196=""),1,0))</f>
         <v/>
       </c>
+      <c r="I196">
+        <f>IF(OR(AND($D196&lt;&gt;"",OR(LEN($D196)&lt;&gt;17,LEN($D196)-LEN(SUBSTITUTE($D196,":",""))&lt;&gt;5)),AND($E196&lt;&gt;"",OR(LEN($E196)&lt;&gt;17,LEN($E196)-LEN(SUBSTITUTE($E196,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="197">
       <c r="H197">
         <f>IF(COUNTA($A197:$F197)=0,0,IF(OR($B197="",$D197=""),1,0))</f>
         <v/>
       </c>
+      <c r="I197">
+        <f>IF(OR(AND($D197&lt;&gt;"",OR(LEN($D197)&lt;&gt;17,LEN($D197)-LEN(SUBSTITUTE($D197,":",""))&lt;&gt;5)),AND($E197&lt;&gt;"",OR(LEN($E197)&lt;&gt;17,LEN($E197)-LEN(SUBSTITUTE($E197,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="198">
       <c r="H198">
         <f>IF(COUNTA($A198:$F198)=0,0,IF(OR($B198="",$D198=""),1,0))</f>
         <v/>
       </c>
+      <c r="I198">
+        <f>IF(OR(AND($D198&lt;&gt;"",OR(LEN($D198)&lt;&gt;17,LEN($D198)-LEN(SUBSTITUTE($D198,":",""))&lt;&gt;5)),AND($E198&lt;&gt;"",OR(LEN($E198)&lt;&gt;17,LEN($E198)-LEN(SUBSTITUTE($E198,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="199">
       <c r="H199">
         <f>IF(COUNTA($A199:$F199)=0,0,IF(OR($B199="",$D199=""),1,0))</f>
         <v/>
       </c>
+      <c r="I199">
+        <f>IF(OR(AND($D199&lt;&gt;"",OR(LEN($D199)&lt;&gt;17,LEN($D199)-LEN(SUBSTITUTE($D199,":",""))&lt;&gt;5)),AND($E199&lt;&gt;"",OR(LEN($E199)&lt;&gt;17,LEN($E199)-LEN(SUBSTITUTE($E199,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="200">
       <c r="H200">
         <f>IF(COUNTA($A200:$F200)=0,0,IF(OR($B200="",$D200=""),1,0))</f>
         <v/>
       </c>
+      <c r="I200">
+        <f>IF(OR(AND($D200&lt;&gt;"",OR(LEN($D200)&lt;&gt;17,LEN($D200)-LEN(SUBSTITUTE($D200,":",""))&lt;&gt;5)),AND($E200&lt;&gt;"",OR(LEN($E200)&lt;&gt;17,LEN($E200)-LEN(SUBSTITUTE($E200,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="201">
       <c r="H201">
         <f>IF(COUNTA($A201:$F201)=0,0,IF(OR($B201="",$D201=""),1,0))</f>
         <v/>
       </c>
+      <c r="I201">
+        <f>IF(OR(AND($D201&lt;&gt;"",OR(LEN($D201)&lt;&gt;17,LEN($D201)-LEN(SUBSTITUTE($D201,":",""))&lt;&gt;5)),AND($E201&lt;&gt;"",OR(LEN($E201)&lt;&gt;17,LEN($E201)-LEN(SUBSTITUTE($E201,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="202">
       <c r="H202">
         <f>IF(COUNTA($A202:$F202)=0,0,IF(OR($B202="",$D202=""),1,0))</f>
         <v/>
       </c>
+      <c r="I202">
+        <f>IF(OR(AND($D202&lt;&gt;"",OR(LEN($D202)&lt;&gt;17,LEN($D202)-LEN(SUBSTITUTE($D202,":",""))&lt;&gt;5)),AND($E202&lt;&gt;"",OR(LEN($E202)&lt;&gt;17,LEN($E202)-LEN(SUBSTITUTE($E202,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="203">
       <c r="H203">
         <f>IF(COUNTA($A203:$F203)=0,0,IF(OR($B203="",$D203=""),1,0))</f>
         <v/>
       </c>
+      <c r="I203">
+        <f>IF(OR(AND($D203&lt;&gt;"",OR(LEN($D203)&lt;&gt;17,LEN($D203)-LEN(SUBSTITUTE($D203,":",""))&lt;&gt;5)),AND($E203&lt;&gt;"",OR(LEN($E203)&lt;&gt;17,LEN($E203)-LEN(SUBSTITUTE($E203,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="204">
       <c r="H204">
         <f>IF(COUNTA($A204:$F204)=0,0,IF(OR($B204="",$D204=""),1,0))</f>
         <v/>
       </c>
+      <c r="I204">
+        <f>IF(OR(AND($D204&lt;&gt;"",OR(LEN($D204)&lt;&gt;17,LEN($D204)-LEN(SUBSTITUTE($D204,":",""))&lt;&gt;5)),AND($E204&lt;&gt;"",OR(LEN($E204)&lt;&gt;17,LEN($E204)-LEN(SUBSTITUTE($E204,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="205">
       <c r="H205">
         <f>IF(COUNTA($A205:$F205)=0,0,IF(OR($B205="",$D205=""),1,0))</f>
         <v/>
       </c>
+      <c r="I205">
+        <f>IF(OR(AND($D205&lt;&gt;"",OR(LEN($D205)&lt;&gt;17,LEN($D205)-LEN(SUBSTITUTE($D205,":",""))&lt;&gt;5)),AND($E205&lt;&gt;"",OR(LEN($E205)&lt;&gt;17,LEN($E205)-LEN(SUBSTITUTE($E205,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="206">
       <c r="H206">
         <f>IF(COUNTA($A206:$F206)=0,0,IF(OR($B206="",$D206=""),1,0))</f>
         <v/>
       </c>
+      <c r="I206">
+        <f>IF(OR(AND($D206&lt;&gt;"",OR(LEN($D206)&lt;&gt;17,LEN($D206)-LEN(SUBSTITUTE($D206,":",""))&lt;&gt;5)),AND($E206&lt;&gt;"",OR(LEN($E206)&lt;&gt;17,LEN($E206)-LEN(SUBSTITUTE($E206,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="207">
       <c r="H207">
         <f>IF(COUNTA($A207:$F207)=0,0,IF(OR($B207="",$D207=""),1,0))</f>
         <v/>
       </c>
+      <c r="I207">
+        <f>IF(OR(AND($D207&lt;&gt;"",OR(LEN($D207)&lt;&gt;17,LEN($D207)-LEN(SUBSTITUTE($D207,":",""))&lt;&gt;5)),AND($E207&lt;&gt;"",OR(LEN($E207)&lt;&gt;17,LEN($E207)-LEN(SUBSTITUTE($E207,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="208">
       <c r="H208">
         <f>IF(COUNTA($A208:$F208)=0,0,IF(OR($B208="",$D208=""),1,0))</f>
         <v/>
       </c>
+      <c r="I208">
+        <f>IF(OR(AND($D208&lt;&gt;"",OR(LEN($D208)&lt;&gt;17,LEN($D208)-LEN(SUBSTITUTE($D208,":",""))&lt;&gt;5)),AND($E208&lt;&gt;"",OR(LEN($E208)&lt;&gt;17,LEN($E208)-LEN(SUBSTITUTE($E208,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="209">
       <c r="H209">
         <f>IF(COUNTA($A209:$F209)=0,0,IF(OR($B209="",$D209=""),1,0))</f>
         <v/>
       </c>
+      <c r="I209">
+        <f>IF(OR(AND($D209&lt;&gt;"",OR(LEN($D209)&lt;&gt;17,LEN($D209)-LEN(SUBSTITUTE($D209,":",""))&lt;&gt;5)),AND($E209&lt;&gt;"",OR(LEN($E209)&lt;&gt;17,LEN($E209)-LEN(SUBSTITUTE($E209,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="210">
       <c r="H210">
         <f>IF(COUNTA($A210:$F210)=0,0,IF(OR($B210="",$D210=""),1,0))</f>
         <v/>
       </c>
+      <c r="I210">
+        <f>IF(OR(AND($D210&lt;&gt;"",OR(LEN($D210)&lt;&gt;17,LEN($D210)-LEN(SUBSTITUTE($D210,":",""))&lt;&gt;5)),AND($E210&lt;&gt;"",OR(LEN($E210)&lt;&gt;17,LEN($E210)-LEN(SUBSTITUTE($E210,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="211">
       <c r="H211">
         <f>IF(COUNTA($A211:$F211)=0,0,IF(OR($B211="",$D211=""),1,0))</f>
         <v/>
       </c>
+      <c r="I211">
+        <f>IF(OR(AND($D211&lt;&gt;"",OR(LEN($D211)&lt;&gt;17,LEN($D211)-LEN(SUBSTITUTE($D211,":",""))&lt;&gt;5)),AND($E211&lt;&gt;"",OR(LEN($E211)&lt;&gt;17,LEN($E211)-LEN(SUBSTITUTE($E211,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="212">
       <c r="H212">
         <f>IF(COUNTA($A212:$F212)=0,0,IF(OR($B212="",$D212=""),1,0))</f>
         <v/>
       </c>
+      <c r="I212">
+        <f>IF(OR(AND($D212&lt;&gt;"",OR(LEN($D212)&lt;&gt;17,LEN($D212)-LEN(SUBSTITUTE($D212,":",""))&lt;&gt;5)),AND($E212&lt;&gt;"",OR(LEN($E212)&lt;&gt;17,LEN($E212)-LEN(SUBSTITUTE($E212,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="213">
       <c r="H213">
         <f>IF(COUNTA($A213:$F213)=0,0,IF(OR($B213="",$D213=""),1,0))</f>
         <v/>
       </c>
+      <c r="I213">
+        <f>IF(OR(AND($D213&lt;&gt;"",OR(LEN($D213)&lt;&gt;17,LEN($D213)-LEN(SUBSTITUTE($D213,":",""))&lt;&gt;5)),AND($E213&lt;&gt;"",OR(LEN($E213)&lt;&gt;17,LEN($E213)-LEN(SUBSTITUTE($E213,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="214">
       <c r="H214">
         <f>IF(COUNTA($A214:$F214)=0,0,IF(OR($B214="",$D214=""),1,0))</f>
         <v/>
       </c>
+      <c r="I214">
+        <f>IF(OR(AND($D214&lt;&gt;"",OR(LEN($D214)&lt;&gt;17,LEN($D214)-LEN(SUBSTITUTE($D214,":",""))&lt;&gt;5)),AND($E214&lt;&gt;"",OR(LEN($E214)&lt;&gt;17,LEN($E214)-LEN(SUBSTITUTE($E214,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="215">
       <c r="H215">
         <f>IF(COUNTA($A215:$F215)=0,0,IF(OR($B215="",$D215=""),1,0))</f>
         <v/>
       </c>
+      <c r="I215">
+        <f>IF(OR(AND($D215&lt;&gt;"",OR(LEN($D215)&lt;&gt;17,LEN($D215)-LEN(SUBSTITUTE($D215,":",""))&lt;&gt;5)),AND($E215&lt;&gt;"",OR(LEN($E215)&lt;&gt;17,LEN($E215)-LEN(SUBSTITUTE($E215,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="216">
       <c r="H216">
         <f>IF(COUNTA($A216:$F216)=0,0,IF(OR($B216="",$D216=""),1,0))</f>
         <v/>
       </c>
+      <c r="I216">
+        <f>IF(OR(AND($D216&lt;&gt;"",OR(LEN($D216)&lt;&gt;17,LEN($D216)-LEN(SUBSTITUTE($D216,":",""))&lt;&gt;5)),AND($E216&lt;&gt;"",OR(LEN($E216)&lt;&gt;17,LEN($E216)-LEN(SUBSTITUTE($E216,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="217">
       <c r="H217">
         <f>IF(COUNTA($A217:$F217)=0,0,IF(OR($B217="",$D217=""),1,0))</f>
         <v/>
       </c>
+      <c r="I217">
+        <f>IF(OR(AND($D217&lt;&gt;"",OR(LEN($D217)&lt;&gt;17,LEN($D217)-LEN(SUBSTITUTE($D217,":",""))&lt;&gt;5)),AND($E217&lt;&gt;"",OR(LEN($E217)&lt;&gt;17,LEN($E217)-LEN(SUBSTITUTE($E217,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="218">
       <c r="H218">
         <f>IF(COUNTA($A218:$F218)=0,0,IF(OR($B218="",$D218=""),1,0))</f>
         <v/>
       </c>
+      <c r="I218">
+        <f>IF(OR(AND($D218&lt;&gt;"",OR(LEN($D218)&lt;&gt;17,LEN($D218)-LEN(SUBSTITUTE($D218,":",""))&lt;&gt;5)),AND($E218&lt;&gt;"",OR(LEN($E218)&lt;&gt;17,LEN($E218)-LEN(SUBSTITUTE($E218,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="219">
       <c r="H219">
         <f>IF(COUNTA($A219:$F219)=0,0,IF(OR($B219="",$D219=""),1,0))</f>
         <v/>
       </c>
+      <c r="I219">
+        <f>IF(OR(AND($D219&lt;&gt;"",OR(LEN($D219)&lt;&gt;17,LEN($D219)-LEN(SUBSTITUTE($D219,":",""))&lt;&gt;5)),AND($E219&lt;&gt;"",OR(LEN($E219)&lt;&gt;17,LEN($E219)-LEN(SUBSTITUTE($E219,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="220">
       <c r="H220">
         <f>IF(COUNTA($A220:$F220)=0,0,IF(OR($B220="",$D220=""),1,0))</f>
         <v/>
       </c>
+      <c r="I220">
+        <f>IF(OR(AND($D220&lt;&gt;"",OR(LEN($D220)&lt;&gt;17,LEN($D220)-LEN(SUBSTITUTE($D220,":",""))&lt;&gt;5)),AND($E220&lt;&gt;"",OR(LEN($E220)&lt;&gt;17,LEN($E220)-LEN(SUBSTITUTE($E220,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="221">
       <c r="H221">
         <f>IF(COUNTA($A221:$F221)=0,0,IF(OR($B221="",$D221=""),1,0))</f>
         <v/>
       </c>
+      <c r="I221">
+        <f>IF(OR(AND($D221&lt;&gt;"",OR(LEN($D221)&lt;&gt;17,LEN($D221)-LEN(SUBSTITUTE($D221,":",""))&lt;&gt;5)),AND($E221&lt;&gt;"",OR(LEN($E221)&lt;&gt;17,LEN($E221)-LEN(SUBSTITUTE($E221,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="222">
       <c r="H222">
         <f>IF(COUNTA($A222:$F222)=0,0,IF(OR($B222="",$D222=""),1,0))</f>
         <v/>
       </c>
+      <c r="I222">
+        <f>IF(OR(AND($D222&lt;&gt;"",OR(LEN($D222)&lt;&gt;17,LEN($D222)-LEN(SUBSTITUTE($D222,":",""))&lt;&gt;5)),AND($E222&lt;&gt;"",OR(LEN($E222)&lt;&gt;17,LEN($E222)-LEN(SUBSTITUTE($E222,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="223">
       <c r="H223">
         <f>IF(COUNTA($A223:$F223)=0,0,IF(OR($B223="",$D223=""),1,0))</f>
         <v/>
       </c>
+      <c r="I223">
+        <f>IF(OR(AND($D223&lt;&gt;"",OR(LEN($D223)&lt;&gt;17,LEN($D223)-LEN(SUBSTITUTE($D223,":",""))&lt;&gt;5)),AND($E223&lt;&gt;"",OR(LEN($E223)&lt;&gt;17,LEN($E223)-LEN(SUBSTITUTE($E223,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="224">
       <c r="H224">
         <f>IF(COUNTA($A224:$F224)=0,0,IF(OR($B224="",$D224=""),1,0))</f>
         <v/>
       </c>
+      <c r="I224">
+        <f>IF(OR(AND($D224&lt;&gt;"",OR(LEN($D224)&lt;&gt;17,LEN($D224)-LEN(SUBSTITUTE($D224,":",""))&lt;&gt;5)),AND($E224&lt;&gt;"",OR(LEN($E224)&lt;&gt;17,LEN($E224)-LEN(SUBSTITUTE($E224,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="225">
       <c r="H225">
         <f>IF(COUNTA($A225:$F225)=0,0,IF(OR($B225="",$D225=""),1,0))</f>
         <v/>
       </c>
+      <c r="I225">
+        <f>IF(OR(AND($D225&lt;&gt;"",OR(LEN($D225)&lt;&gt;17,LEN($D225)-LEN(SUBSTITUTE($D225,":",""))&lt;&gt;5)),AND($E225&lt;&gt;"",OR(LEN($E225)&lt;&gt;17,LEN($E225)-LEN(SUBSTITUTE($E225,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="226">
       <c r="H226">
         <f>IF(COUNTA($A226:$F226)=0,0,IF(OR($B226="",$D226=""),1,0))</f>
         <v/>
       </c>
+      <c r="I226">
+        <f>IF(OR(AND($D226&lt;&gt;"",OR(LEN($D226)&lt;&gt;17,LEN($D226)-LEN(SUBSTITUTE($D226,":",""))&lt;&gt;5)),AND($E226&lt;&gt;"",OR(LEN($E226)&lt;&gt;17,LEN($E226)-LEN(SUBSTITUTE($E226,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="227">
       <c r="H227">
         <f>IF(COUNTA($A227:$F227)=0,0,IF(OR($B227="",$D227=""),1,0))</f>
         <v/>
       </c>
+      <c r="I227">
+        <f>IF(OR(AND($D227&lt;&gt;"",OR(LEN($D227)&lt;&gt;17,LEN($D227)-LEN(SUBSTITUTE($D227,":",""))&lt;&gt;5)),AND($E227&lt;&gt;"",OR(LEN($E227)&lt;&gt;17,LEN($E227)-LEN(SUBSTITUTE($E227,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="228">
       <c r="H228">
         <f>IF(COUNTA($A228:$F228)=0,0,IF(OR($B228="",$D228=""),1,0))</f>
         <v/>
       </c>
+      <c r="I228">
+        <f>IF(OR(AND($D228&lt;&gt;"",OR(LEN($D228)&lt;&gt;17,LEN($D228)-LEN(SUBSTITUTE($D228,":",""))&lt;&gt;5)),AND($E228&lt;&gt;"",OR(LEN($E228)&lt;&gt;17,LEN($E228)-LEN(SUBSTITUTE($E228,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="229">
       <c r="H229">
         <f>IF(COUNTA($A229:$F229)=0,0,IF(OR($B229="",$D229=""),1,0))</f>
         <v/>
       </c>
+      <c r="I229">
+        <f>IF(OR(AND($D229&lt;&gt;"",OR(LEN($D229)&lt;&gt;17,LEN($D229)-LEN(SUBSTITUTE($D229,":",""))&lt;&gt;5)),AND($E229&lt;&gt;"",OR(LEN($E229)&lt;&gt;17,LEN($E229)-LEN(SUBSTITUTE($E229,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="230">
       <c r="H230">
         <f>IF(COUNTA($A230:$F230)=0,0,IF(OR($B230="",$D230=""),1,0))</f>
         <v/>
       </c>
+      <c r="I230">
+        <f>IF(OR(AND($D230&lt;&gt;"",OR(LEN($D230)&lt;&gt;17,LEN($D230)-LEN(SUBSTITUTE($D230,":",""))&lt;&gt;5)),AND($E230&lt;&gt;"",OR(LEN($E230)&lt;&gt;17,LEN($E230)-LEN(SUBSTITUTE($E230,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="231">
       <c r="H231">
         <f>IF(COUNTA($A231:$F231)=0,0,IF(OR($B231="",$D231=""),1,0))</f>
         <v/>
       </c>
+      <c r="I231">
+        <f>IF(OR(AND($D231&lt;&gt;"",OR(LEN($D231)&lt;&gt;17,LEN($D231)-LEN(SUBSTITUTE($D231,":",""))&lt;&gt;5)),AND($E231&lt;&gt;"",OR(LEN($E231)&lt;&gt;17,LEN($E231)-LEN(SUBSTITUTE($E231,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="232">
       <c r="H232">
         <f>IF(COUNTA($A232:$F232)=0,0,IF(OR($B232="",$D232=""),1,0))</f>
         <v/>
       </c>
+      <c r="I232">
+        <f>IF(OR(AND($D232&lt;&gt;"",OR(LEN($D232)&lt;&gt;17,LEN($D232)-LEN(SUBSTITUTE($D232,":",""))&lt;&gt;5)),AND($E232&lt;&gt;"",OR(LEN($E232)&lt;&gt;17,LEN($E232)-LEN(SUBSTITUTE($E232,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="233">
       <c r="H233">
         <f>IF(COUNTA($A233:$F233)=0,0,IF(OR($B233="",$D233=""),1,0))</f>
         <v/>
       </c>
+      <c r="I233">
+        <f>IF(OR(AND($D233&lt;&gt;"",OR(LEN($D233)&lt;&gt;17,LEN($D233)-LEN(SUBSTITUTE($D233,":",""))&lt;&gt;5)),AND($E233&lt;&gt;"",OR(LEN($E233)&lt;&gt;17,LEN($E233)-LEN(SUBSTITUTE($E233,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="234">
       <c r="H234">
         <f>IF(COUNTA($A234:$F234)=0,0,IF(OR($B234="",$D234=""),1,0))</f>
         <v/>
       </c>
+      <c r="I234">
+        <f>IF(OR(AND($D234&lt;&gt;"",OR(LEN($D234)&lt;&gt;17,LEN($D234)-LEN(SUBSTITUTE($D234,":",""))&lt;&gt;5)),AND($E234&lt;&gt;"",OR(LEN($E234)&lt;&gt;17,LEN($E234)-LEN(SUBSTITUTE($E234,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="235">
       <c r="H235">
         <f>IF(COUNTA($A235:$F235)=0,0,IF(OR($B235="",$D235=""),1,0))</f>
         <v/>
       </c>
+      <c r="I235">
+        <f>IF(OR(AND($D235&lt;&gt;"",OR(LEN($D235)&lt;&gt;17,LEN($D235)-LEN(SUBSTITUTE($D235,":",""))&lt;&gt;5)),AND($E235&lt;&gt;"",OR(LEN($E235)&lt;&gt;17,LEN($E235)-LEN(SUBSTITUTE($E235,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="236">
       <c r="H236">
         <f>IF(COUNTA($A236:$F236)=0,0,IF(OR($B236="",$D236=""),1,0))</f>
         <v/>
       </c>
+      <c r="I236">
+        <f>IF(OR(AND($D236&lt;&gt;"",OR(LEN($D236)&lt;&gt;17,LEN($D236)-LEN(SUBSTITUTE($D236,":",""))&lt;&gt;5)),AND($E236&lt;&gt;"",OR(LEN($E236)&lt;&gt;17,LEN($E236)-LEN(SUBSTITUTE($E236,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="237">
       <c r="H237">
         <f>IF(COUNTA($A237:$F237)=0,0,IF(OR($B237="",$D237=""),1,0))</f>
         <v/>
       </c>
+      <c r="I237">
+        <f>IF(OR(AND($D237&lt;&gt;"",OR(LEN($D237)&lt;&gt;17,LEN($D237)-LEN(SUBSTITUTE($D237,":",""))&lt;&gt;5)),AND($E237&lt;&gt;"",OR(LEN($E237)&lt;&gt;17,LEN($E237)-LEN(SUBSTITUTE($E237,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="238">
       <c r="H238">
         <f>IF(COUNTA($A238:$F238)=0,0,IF(OR($B238="",$D238=""),1,0))</f>
         <v/>
       </c>
+      <c r="I238">
+        <f>IF(OR(AND($D238&lt;&gt;"",OR(LEN($D238)&lt;&gt;17,LEN($D238)-LEN(SUBSTITUTE($D238,":",""))&lt;&gt;5)),AND($E238&lt;&gt;"",OR(LEN($E238)&lt;&gt;17,LEN($E238)-LEN(SUBSTITUTE($E238,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="239">
       <c r="H239">
         <f>IF(COUNTA($A239:$F239)=0,0,IF(OR($B239="",$D239=""),1,0))</f>
         <v/>
       </c>
+      <c r="I239">
+        <f>IF(OR(AND($D239&lt;&gt;"",OR(LEN($D239)&lt;&gt;17,LEN($D239)-LEN(SUBSTITUTE($D239,":",""))&lt;&gt;5)),AND($E239&lt;&gt;"",OR(LEN($E239)&lt;&gt;17,LEN($E239)-LEN(SUBSTITUTE($E239,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="240">
       <c r="H240">
         <f>IF(COUNTA($A240:$F240)=0,0,IF(OR($B240="",$D240=""),1,0))</f>
         <v/>
       </c>
+      <c r="I240">
+        <f>IF(OR(AND($D240&lt;&gt;"",OR(LEN($D240)&lt;&gt;17,LEN($D240)-LEN(SUBSTITUTE($D240,":",""))&lt;&gt;5)),AND($E240&lt;&gt;"",OR(LEN($E240)&lt;&gt;17,LEN($E240)-LEN(SUBSTITUTE($E240,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="241">
       <c r="H241">
         <f>IF(COUNTA($A241:$F241)=0,0,IF(OR($B241="",$D241=""),1,0))</f>
         <v/>
       </c>
+      <c r="I241">
+        <f>IF(OR(AND($D241&lt;&gt;"",OR(LEN($D241)&lt;&gt;17,LEN($D241)-LEN(SUBSTITUTE($D241,":",""))&lt;&gt;5)),AND($E241&lt;&gt;"",OR(LEN($E241)&lt;&gt;17,LEN($E241)-LEN(SUBSTITUTE($E241,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="242">
       <c r="H242">
         <f>IF(COUNTA($A242:$F242)=0,0,IF(OR($B242="",$D242=""),1,0))</f>
         <v/>
       </c>
+      <c r="I242">
+        <f>IF(OR(AND($D242&lt;&gt;"",OR(LEN($D242)&lt;&gt;17,LEN($D242)-LEN(SUBSTITUTE($D242,":",""))&lt;&gt;5)),AND($E242&lt;&gt;"",OR(LEN($E242)&lt;&gt;17,LEN($E242)-LEN(SUBSTITUTE($E242,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="243">
       <c r="H243">
         <f>IF(COUNTA($A243:$F243)=0,0,IF(OR($B243="",$D243=""),1,0))</f>
         <v/>
       </c>
+      <c r="I243">
+        <f>IF(OR(AND($D243&lt;&gt;"",OR(LEN($D243)&lt;&gt;17,LEN($D243)-LEN(SUBSTITUTE($D243,":",""))&lt;&gt;5)),AND($E243&lt;&gt;"",OR(LEN($E243)&lt;&gt;17,LEN($E243)-LEN(SUBSTITUTE($E243,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="244">
       <c r="H244">
         <f>IF(COUNTA($A244:$F244)=0,0,IF(OR($B244="",$D244=""),1,0))</f>
         <v/>
       </c>
+      <c r="I244">
+        <f>IF(OR(AND($D244&lt;&gt;"",OR(LEN($D244)&lt;&gt;17,LEN($D244)-LEN(SUBSTITUTE($D244,":",""))&lt;&gt;5)),AND($E244&lt;&gt;"",OR(LEN($E244)&lt;&gt;17,LEN($E244)-LEN(SUBSTITUTE($E244,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="245">
       <c r="H245">
         <f>IF(COUNTA($A245:$F245)=0,0,IF(OR($B245="",$D245=""),1,0))</f>
         <v/>
       </c>
+      <c r="I245">
+        <f>IF(OR(AND($D245&lt;&gt;"",OR(LEN($D245)&lt;&gt;17,LEN($D245)-LEN(SUBSTITUTE($D245,":",""))&lt;&gt;5)),AND($E245&lt;&gt;"",OR(LEN($E245)&lt;&gt;17,LEN($E245)-LEN(SUBSTITUTE($E245,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="246">
       <c r="H246">
         <f>IF(COUNTA($A246:$F246)=0,0,IF(OR($B246="",$D246=""),1,0))</f>
         <v/>
       </c>
+      <c r="I246">
+        <f>IF(OR(AND($D246&lt;&gt;"",OR(LEN($D246)&lt;&gt;17,LEN($D246)-LEN(SUBSTITUTE($D246,":",""))&lt;&gt;5)),AND($E246&lt;&gt;"",OR(LEN($E246)&lt;&gt;17,LEN($E246)-LEN(SUBSTITUTE($E246,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="247">
       <c r="H247">
         <f>IF(COUNTA($A247:$F247)=0,0,IF(OR($B247="",$D247=""),1,0))</f>
         <v/>
       </c>
+      <c r="I247">
+        <f>IF(OR(AND($D247&lt;&gt;"",OR(LEN($D247)&lt;&gt;17,LEN($D247)-LEN(SUBSTITUTE($D247,":",""))&lt;&gt;5)),AND($E247&lt;&gt;"",OR(LEN($E247)&lt;&gt;17,LEN($E247)-LEN(SUBSTITUTE($E247,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="248">
       <c r="H248">
         <f>IF(COUNTA($A248:$F248)=0,0,IF(OR($B248="",$D248=""),1,0))</f>
         <v/>
       </c>
+      <c r="I248">
+        <f>IF(OR(AND($D248&lt;&gt;"",OR(LEN($D248)&lt;&gt;17,LEN($D248)-LEN(SUBSTITUTE($D248,":",""))&lt;&gt;5)),AND($E248&lt;&gt;"",OR(LEN($E248)&lt;&gt;17,LEN($E248)-LEN(SUBSTITUTE($E248,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="249">
       <c r="H249">
         <f>IF(COUNTA($A249:$F249)=0,0,IF(OR($B249="",$D249=""),1,0))</f>
         <v/>
       </c>
+      <c r="I249">
+        <f>IF(OR(AND($D249&lt;&gt;"",OR(LEN($D249)&lt;&gt;17,LEN($D249)-LEN(SUBSTITUTE($D249,":",""))&lt;&gt;5)),AND($E249&lt;&gt;"",OR(LEN($E249)&lt;&gt;17,LEN($E249)-LEN(SUBSTITUTE($E249,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="250">
       <c r="H250">
         <f>IF(COUNTA($A250:$F250)=0,0,IF(OR($B250="",$D250=""),1,0))</f>
         <v/>
       </c>
+      <c r="I250">
+        <f>IF(OR(AND($D250&lt;&gt;"",OR(LEN($D250)&lt;&gt;17,LEN($D250)-LEN(SUBSTITUTE($D250,":",""))&lt;&gt;5)),AND($E250&lt;&gt;"",OR(LEN($E250)&lt;&gt;17,LEN($E250)-LEN(SUBSTITUTE($E250,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="251">
       <c r="H251">
         <f>IF(COUNTA($A251:$F251)=0,0,IF(OR($B251="",$D251=""),1,0))</f>
         <v/>
       </c>
+      <c r="I251">
+        <f>IF(OR(AND($D251&lt;&gt;"",OR(LEN($D251)&lt;&gt;17,LEN($D251)-LEN(SUBSTITUTE($D251,":",""))&lt;&gt;5)),AND($E251&lt;&gt;"",OR(LEN($E251)&lt;&gt;17,LEN($E251)-LEN(SUBSTITUTE($E251,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="252">
       <c r="H252">
         <f>IF(COUNTA($A252:$F252)=0,0,IF(OR($B252="",$D252=""),1,0))</f>
         <v/>
       </c>
+      <c r="I252">
+        <f>IF(OR(AND($D252&lt;&gt;"",OR(LEN($D252)&lt;&gt;17,LEN($D252)-LEN(SUBSTITUTE($D252,":",""))&lt;&gt;5)),AND($E252&lt;&gt;"",OR(LEN($E252)&lt;&gt;17,LEN($E252)-LEN(SUBSTITUTE($E252,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="253">
       <c r="H253">
         <f>IF(COUNTA($A253:$F253)=0,0,IF(OR($B253="",$D253=""),1,0))</f>
         <v/>
       </c>
+      <c r="I253">
+        <f>IF(OR(AND($D253&lt;&gt;"",OR(LEN($D253)&lt;&gt;17,LEN($D253)-LEN(SUBSTITUTE($D253,":",""))&lt;&gt;5)),AND($E253&lt;&gt;"",OR(LEN($E253)&lt;&gt;17,LEN($E253)-LEN(SUBSTITUTE($E253,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="254">
       <c r="H254">
         <f>IF(COUNTA($A254:$F254)=0,0,IF(OR($B254="",$D254=""),1,0))</f>
         <v/>
       </c>
+      <c r="I254">
+        <f>IF(OR(AND($D254&lt;&gt;"",OR(LEN($D254)&lt;&gt;17,LEN($D254)-LEN(SUBSTITUTE($D254,":",""))&lt;&gt;5)),AND($E254&lt;&gt;"",OR(LEN($E254)&lt;&gt;17,LEN($E254)-LEN(SUBSTITUTE($E254,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="255">
       <c r="H255">
         <f>IF(COUNTA($A255:$F255)=0,0,IF(OR($B255="",$D255=""),1,0))</f>
         <v/>
       </c>
+      <c r="I255">
+        <f>IF(OR(AND($D255&lt;&gt;"",OR(LEN($D255)&lt;&gt;17,LEN($D255)-LEN(SUBSTITUTE($D255,":",""))&lt;&gt;5)),AND($E255&lt;&gt;"",OR(LEN($E255)&lt;&gt;17,LEN($E255)-LEN(SUBSTITUTE($E255,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="256">
       <c r="H256">
         <f>IF(COUNTA($A256:$F256)=0,0,IF(OR($B256="",$D256=""),1,0))</f>
         <v/>
       </c>
+      <c r="I256">
+        <f>IF(OR(AND($D256&lt;&gt;"",OR(LEN($D256)&lt;&gt;17,LEN($D256)-LEN(SUBSTITUTE($D256,":",""))&lt;&gt;5)),AND($E256&lt;&gt;"",OR(LEN($E256)&lt;&gt;17,LEN($E256)-LEN(SUBSTITUTE($E256,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="257">
       <c r="H257">
         <f>IF(COUNTA($A257:$F257)=0,0,IF(OR($B257="",$D257=""),1,0))</f>
         <v/>
       </c>
+      <c r="I257">
+        <f>IF(OR(AND($D257&lt;&gt;"",OR(LEN($D257)&lt;&gt;17,LEN($D257)-LEN(SUBSTITUTE($D257,":",""))&lt;&gt;5)),AND($E257&lt;&gt;"",OR(LEN($E257)&lt;&gt;17,LEN($E257)-LEN(SUBSTITUTE($E257,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="258">
       <c r="H258">
         <f>IF(COUNTA($A258:$F258)=0,0,IF(OR($B258="",$D258=""),1,0))</f>
         <v/>
       </c>
+      <c r="I258">
+        <f>IF(OR(AND($D258&lt;&gt;"",OR(LEN($D258)&lt;&gt;17,LEN($D258)-LEN(SUBSTITUTE($D258,":",""))&lt;&gt;5)),AND($E258&lt;&gt;"",OR(LEN($E258)&lt;&gt;17,LEN($E258)-LEN(SUBSTITUTE($E258,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="259">
       <c r="H259">
         <f>IF(COUNTA($A259:$F259)=0,0,IF(OR($B259="",$D259=""),1,0))</f>
         <v/>
       </c>
+      <c r="I259">
+        <f>IF(OR(AND($D259&lt;&gt;"",OR(LEN($D259)&lt;&gt;17,LEN($D259)-LEN(SUBSTITUTE($D259,":",""))&lt;&gt;5)),AND($E259&lt;&gt;"",OR(LEN($E259)&lt;&gt;17,LEN($E259)-LEN(SUBSTITUTE($E259,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="260">
       <c r="H260">
         <f>IF(COUNTA($A260:$F260)=0,0,IF(OR($B260="",$D260=""),1,0))</f>
         <v/>
       </c>
+      <c r="I260">
+        <f>IF(OR(AND($D260&lt;&gt;"",OR(LEN($D260)&lt;&gt;17,LEN($D260)-LEN(SUBSTITUTE($D260,":",""))&lt;&gt;5)),AND($E260&lt;&gt;"",OR(LEN($E260)&lt;&gt;17,LEN($E260)-LEN(SUBSTITUTE($E260,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="261">
       <c r="H261">
         <f>IF(COUNTA($A261:$F261)=0,0,IF(OR($B261="",$D261=""),1,0))</f>
         <v/>
       </c>
+      <c r="I261">
+        <f>IF(OR(AND($D261&lt;&gt;"",OR(LEN($D261)&lt;&gt;17,LEN($D261)-LEN(SUBSTITUTE($D261,":",""))&lt;&gt;5)),AND($E261&lt;&gt;"",OR(LEN($E261)&lt;&gt;17,LEN($E261)-LEN(SUBSTITUTE($E261,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="262">
       <c r="H262">
         <f>IF(COUNTA($A262:$F262)=0,0,IF(OR($B262="",$D262=""),1,0))</f>
         <v/>
       </c>
+      <c r="I262">
+        <f>IF(OR(AND($D262&lt;&gt;"",OR(LEN($D262)&lt;&gt;17,LEN($D262)-LEN(SUBSTITUTE($D262,":",""))&lt;&gt;5)),AND($E262&lt;&gt;"",OR(LEN($E262)&lt;&gt;17,LEN($E262)-LEN(SUBSTITUTE($E262,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="263">
       <c r="H263">
         <f>IF(COUNTA($A263:$F263)=0,0,IF(OR($B263="",$D263=""),1,0))</f>
         <v/>
       </c>
+      <c r="I263">
+        <f>IF(OR(AND($D263&lt;&gt;"",OR(LEN($D263)&lt;&gt;17,LEN($D263)-LEN(SUBSTITUTE($D263,":",""))&lt;&gt;5)),AND($E263&lt;&gt;"",OR(LEN($E263)&lt;&gt;17,LEN($E263)-LEN(SUBSTITUTE($E263,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="264">
       <c r="H264">
         <f>IF(COUNTA($A264:$F264)=0,0,IF(OR($B264="",$D264=""),1,0))</f>
         <v/>
       </c>
+      <c r="I264">
+        <f>IF(OR(AND($D264&lt;&gt;"",OR(LEN($D264)&lt;&gt;17,LEN($D264)-LEN(SUBSTITUTE($D264,":",""))&lt;&gt;5)),AND($E264&lt;&gt;"",OR(LEN($E264)&lt;&gt;17,LEN($E264)-LEN(SUBSTITUTE($E264,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="265">
       <c r="H265">
         <f>IF(COUNTA($A265:$F265)=0,0,IF(OR($B265="",$D265=""),1,0))</f>
         <v/>
       </c>
+      <c r="I265">
+        <f>IF(OR(AND($D265&lt;&gt;"",OR(LEN($D265)&lt;&gt;17,LEN($D265)-LEN(SUBSTITUTE($D265,":",""))&lt;&gt;5)),AND($E265&lt;&gt;"",OR(LEN($E265)&lt;&gt;17,LEN($E265)-LEN(SUBSTITUTE($E265,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="266">
       <c r="H266">
         <f>IF(COUNTA($A266:$F266)=0,0,IF(OR($B266="",$D266=""),1,0))</f>
         <v/>
       </c>
+      <c r="I266">
+        <f>IF(OR(AND($D266&lt;&gt;"",OR(LEN($D266)&lt;&gt;17,LEN($D266)-LEN(SUBSTITUTE($D266,":",""))&lt;&gt;5)),AND($E266&lt;&gt;"",OR(LEN($E266)&lt;&gt;17,LEN($E266)-LEN(SUBSTITUTE($E266,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="267">
       <c r="H267">
         <f>IF(COUNTA($A267:$F267)=0,0,IF(OR($B267="",$D267=""),1,0))</f>
         <v/>
       </c>
+      <c r="I267">
+        <f>IF(OR(AND($D267&lt;&gt;"",OR(LEN($D267)&lt;&gt;17,LEN($D267)-LEN(SUBSTITUTE($D267,":",""))&lt;&gt;5)),AND($E267&lt;&gt;"",OR(LEN($E267)&lt;&gt;17,LEN($E267)-LEN(SUBSTITUTE($E267,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="268">
       <c r="H268">
         <f>IF(COUNTA($A268:$F268)=0,0,IF(OR($B268="",$D268=""),1,0))</f>
         <v/>
       </c>
+      <c r="I268">
+        <f>IF(OR(AND($D268&lt;&gt;"",OR(LEN($D268)&lt;&gt;17,LEN($D268)-LEN(SUBSTITUTE($D268,":",""))&lt;&gt;5)),AND($E268&lt;&gt;"",OR(LEN($E268)&lt;&gt;17,LEN($E268)-LEN(SUBSTITUTE($E268,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="269">
       <c r="H269">
         <f>IF(COUNTA($A269:$F269)=0,0,IF(OR($B269="",$D269=""),1,0))</f>
         <v/>
       </c>
+      <c r="I269">
+        <f>IF(OR(AND($D269&lt;&gt;"",OR(LEN($D269)&lt;&gt;17,LEN($D269)-LEN(SUBSTITUTE($D269,":",""))&lt;&gt;5)),AND($E269&lt;&gt;"",OR(LEN($E269)&lt;&gt;17,LEN($E269)-LEN(SUBSTITUTE($E269,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="270">
       <c r="H270">
         <f>IF(COUNTA($A270:$F270)=0,0,IF(OR($B270="",$D270=""),1,0))</f>
         <v/>
       </c>
+      <c r="I270">
+        <f>IF(OR(AND($D270&lt;&gt;"",OR(LEN($D270)&lt;&gt;17,LEN($D270)-LEN(SUBSTITUTE($D270,":",""))&lt;&gt;5)),AND($E270&lt;&gt;"",OR(LEN($E270)&lt;&gt;17,LEN($E270)-LEN(SUBSTITUTE($E270,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="271">
       <c r="H271">
         <f>IF(COUNTA($A271:$F271)=0,0,IF(OR($B271="",$D271=""),1,0))</f>
         <v/>
       </c>
+      <c r="I271">
+        <f>IF(OR(AND($D271&lt;&gt;"",OR(LEN($D271)&lt;&gt;17,LEN($D271)-LEN(SUBSTITUTE($D271,":",""))&lt;&gt;5)),AND($E271&lt;&gt;"",OR(LEN($E271)&lt;&gt;17,LEN($E271)-LEN(SUBSTITUTE($E271,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="272">
       <c r="H272">
         <f>IF(COUNTA($A272:$F272)=0,0,IF(OR($B272="",$D272=""),1,0))</f>
         <v/>
       </c>
+      <c r="I272">
+        <f>IF(OR(AND($D272&lt;&gt;"",OR(LEN($D272)&lt;&gt;17,LEN($D272)-LEN(SUBSTITUTE($D272,":",""))&lt;&gt;5)),AND($E272&lt;&gt;"",OR(LEN($E272)&lt;&gt;17,LEN($E272)-LEN(SUBSTITUTE($E272,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="273">
       <c r="H273">
         <f>IF(COUNTA($A273:$F273)=0,0,IF(OR($B273="",$D273=""),1,0))</f>
         <v/>
       </c>
+      <c r="I273">
+        <f>IF(OR(AND($D273&lt;&gt;"",OR(LEN($D273)&lt;&gt;17,LEN($D273)-LEN(SUBSTITUTE($D273,":",""))&lt;&gt;5)),AND($E273&lt;&gt;"",OR(LEN($E273)&lt;&gt;17,LEN($E273)-LEN(SUBSTITUTE($E273,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="274">
       <c r="H274">
         <f>IF(COUNTA($A274:$F274)=0,0,IF(OR($B274="",$D274=""),1,0))</f>
         <v/>
       </c>
+      <c r="I274">
+        <f>IF(OR(AND($D274&lt;&gt;"",OR(LEN($D274)&lt;&gt;17,LEN($D274)-LEN(SUBSTITUTE($D274,":",""))&lt;&gt;5)),AND($E274&lt;&gt;"",OR(LEN($E274)&lt;&gt;17,LEN($E274)-LEN(SUBSTITUTE($E274,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="275">
       <c r="H275">
         <f>IF(COUNTA($A275:$F275)=0,0,IF(OR($B275="",$D275=""),1,0))</f>
         <v/>
       </c>
+      <c r="I275">
+        <f>IF(OR(AND($D275&lt;&gt;"",OR(LEN($D275)&lt;&gt;17,LEN($D275)-LEN(SUBSTITUTE($D275,":",""))&lt;&gt;5)),AND($E275&lt;&gt;"",OR(LEN($E275)&lt;&gt;17,LEN($E275)-LEN(SUBSTITUTE($E275,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="276">
       <c r="H276">
         <f>IF(COUNTA($A276:$F276)=0,0,IF(OR($B276="",$D276=""),1,0))</f>
         <v/>
       </c>
+      <c r="I276">
+        <f>IF(OR(AND($D276&lt;&gt;"",OR(LEN($D276)&lt;&gt;17,LEN($D276)-LEN(SUBSTITUTE($D276,":",""))&lt;&gt;5)),AND($E276&lt;&gt;"",OR(LEN($E276)&lt;&gt;17,LEN($E276)-LEN(SUBSTITUTE($E276,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="277">
       <c r="H277">
         <f>IF(COUNTA($A277:$F277)=0,0,IF(OR($B277="",$D277=""),1,0))</f>
         <v/>
       </c>
+      <c r="I277">
+        <f>IF(OR(AND($D277&lt;&gt;"",OR(LEN($D277)&lt;&gt;17,LEN($D277)-LEN(SUBSTITUTE($D277,":",""))&lt;&gt;5)),AND($E277&lt;&gt;"",OR(LEN($E277)&lt;&gt;17,LEN($E277)-LEN(SUBSTITUTE($E277,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="278">
       <c r="H278">
         <f>IF(COUNTA($A278:$F278)=0,0,IF(OR($B278="",$D278=""),1,0))</f>
         <v/>
       </c>
+      <c r="I278">
+        <f>IF(OR(AND($D278&lt;&gt;"",OR(LEN($D278)&lt;&gt;17,LEN($D278)-LEN(SUBSTITUTE($D278,":",""))&lt;&gt;5)),AND($E278&lt;&gt;"",OR(LEN($E278)&lt;&gt;17,LEN($E278)-LEN(SUBSTITUTE($E278,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="279">
       <c r="H279">
         <f>IF(COUNTA($A279:$F279)=0,0,IF(OR($B279="",$D279=""),1,0))</f>
         <v/>
       </c>
+      <c r="I279">
+        <f>IF(OR(AND($D279&lt;&gt;"",OR(LEN($D279)&lt;&gt;17,LEN($D279)-LEN(SUBSTITUTE($D279,":",""))&lt;&gt;5)),AND($E279&lt;&gt;"",OR(LEN($E279)&lt;&gt;17,LEN($E279)-LEN(SUBSTITUTE($E279,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="280">
       <c r="H280">
         <f>IF(COUNTA($A280:$F280)=0,0,IF(OR($B280="",$D280=""),1,0))</f>
         <v/>
       </c>
+      <c r="I280">
+        <f>IF(OR(AND($D280&lt;&gt;"",OR(LEN($D280)&lt;&gt;17,LEN($D280)-LEN(SUBSTITUTE($D280,":",""))&lt;&gt;5)),AND($E280&lt;&gt;"",OR(LEN($E280)&lt;&gt;17,LEN($E280)-LEN(SUBSTITUTE($E280,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="281">
       <c r="H281">
         <f>IF(COUNTA($A281:$F281)=0,0,IF(OR($B281="",$D281=""),1,0))</f>
         <v/>
       </c>
+      <c r="I281">
+        <f>IF(OR(AND($D281&lt;&gt;"",OR(LEN($D281)&lt;&gt;17,LEN($D281)-LEN(SUBSTITUTE($D281,":",""))&lt;&gt;5)),AND($E281&lt;&gt;"",OR(LEN($E281)&lt;&gt;17,LEN($E281)-LEN(SUBSTITUTE($E281,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="282">
       <c r="H282">
         <f>IF(COUNTA($A282:$F282)=0,0,IF(OR($B282="",$D282=""),1,0))</f>
         <v/>
       </c>
+      <c r="I282">
+        <f>IF(OR(AND($D282&lt;&gt;"",OR(LEN($D282)&lt;&gt;17,LEN($D282)-LEN(SUBSTITUTE($D282,":",""))&lt;&gt;5)),AND($E282&lt;&gt;"",OR(LEN($E282)&lt;&gt;17,LEN($E282)-LEN(SUBSTITUTE($E282,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="283">
       <c r="H283">
         <f>IF(COUNTA($A283:$F283)=0,0,IF(OR($B283="",$D283=""),1,0))</f>
         <v/>
       </c>
+      <c r="I283">
+        <f>IF(OR(AND($D283&lt;&gt;"",OR(LEN($D283)&lt;&gt;17,LEN($D283)-LEN(SUBSTITUTE($D283,":",""))&lt;&gt;5)),AND($E283&lt;&gt;"",OR(LEN($E283)&lt;&gt;17,LEN($E283)-LEN(SUBSTITUTE($E283,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="284">
       <c r="H284">
         <f>IF(COUNTA($A284:$F284)=0,0,IF(OR($B284="",$D284=""),1,0))</f>
         <v/>
       </c>
+      <c r="I284">
+        <f>IF(OR(AND($D284&lt;&gt;"",OR(LEN($D284)&lt;&gt;17,LEN($D284)-LEN(SUBSTITUTE($D284,":",""))&lt;&gt;5)),AND($E284&lt;&gt;"",OR(LEN($E284)&lt;&gt;17,LEN($E284)-LEN(SUBSTITUTE($E284,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="285">
       <c r="H285">
         <f>IF(COUNTA($A285:$F285)=0,0,IF(OR($B285="",$D285=""),1,0))</f>
         <v/>
       </c>
+      <c r="I285">
+        <f>IF(OR(AND($D285&lt;&gt;"",OR(LEN($D285)&lt;&gt;17,LEN($D285)-LEN(SUBSTITUTE($D285,":",""))&lt;&gt;5)),AND($E285&lt;&gt;"",OR(LEN($E285)&lt;&gt;17,LEN($E285)-LEN(SUBSTITUTE($E285,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="286">
       <c r="H286">
         <f>IF(COUNTA($A286:$F286)=0,0,IF(OR($B286="",$D286=""),1,0))</f>
         <v/>
       </c>
+      <c r="I286">
+        <f>IF(OR(AND($D286&lt;&gt;"",OR(LEN($D286)&lt;&gt;17,LEN($D286)-LEN(SUBSTITUTE($D286,":",""))&lt;&gt;5)),AND($E286&lt;&gt;"",OR(LEN($E286)&lt;&gt;17,LEN($E286)-LEN(SUBSTITUTE($E286,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="287">
       <c r="H287">
         <f>IF(COUNTA($A287:$F287)=0,0,IF(OR($B287="",$D287=""),1,0))</f>
         <v/>
       </c>
+      <c r="I287">
+        <f>IF(OR(AND($D287&lt;&gt;"",OR(LEN($D287)&lt;&gt;17,LEN($D287)-LEN(SUBSTITUTE($D287,":",""))&lt;&gt;5)),AND($E287&lt;&gt;"",OR(LEN($E287)&lt;&gt;17,LEN($E287)-LEN(SUBSTITUTE($E287,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="288">
       <c r="H288">
         <f>IF(COUNTA($A288:$F288)=0,0,IF(OR($B288="",$D288=""),1,0))</f>
         <v/>
       </c>
+      <c r="I288">
+        <f>IF(OR(AND($D288&lt;&gt;"",OR(LEN($D288)&lt;&gt;17,LEN($D288)-LEN(SUBSTITUTE($D288,":",""))&lt;&gt;5)),AND($E288&lt;&gt;"",OR(LEN($E288)&lt;&gt;17,LEN($E288)-LEN(SUBSTITUTE($E288,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="289">
       <c r="H289">
         <f>IF(COUNTA($A289:$F289)=0,0,IF(OR($B289="",$D289=""),1,0))</f>
         <v/>
       </c>
+      <c r="I289">
+        <f>IF(OR(AND($D289&lt;&gt;"",OR(LEN($D289)&lt;&gt;17,LEN($D289)-LEN(SUBSTITUTE($D289,":",""))&lt;&gt;5)),AND($E289&lt;&gt;"",OR(LEN($E289)&lt;&gt;17,LEN($E289)-LEN(SUBSTITUTE($E289,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="290">
       <c r="H290">
         <f>IF(COUNTA($A290:$F290)=0,0,IF(OR($B290="",$D290=""),1,0))</f>
         <v/>
       </c>
+      <c r="I290">
+        <f>IF(OR(AND($D290&lt;&gt;"",OR(LEN($D290)&lt;&gt;17,LEN($D290)-LEN(SUBSTITUTE($D290,":",""))&lt;&gt;5)),AND($E290&lt;&gt;"",OR(LEN($E290)&lt;&gt;17,LEN($E290)-LEN(SUBSTITUTE($E290,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="291">
       <c r="H291">
         <f>IF(COUNTA($A291:$F291)=0,0,IF(OR($B291="",$D291=""),1,0))</f>
         <v/>
       </c>
+      <c r="I291">
+        <f>IF(OR(AND($D291&lt;&gt;"",OR(LEN($D291)&lt;&gt;17,LEN($D291)-LEN(SUBSTITUTE($D291,":",""))&lt;&gt;5)),AND($E291&lt;&gt;"",OR(LEN($E291)&lt;&gt;17,LEN($E291)-LEN(SUBSTITUTE($E291,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="292">
       <c r="H292">
         <f>IF(COUNTA($A292:$F292)=0,0,IF(OR($B292="",$D292=""),1,0))</f>
         <v/>
       </c>
+      <c r="I292">
+        <f>IF(OR(AND($D292&lt;&gt;"",OR(LEN($D292)&lt;&gt;17,LEN($D292)-LEN(SUBSTITUTE($D292,":",""))&lt;&gt;5)),AND($E292&lt;&gt;"",OR(LEN($E292)&lt;&gt;17,LEN($E292)-LEN(SUBSTITUTE($E292,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="293">
       <c r="H293">
         <f>IF(COUNTA($A293:$F293)=0,0,IF(OR($B293="",$D293=""),1,0))</f>
         <v/>
       </c>
+      <c r="I293">
+        <f>IF(OR(AND($D293&lt;&gt;"",OR(LEN($D293)&lt;&gt;17,LEN($D293)-LEN(SUBSTITUTE($D293,":",""))&lt;&gt;5)),AND($E293&lt;&gt;"",OR(LEN($E293)&lt;&gt;17,LEN($E293)-LEN(SUBSTITUTE($E293,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="294">
       <c r="H294">
         <f>IF(COUNTA($A294:$F294)=0,0,IF(OR($B294="",$D294=""),1,0))</f>
         <v/>
       </c>
+      <c r="I294">
+        <f>IF(OR(AND($D294&lt;&gt;"",OR(LEN($D294)&lt;&gt;17,LEN($D294)-LEN(SUBSTITUTE($D294,":",""))&lt;&gt;5)),AND($E294&lt;&gt;"",OR(LEN($E294)&lt;&gt;17,LEN($E294)-LEN(SUBSTITUTE($E294,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="295">
       <c r="H295">
         <f>IF(COUNTA($A295:$F295)=0,0,IF(OR($B295="",$D295=""),1,0))</f>
         <v/>
       </c>
+      <c r="I295">
+        <f>IF(OR(AND($D295&lt;&gt;"",OR(LEN($D295)&lt;&gt;17,LEN($D295)-LEN(SUBSTITUTE($D295,":",""))&lt;&gt;5)),AND($E295&lt;&gt;"",OR(LEN($E295)&lt;&gt;17,LEN($E295)-LEN(SUBSTITUTE($E295,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="296">
       <c r="H296">
         <f>IF(COUNTA($A296:$F296)=0,0,IF(OR($B296="",$D296=""),1,0))</f>
         <v/>
       </c>
+      <c r="I296">
+        <f>IF(OR(AND($D296&lt;&gt;"",OR(LEN($D296)&lt;&gt;17,LEN($D296)-LEN(SUBSTITUTE($D296,":",""))&lt;&gt;5)),AND($E296&lt;&gt;"",OR(LEN($E296)&lt;&gt;17,LEN($E296)-LEN(SUBSTITUTE($E296,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="297">
       <c r="H297">
         <f>IF(COUNTA($A297:$F297)=0,0,IF(OR($B297="",$D297=""),1,0))</f>
         <v/>
       </c>
+      <c r="I297">
+        <f>IF(OR(AND($D297&lt;&gt;"",OR(LEN($D297)&lt;&gt;17,LEN($D297)-LEN(SUBSTITUTE($D297,":",""))&lt;&gt;5)),AND($E297&lt;&gt;"",OR(LEN($E297)&lt;&gt;17,LEN($E297)-LEN(SUBSTITUTE($E297,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="298">
       <c r="H298">
         <f>IF(COUNTA($A298:$F298)=0,0,IF(OR($B298="",$D298=""),1,0))</f>
         <v/>
       </c>
+      <c r="I298">
+        <f>IF(OR(AND($D298&lt;&gt;"",OR(LEN($D298)&lt;&gt;17,LEN($D298)-LEN(SUBSTITUTE($D298,":",""))&lt;&gt;5)),AND($E298&lt;&gt;"",OR(LEN($E298)&lt;&gt;17,LEN($E298)-LEN(SUBSTITUTE($E298,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="299">
       <c r="H299">
         <f>IF(COUNTA($A299:$F299)=0,0,IF(OR($B299="",$D299=""),1,0))</f>
         <v/>
       </c>
+      <c r="I299">
+        <f>IF(OR(AND($D299&lt;&gt;"",OR(LEN($D299)&lt;&gt;17,LEN($D299)-LEN(SUBSTITUTE($D299,":",""))&lt;&gt;5)),AND($E299&lt;&gt;"",OR(LEN($E299)&lt;&gt;17,LEN($E299)-LEN(SUBSTITUTE($E299,":",""))&lt;&gt;5))),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="300">
       <c r="H300">
         <f>IF(COUNTA($A300:$F300)=0,0,IF(OR($B300="",$D300=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="I300">
+        <f>IF(OR(AND($D300&lt;&gt;"",OR(LEN($D300)&lt;&gt;17,LEN($D300)-LEN(SUBSTITUTE($D300,":",""))&lt;&gt;5)),AND($E300&lt;&gt;"",OR(LEN($E300)&lt;&gt;17,LEN($E300)-LEN(SUBSTITUTE($E300,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
     </row>
@@ -6501,7 +8941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H300"/>
+  <dimension ref="A1:I300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6511,6 +8951,7 @@
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col hidden="1" width="13" customWidth="1" min="8" max="8"/>
+    <col hidden="1" width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -6547,6 +8988,11 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>ctrl</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ctrlfmt</t>
         </is>
       </c>
     </row>
@@ -6561,6 +9007,10 @@
         <f>IF(COUNTA($A2:$F2)=0,0,IF(OR($B2="",$C2="",$E2=""),1,0))</f>
         <v/>
       </c>
+      <c r="I2">
+        <f>IF(AND($E2&lt;&gt;"",OR(LEN($E2)&lt;&gt;17,LEN($E2)-LEN(SUBSTITUTE($E2,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n"/>
@@ -6573,6 +9023,10 @@
         <f>IF(COUNTA($A3:$F3)=0,0,IF(OR($B3="",$C3="",$E3=""),1,0))</f>
         <v/>
       </c>
+      <c r="I3">
+        <f>IF(AND($E3&lt;&gt;"",OR(LEN($E3)&lt;&gt;17,LEN($E3)-LEN(SUBSTITUTE($E3,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n"/>
@@ -6585,6 +9039,10 @@
         <f>IF(COUNTA($A4:$F4)=0,0,IF(OR($B4="",$C4="",$E4=""),1,0))</f>
         <v/>
       </c>
+      <c r="I4">
+        <f>IF(AND($E4&lt;&gt;"",OR(LEN($E4)&lt;&gt;17,LEN($E4)-LEN(SUBSTITUTE($E4,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n"/>
@@ -6597,6 +9055,10 @@
         <f>IF(COUNTA($A5:$F5)=0,0,IF(OR($B5="",$C5="",$E5=""),1,0))</f>
         <v/>
       </c>
+      <c r="I5">
+        <f>IF(AND($E5&lt;&gt;"",OR(LEN($E5)&lt;&gt;17,LEN($E5)-LEN(SUBSTITUTE($E5,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n"/>
@@ -6609,6 +9071,10 @@
         <f>IF(COUNTA($A6:$F6)=0,0,IF(OR($B6="",$C6="",$E6=""),1,0))</f>
         <v/>
       </c>
+      <c r="I6">
+        <f>IF(AND($E6&lt;&gt;"",OR(LEN($E6)&lt;&gt;17,LEN($E6)-LEN(SUBSTITUTE($E6,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n"/>
@@ -6621,6 +9087,10 @@
         <f>IF(COUNTA($A7:$F7)=0,0,IF(OR($B7="",$C7="",$E7=""),1,0))</f>
         <v/>
       </c>
+      <c r="I7">
+        <f>IF(AND($E7&lt;&gt;"",OR(LEN($E7)&lt;&gt;17,LEN($E7)-LEN(SUBSTITUTE($E7,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="n"/>
@@ -6633,6 +9103,10 @@
         <f>IF(COUNTA($A8:$F8)=0,0,IF(OR($B8="",$C8="",$E8=""),1,0))</f>
         <v/>
       </c>
+      <c r="I8">
+        <f>IF(AND($E8&lt;&gt;"",OR(LEN($E8)&lt;&gt;17,LEN($E8)-LEN(SUBSTITUTE($E8,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="n"/>
@@ -6645,6 +9119,10 @@
         <f>IF(COUNTA($A9:$F9)=0,0,IF(OR($B9="",$C9="",$E9=""),1,0))</f>
         <v/>
       </c>
+      <c r="I9">
+        <f>IF(AND($E9&lt;&gt;"",OR(LEN($E9)&lt;&gt;17,LEN($E9)-LEN(SUBSTITUTE($E9,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="n"/>
@@ -6657,6 +9135,10 @@
         <f>IF(COUNTA($A10:$F10)=0,0,IF(OR($B10="",$C10="",$E10=""),1,0))</f>
         <v/>
       </c>
+      <c r="I10">
+        <f>IF(AND($E10&lt;&gt;"",OR(LEN($E10)&lt;&gt;17,LEN($E10)-LEN(SUBSTITUTE($E10,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="n"/>
@@ -6669,6 +9151,10 @@
         <f>IF(COUNTA($A11:$F11)=0,0,IF(OR($B11="",$C11="",$E11=""),1,0))</f>
         <v/>
       </c>
+      <c r="I11">
+        <f>IF(AND($E11&lt;&gt;"",OR(LEN($E11)&lt;&gt;17,LEN($E11)-LEN(SUBSTITUTE($E11,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="n"/>
@@ -6681,6 +9167,10 @@
         <f>IF(COUNTA($A12:$F12)=0,0,IF(OR($B12="",$C12="",$E12=""),1,0))</f>
         <v/>
       </c>
+      <c r="I12">
+        <f>IF(AND($E12&lt;&gt;"",OR(LEN($E12)&lt;&gt;17,LEN($E12)-LEN(SUBSTITUTE($E12,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="n"/>
@@ -6693,6 +9183,10 @@
         <f>IF(COUNTA($A13:$F13)=0,0,IF(OR($B13="",$C13="",$E13=""),1,0))</f>
         <v/>
       </c>
+      <c r="I13">
+        <f>IF(AND($E13&lt;&gt;"",OR(LEN($E13)&lt;&gt;17,LEN($E13)-LEN(SUBSTITUTE($E13,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="n"/>
@@ -6705,6 +9199,10 @@
         <f>IF(COUNTA($A14:$F14)=0,0,IF(OR($B14="",$C14="",$E14=""),1,0))</f>
         <v/>
       </c>
+      <c r="I14">
+        <f>IF(AND($E14&lt;&gt;"",OR(LEN($E14)&lt;&gt;17,LEN($E14)-LEN(SUBSTITUTE($E14,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="n"/>
@@ -6717,6 +9215,10 @@
         <f>IF(COUNTA($A15:$F15)=0,0,IF(OR($B15="",$C15="",$E15=""),1,0))</f>
         <v/>
       </c>
+      <c r="I15">
+        <f>IF(AND($E15&lt;&gt;"",OR(LEN($E15)&lt;&gt;17,LEN($E15)-LEN(SUBSTITUTE($E15,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="n"/>
@@ -6729,6 +9231,10 @@
         <f>IF(COUNTA($A16:$F16)=0,0,IF(OR($B16="",$C16="",$E16=""),1,0))</f>
         <v/>
       </c>
+      <c r="I16">
+        <f>IF(AND($E16&lt;&gt;"",OR(LEN($E16)&lt;&gt;17,LEN($E16)-LEN(SUBSTITUTE($E16,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="n"/>
@@ -6741,6 +9247,10 @@
         <f>IF(COUNTA($A17:$F17)=0,0,IF(OR($B17="",$C17="",$E17=""),1,0))</f>
         <v/>
       </c>
+      <c r="I17">
+        <f>IF(AND($E17&lt;&gt;"",OR(LEN($E17)&lt;&gt;17,LEN($E17)-LEN(SUBSTITUTE($E17,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="n"/>
@@ -6753,6 +9263,10 @@
         <f>IF(COUNTA($A18:$F18)=0,0,IF(OR($B18="",$C18="",$E18=""),1,0))</f>
         <v/>
       </c>
+      <c r="I18">
+        <f>IF(AND($E18&lt;&gt;"",OR(LEN($E18)&lt;&gt;17,LEN($E18)-LEN(SUBSTITUTE($E18,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="n"/>
@@ -6765,6 +9279,10 @@
         <f>IF(COUNTA($A19:$F19)=0,0,IF(OR($B19="",$C19="",$E19=""),1,0))</f>
         <v/>
       </c>
+      <c r="I19">
+        <f>IF(AND($E19&lt;&gt;"",OR(LEN($E19)&lt;&gt;17,LEN($E19)-LEN(SUBSTITUTE($E19,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="n"/>
@@ -6777,6 +9295,10 @@
         <f>IF(COUNTA($A20:$F20)=0,0,IF(OR($B20="",$C20="",$E20=""),1,0))</f>
         <v/>
       </c>
+      <c r="I20">
+        <f>IF(AND($E20&lt;&gt;"",OR(LEN($E20)&lt;&gt;17,LEN($E20)-LEN(SUBSTITUTE($E20,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="n"/>
@@ -6789,6 +9311,10 @@
         <f>IF(COUNTA($A21:$F21)=0,0,IF(OR($B21="",$C21="",$E21=""),1,0))</f>
         <v/>
       </c>
+      <c r="I21">
+        <f>IF(AND($E21&lt;&gt;"",OR(LEN($E21)&lt;&gt;17,LEN($E21)-LEN(SUBSTITUTE($E21,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="n"/>
@@ -6801,6 +9327,10 @@
         <f>IF(COUNTA($A22:$F22)=0,0,IF(OR($B22="",$C22="",$E22=""),1,0))</f>
         <v/>
       </c>
+      <c r="I22">
+        <f>IF(AND($E22&lt;&gt;"",OR(LEN($E22)&lt;&gt;17,LEN($E22)-LEN(SUBSTITUTE($E22,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="n"/>
@@ -6813,6 +9343,10 @@
         <f>IF(COUNTA($A23:$F23)=0,0,IF(OR($B23="",$C23="",$E23=""),1,0))</f>
         <v/>
       </c>
+      <c r="I23">
+        <f>IF(AND($E23&lt;&gt;"",OR(LEN($E23)&lt;&gt;17,LEN($E23)-LEN(SUBSTITUTE($E23,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="n"/>
@@ -6825,6 +9359,10 @@
         <f>IF(COUNTA($A24:$F24)=0,0,IF(OR($B24="",$C24="",$E24=""),1,0))</f>
         <v/>
       </c>
+      <c r="I24">
+        <f>IF(AND($E24&lt;&gt;"",OR(LEN($E24)&lt;&gt;17,LEN($E24)-LEN(SUBSTITUTE($E24,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="n"/>
@@ -6837,6 +9375,10 @@
         <f>IF(COUNTA($A25:$F25)=0,0,IF(OR($B25="",$C25="",$E25=""),1,0))</f>
         <v/>
       </c>
+      <c r="I25">
+        <f>IF(AND($E25&lt;&gt;"",OR(LEN($E25)&lt;&gt;17,LEN($E25)-LEN(SUBSTITUTE($E25,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="n"/>
@@ -6849,6 +9391,10 @@
         <f>IF(COUNTA($A26:$F26)=0,0,IF(OR($B26="",$C26="",$E26=""),1,0))</f>
         <v/>
       </c>
+      <c r="I26">
+        <f>IF(AND($E26&lt;&gt;"",OR(LEN($E26)&lt;&gt;17,LEN($E26)-LEN(SUBSTITUTE($E26,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="n"/>
@@ -6861,6 +9407,10 @@
         <f>IF(COUNTA($A27:$F27)=0,0,IF(OR($B27="",$C27="",$E27=""),1,0))</f>
         <v/>
       </c>
+      <c r="I27">
+        <f>IF(AND($E27&lt;&gt;"",OR(LEN($E27)&lt;&gt;17,LEN($E27)-LEN(SUBSTITUTE($E27,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="n"/>
@@ -6873,6 +9423,10 @@
         <f>IF(COUNTA($A28:$F28)=0,0,IF(OR($B28="",$C28="",$E28=""),1,0))</f>
         <v/>
       </c>
+      <c r="I28">
+        <f>IF(AND($E28&lt;&gt;"",OR(LEN($E28)&lt;&gt;17,LEN($E28)-LEN(SUBSTITUTE($E28,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="n"/>
@@ -6885,6 +9439,10 @@
         <f>IF(COUNTA($A29:$F29)=0,0,IF(OR($B29="",$C29="",$E29=""),1,0))</f>
         <v/>
       </c>
+      <c r="I29">
+        <f>IF(AND($E29&lt;&gt;"",OR(LEN($E29)&lt;&gt;17,LEN($E29)-LEN(SUBSTITUTE($E29,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="n"/>
@@ -6897,6 +9455,10 @@
         <f>IF(COUNTA($A30:$F30)=0,0,IF(OR($B30="",$C30="",$E30=""),1,0))</f>
         <v/>
       </c>
+      <c r="I30">
+        <f>IF(AND($E30&lt;&gt;"",OR(LEN($E30)&lt;&gt;17,LEN($E30)-LEN(SUBSTITUTE($E30,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="n"/>
@@ -6909,6 +9471,10 @@
         <f>IF(COUNTA($A31:$F31)=0,0,IF(OR($B31="",$C31="",$E31=""),1,0))</f>
         <v/>
       </c>
+      <c r="I31">
+        <f>IF(AND($E31&lt;&gt;"",OR(LEN($E31)&lt;&gt;17,LEN($E31)-LEN(SUBSTITUTE($E31,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="n"/>
@@ -6921,6 +9487,10 @@
         <f>IF(COUNTA($A32:$F32)=0,0,IF(OR($B32="",$C32="",$E32=""),1,0))</f>
         <v/>
       </c>
+      <c r="I32">
+        <f>IF(AND($E32&lt;&gt;"",OR(LEN($E32)&lt;&gt;17,LEN($E32)-LEN(SUBSTITUTE($E32,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="n"/>
@@ -6933,6 +9503,10 @@
         <f>IF(COUNTA($A33:$F33)=0,0,IF(OR($B33="",$C33="",$E33=""),1,0))</f>
         <v/>
       </c>
+      <c r="I33">
+        <f>IF(AND($E33&lt;&gt;"",OR(LEN($E33)&lt;&gt;17,LEN($E33)-LEN(SUBSTITUTE($E33,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="n"/>
@@ -6945,6 +9519,10 @@
         <f>IF(COUNTA($A34:$F34)=0,0,IF(OR($B34="",$C34="",$E34=""),1,0))</f>
         <v/>
       </c>
+      <c r="I34">
+        <f>IF(AND($E34&lt;&gt;"",OR(LEN($E34)&lt;&gt;17,LEN($E34)-LEN(SUBSTITUTE($E34,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="n"/>
@@ -6957,6 +9535,10 @@
         <f>IF(COUNTA($A35:$F35)=0,0,IF(OR($B35="",$C35="",$E35=""),1,0))</f>
         <v/>
       </c>
+      <c r="I35">
+        <f>IF(AND($E35&lt;&gt;"",OR(LEN($E35)&lt;&gt;17,LEN($E35)-LEN(SUBSTITUTE($E35,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="11" t="n"/>
@@ -6969,6 +9551,10 @@
         <f>IF(COUNTA($A36:$F36)=0,0,IF(OR($B36="",$C36="",$E36=""),1,0))</f>
         <v/>
       </c>
+      <c r="I36">
+        <f>IF(AND($E36&lt;&gt;"",OR(LEN($E36)&lt;&gt;17,LEN($E36)-LEN(SUBSTITUTE($E36,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="n"/>
@@ -6981,6 +9567,10 @@
         <f>IF(COUNTA($A37:$F37)=0,0,IF(OR($B37="",$C37="",$E37=""),1,0))</f>
         <v/>
       </c>
+      <c r="I37">
+        <f>IF(AND($E37&lt;&gt;"",OR(LEN($E37)&lt;&gt;17,LEN($E37)-LEN(SUBSTITUTE($E37,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="n"/>
@@ -6993,6 +9583,10 @@
         <f>IF(COUNTA($A38:$F38)=0,0,IF(OR($B38="",$C38="",$E38=""),1,0))</f>
         <v/>
       </c>
+      <c r="I38">
+        <f>IF(AND($E38&lt;&gt;"",OR(LEN($E38)&lt;&gt;17,LEN($E38)-LEN(SUBSTITUTE($E38,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="11" t="n"/>
@@ -7005,6 +9599,10 @@
         <f>IF(COUNTA($A39:$F39)=0,0,IF(OR($B39="",$C39="",$E39=""),1,0))</f>
         <v/>
       </c>
+      <c r="I39">
+        <f>IF(AND($E39&lt;&gt;"",OR(LEN($E39)&lt;&gt;17,LEN($E39)-LEN(SUBSTITUTE($E39,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="11" t="n"/>
@@ -7017,6 +9615,10 @@
         <f>IF(COUNTA($A40:$F40)=0,0,IF(OR($B40="",$C40="",$E40=""),1,0))</f>
         <v/>
       </c>
+      <c r="I40">
+        <f>IF(AND($E40&lt;&gt;"",OR(LEN($E40)&lt;&gt;17,LEN($E40)-LEN(SUBSTITUTE($E40,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="11" t="n"/>
@@ -7029,1558 +9631,2598 @@
         <f>IF(COUNTA($A41:$F41)=0,0,IF(OR($B41="",$C41="",$E41=""),1,0))</f>
         <v/>
       </c>
+      <c r="I41">
+        <f>IF(AND($E41&lt;&gt;"",OR(LEN($E41)&lt;&gt;17,LEN($E41)-LEN(SUBSTITUTE($E41,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="H42">
         <f>IF(COUNTA($A42:$F42)=0,0,IF(OR($B42="",$C42="",$E42=""),1,0))</f>
         <v/>
       </c>
+      <c r="I42">
+        <f>IF(AND($E42&lt;&gt;"",OR(LEN($E42)&lt;&gt;17,LEN($E42)-LEN(SUBSTITUTE($E42,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="H43">
         <f>IF(COUNTA($A43:$F43)=0,0,IF(OR($B43="",$C43="",$E43=""),1,0))</f>
         <v/>
       </c>
+      <c r="I43">
+        <f>IF(AND($E43&lt;&gt;"",OR(LEN($E43)&lt;&gt;17,LEN($E43)-LEN(SUBSTITUTE($E43,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="H44">
         <f>IF(COUNTA($A44:$F44)=0,0,IF(OR($B44="",$C44="",$E44=""),1,0))</f>
         <v/>
       </c>
+      <c r="I44">
+        <f>IF(AND($E44&lt;&gt;"",OR(LEN($E44)&lt;&gt;17,LEN($E44)-LEN(SUBSTITUTE($E44,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="H45">
         <f>IF(COUNTA($A45:$F45)=0,0,IF(OR($B45="",$C45="",$E45=""),1,0))</f>
         <v/>
       </c>
+      <c r="I45">
+        <f>IF(AND($E45&lt;&gt;"",OR(LEN($E45)&lt;&gt;17,LEN($E45)-LEN(SUBSTITUTE($E45,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="H46">
         <f>IF(COUNTA($A46:$F46)=0,0,IF(OR($B46="",$C46="",$E46=""),1,0))</f>
         <v/>
       </c>
+      <c r="I46">
+        <f>IF(AND($E46&lt;&gt;"",OR(LEN($E46)&lt;&gt;17,LEN($E46)-LEN(SUBSTITUTE($E46,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="H47">
         <f>IF(COUNTA($A47:$F47)=0,0,IF(OR($B47="",$C47="",$E47=""),1,0))</f>
         <v/>
       </c>
+      <c r="I47">
+        <f>IF(AND($E47&lt;&gt;"",OR(LEN($E47)&lt;&gt;17,LEN($E47)-LEN(SUBSTITUTE($E47,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="H48">
         <f>IF(COUNTA($A48:$F48)=0,0,IF(OR($B48="",$C48="",$E48=""),1,0))</f>
         <v/>
       </c>
+      <c r="I48">
+        <f>IF(AND($E48&lt;&gt;"",OR(LEN($E48)&lt;&gt;17,LEN($E48)-LEN(SUBSTITUTE($E48,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="H49">
         <f>IF(COUNTA($A49:$F49)=0,0,IF(OR($B49="",$C49="",$E49=""),1,0))</f>
         <v/>
       </c>
+      <c r="I49">
+        <f>IF(AND($E49&lt;&gt;"",OR(LEN($E49)&lt;&gt;17,LEN($E49)-LEN(SUBSTITUTE($E49,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="H50">
         <f>IF(COUNTA($A50:$F50)=0,0,IF(OR($B50="",$C50="",$E50=""),1,0))</f>
         <v/>
       </c>
+      <c r="I50">
+        <f>IF(AND($E50&lt;&gt;"",OR(LEN($E50)&lt;&gt;17,LEN($E50)-LEN(SUBSTITUTE($E50,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="H51">
         <f>IF(COUNTA($A51:$F51)=0,0,IF(OR($B51="",$C51="",$E51=""),1,0))</f>
         <v/>
       </c>
+      <c r="I51">
+        <f>IF(AND($E51&lt;&gt;"",OR(LEN($E51)&lt;&gt;17,LEN($E51)-LEN(SUBSTITUTE($E51,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="H52">
         <f>IF(COUNTA($A52:$F52)=0,0,IF(OR($B52="",$C52="",$E52=""),1,0))</f>
         <v/>
       </c>
+      <c r="I52">
+        <f>IF(AND($E52&lt;&gt;"",OR(LEN($E52)&lt;&gt;17,LEN($E52)-LEN(SUBSTITUTE($E52,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="H53">
         <f>IF(COUNTA($A53:$F53)=0,0,IF(OR($B53="",$C53="",$E53=""),1,0))</f>
         <v/>
       </c>
+      <c r="I53">
+        <f>IF(AND($E53&lt;&gt;"",OR(LEN($E53)&lt;&gt;17,LEN($E53)-LEN(SUBSTITUTE($E53,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="H54">
         <f>IF(COUNTA($A54:$F54)=0,0,IF(OR($B54="",$C54="",$E54=""),1,0))</f>
         <v/>
       </c>
+      <c r="I54">
+        <f>IF(AND($E54&lt;&gt;"",OR(LEN($E54)&lt;&gt;17,LEN($E54)-LEN(SUBSTITUTE($E54,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="H55">
         <f>IF(COUNTA($A55:$F55)=0,0,IF(OR($B55="",$C55="",$E55=""),1,0))</f>
         <v/>
       </c>
+      <c r="I55">
+        <f>IF(AND($E55&lt;&gt;"",OR(LEN($E55)&lt;&gt;17,LEN($E55)-LEN(SUBSTITUTE($E55,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="H56">
         <f>IF(COUNTA($A56:$F56)=0,0,IF(OR($B56="",$C56="",$E56=""),1,0))</f>
         <v/>
       </c>
+      <c r="I56">
+        <f>IF(AND($E56&lt;&gt;"",OR(LEN($E56)&lt;&gt;17,LEN($E56)-LEN(SUBSTITUTE($E56,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="H57">
         <f>IF(COUNTA($A57:$F57)=0,0,IF(OR($B57="",$C57="",$E57=""),1,0))</f>
         <v/>
       </c>
+      <c r="I57">
+        <f>IF(AND($E57&lt;&gt;"",OR(LEN($E57)&lt;&gt;17,LEN($E57)-LEN(SUBSTITUTE($E57,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="H58">
         <f>IF(COUNTA($A58:$F58)=0,0,IF(OR($B58="",$C58="",$E58=""),1,0))</f>
         <v/>
       </c>
+      <c r="I58">
+        <f>IF(AND($E58&lt;&gt;"",OR(LEN($E58)&lt;&gt;17,LEN($E58)-LEN(SUBSTITUTE($E58,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="H59">
         <f>IF(COUNTA($A59:$F59)=0,0,IF(OR($B59="",$C59="",$E59=""),1,0))</f>
         <v/>
       </c>
+      <c r="I59">
+        <f>IF(AND($E59&lt;&gt;"",OR(LEN($E59)&lt;&gt;17,LEN($E59)-LEN(SUBSTITUTE($E59,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="H60">
         <f>IF(COUNTA($A60:$F60)=0,0,IF(OR($B60="",$C60="",$E60=""),1,0))</f>
         <v/>
       </c>
+      <c r="I60">
+        <f>IF(AND($E60&lt;&gt;"",OR(LEN($E60)&lt;&gt;17,LEN($E60)-LEN(SUBSTITUTE($E60,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="H61">
         <f>IF(COUNTA($A61:$F61)=0,0,IF(OR($B61="",$C61="",$E61=""),1,0))</f>
         <v/>
       </c>
+      <c r="I61">
+        <f>IF(AND($E61&lt;&gt;"",OR(LEN($E61)&lt;&gt;17,LEN($E61)-LEN(SUBSTITUTE($E61,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="H62">
         <f>IF(COUNTA($A62:$F62)=0,0,IF(OR($B62="",$C62="",$E62=""),1,0))</f>
         <v/>
       </c>
+      <c r="I62">
+        <f>IF(AND($E62&lt;&gt;"",OR(LEN($E62)&lt;&gt;17,LEN($E62)-LEN(SUBSTITUTE($E62,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="H63">
         <f>IF(COUNTA($A63:$F63)=0,0,IF(OR($B63="",$C63="",$E63=""),1,0))</f>
         <v/>
       </c>
+      <c r="I63">
+        <f>IF(AND($E63&lt;&gt;"",OR(LEN($E63)&lt;&gt;17,LEN($E63)-LEN(SUBSTITUTE($E63,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="H64">
         <f>IF(COUNTA($A64:$F64)=0,0,IF(OR($B64="",$C64="",$E64=""),1,0))</f>
         <v/>
       </c>
+      <c r="I64">
+        <f>IF(AND($E64&lt;&gt;"",OR(LEN($E64)&lt;&gt;17,LEN($E64)-LEN(SUBSTITUTE($E64,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="H65">
         <f>IF(COUNTA($A65:$F65)=0,0,IF(OR($B65="",$C65="",$E65=""),1,0))</f>
         <v/>
       </c>
+      <c r="I65">
+        <f>IF(AND($E65&lt;&gt;"",OR(LEN($E65)&lt;&gt;17,LEN($E65)-LEN(SUBSTITUTE($E65,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="H66">
         <f>IF(COUNTA($A66:$F66)=0,0,IF(OR($B66="",$C66="",$E66=""),1,0))</f>
         <v/>
       </c>
+      <c r="I66">
+        <f>IF(AND($E66&lt;&gt;"",OR(LEN($E66)&lt;&gt;17,LEN($E66)-LEN(SUBSTITUTE($E66,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="H67">
         <f>IF(COUNTA($A67:$F67)=0,0,IF(OR($B67="",$C67="",$E67=""),1,0))</f>
         <v/>
       </c>
+      <c r="I67">
+        <f>IF(AND($E67&lt;&gt;"",OR(LEN($E67)&lt;&gt;17,LEN($E67)-LEN(SUBSTITUTE($E67,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="H68">
         <f>IF(COUNTA($A68:$F68)=0,0,IF(OR($B68="",$C68="",$E68=""),1,0))</f>
         <v/>
       </c>
+      <c r="I68">
+        <f>IF(AND($E68&lt;&gt;"",OR(LEN($E68)&lt;&gt;17,LEN($E68)-LEN(SUBSTITUTE($E68,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="H69">
         <f>IF(COUNTA($A69:$F69)=0,0,IF(OR($B69="",$C69="",$E69=""),1,0))</f>
         <v/>
       </c>
+      <c r="I69">
+        <f>IF(AND($E69&lt;&gt;"",OR(LEN($E69)&lt;&gt;17,LEN($E69)-LEN(SUBSTITUTE($E69,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="H70">
         <f>IF(COUNTA($A70:$F70)=0,0,IF(OR($B70="",$C70="",$E70=""),1,0))</f>
         <v/>
       </c>
+      <c r="I70">
+        <f>IF(AND($E70&lt;&gt;"",OR(LEN($E70)&lt;&gt;17,LEN($E70)-LEN(SUBSTITUTE($E70,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="H71">
         <f>IF(COUNTA($A71:$F71)=0,0,IF(OR($B71="",$C71="",$E71=""),1,0))</f>
         <v/>
       </c>
+      <c r="I71">
+        <f>IF(AND($E71&lt;&gt;"",OR(LEN($E71)&lt;&gt;17,LEN($E71)-LEN(SUBSTITUTE($E71,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="H72">
         <f>IF(COUNTA($A72:$F72)=0,0,IF(OR($B72="",$C72="",$E72=""),1,0))</f>
         <v/>
       </c>
+      <c r="I72">
+        <f>IF(AND($E72&lt;&gt;"",OR(LEN($E72)&lt;&gt;17,LEN($E72)-LEN(SUBSTITUTE($E72,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="H73">
         <f>IF(COUNTA($A73:$F73)=0,0,IF(OR($B73="",$C73="",$E73=""),1,0))</f>
         <v/>
       </c>
+      <c r="I73">
+        <f>IF(AND($E73&lt;&gt;"",OR(LEN($E73)&lt;&gt;17,LEN($E73)-LEN(SUBSTITUTE($E73,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="H74">
         <f>IF(COUNTA($A74:$F74)=0,0,IF(OR($B74="",$C74="",$E74=""),1,0))</f>
         <v/>
       </c>
+      <c r="I74">
+        <f>IF(AND($E74&lt;&gt;"",OR(LEN($E74)&lt;&gt;17,LEN($E74)-LEN(SUBSTITUTE($E74,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="H75">
         <f>IF(COUNTA($A75:$F75)=0,0,IF(OR($B75="",$C75="",$E75=""),1,0))</f>
         <v/>
       </c>
+      <c r="I75">
+        <f>IF(AND($E75&lt;&gt;"",OR(LEN($E75)&lt;&gt;17,LEN($E75)-LEN(SUBSTITUTE($E75,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="H76">
         <f>IF(COUNTA($A76:$F76)=0,0,IF(OR($B76="",$C76="",$E76=""),1,0))</f>
         <v/>
       </c>
+      <c r="I76">
+        <f>IF(AND($E76&lt;&gt;"",OR(LEN($E76)&lt;&gt;17,LEN($E76)-LEN(SUBSTITUTE($E76,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="H77">
         <f>IF(COUNTA($A77:$F77)=0,0,IF(OR($B77="",$C77="",$E77=""),1,0))</f>
         <v/>
       </c>
+      <c r="I77">
+        <f>IF(AND($E77&lt;&gt;"",OR(LEN($E77)&lt;&gt;17,LEN($E77)-LEN(SUBSTITUTE($E77,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="H78">
         <f>IF(COUNTA($A78:$F78)=0,0,IF(OR($B78="",$C78="",$E78=""),1,0))</f>
         <v/>
       </c>
+      <c r="I78">
+        <f>IF(AND($E78&lt;&gt;"",OR(LEN($E78)&lt;&gt;17,LEN($E78)-LEN(SUBSTITUTE($E78,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="H79">
         <f>IF(COUNTA($A79:$F79)=0,0,IF(OR($B79="",$C79="",$E79=""),1,0))</f>
         <v/>
       </c>
+      <c r="I79">
+        <f>IF(AND($E79&lt;&gt;"",OR(LEN($E79)&lt;&gt;17,LEN($E79)-LEN(SUBSTITUTE($E79,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="H80">
         <f>IF(COUNTA($A80:$F80)=0,0,IF(OR($B80="",$C80="",$E80=""),1,0))</f>
         <v/>
       </c>
+      <c r="I80">
+        <f>IF(AND($E80&lt;&gt;"",OR(LEN($E80)&lt;&gt;17,LEN($E80)-LEN(SUBSTITUTE($E80,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="H81">
         <f>IF(COUNTA($A81:$F81)=0,0,IF(OR($B81="",$C81="",$E81=""),1,0))</f>
         <v/>
       </c>
+      <c r="I81">
+        <f>IF(AND($E81&lt;&gt;"",OR(LEN($E81)&lt;&gt;17,LEN($E81)-LEN(SUBSTITUTE($E81,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="H82">
         <f>IF(COUNTA($A82:$F82)=0,0,IF(OR($B82="",$C82="",$E82=""),1,0))</f>
         <v/>
       </c>
+      <c r="I82">
+        <f>IF(AND($E82&lt;&gt;"",OR(LEN($E82)&lt;&gt;17,LEN($E82)-LEN(SUBSTITUTE($E82,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="H83">
         <f>IF(COUNTA($A83:$F83)=0,0,IF(OR($B83="",$C83="",$E83=""),1,0))</f>
         <v/>
       </c>
+      <c r="I83">
+        <f>IF(AND($E83&lt;&gt;"",OR(LEN($E83)&lt;&gt;17,LEN($E83)-LEN(SUBSTITUTE($E83,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="H84">
         <f>IF(COUNTA($A84:$F84)=0,0,IF(OR($B84="",$C84="",$E84=""),1,0))</f>
         <v/>
       </c>
+      <c r="I84">
+        <f>IF(AND($E84&lt;&gt;"",OR(LEN($E84)&lt;&gt;17,LEN($E84)-LEN(SUBSTITUTE($E84,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="H85">
         <f>IF(COUNTA($A85:$F85)=0,0,IF(OR($B85="",$C85="",$E85=""),1,0))</f>
         <v/>
       </c>
+      <c r="I85">
+        <f>IF(AND($E85&lt;&gt;"",OR(LEN($E85)&lt;&gt;17,LEN($E85)-LEN(SUBSTITUTE($E85,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="H86">
         <f>IF(COUNTA($A86:$F86)=0,0,IF(OR($B86="",$C86="",$E86=""),1,0))</f>
         <v/>
       </c>
+      <c r="I86">
+        <f>IF(AND($E86&lt;&gt;"",OR(LEN($E86)&lt;&gt;17,LEN($E86)-LEN(SUBSTITUTE($E86,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="H87">
         <f>IF(COUNTA($A87:$F87)=0,0,IF(OR($B87="",$C87="",$E87=""),1,0))</f>
         <v/>
       </c>
+      <c r="I87">
+        <f>IF(AND($E87&lt;&gt;"",OR(LEN($E87)&lt;&gt;17,LEN($E87)-LEN(SUBSTITUTE($E87,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="H88">
         <f>IF(COUNTA($A88:$F88)=0,0,IF(OR($B88="",$C88="",$E88=""),1,0))</f>
         <v/>
       </c>
+      <c r="I88">
+        <f>IF(AND($E88&lt;&gt;"",OR(LEN($E88)&lt;&gt;17,LEN($E88)-LEN(SUBSTITUTE($E88,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="H89">
         <f>IF(COUNTA($A89:$F89)=0,0,IF(OR($B89="",$C89="",$E89=""),1,0))</f>
         <v/>
       </c>
+      <c r="I89">
+        <f>IF(AND($E89&lt;&gt;"",OR(LEN($E89)&lt;&gt;17,LEN($E89)-LEN(SUBSTITUTE($E89,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="H90">
         <f>IF(COUNTA($A90:$F90)=0,0,IF(OR($B90="",$C90="",$E90=""),1,0))</f>
         <v/>
       </c>
+      <c r="I90">
+        <f>IF(AND($E90&lt;&gt;"",OR(LEN($E90)&lt;&gt;17,LEN($E90)-LEN(SUBSTITUTE($E90,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="H91">
         <f>IF(COUNTA($A91:$F91)=0,0,IF(OR($B91="",$C91="",$E91=""),1,0))</f>
         <v/>
       </c>
+      <c r="I91">
+        <f>IF(AND($E91&lt;&gt;"",OR(LEN($E91)&lt;&gt;17,LEN($E91)-LEN(SUBSTITUTE($E91,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="H92">
         <f>IF(COUNTA($A92:$F92)=0,0,IF(OR($B92="",$C92="",$E92=""),1,0))</f>
         <v/>
       </c>
+      <c r="I92">
+        <f>IF(AND($E92&lt;&gt;"",OR(LEN($E92)&lt;&gt;17,LEN($E92)-LEN(SUBSTITUTE($E92,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="H93">
         <f>IF(COUNTA($A93:$F93)=0,0,IF(OR($B93="",$C93="",$E93=""),1,0))</f>
         <v/>
       </c>
+      <c r="I93">
+        <f>IF(AND($E93&lt;&gt;"",OR(LEN($E93)&lt;&gt;17,LEN($E93)-LEN(SUBSTITUTE($E93,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="H94">
         <f>IF(COUNTA($A94:$F94)=0,0,IF(OR($B94="",$C94="",$E94=""),1,0))</f>
         <v/>
       </c>
+      <c r="I94">
+        <f>IF(AND($E94&lt;&gt;"",OR(LEN($E94)&lt;&gt;17,LEN($E94)-LEN(SUBSTITUTE($E94,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="H95">
         <f>IF(COUNTA($A95:$F95)=0,0,IF(OR($B95="",$C95="",$E95=""),1,0))</f>
         <v/>
       </c>
+      <c r="I95">
+        <f>IF(AND($E95&lt;&gt;"",OR(LEN($E95)&lt;&gt;17,LEN($E95)-LEN(SUBSTITUTE($E95,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="H96">
         <f>IF(COUNTA($A96:$F96)=0,0,IF(OR($B96="",$C96="",$E96=""),1,0))</f>
         <v/>
       </c>
+      <c r="I96">
+        <f>IF(AND($E96&lt;&gt;"",OR(LEN($E96)&lt;&gt;17,LEN($E96)-LEN(SUBSTITUTE($E96,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="H97">
         <f>IF(COUNTA($A97:$F97)=0,0,IF(OR($B97="",$C97="",$E97=""),1,0))</f>
         <v/>
       </c>
+      <c r="I97">
+        <f>IF(AND($E97&lt;&gt;"",OR(LEN($E97)&lt;&gt;17,LEN($E97)-LEN(SUBSTITUTE($E97,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="H98">
         <f>IF(COUNTA($A98:$F98)=0,0,IF(OR($B98="",$C98="",$E98=""),1,0))</f>
         <v/>
       </c>
+      <c r="I98">
+        <f>IF(AND($E98&lt;&gt;"",OR(LEN($E98)&lt;&gt;17,LEN($E98)-LEN(SUBSTITUTE($E98,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="H99">
         <f>IF(COUNTA($A99:$F99)=0,0,IF(OR($B99="",$C99="",$E99=""),1,0))</f>
         <v/>
       </c>
+      <c r="I99">
+        <f>IF(AND($E99&lt;&gt;"",OR(LEN($E99)&lt;&gt;17,LEN($E99)-LEN(SUBSTITUTE($E99,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="H100">
         <f>IF(COUNTA($A100:$F100)=0,0,IF(OR($B100="",$C100="",$E100=""),1,0))</f>
         <v/>
       </c>
+      <c r="I100">
+        <f>IF(AND($E100&lt;&gt;"",OR(LEN($E100)&lt;&gt;17,LEN($E100)-LEN(SUBSTITUTE($E100,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="H101">
         <f>IF(COUNTA($A101:$F101)=0,0,IF(OR($B101="",$C101="",$E101=""),1,0))</f>
         <v/>
       </c>
+      <c r="I101">
+        <f>IF(AND($E101&lt;&gt;"",OR(LEN($E101)&lt;&gt;17,LEN($E101)-LEN(SUBSTITUTE($E101,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="H102">
         <f>IF(COUNTA($A102:$F102)=0,0,IF(OR($B102="",$C102="",$E102=""),1,0))</f>
         <v/>
       </c>
+      <c r="I102">
+        <f>IF(AND($E102&lt;&gt;"",OR(LEN($E102)&lt;&gt;17,LEN($E102)-LEN(SUBSTITUTE($E102,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="H103">
         <f>IF(COUNTA($A103:$F103)=0,0,IF(OR($B103="",$C103="",$E103=""),1,0))</f>
         <v/>
       </c>
+      <c r="I103">
+        <f>IF(AND($E103&lt;&gt;"",OR(LEN($E103)&lt;&gt;17,LEN($E103)-LEN(SUBSTITUTE($E103,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="H104">
         <f>IF(COUNTA($A104:$F104)=0,0,IF(OR($B104="",$C104="",$E104=""),1,0))</f>
         <v/>
       </c>
+      <c r="I104">
+        <f>IF(AND($E104&lt;&gt;"",OR(LEN($E104)&lt;&gt;17,LEN($E104)-LEN(SUBSTITUTE($E104,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="H105">
         <f>IF(COUNTA($A105:$F105)=0,0,IF(OR($B105="",$C105="",$E105=""),1,0))</f>
         <v/>
       </c>
+      <c r="I105">
+        <f>IF(AND($E105&lt;&gt;"",OR(LEN($E105)&lt;&gt;17,LEN($E105)-LEN(SUBSTITUTE($E105,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="H106">
         <f>IF(COUNTA($A106:$F106)=0,0,IF(OR($B106="",$C106="",$E106=""),1,0))</f>
         <v/>
       </c>
+      <c r="I106">
+        <f>IF(AND($E106&lt;&gt;"",OR(LEN($E106)&lt;&gt;17,LEN($E106)-LEN(SUBSTITUTE($E106,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="H107">
         <f>IF(COUNTA($A107:$F107)=0,0,IF(OR($B107="",$C107="",$E107=""),1,0))</f>
         <v/>
       </c>
+      <c r="I107">
+        <f>IF(AND($E107&lt;&gt;"",OR(LEN($E107)&lt;&gt;17,LEN($E107)-LEN(SUBSTITUTE($E107,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="H108">
         <f>IF(COUNTA($A108:$F108)=0,0,IF(OR($B108="",$C108="",$E108=""),1,0))</f>
         <v/>
       </c>
+      <c r="I108">
+        <f>IF(AND($E108&lt;&gt;"",OR(LEN($E108)&lt;&gt;17,LEN($E108)-LEN(SUBSTITUTE($E108,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="H109">
         <f>IF(COUNTA($A109:$F109)=0,0,IF(OR($B109="",$C109="",$E109=""),1,0))</f>
         <v/>
       </c>
+      <c r="I109">
+        <f>IF(AND($E109&lt;&gt;"",OR(LEN($E109)&lt;&gt;17,LEN($E109)-LEN(SUBSTITUTE($E109,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="H110">
         <f>IF(COUNTA($A110:$F110)=0,0,IF(OR($B110="",$C110="",$E110=""),1,0))</f>
         <v/>
       </c>
+      <c r="I110">
+        <f>IF(AND($E110&lt;&gt;"",OR(LEN($E110)&lt;&gt;17,LEN($E110)-LEN(SUBSTITUTE($E110,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="H111">
         <f>IF(COUNTA($A111:$F111)=0,0,IF(OR($B111="",$C111="",$E111=""),1,0))</f>
         <v/>
       </c>
+      <c r="I111">
+        <f>IF(AND($E111&lt;&gt;"",OR(LEN($E111)&lt;&gt;17,LEN($E111)-LEN(SUBSTITUTE($E111,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="H112">
         <f>IF(COUNTA($A112:$F112)=0,0,IF(OR($B112="",$C112="",$E112=""),1,0))</f>
         <v/>
       </c>
+      <c r="I112">
+        <f>IF(AND($E112&lt;&gt;"",OR(LEN($E112)&lt;&gt;17,LEN($E112)-LEN(SUBSTITUTE($E112,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="H113">
         <f>IF(COUNTA($A113:$F113)=0,0,IF(OR($B113="",$C113="",$E113=""),1,0))</f>
         <v/>
       </c>
+      <c r="I113">
+        <f>IF(AND($E113&lt;&gt;"",OR(LEN($E113)&lt;&gt;17,LEN($E113)-LEN(SUBSTITUTE($E113,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="H114">
         <f>IF(COUNTA($A114:$F114)=0,0,IF(OR($B114="",$C114="",$E114=""),1,0))</f>
         <v/>
       </c>
+      <c r="I114">
+        <f>IF(AND($E114&lt;&gt;"",OR(LEN($E114)&lt;&gt;17,LEN($E114)-LEN(SUBSTITUTE($E114,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="H115">
         <f>IF(COUNTA($A115:$F115)=0,0,IF(OR($B115="",$C115="",$E115=""),1,0))</f>
         <v/>
       </c>
+      <c r="I115">
+        <f>IF(AND($E115&lt;&gt;"",OR(LEN($E115)&lt;&gt;17,LEN($E115)-LEN(SUBSTITUTE($E115,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="H116">
         <f>IF(COUNTA($A116:$F116)=0,0,IF(OR($B116="",$C116="",$E116=""),1,0))</f>
         <v/>
       </c>
+      <c r="I116">
+        <f>IF(AND($E116&lt;&gt;"",OR(LEN($E116)&lt;&gt;17,LEN($E116)-LEN(SUBSTITUTE($E116,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="H117">
         <f>IF(COUNTA($A117:$F117)=0,0,IF(OR($B117="",$C117="",$E117=""),1,0))</f>
         <v/>
       </c>
+      <c r="I117">
+        <f>IF(AND($E117&lt;&gt;"",OR(LEN($E117)&lt;&gt;17,LEN($E117)-LEN(SUBSTITUTE($E117,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="H118">
         <f>IF(COUNTA($A118:$F118)=0,0,IF(OR($B118="",$C118="",$E118=""),1,0))</f>
         <v/>
       </c>
+      <c r="I118">
+        <f>IF(AND($E118&lt;&gt;"",OR(LEN($E118)&lt;&gt;17,LEN($E118)-LEN(SUBSTITUTE($E118,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="H119">
         <f>IF(COUNTA($A119:$F119)=0,0,IF(OR($B119="",$C119="",$E119=""),1,0))</f>
         <v/>
       </c>
+      <c r="I119">
+        <f>IF(AND($E119&lt;&gt;"",OR(LEN($E119)&lt;&gt;17,LEN($E119)-LEN(SUBSTITUTE($E119,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="H120">
         <f>IF(COUNTA($A120:$F120)=0,0,IF(OR($B120="",$C120="",$E120=""),1,0))</f>
         <v/>
       </c>
+      <c r="I120">
+        <f>IF(AND($E120&lt;&gt;"",OR(LEN($E120)&lt;&gt;17,LEN($E120)-LEN(SUBSTITUTE($E120,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="H121">
         <f>IF(COUNTA($A121:$F121)=0,0,IF(OR($B121="",$C121="",$E121=""),1,0))</f>
         <v/>
       </c>
+      <c r="I121">
+        <f>IF(AND($E121&lt;&gt;"",OR(LEN($E121)&lt;&gt;17,LEN($E121)-LEN(SUBSTITUTE($E121,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="H122">
         <f>IF(COUNTA($A122:$F122)=0,0,IF(OR($B122="",$C122="",$E122=""),1,0))</f>
         <v/>
       </c>
+      <c r="I122">
+        <f>IF(AND($E122&lt;&gt;"",OR(LEN($E122)&lt;&gt;17,LEN($E122)-LEN(SUBSTITUTE($E122,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="H123">
         <f>IF(COUNTA($A123:$F123)=0,0,IF(OR($B123="",$C123="",$E123=""),1,0))</f>
         <v/>
       </c>
+      <c r="I123">
+        <f>IF(AND($E123&lt;&gt;"",OR(LEN($E123)&lt;&gt;17,LEN($E123)-LEN(SUBSTITUTE($E123,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="H124">
         <f>IF(COUNTA($A124:$F124)=0,0,IF(OR($B124="",$C124="",$E124=""),1,0))</f>
         <v/>
       </c>
+      <c r="I124">
+        <f>IF(AND($E124&lt;&gt;"",OR(LEN($E124)&lt;&gt;17,LEN($E124)-LEN(SUBSTITUTE($E124,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="H125">
         <f>IF(COUNTA($A125:$F125)=0,0,IF(OR($B125="",$C125="",$E125=""),1,0))</f>
         <v/>
       </c>
+      <c r="I125">
+        <f>IF(AND($E125&lt;&gt;"",OR(LEN($E125)&lt;&gt;17,LEN($E125)-LEN(SUBSTITUTE($E125,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="H126">
         <f>IF(COUNTA($A126:$F126)=0,0,IF(OR($B126="",$C126="",$E126=""),1,0))</f>
         <v/>
       </c>
+      <c r="I126">
+        <f>IF(AND($E126&lt;&gt;"",OR(LEN($E126)&lt;&gt;17,LEN($E126)-LEN(SUBSTITUTE($E126,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="H127">
         <f>IF(COUNTA($A127:$F127)=0,0,IF(OR($B127="",$C127="",$E127=""),1,0))</f>
         <v/>
       </c>
+      <c r="I127">
+        <f>IF(AND($E127&lt;&gt;"",OR(LEN($E127)&lt;&gt;17,LEN($E127)-LEN(SUBSTITUTE($E127,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="H128">
         <f>IF(COUNTA($A128:$F128)=0,0,IF(OR($B128="",$C128="",$E128=""),1,0))</f>
         <v/>
       </c>
+      <c r="I128">
+        <f>IF(AND($E128&lt;&gt;"",OR(LEN($E128)&lt;&gt;17,LEN($E128)-LEN(SUBSTITUTE($E128,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="H129">
         <f>IF(COUNTA($A129:$F129)=0,0,IF(OR($B129="",$C129="",$E129=""),1,0))</f>
         <v/>
       </c>
+      <c r="I129">
+        <f>IF(AND($E129&lt;&gt;"",OR(LEN($E129)&lt;&gt;17,LEN($E129)-LEN(SUBSTITUTE($E129,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="H130">
         <f>IF(COUNTA($A130:$F130)=0,0,IF(OR($B130="",$C130="",$E130=""),1,0))</f>
         <v/>
       </c>
+      <c r="I130">
+        <f>IF(AND($E130&lt;&gt;"",OR(LEN($E130)&lt;&gt;17,LEN($E130)-LEN(SUBSTITUTE($E130,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="H131">
         <f>IF(COUNTA($A131:$F131)=0,0,IF(OR($B131="",$C131="",$E131=""),1,0))</f>
         <v/>
       </c>
+      <c r="I131">
+        <f>IF(AND($E131&lt;&gt;"",OR(LEN($E131)&lt;&gt;17,LEN($E131)-LEN(SUBSTITUTE($E131,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="H132">
         <f>IF(COUNTA($A132:$F132)=0,0,IF(OR($B132="",$C132="",$E132=""),1,0))</f>
         <v/>
       </c>
+      <c r="I132">
+        <f>IF(AND($E132&lt;&gt;"",OR(LEN($E132)&lt;&gt;17,LEN($E132)-LEN(SUBSTITUTE($E132,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="H133">
         <f>IF(COUNTA($A133:$F133)=0,0,IF(OR($B133="",$C133="",$E133=""),1,0))</f>
         <v/>
       </c>
+      <c r="I133">
+        <f>IF(AND($E133&lt;&gt;"",OR(LEN($E133)&lt;&gt;17,LEN($E133)-LEN(SUBSTITUTE($E133,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="H134">
         <f>IF(COUNTA($A134:$F134)=0,0,IF(OR($B134="",$C134="",$E134=""),1,0))</f>
         <v/>
       </c>
+      <c r="I134">
+        <f>IF(AND($E134&lt;&gt;"",OR(LEN($E134)&lt;&gt;17,LEN($E134)-LEN(SUBSTITUTE($E134,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="H135">
         <f>IF(COUNTA($A135:$F135)=0,0,IF(OR($B135="",$C135="",$E135=""),1,0))</f>
         <v/>
       </c>
+      <c r="I135">
+        <f>IF(AND($E135&lt;&gt;"",OR(LEN($E135)&lt;&gt;17,LEN($E135)-LEN(SUBSTITUTE($E135,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="H136">
         <f>IF(COUNTA($A136:$F136)=0,0,IF(OR($B136="",$C136="",$E136=""),1,0))</f>
         <v/>
       </c>
+      <c r="I136">
+        <f>IF(AND($E136&lt;&gt;"",OR(LEN($E136)&lt;&gt;17,LEN($E136)-LEN(SUBSTITUTE($E136,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="H137">
         <f>IF(COUNTA($A137:$F137)=0,0,IF(OR($B137="",$C137="",$E137=""),1,0))</f>
         <v/>
       </c>
+      <c r="I137">
+        <f>IF(AND($E137&lt;&gt;"",OR(LEN($E137)&lt;&gt;17,LEN($E137)-LEN(SUBSTITUTE($E137,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="H138">
         <f>IF(COUNTA($A138:$F138)=0,0,IF(OR($B138="",$C138="",$E138=""),1,0))</f>
         <v/>
       </c>
+      <c r="I138">
+        <f>IF(AND($E138&lt;&gt;"",OR(LEN($E138)&lt;&gt;17,LEN($E138)-LEN(SUBSTITUTE($E138,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="H139">
         <f>IF(COUNTA($A139:$F139)=0,0,IF(OR($B139="",$C139="",$E139=""),1,0))</f>
         <v/>
       </c>
+      <c r="I139">
+        <f>IF(AND($E139&lt;&gt;"",OR(LEN($E139)&lt;&gt;17,LEN($E139)-LEN(SUBSTITUTE($E139,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="140">
       <c r="H140">
         <f>IF(COUNTA($A140:$F140)=0,0,IF(OR($B140="",$C140="",$E140=""),1,0))</f>
         <v/>
       </c>
+      <c r="I140">
+        <f>IF(AND($E140&lt;&gt;"",OR(LEN($E140)&lt;&gt;17,LEN($E140)-LEN(SUBSTITUTE($E140,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="H141">
         <f>IF(COUNTA($A141:$F141)=0,0,IF(OR($B141="",$C141="",$E141=""),1,0))</f>
         <v/>
       </c>
+      <c r="I141">
+        <f>IF(AND($E141&lt;&gt;"",OR(LEN($E141)&lt;&gt;17,LEN($E141)-LEN(SUBSTITUTE($E141,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="H142">
         <f>IF(COUNTA($A142:$F142)=0,0,IF(OR($B142="",$C142="",$E142=""),1,0))</f>
         <v/>
       </c>
+      <c r="I142">
+        <f>IF(AND($E142&lt;&gt;"",OR(LEN($E142)&lt;&gt;17,LEN($E142)-LEN(SUBSTITUTE($E142,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="H143">
         <f>IF(COUNTA($A143:$F143)=0,0,IF(OR($B143="",$C143="",$E143=""),1,0))</f>
         <v/>
       </c>
+      <c r="I143">
+        <f>IF(AND($E143&lt;&gt;"",OR(LEN($E143)&lt;&gt;17,LEN($E143)-LEN(SUBSTITUTE($E143,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="H144">
         <f>IF(COUNTA($A144:$F144)=0,0,IF(OR($B144="",$C144="",$E144=""),1,0))</f>
         <v/>
       </c>
+      <c r="I144">
+        <f>IF(AND($E144&lt;&gt;"",OR(LEN($E144)&lt;&gt;17,LEN($E144)-LEN(SUBSTITUTE($E144,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="H145">
         <f>IF(COUNTA($A145:$F145)=0,0,IF(OR($B145="",$C145="",$E145=""),1,0))</f>
         <v/>
       </c>
+      <c r="I145">
+        <f>IF(AND($E145&lt;&gt;"",OR(LEN($E145)&lt;&gt;17,LEN($E145)-LEN(SUBSTITUTE($E145,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="H146">
         <f>IF(COUNTA($A146:$F146)=0,0,IF(OR($B146="",$C146="",$E146=""),1,0))</f>
         <v/>
       </c>
+      <c r="I146">
+        <f>IF(AND($E146&lt;&gt;"",OR(LEN($E146)&lt;&gt;17,LEN($E146)-LEN(SUBSTITUTE($E146,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="147">
       <c r="H147">
         <f>IF(COUNTA($A147:$F147)=0,0,IF(OR($B147="",$C147="",$E147=""),1,0))</f>
         <v/>
       </c>
+      <c r="I147">
+        <f>IF(AND($E147&lt;&gt;"",OR(LEN($E147)&lt;&gt;17,LEN($E147)-LEN(SUBSTITUTE($E147,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="H148">
         <f>IF(COUNTA($A148:$F148)=0,0,IF(OR($B148="",$C148="",$E148=""),1,0))</f>
         <v/>
       </c>
+      <c r="I148">
+        <f>IF(AND($E148&lt;&gt;"",OR(LEN($E148)&lt;&gt;17,LEN($E148)-LEN(SUBSTITUTE($E148,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="149">
       <c r="H149">
         <f>IF(COUNTA($A149:$F149)=0,0,IF(OR($B149="",$C149="",$E149=""),1,0))</f>
         <v/>
       </c>
+      <c r="I149">
+        <f>IF(AND($E149&lt;&gt;"",OR(LEN($E149)&lt;&gt;17,LEN($E149)-LEN(SUBSTITUTE($E149,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="150">
       <c r="H150">
         <f>IF(COUNTA($A150:$F150)=0,0,IF(OR($B150="",$C150="",$E150=""),1,0))</f>
         <v/>
       </c>
+      <c r="I150">
+        <f>IF(AND($E150&lt;&gt;"",OR(LEN($E150)&lt;&gt;17,LEN($E150)-LEN(SUBSTITUTE($E150,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="151">
       <c r="H151">
         <f>IF(COUNTA($A151:$F151)=0,0,IF(OR($B151="",$C151="",$E151=""),1,0))</f>
         <v/>
       </c>
+      <c r="I151">
+        <f>IF(AND($E151&lt;&gt;"",OR(LEN($E151)&lt;&gt;17,LEN($E151)-LEN(SUBSTITUTE($E151,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="152">
       <c r="H152">
         <f>IF(COUNTA($A152:$F152)=0,0,IF(OR($B152="",$C152="",$E152=""),1,0))</f>
         <v/>
       </c>
+      <c r="I152">
+        <f>IF(AND($E152&lt;&gt;"",OR(LEN($E152)&lt;&gt;17,LEN($E152)-LEN(SUBSTITUTE($E152,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="153">
       <c r="H153">
         <f>IF(COUNTA($A153:$F153)=0,0,IF(OR($B153="",$C153="",$E153=""),1,0))</f>
         <v/>
       </c>
+      <c r="I153">
+        <f>IF(AND($E153&lt;&gt;"",OR(LEN($E153)&lt;&gt;17,LEN($E153)-LEN(SUBSTITUTE($E153,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="154">
       <c r="H154">
         <f>IF(COUNTA($A154:$F154)=0,0,IF(OR($B154="",$C154="",$E154=""),1,0))</f>
         <v/>
       </c>
+      <c r="I154">
+        <f>IF(AND($E154&lt;&gt;"",OR(LEN($E154)&lt;&gt;17,LEN($E154)-LEN(SUBSTITUTE($E154,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="155">
       <c r="H155">
         <f>IF(COUNTA($A155:$F155)=0,0,IF(OR($B155="",$C155="",$E155=""),1,0))</f>
         <v/>
       </c>
+      <c r="I155">
+        <f>IF(AND($E155&lt;&gt;"",OR(LEN($E155)&lt;&gt;17,LEN($E155)-LEN(SUBSTITUTE($E155,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="156">
       <c r="H156">
         <f>IF(COUNTA($A156:$F156)=0,0,IF(OR($B156="",$C156="",$E156=""),1,0))</f>
         <v/>
       </c>
+      <c r="I156">
+        <f>IF(AND($E156&lt;&gt;"",OR(LEN($E156)&lt;&gt;17,LEN($E156)-LEN(SUBSTITUTE($E156,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="157">
       <c r="H157">
         <f>IF(COUNTA($A157:$F157)=0,0,IF(OR($B157="",$C157="",$E157=""),1,0))</f>
         <v/>
       </c>
+      <c r="I157">
+        <f>IF(AND($E157&lt;&gt;"",OR(LEN($E157)&lt;&gt;17,LEN($E157)-LEN(SUBSTITUTE($E157,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="158">
       <c r="H158">
         <f>IF(COUNTA($A158:$F158)=0,0,IF(OR($B158="",$C158="",$E158=""),1,0))</f>
         <v/>
       </c>
+      <c r="I158">
+        <f>IF(AND($E158&lt;&gt;"",OR(LEN($E158)&lt;&gt;17,LEN($E158)-LEN(SUBSTITUTE($E158,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="159">
       <c r="H159">
         <f>IF(COUNTA($A159:$F159)=0,0,IF(OR($B159="",$C159="",$E159=""),1,0))</f>
         <v/>
       </c>
+      <c r="I159">
+        <f>IF(AND($E159&lt;&gt;"",OR(LEN($E159)&lt;&gt;17,LEN($E159)-LEN(SUBSTITUTE($E159,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="160">
       <c r="H160">
         <f>IF(COUNTA($A160:$F160)=0,0,IF(OR($B160="",$C160="",$E160=""),1,0))</f>
         <v/>
       </c>
+      <c r="I160">
+        <f>IF(AND($E160&lt;&gt;"",OR(LEN($E160)&lt;&gt;17,LEN($E160)-LEN(SUBSTITUTE($E160,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="161">
       <c r="H161">
         <f>IF(COUNTA($A161:$F161)=0,0,IF(OR($B161="",$C161="",$E161=""),1,0))</f>
         <v/>
       </c>
+      <c r="I161">
+        <f>IF(AND($E161&lt;&gt;"",OR(LEN($E161)&lt;&gt;17,LEN($E161)-LEN(SUBSTITUTE($E161,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="162">
       <c r="H162">
         <f>IF(COUNTA($A162:$F162)=0,0,IF(OR($B162="",$C162="",$E162=""),1,0))</f>
         <v/>
       </c>
+      <c r="I162">
+        <f>IF(AND($E162&lt;&gt;"",OR(LEN($E162)&lt;&gt;17,LEN($E162)-LEN(SUBSTITUTE($E162,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="163">
       <c r="H163">
         <f>IF(COUNTA($A163:$F163)=0,0,IF(OR($B163="",$C163="",$E163=""),1,0))</f>
         <v/>
       </c>
+      <c r="I163">
+        <f>IF(AND($E163&lt;&gt;"",OR(LEN($E163)&lt;&gt;17,LEN($E163)-LEN(SUBSTITUTE($E163,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="164">
       <c r="H164">
         <f>IF(COUNTA($A164:$F164)=0,0,IF(OR($B164="",$C164="",$E164=""),1,0))</f>
         <v/>
       </c>
+      <c r="I164">
+        <f>IF(AND($E164&lt;&gt;"",OR(LEN($E164)&lt;&gt;17,LEN($E164)-LEN(SUBSTITUTE($E164,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="165">
       <c r="H165">
         <f>IF(COUNTA($A165:$F165)=0,0,IF(OR($B165="",$C165="",$E165=""),1,0))</f>
         <v/>
       </c>
+      <c r="I165">
+        <f>IF(AND($E165&lt;&gt;"",OR(LEN($E165)&lt;&gt;17,LEN($E165)-LEN(SUBSTITUTE($E165,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="166">
       <c r="H166">
         <f>IF(COUNTA($A166:$F166)=0,0,IF(OR($B166="",$C166="",$E166=""),1,0))</f>
         <v/>
       </c>
+      <c r="I166">
+        <f>IF(AND($E166&lt;&gt;"",OR(LEN($E166)&lt;&gt;17,LEN($E166)-LEN(SUBSTITUTE($E166,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="167">
       <c r="H167">
         <f>IF(COUNTA($A167:$F167)=0,0,IF(OR($B167="",$C167="",$E167=""),1,0))</f>
         <v/>
       </c>
+      <c r="I167">
+        <f>IF(AND($E167&lt;&gt;"",OR(LEN($E167)&lt;&gt;17,LEN($E167)-LEN(SUBSTITUTE($E167,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="168">
       <c r="H168">
         <f>IF(COUNTA($A168:$F168)=0,0,IF(OR($B168="",$C168="",$E168=""),1,0))</f>
         <v/>
       </c>
+      <c r="I168">
+        <f>IF(AND($E168&lt;&gt;"",OR(LEN($E168)&lt;&gt;17,LEN($E168)-LEN(SUBSTITUTE($E168,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="169">
       <c r="H169">
         <f>IF(COUNTA($A169:$F169)=0,0,IF(OR($B169="",$C169="",$E169=""),1,0))</f>
         <v/>
       </c>
+      <c r="I169">
+        <f>IF(AND($E169&lt;&gt;"",OR(LEN($E169)&lt;&gt;17,LEN($E169)-LEN(SUBSTITUTE($E169,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="170">
       <c r="H170">
         <f>IF(COUNTA($A170:$F170)=0,0,IF(OR($B170="",$C170="",$E170=""),1,0))</f>
         <v/>
       </c>
+      <c r="I170">
+        <f>IF(AND($E170&lt;&gt;"",OR(LEN($E170)&lt;&gt;17,LEN($E170)-LEN(SUBSTITUTE($E170,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="171">
       <c r="H171">
         <f>IF(COUNTA($A171:$F171)=0,0,IF(OR($B171="",$C171="",$E171=""),1,0))</f>
         <v/>
       </c>
+      <c r="I171">
+        <f>IF(AND($E171&lt;&gt;"",OR(LEN($E171)&lt;&gt;17,LEN($E171)-LEN(SUBSTITUTE($E171,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="172">
       <c r="H172">
         <f>IF(COUNTA($A172:$F172)=0,0,IF(OR($B172="",$C172="",$E172=""),1,0))</f>
         <v/>
       </c>
+      <c r="I172">
+        <f>IF(AND($E172&lt;&gt;"",OR(LEN($E172)&lt;&gt;17,LEN($E172)-LEN(SUBSTITUTE($E172,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="173">
       <c r="H173">
         <f>IF(COUNTA($A173:$F173)=0,0,IF(OR($B173="",$C173="",$E173=""),1,0))</f>
         <v/>
       </c>
+      <c r="I173">
+        <f>IF(AND($E173&lt;&gt;"",OR(LEN($E173)&lt;&gt;17,LEN($E173)-LEN(SUBSTITUTE($E173,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="174">
       <c r="H174">
         <f>IF(COUNTA($A174:$F174)=0,0,IF(OR($B174="",$C174="",$E174=""),1,0))</f>
         <v/>
       </c>
+      <c r="I174">
+        <f>IF(AND($E174&lt;&gt;"",OR(LEN($E174)&lt;&gt;17,LEN($E174)-LEN(SUBSTITUTE($E174,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="175">
       <c r="H175">
         <f>IF(COUNTA($A175:$F175)=0,0,IF(OR($B175="",$C175="",$E175=""),1,0))</f>
         <v/>
       </c>
+      <c r="I175">
+        <f>IF(AND($E175&lt;&gt;"",OR(LEN($E175)&lt;&gt;17,LEN($E175)-LEN(SUBSTITUTE($E175,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="176">
       <c r="H176">
         <f>IF(COUNTA($A176:$F176)=0,0,IF(OR($B176="",$C176="",$E176=""),1,0))</f>
         <v/>
       </c>
+      <c r="I176">
+        <f>IF(AND($E176&lt;&gt;"",OR(LEN($E176)&lt;&gt;17,LEN($E176)-LEN(SUBSTITUTE($E176,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="177">
       <c r="H177">
         <f>IF(COUNTA($A177:$F177)=0,0,IF(OR($B177="",$C177="",$E177=""),1,0))</f>
         <v/>
       </c>
+      <c r="I177">
+        <f>IF(AND($E177&lt;&gt;"",OR(LEN($E177)&lt;&gt;17,LEN($E177)-LEN(SUBSTITUTE($E177,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="178">
       <c r="H178">
         <f>IF(COUNTA($A178:$F178)=0,0,IF(OR($B178="",$C178="",$E178=""),1,0))</f>
         <v/>
       </c>
+      <c r="I178">
+        <f>IF(AND($E178&lt;&gt;"",OR(LEN($E178)&lt;&gt;17,LEN($E178)-LEN(SUBSTITUTE($E178,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="179">
       <c r="H179">
         <f>IF(COUNTA($A179:$F179)=0,0,IF(OR($B179="",$C179="",$E179=""),1,0))</f>
         <v/>
       </c>
+      <c r="I179">
+        <f>IF(AND($E179&lt;&gt;"",OR(LEN($E179)&lt;&gt;17,LEN($E179)-LEN(SUBSTITUTE($E179,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="180">
       <c r="H180">
         <f>IF(COUNTA($A180:$F180)=0,0,IF(OR($B180="",$C180="",$E180=""),1,0))</f>
         <v/>
       </c>
+      <c r="I180">
+        <f>IF(AND($E180&lt;&gt;"",OR(LEN($E180)&lt;&gt;17,LEN($E180)-LEN(SUBSTITUTE($E180,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="181">
       <c r="H181">
         <f>IF(COUNTA($A181:$F181)=0,0,IF(OR($B181="",$C181="",$E181=""),1,0))</f>
         <v/>
       </c>
+      <c r="I181">
+        <f>IF(AND($E181&lt;&gt;"",OR(LEN($E181)&lt;&gt;17,LEN($E181)-LEN(SUBSTITUTE($E181,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="182">
       <c r="H182">
         <f>IF(COUNTA($A182:$F182)=0,0,IF(OR($B182="",$C182="",$E182=""),1,0))</f>
         <v/>
       </c>
+      <c r="I182">
+        <f>IF(AND($E182&lt;&gt;"",OR(LEN($E182)&lt;&gt;17,LEN($E182)-LEN(SUBSTITUTE($E182,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="183">
       <c r="H183">
         <f>IF(COUNTA($A183:$F183)=0,0,IF(OR($B183="",$C183="",$E183=""),1,0))</f>
         <v/>
       </c>
+      <c r="I183">
+        <f>IF(AND($E183&lt;&gt;"",OR(LEN($E183)&lt;&gt;17,LEN($E183)-LEN(SUBSTITUTE($E183,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="184">
       <c r="H184">
         <f>IF(COUNTA($A184:$F184)=0,0,IF(OR($B184="",$C184="",$E184=""),1,0))</f>
         <v/>
       </c>
+      <c r="I184">
+        <f>IF(AND($E184&lt;&gt;"",OR(LEN($E184)&lt;&gt;17,LEN($E184)-LEN(SUBSTITUTE($E184,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="185">
       <c r="H185">
         <f>IF(COUNTA($A185:$F185)=0,0,IF(OR($B185="",$C185="",$E185=""),1,0))</f>
         <v/>
       </c>
+      <c r="I185">
+        <f>IF(AND($E185&lt;&gt;"",OR(LEN($E185)&lt;&gt;17,LEN($E185)-LEN(SUBSTITUTE($E185,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="186">
       <c r="H186">
         <f>IF(COUNTA($A186:$F186)=0,0,IF(OR($B186="",$C186="",$E186=""),1,0))</f>
         <v/>
       </c>
+      <c r="I186">
+        <f>IF(AND($E186&lt;&gt;"",OR(LEN($E186)&lt;&gt;17,LEN($E186)-LEN(SUBSTITUTE($E186,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="187">
       <c r="H187">
         <f>IF(COUNTA($A187:$F187)=0,0,IF(OR($B187="",$C187="",$E187=""),1,0))</f>
         <v/>
       </c>
+      <c r="I187">
+        <f>IF(AND($E187&lt;&gt;"",OR(LEN($E187)&lt;&gt;17,LEN($E187)-LEN(SUBSTITUTE($E187,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="188">
       <c r="H188">
         <f>IF(COUNTA($A188:$F188)=0,0,IF(OR($B188="",$C188="",$E188=""),1,0))</f>
         <v/>
       </c>
+      <c r="I188">
+        <f>IF(AND($E188&lt;&gt;"",OR(LEN($E188)&lt;&gt;17,LEN($E188)-LEN(SUBSTITUTE($E188,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="189">
       <c r="H189">
         <f>IF(COUNTA($A189:$F189)=0,0,IF(OR($B189="",$C189="",$E189=""),1,0))</f>
         <v/>
       </c>
+      <c r="I189">
+        <f>IF(AND($E189&lt;&gt;"",OR(LEN($E189)&lt;&gt;17,LEN($E189)-LEN(SUBSTITUTE($E189,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="190">
       <c r="H190">
         <f>IF(COUNTA($A190:$F190)=0,0,IF(OR($B190="",$C190="",$E190=""),1,0))</f>
         <v/>
       </c>
+      <c r="I190">
+        <f>IF(AND($E190&lt;&gt;"",OR(LEN($E190)&lt;&gt;17,LEN($E190)-LEN(SUBSTITUTE($E190,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="191">
       <c r="H191">
         <f>IF(COUNTA($A191:$F191)=0,0,IF(OR($B191="",$C191="",$E191=""),1,0))</f>
         <v/>
       </c>
+      <c r="I191">
+        <f>IF(AND($E191&lt;&gt;"",OR(LEN($E191)&lt;&gt;17,LEN($E191)-LEN(SUBSTITUTE($E191,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="192">
       <c r="H192">
         <f>IF(COUNTA($A192:$F192)=0,0,IF(OR($B192="",$C192="",$E192=""),1,0))</f>
         <v/>
       </c>
+      <c r="I192">
+        <f>IF(AND($E192&lt;&gt;"",OR(LEN($E192)&lt;&gt;17,LEN($E192)-LEN(SUBSTITUTE($E192,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="193">
       <c r="H193">
         <f>IF(COUNTA($A193:$F193)=0,0,IF(OR($B193="",$C193="",$E193=""),1,0))</f>
         <v/>
       </c>
+      <c r="I193">
+        <f>IF(AND($E193&lt;&gt;"",OR(LEN($E193)&lt;&gt;17,LEN($E193)-LEN(SUBSTITUTE($E193,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="194">
       <c r="H194">
         <f>IF(COUNTA($A194:$F194)=0,0,IF(OR($B194="",$C194="",$E194=""),1,0))</f>
         <v/>
       </c>
+      <c r="I194">
+        <f>IF(AND($E194&lt;&gt;"",OR(LEN($E194)&lt;&gt;17,LEN($E194)-LEN(SUBSTITUTE($E194,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="195">
       <c r="H195">
         <f>IF(COUNTA($A195:$F195)=0,0,IF(OR($B195="",$C195="",$E195=""),1,0))</f>
         <v/>
       </c>
+      <c r="I195">
+        <f>IF(AND($E195&lt;&gt;"",OR(LEN($E195)&lt;&gt;17,LEN($E195)-LEN(SUBSTITUTE($E195,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="196">
       <c r="H196">
         <f>IF(COUNTA($A196:$F196)=0,0,IF(OR($B196="",$C196="",$E196=""),1,0))</f>
         <v/>
       </c>
+      <c r="I196">
+        <f>IF(AND($E196&lt;&gt;"",OR(LEN($E196)&lt;&gt;17,LEN($E196)-LEN(SUBSTITUTE($E196,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="197">
       <c r="H197">
         <f>IF(COUNTA($A197:$F197)=0,0,IF(OR($B197="",$C197="",$E197=""),1,0))</f>
         <v/>
       </c>
+      <c r="I197">
+        <f>IF(AND($E197&lt;&gt;"",OR(LEN($E197)&lt;&gt;17,LEN($E197)-LEN(SUBSTITUTE($E197,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="198">
       <c r="H198">
         <f>IF(COUNTA($A198:$F198)=0,0,IF(OR($B198="",$C198="",$E198=""),1,0))</f>
         <v/>
       </c>
+      <c r="I198">
+        <f>IF(AND($E198&lt;&gt;"",OR(LEN($E198)&lt;&gt;17,LEN($E198)-LEN(SUBSTITUTE($E198,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="199">
       <c r="H199">
         <f>IF(COUNTA($A199:$F199)=0,0,IF(OR($B199="",$C199="",$E199=""),1,0))</f>
         <v/>
       </c>
+      <c r="I199">
+        <f>IF(AND($E199&lt;&gt;"",OR(LEN($E199)&lt;&gt;17,LEN($E199)-LEN(SUBSTITUTE($E199,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="200">
       <c r="H200">
         <f>IF(COUNTA($A200:$F200)=0,0,IF(OR($B200="",$C200="",$E200=""),1,0))</f>
         <v/>
       </c>
+      <c r="I200">
+        <f>IF(AND($E200&lt;&gt;"",OR(LEN($E200)&lt;&gt;17,LEN($E200)-LEN(SUBSTITUTE($E200,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="201">
       <c r="H201">
         <f>IF(COUNTA($A201:$F201)=0,0,IF(OR($B201="",$C201="",$E201=""),1,0))</f>
         <v/>
       </c>
+      <c r="I201">
+        <f>IF(AND($E201&lt;&gt;"",OR(LEN($E201)&lt;&gt;17,LEN($E201)-LEN(SUBSTITUTE($E201,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="202">
       <c r="H202">
         <f>IF(COUNTA($A202:$F202)=0,0,IF(OR($B202="",$C202="",$E202=""),1,0))</f>
         <v/>
       </c>
+      <c r="I202">
+        <f>IF(AND($E202&lt;&gt;"",OR(LEN($E202)&lt;&gt;17,LEN($E202)-LEN(SUBSTITUTE($E202,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="203">
       <c r="H203">
         <f>IF(COUNTA($A203:$F203)=0,0,IF(OR($B203="",$C203="",$E203=""),1,0))</f>
         <v/>
       </c>
+      <c r="I203">
+        <f>IF(AND($E203&lt;&gt;"",OR(LEN($E203)&lt;&gt;17,LEN($E203)-LEN(SUBSTITUTE($E203,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="204">
       <c r="H204">
         <f>IF(COUNTA($A204:$F204)=0,0,IF(OR($B204="",$C204="",$E204=""),1,0))</f>
         <v/>
       </c>
+      <c r="I204">
+        <f>IF(AND($E204&lt;&gt;"",OR(LEN($E204)&lt;&gt;17,LEN($E204)-LEN(SUBSTITUTE($E204,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="205">
       <c r="H205">
         <f>IF(COUNTA($A205:$F205)=0,0,IF(OR($B205="",$C205="",$E205=""),1,0))</f>
         <v/>
       </c>
+      <c r="I205">
+        <f>IF(AND($E205&lt;&gt;"",OR(LEN($E205)&lt;&gt;17,LEN($E205)-LEN(SUBSTITUTE($E205,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="206">
       <c r="H206">
         <f>IF(COUNTA($A206:$F206)=0,0,IF(OR($B206="",$C206="",$E206=""),1,0))</f>
         <v/>
       </c>
+      <c r="I206">
+        <f>IF(AND($E206&lt;&gt;"",OR(LEN($E206)&lt;&gt;17,LEN($E206)-LEN(SUBSTITUTE($E206,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="207">
       <c r="H207">
         <f>IF(COUNTA($A207:$F207)=0,0,IF(OR($B207="",$C207="",$E207=""),1,0))</f>
         <v/>
       </c>
+      <c r="I207">
+        <f>IF(AND($E207&lt;&gt;"",OR(LEN($E207)&lt;&gt;17,LEN($E207)-LEN(SUBSTITUTE($E207,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="208">
       <c r="H208">
         <f>IF(COUNTA($A208:$F208)=0,0,IF(OR($B208="",$C208="",$E208=""),1,0))</f>
         <v/>
       </c>
+      <c r="I208">
+        <f>IF(AND($E208&lt;&gt;"",OR(LEN($E208)&lt;&gt;17,LEN($E208)-LEN(SUBSTITUTE($E208,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="209">
       <c r="H209">
         <f>IF(COUNTA($A209:$F209)=0,0,IF(OR($B209="",$C209="",$E209=""),1,0))</f>
         <v/>
       </c>
+      <c r="I209">
+        <f>IF(AND($E209&lt;&gt;"",OR(LEN($E209)&lt;&gt;17,LEN($E209)-LEN(SUBSTITUTE($E209,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="210">
       <c r="H210">
         <f>IF(COUNTA($A210:$F210)=0,0,IF(OR($B210="",$C210="",$E210=""),1,0))</f>
         <v/>
       </c>
+      <c r="I210">
+        <f>IF(AND($E210&lt;&gt;"",OR(LEN($E210)&lt;&gt;17,LEN($E210)-LEN(SUBSTITUTE($E210,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="211">
       <c r="H211">
         <f>IF(COUNTA($A211:$F211)=0,0,IF(OR($B211="",$C211="",$E211=""),1,0))</f>
         <v/>
       </c>
+      <c r="I211">
+        <f>IF(AND($E211&lt;&gt;"",OR(LEN($E211)&lt;&gt;17,LEN($E211)-LEN(SUBSTITUTE($E211,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="212">
       <c r="H212">
         <f>IF(COUNTA($A212:$F212)=0,0,IF(OR($B212="",$C212="",$E212=""),1,0))</f>
         <v/>
       </c>
+      <c r="I212">
+        <f>IF(AND($E212&lt;&gt;"",OR(LEN($E212)&lt;&gt;17,LEN($E212)-LEN(SUBSTITUTE($E212,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="213">
       <c r="H213">
         <f>IF(COUNTA($A213:$F213)=0,0,IF(OR($B213="",$C213="",$E213=""),1,0))</f>
         <v/>
       </c>
+      <c r="I213">
+        <f>IF(AND($E213&lt;&gt;"",OR(LEN($E213)&lt;&gt;17,LEN($E213)-LEN(SUBSTITUTE($E213,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="214">
       <c r="H214">
         <f>IF(COUNTA($A214:$F214)=0,0,IF(OR($B214="",$C214="",$E214=""),1,0))</f>
         <v/>
       </c>
+      <c r="I214">
+        <f>IF(AND($E214&lt;&gt;"",OR(LEN($E214)&lt;&gt;17,LEN($E214)-LEN(SUBSTITUTE($E214,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="215">
       <c r="H215">
         <f>IF(COUNTA($A215:$F215)=0,0,IF(OR($B215="",$C215="",$E215=""),1,0))</f>
         <v/>
       </c>
+      <c r="I215">
+        <f>IF(AND($E215&lt;&gt;"",OR(LEN($E215)&lt;&gt;17,LEN($E215)-LEN(SUBSTITUTE($E215,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="216">
       <c r="H216">
         <f>IF(COUNTA($A216:$F216)=0,0,IF(OR($B216="",$C216="",$E216=""),1,0))</f>
         <v/>
       </c>
+      <c r="I216">
+        <f>IF(AND($E216&lt;&gt;"",OR(LEN($E216)&lt;&gt;17,LEN($E216)-LEN(SUBSTITUTE($E216,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="217">
       <c r="H217">
         <f>IF(COUNTA($A217:$F217)=0,0,IF(OR($B217="",$C217="",$E217=""),1,0))</f>
         <v/>
       </c>
+      <c r="I217">
+        <f>IF(AND($E217&lt;&gt;"",OR(LEN($E217)&lt;&gt;17,LEN($E217)-LEN(SUBSTITUTE($E217,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="218">
       <c r="H218">
         <f>IF(COUNTA($A218:$F218)=0,0,IF(OR($B218="",$C218="",$E218=""),1,0))</f>
         <v/>
       </c>
+      <c r="I218">
+        <f>IF(AND($E218&lt;&gt;"",OR(LEN($E218)&lt;&gt;17,LEN($E218)-LEN(SUBSTITUTE($E218,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="219">
       <c r="H219">
         <f>IF(COUNTA($A219:$F219)=0,0,IF(OR($B219="",$C219="",$E219=""),1,0))</f>
         <v/>
       </c>
+      <c r="I219">
+        <f>IF(AND($E219&lt;&gt;"",OR(LEN($E219)&lt;&gt;17,LEN($E219)-LEN(SUBSTITUTE($E219,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="220">
       <c r="H220">
         <f>IF(COUNTA($A220:$F220)=0,0,IF(OR($B220="",$C220="",$E220=""),1,0))</f>
         <v/>
       </c>
+      <c r="I220">
+        <f>IF(AND($E220&lt;&gt;"",OR(LEN($E220)&lt;&gt;17,LEN($E220)-LEN(SUBSTITUTE($E220,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="221">
       <c r="H221">
         <f>IF(COUNTA($A221:$F221)=0,0,IF(OR($B221="",$C221="",$E221=""),1,0))</f>
         <v/>
       </c>
+      <c r="I221">
+        <f>IF(AND($E221&lt;&gt;"",OR(LEN($E221)&lt;&gt;17,LEN($E221)-LEN(SUBSTITUTE($E221,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="222">
       <c r="H222">
         <f>IF(COUNTA($A222:$F222)=0,0,IF(OR($B222="",$C222="",$E222=""),1,0))</f>
         <v/>
       </c>
+      <c r="I222">
+        <f>IF(AND($E222&lt;&gt;"",OR(LEN($E222)&lt;&gt;17,LEN($E222)-LEN(SUBSTITUTE($E222,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="223">
       <c r="H223">
         <f>IF(COUNTA($A223:$F223)=0,0,IF(OR($B223="",$C223="",$E223=""),1,0))</f>
         <v/>
       </c>
+      <c r="I223">
+        <f>IF(AND($E223&lt;&gt;"",OR(LEN($E223)&lt;&gt;17,LEN($E223)-LEN(SUBSTITUTE($E223,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="224">
       <c r="H224">
         <f>IF(COUNTA($A224:$F224)=0,0,IF(OR($B224="",$C224="",$E224=""),1,0))</f>
         <v/>
       </c>
+      <c r="I224">
+        <f>IF(AND($E224&lt;&gt;"",OR(LEN($E224)&lt;&gt;17,LEN($E224)-LEN(SUBSTITUTE($E224,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="225">
       <c r="H225">
         <f>IF(COUNTA($A225:$F225)=0,0,IF(OR($B225="",$C225="",$E225=""),1,0))</f>
         <v/>
       </c>
+      <c r="I225">
+        <f>IF(AND($E225&lt;&gt;"",OR(LEN($E225)&lt;&gt;17,LEN($E225)-LEN(SUBSTITUTE($E225,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="226">
       <c r="H226">
         <f>IF(COUNTA($A226:$F226)=0,0,IF(OR($B226="",$C226="",$E226=""),1,0))</f>
         <v/>
       </c>
+      <c r="I226">
+        <f>IF(AND($E226&lt;&gt;"",OR(LEN($E226)&lt;&gt;17,LEN($E226)-LEN(SUBSTITUTE($E226,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="227">
       <c r="H227">
         <f>IF(COUNTA($A227:$F227)=0,0,IF(OR($B227="",$C227="",$E227=""),1,0))</f>
         <v/>
       </c>
+      <c r="I227">
+        <f>IF(AND($E227&lt;&gt;"",OR(LEN($E227)&lt;&gt;17,LEN($E227)-LEN(SUBSTITUTE($E227,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="228">
       <c r="H228">
         <f>IF(COUNTA($A228:$F228)=0,0,IF(OR($B228="",$C228="",$E228=""),1,0))</f>
         <v/>
       </c>
+      <c r="I228">
+        <f>IF(AND($E228&lt;&gt;"",OR(LEN($E228)&lt;&gt;17,LEN($E228)-LEN(SUBSTITUTE($E228,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="229">
       <c r="H229">
         <f>IF(COUNTA($A229:$F229)=0,0,IF(OR($B229="",$C229="",$E229=""),1,0))</f>
         <v/>
       </c>
+      <c r="I229">
+        <f>IF(AND($E229&lt;&gt;"",OR(LEN($E229)&lt;&gt;17,LEN($E229)-LEN(SUBSTITUTE($E229,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="230">
       <c r="H230">
         <f>IF(COUNTA($A230:$F230)=0,0,IF(OR($B230="",$C230="",$E230=""),1,0))</f>
         <v/>
       </c>
+      <c r="I230">
+        <f>IF(AND($E230&lt;&gt;"",OR(LEN($E230)&lt;&gt;17,LEN($E230)-LEN(SUBSTITUTE($E230,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="231">
       <c r="H231">
         <f>IF(COUNTA($A231:$F231)=0,0,IF(OR($B231="",$C231="",$E231=""),1,0))</f>
         <v/>
       </c>
+      <c r="I231">
+        <f>IF(AND($E231&lt;&gt;"",OR(LEN($E231)&lt;&gt;17,LEN($E231)-LEN(SUBSTITUTE($E231,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="232">
       <c r="H232">
         <f>IF(COUNTA($A232:$F232)=0,0,IF(OR($B232="",$C232="",$E232=""),1,0))</f>
         <v/>
       </c>
+      <c r="I232">
+        <f>IF(AND($E232&lt;&gt;"",OR(LEN($E232)&lt;&gt;17,LEN($E232)-LEN(SUBSTITUTE($E232,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="233">
       <c r="H233">
         <f>IF(COUNTA($A233:$F233)=0,0,IF(OR($B233="",$C233="",$E233=""),1,0))</f>
         <v/>
       </c>
+      <c r="I233">
+        <f>IF(AND($E233&lt;&gt;"",OR(LEN($E233)&lt;&gt;17,LEN($E233)-LEN(SUBSTITUTE($E233,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="234">
       <c r="H234">
         <f>IF(COUNTA($A234:$F234)=0,0,IF(OR($B234="",$C234="",$E234=""),1,0))</f>
         <v/>
       </c>
+      <c r="I234">
+        <f>IF(AND($E234&lt;&gt;"",OR(LEN($E234)&lt;&gt;17,LEN($E234)-LEN(SUBSTITUTE($E234,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="235">
       <c r="H235">
         <f>IF(COUNTA($A235:$F235)=0,0,IF(OR($B235="",$C235="",$E235=""),1,0))</f>
         <v/>
       </c>
+      <c r="I235">
+        <f>IF(AND($E235&lt;&gt;"",OR(LEN($E235)&lt;&gt;17,LEN($E235)-LEN(SUBSTITUTE($E235,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="236">
       <c r="H236">
         <f>IF(COUNTA($A236:$F236)=0,0,IF(OR($B236="",$C236="",$E236=""),1,0))</f>
         <v/>
       </c>
+      <c r="I236">
+        <f>IF(AND($E236&lt;&gt;"",OR(LEN($E236)&lt;&gt;17,LEN($E236)-LEN(SUBSTITUTE($E236,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="237">
       <c r="H237">
         <f>IF(COUNTA($A237:$F237)=0,0,IF(OR($B237="",$C237="",$E237=""),1,0))</f>
         <v/>
       </c>
+      <c r="I237">
+        <f>IF(AND($E237&lt;&gt;"",OR(LEN($E237)&lt;&gt;17,LEN($E237)-LEN(SUBSTITUTE($E237,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="238">
       <c r="H238">
         <f>IF(COUNTA($A238:$F238)=0,0,IF(OR($B238="",$C238="",$E238=""),1,0))</f>
         <v/>
       </c>
+      <c r="I238">
+        <f>IF(AND($E238&lt;&gt;"",OR(LEN($E238)&lt;&gt;17,LEN($E238)-LEN(SUBSTITUTE($E238,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="239">
       <c r="H239">
         <f>IF(COUNTA($A239:$F239)=0,0,IF(OR($B239="",$C239="",$E239=""),1,0))</f>
         <v/>
       </c>
+      <c r="I239">
+        <f>IF(AND($E239&lt;&gt;"",OR(LEN($E239)&lt;&gt;17,LEN($E239)-LEN(SUBSTITUTE($E239,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="240">
       <c r="H240">
         <f>IF(COUNTA($A240:$F240)=0,0,IF(OR($B240="",$C240="",$E240=""),1,0))</f>
         <v/>
       </c>
+      <c r="I240">
+        <f>IF(AND($E240&lt;&gt;"",OR(LEN($E240)&lt;&gt;17,LEN($E240)-LEN(SUBSTITUTE($E240,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="241">
       <c r="H241">
         <f>IF(COUNTA($A241:$F241)=0,0,IF(OR($B241="",$C241="",$E241=""),1,0))</f>
         <v/>
       </c>
+      <c r="I241">
+        <f>IF(AND($E241&lt;&gt;"",OR(LEN($E241)&lt;&gt;17,LEN($E241)-LEN(SUBSTITUTE($E241,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="242">
       <c r="H242">
         <f>IF(COUNTA($A242:$F242)=0,0,IF(OR($B242="",$C242="",$E242=""),1,0))</f>
         <v/>
       </c>
+      <c r="I242">
+        <f>IF(AND($E242&lt;&gt;"",OR(LEN($E242)&lt;&gt;17,LEN($E242)-LEN(SUBSTITUTE($E242,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="243">
       <c r="H243">
         <f>IF(COUNTA($A243:$F243)=0,0,IF(OR($B243="",$C243="",$E243=""),1,0))</f>
         <v/>
       </c>
+      <c r="I243">
+        <f>IF(AND($E243&lt;&gt;"",OR(LEN($E243)&lt;&gt;17,LEN($E243)-LEN(SUBSTITUTE($E243,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="244">
       <c r="H244">
         <f>IF(COUNTA($A244:$F244)=0,0,IF(OR($B244="",$C244="",$E244=""),1,0))</f>
         <v/>
       </c>
+      <c r="I244">
+        <f>IF(AND($E244&lt;&gt;"",OR(LEN($E244)&lt;&gt;17,LEN($E244)-LEN(SUBSTITUTE($E244,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="245">
       <c r="H245">
         <f>IF(COUNTA($A245:$F245)=0,0,IF(OR($B245="",$C245="",$E245=""),1,0))</f>
         <v/>
       </c>
+      <c r="I245">
+        <f>IF(AND($E245&lt;&gt;"",OR(LEN($E245)&lt;&gt;17,LEN($E245)-LEN(SUBSTITUTE($E245,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="246">
       <c r="H246">
         <f>IF(COUNTA($A246:$F246)=0,0,IF(OR($B246="",$C246="",$E246=""),1,0))</f>
         <v/>
       </c>
+      <c r="I246">
+        <f>IF(AND($E246&lt;&gt;"",OR(LEN($E246)&lt;&gt;17,LEN($E246)-LEN(SUBSTITUTE($E246,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="247">
       <c r="H247">
         <f>IF(COUNTA($A247:$F247)=0,0,IF(OR($B247="",$C247="",$E247=""),1,0))</f>
         <v/>
       </c>
+      <c r="I247">
+        <f>IF(AND($E247&lt;&gt;"",OR(LEN($E247)&lt;&gt;17,LEN($E247)-LEN(SUBSTITUTE($E247,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="248">
       <c r="H248">
         <f>IF(COUNTA($A248:$F248)=0,0,IF(OR($B248="",$C248="",$E248=""),1,0))</f>
         <v/>
       </c>
+      <c r="I248">
+        <f>IF(AND($E248&lt;&gt;"",OR(LEN($E248)&lt;&gt;17,LEN($E248)-LEN(SUBSTITUTE($E248,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="249">
       <c r="H249">
         <f>IF(COUNTA($A249:$F249)=0,0,IF(OR($B249="",$C249="",$E249=""),1,0))</f>
         <v/>
       </c>
+      <c r="I249">
+        <f>IF(AND($E249&lt;&gt;"",OR(LEN($E249)&lt;&gt;17,LEN($E249)-LEN(SUBSTITUTE($E249,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="250">
       <c r="H250">
         <f>IF(COUNTA($A250:$F250)=0,0,IF(OR($B250="",$C250="",$E250=""),1,0))</f>
         <v/>
       </c>
+      <c r="I250">
+        <f>IF(AND($E250&lt;&gt;"",OR(LEN($E250)&lt;&gt;17,LEN($E250)-LEN(SUBSTITUTE($E250,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="251">
       <c r="H251">
         <f>IF(COUNTA($A251:$F251)=0,0,IF(OR($B251="",$C251="",$E251=""),1,0))</f>
         <v/>
       </c>
+      <c r="I251">
+        <f>IF(AND($E251&lt;&gt;"",OR(LEN($E251)&lt;&gt;17,LEN($E251)-LEN(SUBSTITUTE($E251,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="252">
       <c r="H252">
         <f>IF(COUNTA($A252:$F252)=0,0,IF(OR($B252="",$C252="",$E252=""),1,0))</f>
         <v/>
       </c>
+      <c r="I252">
+        <f>IF(AND($E252&lt;&gt;"",OR(LEN($E252)&lt;&gt;17,LEN($E252)-LEN(SUBSTITUTE($E252,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="253">
       <c r="H253">
         <f>IF(COUNTA($A253:$F253)=0,0,IF(OR($B253="",$C253="",$E253=""),1,0))</f>
         <v/>
       </c>
+      <c r="I253">
+        <f>IF(AND($E253&lt;&gt;"",OR(LEN($E253)&lt;&gt;17,LEN($E253)-LEN(SUBSTITUTE($E253,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="254">
       <c r="H254">
         <f>IF(COUNTA($A254:$F254)=0,0,IF(OR($B254="",$C254="",$E254=""),1,0))</f>
         <v/>
       </c>
+      <c r="I254">
+        <f>IF(AND($E254&lt;&gt;"",OR(LEN($E254)&lt;&gt;17,LEN($E254)-LEN(SUBSTITUTE($E254,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="255">
       <c r="H255">
         <f>IF(COUNTA($A255:$F255)=0,0,IF(OR($B255="",$C255="",$E255=""),1,0))</f>
         <v/>
       </c>
+      <c r="I255">
+        <f>IF(AND($E255&lt;&gt;"",OR(LEN($E255)&lt;&gt;17,LEN($E255)-LEN(SUBSTITUTE($E255,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="256">
       <c r="H256">
         <f>IF(COUNTA($A256:$F256)=0,0,IF(OR($B256="",$C256="",$E256=""),1,0))</f>
         <v/>
       </c>
+      <c r="I256">
+        <f>IF(AND($E256&lt;&gt;"",OR(LEN($E256)&lt;&gt;17,LEN($E256)-LEN(SUBSTITUTE($E256,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="257">
       <c r="H257">
         <f>IF(COUNTA($A257:$F257)=0,0,IF(OR($B257="",$C257="",$E257=""),1,0))</f>
         <v/>
       </c>
+      <c r="I257">
+        <f>IF(AND($E257&lt;&gt;"",OR(LEN($E257)&lt;&gt;17,LEN($E257)-LEN(SUBSTITUTE($E257,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="258">
       <c r="H258">
         <f>IF(COUNTA($A258:$F258)=0,0,IF(OR($B258="",$C258="",$E258=""),1,0))</f>
         <v/>
       </c>
+      <c r="I258">
+        <f>IF(AND($E258&lt;&gt;"",OR(LEN($E258)&lt;&gt;17,LEN($E258)-LEN(SUBSTITUTE($E258,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="259">
       <c r="H259">
         <f>IF(COUNTA($A259:$F259)=0,0,IF(OR($B259="",$C259="",$E259=""),1,0))</f>
         <v/>
       </c>
+      <c r="I259">
+        <f>IF(AND($E259&lt;&gt;"",OR(LEN($E259)&lt;&gt;17,LEN($E259)-LEN(SUBSTITUTE($E259,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="260">
       <c r="H260">
         <f>IF(COUNTA($A260:$F260)=0,0,IF(OR($B260="",$C260="",$E260=""),1,0))</f>
         <v/>
       </c>
+      <c r="I260">
+        <f>IF(AND($E260&lt;&gt;"",OR(LEN($E260)&lt;&gt;17,LEN($E260)-LEN(SUBSTITUTE($E260,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="261">
       <c r="H261">
         <f>IF(COUNTA($A261:$F261)=0,0,IF(OR($B261="",$C261="",$E261=""),1,0))</f>
         <v/>
       </c>
+      <c r="I261">
+        <f>IF(AND($E261&lt;&gt;"",OR(LEN($E261)&lt;&gt;17,LEN($E261)-LEN(SUBSTITUTE($E261,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="262">
       <c r="H262">
         <f>IF(COUNTA($A262:$F262)=0,0,IF(OR($B262="",$C262="",$E262=""),1,0))</f>
         <v/>
       </c>
+      <c r="I262">
+        <f>IF(AND($E262&lt;&gt;"",OR(LEN($E262)&lt;&gt;17,LEN($E262)-LEN(SUBSTITUTE($E262,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="263">
       <c r="H263">
         <f>IF(COUNTA($A263:$F263)=0,0,IF(OR($B263="",$C263="",$E263=""),1,0))</f>
         <v/>
       </c>
+      <c r="I263">
+        <f>IF(AND($E263&lt;&gt;"",OR(LEN($E263)&lt;&gt;17,LEN($E263)-LEN(SUBSTITUTE($E263,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="264">
       <c r="H264">
         <f>IF(COUNTA($A264:$F264)=0,0,IF(OR($B264="",$C264="",$E264=""),1,0))</f>
         <v/>
       </c>
+      <c r="I264">
+        <f>IF(AND($E264&lt;&gt;"",OR(LEN($E264)&lt;&gt;17,LEN($E264)-LEN(SUBSTITUTE($E264,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="265">
       <c r="H265">
         <f>IF(COUNTA($A265:$F265)=0,0,IF(OR($B265="",$C265="",$E265=""),1,0))</f>
         <v/>
       </c>
+      <c r="I265">
+        <f>IF(AND($E265&lt;&gt;"",OR(LEN($E265)&lt;&gt;17,LEN($E265)-LEN(SUBSTITUTE($E265,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="266">
       <c r="H266">
         <f>IF(COUNTA($A266:$F266)=0,0,IF(OR($B266="",$C266="",$E266=""),1,0))</f>
         <v/>
       </c>
+      <c r="I266">
+        <f>IF(AND($E266&lt;&gt;"",OR(LEN($E266)&lt;&gt;17,LEN($E266)-LEN(SUBSTITUTE($E266,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="267">
       <c r="H267">
         <f>IF(COUNTA($A267:$F267)=0,0,IF(OR($B267="",$C267="",$E267=""),1,0))</f>
         <v/>
       </c>
+      <c r="I267">
+        <f>IF(AND($E267&lt;&gt;"",OR(LEN($E267)&lt;&gt;17,LEN($E267)-LEN(SUBSTITUTE($E267,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="268">
       <c r="H268">
         <f>IF(COUNTA($A268:$F268)=0,0,IF(OR($B268="",$C268="",$E268=""),1,0))</f>
         <v/>
       </c>
+      <c r="I268">
+        <f>IF(AND($E268&lt;&gt;"",OR(LEN($E268)&lt;&gt;17,LEN($E268)-LEN(SUBSTITUTE($E268,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="269">
       <c r="H269">
         <f>IF(COUNTA($A269:$F269)=0,0,IF(OR($B269="",$C269="",$E269=""),1,0))</f>
         <v/>
       </c>
+      <c r="I269">
+        <f>IF(AND($E269&lt;&gt;"",OR(LEN($E269)&lt;&gt;17,LEN($E269)-LEN(SUBSTITUTE($E269,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="270">
       <c r="H270">
         <f>IF(COUNTA($A270:$F270)=0,0,IF(OR($B270="",$C270="",$E270=""),1,0))</f>
         <v/>
       </c>
+      <c r="I270">
+        <f>IF(AND($E270&lt;&gt;"",OR(LEN($E270)&lt;&gt;17,LEN($E270)-LEN(SUBSTITUTE($E270,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="271">
       <c r="H271">
         <f>IF(COUNTA($A271:$F271)=0,0,IF(OR($B271="",$C271="",$E271=""),1,0))</f>
         <v/>
       </c>
+      <c r="I271">
+        <f>IF(AND($E271&lt;&gt;"",OR(LEN($E271)&lt;&gt;17,LEN($E271)-LEN(SUBSTITUTE($E271,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="272">
       <c r="H272">
         <f>IF(COUNTA($A272:$F272)=0,0,IF(OR($B272="",$C272="",$E272=""),1,0))</f>
         <v/>
       </c>
+      <c r="I272">
+        <f>IF(AND($E272&lt;&gt;"",OR(LEN($E272)&lt;&gt;17,LEN($E272)-LEN(SUBSTITUTE($E272,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="273">
       <c r="H273">
         <f>IF(COUNTA($A273:$F273)=0,0,IF(OR($B273="",$C273="",$E273=""),1,0))</f>
         <v/>
       </c>
+      <c r="I273">
+        <f>IF(AND($E273&lt;&gt;"",OR(LEN($E273)&lt;&gt;17,LEN($E273)-LEN(SUBSTITUTE($E273,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="274">
       <c r="H274">
         <f>IF(COUNTA($A274:$F274)=0,0,IF(OR($B274="",$C274="",$E274=""),1,0))</f>
         <v/>
       </c>
+      <c r="I274">
+        <f>IF(AND($E274&lt;&gt;"",OR(LEN($E274)&lt;&gt;17,LEN($E274)-LEN(SUBSTITUTE($E274,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="275">
       <c r="H275">
         <f>IF(COUNTA($A275:$F275)=0,0,IF(OR($B275="",$C275="",$E275=""),1,0))</f>
         <v/>
       </c>
+      <c r="I275">
+        <f>IF(AND($E275&lt;&gt;"",OR(LEN($E275)&lt;&gt;17,LEN($E275)-LEN(SUBSTITUTE($E275,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="276">
       <c r="H276">
         <f>IF(COUNTA($A276:$F276)=0,0,IF(OR($B276="",$C276="",$E276=""),1,0))</f>
         <v/>
       </c>
+      <c r="I276">
+        <f>IF(AND($E276&lt;&gt;"",OR(LEN($E276)&lt;&gt;17,LEN($E276)-LEN(SUBSTITUTE($E276,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="277">
       <c r="H277">
         <f>IF(COUNTA($A277:$F277)=0,0,IF(OR($B277="",$C277="",$E277=""),1,0))</f>
         <v/>
       </c>
+      <c r="I277">
+        <f>IF(AND($E277&lt;&gt;"",OR(LEN($E277)&lt;&gt;17,LEN($E277)-LEN(SUBSTITUTE($E277,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="278">
       <c r="H278">
         <f>IF(COUNTA($A278:$F278)=0,0,IF(OR($B278="",$C278="",$E278=""),1,0))</f>
         <v/>
       </c>
+      <c r="I278">
+        <f>IF(AND($E278&lt;&gt;"",OR(LEN($E278)&lt;&gt;17,LEN($E278)-LEN(SUBSTITUTE($E278,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="279">
       <c r="H279">
         <f>IF(COUNTA($A279:$F279)=0,0,IF(OR($B279="",$C279="",$E279=""),1,0))</f>
         <v/>
       </c>
+      <c r="I279">
+        <f>IF(AND($E279&lt;&gt;"",OR(LEN($E279)&lt;&gt;17,LEN($E279)-LEN(SUBSTITUTE($E279,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="280">
       <c r="H280">
         <f>IF(COUNTA($A280:$F280)=0,0,IF(OR($B280="",$C280="",$E280=""),1,0))</f>
         <v/>
       </c>
+      <c r="I280">
+        <f>IF(AND($E280&lt;&gt;"",OR(LEN($E280)&lt;&gt;17,LEN($E280)-LEN(SUBSTITUTE($E280,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="281">
       <c r="H281">
         <f>IF(COUNTA($A281:$F281)=0,0,IF(OR($B281="",$C281="",$E281=""),1,0))</f>
         <v/>
       </c>
+      <c r="I281">
+        <f>IF(AND($E281&lt;&gt;"",OR(LEN($E281)&lt;&gt;17,LEN($E281)-LEN(SUBSTITUTE($E281,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="282">
       <c r="H282">
         <f>IF(COUNTA($A282:$F282)=0,0,IF(OR($B282="",$C282="",$E282=""),1,0))</f>
         <v/>
       </c>
+      <c r="I282">
+        <f>IF(AND($E282&lt;&gt;"",OR(LEN($E282)&lt;&gt;17,LEN($E282)-LEN(SUBSTITUTE($E282,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="283">
       <c r="H283">
         <f>IF(COUNTA($A283:$F283)=0,0,IF(OR($B283="",$C283="",$E283=""),1,0))</f>
         <v/>
       </c>
+      <c r="I283">
+        <f>IF(AND($E283&lt;&gt;"",OR(LEN($E283)&lt;&gt;17,LEN($E283)-LEN(SUBSTITUTE($E283,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="284">
       <c r="H284">
         <f>IF(COUNTA($A284:$F284)=0,0,IF(OR($B284="",$C284="",$E284=""),1,0))</f>
         <v/>
       </c>
+      <c r="I284">
+        <f>IF(AND($E284&lt;&gt;"",OR(LEN($E284)&lt;&gt;17,LEN($E284)-LEN(SUBSTITUTE($E284,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="285">
       <c r="H285">
         <f>IF(COUNTA($A285:$F285)=0,0,IF(OR($B285="",$C285="",$E285=""),1,0))</f>
         <v/>
       </c>
+      <c r="I285">
+        <f>IF(AND($E285&lt;&gt;"",OR(LEN($E285)&lt;&gt;17,LEN($E285)-LEN(SUBSTITUTE($E285,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="286">
       <c r="H286">
         <f>IF(COUNTA($A286:$F286)=0,0,IF(OR($B286="",$C286="",$E286=""),1,0))</f>
         <v/>
       </c>
+      <c r="I286">
+        <f>IF(AND($E286&lt;&gt;"",OR(LEN($E286)&lt;&gt;17,LEN($E286)-LEN(SUBSTITUTE($E286,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="287">
       <c r="H287">
         <f>IF(COUNTA($A287:$F287)=0,0,IF(OR($B287="",$C287="",$E287=""),1,0))</f>
         <v/>
       </c>
+      <c r="I287">
+        <f>IF(AND($E287&lt;&gt;"",OR(LEN($E287)&lt;&gt;17,LEN($E287)-LEN(SUBSTITUTE($E287,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="288">
       <c r="H288">
         <f>IF(COUNTA($A288:$F288)=0,0,IF(OR($B288="",$C288="",$E288=""),1,0))</f>
         <v/>
       </c>
+      <c r="I288">
+        <f>IF(AND($E288&lt;&gt;"",OR(LEN($E288)&lt;&gt;17,LEN($E288)-LEN(SUBSTITUTE($E288,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="289">
       <c r="H289">
         <f>IF(COUNTA($A289:$F289)=0,0,IF(OR($B289="",$C289="",$E289=""),1,0))</f>
         <v/>
       </c>
+      <c r="I289">
+        <f>IF(AND($E289&lt;&gt;"",OR(LEN($E289)&lt;&gt;17,LEN($E289)-LEN(SUBSTITUTE($E289,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="290">
       <c r="H290">
         <f>IF(COUNTA($A290:$F290)=0,0,IF(OR($B290="",$C290="",$E290=""),1,0))</f>
         <v/>
       </c>
+      <c r="I290">
+        <f>IF(AND($E290&lt;&gt;"",OR(LEN($E290)&lt;&gt;17,LEN($E290)-LEN(SUBSTITUTE($E290,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="291">
       <c r="H291">
         <f>IF(COUNTA($A291:$F291)=0,0,IF(OR($B291="",$C291="",$E291=""),1,0))</f>
         <v/>
       </c>
+      <c r="I291">
+        <f>IF(AND($E291&lt;&gt;"",OR(LEN($E291)&lt;&gt;17,LEN($E291)-LEN(SUBSTITUTE($E291,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="292">
       <c r="H292">
         <f>IF(COUNTA($A292:$F292)=0,0,IF(OR($B292="",$C292="",$E292=""),1,0))</f>
         <v/>
       </c>
+      <c r="I292">
+        <f>IF(AND($E292&lt;&gt;"",OR(LEN($E292)&lt;&gt;17,LEN($E292)-LEN(SUBSTITUTE($E292,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="293">
       <c r="H293">
         <f>IF(COUNTA($A293:$F293)=0,0,IF(OR($B293="",$C293="",$E293=""),1,0))</f>
         <v/>
       </c>
+      <c r="I293">
+        <f>IF(AND($E293&lt;&gt;"",OR(LEN($E293)&lt;&gt;17,LEN($E293)-LEN(SUBSTITUTE($E293,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="294">
       <c r="H294">
         <f>IF(COUNTA($A294:$F294)=0,0,IF(OR($B294="",$C294="",$E294=""),1,0))</f>
         <v/>
       </c>
+      <c r="I294">
+        <f>IF(AND($E294&lt;&gt;"",OR(LEN($E294)&lt;&gt;17,LEN($E294)-LEN(SUBSTITUTE($E294,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="295">
       <c r="H295">
         <f>IF(COUNTA($A295:$F295)=0,0,IF(OR($B295="",$C295="",$E295=""),1,0))</f>
         <v/>
       </c>
+      <c r="I295">
+        <f>IF(AND($E295&lt;&gt;"",OR(LEN($E295)&lt;&gt;17,LEN($E295)-LEN(SUBSTITUTE($E295,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="296">
       <c r="H296">
         <f>IF(COUNTA($A296:$F296)=0,0,IF(OR($B296="",$C296="",$E296=""),1,0))</f>
         <v/>
       </c>
+      <c r="I296">
+        <f>IF(AND($E296&lt;&gt;"",OR(LEN($E296)&lt;&gt;17,LEN($E296)-LEN(SUBSTITUTE($E296,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="297">
       <c r="H297">
         <f>IF(COUNTA($A297:$F297)=0,0,IF(OR($B297="",$C297="",$E297=""),1,0))</f>
         <v/>
       </c>
+      <c r="I297">
+        <f>IF(AND($E297&lt;&gt;"",OR(LEN($E297)&lt;&gt;17,LEN($E297)-LEN(SUBSTITUTE($E297,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="298">
       <c r="H298">
         <f>IF(COUNTA($A298:$F298)=0,0,IF(OR($B298="",$C298="",$E298=""),1,0))</f>
         <v/>
       </c>
+      <c r="I298">
+        <f>IF(AND($E298&lt;&gt;"",OR(LEN($E298)&lt;&gt;17,LEN($E298)-LEN(SUBSTITUTE($E298,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="299">
       <c r="H299">
         <f>IF(COUNTA($A299:$F299)=0,0,IF(OR($B299="",$C299="",$E299=""),1,0))</f>
         <v/>
       </c>
+      <c r="I299">
+        <f>IF(AND($E299&lt;&gt;"",OR(LEN($E299)&lt;&gt;17,LEN($E299)-LEN(SUBSTITUTE($E299,":",""))&lt;&gt;5)),1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="300">
       <c r="H300">
         <f>IF(COUNTA($A300:$F300)=0,0,IF(OR($B300="",$C300="",$E300=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="I300">
+        <f>IF(AND($E300&lt;&gt;"",OR(LEN($E300)&lt;&gt;17,LEN($E300)-LEN(SUBSTITUTE($E300,":",""))&lt;&gt;5)),1,0)</f>
         <v/>
       </c>
     </row>

--- a/src/main/resources/canevas/canevas-vierge.xlsx
+++ b/src/main/resources/canevas/canevas-vierge.xlsx
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="B16" s="21">
-        <f>IF(AND($B$3&lt;&gt;"",$B$4&lt;&gt;"",$B$6&lt;&gt;"",$B$7&lt;&gt;"",$B$8&lt;&gt;"",$B$9&lt;&gt;"",$B$10&lt;&gt;"",$B$11&lt;&gt;"",SUM('2-Membres mission'!$H$2:$H$100)=0,SUM('3-Ordinateurs'!$N$2:$N$300)=0,SUM('4-Imprimantes'!$H$2:$H$300)=0,SUM('5-Switchs et AP'!$H$2:$H$300)=0,SUM('6-Scanners chèque'!$F$2:$F$300)=0,SUM('Agents TPR'!$J$2:$J$203)=0),IF(AND(SUM('3-Ordinateurs'!$O$2:$O$300)=0,SUM('4-Imprimantes'!$I$2:$I$300)=0,SUM('5-Switchs et AP'!$I$2:$I$300)=0),"CANEVAS CONFORME","CANEVAS NON CONFORME - un ou plusieurs champs ont un format invalide (ex. MAC)"),"CANEVAS INCOMPLET - un ou plusieurs champs obligatoires manquent")</f>
+        <f>IF(AND($B$3&lt;&gt;"",$B$4&lt;&gt;"",$B$6&lt;&gt;"",$B$7&lt;&gt;"",$B$8&lt;&gt;"",$B$9&lt;&gt;"",$B$10&lt;&gt;"",$B$11&lt;&gt;"",SUM('2-Membres mission'!$H$2:$H$100)=0,SUM('3-Ordinateurs'!$P$2:$P$300)=0,SUM('4-Imprimantes'!$H$2:$H$300)=0,SUM('5-Switchs et AP'!$H$2:$H$300)=0,SUM('6-Scanners chèque'!$F$2:$F$300)=0,SUM('Agents TPR'!$J$2:$J$203)=0),IF(AND(SUM('3-Ordinateurs'!$Q$2:$Q$300)=0,SUM('4-Imprimantes'!$I$2:$I$300)=0,SUM('5-Switchs et AP'!$I$2:$I$300)=0),"CANEVAS CONFORME","CANEVAS NON CONFORME - un ou plusieurs champs ont un format invalide (ex. MAC)"),"CANEVAS INCOMPLET - un ou plusieurs champs obligatoires manquent")</f>
         <v/>
       </c>
     </row>
@@ -2369,7 +2369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O300"/>
+  <dimension ref="A1:Q300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2384,8 +2384,11 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col hidden="1" width="13" customWidth="1" min="14" max="14"/>
-    <col hidden="1" width="13" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col hidden="1" width="13" customWidth="1" min="16" max="16"/>
+    <col hidden="1" width="13" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2449,12 +2452,27 @@
           <t>Sysbudget</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="M1" s="10" t="inlineStr">
+        <is>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="N1" s="10" t="inlineStr">
+        <is>
+          <t>Processeur</t>
+        </is>
+      </c>
+      <c r="O1" s="10" t="inlineStr">
+        <is>
+          <t>Disque dur</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
         <is>
           <t>ctrl</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>ctrlfmt</t>
         </is>
@@ -2473,11 +2491,14 @@
       <c r="J2" s="23" t="n"/>
       <c r="K2" s="23" t="n"/>
       <c r="L2" s="23" t="n"/>
-      <c r="N2">
-        <f>IF(COUNTA($A2:$L2)=0,0,IF(OR($B2="",$D2="",$F2="",$G2=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O2">
+      <c r="M2" s="24" t="n"/>
+      <c r="N2" s="24" t="n"/>
+      <c r="O2" s="24" t="n"/>
+      <c r="P2">
+        <f>IF(COUNTA($A2:$O2)=0,0,IF(OR($B2="",$D2="",$F2="",$G2=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q2">
         <f>IF(OR(AND($D2&lt;&gt;"",OR(LEN($D2)&lt;&gt;17,LEN($D2)-LEN(SUBSTITUTE($D2,":",""))&lt;&gt;5)),AND($E2&lt;&gt;"",OR(LEN($E2)&lt;&gt;17,LEN($E2)-LEN(SUBSTITUTE($E2,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -2495,11 +2516,14 @@
       <c r="J3" s="23" t="n"/>
       <c r="K3" s="23" t="n"/>
       <c r="L3" s="23" t="n"/>
-      <c r="N3">
-        <f>IF(COUNTA($A3:$L3)=0,0,IF(OR($B3="",$D3="",$F3="",$G3=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O3">
+      <c r="M3" s="24" t="n"/>
+      <c r="N3" s="24" t="n"/>
+      <c r="O3" s="24" t="n"/>
+      <c r="P3">
+        <f>IF(COUNTA($A3:$O3)=0,0,IF(OR($B3="",$D3="",$F3="",$G3=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q3">
         <f>IF(OR(AND($D3&lt;&gt;"",OR(LEN($D3)&lt;&gt;17,LEN($D3)-LEN(SUBSTITUTE($D3,":",""))&lt;&gt;5)),AND($E3&lt;&gt;"",OR(LEN($E3)&lt;&gt;17,LEN($E3)-LEN(SUBSTITUTE($E3,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -2517,11 +2541,14 @@
       <c r="J4" s="23" t="n"/>
       <c r="K4" s="23" t="n"/>
       <c r="L4" s="23" t="n"/>
-      <c r="N4">
-        <f>IF(COUNTA($A4:$L4)=0,0,IF(OR($B4="",$D4="",$F4="",$G4=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O4">
+      <c r="M4" s="24" t="n"/>
+      <c r="N4" s="24" t="n"/>
+      <c r="O4" s="24" t="n"/>
+      <c r="P4">
+        <f>IF(COUNTA($A4:$O4)=0,0,IF(OR($B4="",$D4="",$F4="",$G4=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q4">
         <f>IF(OR(AND($D4&lt;&gt;"",OR(LEN($D4)&lt;&gt;17,LEN($D4)-LEN(SUBSTITUTE($D4,":",""))&lt;&gt;5)),AND($E4&lt;&gt;"",OR(LEN($E4)&lt;&gt;17,LEN($E4)-LEN(SUBSTITUTE($E4,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -2539,11 +2566,14 @@
       <c r="J5" s="23" t="n"/>
       <c r="K5" s="23" t="n"/>
       <c r="L5" s="23" t="n"/>
-      <c r="N5">
-        <f>IF(COUNTA($A5:$L5)=0,0,IF(OR($B5="",$D5="",$F5="",$G5=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O5">
+      <c r="M5" s="24" t="n"/>
+      <c r="N5" s="24" t="n"/>
+      <c r="O5" s="24" t="n"/>
+      <c r="P5">
+        <f>IF(COUNTA($A5:$O5)=0,0,IF(OR($B5="",$D5="",$F5="",$G5=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q5">
         <f>IF(OR(AND($D5&lt;&gt;"",OR(LEN($D5)&lt;&gt;17,LEN($D5)-LEN(SUBSTITUTE($D5,":",""))&lt;&gt;5)),AND($E5&lt;&gt;"",OR(LEN($E5)&lt;&gt;17,LEN($E5)-LEN(SUBSTITUTE($E5,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -2561,11 +2591,14 @@
       <c r="J6" s="23" t="n"/>
       <c r="K6" s="23" t="n"/>
       <c r="L6" s="23" t="n"/>
-      <c r="N6">
-        <f>IF(COUNTA($A6:$L6)=0,0,IF(OR($B6="",$D6="",$F6="",$G6=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O6">
+      <c r="M6" s="24" t="n"/>
+      <c r="N6" s="24" t="n"/>
+      <c r="O6" s="24" t="n"/>
+      <c r="P6">
+        <f>IF(COUNTA($A6:$O6)=0,0,IF(OR($B6="",$D6="",$F6="",$G6=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q6">
         <f>IF(OR(AND($D6&lt;&gt;"",OR(LEN($D6)&lt;&gt;17,LEN($D6)-LEN(SUBSTITUTE($D6,":",""))&lt;&gt;5)),AND($E6&lt;&gt;"",OR(LEN($E6)&lt;&gt;17,LEN($E6)-LEN(SUBSTITUTE($E6,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -2583,11 +2616,14 @@
       <c r="J7" s="23" t="n"/>
       <c r="K7" s="23" t="n"/>
       <c r="L7" s="23" t="n"/>
-      <c r="N7">
-        <f>IF(COUNTA($A7:$L7)=0,0,IF(OR($B7="",$D7="",$F7="",$G7=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O7">
+      <c r="M7" s="24" t="n"/>
+      <c r="N7" s="24" t="n"/>
+      <c r="O7" s="24" t="n"/>
+      <c r="P7">
+        <f>IF(COUNTA($A7:$O7)=0,0,IF(OR($B7="",$D7="",$F7="",$G7=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q7">
         <f>IF(OR(AND($D7&lt;&gt;"",OR(LEN($D7)&lt;&gt;17,LEN($D7)-LEN(SUBSTITUTE($D7,":",""))&lt;&gt;5)),AND($E7&lt;&gt;"",OR(LEN($E7)&lt;&gt;17,LEN($E7)-LEN(SUBSTITUTE($E7,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -2605,11 +2641,14 @@
       <c r="J8" s="23" t="n"/>
       <c r="K8" s="23" t="n"/>
       <c r="L8" s="23" t="n"/>
-      <c r="N8">
-        <f>IF(COUNTA($A8:$L8)=0,0,IF(OR($B8="",$D8="",$F8="",$G8=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O8">
+      <c r="M8" s="24" t="n"/>
+      <c r="N8" s="24" t="n"/>
+      <c r="O8" s="24" t="n"/>
+      <c r="P8">
+        <f>IF(COUNTA($A8:$O8)=0,0,IF(OR($B8="",$D8="",$F8="",$G8=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q8">
         <f>IF(OR(AND($D8&lt;&gt;"",OR(LEN($D8)&lt;&gt;17,LEN($D8)-LEN(SUBSTITUTE($D8,":",""))&lt;&gt;5)),AND($E8&lt;&gt;"",OR(LEN($E8)&lt;&gt;17,LEN($E8)-LEN(SUBSTITUTE($E8,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -2627,11 +2666,14 @@
       <c r="J9" s="23" t="n"/>
       <c r="K9" s="23" t="n"/>
       <c r="L9" s="23" t="n"/>
-      <c r="N9">
-        <f>IF(COUNTA($A9:$L9)=0,0,IF(OR($B9="",$D9="",$F9="",$G9=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O9">
+      <c r="M9" s="24" t="n"/>
+      <c r="N9" s="24" t="n"/>
+      <c r="O9" s="24" t="n"/>
+      <c r="P9">
+        <f>IF(COUNTA($A9:$O9)=0,0,IF(OR($B9="",$D9="",$F9="",$G9=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q9">
         <f>IF(OR(AND($D9&lt;&gt;"",OR(LEN($D9)&lt;&gt;17,LEN($D9)-LEN(SUBSTITUTE($D9,":",""))&lt;&gt;5)),AND($E9&lt;&gt;"",OR(LEN($E9)&lt;&gt;17,LEN($E9)-LEN(SUBSTITUTE($E9,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -2649,11 +2691,14 @@
       <c r="J10" s="23" t="n"/>
       <c r="K10" s="23" t="n"/>
       <c r="L10" s="23" t="n"/>
-      <c r="N10">
-        <f>IF(COUNTA($A10:$L10)=0,0,IF(OR($B10="",$D10="",$F10="",$G10=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O10">
+      <c r="M10" s="24" t="n"/>
+      <c r="N10" s="24" t="n"/>
+      <c r="O10" s="24" t="n"/>
+      <c r="P10">
+        <f>IF(COUNTA($A10:$O10)=0,0,IF(OR($B10="",$D10="",$F10="",$G10=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q10">
         <f>IF(OR(AND($D10&lt;&gt;"",OR(LEN($D10)&lt;&gt;17,LEN($D10)-LEN(SUBSTITUTE($D10,":",""))&lt;&gt;5)),AND($E10&lt;&gt;"",OR(LEN($E10)&lt;&gt;17,LEN($E10)-LEN(SUBSTITUTE($E10,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -2671,11 +2716,14 @@
       <c r="J11" s="23" t="n"/>
       <c r="K11" s="23" t="n"/>
       <c r="L11" s="23" t="n"/>
-      <c r="N11">
-        <f>IF(COUNTA($A11:$L11)=0,0,IF(OR($B11="",$D11="",$F11="",$G11=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O11">
+      <c r="M11" s="24" t="n"/>
+      <c r="N11" s="24" t="n"/>
+      <c r="O11" s="24" t="n"/>
+      <c r="P11">
+        <f>IF(COUNTA($A11:$O11)=0,0,IF(OR($B11="",$D11="",$F11="",$G11=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q11">
         <f>IF(OR(AND($D11&lt;&gt;"",OR(LEN($D11)&lt;&gt;17,LEN($D11)-LEN(SUBSTITUTE($D11,":",""))&lt;&gt;5)),AND($E11&lt;&gt;"",OR(LEN($E11)&lt;&gt;17,LEN($E11)-LEN(SUBSTITUTE($E11,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -2693,11 +2741,14 @@
       <c r="J12" s="23" t="n"/>
       <c r="K12" s="23" t="n"/>
       <c r="L12" s="23" t="n"/>
-      <c r="N12">
-        <f>IF(COUNTA($A12:$L12)=0,0,IF(OR($B12="",$D12="",$F12="",$G12=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O12">
+      <c r="M12" s="24" t="n"/>
+      <c r="N12" s="24" t="n"/>
+      <c r="O12" s="24" t="n"/>
+      <c r="P12">
+        <f>IF(COUNTA($A12:$O12)=0,0,IF(OR($B12="",$D12="",$F12="",$G12=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q12">
         <f>IF(OR(AND($D12&lt;&gt;"",OR(LEN($D12)&lt;&gt;17,LEN($D12)-LEN(SUBSTITUTE($D12,":",""))&lt;&gt;5)),AND($E12&lt;&gt;"",OR(LEN($E12)&lt;&gt;17,LEN($E12)-LEN(SUBSTITUTE($E12,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -2715,11 +2766,14 @@
       <c r="J13" s="23" t="n"/>
       <c r="K13" s="23" t="n"/>
       <c r="L13" s="23" t="n"/>
-      <c r="N13">
-        <f>IF(COUNTA($A13:$L13)=0,0,IF(OR($B13="",$D13="",$F13="",$G13=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O13">
+      <c r="M13" s="24" t="n"/>
+      <c r="N13" s="24" t="n"/>
+      <c r="O13" s="24" t="n"/>
+      <c r="P13">
+        <f>IF(COUNTA($A13:$O13)=0,0,IF(OR($B13="",$D13="",$F13="",$G13=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q13">
         <f>IF(OR(AND($D13&lt;&gt;"",OR(LEN($D13)&lt;&gt;17,LEN($D13)-LEN(SUBSTITUTE($D13,":",""))&lt;&gt;5)),AND($E13&lt;&gt;"",OR(LEN($E13)&lt;&gt;17,LEN($E13)-LEN(SUBSTITUTE($E13,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -2737,11 +2791,14 @@
       <c r="J14" s="23" t="n"/>
       <c r="K14" s="23" t="n"/>
       <c r="L14" s="23" t="n"/>
-      <c r="N14">
-        <f>IF(COUNTA($A14:$L14)=0,0,IF(OR($B14="",$D14="",$F14="",$G14=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O14">
+      <c r="M14" s="24" t="n"/>
+      <c r="N14" s="24" t="n"/>
+      <c r="O14" s="24" t="n"/>
+      <c r="P14">
+        <f>IF(COUNTA($A14:$O14)=0,0,IF(OR($B14="",$D14="",$F14="",$G14=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q14">
         <f>IF(OR(AND($D14&lt;&gt;"",OR(LEN($D14)&lt;&gt;17,LEN($D14)-LEN(SUBSTITUTE($D14,":",""))&lt;&gt;5)),AND($E14&lt;&gt;"",OR(LEN($E14)&lt;&gt;17,LEN($E14)-LEN(SUBSTITUTE($E14,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -2759,11 +2816,14 @@
       <c r="J15" s="23" t="n"/>
       <c r="K15" s="23" t="n"/>
       <c r="L15" s="23" t="n"/>
-      <c r="N15">
-        <f>IF(COUNTA($A15:$L15)=0,0,IF(OR($B15="",$D15="",$F15="",$G15=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O15">
+      <c r="M15" s="24" t="n"/>
+      <c r="N15" s="24" t="n"/>
+      <c r="O15" s="24" t="n"/>
+      <c r="P15">
+        <f>IF(COUNTA($A15:$O15)=0,0,IF(OR($B15="",$D15="",$F15="",$G15=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q15">
         <f>IF(OR(AND($D15&lt;&gt;"",OR(LEN($D15)&lt;&gt;17,LEN($D15)-LEN(SUBSTITUTE($D15,":",""))&lt;&gt;5)),AND($E15&lt;&gt;"",OR(LEN($E15)&lt;&gt;17,LEN($E15)-LEN(SUBSTITUTE($E15,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -2781,11 +2841,14 @@
       <c r="J16" s="23" t="n"/>
       <c r="K16" s="23" t="n"/>
       <c r="L16" s="23" t="n"/>
-      <c r="N16">
-        <f>IF(COUNTA($A16:$L16)=0,0,IF(OR($B16="",$D16="",$F16="",$G16=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O16">
+      <c r="M16" s="24" t="n"/>
+      <c r="N16" s="24" t="n"/>
+      <c r="O16" s="24" t="n"/>
+      <c r="P16">
+        <f>IF(COUNTA($A16:$O16)=0,0,IF(OR($B16="",$D16="",$F16="",$G16=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q16">
         <f>IF(OR(AND($D16&lt;&gt;"",OR(LEN($D16)&lt;&gt;17,LEN($D16)-LEN(SUBSTITUTE($D16,":",""))&lt;&gt;5)),AND($E16&lt;&gt;"",OR(LEN($E16)&lt;&gt;17,LEN($E16)-LEN(SUBSTITUTE($E16,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -2803,11 +2866,14 @@
       <c r="J17" s="23" t="n"/>
       <c r="K17" s="23" t="n"/>
       <c r="L17" s="23" t="n"/>
-      <c r="N17">
-        <f>IF(COUNTA($A17:$L17)=0,0,IF(OR($B17="",$D17="",$F17="",$G17=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O17">
+      <c r="M17" s="24" t="n"/>
+      <c r="N17" s="24" t="n"/>
+      <c r="O17" s="24" t="n"/>
+      <c r="P17">
+        <f>IF(COUNTA($A17:$O17)=0,0,IF(OR($B17="",$D17="",$F17="",$G17=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q17">
         <f>IF(OR(AND($D17&lt;&gt;"",OR(LEN($D17)&lt;&gt;17,LEN($D17)-LEN(SUBSTITUTE($D17,":",""))&lt;&gt;5)),AND($E17&lt;&gt;"",OR(LEN($E17)&lt;&gt;17,LEN($E17)-LEN(SUBSTITUTE($E17,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -2825,11 +2891,14 @@
       <c r="J18" s="23" t="n"/>
       <c r="K18" s="23" t="n"/>
       <c r="L18" s="23" t="n"/>
-      <c r="N18">
-        <f>IF(COUNTA($A18:$L18)=0,0,IF(OR($B18="",$D18="",$F18="",$G18=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O18">
+      <c r="M18" s="24" t="n"/>
+      <c r="N18" s="24" t="n"/>
+      <c r="O18" s="24" t="n"/>
+      <c r="P18">
+        <f>IF(COUNTA($A18:$O18)=0,0,IF(OR($B18="",$D18="",$F18="",$G18=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q18">
         <f>IF(OR(AND($D18&lt;&gt;"",OR(LEN($D18)&lt;&gt;17,LEN($D18)-LEN(SUBSTITUTE($D18,":",""))&lt;&gt;5)),AND($E18&lt;&gt;"",OR(LEN($E18)&lt;&gt;17,LEN($E18)-LEN(SUBSTITUTE($E18,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -2847,11 +2916,14 @@
       <c r="J19" s="23" t="n"/>
       <c r="K19" s="23" t="n"/>
       <c r="L19" s="23" t="n"/>
-      <c r="N19">
-        <f>IF(COUNTA($A19:$L19)=0,0,IF(OR($B19="",$D19="",$F19="",$G19=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O19">
+      <c r="M19" s="24" t="n"/>
+      <c r="N19" s="24" t="n"/>
+      <c r="O19" s="24" t="n"/>
+      <c r="P19">
+        <f>IF(COUNTA($A19:$O19)=0,0,IF(OR($B19="",$D19="",$F19="",$G19=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q19">
         <f>IF(OR(AND($D19&lt;&gt;"",OR(LEN($D19)&lt;&gt;17,LEN($D19)-LEN(SUBSTITUTE($D19,":",""))&lt;&gt;5)),AND($E19&lt;&gt;"",OR(LEN($E19)&lt;&gt;17,LEN($E19)-LEN(SUBSTITUTE($E19,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -2869,11 +2941,14 @@
       <c r="J20" s="23" t="n"/>
       <c r="K20" s="23" t="n"/>
       <c r="L20" s="23" t="n"/>
-      <c r="N20">
-        <f>IF(COUNTA($A20:$L20)=0,0,IF(OR($B20="",$D20="",$F20="",$G20=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O20">
+      <c r="M20" s="24" t="n"/>
+      <c r="N20" s="24" t="n"/>
+      <c r="O20" s="24" t="n"/>
+      <c r="P20">
+        <f>IF(COUNTA($A20:$O20)=0,0,IF(OR($B20="",$D20="",$F20="",$G20=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q20">
         <f>IF(OR(AND($D20&lt;&gt;"",OR(LEN($D20)&lt;&gt;17,LEN($D20)-LEN(SUBSTITUTE($D20,":",""))&lt;&gt;5)),AND($E20&lt;&gt;"",OR(LEN($E20)&lt;&gt;17,LEN($E20)-LEN(SUBSTITUTE($E20,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -2891,11 +2966,14 @@
       <c r="J21" s="23" t="n"/>
       <c r="K21" s="23" t="n"/>
       <c r="L21" s="23" t="n"/>
-      <c r="N21">
-        <f>IF(COUNTA($A21:$L21)=0,0,IF(OR($B21="",$D21="",$F21="",$G21=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O21">
+      <c r="M21" s="24" t="n"/>
+      <c r="N21" s="24" t="n"/>
+      <c r="O21" s="24" t="n"/>
+      <c r="P21">
+        <f>IF(COUNTA($A21:$O21)=0,0,IF(OR($B21="",$D21="",$F21="",$G21=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q21">
         <f>IF(OR(AND($D21&lt;&gt;"",OR(LEN($D21)&lt;&gt;17,LEN($D21)-LEN(SUBSTITUTE($D21,":",""))&lt;&gt;5)),AND($E21&lt;&gt;"",OR(LEN($E21)&lt;&gt;17,LEN($E21)-LEN(SUBSTITUTE($E21,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -2913,11 +2991,14 @@
       <c r="J22" s="23" t="n"/>
       <c r="K22" s="23" t="n"/>
       <c r="L22" s="23" t="n"/>
-      <c r="N22">
-        <f>IF(COUNTA($A22:$L22)=0,0,IF(OR($B22="",$D22="",$F22="",$G22=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O22">
+      <c r="M22" s="24" t="n"/>
+      <c r="N22" s="24" t="n"/>
+      <c r="O22" s="24" t="n"/>
+      <c r="P22">
+        <f>IF(COUNTA($A22:$O22)=0,0,IF(OR($B22="",$D22="",$F22="",$G22=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q22">
         <f>IF(OR(AND($D22&lt;&gt;"",OR(LEN($D22)&lt;&gt;17,LEN($D22)-LEN(SUBSTITUTE($D22,":",""))&lt;&gt;5)),AND($E22&lt;&gt;"",OR(LEN($E22)&lt;&gt;17,LEN($E22)-LEN(SUBSTITUTE($E22,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -2935,11 +3016,14 @@
       <c r="J23" s="23" t="n"/>
       <c r="K23" s="23" t="n"/>
       <c r="L23" s="23" t="n"/>
-      <c r="N23">
-        <f>IF(COUNTA($A23:$L23)=0,0,IF(OR($B23="",$D23="",$F23="",$G23=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O23">
+      <c r="M23" s="24" t="n"/>
+      <c r="N23" s="24" t="n"/>
+      <c r="O23" s="24" t="n"/>
+      <c r="P23">
+        <f>IF(COUNTA($A23:$O23)=0,0,IF(OR($B23="",$D23="",$F23="",$G23=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q23">
         <f>IF(OR(AND($D23&lt;&gt;"",OR(LEN($D23)&lt;&gt;17,LEN($D23)-LEN(SUBSTITUTE($D23,":",""))&lt;&gt;5)),AND($E23&lt;&gt;"",OR(LEN($E23)&lt;&gt;17,LEN($E23)-LEN(SUBSTITUTE($E23,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -2957,11 +3041,14 @@
       <c r="J24" s="23" t="n"/>
       <c r="K24" s="23" t="n"/>
       <c r="L24" s="23" t="n"/>
-      <c r="N24">
-        <f>IF(COUNTA($A24:$L24)=0,0,IF(OR($B24="",$D24="",$F24="",$G24=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O24">
+      <c r="M24" s="24" t="n"/>
+      <c r="N24" s="24" t="n"/>
+      <c r="O24" s="24" t="n"/>
+      <c r="P24">
+        <f>IF(COUNTA($A24:$O24)=0,0,IF(OR($B24="",$D24="",$F24="",$G24=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q24">
         <f>IF(OR(AND($D24&lt;&gt;"",OR(LEN($D24)&lt;&gt;17,LEN($D24)-LEN(SUBSTITUTE($D24,":",""))&lt;&gt;5)),AND($E24&lt;&gt;"",OR(LEN($E24)&lt;&gt;17,LEN($E24)-LEN(SUBSTITUTE($E24,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -2979,11 +3066,14 @@
       <c r="J25" s="23" t="n"/>
       <c r="K25" s="23" t="n"/>
       <c r="L25" s="23" t="n"/>
-      <c r="N25">
-        <f>IF(COUNTA($A25:$L25)=0,0,IF(OR($B25="",$D25="",$F25="",$G25=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O25">
+      <c r="M25" s="24" t="n"/>
+      <c r="N25" s="24" t="n"/>
+      <c r="O25" s="24" t="n"/>
+      <c r="P25">
+        <f>IF(COUNTA($A25:$O25)=0,0,IF(OR($B25="",$D25="",$F25="",$G25=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q25">
         <f>IF(OR(AND($D25&lt;&gt;"",OR(LEN($D25)&lt;&gt;17,LEN($D25)-LEN(SUBSTITUTE($D25,":",""))&lt;&gt;5)),AND($E25&lt;&gt;"",OR(LEN($E25)&lt;&gt;17,LEN($E25)-LEN(SUBSTITUTE($E25,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3001,11 +3091,14 @@
       <c r="J26" s="23" t="n"/>
       <c r="K26" s="23" t="n"/>
       <c r="L26" s="23" t="n"/>
-      <c r="N26">
-        <f>IF(COUNTA($A26:$L26)=0,0,IF(OR($B26="",$D26="",$F26="",$G26=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O26">
+      <c r="M26" s="24" t="n"/>
+      <c r="N26" s="24" t="n"/>
+      <c r="O26" s="24" t="n"/>
+      <c r="P26">
+        <f>IF(COUNTA($A26:$O26)=0,0,IF(OR($B26="",$D26="",$F26="",$G26=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q26">
         <f>IF(OR(AND($D26&lt;&gt;"",OR(LEN($D26)&lt;&gt;17,LEN($D26)-LEN(SUBSTITUTE($D26,":",""))&lt;&gt;5)),AND($E26&lt;&gt;"",OR(LEN($E26)&lt;&gt;17,LEN($E26)-LEN(SUBSTITUTE($E26,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3023,11 +3116,14 @@
       <c r="J27" s="23" t="n"/>
       <c r="K27" s="23" t="n"/>
       <c r="L27" s="23" t="n"/>
-      <c r="N27">
-        <f>IF(COUNTA($A27:$L27)=0,0,IF(OR($B27="",$D27="",$F27="",$G27=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O27">
+      <c r="M27" s="24" t="n"/>
+      <c r="N27" s="24" t="n"/>
+      <c r="O27" s="24" t="n"/>
+      <c r="P27">
+        <f>IF(COUNTA($A27:$O27)=0,0,IF(OR($B27="",$D27="",$F27="",$G27=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q27">
         <f>IF(OR(AND($D27&lt;&gt;"",OR(LEN($D27)&lt;&gt;17,LEN($D27)-LEN(SUBSTITUTE($D27,":",""))&lt;&gt;5)),AND($E27&lt;&gt;"",OR(LEN($E27)&lt;&gt;17,LEN($E27)-LEN(SUBSTITUTE($E27,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3045,11 +3141,14 @@
       <c r="J28" s="23" t="n"/>
       <c r="K28" s="23" t="n"/>
       <c r="L28" s="23" t="n"/>
-      <c r="N28">
-        <f>IF(COUNTA($A28:$L28)=0,0,IF(OR($B28="",$D28="",$F28="",$G28=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O28">
+      <c r="M28" s="24" t="n"/>
+      <c r="N28" s="24" t="n"/>
+      <c r="O28" s="24" t="n"/>
+      <c r="P28">
+        <f>IF(COUNTA($A28:$O28)=0,0,IF(OR($B28="",$D28="",$F28="",$G28=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q28">
         <f>IF(OR(AND($D28&lt;&gt;"",OR(LEN($D28)&lt;&gt;17,LEN($D28)-LEN(SUBSTITUTE($D28,":",""))&lt;&gt;5)),AND($E28&lt;&gt;"",OR(LEN($E28)&lt;&gt;17,LEN($E28)-LEN(SUBSTITUTE($E28,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3067,11 +3166,14 @@
       <c r="J29" s="23" t="n"/>
       <c r="K29" s="23" t="n"/>
       <c r="L29" s="23" t="n"/>
-      <c r="N29">
-        <f>IF(COUNTA($A29:$L29)=0,0,IF(OR($B29="",$D29="",$F29="",$G29=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O29">
+      <c r="M29" s="24" t="n"/>
+      <c r="N29" s="24" t="n"/>
+      <c r="O29" s="24" t="n"/>
+      <c r="P29">
+        <f>IF(COUNTA($A29:$O29)=0,0,IF(OR($B29="",$D29="",$F29="",$G29=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q29">
         <f>IF(OR(AND($D29&lt;&gt;"",OR(LEN($D29)&lt;&gt;17,LEN($D29)-LEN(SUBSTITUTE($D29,":",""))&lt;&gt;5)),AND($E29&lt;&gt;"",OR(LEN($E29)&lt;&gt;17,LEN($E29)-LEN(SUBSTITUTE($E29,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3089,11 +3191,14 @@
       <c r="J30" s="23" t="n"/>
       <c r="K30" s="23" t="n"/>
       <c r="L30" s="23" t="n"/>
-      <c r="N30">
-        <f>IF(COUNTA($A30:$L30)=0,0,IF(OR($B30="",$D30="",$F30="",$G30=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O30">
+      <c r="M30" s="24" t="n"/>
+      <c r="N30" s="24" t="n"/>
+      <c r="O30" s="24" t="n"/>
+      <c r="P30">
+        <f>IF(COUNTA($A30:$O30)=0,0,IF(OR($B30="",$D30="",$F30="",$G30=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q30">
         <f>IF(OR(AND($D30&lt;&gt;"",OR(LEN($D30)&lt;&gt;17,LEN($D30)-LEN(SUBSTITUTE($D30,":",""))&lt;&gt;5)),AND($E30&lt;&gt;"",OR(LEN($E30)&lt;&gt;17,LEN($E30)-LEN(SUBSTITUTE($E30,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3111,11 +3216,14 @@
       <c r="J31" s="23" t="n"/>
       <c r="K31" s="23" t="n"/>
       <c r="L31" s="23" t="n"/>
-      <c r="N31">
-        <f>IF(COUNTA($A31:$L31)=0,0,IF(OR($B31="",$D31="",$F31="",$G31=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O31">
+      <c r="M31" s="24" t="n"/>
+      <c r="N31" s="24" t="n"/>
+      <c r="O31" s="24" t="n"/>
+      <c r="P31">
+        <f>IF(COUNTA($A31:$O31)=0,0,IF(OR($B31="",$D31="",$F31="",$G31=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q31">
         <f>IF(OR(AND($D31&lt;&gt;"",OR(LEN($D31)&lt;&gt;17,LEN($D31)-LEN(SUBSTITUTE($D31,":",""))&lt;&gt;5)),AND($E31&lt;&gt;"",OR(LEN($E31)&lt;&gt;17,LEN($E31)-LEN(SUBSTITUTE($E31,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3133,11 +3241,14 @@
       <c r="J32" s="23" t="n"/>
       <c r="K32" s="23" t="n"/>
       <c r="L32" s="23" t="n"/>
-      <c r="N32">
-        <f>IF(COUNTA($A32:$L32)=0,0,IF(OR($B32="",$D32="",$F32="",$G32=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O32">
+      <c r="M32" s="24" t="n"/>
+      <c r="N32" s="24" t="n"/>
+      <c r="O32" s="24" t="n"/>
+      <c r="P32">
+        <f>IF(COUNTA($A32:$O32)=0,0,IF(OR($B32="",$D32="",$F32="",$G32=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q32">
         <f>IF(OR(AND($D32&lt;&gt;"",OR(LEN($D32)&lt;&gt;17,LEN($D32)-LEN(SUBSTITUTE($D32,":",""))&lt;&gt;5)),AND($E32&lt;&gt;"",OR(LEN($E32)&lt;&gt;17,LEN($E32)-LEN(SUBSTITUTE($E32,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3155,11 +3266,14 @@
       <c r="J33" s="23" t="n"/>
       <c r="K33" s="23" t="n"/>
       <c r="L33" s="23" t="n"/>
-      <c r="N33">
-        <f>IF(COUNTA($A33:$L33)=0,0,IF(OR($B33="",$D33="",$F33="",$G33=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O33">
+      <c r="M33" s="24" t="n"/>
+      <c r="N33" s="24" t="n"/>
+      <c r="O33" s="24" t="n"/>
+      <c r="P33">
+        <f>IF(COUNTA($A33:$O33)=0,0,IF(OR($B33="",$D33="",$F33="",$G33=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q33">
         <f>IF(OR(AND($D33&lt;&gt;"",OR(LEN($D33)&lt;&gt;17,LEN($D33)-LEN(SUBSTITUTE($D33,":",""))&lt;&gt;5)),AND($E33&lt;&gt;"",OR(LEN($E33)&lt;&gt;17,LEN($E33)-LEN(SUBSTITUTE($E33,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3177,11 +3291,14 @@
       <c r="J34" s="23" t="n"/>
       <c r="K34" s="23" t="n"/>
       <c r="L34" s="23" t="n"/>
-      <c r="N34">
-        <f>IF(COUNTA($A34:$L34)=0,0,IF(OR($B34="",$D34="",$F34="",$G34=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O34">
+      <c r="M34" s="24" t="n"/>
+      <c r="N34" s="24" t="n"/>
+      <c r="O34" s="24" t="n"/>
+      <c r="P34">
+        <f>IF(COUNTA($A34:$O34)=0,0,IF(OR($B34="",$D34="",$F34="",$G34=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q34">
         <f>IF(OR(AND($D34&lt;&gt;"",OR(LEN($D34)&lt;&gt;17,LEN($D34)-LEN(SUBSTITUTE($D34,":",""))&lt;&gt;5)),AND($E34&lt;&gt;"",OR(LEN($E34)&lt;&gt;17,LEN($E34)-LEN(SUBSTITUTE($E34,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3199,11 +3316,14 @@
       <c r="J35" s="23" t="n"/>
       <c r="K35" s="23" t="n"/>
       <c r="L35" s="23" t="n"/>
-      <c r="N35">
-        <f>IF(COUNTA($A35:$L35)=0,0,IF(OR($B35="",$D35="",$F35="",$G35=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O35">
+      <c r="M35" s="24" t="n"/>
+      <c r="N35" s="24" t="n"/>
+      <c r="O35" s="24" t="n"/>
+      <c r="P35">
+        <f>IF(COUNTA($A35:$O35)=0,0,IF(OR($B35="",$D35="",$F35="",$G35=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q35">
         <f>IF(OR(AND($D35&lt;&gt;"",OR(LEN($D35)&lt;&gt;17,LEN($D35)-LEN(SUBSTITUTE($D35,":",""))&lt;&gt;5)),AND($E35&lt;&gt;"",OR(LEN($E35)&lt;&gt;17,LEN($E35)-LEN(SUBSTITUTE($E35,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3221,11 +3341,14 @@
       <c r="J36" s="23" t="n"/>
       <c r="K36" s="23" t="n"/>
       <c r="L36" s="23" t="n"/>
-      <c r="N36">
-        <f>IF(COUNTA($A36:$L36)=0,0,IF(OR($B36="",$D36="",$F36="",$G36=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O36">
+      <c r="M36" s="24" t="n"/>
+      <c r="N36" s="24" t="n"/>
+      <c r="O36" s="24" t="n"/>
+      <c r="P36">
+        <f>IF(COUNTA($A36:$O36)=0,0,IF(OR($B36="",$D36="",$F36="",$G36=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q36">
         <f>IF(OR(AND($D36&lt;&gt;"",OR(LEN($D36)&lt;&gt;17,LEN($D36)-LEN(SUBSTITUTE($D36,":",""))&lt;&gt;5)),AND($E36&lt;&gt;"",OR(LEN($E36)&lt;&gt;17,LEN($E36)-LEN(SUBSTITUTE($E36,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3243,11 +3366,14 @@
       <c r="J37" s="23" t="n"/>
       <c r="K37" s="23" t="n"/>
       <c r="L37" s="23" t="n"/>
-      <c r="N37">
-        <f>IF(COUNTA($A37:$L37)=0,0,IF(OR($B37="",$D37="",$F37="",$G37=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O37">
+      <c r="M37" s="24" t="n"/>
+      <c r="N37" s="24" t="n"/>
+      <c r="O37" s="24" t="n"/>
+      <c r="P37">
+        <f>IF(COUNTA($A37:$O37)=0,0,IF(OR($B37="",$D37="",$F37="",$G37=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q37">
         <f>IF(OR(AND($D37&lt;&gt;"",OR(LEN($D37)&lt;&gt;17,LEN($D37)-LEN(SUBSTITUTE($D37,":",""))&lt;&gt;5)),AND($E37&lt;&gt;"",OR(LEN($E37)&lt;&gt;17,LEN($E37)-LEN(SUBSTITUTE($E37,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3265,11 +3391,14 @@
       <c r="J38" s="23" t="n"/>
       <c r="K38" s="23" t="n"/>
       <c r="L38" s="23" t="n"/>
-      <c r="N38">
-        <f>IF(COUNTA($A38:$L38)=0,0,IF(OR($B38="",$D38="",$F38="",$G38=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O38">
+      <c r="M38" s="24" t="n"/>
+      <c r="N38" s="24" t="n"/>
+      <c r="O38" s="24" t="n"/>
+      <c r="P38">
+        <f>IF(COUNTA($A38:$O38)=0,0,IF(OR($B38="",$D38="",$F38="",$G38=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q38">
         <f>IF(OR(AND($D38&lt;&gt;"",OR(LEN($D38)&lt;&gt;17,LEN($D38)-LEN(SUBSTITUTE($D38,":",""))&lt;&gt;5)),AND($E38&lt;&gt;"",OR(LEN($E38)&lt;&gt;17,LEN($E38)-LEN(SUBSTITUTE($E38,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3287,11 +3416,14 @@
       <c r="J39" s="23" t="n"/>
       <c r="K39" s="23" t="n"/>
       <c r="L39" s="23" t="n"/>
-      <c r="N39">
-        <f>IF(COUNTA($A39:$L39)=0,0,IF(OR($B39="",$D39="",$F39="",$G39=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O39">
+      <c r="M39" s="24" t="n"/>
+      <c r="N39" s="24" t="n"/>
+      <c r="O39" s="24" t="n"/>
+      <c r="P39">
+        <f>IF(COUNTA($A39:$O39)=0,0,IF(OR($B39="",$D39="",$F39="",$G39=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q39">
         <f>IF(OR(AND($D39&lt;&gt;"",OR(LEN($D39)&lt;&gt;17,LEN($D39)-LEN(SUBSTITUTE($D39,":",""))&lt;&gt;5)),AND($E39&lt;&gt;"",OR(LEN($E39)&lt;&gt;17,LEN($E39)-LEN(SUBSTITUTE($E39,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3309,11 +3441,14 @@
       <c r="J40" s="23" t="n"/>
       <c r="K40" s="23" t="n"/>
       <c r="L40" s="23" t="n"/>
-      <c r="N40">
-        <f>IF(COUNTA($A40:$L40)=0,0,IF(OR($B40="",$D40="",$F40="",$G40=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O40">
+      <c r="M40" s="24" t="n"/>
+      <c r="N40" s="24" t="n"/>
+      <c r="O40" s="24" t="n"/>
+      <c r="P40">
+        <f>IF(COUNTA($A40:$O40)=0,0,IF(OR($B40="",$D40="",$F40="",$G40=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q40">
         <f>IF(OR(AND($D40&lt;&gt;"",OR(LEN($D40)&lt;&gt;17,LEN($D40)-LEN(SUBSTITUTE($D40,":",""))&lt;&gt;5)),AND($E40&lt;&gt;"",OR(LEN($E40)&lt;&gt;17,LEN($E40)-LEN(SUBSTITUTE($E40,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3331,11 +3466,14 @@
       <c r="J41" s="23" t="n"/>
       <c r="K41" s="23" t="n"/>
       <c r="L41" s="23" t="n"/>
-      <c r="N41">
-        <f>IF(COUNTA($A41:$L41)=0,0,IF(OR($B41="",$D41="",$F41="",$G41=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O41">
+      <c r="M41" s="24" t="n"/>
+      <c r="N41" s="24" t="n"/>
+      <c r="O41" s="24" t="n"/>
+      <c r="P41">
+        <f>IF(COUNTA($A41:$O41)=0,0,IF(OR($B41="",$D41="",$F41="",$G41=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q41">
         <f>IF(OR(AND($D41&lt;&gt;"",OR(LEN($D41)&lt;&gt;17,LEN($D41)-LEN(SUBSTITUTE($D41,":",""))&lt;&gt;5)),AND($E41&lt;&gt;"",OR(LEN($E41)&lt;&gt;17,LEN($E41)-LEN(SUBSTITUTE($E41,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3353,11 +3491,14 @@
       <c r="J42" s="24" t="n"/>
       <c r="K42" s="24" t="n"/>
       <c r="L42" s="24" t="n"/>
-      <c r="N42">
-        <f>IF(COUNTA($A42:$L42)=0,0,IF(OR($B42="",$D42="",$F42="",$G42=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O42">
+      <c r="M42" s="24" t="n"/>
+      <c r="N42" s="24" t="n"/>
+      <c r="O42" s="24" t="n"/>
+      <c r="P42">
+        <f>IF(COUNTA($A42:$O42)=0,0,IF(OR($B42="",$D42="",$F42="",$G42=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q42">
         <f>IF(OR(AND($D42&lt;&gt;"",OR(LEN($D42)&lt;&gt;17,LEN($D42)-LEN(SUBSTITUTE($D42,":",""))&lt;&gt;5)),AND($E42&lt;&gt;"",OR(LEN($E42)&lt;&gt;17,LEN($E42)-LEN(SUBSTITUTE($E42,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3375,11 +3516,14 @@
       <c r="J43" s="24" t="n"/>
       <c r="K43" s="24" t="n"/>
       <c r="L43" s="24" t="n"/>
-      <c r="N43">
-        <f>IF(COUNTA($A43:$L43)=0,0,IF(OR($B43="",$D43="",$F43="",$G43=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O43">
+      <c r="M43" s="24" t="n"/>
+      <c r="N43" s="24" t="n"/>
+      <c r="O43" s="24" t="n"/>
+      <c r="P43">
+        <f>IF(COUNTA($A43:$O43)=0,0,IF(OR($B43="",$D43="",$F43="",$G43=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q43">
         <f>IF(OR(AND($D43&lt;&gt;"",OR(LEN($D43)&lt;&gt;17,LEN($D43)-LEN(SUBSTITUTE($D43,":",""))&lt;&gt;5)),AND($E43&lt;&gt;"",OR(LEN($E43)&lt;&gt;17,LEN($E43)-LEN(SUBSTITUTE($E43,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3397,11 +3541,14 @@
       <c r="J44" s="24" t="n"/>
       <c r="K44" s="24" t="n"/>
       <c r="L44" s="24" t="n"/>
-      <c r="N44">
-        <f>IF(COUNTA($A44:$L44)=0,0,IF(OR($B44="",$D44="",$F44="",$G44=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O44">
+      <c r="M44" s="24" t="n"/>
+      <c r="N44" s="24" t="n"/>
+      <c r="O44" s="24" t="n"/>
+      <c r="P44">
+        <f>IF(COUNTA($A44:$O44)=0,0,IF(OR($B44="",$D44="",$F44="",$G44=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q44">
         <f>IF(OR(AND($D44&lt;&gt;"",OR(LEN($D44)&lt;&gt;17,LEN($D44)-LEN(SUBSTITUTE($D44,":",""))&lt;&gt;5)),AND($E44&lt;&gt;"",OR(LEN($E44)&lt;&gt;17,LEN($E44)-LEN(SUBSTITUTE($E44,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3419,11 +3566,14 @@
       <c r="J45" s="24" t="n"/>
       <c r="K45" s="24" t="n"/>
       <c r="L45" s="24" t="n"/>
-      <c r="N45">
-        <f>IF(COUNTA($A45:$L45)=0,0,IF(OR($B45="",$D45="",$F45="",$G45=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O45">
+      <c r="M45" s="24" t="n"/>
+      <c r="N45" s="24" t="n"/>
+      <c r="O45" s="24" t="n"/>
+      <c r="P45">
+        <f>IF(COUNTA($A45:$O45)=0,0,IF(OR($B45="",$D45="",$F45="",$G45=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q45">
         <f>IF(OR(AND($D45&lt;&gt;"",OR(LEN($D45)&lt;&gt;17,LEN($D45)-LEN(SUBSTITUTE($D45,":",""))&lt;&gt;5)),AND($E45&lt;&gt;"",OR(LEN($E45)&lt;&gt;17,LEN($E45)-LEN(SUBSTITUTE($E45,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3441,11 +3591,14 @@
       <c r="J46" s="24" t="n"/>
       <c r="K46" s="24" t="n"/>
       <c r="L46" s="24" t="n"/>
-      <c r="N46">
-        <f>IF(COUNTA($A46:$L46)=0,0,IF(OR($B46="",$D46="",$F46="",$G46=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O46">
+      <c r="M46" s="24" t="n"/>
+      <c r="N46" s="24" t="n"/>
+      <c r="O46" s="24" t="n"/>
+      <c r="P46">
+        <f>IF(COUNTA($A46:$O46)=0,0,IF(OR($B46="",$D46="",$F46="",$G46=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q46">
         <f>IF(OR(AND($D46&lt;&gt;"",OR(LEN($D46)&lt;&gt;17,LEN($D46)-LEN(SUBSTITUTE($D46,":",""))&lt;&gt;5)),AND($E46&lt;&gt;"",OR(LEN($E46)&lt;&gt;17,LEN($E46)-LEN(SUBSTITUTE($E46,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3463,11 +3616,14 @@
       <c r="J47" s="24" t="n"/>
       <c r="K47" s="24" t="n"/>
       <c r="L47" s="24" t="n"/>
-      <c r="N47">
-        <f>IF(COUNTA($A47:$L47)=0,0,IF(OR($B47="",$D47="",$F47="",$G47=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O47">
+      <c r="M47" s="24" t="n"/>
+      <c r="N47" s="24" t="n"/>
+      <c r="O47" s="24" t="n"/>
+      <c r="P47">
+        <f>IF(COUNTA($A47:$O47)=0,0,IF(OR($B47="",$D47="",$F47="",$G47=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q47">
         <f>IF(OR(AND($D47&lt;&gt;"",OR(LEN($D47)&lt;&gt;17,LEN($D47)-LEN(SUBSTITUTE($D47,":",""))&lt;&gt;5)),AND($E47&lt;&gt;"",OR(LEN($E47)&lt;&gt;17,LEN($E47)-LEN(SUBSTITUTE($E47,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3485,11 +3641,14 @@
       <c r="J48" s="24" t="n"/>
       <c r="K48" s="24" t="n"/>
       <c r="L48" s="24" t="n"/>
-      <c r="N48">
-        <f>IF(COUNTA($A48:$L48)=0,0,IF(OR($B48="",$D48="",$F48="",$G48=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O48">
+      <c r="M48" s="24" t="n"/>
+      <c r="N48" s="24" t="n"/>
+      <c r="O48" s="24" t="n"/>
+      <c r="P48">
+        <f>IF(COUNTA($A48:$O48)=0,0,IF(OR($B48="",$D48="",$F48="",$G48=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q48">
         <f>IF(OR(AND($D48&lt;&gt;"",OR(LEN($D48)&lt;&gt;17,LEN($D48)-LEN(SUBSTITUTE($D48,":",""))&lt;&gt;5)),AND($E48&lt;&gt;"",OR(LEN($E48)&lt;&gt;17,LEN($E48)-LEN(SUBSTITUTE($E48,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3507,11 +3666,14 @@
       <c r="J49" s="24" t="n"/>
       <c r="K49" s="24" t="n"/>
       <c r="L49" s="24" t="n"/>
-      <c r="N49">
-        <f>IF(COUNTA($A49:$L49)=0,0,IF(OR($B49="",$D49="",$F49="",$G49=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O49">
+      <c r="M49" s="24" t="n"/>
+      <c r="N49" s="24" t="n"/>
+      <c r="O49" s="24" t="n"/>
+      <c r="P49">
+        <f>IF(COUNTA($A49:$O49)=0,0,IF(OR($B49="",$D49="",$F49="",$G49=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q49">
         <f>IF(OR(AND($D49&lt;&gt;"",OR(LEN($D49)&lt;&gt;17,LEN($D49)-LEN(SUBSTITUTE($D49,":",""))&lt;&gt;5)),AND($E49&lt;&gt;"",OR(LEN($E49)&lt;&gt;17,LEN($E49)-LEN(SUBSTITUTE($E49,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3529,11 +3691,14 @@
       <c r="J50" s="24" t="n"/>
       <c r="K50" s="24" t="n"/>
       <c r="L50" s="24" t="n"/>
-      <c r="N50">
-        <f>IF(COUNTA($A50:$L50)=0,0,IF(OR($B50="",$D50="",$F50="",$G50=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O50">
+      <c r="M50" s="24" t="n"/>
+      <c r="N50" s="24" t="n"/>
+      <c r="O50" s="24" t="n"/>
+      <c r="P50">
+        <f>IF(COUNTA($A50:$O50)=0,0,IF(OR($B50="",$D50="",$F50="",$G50=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q50">
         <f>IF(OR(AND($D50&lt;&gt;"",OR(LEN($D50)&lt;&gt;17,LEN($D50)-LEN(SUBSTITUTE($D50,":",""))&lt;&gt;5)),AND($E50&lt;&gt;"",OR(LEN($E50)&lt;&gt;17,LEN($E50)-LEN(SUBSTITUTE($E50,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3551,11 +3716,14 @@
       <c r="J51" s="24" t="n"/>
       <c r="K51" s="24" t="n"/>
       <c r="L51" s="24" t="n"/>
-      <c r="N51">
-        <f>IF(COUNTA($A51:$L51)=0,0,IF(OR($B51="",$D51="",$F51="",$G51=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O51">
+      <c r="M51" s="24" t="n"/>
+      <c r="N51" s="24" t="n"/>
+      <c r="O51" s="24" t="n"/>
+      <c r="P51">
+        <f>IF(COUNTA($A51:$O51)=0,0,IF(OR($B51="",$D51="",$F51="",$G51=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q51">
         <f>IF(OR(AND($D51&lt;&gt;"",OR(LEN($D51)&lt;&gt;17,LEN($D51)-LEN(SUBSTITUTE($D51,":",""))&lt;&gt;5)),AND($E51&lt;&gt;"",OR(LEN($E51)&lt;&gt;17,LEN($E51)-LEN(SUBSTITUTE($E51,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3573,11 +3741,14 @@
       <c r="J52" s="24" t="n"/>
       <c r="K52" s="24" t="n"/>
       <c r="L52" s="24" t="n"/>
-      <c r="N52">
-        <f>IF(COUNTA($A52:$L52)=0,0,IF(OR($B52="",$D52="",$F52="",$G52=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O52">
+      <c r="M52" s="24" t="n"/>
+      <c r="N52" s="24" t="n"/>
+      <c r="O52" s="24" t="n"/>
+      <c r="P52">
+        <f>IF(COUNTA($A52:$O52)=0,0,IF(OR($B52="",$D52="",$F52="",$G52=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q52">
         <f>IF(OR(AND($D52&lt;&gt;"",OR(LEN($D52)&lt;&gt;17,LEN($D52)-LEN(SUBSTITUTE($D52,":",""))&lt;&gt;5)),AND($E52&lt;&gt;"",OR(LEN($E52)&lt;&gt;17,LEN($E52)-LEN(SUBSTITUTE($E52,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3595,11 +3766,14 @@
       <c r="J53" s="24" t="n"/>
       <c r="K53" s="24" t="n"/>
       <c r="L53" s="24" t="n"/>
-      <c r="N53">
-        <f>IF(COUNTA($A53:$L53)=0,0,IF(OR($B53="",$D53="",$F53="",$G53=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O53">
+      <c r="M53" s="24" t="n"/>
+      <c r="N53" s="24" t="n"/>
+      <c r="O53" s="24" t="n"/>
+      <c r="P53">
+        <f>IF(COUNTA($A53:$O53)=0,0,IF(OR($B53="",$D53="",$F53="",$G53=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q53">
         <f>IF(OR(AND($D53&lt;&gt;"",OR(LEN($D53)&lt;&gt;17,LEN($D53)-LEN(SUBSTITUTE($D53,":",""))&lt;&gt;5)),AND($E53&lt;&gt;"",OR(LEN($E53)&lt;&gt;17,LEN($E53)-LEN(SUBSTITUTE($E53,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3617,11 +3791,14 @@
       <c r="J54" s="24" t="n"/>
       <c r="K54" s="24" t="n"/>
       <c r="L54" s="24" t="n"/>
-      <c r="N54">
-        <f>IF(COUNTA($A54:$L54)=0,0,IF(OR($B54="",$D54="",$F54="",$G54=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O54">
+      <c r="M54" s="24" t="n"/>
+      <c r="N54" s="24" t="n"/>
+      <c r="O54" s="24" t="n"/>
+      <c r="P54">
+        <f>IF(COUNTA($A54:$O54)=0,0,IF(OR($B54="",$D54="",$F54="",$G54=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q54">
         <f>IF(OR(AND($D54&lt;&gt;"",OR(LEN($D54)&lt;&gt;17,LEN($D54)-LEN(SUBSTITUTE($D54,":",""))&lt;&gt;5)),AND($E54&lt;&gt;"",OR(LEN($E54)&lt;&gt;17,LEN($E54)-LEN(SUBSTITUTE($E54,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3639,11 +3816,14 @@
       <c r="J55" s="24" t="n"/>
       <c r="K55" s="24" t="n"/>
       <c r="L55" s="24" t="n"/>
-      <c r="N55">
-        <f>IF(COUNTA($A55:$L55)=0,0,IF(OR($B55="",$D55="",$F55="",$G55=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O55">
+      <c r="M55" s="24" t="n"/>
+      <c r="N55" s="24" t="n"/>
+      <c r="O55" s="24" t="n"/>
+      <c r="P55">
+        <f>IF(COUNTA($A55:$O55)=0,0,IF(OR($B55="",$D55="",$F55="",$G55=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q55">
         <f>IF(OR(AND($D55&lt;&gt;"",OR(LEN($D55)&lt;&gt;17,LEN($D55)-LEN(SUBSTITUTE($D55,":",""))&lt;&gt;5)),AND($E55&lt;&gt;"",OR(LEN($E55)&lt;&gt;17,LEN($E55)-LEN(SUBSTITUTE($E55,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3661,11 +3841,14 @@
       <c r="J56" s="24" t="n"/>
       <c r="K56" s="24" t="n"/>
       <c r="L56" s="24" t="n"/>
-      <c r="N56">
-        <f>IF(COUNTA($A56:$L56)=0,0,IF(OR($B56="",$D56="",$F56="",$G56=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O56">
+      <c r="M56" s="24" t="n"/>
+      <c r="N56" s="24" t="n"/>
+      <c r="O56" s="24" t="n"/>
+      <c r="P56">
+        <f>IF(COUNTA($A56:$O56)=0,0,IF(OR($B56="",$D56="",$F56="",$G56=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q56">
         <f>IF(OR(AND($D56&lt;&gt;"",OR(LEN($D56)&lt;&gt;17,LEN($D56)-LEN(SUBSTITUTE($D56,":",""))&lt;&gt;5)),AND($E56&lt;&gt;"",OR(LEN($E56)&lt;&gt;17,LEN($E56)-LEN(SUBSTITUTE($E56,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3683,11 +3866,14 @@
       <c r="J57" s="24" t="n"/>
       <c r="K57" s="24" t="n"/>
       <c r="L57" s="24" t="n"/>
-      <c r="N57">
-        <f>IF(COUNTA($A57:$L57)=0,0,IF(OR($B57="",$D57="",$F57="",$G57=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O57">
+      <c r="M57" s="24" t="n"/>
+      <c r="N57" s="24" t="n"/>
+      <c r="O57" s="24" t="n"/>
+      <c r="P57">
+        <f>IF(COUNTA($A57:$O57)=0,0,IF(OR($B57="",$D57="",$F57="",$G57=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q57">
         <f>IF(OR(AND($D57&lt;&gt;"",OR(LEN($D57)&lt;&gt;17,LEN($D57)-LEN(SUBSTITUTE($D57,":",""))&lt;&gt;5)),AND($E57&lt;&gt;"",OR(LEN($E57)&lt;&gt;17,LEN($E57)-LEN(SUBSTITUTE($E57,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3705,11 +3891,14 @@
       <c r="J58" s="24" t="n"/>
       <c r="K58" s="24" t="n"/>
       <c r="L58" s="24" t="n"/>
-      <c r="N58">
-        <f>IF(COUNTA($A58:$L58)=0,0,IF(OR($B58="",$D58="",$F58="",$G58=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O58">
+      <c r="M58" s="24" t="n"/>
+      <c r="N58" s="24" t="n"/>
+      <c r="O58" s="24" t="n"/>
+      <c r="P58">
+        <f>IF(COUNTA($A58:$O58)=0,0,IF(OR($B58="",$D58="",$F58="",$G58=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q58">
         <f>IF(OR(AND($D58&lt;&gt;"",OR(LEN($D58)&lt;&gt;17,LEN($D58)-LEN(SUBSTITUTE($D58,":",""))&lt;&gt;5)),AND($E58&lt;&gt;"",OR(LEN($E58)&lt;&gt;17,LEN($E58)-LEN(SUBSTITUTE($E58,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3727,11 +3916,14 @@
       <c r="J59" s="24" t="n"/>
       <c r="K59" s="24" t="n"/>
       <c r="L59" s="24" t="n"/>
-      <c r="N59">
-        <f>IF(COUNTA($A59:$L59)=0,0,IF(OR($B59="",$D59="",$F59="",$G59=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O59">
+      <c r="M59" s="24" t="n"/>
+      <c r="N59" s="24" t="n"/>
+      <c r="O59" s="24" t="n"/>
+      <c r="P59">
+        <f>IF(COUNTA($A59:$O59)=0,0,IF(OR($B59="",$D59="",$F59="",$G59=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q59">
         <f>IF(OR(AND($D59&lt;&gt;"",OR(LEN($D59)&lt;&gt;17,LEN($D59)-LEN(SUBSTITUTE($D59,":",""))&lt;&gt;5)),AND($E59&lt;&gt;"",OR(LEN($E59)&lt;&gt;17,LEN($E59)-LEN(SUBSTITUTE($E59,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3749,11 +3941,14 @@
       <c r="J60" s="24" t="n"/>
       <c r="K60" s="24" t="n"/>
       <c r="L60" s="24" t="n"/>
-      <c r="N60">
-        <f>IF(COUNTA($A60:$L60)=0,0,IF(OR($B60="",$D60="",$F60="",$G60=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O60">
+      <c r="M60" s="24" t="n"/>
+      <c r="N60" s="24" t="n"/>
+      <c r="O60" s="24" t="n"/>
+      <c r="P60">
+        <f>IF(COUNTA($A60:$O60)=0,0,IF(OR($B60="",$D60="",$F60="",$G60=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q60">
         <f>IF(OR(AND($D60&lt;&gt;"",OR(LEN($D60)&lt;&gt;17,LEN($D60)-LEN(SUBSTITUTE($D60,":",""))&lt;&gt;5)),AND($E60&lt;&gt;"",OR(LEN($E60)&lt;&gt;17,LEN($E60)-LEN(SUBSTITUTE($E60,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3771,11 +3966,14 @@
       <c r="J61" s="24" t="n"/>
       <c r="K61" s="24" t="n"/>
       <c r="L61" s="24" t="n"/>
-      <c r="N61">
-        <f>IF(COUNTA($A61:$L61)=0,0,IF(OR($B61="",$D61="",$F61="",$G61=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O61">
+      <c r="M61" s="24" t="n"/>
+      <c r="N61" s="24" t="n"/>
+      <c r="O61" s="24" t="n"/>
+      <c r="P61">
+        <f>IF(COUNTA($A61:$O61)=0,0,IF(OR($B61="",$D61="",$F61="",$G61=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q61">
         <f>IF(OR(AND($D61&lt;&gt;"",OR(LEN($D61)&lt;&gt;17,LEN($D61)-LEN(SUBSTITUTE($D61,":",""))&lt;&gt;5)),AND($E61&lt;&gt;"",OR(LEN($E61)&lt;&gt;17,LEN($E61)-LEN(SUBSTITUTE($E61,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3793,11 +3991,14 @@
       <c r="J62" s="24" t="n"/>
       <c r="K62" s="24" t="n"/>
       <c r="L62" s="24" t="n"/>
-      <c r="N62">
-        <f>IF(COUNTA($A62:$L62)=0,0,IF(OR($B62="",$D62="",$F62="",$G62=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O62">
+      <c r="M62" s="24" t="n"/>
+      <c r="N62" s="24" t="n"/>
+      <c r="O62" s="24" t="n"/>
+      <c r="P62">
+        <f>IF(COUNTA($A62:$O62)=0,0,IF(OR($B62="",$D62="",$F62="",$G62=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q62">
         <f>IF(OR(AND($D62&lt;&gt;"",OR(LEN($D62)&lt;&gt;17,LEN($D62)-LEN(SUBSTITUTE($D62,":",""))&lt;&gt;5)),AND($E62&lt;&gt;"",OR(LEN($E62)&lt;&gt;17,LEN($E62)-LEN(SUBSTITUTE($E62,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3815,11 +4016,14 @@
       <c r="J63" s="24" t="n"/>
       <c r="K63" s="24" t="n"/>
       <c r="L63" s="24" t="n"/>
-      <c r="N63">
-        <f>IF(COUNTA($A63:$L63)=0,0,IF(OR($B63="",$D63="",$F63="",$G63=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O63">
+      <c r="M63" s="24" t="n"/>
+      <c r="N63" s="24" t="n"/>
+      <c r="O63" s="24" t="n"/>
+      <c r="P63">
+        <f>IF(COUNTA($A63:$O63)=0,0,IF(OR($B63="",$D63="",$F63="",$G63=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q63">
         <f>IF(OR(AND($D63&lt;&gt;"",OR(LEN($D63)&lt;&gt;17,LEN($D63)-LEN(SUBSTITUTE($D63,":",""))&lt;&gt;5)),AND($E63&lt;&gt;"",OR(LEN($E63)&lt;&gt;17,LEN($E63)-LEN(SUBSTITUTE($E63,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3837,11 +4041,14 @@
       <c r="J64" s="24" t="n"/>
       <c r="K64" s="24" t="n"/>
       <c r="L64" s="24" t="n"/>
-      <c r="N64">
-        <f>IF(COUNTA($A64:$L64)=0,0,IF(OR($B64="",$D64="",$F64="",$G64=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O64">
+      <c r="M64" s="24" t="n"/>
+      <c r="N64" s="24" t="n"/>
+      <c r="O64" s="24" t="n"/>
+      <c r="P64">
+        <f>IF(COUNTA($A64:$O64)=0,0,IF(OR($B64="",$D64="",$F64="",$G64=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q64">
         <f>IF(OR(AND($D64&lt;&gt;"",OR(LEN($D64)&lt;&gt;17,LEN($D64)-LEN(SUBSTITUTE($D64,":",""))&lt;&gt;5)),AND($E64&lt;&gt;"",OR(LEN($E64)&lt;&gt;17,LEN($E64)-LEN(SUBSTITUTE($E64,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3859,11 +4066,14 @@
       <c r="J65" s="24" t="n"/>
       <c r="K65" s="24" t="n"/>
       <c r="L65" s="24" t="n"/>
-      <c r="N65">
-        <f>IF(COUNTA($A65:$L65)=0,0,IF(OR($B65="",$D65="",$F65="",$G65=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O65">
+      <c r="M65" s="24" t="n"/>
+      <c r="N65" s="24" t="n"/>
+      <c r="O65" s="24" t="n"/>
+      <c r="P65">
+        <f>IF(COUNTA($A65:$O65)=0,0,IF(OR($B65="",$D65="",$F65="",$G65=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q65">
         <f>IF(OR(AND($D65&lt;&gt;"",OR(LEN($D65)&lt;&gt;17,LEN($D65)-LEN(SUBSTITUTE($D65,":",""))&lt;&gt;5)),AND($E65&lt;&gt;"",OR(LEN($E65)&lt;&gt;17,LEN($E65)-LEN(SUBSTITUTE($E65,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3881,11 +4091,14 @@
       <c r="J66" s="24" t="n"/>
       <c r="K66" s="24" t="n"/>
       <c r="L66" s="24" t="n"/>
-      <c r="N66">
-        <f>IF(COUNTA($A66:$L66)=0,0,IF(OR($B66="",$D66="",$F66="",$G66=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O66">
+      <c r="M66" s="24" t="n"/>
+      <c r="N66" s="24" t="n"/>
+      <c r="O66" s="24" t="n"/>
+      <c r="P66">
+        <f>IF(COUNTA($A66:$O66)=0,0,IF(OR($B66="",$D66="",$F66="",$G66=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q66">
         <f>IF(OR(AND($D66&lt;&gt;"",OR(LEN($D66)&lt;&gt;17,LEN($D66)-LEN(SUBSTITUTE($D66,":",""))&lt;&gt;5)),AND($E66&lt;&gt;"",OR(LEN($E66)&lt;&gt;17,LEN($E66)-LEN(SUBSTITUTE($E66,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3903,11 +4116,14 @@
       <c r="J67" s="24" t="n"/>
       <c r="K67" s="24" t="n"/>
       <c r="L67" s="24" t="n"/>
-      <c r="N67">
-        <f>IF(COUNTA($A67:$L67)=0,0,IF(OR($B67="",$D67="",$F67="",$G67=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O67">
+      <c r="M67" s="24" t="n"/>
+      <c r="N67" s="24" t="n"/>
+      <c r="O67" s="24" t="n"/>
+      <c r="P67">
+        <f>IF(COUNTA($A67:$O67)=0,0,IF(OR($B67="",$D67="",$F67="",$G67=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q67">
         <f>IF(OR(AND($D67&lt;&gt;"",OR(LEN($D67)&lt;&gt;17,LEN($D67)-LEN(SUBSTITUTE($D67,":",""))&lt;&gt;5)),AND($E67&lt;&gt;"",OR(LEN($E67)&lt;&gt;17,LEN($E67)-LEN(SUBSTITUTE($E67,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3925,11 +4141,14 @@
       <c r="J68" s="24" t="n"/>
       <c r="K68" s="24" t="n"/>
       <c r="L68" s="24" t="n"/>
-      <c r="N68">
-        <f>IF(COUNTA($A68:$L68)=0,0,IF(OR($B68="",$D68="",$F68="",$G68=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O68">
+      <c r="M68" s="24" t="n"/>
+      <c r="N68" s="24" t="n"/>
+      <c r="O68" s="24" t="n"/>
+      <c r="P68">
+        <f>IF(COUNTA($A68:$O68)=0,0,IF(OR($B68="",$D68="",$F68="",$G68=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q68">
         <f>IF(OR(AND($D68&lt;&gt;"",OR(LEN($D68)&lt;&gt;17,LEN($D68)-LEN(SUBSTITUTE($D68,":",""))&lt;&gt;5)),AND($E68&lt;&gt;"",OR(LEN($E68)&lt;&gt;17,LEN($E68)-LEN(SUBSTITUTE($E68,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3947,11 +4166,14 @@
       <c r="J69" s="24" t="n"/>
       <c r="K69" s="24" t="n"/>
       <c r="L69" s="24" t="n"/>
-      <c r="N69">
-        <f>IF(COUNTA($A69:$L69)=0,0,IF(OR($B69="",$D69="",$F69="",$G69=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O69">
+      <c r="M69" s="24" t="n"/>
+      <c r="N69" s="24" t="n"/>
+      <c r="O69" s="24" t="n"/>
+      <c r="P69">
+        <f>IF(COUNTA($A69:$O69)=0,0,IF(OR($B69="",$D69="",$F69="",$G69=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q69">
         <f>IF(OR(AND($D69&lt;&gt;"",OR(LEN($D69)&lt;&gt;17,LEN($D69)-LEN(SUBSTITUTE($D69,":",""))&lt;&gt;5)),AND($E69&lt;&gt;"",OR(LEN($E69)&lt;&gt;17,LEN($E69)-LEN(SUBSTITUTE($E69,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3969,11 +4191,14 @@
       <c r="J70" s="24" t="n"/>
       <c r="K70" s="24" t="n"/>
       <c r="L70" s="24" t="n"/>
-      <c r="N70">
-        <f>IF(COUNTA($A70:$L70)=0,0,IF(OR($B70="",$D70="",$F70="",$G70=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O70">
+      <c r="M70" s="24" t="n"/>
+      <c r="N70" s="24" t="n"/>
+      <c r="O70" s="24" t="n"/>
+      <c r="P70">
+        <f>IF(COUNTA($A70:$O70)=0,0,IF(OR($B70="",$D70="",$F70="",$G70=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q70">
         <f>IF(OR(AND($D70&lt;&gt;"",OR(LEN($D70)&lt;&gt;17,LEN($D70)-LEN(SUBSTITUTE($D70,":",""))&lt;&gt;5)),AND($E70&lt;&gt;"",OR(LEN($E70)&lt;&gt;17,LEN($E70)-LEN(SUBSTITUTE($E70,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3991,11 +4216,14 @@
       <c r="J71" s="24" t="n"/>
       <c r="K71" s="24" t="n"/>
       <c r="L71" s="24" t="n"/>
-      <c r="N71">
-        <f>IF(COUNTA($A71:$L71)=0,0,IF(OR($B71="",$D71="",$F71="",$G71=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O71">
+      <c r="M71" s="24" t="n"/>
+      <c r="N71" s="24" t="n"/>
+      <c r="O71" s="24" t="n"/>
+      <c r="P71">
+        <f>IF(COUNTA($A71:$O71)=0,0,IF(OR($B71="",$D71="",$F71="",$G71=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q71">
         <f>IF(OR(AND($D71&lt;&gt;"",OR(LEN($D71)&lt;&gt;17,LEN($D71)-LEN(SUBSTITUTE($D71,":",""))&lt;&gt;5)),AND($E71&lt;&gt;"",OR(LEN($E71)&lt;&gt;17,LEN($E71)-LEN(SUBSTITUTE($E71,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4013,11 +4241,14 @@
       <c r="J72" s="24" t="n"/>
       <c r="K72" s="24" t="n"/>
       <c r="L72" s="24" t="n"/>
-      <c r="N72">
-        <f>IF(COUNTA($A72:$L72)=0,0,IF(OR($B72="",$D72="",$F72="",$G72=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O72">
+      <c r="M72" s="24" t="n"/>
+      <c r="N72" s="24" t="n"/>
+      <c r="O72" s="24" t="n"/>
+      <c r="P72">
+        <f>IF(COUNTA($A72:$O72)=0,0,IF(OR($B72="",$D72="",$F72="",$G72=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q72">
         <f>IF(OR(AND($D72&lt;&gt;"",OR(LEN($D72)&lt;&gt;17,LEN($D72)-LEN(SUBSTITUTE($D72,":",""))&lt;&gt;5)),AND($E72&lt;&gt;"",OR(LEN($E72)&lt;&gt;17,LEN($E72)-LEN(SUBSTITUTE($E72,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4035,11 +4266,14 @@
       <c r="J73" s="24" t="n"/>
       <c r="K73" s="24" t="n"/>
       <c r="L73" s="24" t="n"/>
-      <c r="N73">
-        <f>IF(COUNTA($A73:$L73)=0,0,IF(OR($B73="",$D73="",$F73="",$G73=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O73">
+      <c r="M73" s="24" t="n"/>
+      <c r="N73" s="24" t="n"/>
+      <c r="O73" s="24" t="n"/>
+      <c r="P73">
+        <f>IF(COUNTA($A73:$O73)=0,0,IF(OR($B73="",$D73="",$F73="",$G73=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q73">
         <f>IF(OR(AND($D73&lt;&gt;"",OR(LEN($D73)&lt;&gt;17,LEN($D73)-LEN(SUBSTITUTE($D73,":",""))&lt;&gt;5)),AND($E73&lt;&gt;"",OR(LEN($E73)&lt;&gt;17,LEN($E73)-LEN(SUBSTITUTE($E73,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4057,11 +4291,14 @@
       <c r="J74" s="24" t="n"/>
       <c r="K74" s="24" t="n"/>
       <c r="L74" s="24" t="n"/>
-      <c r="N74">
-        <f>IF(COUNTA($A74:$L74)=0,0,IF(OR($B74="",$D74="",$F74="",$G74=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O74">
+      <c r="M74" s="24" t="n"/>
+      <c r="N74" s="24" t="n"/>
+      <c r="O74" s="24" t="n"/>
+      <c r="P74">
+        <f>IF(COUNTA($A74:$O74)=0,0,IF(OR($B74="",$D74="",$F74="",$G74=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q74">
         <f>IF(OR(AND($D74&lt;&gt;"",OR(LEN($D74)&lt;&gt;17,LEN($D74)-LEN(SUBSTITUTE($D74,":",""))&lt;&gt;5)),AND($E74&lt;&gt;"",OR(LEN($E74)&lt;&gt;17,LEN($E74)-LEN(SUBSTITUTE($E74,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4079,11 +4316,14 @@
       <c r="J75" s="24" t="n"/>
       <c r="K75" s="24" t="n"/>
       <c r="L75" s="24" t="n"/>
-      <c r="N75">
-        <f>IF(COUNTA($A75:$L75)=0,0,IF(OR($B75="",$D75="",$F75="",$G75=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O75">
+      <c r="M75" s="24" t="n"/>
+      <c r="N75" s="24" t="n"/>
+      <c r="O75" s="24" t="n"/>
+      <c r="P75">
+        <f>IF(COUNTA($A75:$O75)=0,0,IF(OR($B75="",$D75="",$F75="",$G75=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q75">
         <f>IF(OR(AND($D75&lt;&gt;"",OR(LEN($D75)&lt;&gt;17,LEN($D75)-LEN(SUBSTITUTE($D75,":",""))&lt;&gt;5)),AND($E75&lt;&gt;"",OR(LEN($E75)&lt;&gt;17,LEN($E75)-LEN(SUBSTITUTE($E75,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4101,11 +4341,14 @@
       <c r="J76" s="24" t="n"/>
       <c r="K76" s="24" t="n"/>
       <c r="L76" s="24" t="n"/>
-      <c r="N76">
-        <f>IF(COUNTA($A76:$L76)=0,0,IF(OR($B76="",$D76="",$F76="",$G76=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O76">
+      <c r="M76" s="24" t="n"/>
+      <c r="N76" s="24" t="n"/>
+      <c r="O76" s="24" t="n"/>
+      <c r="P76">
+        <f>IF(COUNTA($A76:$O76)=0,0,IF(OR($B76="",$D76="",$F76="",$G76=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q76">
         <f>IF(OR(AND($D76&lt;&gt;"",OR(LEN($D76)&lt;&gt;17,LEN($D76)-LEN(SUBSTITUTE($D76,":",""))&lt;&gt;5)),AND($E76&lt;&gt;"",OR(LEN($E76)&lt;&gt;17,LEN($E76)-LEN(SUBSTITUTE($E76,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4123,11 +4366,14 @@
       <c r="J77" s="24" t="n"/>
       <c r="K77" s="24" t="n"/>
       <c r="L77" s="24" t="n"/>
-      <c r="N77">
-        <f>IF(COUNTA($A77:$L77)=0,0,IF(OR($B77="",$D77="",$F77="",$G77=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O77">
+      <c r="M77" s="24" t="n"/>
+      <c r="N77" s="24" t="n"/>
+      <c r="O77" s="24" t="n"/>
+      <c r="P77">
+        <f>IF(COUNTA($A77:$O77)=0,0,IF(OR($B77="",$D77="",$F77="",$G77=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q77">
         <f>IF(OR(AND($D77&lt;&gt;"",OR(LEN($D77)&lt;&gt;17,LEN($D77)-LEN(SUBSTITUTE($D77,":",""))&lt;&gt;5)),AND($E77&lt;&gt;"",OR(LEN($E77)&lt;&gt;17,LEN($E77)-LEN(SUBSTITUTE($E77,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4145,11 +4391,14 @@
       <c r="J78" s="24" t="n"/>
       <c r="K78" s="24" t="n"/>
       <c r="L78" s="24" t="n"/>
-      <c r="N78">
-        <f>IF(COUNTA($A78:$L78)=0,0,IF(OR($B78="",$D78="",$F78="",$G78=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O78">
+      <c r="M78" s="24" t="n"/>
+      <c r="N78" s="24" t="n"/>
+      <c r="O78" s="24" t="n"/>
+      <c r="P78">
+        <f>IF(COUNTA($A78:$O78)=0,0,IF(OR($B78="",$D78="",$F78="",$G78=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q78">
         <f>IF(OR(AND($D78&lt;&gt;"",OR(LEN($D78)&lt;&gt;17,LEN($D78)-LEN(SUBSTITUTE($D78,":",""))&lt;&gt;5)),AND($E78&lt;&gt;"",OR(LEN($E78)&lt;&gt;17,LEN($E78)-LEN(SUBSTITUTE($E78,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4167,11 +4416,14 @@
       <c r="J79" s="24" t="n"/>
       <c r="K79" s="24" t="n"/>
       <c r="L79" s="24" t="n"/>
-      <c r="N79">
-        <f>IF(COUNTA($A79:$L79)=0,0,IF(OR($B79="",$D79="",$F79="",$G79=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O79">
+      <c r="M79" s="24" t="n"/>
+      <c r="N79" s="24" t="n"/>
+      <c r="O79" s="24" t="n"/>
+      <c r="P79">
+        <f>IF(COUNTA($A79:$O79)=0,0,IF(OR($B79="",$D79="",$F79="",$G79=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q79">
         <f>IF(OR(AND($D79&lt;&gt;"",OR(LEN($D79)&lt;&gt;17,LEN($D79)-LEN(SUBSTITUTE($D79,":",""))&lt;&gt;5)),AND($E79&lt;&gt;"",OR(LEN($E79)&lt;&gt;17,LEN($E79)-LEN(SUBSTITUTE($E79,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4189,11 +4441,14 @@
       <c r="J80" s="24" t="n"/>
       <c r="K80" s="24" t="n"/>
       <c r="L80" s="24" t="n"/>
-      <c r="N80">
-        <f>IF(COUNTA($A80:$L80)=0,0,IF(OR($B80="",$D80="",$F80="",$G80=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O80">
+      <c r="M80" s="24" t="n"/>
+      <c r="N80" s="24" t="n"/>
+      <c r="O80" s="24" t="n"/>
+      <c r="P80">
+        <f>IF(COUNTA($A80:$O80)=0,0,IF(OR($B80="",$D80="",$F80="",$G80=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q80">
         <f>IF(OR(AND($D80&lt;&gt;"",OR(LEN($D80)&lt;&gt;17,LEN($D80)-LEN(SUBSTITUTE($D80,":",""))&lt;&gt;5)),AND($E80&lt;&gt;"",OR(LEN($E80)&lt;&gt;17,LEN($E80)-LEN(SUBSTITUTE($E80,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4211,11 +4466,14 @@
       <c r="J81" s="24" t="n"/>
       <c r="K81" s="24" t="n"/>
       <c r="L81" s="24" t="n"/>
-      <c r="N81">
-        <f>IF(COUNTA($A81:$L81)=0,0,IF(OR($B81="",$D81="",$F81="",$G81=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O81">
+      <c r="M81" s="24" t="n"/>
+      <c r="N81" s="24" t="n"/>
+      <c r="O81" s="24" t="n"/>
+      <c r="P81">
+        <f>IF(COUNTA($A81:$O81)=0,0,IF(OR($B81="",$D81="",$F81="",$G81=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q81">
         <f>IF(OR(AND($D81&lt;&gt;"",OR(LEN($D81)&lt;&gt;17,LEN($D81)-LEN(SUBSTITUTE($D81,":",""))&lt;&gt;5)),AND($E81&lt;&gt;"",OR(LEN($E81)&lt;&gt;17,LEN($E81)-LEN(SUBSTITUTE($E81,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4233,11 +4491,14 @@
       <c r="J82" s="24" t="n"/>
       <c r="K82" s="24" t="n"/>
       <c r="L82" s="24" t="n"/>
-      <c r="N82">
-        <f>IF(COUNTA($A82:$L82)=0,0,IF(OR($B82="",$D82="",$F82="",$G82=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O82">
+      <c r="M82" s="24" t="n"/>
+      <c r="N82" s="24" t="n"/>
+      <c r="O82" s="24" t="n"/>
+      <c r="P82">
+        <f>IF(COUNTA($A82:$O82)=0,0,IF(OR($B82="",$D82="",$F82="",$G82=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q82">
         <f>IF(OR(AND($D82&lt;&gt;"",OR(LEN($D82)&lt;&gt;17,LEN($D82)-LEN(SUBSTITUTE($D82,":",""))&lt;&gt;5)),AND($E82&lt;&gt;"",OR(LEN($E82)&lt;&gt;17,LEN($E82)-LEN(SUBSTITUTE($E82,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4255,11 +4516,14 @@
       <c r="J83" s="24" t="n"/>
       <c r="K83" s="24" t="n"/>
       <c r="L83" s="24" t="n"/>
-      <c r="N83">
-        <f>IF(COUNTA($A83:$L83)=0,0,IF(OR($B83="",$D83="",$F83="",$G83=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O83">
+      <c r="M83" s="24" t="n"/>
+      <c r="N83" s="24" t="n"/>
+      <c r="O83" s="24" t="n"/>
+      <c r="P83">
+        <f>IF(COUNTA($A83:$O83)=0,0,IF(OR($B83="",$D83="",$F83="",$G83=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q83">
         <f>IF(OR(AND($D83&lt;&gt;"",OR(LEN($D83)&lt;&gt;17,LEN($D83)-LEN(SUBSTITUTE($D83,":",""))&lt;&gt;5)),AND($E83&lt;&gt;"",OR(LEN($E83)&lt;&gt;17,LEN($E83)-LEN(SUBSTITUTE($E83,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4277,11 +4541,14 @@
       <c r="J84" s="24" t="n"/>
       <c r="K84" s="24" t="n"/>
       <c r="L84" s="24" t="n"/>
-      <c r="N84">
-        <f>IF(COUNTA($A84:$L84)=0,0,IF(OR($B84="",$D84="",$F84="",$G84=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O84">
+      <c r="M84" s="24" t="n"/>
+      <c r="N84" s="24" t="n"/>
+      <c r="O84" s="24" t="n"/>
+      <c r="P84">
+        <f>IF(COUNTA($A84:$O84)=0,0,IF(OR($B84="",$D84="",$F84="",$G84=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q84">
         <f>IF(OR(AND($D84&lt;&gt;"",OR(LEN($D84)&lt;&gt;17,LEN($D84)-LEN(SUBSTITUTE($D84,":",""))&lt;&gt;5)),AND($E84&lt;&gt;"",OR(LEN($E84)&lt;&gt;17,LEN($E84)-LEN(SUBSTITUTE($E84,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4299,11 +4566,14 @@
       <c r="J85" s="24" t="n"/>
       <c r="K85" s="24" t="n"/>
       <c r="L85" s="24" t="n"/>
-      <c r="N85">
-        <f>IF(COUNTA($A85:$L85)=0,0,IF(OR($B85="",$D85="",$F85="",$G85=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O85">
+      <c r="M85" s="24" t="n"/>
+      <c r="N85" s="24" t="n"/>
+      <c r="O85" s="24" t="n"/>
+      <c r="P85">
+        <f>IF(COUNTA($A85:$O85)=0,0,IF(OR($B85="",$D85="",$F85="",$G85=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q85">
         <f>IF(OR(AND($D85&lt;&gt;"",OR(LEN($D85)&lt;&gt;17,LEN($D85)-LEN(SUBSTITUTE($D85,":",""))&lt;&gt;5)),AND($E85&lt;&gt;"",OR(LEN($E85)&lt;&gt;17,LEN($E85)-LEN(SUBSTITUTE($E85,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4321,11 +4591,14 @@
       <c r="J86" s="24" t="n"/>
       <c r="K86" s="24" t="n"/>
       <c r="L86" s="24" t="n"/>
-      <c r="N86">
-        <f>IF(COUNTA($A86:$L86)=0,0,IF(OR($B86="",$D86="",$F86="",$G86=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O86">
+      <c r="M86" s="24" t="n"/>
+      <c r="N86" s="24" t="n"/>
+      <c r="O86" s="24" t="n"/>
+      <c r="P86">
+        <f>IF(COUNTA($A86:$O86)=0,0,IF(OR($B86="",$D86="",$F86="",$G86=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q86">
         <f>IF(OR(AND($D86&lt;&gt;"",OR(LEN($D86)&lt;&gt;17,LEN($D86)-LEN(SUBSTITUTE($D86,":",""))&lt;&gt;5)),AND($E86&lt;&gt;"",OR(LEN($E86)&lt;&gt;17,LEN($E86)-LEN(SUBSTITUTE($E86,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4343,11 +4616,14 @@
       <c r="J87" s="24" t="n"/>
       <c r="K87" s="24" t="n"/>
       <c r="L87" s="24" t="n"/>
-      <c r="N87">
-        <f>IF(COUNTA($A87:$L87)=0,0,IF(OR($B87="",$D87="",$F87="",$G87=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O87">
+      <c r="M87" s="24" t="n"/>
+      <c r="N87" s="24" t="n"/>
+      <c r="O87" s="24" t="n"/>
+      <c r="P87">
+        <f>IF(COUNTA($A87:$O87)=0,0,IF(OR($B87="",$D87="",$F87="",$G87=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q87">
         <f>IF(OR(AND($D87&lt;&gt;"",OR(LEN($D87)&lt;&gt;17,LEN($D87)-LEN(SUBSTITUTE($D87,":",""))&lt;&gt;5)),AND($E87&lt;&gt;"",OR(LEN($E87)&lt;&gt;17,LEN($E87)-LEN(SUBSTITUTE($E87,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4365,11 +4641,14 @@
       <c r="J88" s="24" t="n"/>
       <c r="K88" s="24" t="n"/>
       <c r="L88" s="24" t="n"/>
-      <c r="N88">
-        <f>IF(COUNTA($A88:$L88)=0,0,IF(OR($B88="",$D88="",$F88="",$G88=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O88">
+      <c r="M88" s="24" t="n"/>
+      <c r="N88" s="24" t="n"/>
+      <c r="O88" s="24" t="n"/>
+      <c r="P88">
+        <f>IF(COUNTA($A88:$O88)=0,0,IF(OR($B88="",$D88="",$F88="",$G88=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q88">
         <f>IF(OR(AND($D88&lt;&gt;"",OR(LEN($D88)&lt;&gt;17,LEN($D88)-LEN(SUBSTITUTE($D88,":",""))&lt;&gt;5)),AND($E88&lt;&gt;"",OR(LEN($E88)&lt;&gt;17,LEN($E88)-LEN(SUBSTITUTE($E88,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4387,11 +4666,14 @@
       <c r="J89" s="24" t="n"/>
       <c r="K89" s="24" t="n"/>
       <c r="L89" s="24" t="n"/>
-      <c r="N89">
-        <f>IF(COUNTA($A89:$L89)=0,0,IF(OR($B89="",$D89="",$F89="",$G89=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O89">
+      <c r="M89" s="24" t="n"/>
+      <c r="N89" s="24" t="n"/>
+      <c r="O89" s="24" t="n"/>
+      <c r="P89">
+        <f>IF(COUNTA($A89:$O89)=0,0,IF(OR($B89="",$D89="",$F89="",$G89=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q89">
         <f>IF(OR(AND($D89&lt;&gt;"",OR(LEN($D89)&lt;&gt;17,LEN($D89)-LEN(SUBSTITUTE($D89,":",""))&lt;&gt;5)),AND($E89&lt;&gt;"",OR(LEN($E89)&lt;&gt;17,LEN($E89)-LEN(SUBSTITUTE($E89,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4409,11 +4691,14 @@
       <c r="J90" s="24" t="n"/>
       <c r="K90" s="24" t="n"/>
       <c r="L90" s="24" t="n"/>
-      <c r="N90">
-        <f>IF(COUNTA($A90:$L90)=0,0,IF(OR($B90="",$D90="",$F90="",$G90=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O90">
+      <c r="M90" s="24" t="n"/>
+      <c r="N90" s="24" t="n"/>
+      <c r="O90" s="24" t="n"/>
+      <c r="P90">
+        <f>IF(COUNTA($A90:$O90)=0,0,IF(OR($B90="",$D90="",$F90="",$G90=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q90">
         <f>IF(OR(AND($D90&lt;&gt;"",OR(LEN($D90)&lt;&gt;17,LEN($D90)-LEN(SUBSTITUTE($D90,":",""))&lt;&gt;5)),AND($E90&lt;&gt;"",OR(LEN($E90)&lt;&gt;17,LEN($E90)-LEN(SUBSTITUTE($E90,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4431,11 +4716,14 @@
       <c r="J91" s="24" t="n"/>
       <c r="K91" s="24" t="n"/>
       <c r="L91" s="24" t="n"/>
-      <c r="N91">
-        <f>IF(COUNTA($A91:$L91)=0,0,IF(OR($B91="",$D91="",$F91="",$G91=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O91">
+      <c r="M91" s="24" t="n"/>
+      <c r="N91" s="24" t="n"/>
+      <c r="O91" s="24" t="n"/>
+      <c r="P91">
+        <f>IF(COUNTA($A91:$O91)=0,0,IF(OR($B91="",$D91="",$F91="",$G91=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q91">
         <f>IF(OR(AND($D91&lt;&gt;"",OR(LEN($D91)&lt;&gt;17,LEN($D91)-LEN(SUBSTITUTE($D91,":",""))&lt;&gt;5)),AND($E91&lt;&gt;"",OR(LEN($E91)&lt;&gt;17,LEN($E91)-LEN(SUBSTITUTE($E91,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4453,11 +4741,14 @@
       <c r="J92" s="24" t="n"/>
       <c r="K92" s="24" t="n"/>
       <c r="L92" s="24" t="n"/>
-      <c r="N92">
-        <f>IF(COUNTA($A92:$L92)=0,0,IF(OR($B92="",$D92="",$F92="",$G92=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O92">
+      <c r="M92" s="24" t="n"/>
+      <c r="N92" s="24" t="n"/>
+      <c r="O92" s="24" t="n"/>
+      <c r="P92">
+        <f>IF(COUNTA($A92:$O92)=0,0,IF(OR($B92="",$D92="",$F92="",$G92=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q92">
         <f>IF(OR(AND($D92&lt;&gt;"",OR(LEN($D92)&lt;&gt;17,LEN($D92)-LEN(SUBSTITUTE($D92,":",""))&lt;&gt;5)),AND($E92&lt;&gt;"",OR(LEN($E92)&lt;&gt;17,LEN($E92)-LEN(SUBSTITUTE($E92,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4475,11 +4766,14 @@
       <c r="J93" s="24" t="n"/>
       <c r="K93" s="24" t="n"/>
       <c r="L93" s="24" t="n"/>
-      <c r="N93">
-        <f>IF(COUNTA($A93:$L93)=0,0,IF(OR($B93="",$D93="",$F93="",$G93=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O93">
+      <c r="M93" s="24" t="n"/>
+      <c r="N93" s="24" t="n"/>
+      <c r="O93" s="24" t="n"/>
+      <c r="P93">
+        <f>IF(COUNTA($A93:$O93)=0,0,IF(OR($B93="",$D93="",$F93="",$G93=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q93">
         <f>IF(OR(AND($D93&lt;&gt;"",OR(LEN($D93)&lt;&gt;17,LEN($D93)-LEN(SUBSTITUTE($D93,":",""))&lt;&gt;5)),AND($E93&lt;&gt;"",OR(LEN($E93)&lt;&gt;17,LEN($E93)-LEN(SUBSTITUTE($E93,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4497,11 +4791,14 @@
       <c r="J94" s="24" t="n"/>
       <c r="K94" s="24" t="n"/>
       <c r="L94" s="24" t="n"/>
-      <c r="N94">
-        <f>IF(COUNTA($A94:$L94)=0,0,IF(OR($B94="",$D94="",$F94="",$G94=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O94">
+      <c r="M94" s="24" t="n"/>
+      <c r="N94" s="24" t="n"/>
+      <c r="O94" s="24" t="n"/>
+      <c r="P94">
+        <f>IF(COUNTA($A94:$O94)=0,0,IF(OR($B94="",$D94="",$F94="",$G94=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q94">
         <f>IF(OR(AND($D94&lt;&gt;"",OR(LEN($D94)&lt;&gt;17,LEN($D94)-LEN(SUBSTITUTE($D94,":",""))&lt;&gt;5)),AND($E94&lt;&gt;"",OR(LEN($E94)&lt;&gt;17,LEN($E94)-LEN(SUBSTITUTE($E94,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4519,11 +4816,14 @@
       <c r="J95" s="24" t="n"/>
       <c r="K95" s="24" t="n"/>
       <c r="L95" s="24" t="n"/>
-      <c r="N95">
-        <f>IF(COUNTA($A95:$L95)=0,0,IF(OR($B95="",$D95="",$F95="",$G95=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O95">
+      <c r="M95" s="24" t="n"/>
+      <c r="N95" s="24" t="n"/>
+      <c r="O95" s="24" t="n"/>
+      <c r="P95">
+        <f>IF(COUNTA($A95:$O95)=0,0,IF(OR($B95="",$D95="",$F95="",$G95=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q95">
         <f>IF(OR(AND($D95&lt;&gt;"",OR(LEN($D95)&lt;&gt;17,LEN($D95)-LEN(SUBSTITUTE($D95,":",""))&lt;&gt;5)),AND($E95&lt;&gt;"",OR(LEN($E95)&lt;&gt;17,LEN($E95)-LEN(SUBSTITUTE($E95,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4541,11 +4841,14 @@
       <c r="J96" s="24" t="n"/>
       <c r="K96" s="24" t="n"/>
       <c r="L96" s="24" t="n"/>
-      <c r="N96">
-        <f>IF(COUNTA($A96:$L96)=0,0,IF(OR($B96="",$D96="",$F96="",$G96=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O96">
+      <c r="M96" s="24" t="n"/>
+      <c r="N96" s="24" t="n"/>
+      <c r="O96" s="24" t="n"/>
+      <c r="P96">
+        <f>IF(COUNTA($A96:$O96)=0,0,IF(OR($B96="",$D96="",$F96="",$G96=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q96">
         <f>IF(OR(AND($D96&lt;&gt;"",OR(LEN($D96)&lt;&gt;17,LEN($D96)-LEN(SUBSTITUTE($D96,":",""))&lt;&gt;5)),AND($E96&lt;&gt;"",OR(LEN($E96)&lt;&gt;17,LEN($E96)-LEN(SUBSTITUTE($E96,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4563,11 +4866,14 @@
       <c r="J97" s="24" t="n"/>
       <c r="K97" s="24" t="n"/>
       <c r="L97" s="24" t="n"/>
-      <c r="N97">
-        <f>IF(COUNTA($A97:$L97)=0,0,IF(OR($B97="",$D97="",$F97="",$G97=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O97">
+      <c r="M97" s="24" t="n"/>
+      <c r="N97" s="24" t="n"/>
+      <c r="O97" s="24" t="n"/>
+      <c r="P97">
+        <f>IF(COUNTA($A97:$O97)=0,0,IF(OR($B97="",$D97="",$F97="",$G97=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q97">
         <f>IF(OR(AND($D97&lt;&gt;"",OR(LEN($D97)&lt;&gt;17,LEN($D97)-LEN(SUBSTITUTE($D97,":",""))&lt;&gt;5)),AND($E97&lt;&gt;"",OR(LEN($E97)&lt;&gt;17,LEN($E97)-LEN(SUBSTITUTE($E97,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4585,11 +4891,14 @@
       <c r="J98" s="24" t="n"/>
       <c r="K98" s="24" t="n"/>
       <c r="L98" s="24" t="n"/>
-      <c r="N98">
-        <f>IF(COUNTA($A98:$L98)=0,0,IF(OR($B98="",$D98="",$F98="",$G98=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O98">
+      <c r="M98" s="24" t="n"/>
+      <c r="N98" s="24" t="n"/>
+      <c r="O98" s="24" t="n"/>
+      <c r="P98">
+        <f>IF(COUNTA($A98:$O98)=0,0,IF(OR($B98="",$D98="",$F98="",$G98=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q98">
         <f>IF(OR(AND($D98&lt;&gt;"",OR(LEN($D98)&lt;&gt;17,LEN($D98)-LEN(SUBSTITUTE($D98,":",""))&lt;&gt;5)),AND($E98&lt;&gt;"",OR(LEN($E98)&lt;&gt;17,LEN($E98)-LEN(SUBSTITUTE($E98,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4607,11 +4916,14 @@
       <c r="J99" s="24" t="n"/>
       <c r="K99" s="24" t="n"/>
       <c r="L99" s="24" t="n"/>
-      <c r="N99">
-        <f>IF(COUNTA($A99:$L99)=0,0,IF(OR($B99="",$D99="",$F99="",$G99=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O99">
+      <c r="M99" s="24" t="n"/>
+      <c r="N99" s="24" t="n"/>
+      <c r="O99" s="24" t="n"/>
+      <c r="P99">
+        <f>IF(COUNTA($A99:$O99)=0,0,IF(OR($B99="",$D99="",$F99="",$G99=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q99">
         <f>IF(OR(AND($D99&lt;&gt;"",OR(LEN($D99)&lt;&gt;17,LEN($D99)-LEN(SUBSTITUTE($D99,":",""))&lt;&gt;5)),AND($E99&lt;&gt;"",OR(LEN($E99)&lt;&gt;17,LEN($E99)-LEN(SUBSTITUTE($E99,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4629,11 +4941,14 @@
       <c r="J100" s="24" t="n"/>
       <c r="K100" s="24" t="n"/>
       <c r="L100" s="24" t="n"/>
-      <c r="N100">
-        <f>IF(COUNTA($A100:$L100)=0,0,IF(OR($B100="",$D100="",$F100="",$G100=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O100">
+      <c r="M100" s="24" t="n"/>
+      <c r="N100" s="24" t="n"/>
+      <c r="O100" s="24" t="n"/>
+      <c r="P100">
+        <f>IF(COUNTA($A100:$O100)=0,0,IF(OR($B100="",$D100="",$F100="",$G100=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q100">
         <f>IF(OR(AND($D100&lt;&gt;"",OR(LEN($D100)&lt;&gt;17,LEN($D100)-LEN(SUBSTITUTE($D100,":",""))&lt;&gt;5)),AND($E100&lt;&gt;"",OR(LEN($E100)&lt;&gt;17,LEN($E100)-LEN(SUBSTITUTE($E100,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4651,11 +4966,14 @@
       <c r="J101" s="24" t="n"/>
       <c r="K101" s="24" t="n"/>
       <c r="L101" s="24" t="n"/>
-      <c r="N101">
-        <f>IF(COUNTA($A101:$L101)=0,0,IF(OR($B101="",$D101="",$F101="",$G101=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O101">
+      <c r="M101" s="24" t="n"/>
+      <c r="N101" s="24" t="n"/>
+      <c r="O101" s="24" t="n"/>
+      <c r="P101">
+        <f>IF(COUNTA($A101:$O101)=0,0,IF(OR($B101="",$D101="",$F101="",$G101=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q101">
         <f>IF(OR(AND($D101&lt;&gt;"",OR(LEN($D101)&lt;&gt;17,LEN($D101)-LEN(SUBSTITUTE($D101,":",""))&lt;&gt;5)),AND($E101&lt;&gt;"",OR(LEN($E101)&lt;&gt;17,LEN($E101)-LEN(SUBSTITUTE($E101,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4673,11 +4991,14 @@
       <c r="J102" s="24" t="n"/>
       <c r="K102" s="24" t="n"/>
       <c r="L102" s="24" t="n"/>
-      <c r="N102">
-        <f>IF(COUNTA($A102:$L102)=0,0,IF(OR($B102="",$D102="",$F102="",$G102=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O102">
+      <c r="M102" s="24" t="n"/>
+      <c r="N102" s="24" t="n"/>
+      <c r="O102" s="24" t="n"/>
+      <c r="P102">
+        <f>IF(COUNTA($A102:$O102)=0,0,IF(OR($B102="",$D102="",$F102="",$G102=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q102">
         <f>IF(OR(AND($D102&lt;&gt;"",OR(LEN($D102)&lt;&gt;17,LEN($D102)-LEN(SUBSTITUTE($D102,":",""))&lt;&gt;5)),AND($E102&lt;&gt;"",OR(LEN($E102)&lt;&gt;17,LEN($E102)-LEN(SUBSTITUTE($E102,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4695,11 +5016,14 @@
       <c r="J103" s="24" t="n"/>
       <c r="K103" s="24" t="n"/>
       <c r="L103" s="24" t="n"/>
-      <c r="N103">
-        <f>IF(COUNTA($A103:$L103)=0,0,IF(OR($B103="",$D103="",$F103="",$G103=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O103">
+      <c r="M103" s="24" t="n"/>
+      <c r="N103" s="24" t="n"/>
+      <c r="O103" s="24" t="n"/>
+      <c r="P103">
+        <f>IF(COUNTA($A103:$O103)=0,0,IF(OR($B103="",$D103="",$F103="",$G103=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q103">
         <f>IF(OR(AND($D103&lt;&gt;"",OR(LEN($D103)&lt;&gt;17,LEN($D103)-LEN(SUBSTITUTE($D103,":",""))&lt;&gt;5)),AND($E103&lt;&gt;"",OR(LEN($E103)&lt;&gt;17,LEN($E103)-LEN(SUBSTITUTE($E103,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4717,11 +5041,14 @@
       <c r="J104" s="24" t="n"/>
       <c r="K104" s="24" t="n"/>
       <c r="L104" s="24" t="n"/>
-      <c r="N104">
-        <f>IF(COUNTA($A104:$L104)=0,0,IF(OR($B104="",$D104="",$F104="",$G104=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O104">
+      <c r="M104" s="24" t="n"/>
+      <c r="N104" s="24" t="n"/>
+      <c r="O104" s="24" t="n"/>
+      <c r="P104">
+        <f>IF(COUNTA($A104:$O104)=0,0,IF(OR($B104="",$D104="",$F104="",$G104=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q104">
         <f>IF(OR(AND($D104&lt;&gt;"",OR(LEN($D104)&lt;&gt;17,LEN($D104)-LEN(SUBSTITUTE($D104,":",""))&lt;&gt;5)),AND($E104&lt;&gt;"",OR(LEN($E104)&lt;&gt;17,LEN($E104)-LEN(SUBSTITUTE($E104,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4739,11 +5066,14 @@
       <c r="J105" s="24" t="n"/>
       <c r="K105" s="24" t="n"/>
       <c r="L105" s="24" t="n"/>
-      <c r="N105">
-        <f>IF(COUNTA($A105:$L105)=0,0,IF(OR($B105="",$D105="",$F105="",$G105=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O105">
+      <c r="M105" s="24" t="n"/>
+      <c r="N105" s="24" t="n"/>
+      <c r="O105" s="24" t="n"/>
+      <c r="P105">
+        <f>IF(COUNTA($A105:$O105)=0,0,IF(OR($B105="",$D105="",$F105="",$G105=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q105">
         <f>IF(OR(AND($D105&lt;&gt;"",OR(LEN($D105)&lt;&gt;17,LEN($D105)-LEN(SUBSTITUTE($D105,":",""))&lt;&gt;5)),AND($E105&lt;&gt;"",OR(LEN($E105)&lt;&gt;17,LEN($E105)-LEN(SUBSTITUTE($E105,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4761,11 +5091,14 @@
       <c r="J106" s="24" t="n"/>
       <c r="K106" s="24" t="n"/>
       <c r="L106" s="24" t="n"/>
-      <c r="N106">
-        <f>IF(COUNTA($A106:$L106)=0,0,IF(OR($B106="",$D106="",$F106="",$G106=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O106">
+      <c r="M106" s="24" t="n"/>
+      <c r="N106" s="24" t="n"/>
+      <c r="O106" s="24" t="n"/>
+      <c r="P106">
+        <f>IF(COUNTA($A106:$O106)=0,0,IF(OR($B106="",$D106="",$F106="",$G106=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q106">
         <f>IF(OR(AND($D106&lt;&gt;"",OR(LEN($D106)&lt;&gt;17,LEN($D106)-LEN(SUBSTITUTE($D106,":",""))&lt;&gt;5)),AND($E106&lt;&gt;"",OR(LEN($E106)&lt;&gt;17,LEN($E106)-LEN(SUBSTITUTE($E106,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4783,11 +5116,14 @@
       <c r="J107" s="24" t="n"/>
       <c r="K107" s="24" t="n"/>
       <c r="L107" s="24" t="n"/>
-      <c r="N107">
-        <f>IF(COUNTA($A107:$L107)=0,0,IF(OR($B107="",$D107="",$F107="",$G107=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O107">
+      <c r="M107" s="24" t="n"/>
+      <c r="N107" s="24" t="n"/>
+      <c r="O107" s="24" t="n"/>
+      <c r="P107">
+        <f>IF(COUNTA($A107:$O107)=0,0,IF(OR($B107="",$D107="",$F107="",$G107=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q107">
         <f>IF(OR(AND($D107&lt;&gt;"",OR(LEN($D107)&lt;&gt;17,LEN($D107)-LEN(SUBSTITUTE($D107,":",""))&lt;&gt;5)),AND($E107&lt;&gt;"",OR(LEN($E107)&lt;&gt;17,LEN($E107)-LEN(SUBSTITUTE($E107,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4805,11 +5141,14 @@
       <c r="J108" s="24" t="n"/>
       <c r="K108" s="24" t="n"/>
       <c r="L108" s="24" t="n"/>
-      <c r="N108">
-        <f>IF(COUNTA($A108:$L108)=0,0,IF(OR($B108="",$D108="",$F108="",$G108=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O108">
+      <c r="M108" s="24" t="n"/>
+      <c r="N108" s="24" t="n"/>
+      <c r="O108" s="24" t="n"/>
+      <c r="P108">
+        <f>IF(COUNTA($A108:$O108)=0,0,IF(OR($B108="",$D108="",$F108="",$G108=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q108">
         <f>IF(OR(AND($D108&lt;&gt;"",OR(LEN($D108)&lt;&gt;17,LEN($D108)-LEN(SUBSTITUTE($D108,":",""))&lt;&gt;5)),AND($E108&lt;&gt;"",OR(LEN($E108)&lt;&gt;17,LEN($E108)-LEN(SUBSTITUTE($E108,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4827,11 +5166,14 @@
       <c r="J109" s="24" t="n"/>
       <c r="K109" s="24" t="n"/>
       <c r="L109" s="24" t="n"/>
-      <c r="N109">
-        <f>IF(COUNTA($A109:$L109)=0,0,IF(OR($B109="",$D109="",$F109="",$G109=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O109">
+      <c r="M109" s="24" t="n"/>
+      <c r="N109" s="24" t="n"/>
+      <c r="O109" s="24" t="n"/>
+      <c r="P109">
+        <f>IF(COUNTA($A109:$O109)=0,0,IF(OR($B109="",$D109="",$F109="",$G109=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q109">
         <f>IF(OR(AND($D109&lt;&gt;"",OR(LEN($D109)&lt;&gt;17,LEN($D109)-LEN(SUBSTITUTE($D109,":",""))&lt;&gt;5)),AND($E109&lt;&gt;"",OR(LEN($E109)&lt;&gt;17,LEN($E109)-LEN(SUBSTITUTE($E109,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4849,11 +5191,14 @@
       <c r="J110" s="24" t="n"/>
       <c r="K110" s="24" t="n"/>
       <c r="L110" s="24" t="n"/>
-      <c r="N110">
-        <f>IF(COUNTA($A110:$L110)=0,0,IF(OR($B110="",$D110="",$F110="",$G110=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O110">
+      <c r="M110" s="24" t="n"/>
+      <c r="N110" s="24" t="n"/>
+      <c r="O110" s="24" t="n"/>
+      <c r="P110">
+        <f>IF(COUNTA($A110:$O110)=0,0,IF(OR($B110="",$D110="",$F110="",$G110=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q110">
         <f>IF(OR(AND($D110&lt;&gt;"",OR(LEN($D110)&lt;&gt;17,LEN($D110)-LEN(SUBSTITUTE($D110,":",""))&lt;&gt;5)),AND($E110&lt;&gt;"",OR(LEN($E110)&lt;&gt;17,LEN($E110)-LEN(SUBSTITUTE($E110,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4871,11 +5216,14 @@
       <c r="J111" s="24" t="n"/>
       <c r="K111" s="24" t="n"/>
       <c r="L111" s="24" t="n"/>
-      <c r="N111">
-        <f>IF(COUNTA($A111:$L111)=0,0,IF(OR($B111="",$D111="",$F111="",$G111=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O111">
+      <c r="M111" s="24" t="n"/>
+      <c r="N111" s="24" t="n"/>
+      <c r="O111" s="24" t="n"/>
+      <c r="P111">
+        <f>IF(COUNTA($A111:$O111)=0,0,IF(OR($B111="",$D111="",$F111="",$G111=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q111">
         <f>IF(OR(AND($D111&lt;&gt;"",OR(LEN($D111)&lt;&gt;17,LEN($D111)-LEN(SUBSTITUTE($D111,":",""))&lt;&gt;5)),AND($E111&lt;&gt;"",OR(LEN($E111)&lt;&gt;17,LEN($E111)-LEN(SUBSTITUTE($E111,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4893,11 +5241,14 @@
       <c r="J112" s="24" t="n"/>
       <c r="K112" s="24" t="n"/>
       <c r="L112" s="24" t="n"/>
-      <c r="N112">
-        <f>IF(COUNTA($A112:$L112)=0,0,IF(OR($B112="",$D112="",$F112="",$G112=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O112">
+      <c r="M112" s="24" t="n"/>
+      <c r="N112" s="24" t="n"/>
+      <c r="O112" s="24" t="n"/>
+      <c r="P112">
+        <f>IF(COUNTA($A112:$O112)=0,0,IF(OR($B112="",$D112="",$F112="",$G112=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q112">
         <f>IF(OR(AND($D112&lt;&gt;"",OR(LEN($D112)&lt;&gt;17,LEN($D112)-LEN(SUBSTITUTE($D112,":",""))&lt;&gt;5)),AND($E112&lt;&gt;"",OR(LEN($E112)&lt;&gt;17,LEN($E112)-LEN(SUBSTITUTE($E112,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4915,11 +5266,14 @@
       <c r="J113" s="24" t="n"/>
       <c r="K113" s="24" t="n"/>
       <c r="L113" s="24" t="n"/>
-      <c r="N113">
-        <f>IF(COUNTA($A113:$L113)=0,0,IF(OR($B113="",$D113="",$F113="",$G113=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O113">
+      <c r="M113" s="24" t="n"/>
+      <c r="N113" s="24" t="n"/>
+      <c r="O113" s="24" t="n"/>
+      <c r="P113">
+        <f>IF(COUNTA($A113:$O113)=0,0,IF(OR($B113="",$D113="",$F113="",$G113=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q113">
         <f>IF(OR(AND($D113&lt;&gt;"",OR(LEN($D113)&lt;&gt;17,LEN($D113)-LEN(SUBSTITUTE($D113,":",""))&lt;&gt;5)),AND($E113&lt;&gt;"",OR(LEN($E113)&lt;&gt;17,LEN($E113)-LEN(SUBSTITUTE($E113,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4937,11 +5291,14 @@
       <c r="J114" s="24" t="n"/>
       <c r="K114" s="24" t="n"/>
       <c r="L114" s="24" t="n"/>
-      <c r="N114">
-        <f>IF(COUNTA($A114:$L114)=0,0,IF(OR($B114="",$D114="",$F114="",$G114=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O114">
+      <c r="M114" s="24" t="n"/>
+      <c r="N114" s="24" t="n"/>
+      <c r="O114" s="24" t="n"/>
+      <c r="P114">
+        <f>IF(COUNTA($A114:$O114)=0,0,IF(OR($B114="",$D114="",$F114="",$G114=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q114">
         <f>IF(OR(AND($D114&lt;&gt;"",OR(LEN($D114)&lt;&gt;17,LEN($D114)-LEN(SUBSTITUTE($D114,":",""))&lt;&gt;5)),AND($E114&lt;&gt;"",OR(LEN($E114)&lt;&gt;17,LEN($E114)-LEN(SUBSTITUTE($E114,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4959,11 +5316,14 @@
       <c r="J115" s="24" t="n"/>
       <c r="K115" s="24" t="n"/>
       <c r="L115" s="24" t="n"/>
-      <c r="N115">
-        <f>IF(COUNTA($A115:$L115)=0,0,IF(OR($B115="",$D115="",$F115="",$G115=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O115">
+      <c r="M115" s="24" t="n"/>
+      <c r="N115" s="24" t="n"/>
+      <c r="O115" s="24" t="n"/>
+      <c r="P115">
+        <f>IF(COUNTA($A115:$O115)=0,0,IF(OR($B115="",$D115="",$F115="",$G115=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q115">
         <f>IF(OR(AND($D115&lt;&gt;"",OR(LEN($D115)&lt;&gt;17,LEN($D115)-LEN(SUBSTITUTE($D115,":",""))&lt;&gt;5)),AND($E115&lt;&gt;"",OR(LEN($E115)&lt;&gt;17,LEN($E115)-LEN(SUBSTITUTE($E115,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4981,11 +5341,14 @@
       <c r="J116" s="24" t="n"/>
       <c r="K116" s="24" t="n"/>
       <c r="L116" s="24" t="n"/>
-      <c r="N116">
-        <f>IF(COUNTA($A116:$L116)=0,0,IF(OR($B116="",$D116="",$F116="",$G116=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O116">
+      <c r="M116" s="24" t="n"/>
+      <c r="N116" s="24" t="n"/>
+      <c r="O116" s="24" t="n"/>
+      <c r="P116">
+        <f>IF(COUNTA($A116:$O116)=0,0,IF(OR($B116="",$D116="",$F116="",$G116=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q116">
         <f>IF(OR(AND($D116&lt;&gt;"",OR(LEN($D116)&lt;&gt;17,LEN($D116)-LEN(SUBSTITUTE($D116,":",""))&lt;&gt;5)),AND($E116&lt;&gt;"",OR(LEN($E116)&lt;&gt;17,LEN($E116)-LEN(SUBSTITUTE($E116,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5003,11 +5366,14 @@
       <c r="J117" s="24" t="n"/>
       <c r="K117" s="24" t="n"/>
       <c r="L117" s="24" t="n"/>
-      <c r="N117">
-        <f>IF(COUNTA($A117:$L117)=0,0,IF(OR($B117="",$D117="",$F117="",$G117=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O117">
+      <c r="M117" s="24" t="n"/>
+      <c r="N117" s="24" t="n"/>
+      <c r="O117" s="24" t="n"/>
+      <c r="P117">
+        <f>IF(COUNTA($A117:$O117)=0,0,IF(OR($B117="",$D117="",$F117="",$G117=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q117">
         <f>IF(OR(AND($D117&lt;&gt;"",OR(LEN($D117)&lt;&gt;17,LEN($D117)-LEN(SUBSTITUTE($D117,":",""))&lt;&gt;5)),AND($E117&lt;&gt;"",OR(LEN($E117)&lt;&gt;17,LEN($E117)-LEN(SUBSTITUTE($E117,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5025,11 +5391,14 @@
       <c r="J118" s="24" t="n"/>
       <c r="K118" s="24" t="n"/>
       <c r="L118" s="24" t="n"/>
-      <c r="N118">
-        <f>IF(COUNTA($A118:$L118)=0,0,IF(OR($B118="",$D118="",$F118="",$G118=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O118">
+      <c r="M118" s="24" t="n"/>
+      <c r="N118" s="24" t="n"/>
+      <c r="O118" s="24" t="n"/>
+      <c r="P118">
+        <f>IF(COUNTA($A118:$O118)=0,0,IF(OR($B118="",$D118="",$F118="",$G118=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q118">
         <f>IF(OR(AND($D118&lt;&gt;"",OR(LEN($D118)&lt;&gt;17,LEN($D118)-LEN(SUBSTITUTE($D118,":",""))&lt;&gt;5)),AND($E118&lt;&gt;"",OR(LEN($E118)&lt;&gt;17,LEN($E118)-LEN(SUBSTITUTE($E118,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5047,11 +5416,14 @@
       <c r="J119" s="24" t="n"/>
       <c r="K119" s="24" t="n"/>
       <c r="L119" s="24" t="n"/>
-      <c r="N119">
-        <f>IF(COUNTA($A119:$L119)=0,0,IF(OR($B119="",$D119="",$F119="",$G119=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O119">
+      <c r="M119" s="24" t="n"/>
+      <c r="N119" s="24" t="n"/>
+      <c r="O119" s="24" t="n"/>
+      <c r="P119">
+        <f>IF(COUNTA($A119:$O119)=0,0,IF(OR($B119="",$D119="",$F119="",$G119=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q119">
         <f>IF(OR(AND($D119&lt;&gt;"",OR(LEN($D119)&lt;&gt;17,LEN($D119)-LEN(SUBSTITUTE($D119,":",""))&lt;&gt;5)),AND($E119&lt;&gt;"",OR(LEN($E119)&lt;&gt;17,LEN($E119)-LEN(SUBSTITUTE($E119,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5069,11 +5441,14 @@
       <c r="J120" s="24" t="n"/>
       <c r="K120" s="24" t="n"/>
       <c r="L120" s="24" t="n"/>
-      <c r="N120">
-        <f>IF(COUNTA($A120:$L120)=0,0,IF(OR($B120="",$D120="",$F120="",$G120=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O120">
+      <c r="M120" s="24" t="n"/>
+      <c r="N120" s="24" t="n"/>
+      <c r="O120" s="24" t="n"/>
+      <c r="P120">
+        <f>IF(COUNTA($A120:$O120)=0,0,IF(OR($B120="",$D120="",$F120="",$G120=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q120">
         <f>IF(OR(AND($D120&lt;&gt;"",OR(LEN($D120)&lt;&gt;17,LEN($D120)-LEN(SUBSTITUTE($D120,":",""))&lt;&gt;5)),AND($E120&lt;&gt;"",OR(LEN($E120)&lt;&gt;17,LEN($E120)-LEN(SUBSTITUTE($E120,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5091,11 +5466,14 @@
       <c r="J121" s="24" t="n"/>
       <c r="K121" s="24" t="n"/>
       <c r="L121" s="24" t="n"/>
-      <c r="N121">
-        <f>IF(COUNTA($A121:$L121)=0,0,IF(OR($B121="",$D121="",$F121="",$G121=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O121">
+      <c r="M121" s="24" t="n"/>
+      <c r="N121" s="24" t="n"/>
+      <c r="O121" s="24" t="n"/>
+      <c r="P121">
+        <f>IF(COUNTA($A121:$O121)=0,0,IF(OR($B121="",$D121="",$F121="",$G121=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q121">
         <f>IF(OR(AND($D121&lt;&gt;"",OR(LEN($D121)&lt;&gt;17,LEN($D121)-LEN(SUBSTITUTE($D121,":",""))&lt;&gt;5)),AND($E121&lt;&gt;"",OR(LEN($E121)&lt;&gt;17,LEN($E121)-LEN(SUBSTITUTE($E121,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5113,11 +5491,14 @@
       <c r="J122" s="24" t="n"/>
       <c r="K122" s="24" t="n"/>
       <c r="L122" s="24" t="n"/>
-      <c r="N122">
-        <f>IF(COUNTA($A122:$L122)=0,0,IF(OR($B122="",$D122="",$F122="",$G122=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O122">
+      <c r="M122" s="24" t="n"/>
+      <c r="N122" s="24" t="n"/>
+      <c r="O122" s="24" t="n"/>
+      <c r="P122">
+        <f>IF(COUNTA($A122:$O122)=0,0,IF(OR($B122="",$D122="",$F122="",$G122=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q122">
         <f>IF(OR(AND($D122&lt;&gt;"",OR(LEN($D122)&lt;&gt;17,LEN($D122)-LEN(SUBSTITUTE($D122,":",""))&lt;&gt;5)),AND($E122&lt;&gt;"",OR(LEN($E122)&lt;&gt;17,LEN($E122)-LEN(SUBSTITUTE($E122,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5135,11 +5516,14 @@
       <c r="J123" s="24" t="n"/>
       <c r="K123" s="24" t="n"/>
       <c r="L123" s="24" t="n"/>
-      <c r="N123">
-        <f>IF(COUNTA($A123:$L123)=0,0,IF(OR($B123="",$D123="",$F123="",$G123=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O123">
+      <c r="M123" s="24" t="n"/>
+      <c r="N123" s="24" t="n"/>
+      <c r="O123" s="24" t="n"/>
+      <c r="P123">
+        <f>IF(COUNTA($A123:$O123)=0,0,IF(OR($B123="",$D123="",$F123="",$G123=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q123">
         <f>IF(OR(AND($D123&lt;&gt;"",OR(LEN($D123)&lt;&gt;17,LEN($D123)-LEN(SUBSTITUTE($D123,":",""))&lt;&gt;5)),AND($E123&lt;&gt;"",OR(LEN($E123)&lt;&gt;17,LEN($E123)-LEN(SUBSTITUTE($E123,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5157,11 +5541,14 @@
       <c r="J124" s="24" t="n"/>
       <c r="K124" s="24" t="n"/>
       <c r="L124" s="24" t="n"/>
-      <c r="N124">
-        <f>IF(COUNTA($A124:$L124)=0,0,IF(OR($B124="",$D124="",$F124="",$G124=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O124">
+      <c r="M124" s="24" t="n"/>
+      <c r="N124" s="24" t="n"/>
+      <c r="O124" s="24" t="n"/>
+      <c r="P124">
+        <f>IF(COUNTA($A124:$O124)=0,0,IF(OR($B124="",$D124="",$F124="",$G124=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q124">
         <f>IF(OR(AND($D124&lt;&gt;"",OR(LEN($D124)&lt;&gt;17,LEN($D124)-LEN(SUBSTITUTE($D124,":",""))&lt;&gt;5)),AND($E124&lt;&gt;"",OR(LEN($E124)&lt;&gt;17,LEN($E124)-LEN(SUBSTITUTE($E124,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5179,11 +5566,14 @@
       <c r="J125" s="24" t="n"/>
       <c r="K125" s="24" t="n"/>
       <c r="L125" s="24" t="n"/>
-      <c r="N125">
-        <f>IF(COUNTA($A125:$L125)=0,0,IF(OR($B125="",$D125="",$F125="",$G125=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O125">
+      <c r="M125" s="24" t="n"/>
+      <c r="N125" s="24" t="n"/>
+      <c r="O125" s="24" t="n"/>
+      <c r="P125">
+        <f>IF(COUNTA($A125:$O125)=0,0,IF(OR($B125="",$D125="",$F125="",$G125=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q125">
         <f>IF(OR(AND($D125&lt;&gt;"",OR(LEN($D125)&lt;&gt;17,LEN($D125)-LEN(SUBSTITUTE($D125,":",""))&lt;&gt;5)),AND($E125&lt;&gt;"",OR(LEN($E125)&lt;&gt;17,LEN($E125)-LEN(SUBSTITUTE($E125,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5201,11 +5591,14 @@
       <c r="J126" s="24" t="n"/>
       <c r="K126" s="24" t="n"/>
       <c r="L126" s="24" t="n"/>
-      <c r="N126">
-        <f>IF(COUNTA($A126:$L126)=0,0,IF(OR($B126="",$D126="",$F126="",$G126=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O126">
+      <c r="M126" s="24" t="n"/>
+      <c r="N126" s="24" t="n"/>
+      <c r="O126" s="24" t="n"/>
+      <c r="P126">
+        <f>IF(COUNTA($A126:$O126)=0,0,IF(OR($B126="",$D126="",$F126="",$G126=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q126">
         <f>IF(OR(AND($D126&lt;&gt;"",OR(LEN($D126)&lt;&gt;17,LEN($D126)-LEN(SUBSTITUTE($D126,":",""))&lt;&gt;5)),AND($E126&lt;&gt;"",OR(LEN($E126)&lt;&gt;17,LEN($E126)-LEN(SUBSTITUTE($E126,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5223,11 +5616,14 @@
       <c r="J127" s="24" t="n"/>
       <c r="K127" s="24" t="n"/>
       <c r="L127" s="24" t="n"/>
-      <c r="N127">
-        <f>IF(COUNTA($A127:$L127)=0,0,IF(OR($B127="",$D127="",$F127="",$G127=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O127">
+      <c r="M127" s="24" t="n"/>
+      <c r="N127" s="24" t="n"/>
+      <c r="O127" s="24" t="n"/>
+      <c r="P127">
+        <f>IF(COUNTA($A127:$O127)=0,0,IF(OR($B127="",$D127="",$F127="",$G127=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q127">
         <f>IF(OR(AND($D127&lt;&gt;"",OR(LEN($D127)&lt;&gt;17,LEN($D127)-LEN(SUBSTITUTE($D127,":",""))&lt;&gt;5)),AND($E127&lt;&gt;"",OR(LEN($E127)&lt;&gt;17,LEN($E127)-LEN(SUBSTITUTE($E127,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5245,11 +5641,14 @@
       <c r="J128" s="24" t="n"/>
       <c r="K128" s="24" t="n"/>
       <c r="L128" s="24" t="n"/>
-      <c r="N128">
-        <f>IF(COUNTA($A128:$L128)=0,0,IF(OR($B128="",$D128="",$F128="",$G128=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O128">
+      <c r="M128" s="24" t="n"/>
+      <c r="N128" s="24" t="n"/>
+      <c r="O128" s="24" t="n"/>
+      <c r="P128">
+        <f>IF(COUNTA($A128:$O128)=0,0,IF(OR($B128="",$D128="",$F128="",$G128=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q128">
         <f>IF(OR(AND($D128&lt;&gt;"",OR(LEN($D128)&lt;&gt;17,LEN($D128)-LEN(SUBSTITUTE($D128,":",""))&lt;&gt;5)),AND($E128&lt;&gt;"",OR(LEN($E128)&lt;&gt;17,LEN($E128)-LEN(SUBSTITUTE($E128,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5267,11 +5666,14 @@
       <c r="J129" s="24" t="n"/>
       <c r="K129" s="24" t="n"/>
       <c r="L129" s="24" t="n"/>
-      <c r="N129">
-        <f>IF(COUNTA($A129:$L129)=0,0,IF(OR($B129="",$D129="",$F129="",$G129=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O129">
+      <c r="M129" s="24" t="n"/>
+      <c r="N129" s="24" t="n"/>
+      <c r="O129" s="24" t="n"/>
+      <c r="P129">
+        <f>IF(COUNTA($A129:$O129)=0,0,IF(OR($B129="",$D129="",$F129="",$G129=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q129">
         <f>IF(OR(AND($D129&lt;&gt;"",OR(LEN($D129)&lt;&gt;17,LEN($D129)-LEN(SUBSTITUTE($D129,":",""))&lt;&gt;5)),AND($E129&lt;&gt;"",OR(LEN($E129)&lt;&gt;17,LEN($E129)-LEN(SUBSTITUTE($E129,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5289,11 +5691,14 @@
       <c r="J130" s="24" t="n"/>
       <c r="K130" s="24" t="n"/>
       <c r="L130" s="24" t="n"/>
-      <c r="N130">
-        <f>IF(COUNTA($A130:$L130)=0,0,IF(OR($B130="",$D130="",$F130="",$G130=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O130">
+      <c r="M130" s="24" t="n"/>
+      <c r="N130" s="24" t="n"/>
+      <c r="O130" s="24" t="n"/>
+      <c r="P130">
+        <f>IF(COUNTA($A130:$O130)=0,0,IF(OR($B130="",$D130="",$F130="",$G130=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q130">
         <f>IF(OR(AND($D130&lt;&gt;"",OR(LEN($D130)&lt;&gt;17,LEN($D130)-LEN(SUBSTITUTE($D130,":",""))&lt;&gt;5)),AND($E130&lt;&gt;"",OR(LEN($E130)&lt;&gt;17,LEN($E130)-LEN(SUBSTITUTE($E130,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5311,11 +5716,14 @@
       <c r="J131" s="24" t="n"/>
       <c r="K131" s="24" t="n"/>
       <c r="L131" s="24" t="n"/>
-      <c r="N131">
-        <f>IF(COUNTA($A131:$L131)=0,0,IF(OR($B131="",$D131="",$F131="",$G131=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O131">
+      <c r="M131" s="24" t="n"/>
+      <c r="N131" s="24" t="n"/>
+      <c r="O131" s="24" t="n"/>
+      <c r="P131">
+        <f>IF(COUNTA($A131:$O131)=0,0,IF(OR($B131="",$D131="",$F131="",$G131=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q131">
         <f>IF(OR(AND($D131&lt;&gt;"",OR(LEN($D131)&lt;&gt;17,LEN($D131)-LEN(SUBSTITUTE($D131,":",""))&lt;&gt;5)),AND($E131&lt;&gt;"",OR(LEN($E131)&lt;&gt;17,LEN($E131)-LEN(SUBSTITUTE($E131,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5333,11 +5741,14 @@
       <c r="J132" s="24" t="n"/>
       <c r="K132" s="24" t="n"/>
       <c r="L132" s="24" t="n"/>
-      <c r="N132">
-        <f>IF(COUNTA($A132:$L132)=0,0,IF(OR($B132="",$D132="",$F132="",$G132=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O132">
+      <c r="M132" s="24" t="n"/>
+      <c r="N132" s="24" t="n"/>
+      <c r="O132" s="24" t="n"/>
+      <c r="P132">
+        <f>IF(COUNTA($A132:$O132)=0,0,IF(OR($B132="",$D132="",$F132="",$G132=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q132">
         <f>IF(OR(AND($D132&lt;&gt;"",OR(LEN($D132)&lt;&gt;17,LEN($D132)-LEN(SUBSTITUTE($D132,":",""))&lt;&gt;5)),AND($E132&lt;&gt;"",OR(LEN($E132)&lt;&gt;17,LEN($E132)-LEN(SUBSTITUTE($E132,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5355,11 +5766,14 @@
       <c r="J133" s="24" t="n"/>
       <c r="K133" s="24" t="n"/>
       <c r="L133" s="24" t="n"/>
-      <c r="N133">
-        <f>IF(COUNTA($A133:$L133)=0,0,IF(OR($B133="",$D133="",$F133="",$G133=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O133">
+      <c r="M133" s="24" t="n"/>
+      <c r="N133" s="24" t="n"/>
+      <c r="O133" s="24" t="n"/>
+      <c r="P133">
+        <f>IF(COUNTA($A133:$O133)=0,0,IF(OR($B133="",$D133="",$F133="",$G133=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q133">
         <f>IF(OR(AND($D133&lt;&gt;"",OR(LEN($D133)&lt;&gt;17,LEN($D133)-LEN(SUBSTITUTE($D133,":",""))&lt;&gt;5)),AND($E133&lt;&gt;"",OR(LEN($E133)&lt;&gt;17,LEN($E133)-LEN(SUBSTITUTE($E133,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5377,11 +5791,14 @@
       <c r="J134" s="24" t="n"/>
       <c r="K134" s="24" t="n"/>
       <c r="L134" s="24" t="n"/>
-      <c r="N134">
-        <f>IF(COUNTA($A134:$L134)=0,0,IF(OR($B134="",$D134="",$F134="",$G134=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O134">
+      <c r="M134" s="24" t="n"/>
+      <c r="N134" s="24" t="n"/>
+      <c r="O134" s="24" t="n"/>
+      <c r="P134">
+        <f>IF(COUNTA($A134:$O134)=0,0,IF(OR($B134="",$D134="",$F134="",$G134=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q134">
         <f>IF(OR(AND($D134&lt;&gt;"",OR(LEN($D134)&lt;&gt;17,LEN($D134)-LEN(SUBSTITUTE($D134,":",""))&lt;&gt;5)),AND($E134&lt;&gt;"",OR(LEN($E134)&lt;&gt;17,LEN($E134)-LEN(SUBSTITUTE($E134,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5399,11 +5816,14 @@
       <c r="J135" s="24" t="n"/>
       <c r="K135" s="24" t="n"/>
       <c r="L135" s="24" t="n"/>
-      <c r="N135">
-        <f>IF(COUNTA($A135:$L135)=0,0,IF(OR($B135="",$D135="",$F135="",$G135=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O135">
+      <c r="M135" s="24" t="n"/>
+      <c r="N135" s="24" t="n"/>
+      <c r="O135" s="24" t="n"/>
+      <c r="P135">
+        <f>IF(COUNTA($A135:$O135)=0,0,IF(OR($B135="",$D135="",$F135="",$G135=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q135">
         <f>IF(OR(AND($D135&lt;&gt;"",OR(LEN($D135)&lt;&gt;17,LEN($D135)-LEN(SUBSTITUTE($D135,":",""))&lt;&gt;5)),AND($E135&lt;&gt;"",OR(LEN($E135)&lt;&gt;17,LEN($E135)-LEN(SUBSTITUTE($E135,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5421,11 +5841,14 @@
       <c r="J136" s="24" t="n"/>
       <c r="K136" s="24" t="n"/>
       <c r="L136" s="24" t="n"/>
-      <c r="N136">
-        <f>IF(COUNTA($A136:$L136)=0,0,IF(OR($B136="",$D136="",$F136="",$G136=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O136">
+      <c r="M136" s="24" t="n"/>
+      <c r="N136" s="24" t="n"/>
+      <c r="O136" s="24" t="n"/>
+      <c r="P136">
+        <f>IF(COUNTA($A136:$O136)=0,0,IF(OR($B136="",$D136="",$F136="",$G136=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q136">
         <f>IF(OR(AND($D136&lt;&gt;"",OR(LEN($D136)&lt;&gt;17,LEN($D136)-LEN(SUBSTITUTE($D136,":",""))&lt;&gt;5)),AND($E136&lt;&gt;"",OR(LEN($E136)&lt;&gt;17,LEN($E136)-LEN(SUBSTITUTE($E136,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5443,11 +5866,14 @@
       <c r="J137" s="24" t="n"/>
       <c r="K137" s="24" t="n"/>
       <c r="L137" s="24" t="n"/>
-      <c r="N137">
-        <f>IF(COUNTA($A137:$L137)=0,0,IF(OR($B137="",$D137="",$F137="",$G137=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O137">
+      <c r="M137" s="24" t="n"/>
+      <c r="N137" s="24" t="n"/>
+      <c r="O137" s="24" t="n"/>
+      <c r="P137">
+        <f>IF(COUNTA($A137:$O137)=0,0,IF(OR($B137="",$D137="",$F137="",$G137=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q137">
         <f>IF(OR(AND($D137&lt;&gt;"",OR(LEN($D137)&lt;&gt;17,LEN($D137)-LEN(SUBSTITUTE($D137,":",""))&lt;&gt;5)),AND($E137&lt;&gt;"",OR(LEN($E137)&lt;&gt;17,LEN($E137)-LEN(SUBSTITUTE($E137,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5465,11 +5891,14 @@
       <c r="J138" s="24" t="n"/>
       <c r="K138" s="24" t="n"/>
       <c r="L138" s="24" t="n"/>
-      <c r="N138">
-        <f>IF(COUNTA($A138:$L138)=0,0,IF(OR($B138="",$D138="",$F138="",$G138=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O138">
+      <c r="M138" s="24" t="n"/>
+      <c r="N138" s="24" t="n"/>
+      <c r="O138" s="24" t="n"/>
+      <c r="P138">
+        <f>IF(COUNTA($A138:$O138)=0,0,IF(OR($B138="",$D138="",$F138="",$G138=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q138">
         <f>IF(OR(AND($D138&lt;&gt;"",OR(LEN($D138)&lt;&gt;17,LEN($D138)-LEN(SUBSTITUTE($D138,":",""))&lt;&gt;5)),AND($E138&lt;&gt;"",OR(LEN($E138)&lt;&gt;17,LEN($E138)-LEN(SUBSTITUTE($E138,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5487,11 +5916,14 @@
       <c r="J139" s="24" t="n"/>
       <c r="K139" s="24" t="n"/>
       <c r="L139" s="24" t="n"/>
-      <c r="N139">
-        <f>IF(COUNTA($A139:$L139)=0,0,IF(OR($B139="",$D139="",$F139="",$G139=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O139">
+      <c r="M139" s="24" t="n"/>
+      <c r="N139" s="24" t="n"/>
+      <c r="O139" s="24" t="n"/>
+      <c r="P139">
+        <f>IF(COUNTA($A139:$O139)=0,0,IF(OR($B139="",$D139="",$F139="",$G139=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q139">
         <f>IF(OR(AND($D139&lt;&gt;"",OR(LEN($D139)&lt;&gt;17,LEN($D139)-LEN(SUBSTITUTE($D139,":",""))&lt;&gt;5)),AND($E139&lt;&gt;"",OR(LEN($E139)&lt;&gt;17,LEN($E139)-LEN(SUBSTITUTE($E139,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5509,11 +5941,14 @@
       <c r="J140" s="24" t="n"/>
       <c r="K140" s="24" t="n"/>
       <c r="L140" s="24" t="n"/>
-      <c r="N140">
-        <f>IF(COUNTA($A140:$L140)=0,0,IF(OR($B140="",$D140="",$F140="",$G140=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O140">
+      <c r="M140" s="24" t="n"/>
+      <c r="N140" s="24" t="n"/>
+      <c r="O140" s="24" t="n"/>
+      <c r="P140">
+        <f>IF(COUNTA($A140:$O140)=0,0,IF(OR($B140="",$D140="",$F140="",$G140=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q140">
         <f>IF(OR(AND($D140&lt;&gt;"",OR(LEN($D140)&lt;&gt;17,LEN($D140)-LEN(SUBSTITUTE($D140,":",""))&lt;&gt;5)),AND($E140&lt;&gt;"",OR(LEN($E140)&lt;&gt;17,LEN($E140)-LEN(SUBSTITUTE($E140,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5531,11 +5966,14 @@
       <c r="J141" s="24" t="n"/>
       <c r="K141" s="24" t="n"/>
       <c r="L141" s="24" t="n"/>
-      <c r="N141">
-        <f>IF(COUNTA($A141:$L141)=0,0,IF(OR($B141="",$D141="",$F141="",$G141=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O141">
+      <c r="M141" s="24" t="n"/>
+      <c r="N141" s="24" t="n"/>
+      <c r="O141" s="24" t="n"/>
+      <c r="P141">
+        <f>IF(COUNTA($A141:$O141)=0,0,IF(OR($B141="",$D141="",$F141="",$G141=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q141">
         <f>IF(OR(AND($D141&lt;&gt;"",OR(LEN($D141)&lt;&gt;17,LEN($D141)-LEN(SUBSTITUTE($D141,":",""))&lt;&gt;5)),AND($E141&lt;&gt;"",OR(LEN($E141)&lt;&gt;17,LEN($E141)-LEN(SUBSTITUTE($E141,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5553,11 +5991,14 @@
       <c r="J142" s="24" t="n"/>
       <c r="K142" s="24" t="n"/>
       <c r="L142" s="24" t="n"/>
-      <c r="N142">
-        <f>IF(COUNTA($A142:$L142)=0,0,IF(OR($B142="",$D142="",$F142="",$G142=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O142">
+      <c r="M142" s="24" t="n"/>
+      <c r="N142" s="24" t="n"/>
+      <c r="O142" s="24" t="n"/>
+      <c r="P142">
+        <f>IF(COUNTA($A142:$O142)=0,0,IF(OR($B142="",$D142="",$F142="",$G142=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q142">
         <f>IF(OR(AND($D142&lt;&gt;"",OR(LEN($D142)&lt;&gt;17,LEN($D142)-LEN(SUBSTITUTE($D142,":",""))&lt;&gt;5)),AND($E142&lt;&gt;"",OR(LEN($E142)&lt;&gt;17,LEN($E142)-LEN(SUBSTITUTE($E142,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5575,11 +6016,14 @@
       <c r="J143" s="24" t="n"/>
       <c r="K143" s="24" t="n"/>
       <c r="L143" s="24" t="n"/>
-      <c r="N143">
-        <f>IF(COUNTA($A143:$L143)=0,0,IF(OR($B143="",$D143="",$F143="",$G143=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O143">
+      <c r="M143" s="24" t="n"/>
+      <c r="N143" s="24" t="n"/>
+      <c r="O143" s="24" t="n"/>
+      <c r="P143">
+        <f>IF(COUNTA($A143:$O143)=0,0,IF(OR($B143="",$D143="",$F143="",$G143=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q143">
         <f>IF(OR(AND($D143&lt;&gt;"",OR(LEN($D143)&lt;&gt;17,LEN($D143)-LEN(SUBSTITUTE($D143,":",""))&lt;&gt;5)),AND($E143&lt;&gt;"",OR(LEN($E143)&lt;&gt;17,LEN($E143)-LEN(SUBSTITUTE($E143,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5597,11 +6041,14 @@
       <c r="J144" s="24" t="n"/>
       <c r="K144" s="24" t="n"/>
       <c r="L144" s="24" t="n"/>
-      <c r="N144">
-        <f>IF(COUNTA($A144:$L144)=0,0,IF(OR($B144="",$D144="",$F144="",$G144=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O144">
+      <c r="M144" s="24" t="n"/>
+      <c r="N144" s="24" t="n"/>
+      <c r="O144" s="24" t="n"/>
+      <c r="P144">
+        <f>IF(COUNTA($A144:$O144)=0,0,IF(OR($B144="",$D144="",$F144="",$G144=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q144">
         <f>IF(OR(AND($D144&lt;&gt;"",OR(LEN($D144)&lt;&gt;17,LEN($D144)-LEN(SUBSTITUTE($D144,":",""))&lt;&gt;5)),AND($E144&lt;&gt;"",OR(LEN($E144)&lt;&gt;17,LEN($E144)-LEN(SUBSTITUTE($E144,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5619,11 +6066,14 @@
       <c r="J145" s="24" t="n"/>
       <c r="K145" s="24" t="n"/>
       <c r="L145" s="24" t="n"/>
-      <c r="N145">
-        <f>IF(COUNTA($A145:$L145)=0,0,IF(OR($B145="",$D145="",$F145="",$G145=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O145">
+      <c r="M145" s="24" t="n"/>
+      <c r="N145" s="24" t="n"/>
+      <c r="O145" s="24" t="n"/>
+      <c r="P145">
+        <f>IF(COUNTA($A145:$O145)=0,0,IF(OR($B145="",$D145="",$F145="",$G145=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q145">
         <f>IF(OR(AND($D145&lt;&gt;"",OR(LEN($D145)&lt;&gt;17,LEN($D145)-LEN(SUBSTITUTE($D145,":",""))&lt;&gt;5)),AND($E145&lt;&gt;"",OR(LEN($E145)&lt;&gt;17,LEN($E145)-LEN(SUBSTITUTE($E145,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5641,11 +6091,14 @@
       <c r="J146" s="24" t="n"/>
       <c r="K146" s="24" t="n"/>
       <c r="L146" s="24" t="n"/>
-      <c r="N146">
-        <f>IF(COUNTA($A146:$L146)=0,0,IF(OR($B146="",$D146="",$F146="",$G146=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O146">
+      <c r="M146" s="24" t="n"/>
+      <c r="N146" s="24" t="n"/>
+      <c r="O146" s="24" t="n"/>
+      <c r="P146">
+        <f>IF(COUNTA($A146:$O146)=0,0,IF(OR($B146="",$D146="",$F146="",$G146=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q146">
         <f>IF(OR(AND($D146&lt;&gt;"",OR(LEN($D146)&lt;&gt;17,LEN($D146)-LEN(SUBSTITUTE($D146,":",""))&lt;&gt;5)),AND($E146&lt;&gt;"",OR(LEN($E146)&lt;&gt;17,LEN($E146)-LEN(SUBSTITUTE($E146,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5663,11 +6116,14 @@
       <c r="J147" s="24" t="n"/>
       <c r="K147" s="24" t="n"/>
       <c r="L147" s="24" t="n"/>
-      <c r="N147">
-        <f>IF(COUNTA($A147:$L147)=0,0,IF(OR($B147="",$D147="",$F147="",$G147=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O147">
+      <c r="M147" s="24" t="n"/>
+      <c r="N147" s="24" t="n"/>
+      <c r="O147" s="24" t="n"/>
+      <c r="P147">
+        <f>IF(COUNTA($A147:$O147)=0,0,IF(OR($B147="",$D147="",$F147="",$G147=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q147">
         <f>IF(OR(AND($D147&lt;&gt;"",OR(LEN($D147)&lt;&gt;17,LEN($D147)-LEN(SUBSTITUTE($D147,":",""))&lt;&gt;5)),AND($E147&lt;&gt;"",OR(LEN($E147)&lt;&gt;17,LEN($E147)-LEN(SUBSTITUTE($E147,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5685,11 +6141,14 @@
       <c r="J148" s="24" t="n"/>
       <c r="K148" s="24" t="n"/>
       <c r="L148" s="24" t="n"/>
-      <c r="N148">
-        <f>IF(COUNTA($A148:$L148)=0,0,IF(OR($B148="",$D148="",$F148="",$G148=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O148">
+      <c r="M148" s="24" t="n"/>
+      <c r="N148" s="24" t="n"/>
+      <c r="O148" s="24" t="n"/>
+      <c r="P148">
+        <f>IF(COUNTA($A148:$O148)=0,0,IF(OR($B148="",$D148="",$F148="",$G148=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q148">
         <f>IF(OR(AND($D148&lt;&gt;"",OR(LEN($D148)&lt;&gt;17,LEN($D148)-LEN(SUBSTITUTE($D148,":",""))&lt;&gt;5)),AND($E148&lt;&gt;"",OR(LEN($E148)&lt;&gt;17,LEN($E148)-LEN(SUBSTITUTE($E148,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5707,11 +6166,14 @@
       <c r="J149" s="24" t="n"/>
       <c r="K149" s="24" t="n"/>
       <c r="L149" s="24" t="n"/>
-      <c r="N149">
-        <f>IF(COUNTA($A149:$L149)=0,0,IF(OR($B149="",$D149="",$F149="",$G149=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O149">
+      <c r="M149" s="24" t="n"/>
+      <c r="N149" s="24" t="n"/>
+      <c r="O149" s="24" t="n"/>
+      <c r="P149">
+        <f>IF(COUNTA($A149:$O149)=0,0,IF(OR($B149="",$D149="",$F149="",$G149=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q149">
         <f>IF(OR(AND($D149&lt;&gt;"",OR(LEN($D149)&lt;&gt;17,LEN($D149)-LEN(SUBSTITUTE($D149,":",""))&lt;&gt;5)),AND($E149&lt;&gt;"",OR(LEN($E149)&lt;&gt;17,LEN($E149)-LEN(SUBSTITUTE($E149,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5729,11 +6191,14 @@
       <c r="J150" s="24" t="n"/>
       <c r="K150" s="24" t="n"/>
       <c r="L150" s="24" t="n"/>
-      <c r="N150">
-        <f>IF(COUNTA($A150:$L150)=0,0,IF(OR($B150="",$D150="",$F150="",$G150=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O150">
+      <c r="M150" s="24" t="n"/>
+      <c r="N150" s="24" t="n"/>
+      <c r="O150" s="24" t="n"/>
+      <c r="P150">
+        <f>IF(COUNTA($A150:$O150)=0,0,IF(OR($B150="",$D150="",$F150="",$G150=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q150">
         <f>IF(OR(AND($D150&lt;&gt;"",OR(LEN($D150)&lt;&gt;17,LEN($D150)-LEN(SUBSTITUTE($D150,":",""))&lt;&gt;5)),AND($E150&lt;&gt;"",OR(LEN($E150)&lt;&gt;17,LEN($E150)-LEN(SUBSTITUTE($E150,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5751,11 +6216,14 @@
       <c r="J151" s="24" t="n"/>
       <c r="K151" s="24" t="n"/>
       <c r="L151" s="24" t="n"/>
-      <c r="N151">
-        <f>IF(COUNTA($A151:$L151)=0,0,IF(OR($B151="",$D151="",$F151="",$G151=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O151">
+      <c r="M151" s="24" t="n"/>
+      <c r="N151" s="24" t="n"/>
+      <c r="O151" s="24" t="n"/>
+      <c r="P151">
+        <f>IF(COUNTA($A151:$O151)=0,0,IF(OR($B151="",$D151="",$F151="",$G151=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q151">
         <f>IF(OR(AND($D151&lt;&gt;"",OR(LEN($D151)&lt;&gt;17,LEN($D151)-LEN(SUBSTITUTE($D151,":",""))&lt;&gt;5)),AND($E151&lt;&gt;"",OR(LEN($E151)&lt;&gt;17,LEN($E151)-LEN(SUBSTITUTE($E151,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5773,11 +6241,14 @@
       <c r="J152" s="24" t="n"/>
       <c r="K152" s="24" t="n"/>
       <c r="L152" s="24" t="n"/>
-      <c r="N152">
-        <f>IF(COUNTA($A152:$L152)=0,0,IF(OR($B152="",$D152="",$F152="",$G152=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O152">
+      <c r="M152" s="24" t="n"/>
+      <c r="N152" s="24" t="n"/>
+      <c r="O152" s="24" t="n"/>
+      <c r="P152">
+        <f>IF(COUNTA($A152:$O152)=0,0,IF(OR($B152="",$D152="",$F152="",$G152=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q152">
         <f>IF(OR(AND($D152&lt;&gt;"",OR(LEN($D152)&lt;&gt;17,LEN($D152)-LEN(SUBSTITUTE($D152,":",""))&lt;&gt;5)),AND($E152&lt;&gt;"",OR(LEN($E152)&lt;&gt;17,LEN($E152)-LEN(SUBSTITUTE($E152,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5795,11 +6266,14 @@
       <c r="J153" s="24" t="n"/>
       <c r="K153" s="24" t="n"/>
       <c r="L153" s="24" t="n"/>
-      <c r="N153">
-        <f>IF(COUNTA($A153:$L153)=0,0,IF(OR($B153="",$D153="",$F153="",$G153=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O153">
+      <c r="M153" s="24" t="n"/>
+      <c r="N153" s="24" t="n"/>
+      <c r="O153" s="24" t="n"/>
+      <c r="P153">
+        <f>IF(COUNTA($A153:$O153)=0,0,IF(OR($B153="",$D153="",$F153="",$G153=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q153">
         <f>IF(OR(AND($D153&lt;&gt;"",OR(LEN($D153)&lt;&gt;17,LEN($D153)-LEN(SUBSTITUTE($D153,":",""))&lt;&gt;5)),AND($E153&lt;&gt;"",OR(LEN($E153)&lt;&gt;17,LEN($E153)-LEN(SUBSTITUTE($E153,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5817,11 +6291,14 @@
       <c r="J154" s="24" t="n"/>
       <c r="K154" s="24" t="n"/>
       <c r="L154" s="24" t="n"/>
-      <c r="N154">
-        <f>IF(COUNTA($A154:$L154)=0,0,IF(OR($B154="",$D154="",$F154="",$G154=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O154">
+      <c r="M154" s="24" t="n"/>
+      <c r="N154" s="24" t="n"/>
+      <c r="O154" s="24" t="n"/>
+      <c r="P154">
+        <f>IF(COUNTA($A154:$O154)=0,0,IF(OR($B154="",$D154="",$F154="",$G154=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q154">
         <f>IF(OR(AND($D154&lt;&gt;"",OR(LEN($D154)&lt;&gt;17,LEN($D154)-LEN(SUBSTITUTE($D154,":",""))&lt;&gt;5)),AND($E154&lt;&gt;"",OR(LEN($E154)&lt;&gt;17,LEN($E154)-LEN(SUBSTITUTE($E154,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5839,11 +6316,14 @@
       <c r="J155" s="24" t="n"/>
       <c r="K155" s="24" t="n"/>
       <c r="L155" s="24" t="n"/>
-      <c r="N155">
-        <f>IF(COUNTA($A155:$L155)=0,0,IF(OR($B155="",$D155="",$F155="",$G155=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O155">
+      <c r="M155" s="24" t="n"/>
+      <c r="N155" s="24" t="n"/>
+      <c r="O155" s="24" t="n"/>
+      <c r="P155">
+        <f>IF(COUNTA($A155:$O155)=0,0,IF(OR($B155="",$D155="",$F155="",$G155=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q155">
         <f>IF(OR(AND($D155&lt;&gt;"",OR(LEN($D155)&lt;&gt;17,LEN($D155)-LEN(SUBSTITUTE($D155,":",""))&lt;&gt;5)),AND($E155&lt;&gt;"",OR(LEN($E155)&lt;&gt;17,LEN($E155)-LEN(SUBSTITUTE($E155,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5861,11 +6341,14 @@
       <c r="J156" s="24" t="n"/>
       <c r="K156" s="24" t="n"/>
       <c r="L156" s="24" t="n"/>
-      <c r="N156">
-        <f>IF(COUNTA($A156:$L156)=0,0,IF(OR($B156="",$D156="",$F156="",$G156=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O156">
+      <c r="M156" s="24" t="n"/>
+      <c r="N156" s="24" t="n"/>
+      <c r="O156" s="24" t="n"/>
+      <c r="P156">
+        <f>IF(COUNTA($A156:$O156)=0,0,IF(OR($B156="",$D156="",$F156="",$G156=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q156">
         <f>IF(OR(AND($D156&lt;&gt;"",OR(LEN($D156)&lt;&gt;17,LEN($D156)-LEN(SUBSTITUTE($D156,":",""))&lt;&gt;5)),AND($E156&lt;&gt;"",OR(LEN($E156)&lt;&gt;17,LEN($E156)-LEN(SUBSTITUTE($E156,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5883,11 +6366,14 @@
       <c r="J157" s="24" t="n"/>
       <c r="K157" s="24" t="n"/>
       <c r="L157" s="24" t="n"/>
-      <c r="N157">
-        <f>IF(COUNTA($A157:$L157)=0,0,IF(OR($B157="",$D157="",$F157="",$G157=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O157">
+      <c r="M157" s="24" t="n"/>
+      <c r="N157" s="24" t="n"/>
+      <c r="O157" s="24" t="n"/>
+      <c r="P157">
+        <f>IF(COUNTA($A157:$O157)=0,0,IF(OR($B157="",$D157="",$F157="",$G157=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q157">
         <f>IF(OR(AND($D157&lt;&gt;"",OR(LEN($D157)&lt;&gt;17,LEN($D157)-LEN(SUBSTITUTE($D157,":",""))&lt;&gt;5)),AND($E157&lt;&gt;"",OR(LEN($E157)&lt;&gt;17,LEN($E157)-LEN(SUBSTITUTE($E157,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5905,11 +6391,14 @@
       <c r="J158" s="24" t="n"/>
       <c r="K158" s="24" t="n"/>
       <c r="L158" s="24" t="n"/>
-      <c r="N158">
-        <f>IF(COUNTA($A158:$L158)=0,0,IF(OR($B158="",$D158="",$F158="",$G158=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O158">
+      <c r="M158" s="24" t="n"/>
+      <c r="N158" s="24" t="n"/>
+      <c r="O158" s="24" t="n"/>
+      <c r="P158">
+        <f>IF(COUNTA($A158:$O158)=0,0,IF(OR($B158="",$D158="",$F158="",$G158=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q158">
         <f>IF(OR(AND($D158&lt;&gt;"",OR(LEN($D158)&lt;&gt;17,LEN($D158)-LEN(SUBSTITUTE($D158,":",""))&lt;&gt;5)),AND($E158&lt;&gt;"",OR(LEN($E158)&lt;&gt;17,LEN($E158)-LEN(SUBSTITUTE($E158,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5927,11 +6416,14 @@
       <c r="J159" s="24" t="n"/>
       <c r="K159" s="24" t="n"/>
       <c r="L159" s="24" t="n"/>
-      <c r="N159">
-        <f>IF(COUNTA($A159:$L159)=0,0,IF(OR($B159="",$D159="",$F159="",$G159=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O159">
+      <c r="M159" s="24" t="n"/>
+      <c r="N159" s="24" t="n"/>
+      <c r="O159" s="24" t="n"/>
+      <c r="P159">
+        <f>IF(COUNTA($A159:$O159)=0,0,IF(OR($B159="",$D159="",$F159="",$G159=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q159">
         <f>IF(OR(AND($D159&lt;&gt;"",OR(LEN($D159)&lt;&gt;17,LEN($D159)-LEN(SUBSTITUTE($D159,":",""))&lt;&gt;5)),AND($E159&lt;&gt;"",OR(LEN($E159)&lt;&gt;17,LEN($E159)-LEN(SUBSTITUTE($E159,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5949,11 +6441,14 @@
       <c r="J160" s="24" t="n"/>
       <c r="K160" s="24" t="n"/>
       <c r="L160" s="24" t="n"/>
-      <c r="N160">
-        <f>IF(COUNTA($A160:$L160)=0,0,IF(OR($B160="",$D160="",$F160="",$G160=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O160">
+      <c r="M160" s="24" t="n"/>
+      <c r="N160" s="24" t="n"/>
+      <c r="O160" s="24" t="n"/>
+      <c r="P160">
+        <f>IF(COUNTA($A160:$O160)=0,0,IF(OR($B160="",$D160="",$F160="",$G160=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q160">
         <f>IF(OR(AND($D160&lt;&gt;"",OR(LEN($D160)&lt;&gt;17,LEN($D160)-LEN(SUBSTITUTE($D160,":",""))&lt;&gt;5)),AND($E160&lt;&gt;"",OR(LEN($E160)&lt;&gt;17,LEN($E160)-LEN(SUBSTITUTE($E160,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5971,11 +6466,14 @@
       <c r="J161" s="24" t="n"/>
       <c r="K161" s="24" t="n"/>
       <c r="L161" s="24" t="n"/>
-      <c r="N161">
-        <f>IF(COUNTA($A161:$L161)=0,0,IF(OR($B161="",$D161="",$F161="",$G161=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O161">
+      <c r="M161" s="24" t="n"/>
+      <c r="N161" s="24" t="n"/>
+      <c r="O161" s="24" t="n"/>
+      <c r="P161">
+        <f>IF(COUNTA($A161:$O161)=0,0,IF(OR($B161="",$D161="",$F161="",$G161=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q161">
         <f>IF(OR(AND($D161&lt;&gt;"",OR(LEN($D161)&lt;&gt;17,LEN($D161)-LEN(SUBSTITUTE($D161,":",""))&lt;&gt;5)),AND($E161&lt;&gt;"",OR(LEN($E161)&lt;&gt;17,LEN($E161)-LEN(SUBSTITUTE($E161,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5993,11 +6491,14 @@
       <c r="J162" s="24" t="n"/>
       <c r="K162" s="24" t="n"/>
       <c r="L162" s="24" t="n"/>
-      <c r="N162">
-        <f>IF(COUNTA($A162:$L162)=0,0,IF(OR($B162="",$D162="",$F162="",$G162=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O162">
+      <c r="M162" s="24" t="n"/>
+      <c r="N162" s="24" t="n"/>
+      <c r="O162" s="24" t="n"/>
+      <c r="P162">
+        <f>IF(COUNTA($A162:$O162)=0,0,IF(OR($B162="",$D162="",$F162="",$G162=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q162">
         <f>IF(OR(AND($D162&lt;&gt;"",OR(LEN($D162)&lt;&gt;17,LEN($D162)-LEN(SUBSTITUTE($D162,":",""))&lt;&gt;5)),AND($E162&lt;&gt;"",OR(LEN($E162)&lt;&gt;17,LEN($E162)-LEN(SUBSTITUTE($E162,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6015,11 +6516,14 @@
       <c r="J163" s="24" t="n"/>
       <c r="K163" s="24" t="n"/>
       <c r="L163" s="24" t="n"/>
-      <c r="N163">
-        <f>IF(COUNTA($A163:$L163)=0,0,IF(OR($B163="",$D163="",$F163="",$G163=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O163">
+      <c r="M163" s="24" t="n"/>
+      <c r="N163" s="24" t="n"/>
+      <c r="O163" s="24" t="n"/>
+      <c r="P163">
+        <f>IF(COUNTA($A163:$O163)=0,0,IF(OR($B163="",$D163="",$F163="",$G163=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q163">
         <f>IF(OR(AND($D163&lt;&gt;"",OR(LEN($D163)&lt;&gt;17,LEN($D163)-LEN(SUBSTITUTE($D163,":",""))&lt;&gt;5)),AND($E163&lt;&gt;"",OR(LEN($E163)&lt;&gt;17,LEN($E163)-LEN(SUBSTITUTE($E163,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6037,11 +6541,14 @@
       <c r="J164" s="24" t="n"/>
       <c r="K164" s="24" t="n"/>
       <c r="L164" s="24" t="n"/>
-      <c r="N164">
-        <f>IF(COUNTA($A164:$L164)=0,0,IF(OR($B164="",$D164="",$F164="",$G164=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O164">
+      <c r="M164" s="24" t="n"/>
+      <c r="N164" s="24" t="n"/>
+      <c r="O164" s="24" t="n"/>
+      <c r="P164">
+        <f>IF(COUNTA($A164:$O164)=0,0,IF(OR($B164="",$D164="",$F164="",$G164=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q164">
         <f>IF(OR(AND($D164&lt;&gt;"",OR(LEN($D164)&lt;&gt;17,LEN($D164)-LEN(SUBSTITUTE($D164,":",""))&lt;&gt;5)),AND($E164&lt;&gt;"",OR(LEN($E164)&lt;&gt;17,LEN($E164)-LEN(SUBSTITUTE($E164,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6059,11 +6566,14 @@
       <c r="J165" s="24" t="n"/>
       <c r="K165" s="24" t="n"/>
       <c r="L165" s="24" t="n"/>
-      <c r="N165">
-        <f>IF(COUNTA($A165:$L165)=0,0,IF(OR($B165="",$D165="",$F165="",$G165=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O165">
+      <c r="M165" s="24" t="n"/>
+      <c r="N165" s="24" t="n"/>
+      <c r="O165" s="24" t="n"/>
+      <c r="P165">
+        <f>IF(COUNTA($A165:$O165)=0,0,IF(OR($B165="",$D165="",$F165="",$G165=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q165">
         <f>IF(OR(AND($D165&lt;&gt;"",OR(LEN($D165)&lt;&gt;17,LEN($D165)-LEN(SUBSTITUTE($D165,":",""))&lt;&gt;5)),AND($E165&lt;&gt;"",OR(LEN($E165)&lt;&gt;17,LEN($E165)-LEN(SUBSTITUTE($E165,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6081,11 +6591,14 @@
       <c r="J166" s="24" t="n"/>
       <c r="K166" s="24" t="n"/>
       <c r="L166" s="24" t="n"/>
-      <c r="N166">
-        <f>IF(COUNTA($A166:$L166)=0,0,IF(OR($B166="",$D166="",$F166="",$G166=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O166">
+      <c r="M166" s="24" t="n"/>
+      <c r="N166" s="24" t="n"/>
+      <c r="O166" s="24" t="n"/>
+      <c r="P166">
+        <f>IF(COUNTA($A166:$O166)=0,0,IF(OR($B166="",$D166="",$F166="",$G166=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q166">
         <f>IF(OR(AND($D166&lt;&gt;"",OR(LEN($D166)&lt;&gt;17,LEN($D166)-LEN(SUBSTITUTE($D166,":",""))&lt;&gt;5)),AND($E166&lt;&gt;"",OR(LEN($E166)&lt;&gt;17,LEN($E166)-LEN(SUBSTITUTE($E166,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6103,11 +6616,14 @@
       <c r="J167" s="24" t="n"/>
       <c r="K167" s="24" t="n"/>
       <c r="L167" s="24" t="n"/>
-      <c r="N167">
-        <f>IF(COUNTA($A167:$L167)=0,0,IF(OR($B167="",$D167="",$F167="",$G167=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O167">
+      <c r="M167" s="24" t="n"/>
+      <c r="N167" s="24" t="n"/>
+      <c r="O167" s="24" t="n"/>
+      <c r="P167">
+        <f>IF(COUNTA($A167:$O167)=0,0,IF(OR($B167="",$D167="",$F167="",$G167=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q167">
         <f>IF(OR(AND($D167&lt;&gt;"",OR(LEN($D167)&lt;&gt;17,LEN($D167)-LEN(SUBSTITUTE($D167,":",""))&lt;&gt;5)),AND($E167&lt;&gt;"",OR(LEN($E167)&lt;&gt;17,LEN($E167)-LEN(SUBSTITUTE($E167,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6125,11 +6641,14 @@
       <c r="J168" s="24" t="n"/>
       <c r="K168" s="24" t="n"/>
       <c r="L168" s="24" t="n"/>
-      <c r="N168">
-        <f>IF(COUNTA($A168:$L168)=0,0,IF(OR($B168="",$D168="",$F168="",$G168=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O168">
+      <c r="M168" s="24" t="n"/>
+      <c r="N168" s="24" t="n"/>
+      <c r="O168" s="24" t="n"/>
+      <c r="P168">
+        <f>IF(COUNTA($A168:$O168)=0,0,IF(OR($B168="",$D168="",$F168="",$G168=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q168">
         <f>IF(OR(AND($D168&lt;&gt;"",OR(LEN($D168)&lt;&gt;17,LEN($D168)-LEN(SUBSTITUTE($D168,":",""))&lt;&gt;5)),AND($E168&lt;&gt;"",OR(LEN($E168)&lt;&gt;17,LEN($E168)-LEN(SUBSTITUTE($E168,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6147,11 +6666,14 @@
       <c r="J169" s="24" t="n"/>
       <c r="K169" s="24" t="n"/>
       <c r="L169" s="24" t="n"/>
-      <c r="N169">
-        <f>IF(COUNTA($A169:$L169)=0,0,IF(OR($B169="",$D169="",$F169="",$G169=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O169">
+      <c r="M169" s="24" t="n"/>
+      <c r="N169" s="24" t="n"/>
+      <c r="O169" s="24" t="n"/>
+      <c r="P169">
+        <f>IF(COUNTA($A169:$O169)=0,0,IF(OR($B169="",$D169="",$F169="",$G169=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q169">
         <f>IF(OR(AND($D169&lt;&gt;"",OR(LEN($D169)&lt;&gt;17,LEN($D169)-LEN(SUBSTITUTE($D169,":",""))&lt;&gt;5)),AND($E169&lt;&gt;"",OR(LEN($E169)&lt;&gt;17,LEN($E169)-LEN(SUBSTITUTE($E169,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6169,11 +6691,14 @@
       <c r="J170" s="24" t="n"/>
       <c r="K170" s="24" t="n"/>
       <c r="L170" s="24" t="n"/>
-      <c r="N170">
-        <f>IF(COUNTA($A170:$L170)=0,0,IF(OR($B170="",$D170="",$F170="",$G170=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O170">
+      <c r="M170" s="24" t="n"/>
+      <c r="N170" s="24" t="n"/>
+      <c r="O170" s="24" t="n"/>
+      <c r="P170">
+        <f>IF(COUNTA($A170:$O170)=0,0,IF(OR($B170="",$D170="",$F170="",$G170=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q170">
         <f>IF(OR(AND($D170&lt;&gt;"",OR(LEN($D170)&lt;&gt;17,LEN($D170)-LEN(SUBSTITUTE($D170,":",""))&lt;&gt;5)),AND($E170&lt;&gt;"",OR(LEN($E170)&lt;&gt;17,LEN($E170)-LEN(SUBSTITUTE($E170,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6191,11 +6716,14 @@
       <c r="J171" s="24" t="n"/>
       <c r="K171" s="24" t="n"/>
       <c r="L171" s="24" t="n"/>
-      <c r="N171">
-        <f>IF(COUNTA($A171:$L171)=0,0,IF(OR($B171="",$D171="",$F171="",$G171=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O171">
+      <c r="M171" s="24" t="n"/>
+      <c r="N171" s="24" t="n"/>
+      <c r="O171" s="24" t="n"/>
+      <c r="P171">
+        <f>IF(COUNTA($A171:$O171)=0,0,IF(OR($B171="",$D171="",$F171="",$G171=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q171">
         <f>IF(OR(AND($D171&lt;&gt;"",OR(LEN($D171)&lt;&gt;17,LEN($D171)-LEN(SUBSTITUTE($D171,":",""))&lt;&gt;5)),AND($E171&lt;&gt;"",OR(LEN($E171)&lt;&gt;17,LEN($E171)-LEN(SUBSTITUTE($E171,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6213,11 +6741,14 @@
       <c r="J172" s="24" t="n"/>
       <c r="K172" s="24" t="n"/>
       <c r="L172" s="24" t="n"/>
-      <c r="N172">
-        <f>IF(COUNTA($A172:$L172)=0,0,IF(OR($B172="",$D172="",$F172="",$G172=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O172">
+      <c r="M172" s="24" t="n"/>
+      <c r="N172" s="24" t="n"/>
+      <c r="O172" s="24" t="n"/>
+      <c r="P172">
+        <f>IF(COUNTA($A172:$O172)=0,0,IF(OR($B172="",$D172="",$F172="",$G172=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q172">
         <f>IF(OR(AND($D172&lt;&gt;"",OR(LEN($D172)&lt;&gt;17,LEN($D172)-LEN(SUBSTITUTE($D172,":",""))&lt;&gt;5)),AND($E172&lt;&gt;"",OR(LEN($E172)&lt;&gt;17,LEN($E172)-LEN(SUBSTITUTE($E172,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6235,11 +6766,14 @@
       <c r="J173" s="24" t="n"/>
       <c r="K173" s="24" t="n"/>
       <c r="L173" s="24" t="n"/>
-      <c r="N173">
-        <f>IF(COUNTA($A173:$L173)=0,0,IF(OR($B173="",$D173="",$F173="",$G173=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O173">
+      <c r="M173" s="24" t="n"/>
+      <c r="N173" s="24" t="n"/>
+      <c r="O173" s="24" t="n"/>
+      <c r="P173">
+        <f>IF(COUNTA($A173:$O173)=0,0,IF(OR($B173="",$D173="",$F173="",$G173=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q173">
         <f>IF(OR(AND($D173&lt;&gt;"",OR(LEN($D173)&lt;&gt;17,LEN($D173)-LEN(SUBSTITUTE($D173,":",""))&lt;&gt;5)),AND($E173&lt;&gt;"",OR(LEN($E173)&lt;&gt;17,LEN($E173)-LEN(SUBSTITUTE($E173,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6257,11 +6791,14 @@
       <c r="J174" s="24" t="n"/>
       <c r="K174" s="24" t="n"/>
       <c r="L174" s="24" t="n"/>
-      <c r="N174">
-        <f>IF(COUNTA($A174:$L174)=0,0,IF(OR($B174="",$D174="",$F174="",$G174=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O174">
+      <c r="M174" s="24" t="n"/>
+      <c r="N174" s="24" t="n"/>
+      <c r="O174" s="24" t="n"/>
+      <c r="P174">
+        <f>IF(COUNTA($A174:$O174)=0,0,IF(OR($B174="",$D174="",$F174="",$G174=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q174">
         <f>IF(OR(AND($D174&lt;&gt;"",OR(LEN($D174)&lt;&gt;17,LEN($D174)-LEN(SUBSTITUTE($D174,":",""))&lt;&gt;5)),AND($E174&lt;&gt;"",OR(LEN($E174)&lt;&gt;17,LEN($E174)-LEN(SUBSTITUTE($E174,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6279,11 +6816,14 @@
       <c r="J175" s="24" t="n"/>
       <c r="K175" s="24" t="n"/>
       <c r="L175" s="24" t="n"/>
-      <c r="N175">
-        <f>IF(COUNTA($A175:$L175)=0,0,IF(OR($B175="",$D175="",$F175="",$G175=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O175">
+      <c r="M175" s="24" t="n"/>
+      <c r="N175" s="24" t="n"/>
+      <c r="O175" s="24" t="n"/>
+      <c r="P175">
+        <f>IF(COUNTA($A175:$O175)=0,0,IF(OR($B175="",$D175="",$F175="",$G175=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q175">
         <f>IF(OR(AND($D175&lt;&gt;"",OR(LEN($D175)&lt;&gt;17,LEN($D175)-LEN(SUBSTITUTE($D175,":",""))&lt;&gt;5)),AND($E175&lt;&gt;"",OR(LEN($E175)&lt;&gt;17,LEN($E175)-LEN(SUBSTITUTE($E175,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6301,11 +6841,14 @@
       <c r="J176" s="24" t="n"/>
       <c r="K176" s="24" t="n"/>
       <c r="L176" s="24" t="n"/>
-      <c r="N176">
-        <f>IF(COUNTA($A176:$L176)=0,0,IF(OR($B176="",$D176="",$F176="",$G176=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O176">
+      <c r="M176" s="24" t="n"/>
+      <c r="N176" s="24" t="n"/>
+      <c r="O176" s="24" t="n"/>
+      <c r="P176">
+        <f>IF(COUNTA($A176:$O176)=0,0,IF(OR($B176="",$D176="",$F176="",$G176=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q176">
         <f>IF(OR(AND($D176&lt;&gt;"",OR(LEN($D176)&lt;&gt;17,LEN($D176)-LEN(SUBSTITUTE($D176,":",""))&lt;&gt;5)),AND($E176&lt;&gt;"",OR(LEN($E176)&lt;&gt;17,LEN($E176)-LEN(SUBSTITUTE($E176,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6323,11 +6866,14 @@
       <c r="J177" s="24" t="n"/>
       <c r="K177" s="24" t="n"/>
       <c r="L177" s="24" t="n"/>
-      <c r="N177">
-        <f>IF(COUNTA($A177:$L177)=0,0,IF(OR($B177="",$D177="",$F177="",$G177=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O177">
+      <c r="M177" s="24" t="n"/>
+      <c r="N177" s="24" t="n"/>
+      <c r="O177" s="24" t="n"/>
+      <c r="P177">
+        <f>IF(COUNTA($A177:$O177)=0,0,IF(OR($B177="",$D177="",$F177="",$G177=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q177">
         <f>IF(OR(AND($D177&lt;&gt;"",OR(LEN($D177)&lt;&gt;17,LEN($D177)-LEN(SUBSTITUTE($D177,":",""))&lt;&gt;5)),AND($E177&lt;&gt;"",OR(LEN($E177)&lt;&gt;17,LEN($E177)-LEN(SUBSTITUTE($E177,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6345,11 +6891,14 @@
       <c r="J178" s="24" t="n"/>
       <c r="K178" s="24" t="n"/>
       <c r="L178" s="24" t="n"/>
-      <c r="N178">
-        <f>IF(COUNTA($A178:$L178)=0,0,IF(OR($B178="",$D178="",$F178="",$G178=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O178">
+      <c r="M178" s="24" t="n"/>
+      <c r="N178" s="24" t="n"/>
+      <c r="O178" s="24" t="n"/>
+      <c r="P178">
+        <f>IF(COUNTA($A178:$O178)=0,0,IF(OR($B178="",$D178="",$F178="",$G178=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q178">
         <f>IF(OR(AND($D178&lt;&gt;"",OR(LEN($D178)&lt;&gt;17,LEN($D178)-LEN(SUBSTITUTE($D178,":",""))&lt;&gt;5)),AND($E178&lt;&gt;"",OR(LEN($E178)&lt;&gt;17,LEN($E178)-LEN(SUBSTITUTE($E178,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6367,11 +6916,14 @@
       <c r="J179" s="24" t="n"/>
       <c r="K179" s="24" t="n"/>
       <c r="L179" s="24" t="n"/>
-      <c r="N179">
-        <f>IF(COUNTA($A179:$L179)=0,0,IF(OR($B179="",$D179="",$F179="",$G179=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O179">
+      <c r="M179" s="24" t="n"/>
+      <c r="N179" s="24" t="n"/>
+      <c r="O179" s="24" t="n"/>
+      <c r="P179">
+        <f>IF(COUNTA($A179:$O179)=0,0,IF(OR($B179="",$D179="",$F179="",$G179=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q179">
         <f>IF(OR(AND($D179&lt;&gt;"",OR(LEN($D179)&lt;&gt;17,LEN($D179)-LEN(SUBSTITUTE($D179,":",""))&lt;&gt;5)),AND($E179&lt;&gt;"",OR(LEN($E179)&lt;&gt;17,LEN($E179)-LEN(SUBSTITUTE($E179,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6389,11 +6941,14 @@
       <c r="J180" s="24" t="n"/>
       <c r="K180" s="24" t="n"/>
       <c r="L180" s="24" t="n"/>
-      <c r="N180">
-        <f>IF(COUNTA($A180:$L180)=0,0,IF(OR($B180="",$D180="",$F180="",$G180=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O180">
+      <c r="M180" s="24" t="n"/>
+      <c r="N180" s="24" t="n"/>
+      <c r="O180" s="24" t="n"/>
+      <c r="P180">
+        <f>IF(COUNTA($A180:$O180)=0,0,IF(OR($B180="",$D180="",$F180="",$G180=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q180">
         <f>IF(OR(AND($D180&lt;&gt;"",OR(LEN($D180)&lt;&gt;17,LEN($D180)-LEN(SUBSTITUTE($D180,":",""))&lt;&gt;5)),AND($E180&lt;&gt;"",OR(LEN($E180)&lt;&gt;17,LEN($E180)-LEN(SUBSTITUTE($E180,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6411,11 +6966,14 @@
       <c r="J181" s="24" t="n"/>
       <c r="K181" s="24" t="n"/>
       <c r="L181" s="24" t="n"/>
-      <c r="N181">
-        <f>IF(COUNTA($A181:$L181)=0,0,IF(OR($B181="",$D181="",$F181="",$G181=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O181">
+      <c r="M181" s="24" t="n"/>
+      <c r="N181" s="24" t="n"/>
+      <c r="O181" s="24" t="n"/>
+      <c r="P181">
+        <f>IF(COUNTA($A181:$O181)=0,0,IF(OR($B181="",$D181="",$F181="",$G181=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q181">
         <f>IF(OR(AND($D181&lt;&gt;"",OR(LEN($D181)&lt;&gt;17,LEN($D181)-LEN(SUBSTITUTE($D181,":",""))&lt;&gt;5)),AND($E181&lt;&gt;"",OR(LEN($E181)&lt;&gt;17,LEN($E181)-LEN(SUBSTITUTE($E181,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6433,11 +6991,14 @@
       <c r="J182" s="24" t="n"/>
       <c r="K182" s="24" t="n"/>
       <c r="L182" s="24" t="n"/>
-      <c r="N182">
-        <f>IF(COUNTA($A182:$L182)=0,0,IF(OR($B182="",$D182="",$F182="",$G182=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O182">
+      <c r="M182" s="24" t="n"/>
+      <c r="N182" s="24" t="n"/>
+      <c r="O182" s="24" t="n"/>
+      <c r="P182">
+        <f>IF(COUNTA($A182:$O182)=0,0,IF(OR($B182="",$D182="",$F182="",$G182=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q182">
         <f>IF(OR(AND($D182&lt;&gt;"",OR(LEN($D182)&lt;&gt;17,LEN($D182)-LEN(SUBSTITUTE($D182,":",""))&lt;&gt;5)),AND($E182&lt;&gt;"",OR(LEN($E182)&lt;&gt;17,LEN($E182)-LEN(SUBSTITUTE($E182,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6455,11 +7016,14 @@
       <c r="J183" s="24" t="n"/>
       <c r="K183" s="24" t="n"/>
       <c r="L183" s="24" t="n"/>
-      <c r="N183">
-        <f>IF(COUNTA($A183:$L183)=0,0,IF(OR($B183="",$D183="",$F183="",$G183=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O183">
+      <c r="M183" s="24" t="n"/>
+      <c r="N183" s="24" t="n"/>
+      <c r="O183" s="24" t="n"/>
+      <c r="P183">
+        <f>IF(COUNTA($A183:$O183)=0,0,IF(OR($B183="",$D183="",$F183="",$G183=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q183">
         <f>IF(OR(AND($D183&lt;&gt;"",OR(LEN($D183)&lt;&gt;17,LEN($D183)-LEN(SUBSTITUTE($D183,":",""))&lt;&gt;5)),AND($E183&lt;&gt;"",OR(LEN($E183)&lt;&gt;17,LEN($E183)-LEN(SUBSTITUTE($E183,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6477,11 +7041,14 @@
       <c r="J184" s="24" t="n"/>
       <c r="K184" s="24" t="n"/>
       <c r="L184" s="24" t="n"/>
-      <c r="N184">
-        <f>IF(COUNTA($A184:$L184)=0,0,IF(OR($B184="",$D184="",$F184="",$G184=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O184">
+      <c r="M184" s="24" t="n"/>
+      <c r="N184" s="24" t="n"/>
+      <c r="O184" s="24" t="n"/>
+      <c r="P184">
+        <f>IF(COUNTA($A184:$O184)=0,0,IF(OR($B184="",$D184="",$F184="",$G184=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q184">
         <f>IF(OR(AND($D184&lt;&gt;"",OR(LEN($D184)&lt;&gt;17,LEN($D184)-LEN(SUBSTITUTE($D184,":",""))&lt;&gt;5)),AND($E184&lt;&gt;"",OR(LEN($E184)&lt;&gt;17,LEN($E184)-LEN(SUBSTITUTE($E184,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6499,11 +7066,14 @@
       <c r="J185" s="24" t="n"/>
       <c r="K185" s="24" t="n"/>
       <c r="L185" s="24" t="n"/>
-      <c r="N185">
-        <f>IF(COUNTA($A185:$L185)=0,0,IF(OR($B185="",$D185="",$F185="",$G185=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O185">
+      <c r="M185" s="24" t="n"/>
+      <c r="N185" s="24" t="n"/>
+      <c r="O185" s="24" t="n"/>
+      <c r="P185">
+        <f>IF(COUNTA($A185:$O185)=0,0,IF(OR($B185="",$D185="",$F185="",$G185=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q185">
         <f>IF(OR(AND($D185&lt;&gt;"",OR(LEN($D185)&lt;&gt;17,LEN($D185)-LEN(SUBSTITUTE($D185,":",""))&lt;&gt;5)),AND($E185&lt;&gt;"",OR(LEN($E185)&lt;&gt;17,LEN($E185)-LEN(SUBSTITUTE($E185,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6521,11 +7091,14 @@
       <c r="J186" s="24" t="n"/>
       <c r="K186" s="24" t="n"/>
       <c r="L186" s="24" t="n"/>
-      <c r="N186">
-        <f>IF(COUNTA($A186:$L186)=0,0,IF(OR($B186="",$D186="",$F186="",$G186=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O186">
+      <c r="M186" s="24" t="n"/>
+      <c r="N186" s="24" t="n"/>
+      <c r="O186" s="24" t="n"/>
+      <c r="P186">
+        <f>IF(COUNTA($A186:$O186)=0,0,IF(OR($B186="",$D186="",$F186="",$G186=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q186">
         <f>IF(OR(AND($D186&lt;&gt;"",OR(LEN($D186)&lt;&gt;17,LEN($D186)-LEN(SUBSTITUTE($D186,":",""))&lt;&gt;5)),AND($E186&lt;&gt;"",OR(LEN($E186)&lt;&gt;17,LEN($E186)-LEN(SUBSTITUTE($E186,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6543,11 +7116,14 @@
       <c r="J187" s="24" t="n"/>
       <c r="K187" s="24" t="n"/>
       <c r="L187" s="24" t="n"/>
-      <c r="N187">
-        <f>IF(COUNTA($A187:$L187)=0,0,IF(OR($B187="",$D187="",$F187="",$G187=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O187">
+      <c r="M187" s="24" t="n"/>
+      <c r="N187" s="24" t="n"/>
+      <c r="O187" s="24" t="n"/>
+      <c r="P187">
+        <f>IF(COUNTA($A187:$O187)=0,0,IF(OR($B187="",$D187="",$F187="",$G187=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q187">
         <f>IF(OR(AND($D187&lt;&gt;"",OR(LEN($D187)&lt;&gt;17,LEN($D187)-LEN(SUBSTITUTE($D187,":",""))&lt;&gt;5)),AND($E187&lt;&gt;"",OR(LEN($E187)&lt;&gt;17,LEN($E187)-LEN(SUBSTITUTE($E187,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6565,11 +7141,14 @@
       <c r="J188" s="24" t="n"/>
       <c r="K188" s="24" t="n"/>
       <c r="L188" s="24" t="n"/>
-      <c r="N188">
-        <f>IF(COUNTA($A188:$L188)=0,0,IF(OR($B188="",$D188="",$F188="",$G188=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O188">
+      <c r="M188" s="24" t="n"/>
+      <c r="N188" s="24" t="n"/>
+      <c r="O188" s="24" t="n"/>
+      <c r="P188">
+        <f>IF(COUNTA($A188:$O188)=0,0,IF(OR($B188="",$D188="",$F188="",$G188=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q188">
         <f>IF(OR(AND($D188&lt;&gt;"",OR(LEN($D188)&lt;&gt;17,LEN($D188)-LEN(SUBSTITUTE($D188,":",""))&lt;&gt;5)),AND($E188&lt;&gt;"",OR(LEN($E188)&lt;&gt;17,LEN($E188)-LEN(SUBSTITUTE($E188,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6587,11 +7166,14 @@
       <c r="J189" s="24" t="n"/>
       <c r="K189" s="24" t="n"/>
       <c r="L189" s="24" t="n"/>
-      <c r="N189">
-        <f>IF(COUNTA($A189:$L189)=0,0,IF(OR($B189="",$D189="",$F189="",$G189=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O189">
+      <c r="M189" s="24" t="n"/>
+      <c r="N189" s="24" t="n"/>
+      <c r="O189" s="24" t="n"/>
+      <c r="P189">
+        <f>IF(COUNTA($A189:$O189)=0,0,IF(OR($B189="",$D189="",$F189="",$G189=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q189">
         <f>IF(OR(AND($D189&lt;&gt;"",OR(LEN($D189)&lt;&gt;17,LEN($D189)-LEN(SUBSTITUTE($D189,":",""))&lt;&gt;5)),AND($E189&lt;&gt;"",OR(LEN($E189)&lt;&gt;17,LEN($E189)-LEN(SUBSTITUTE($E189,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6609,11 +7191,14 @@
       <c r="J190" s="24" t="n"/>
       <c r="K190" s="24" t="n"/>
       <c r="L190" s="24" t="n"/>
-      <c r="N190">
-        <f>IF(COUNTA($A190:$L190)=0,0,IF(OR($B190="",$D190="",$F190="",$G190=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O190">
+      <c r="M190" s="24" t="n"/>
+      <c r="N190" s="24" t="n"/>
+      <c r="O190" s="24" t="n"/>
+      <c r="P190">
+        <f>IF(COUNTA($A190:$O190)=0,0,IF(OR($B190="",$D190="",$F190="",$G190=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q190">
         <f>IF(OR(AND($D190&lt;&gt;"",OR(LEN($D190)&lt;&gt;17,LEN($D190)-LEN(SUBSTITUTE($D190,":",""))&lt;&gt;5)),AND($E190&lt;&gt;"",OR(LEN($E190)&lt;&gt;17,LEN($E190)-LEN(SUBSTITUTE($E190,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6631,11 +7216,14 @@
       <c r="J191" s="24" t="n"/>
       <c r="K191" s="24" t="n"/>
       <c r="L191" s="24" t="n"/>
-      <c r="N191">
-        <f>IF(COUNTA($A191:$L191)=0,0,IF(OR($B191="",$D191="",$F191="",$G191=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O191">
+      <c r="M191" s="24" t="n"/>
+      <c r="N191" s="24" t="n"/>
+      <c r="O191" s="24" t="n"/>
+      <c r="P191">
+        <f>IF(COUNTA($A191:$O191)=0,0,IF(OR($B191="",$D191="",$F191="",$G191=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q191">
         <f>IF(OR(AND($D191&lt;&gt;"",OR(LEN($D191)&lt;&gt;17,LEN($D191)-LEN(SUBSTITUTE($D191,":",""))&lt;&gt;5)),AND($E191&lt;&gt;"",OR(LEN($E191)&lt;&gt;17,LEN($E191)-LEN(SUBSTITUTE($E191,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6653,11 +7241,14 @@
       <c r="J192" s="24" t="n"/>
       <c r="K192" s="24" t="n"/>
       <c r="L192" s="24" t="n"/>
-      <c r="N192">
-        <f>IF(COUNTA($A192:$L192)=0,0,IF(OR($B192="",$D192="",$F192="",$G192=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O192">
+      <c r="M192" s="24" t="n"/>
+      <c r="N192" s="24" t="n"/>
+      <c r="O192" s="24" t="n"/>
+      <c r="P192">
+        <f>IF(COUNTA($A192:$O192)=0,0,IF(OR($B192="",$D192="",$F192="",$G192=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q192">
         <f>IF(OR(AND($D192&lt;&gt;"",OR(LEN($D192)&lt;&gt;17,LEN($D192)-LEN(SUBSTITUTE($D192,":",""))&lt;&gt;5)),AND($E192&lt;&gt;"",OR(LEN($E192)&lt;&gt;17,LEN($E192)-LEN(SUBSTITUTE($E192,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6675,11 +7266,14 @@
       <c r="J193" s="24" t="n"/>
       <c r="K193" s="24" t="n"/>
       <c r="L193" s="24" t="n"/>
-      <c r="N193">
-        <f>IF(COUNTA($A193:$L193)=0,0,IF(OR($B193="",$D193="",$F193="",$G193=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O193">
+      <c r="M193" s="24" t="n"/>
+      <c r="N193" s="24" t="n"/>
+      <c r="O193" s="24" t="n"/>
+      <c r="P193">
+        <f>IF(COUNTA($A193:$O193)=0,0,IF(OR($B193="",$D193="",$F193="",$G193=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q193">
         <f>IF(OR(AND($D193&lt;&gt;"",OR(LEN($D193)&lt;&gt;17,LEN($D193)-LEN(SUBSTITUTE($D193,":",""))&lt;&gt;5)),AND($E193&lt;&gt;"",OR(LEN($E193)&lt;&gt;17,LEN($E193)-LEN(SUBSTITUTE($E193,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6697,11 +7291,14 @@
       <c r="J194" s="24" t="n"/>
       <c r="K194" s="24" t="n"/>
       <c r="L194" s="24" t="n"/>
-      <c r="N194">
-        <f>IF(COUNTA($A194:$L194)=0,0,IF(OR($B194="",$D194="",$F194="",$G194=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O194">
+      <c r="M194" s="24" t="n"/>
+      <c r="N194" s="24" t="n"/>
+      <c r="O194" s="24" t="n"/>
+      <c r="P194">
+        <f>IF(COUNTA($A194:$O194)=0,0,IF(OR($B194="",$D194="",$F194="",$G194=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q194">
         <f>IF(OR(AND($D194&lt;&gt;"",OR(LEN($D194)&lt;&gt;17,LEN($D194)-LEN(SUBSTITUTE($D194,":",""))&lt;&gt;5)),AND($E194&lt;&gt;"",OR(LEN($E194)&lt;&gt;17,LEN($E194)-LEN(SUBSTITUTE($E194,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6719,11 +7316,14 @@
       <c r="J195" s="24" t="n"/>
       <c r="K195" s="24" t="n"/>
       <c r="L195" s="24" t="n"/>
-      <c r="N195">
-        <f>IF(COUNTA($A195:$L195)=0,0,IF(OR($B195="",$D195="",$F195="",$G195=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O195">
+      <c r="M195" s="24" t="n"/>
+      <c r="N195" s="24" t="n"/>
+      <c r="O195" s="24" t="n"/>
+      <c r="P195">
+        <f>IF(COUNTA($A195:$O195)=0,0,IF(OR($B195="",$D195="",$F195="",$G195=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q195">
         <f>IF(OR(AND($D195&lt;&gt;"",OR(LEN($D195)&lt;&gt;17,LEN($D195)-LEN(SUBSTITUTE($D195,":",""))&lt;&gt;5)),AND($E195&lt;&gt;"",OR(LEN($E195)&lt;&gt;17,LEN($E195)-LEN(SUBSTITUTE($E195,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6741,11 +7341,14 @@
       <c r="J196" s="24" t="n"/>
       <c r="K196" s="24" t="n"/>
       <c r="L196" s="24" t="n"/>
-      <c r="N196">
-        <f>IF(COUNTA($A196:$L196)=0,0,IF(OR($B196="",$D196="",$F196="",$G196=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O196">
+      <c r="M196" s="24" t="n"/>
+      <c r="N196" s="24" t="n"/>
+      <c r="O196" s="24" t="n"/>
+      <c r="P196">
+        <f>IF(COUNTA($A196:$O196)=0,0,IF(OR($B196="",$D196="",$F196="",$G196=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q196">
         <f>IF(OR(AND($D196&lt;&gt;"",OR(LEN($D196)&lt;&gt;17,LEN($D196)-LEN(SUBSTITUTE($D196,":",""))&lt;&gt;5)),AND($E196&lt;&gt;"",OR(LEN($E196)&lt;&gt;17,LEN($E196)-LEN(SUBSTITUTE($E196,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6763,11 +7366,14 @@
       <c r="J197" s="24" t="n"/>
       <c r="K197" s="24" t="n"/>
       <c r="L197" s="24" t="n"/>
-      <c r="N197">
-        <f>IF(COUNTA($A197:$L197)=0,0,IF(OR($B197="",$D197="",$F197="",$G197=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O197">
+      <c r="M197" s="24" t="n"/>
+      <c r="N197" s="24" t="n"/>
+      <c r="O197" s="24" t="n"/>
+      <c r="P197">
+        <f>IF(COUNTA($A197:$O197)=0,0,IF(OR($B197="",$D197="",$F197="",$G197=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q197">
         <f>IF(OR(AND($D197&lt;&gt;"",OR(LEN($D197)&lt;&gt;17,LEN($D197)-LEN(SUBSTITUTE($D197,":",""))&lt;&gt;5)),AND($E197&lt;&gt;"",OR(LEN($E197)&lt;&gt;17,LEN($E197)-LEN(SUBSTITUTE($E197,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6785,11 +7391,14 @@
       <c r="J198" s="24" t="n"/>
       <c r="K198" s="24" t="n"/>
       <c r="L198" s="24" t="n"/>
-      <c r="N198">
-        <f>IF(COUNTA($A198:$L198)=0,0,IF(OR($B198="",$D198="",$F198="",$G198=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O198">
+      <c r="M198" s="24" t="n"/>
+      <c r="N198" s="24" t="n"/>
+      <c r="O198" s="24" t="n"/>
+      <c r="P198">
+        <f>IF(COUNTA($A198:$O198)=0,0,IF(OR($B198="",$D198="",$F198="",$G198=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q198">
         <f>IF(OR(AND($D198&lt;&gt;"",OR(LEN($D198)&lt;&gt;17,LEN($D198)-LEN(SUBSTITUTE($D198,":",""))&lt;&gt;5)),AND($E198&lt;&gt;"",OR(LEN($E198)&lt;&gt;17,LEN($E198)-LEN(SUBSTITUTE($E198,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6807,11 +7416,14 @@
       <c r="J199" s="24" t="n"/>
       <c r="K199" s="24" t="n"/>
       <c r="L199" s="24" t="n"/>
-      <c r="N199">
-        <f>IF(COUNTA($A199:$L199)=0,0,IF(OR($B199="",$D199="",$F199="",$G199=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O199">
+      <c r="M199" s="24" t="n"/>
+      <c r="N199" s="24" t="n"/>
+      <c r="O199" s="24" t="n"/>
+      <c r="P199">
+        <f>IF(COUNTA($A199:$O199)=0,0,IF(OR($B199="",$D199="",$F199="",$G199=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q199">
         <f>IF(OR(AND($D199&lt;&gt;"",OR(LEN($D199)&lt;&gt;17,LEN($D199)-LEN(SUBSTITUTE($D199,":",""))&lt;&gt;5)),AND($E199&lt;&gt;"",OR(LEN($E199)&lt;&gt;17,LEN($E199)-LEN(SUBSTITUTE($E199,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6829,11 +7441,14 @@
       <c r="J200" s="24" t="n"/>
       <c r="K200" s="24" t="n"/>
       <c r="L200" s="24" t="n"/>
-      <c r="N200">
-        <f>IF(COUNTA($A200:$L200)=0,0,IF(OR($B200="",$D200="",$F200="",$G200=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O200">
+      <c r="M200" s="24" t="n"/>
+      <c r="N200" s="24" t="n"/>
+      <c r="O200" s="24" t="n"/>
+      <c r="P200">
+        <f>IF(COUNTA($A200:$O200)=0,0,IF(OR($B200="",$D200="",$F200="",$G200=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q200">
         <f>IF(OR(AND($D200&lt;&gt;"",OR(LEN($D200)&lt;&gt;17,LEN($D200)-LEN(SUBSTITUTE($D200,":",""))&lt;&gt;5)),AND($E200&lt;&gt;"",OR(LEN($E200)&lt;&gt;17,LEN($E200)-LEN(SUBSTITUTE($E200,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6851,11 +7466,14 @@
       <c r="J201" s="24" t="n"/>
       <c r="K201" s="24" t="n"/>
       <c r="L201" s="24" t="n"/>
-      <c r="N201">
-        <f>IF(COUNTA($A201:$L201)=0,0,IF(OR($B201="",$D201="",$F201="",$G201=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O201">
+      <c r="M201" s="24" t="n"/>
+      <c r="N201" s="24" t="n"/>
+      <c r="O201" s="24" t="n"/>
+      <c r="P201">
+        <f>IF(COUNTA($A201:$O201)=0,0,IF(OR($B201="",$D201="",$F201="",$G201=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q201">
         <f>IF(OR(AND($D201&lt;&gt;"",OR(LEN($D201)&lt;&gt;17,LEN($D201)-LEN(SUBSTITUTE($D201,":",""))&lt;&gt;5)),AND($E201&lt;&gt;"",OR(LEN($E201)&lt;&gt;17,LEN($E201)-LEN(SUBSTITUTE($E201,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6873,11 +7491,14 @@
       <c r="J202" s="24" t="n"/>
       <c r="K202" s="24" t="n"/>
       <c r="L202" s="24" t="n"/>
-      <c r="N202">
-        <f>IF(COUNTA($A202:$L202)=0,0,IF(OR($B202="",$D202="",$F202="",$G202=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O202">
+      <c r="M202" s="24" t="n"/>
+      <c r="N202" s="24" t="n"/>
+      <c r="O202" s="24" t="n"/>
+      <c r="P202">
+        <f>IF(COUNTA($A202:$O202)=0,0,IF(OR($B202="",$D202="",$F202="",$G202=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q202">
         <f>IF(OR(AND($D202&lt;&gt;"",OR(LEN($D202)&lt;&gt;17,LEN($D202)-LEN(SUBSTITUTE($D202,":",""))&lt;&gt;5)),AND($E202&lt;&gt;"",OR(LEN($E202)&lt;&gt;17,LEN($E202)-LEN(SUBSTITUTE($E202,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6895,11 +7516,14 @@
       <c r="J203" s="24" t="n"/>
       <c r="K203" s="24" t="n"/>
       <c r="L203" s="24" t="n"/>
-      <c r="N203">
-        <f>IF(COUNTA($A203:$L203)=0,0,IF(OR($B203="",$D203="",$F203="",$G203=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O203">
+      <c r="M203" s="24" t="n"/>
+      <c r="N203" s="24" t="n"/>
+      <c r="O203" s="24" t="n"/>
+      <c r="P203">
+        <f>IF(COUNTA($A203:$O203)=0,0,IF(OR($B203="",$D203="",$F203="",$G203=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q203">
         <f>IF(OR(AND($D203&lt;&gt;"",OR(LEN($D203)&lt;&gt;17,LEN($D203)-LEN(SUBSTITUTE($D203,":",""))&lt;&gt;5)),AND($E203&lt;&gt;"",OR(LEN($E203)&lt;&gt;17,LEN($E203)-LEN(SUBSTITUTE($E203,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6917,11 +7541,14 @@
       <c r="J204" s="24" t="n"/>
       <c r="K204" s="24" t="n"/>
       <c r="L204" s="24" t="n"/>
-      <c r="N204">
-        <f>IF(COUNTA($A204:$L204)=0,0,IF(OR($B204="",$D204="",$F204="",$G204=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O204">
+      <c r="M204" s="24" t="n"/>
+      <c r="N204" s="24" t="n"/>
+      <c r="O204" s="24" t="n"/>
+      <c r="P204">
+        <f>IF(COUNTA($A204:$O204)=0,0,IF(OR($B204="",$D204="",$F204="",$G204=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q204">
         <f>IF(OR(AND($D204&lt;&gt;"",OR(LEN($D204)&lt;&gt;17,LEN($D204)-LEN(SUBSTITUTE($D204,":",""))&lt;&gt;5)),AND($E204&lt;&gt;"",OR(LEN($E204)&lt;&gt;17,LEN($E204)-LEN(SUBSTITUTE($E204,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6939,11 +7566,14 @@
       <c r="J205" s="24" t="n"/>
       <c r="K205" s="24" t="n"/>
       <c r="L205" s="24" t="n"/>
-      <c r="N205">
-        <f>IF(COUNTA($A205:$L205)=0,0,IF(OR($B205="",$D205="",$F205="",$G205=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O205">
+      <c r="M205" s="24" t="n"/>
+      <c r="N205" s="24" t="n"/>
+      <c r="O205" s="24" t="n"/>
+      <c r="P205">
+        <f>IF(COUNTA($A205:$O205)=0,0,IF(OR($B205="",$D205="",$F205="",$G205=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q205">
         <f>IF(OR(AND($D205&lt;&gt;"",OR(LEN($D205)&lt;&gt;17,LEN($D205)-LEN(SUBSTITUTE($D205,":",""))&lt;&gt;5)),AND($E205&lt;&gt;"",OR(LEN($E205)&lt;&gt;17,LEN($E205)-LEN(SUBSTITUTE($E205,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6961,11 +7591,14 @@
       <c r="J206" s="24" t="n"/>
       <c r="K206" s="24" t="n"/>
       <c r="L206" s="24" t="n"/>
-      <c r="N206">
-        <f>IF(COUNTA($A206:$L206)=0,0,IF(OR($B206="",$D206="",$F206="",$G206=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O206">
+      <c r="M206" s="24" t="n"/>
+      <c r="N206" s="24" t="n"/>
+      <c r="O206" s="24" t="n"/>
+      <c r="P206">
+        <f>IF(COUNTA($A206:$O206)=0,0,IF(OR($B206="",$D206="",$F206="",$G206=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q206">
         <f>IF(OR(AND($D206&lt;&gt;"",OR(LEN($D206)&lt;&gt;17,LEN($D206)-LEN(SUBSTITUTE($D206,":",""))&lt;&gt;5)),AND($E206&lt;&gt;"",OR(LEN($E206)&lt;&gt;17,LEN($E206)-LEN(SUBSTITUTE($E206,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6983,11 +7616,14 @@
       <c r="J207" s="24" t="n"/>
       <c r="K207" s="24" t="n"/>
       <c r="L207" s="24" t="n"/>
-      <c r="N207">
-        <f>IF(COUNTA($A207:$L207)=0,0,IF(OR($B207="",$D207="",$F207="",$G207=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O207">
+      <c r="M207" s="24" t="n"/>
+      <c r="N207" s="24" t="n"/>
+      <c r="O207" s="24" t="n"/>
+      <c r="P207">
+        <f>IF(COUNTA($A207:$O207)=0,0,IF(OR($B207="",$D207="",$F207="",$G207=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q207">
         <f>IF(OR(AND($D207&lt;&gt;"",OR(LEN($D207)&lt;&gt;17,LEN($D207)-LEN(SUBSTITUTE($D207,":",""))&lt;&gt;5)),AND($E207&lt;&gt;"",OR(LEN($E207)&lt;&gt;17,LEN($E207)-LEN(SUBSTITUTE($E207,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7005,11 +7641,14 @@
       <c r="J208" s="24" t="n"/>
       <c r="K208" s="24" t="n"/>
       <c r="L208" s="24" t="n"/>
-      <c r="N208">
-        <f>IF(COUNTA($A208:$L208)=0,0,IF(OR($B208="",$D208="",$F208="",$G208=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O208">
+      <c r="M208" s="24" t="n"/>
+      <c r="N208" s="24" t="n"/>
+      <c r="O208" s="24" t="n"/>
+      <c r="P208">
+        <f>IF(COUNTA($A208:$O208)=0,0,IF(OR($B208="",$D208="",$F208="",$G208=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q208">
         <f>IF(OR(AND($D208&lt;&gt;"",OR(LEN($D208)&lt;&gt;17,LEN($D208)-LEN(SUBSTITUTE($D208,":",""))&lt;&gt;5)),AND($E208&lt;&gt;"",OR(LEN($E208)&lt;&gt;17,LEN($E208)-LEN(SUBSTITUTE($E208,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7027,11 +7666,14 @@
       <c r="J209" s="24" t="n"/>
       <c r="K209" s="24" t="n"/>
       <c r="L209" s="24" t="n"/>
-      <c r="N209">
-        <f>IF(COUNTA($A209:$L209)=0,0,IF(OR($B209="",$D209="",$F209="",$G209=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O209">
+      <c r="M209" s="24" t="n"/>
+      <c r="N209" s="24" t="n"/>
+      <c r="O209" s="24" t="n"/>
+      <c r="P209">
+        <f>IF(COUNTA($A209:$O209)=0,0,IF(OR($B209="",$D209="",$F209="",$G209=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q209">
         <f>IF(OR(AND($D209&lt;&gt;"",OR(LEN($D209)&lt;&gt;17,LEN($D209)-LEN(SUBSTITUTE($D209,":",""))&lt;&gt;5)),AND($E209&lt;&gt;"",OR(LEN($E209)&lt;&gt;17,LEN($E209)-LEN(SUBSTITUTE($E209,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7049,11 +7691,14 @@
       <c r="J210" s="24" t="n"/>
       <c r="K210" s="24" t="n"/>
       <c r="L210" s="24" t="n"/>
-      <c r="N210">
-        <f>IF(COUNTA($A210:$L210)=0,0,IF(OR($B210="",$D210="",$F210="",$G210=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O210">
+      <c r="M210" s="24" t="n"/>
+      <c r="N210" s="24" t="n"/>
+      <c r="O210" s="24" t="n"/>
+      <c r="P210">
+        <f>IF(COUNTA($A210:$O210)=0,0,IF(OR($B210="",$D210="",$F210="",$G210=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q210">
         <f>IF(OR(AND($D210&lt;&gt;"",OR(LEN($D210)&lt;&gt;17,LEN($D210)-LEN(SUBSTITUTE($D210,":",""))&lt;&gt;5)),AND($E210&lt;&gt;"",OR(LEN($E210)&lt;&gt;17,LEN($E210)-LEN(SUBSTITUTE($E210,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7071,11 +7716,14 @@
       <c r="J211" s="24" t="n"/>
       <c r="K211" s="24" t="n"/>
       <c r="L211" s="24" t="n"/>
-      <c r="N211">
-        <f>IF(COUNTA($A211:$L211)=0,0,IF(OR($B211="",$D211="",$F211="",$G211=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O211">
+      <c r="M211" s="24" t="n"/>
+      <c r="N211" s="24" t="n"/>
+      <c r="O211" s="24" t="n"/>
+      <c r="P211">
+        <f>IF(COUNTA($A211:$O211)=0,0,IF(OR($B211="",$D211="",$F211="",$G211=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q211">
         <f>IF(OR(AND($D211&lt;&gt;"",OR(LEN($D211)&lt;&gt;17,LEN($D211)-LEN(SUBSTITUTE($D211,":",""))&lt;&gt;5)),AND($E211&lt;&gt;"",OR(LEN($E211)&lt;&gt;17,LEN($E211)-LEN(SUBSTITUTE($E211,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7093,11 +7741,14 @@
       <c r="J212" s="24" t="n"/>
       <c r="K212" s="24" t="n"/>
       <c r="L212" s="24" t="n"/>
-      <c r="N212">
-        <f>IF(COUNTA($A212:$L212)=0,0,IF(OR($B212="",$D212="",$F212="",$G212=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O212">
+      <c r="M212" s="24" t="n"/>
+      <c r="N212" s="24" t="n"/>
+      <c r="O212" s="24" t="n"/>
+      <c r="P212">
+        <f>IF(COUNTA($A212:$O212)=0,0,IF(OR($B212="",$D212="",$F212="",$G212=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q212">
         <f>IF(OR(AND($D212&lt;&gt;"",OR(LEN($D212)&lt;&gt;17,LEN($D212)-LEN(SUBSTITUTE($D212,":",""))&lt;&gt;5)),AND($E212&lt;&gt;"",OR(LEN($E212)&lt;&gt;17,LEN($E212)-LEN(SUBSTITUTE($E212,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7115,11 +7766,14 @@
       <c r="J213" s="24" t="n"/>
       <c r="K213" s="24" t="n"/>
       <c r="L213" s="24" t="n"/>
-      <c r="N213">
-        <f>IF(COUNTA($A213:$L213)=0,0,IF(OR($B213="",$D213="",$F213="",$G213=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O213">
+      <c r="M213" s="24" t="n"/>
+      <c r="N213" s="24" t="n"/>
+      <c r="O213" s="24" t="n"/>
+      <c r="P213">
+        <f>IF(COUNTA($A213:$O213)=0,0,IF(OR($B213="",$D213="",$F213="",$G213=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q213">
         <f>IF(OR(AND($D213&lt;&gt;"",OR(LEN($D213)&lt;&gt;17,LEN($D213)-LEN(SUBSTITUTE($D213,":",""))&lt;&gt;5)),AND($E213&lt;&gt;"",OR(LEN($E213)&lt;&gt;17,LEN($E213)-LEN(SUBSTITUTE($E213,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7137,11 +7791,14 @@
       <c r="J214" s="24" t="n"/>
       <c r="K214" s="24" t="n"/>
       <c r="L214" s="24" t="n"/>
-      <c r="N214">
-        <f>IF(COUNTA($A214:$L214)=0,0,IF(OR($B214="",$D214="",$F214="",$G214=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O214">
+      <c r="M214" s="24" t="n"/>
+      <c r="N214" s="24" t="n"/>
+      <c r="O214" s="24" t="n"/>
+      <c r="P214">
+        <f>IF(COUNTA($A214:$O214)=0,0,IF(OR($B214="",$D214="",$F214="",$G214=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q214">
         <f>IF(OR(AND($D214&lt;&gt;"",OR(LEN($D214)&lt;&gt;17,LEN($D214)-LEN(SUBSTITUTE($D214,":",""))&lt;&gt;5)),AND($E214&lt;&gt;"",OR(LEN($E214)&lt;&gt;17,LEN($E214)-LEN(SUBSTITUTE($E214,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7159,11 +7816,14 @@
       <c r="J215" s="24" t="n"/>
       <c r="K215" s="24" t="n"/>
       <c r="L215" s="24" t="n"/>
-      <c r="N215">
-        <f>IF(COUNTA($A215:$L215)=0,0,IF(OR($B215="",$D215="",$F215="",$G215=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O215">
+      <c r="M215" s="24" t="n"/>
+      <c r="N215" s="24" t="n"/>
+      <c r="O215" s="24" t="n"/>
+      <c r="P215">
+        <f>IF(COUNTA($A215:$O215)=0,0,IF(OR($B215="",$D215="",$F215="",$G215=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q215">
         <f>IF(OR(AND($D215&lt;&gt;"",OR(LEN($D215)&lt;&gt;17,LEN($D215)-LEN(SUBSTITUTE($D215,":",""))&lt;&gt;5)),AND($E215&lt;&gt;"",OR(LEN($E215)&lt;&gt;17,LEN($E215)-LEN(SUBSTITUTE($E215,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7181,11 +7841,14 @@
       <c r="J216" s="24" t="n"/>
       <c r="K216" s="24" t="n"/>
       <c r="L216" s="24" t="n"/>
-      <c r="N216">
-        <f>IF(COUNTA($A216:$L216)=0,0,IF(OR($B216="",$D216="",$F216="",$G216=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O216">
+      <c r="M216" s="24" t="n"/>
+      <c r="N216" s="24" t="n"/>
+      <c r="O216" s="24" t="n"/>
+      <c r="P216">
+        <f>IF(COUNTA($A216:$O216)=0,0,IF(OR($B216="",$D216="",$F216="",$G216=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q216">
         <f>IF(OR(AND($D216&lt;&gt;"",OR(LEN($D216)&lt;&gt;17,LEN($D216)-LEN(SUBSTITUTE($D216,":",""))&lt;&gt;5)),AND($E216&lt;&gt;"",OR(LEN($E216)&lt;&gt;17,LEN($E216)-LEN(SUBSTITUTE($E216,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7203,11 +7866,14 @@
       <c r="J217" s="24" t="n"/>
       <c r="K217" s="24" t="n"/>
       <c r="L217" s="24" t="n"/>
-      <c r="N217">
-        <f>IF(COUNTA($A217:$L217)=0,0,IF(OR($B217="",$D217="",$F217="",$G217=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O217">
+      <c r="M217" s="24" t="n"/>
+      <c r="N217" s="24" t="n"/>
+      <c r="O217" s="24" t="n"/>
+      <c r="P217">
+        <f>IF(COUNTA($A217:$O217)=0,0,IF(OR($B217="",$D217="",$F217="",$G217=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q217">
         <f>IF(OR(AND($D217&lt;&gt;"",OR(LEN($D217)&lt;&gt;17,LEN($D217)-LEN(SUBSTITUTE($D217,":",""))&lt;&gt;5)),AND($E217&lt;&gt;"",OR(LEN($E217)&lt;&gt;17,LEN($E217)-LEN(SUBSTITUTE($E217,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7225,11 +7891,14 @@
       <c r="J218" s="24" t="n"/>
       <c r="K218" s="24" t="n"/>
       <c r="L218" s="24" t="n"/>
-      <c r="N218">
-        <f>IF(COUNTA($A218:$L218)=0,0,IF(OR($B218="",$D218="",$F218="",$G218=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O218">
+      <c r="M218" s="24" t="n"/>
+      <c r="N218" s="24" t="n"/>
+      <c r="O218" s="24" t="n"/>
+      <c r="P218">
+        <f>IF(COUNTA($A218:$O218)=0,0,IF(OR($B218="",$D218="",$F218="",$G218=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q218">
         <f>IF(OR(AND($D218&lt;&gt;"",OR(LEN($D218)&lt;&gt;17,LEN($D218)-LEN(SUBSTITUTE($D218,":",""))&lt;&gt;5)),AND($E218&lt;&gt;"",OR(LEN($E218)&lt;&gt;17,LEN($E218)-LEN(SUBSTITUTE($E218,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7247,11 +7916,14 @@
       <c r="J219" s="24" t="n"/>
       <c r="K219" s="24" t="n"/>
       <c r="L219" s="24" t="n"/>
-      <c r="N219">
-        <f>IF(COUNTA($A219:$L219)=0,0,IF(OR($B219="",$D219="",$F219="",$G219=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O219">
+      <c r="M219" s="24" t="n"/>
+      <c r="N219" s="24" t="n"/>
+      <c r="O219" s="24" t="n"/>
+      <c r="P219">
+        <f>IF(COUNTA($A219:$O219)=0,0,IF(OR($B219="",$D219="",$F219="",$G219=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q219">
         <f>IF(OR(AND($D219&lt;&gt;"",OR(LEN($D219)&lt;&gt;17,LEN($D219)-LEN(SUBSTITUTE($D219,":",""))&lt;&gt;5)),AND($E219&lt;&gt;"",OR(LEN($E219)&lt;&gt;17,LEN($E219)-LEN(SUBSTITUTE($E219,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7269,11 +7941,14 @@
       <c r="J220" s="24" t="n"/>
       <c r="K220" s="24" t="n"/>
       <c r="L220" s="24" t="n"/>
-      <c r="N220">
-        <f>IF(COUNTA($A220:$L220)=0,0,IF(OR($B220="",$D220="",$F220="",$G220=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O220">
+      <c r="M220" s="24" t="n"/>
+      <c r="N220" s="24" t="n"/>
+      <c r="O220" s="24" t="n"/>
+      <c r="P220">
+        <f>IF(COUNTA($A220:$O220)=0,0,IF(OR($B220="",$D220="",$F220="",$G220=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q220">
         <f>IF(OR(AND($D220&lt;&gt;"",OR(LEN($D220)&lt;&gt;17,LEN($D220)-LEN(SUBSTITUTE($D220,":",""))&lt;&gt;5)),AND($E220&lt;&gt;"",OR(LEN($E220)&lt;&gt;17,LEN($E220)-LEN(SUBSTITUTE($E220,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7291,11 +7966,14 @@
       <c r="J221" s="24" t="n"/>
       <c r="K221" s="24" t="n"/>
       <c r="L221" s="24" t="n"/>
-      <c r="N221">
-        <f>IF(COUNTA($A221:$L221)=0,0,IF(OR($B221="",$D221="",$F221="",$G221=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O221">
+      <c r="M221" s="24" t="n"/>
+      <c r="N221" s="24" t="n"/>
+      <c r="O221" s="24" t="n"/>
+      <c r="P221">
+        <f>IF(COUNTA($A221:$O221)=0,0,IF(OR($B221="",$D221="",$F221="",$G221=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q221">
         <f>IF(OR(AND($D221&lt;&gt;"",OR(LEN($D221)&lt;&gt;17,LEN($D221)-LEN(SUBSTITUTE($D221,":",""))&lt;&gt;5)),AND($E221&lt;&gt;"",OR(LEN($E221)&lt;&gt;17,LEN($E221)-LEN(SUBSTITUTE($E221,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7313,11 +7991,14 @@
       <c r="J222" s="24" t="n"/>
       <c r="K222" s="24" t="n"/>
       <c r="L222" s="24" t="n"/>
-      <c r="N222">
-        <f>IF(COUNTA($A222:$L222)=0,0,IF(OR($B222="",$D222="",$F222="",$G222=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O222">
+      <c r="M222" s="24" t="n"/>
+      <c r="N222" s="24" t="n"/>
+      <c r="O222" s="24" t="n"/>
+      <c r="P222">
+        <f>IF(COUNTA($A222:$O222)=0,0,IF(OR($B222="",$D222="",$F222="",$G222=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q222">
         <f>IF(OR(AND($D222&lt;&gt;"",OR(LEN($D222)&lt;&gt;17,LEN($D222)-LEN(SUBSTITUTE($D222,":",""))&lt;&gt;5)),AND($E222&lt;&gt;"",OR(LEN($E222)&lt;&gt;17,LEN($E222)-LEN(SUBSTITUTE($E222,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7335,11 +8016,14 @@
       <c r="J223" s="24" t="n"/>
       <c r="K223" s="24" t="n"/>
       <c r="L223" s="24" t="n"/>
-      <c r="N223">
-        <f>IF(COUNTA($A223:$L223)=0,0,IF(OR($B223="",$D223="",$F223="",$G223=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O223">
+      <c r="M223" s="24" t="n"/>
+      <c r="N223" s="24" t="n"/>
+      <c r="O223" s="24" t="n"/>
+      <c r="P223">
+        <f>IF(COUNTA($A223:$O223)=0,0,IF(OR($B223="",$D223="",$F223="",$G223=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q223">
         <f>IF(OR(AND($D223&lt;&gt;"",OR(LEN($D223)&lt;&gt;17,LEN($D223)-LEN(SUBSTITUTE($D223,":",""))&lt;&gt;5)),AND($E223&lt;&gt;"",OR(LEN($E223)&lt;&gt;17,LEN($E223)-LEN(SUBSTITUTE($E223,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7357,11 +8041,14 @@
       <c r="J224" s="24" t="n"/>
       <c r="K224" s="24" t="n"/>
       <c r="L224" s="24" t="n"/>
-      <c r="N224">
-        <f>IF(COUNTA($A224:$L224)=0,0,IF(OR($B224="",$D224="",$F224="",$G224=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O224">
+      <c r="M224" s="24" t="n"/>
+      <c r="N224" s="24" t="n"/>
+      <c r="O224" s="24" t="n"/>
+      <c r="P224">
+        <f>IF(COUNTA($A224:$O224)=0,0,IF(OR($B224="",$D224="",$F224="",$G224=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q224">
         <f>IF(OR(AND($D224&lt;&gt;"",OR(LEN($D224)&lt;&gt;17,LEN($D224)-LEN(SUBSTITUTE($D224,":",""))&lt;&gt;5)),AND($E224&lt;&gt;"",OR(LEN($E224)&lt;&gt;17,LEN($E224)-LEN(SUBSTITUTE($E224,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7379,11 +8066,14 @@
       <c r="J225" s="24" t="n"/>
       <c r="K225" s="24" t="n"/>
       <c r="L225" s="24" t="n"/>
-      <c r="N225">
-        <f>IF(COUNTA($A225:$L225)=0,0,IF(OR($B225="",$D225="",$F225="",$G225=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O225">
+      <c r="M225" s="24" t="n"/>
+      <c r="N225" s="24" t="n"/>
+      <c r="O225" s="24" t="n"/>
+      <c r="P225">
+        <f>IF(COUNTA($A225:$O225)=0,0,IF(OR($B225="",$D225="",$F225="",$G225=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q225">
         <f>IF(OR(AND($D225&lt;&gt;"",OR(LEN($D225)&lt;&gt;17,LEN($D225)-LEN(SUBSTITUTE($D225,":",""))&lt;&gt;5)),AND($E225&lt;&gt;"",OR(LEN($E225)&lt;&gt;17,LEN($E225)-LEN(SUBSTITUTE($E225,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7401,11 +8091,14 @@
       <c r="J226" s="24" t="n"/>
       <c r="K226" s="24" t="n"/>
       <c r="L226" s="24" t="n"/>
-      <c r="N226">
-        <f>IF(COUNTA($A226:$L226)=0,0,IF(OR($B226="",$D226="",$F226="",$G226=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O226">
+      <c r="M226" s="24" t="n"/>
+      <c r="N226" s="24" t="n"/>
+      <c r="O226" s="24" t="n"/>
+      <c r="P226">
+        <f>IF(COUNTA($A226:$O226)=0,0,IF(OR($B226="",$D226="",$F226="",$G226=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q226">
         <f>IF(OR(AND($D226&lt;&gt;"",OR(LEN($D226)&lt;&gt;17,LEN($D226)-LEN(SUBSTITUTE($D226,":",""))&lt;&gt;5)),AND($E226&lt;&gt;"",OR(LEN($E226)&lt;&gt;17,LEN($E226)-LEN(SUBSTITUTE($E226,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7423,11 +8116,14 @@
       <c r="J227" s="24" t="n"/>
       <c r="K227" s="24" t="n"/>
       <c r="L227" s="24" t="n"/>
-      <c r="N227">
-        <f>IF(COUNTA($A227:$L227)=0,0,IF(OR($B227="",$D227="",$F227="",$G227=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O227">
+      <c r="M227" s="24" t="n"/>
+      <c r="N227" s="24" t="n"/>
+      <c r="O227" s="24" t="n"/>
+      <c r="P227">
+        <f>IF(COUNTA($A227:$O227)=0,0,IF(OR($B227="",$D227="",$F227="",$G227=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q227">
         <f>IF(OR(AND($D227&lt;&gt;"",OR(LEN($D227)&lt;&gt;17,LEN($D227)-LEN(SUBSTITUTE($D227,":",""))&lt;&gt;5)),AND($E227&lt;&gt;"",OR(LEN($E227)&lt;&gt;17,LEN($E227)-LEN(SUBSTITUTE($E227,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7445,11 +8141,14 @@
       <c r="J228" s="24" t="n"/>
       <c r="K228" s="24" t="n"/>
       <c r="L228" s="24" t="n"/>
-      <c r="N228">
-        <f>IF(COUNTA($A228:$L228)=0,0,IF(OR($B228="",$D228="",$F228="",$G228=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O228">
+      <c r="M228" s="24" t="n"/>
+      <c r="N228" s="24" t="n"/>
+      <c r="O228" s="24" t="n"/>
+      <c r="P228">
+        <f>IF(COUNTA($A228:$O228)=0,0,IF(OR($B228="",$D228="",$F228="",$G228=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q228">
         <f>IF(OR(AND($D228&lt;&gt;"",OR(LEN($D228)&lt;&gt;17,LEN($D228)-LEN(SUBSTITUTE($D228,":",""))&lt;&gt;5)),AND($E228&lt;&gt;"",OR(LEN($E228)&lt;&gt;17,LEN($E228)-LEN(SUBSTITUTE($E228,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7467,11 +8166,14 @@
       <c r="J229" s="24" t="n"/>
       <c r="K229" s="24" t="n"/>
       <c r="L229" s="24" t="n"/>
-      <c r="N229">
-        <f>IF(COUNTA($A229:$L229)=0,0,IF(OR($B229="",$D229="",$F229="",$G229=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O229">
+      <c r="M229" s="24" t="n"/>
+      <c r="N229" s="24" t="n"/>
+      <c r="O229" s="24" t="n"/>
+      <c r="P229">
+        <f>IF(COUNTA($A229:$O229)=0,0,IF(OR($B229="",$D229="",$F229="",$G229=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q229">
         <f>IF(OR(AND($D229&lt;&gt;"",OR(LEN($D229)&lt;&gt;17,LEN($D229)-LEN(SUBSTITUTE($D229,":",""))&lt;&gt;5)),AND($E229&lt;&gt;"",OR(LEN($E229)&lt;&gt;17,LEN($E229)-LEN(SUBSTITUTE($E229,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7489,11 +8191,14 @@
       <c r="J230" s="24" t="n"/>
       <c r="K230" s="24" t="n"/>
       <c r="L230" s="24" t="n"/>
-      <c r="N230">
-        <f>IF(COUNTA($A230:$L230)=0,0,IF(OR($B230="",$D230="",$F230="",$G230=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O230">
+      <c r="M230" s="24" t="n"/>
+      <c r="N230" s="24" t="n"/>
+      <c r="O230" s="24" t="n"/>
+      <c r="P230">
+        <f>IF(COUNTA($A230:$O230)=0,0,IF(OR($B230="",$D230="",$F230="",$G230=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q230">
         <f>IF(OR(AND($D230&lt;&gt;"",OR(LEN($D230)&lt;&gt;17,LEN($D230)-LEN(SUBSTITUTE($D230,":",""))&lt;&gt;5)),AND($E230&lt;&gt;"",OR(LEN($E230)&lt;&gt;17,LEN($E230)-LEN(SUBSTITUTE($E230,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7511,11 +8216,14 @@
       <c r="J231" s="24" t="n"/>
       <c r="K231" s="24" t="n"/>
       <c r="L231" s="24" t="n"/>
-      <c r="N231">
-        <f>IF(COUNTA($A231:$L231)=0,0,IF(OR($B231="",$D231="",$F231="",$G231=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O231">
+      <c r="M231" s="24" t="n"/>
+      <c r="N231" s="24" t="n"/>
+      <c r="O231" s="24" t="n"/>
+      <c r="P231">
+        <f>IF(COUNTA($A231:$O231)=0,0,IF(OR($B231="",$D231="",$F231="",$G231=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q231">
         <f>IF(OR(AND($D231&lt;&gt;"",OR(LEN($D231)&lt;&gt;17,LEN($D231)-LEN(SUBSTITUTE($D231,":",""))&lt;&gt;5)),AND($E231&lt;&gt;"",OR(LEN($E231)&lt;&gt;17,LEN($E231)-LEN(SUBSTITUTE($E231,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7533,11 +8241,14 @@
       <c r="J232" s="24" t="n"/>
       <c r="K232" s="24" t="n"/>
       <c r="L232" s="24" t="n"/>
-      <c r="N232">
-        <f>IF(COUNTA($A232:$L232)=0,0,IF(OR($B232="",$D232="",$F232="",$G232=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O232">
+      <c r="M232" s="24" t="n"/>
+      <c r="N232" s="24" t="n"/>
+      <c r="O232" s="24" t="n"/>
+      <c r="P232">
+        <f>IF(COUNTA($A232:$O232)=0,0,IF(OR($B232="",$D232="",$F232="",$G232=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q232">
         <f>IF(OR(AND($D232&lt;&gt;"",OR(LEN($D232)&lt;&gt;17,LEN($D232)-LEN(SUBSTITUTE($D232,":",""))&lt;&gt;5)),AND($E232&lt;&gt;"",OR(LEN($E232)&lt;&gt;17,LEN($E232)-LEN(SUBSTITUTE($E232,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7555,11 +8266,14 @@
       <c r="J233" s="24" t="n"/>
       <c r="K233" s="24" t="n"/>
       <c r="L233" s="24" t="n"/>
-      <c r="N233">
-        <f>IF(COUNTA($A233:$L233)=0,0,IF(OR($B233="",$D233="",$F233="",$G233=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O233">
+      <c r="M233" s="24" t="n"/>
+      <c r="N233" s="24" t="n"/>
+      <c r="O233" s="24" t="n"/>
+      <c r="P233">
+        <f>IF(COUNTA($A233:$O233)=0,0,IF(OR($B233="",$D233="",$F233="",$G233=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q233">
         <f>IF(OR(AND($D233&lt;&gt;"",OR(LEN($D233)&lt;&gt;17,LEN($D233)-LEN(SUBSTITUTE($D233,":",""))&lt;&gt;5)),AND($E233&lt;&gt;"",OR(LEN($E233)&lt;&gt;17,LEN($E233)-LEN(SUBSTITUTE($E233,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7577,11 +8291,14 @@
       <c r="J234" s="24" t="n"/>
       <c r="K234" s="24" t="n"/>
       <c r="L234" s="24" t="n"/>
-      <c r="N234">
-        <f>IF(COUNTA($A234:$L234)=0,0,IF(OR($B234="",$D234="",$F234="",$G234=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O234">
+      <c r="M234" s="24" t="n"/>
+      <c r="N234" s="24" t="n"/>
+      <c r="O234" s="24" t="n"/>
+      <c r="P234">
+        <f>IF(COUNTA($A234:$O234)=0,0,IF(OR($B234="",$D234="",$F234="",$G234=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q234">
         <f>IF(OR(AND($D234&lt;&gt;"",OR(LEN($D234)&lt;&gt;17,LEN($D234)-LEN(SUBSTITUTE($D234,":",""))&lt;&gt;5)),AND($E234&lt;&gt;"",OR(LEN($E234)&lt;&gt;17,LEN($E234)-LEN(SUBSTITUTE($E234,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7599,11 +8316,14 @@
       <c r="J235" s="24" t="n"/>
       <c r="K235" s="24" t="n"/>
       <c r="L235" s="24" t="n"/>
-      <c r="N235">
-        <f>IF(COUNTA($A235:$L235)=0,0,IF(OR($B235="",$D235="",$F235="",$G235=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O235">
+      <c r="M235" s="24" t="n"/>
+      <c r="N235" s="24" t="n"/>
+      <c r="O235" s="24" t="n"/>
+      <c r="P235">
+        <f>IF(COUNTA($A235:$O235)=0,0,IF(OR($B235="",$D235="",$F235="",$G235=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q235">
         <f>IF(OR(AND($D235&lt;&gt;"",OR(LEN($D235)&lt;&gt;17,LEN($D235)-LEN(SUBSTITUTE($D235,":",""))&lt;&gt;5)),AND($E235&lt;&gt;"",OR(LEN($E235)&lt;&gt;17,LEN($E235)-LEN(SUBSTITUTE($E235,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7621,11 +8341,14 @@
       <c r="J236" s="24" t="n"/>
       <c r="K236" s="24" t="n"/>
       <c r="L236" s="24" t="n"/>
-      <c r="N236">
-        <f>IF(COUNTA($A236:$L236)=0,0,IF(OR($B236="",$D236="",$F236="",$G236=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O236">
+      <c r="M236" s="24" t="n"/>
+      <c r="N236" s="24" t="n"/>
+      <c r="O236" s="24" t="n"/>
+      <c r="P236">
+        <f>IF(COUNTA($A236:$O236)=0,0,IF(OR($B236="",$D236="",$F236="",$G236=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q236">
         <f>IF(OR(AND($D236&lt;&gt;"",OR(LEN($D236)&lt;&gt;17,LEN($D236)-LEN(SUBSTITUTE($D236,":",""))&lt;&gt;5)),AND($E236&lt;&gt;"",OR(LEN($E236)&lt;&gt;17,LEN($E236)-LEN(SUBSTITUTE($E236,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7643,11 +8366,14 @@
       <c r="J237" s="24" t="n"/>
       <c r="K237" s="24" t="n"/>
       <c r="L237" s="24" t="n"/>
-      <c r="N237">
-        <f>IF(COUNTA($A237:$L237)=0,0,IF(OR($B237="",$D237="",$F237="",$G237=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O237">
+      <c r="M237" s="24" t="n"/>
+      <c r="N237" s="24" t="n"/>
+      <c r="O237" s="24" t="n"/>
+      <c r="P237">
+        <f>IF(COUNTA($A237:$O237)=0,0,IF(OR($B237="",$D237="",$F237="",$G237=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q237">
         <f>IF(OR(AND($D237&lt;&gt;"",OR(LEN($D237)&lt;&gt;17,LEN($D237)-LEN(SUBSTITUTE($D237,":",""))&lt;&gt;5)),AND($E237&lt;&gt;"",OR(LEN($E237)&lt;&gt;17,LEN($E237)-LEN(SUBSTITUTE($E237,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7665,11 +8391,14 @@
       <c r="J238" s="24" t="n"/>
       <c r="K238" s="24" t="n"/>
       <c r="L238" s="24" t="n"/>
-      <c r="N238">
-        <f>IF(COUNTA($A238:$L238)=0,0,IF(OR($B238="",$D238="",$F238="",$G238=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O238">
+      <c r="M238" s="24" t="n"/>
+      <c r="N238" s="24" t="n"/>
+      <c r="O238" s="24" t="n"/>
+      <c r="P238">
+        <f>IF(COUNTA($A238:$O238)=0,0,IF(OR($B238="",$D238="",$F238="",$G238=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q238">
         <f>IF(OR(AND($D238&lt;&gt;"",OR(LEN($D238)&lt;&gt;17,LEN($D238)-LEN(SUBSTITUTE($D238,":",""))&lt;&gt;5)),AND($E238&lt;&gt;"",OR(LEN($E238)&lt;&gt;17,LEN($E238)-LEN(SUBSTITUTE($E238,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7687,11 +8416,14 @@
       <c r="J239" s="24" t="n"/>
       <c r="K239" s="24" t="n"/>
       <c r="L239" s="24" t="n"/>
-      <c r="N239">
-        <f>IF(COUNTA($A239:$L239)=0,0,IF(OR($B239="",$D239="",$F239="",$G239=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O239">
+      <c r="M239" s="24" t="n"/>
+      <c r="N239" s="24" t="n"/>
+      <c r="O239" s="24" t="n"/>
+      <c r="P239">
+        <f>IF(COUNTA($A239:$O239)=0,0,IF(OR($B239="",$D239="",$F239="",$G239=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q239">
         <f>IF(OR(AND($D239&lt;&gt;"",OR(LEN($D239)&lt;&gt;17,LEN($D239)-LEN(SUBSTITUTE($D239,":",""))&lt;&gt;5)),AND($E239&lt;&gt;"",OR(LEN($E239)&lt;&gt;17,LEN($E239)-LEN(SUBSTITUTE($E239,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7709,11 +8441,14 @@
       <c r="J240" s="24" t="n"/>
       <c r="K240" s="24" t="n"/>
       <c r="L240" s="24" t="n"/>
-      <c r="N240">
-        <f>IF(COUNTA($A240:$L240)=0,0,IF(OR($B240="",$D240="",$F240="",$G240=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O240">
+      <c r="M240" s="24" t="n"/>
+      <c r="N240" s="24" t="n"/>
+      <c r="O240" s="24" t="n"/>
+      <c r="P240">
+        <f>IF(COUNTA($A240:$O240)=0,0,IF(OR($B240="",$D240="",$F240="",$G240=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q240">
         <f>IF(OR(AND($D240&lt;&gt;"",OR(LEN($D240)&lt;&gt;17,LEN($D240)-LEN(SUBSTITUTE($D240,":",""))&lt;&gt;5)),AND($E240&lt;&gt;"",OR(LEN($E240)&lt;&gt;17,LEN($E240)-LEN(SUBSTITUTE($E240,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7731,11 +8466,14 @@
       <c r="J241" s="24" t="n"/>
       <c r="K241" s="24" t="n"/>
       <c r="L241" s="24" t="n"/>
-      <c r="N241">
-        <f>IF(COUNTA($A241:$L241)=0,0,IF(OR($B241="",$D241="",$F241="",$G241=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O241">
+      <c r="M241" s="24" t="n"/>
+      <c r="N241" s="24" t="n"/>
+      <c r="O241" s="24" t="n"/>
+      <c r="P241">
+        <f>IF(COUNTA($A241:$O241)=0,0,IF(OR($B241="",$D241="",$F241="",$G241=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q241">
         <f>IF(OR(AND($D241&lt;&gt;"",OR(LEN($D241)&lt;&gt;17,LEN($D241)-LEN(SUBSTITUTE($D241,":",""))&lt;&gt;5)),AND($E241&lt;&gt;"",OR(LEN($E241)&lt;&gt;17,LEN($E241)-LEN(SUBSTITUTE($E241,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7753,11 +8491,14 @@
       <c r="J242" s="24" t="n"/>
       <c r="K242" s="24" t="n"/>
       <c r="L242" s="24" t="n"/>
-      <c r="N242">
-        <f>IF(COUNTA($A242:$L242)=0,0,IF(OR($B242="",$D242="",$F242="",$G242=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O242">
+      <c r="M242" s="24" t="n"/>
+      <c r="N242" s="24" t="n"/>
+      <c r="O242" s="24" t="n"/>
+      <c r="P242">
+        <f>IF(COUNTA($A242:$O242)=0,0,IF(OR($B242="",$D242="",$F242="",$G242=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q242">
         <f>IF(OR(AND($D242&lt;&gt;"",OR(LEN($D242)&lt;&gt;17,LEN($D242)-LEN(SUBSTITUTE($D242,":",""))&lt;&gt;5)),AND($E242&lt;&gt;"",OR(LEN($E242)&lt;&gt;17,LEN($E242)-LEN(SUBSTITUTE($E242,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7775,11 +8516,14 @@
       <c r="J243" s="24" t="n"/>
       <c r="K243" s="24" t="n"/>
       <c r="L243" s="24" t="n"/>
-      <c r="N243">
-        <f>IF(COUNTA($A243:$L243)=0,0,IF(OR($B243="",$D243="",$F243="",$G243=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O243">
+      <c r="M243" s="24" t="n"/>
+      <c r="N243" s="24" t="n"/>
+      <c r="O243" s="24" t="n"/>
+      <c r="P243">
+        <f>IF(COUNTA($A243:$O243)=0,0,IF(OR($B243="",$D243="",$F243="",$G243=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q243">
         <f>IF(OR(AND($D243&lt;&gt;"",OR(LEN($D243)&lt;&gt;17,LEN($D243)-LEN(SUBSTITUTE($D243,":",""))&lt;&gt;5)),AND($E243&lt;&gt;"",OR(LEN($E243)&lt;&gt;17,LEN($E243)-LEN(SUBSTITUTE($E243,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7797,11 +8541,14 @@
       <c r="J244" s="24" t="n"/>
       <c r="K244" s="24" t="n"/>
       <c r="L244" s="24" t="n"/>
-      <c r="N244">
-        <f>IF(COUNTA($A244:$L244)=0,0,IF(OR($B244="",$D244="",$F244="",$G244=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O244">
+      <c r="M244" s="24" t="n"/>
+      <c r="N244" s="24" t="n"/>
+      <c r="O244" s="24" t="n"/>
+      <c r="P244">
+        <f>IF(COUNTA($A244:$O244)=0,0,IF(OR($B244="",$D244="",$F244="",$G244=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q244">
         <f>IF(OR(AND($D244&lt;&gt;"",OR(LEN($D244)&lt;&gt;17,LEN($D244)-LEN(SUBSTITUTE($D244,":",""))&lt;&gt;5)),AND($E244&lt;&gt;"",OR(LEN($E244)&lt;&gt;17,LEN($E244)-LEN(SUBSTITUTE($E244,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7819,11 +8566,14 @@
       <c r="J245" s="24" t="n"/>
       <c r="K245" s="24" t="n"/>
       <c r="L245" s="24" t="n"/>
-      <c r="N245">
-        <f>IF(COUNTA($A245:$L245)=0,0,IF(OR($B245="",$D245="",$F245="",$G245=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O245">
+      <c r="M245" s="24" t="n"/>
+      <c r="N245" s="24" t="n"/>
+      <c r="O245" s="24" t="n"/>
+      <c r="P245">
+        <f>IF(COUNTA($A245:$O245)=0,0,IF(OR($B245="",$D245="",$F245="",$G245=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q245">
         <f>IF(OR(AND($D245&lt;&gt;"",OR(LEN($D245)&lt;&gt;17,LEN($D245)-LEN(SUBSTITUTE($D245,":",""))&lt;&gt;5)),AND($E245&lt;&gt;"",OR(LEN($E245)&lt;&gt;17,LEN($E245)-LEN(SUBSTITUTE($E245,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7841,11 +8591,14 @@
       <c r="J246" s="24" t="n"/>
       <c r="K246" s="24" t="n"/>
       <c r="L246" s="24" t="n"/>
-      <c r="N246">
-        <f>IF(COUNTA($A246:$L246)=0,0,IF(OR($B246="",$D246="",$F246="",$G246=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O246">
+      <c r="M246" s="24" t="n"/>
+      <c r="N246" s="24" t="n"/>
+      <c r="O246" s="24" t="n"/>
+      <c r="P246">
+        <f>IF(COUNTA($A246:$O246)=0,0,IF(OR($B246="",$D246="",$F246="",$G246=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q246">
         <f>IF(OR(AND($D246&lt;&gt;"",OR(LEN($D246)&lt;&gt;17,LEN($D246)-LEN(SUBSTITUTE($D246,":",""))&lt;&gt;5)),AND($E246&lt;&gt;"",OR(LEN($E246)&lt;&gt;17,LEN($E246)-LEN(SUBSTITUTE($E246,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7863,11 +8616,14 @@
       <c r="J247" s="24" t="n"/>
       <c r="K247" s="24" t="n"/>
       <c r="L247" s="24" t="n"/>
-      <c r="N247">
-        <f>IF(COUNTA($A247:$L247)=0,0,IF(OR($B247="",$D247="",$F247="",$G247=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O247">
+      <c r="M247" s="24" t="n"/>
+      <c r="N247" s="24" t="n"/>
+      <c r="O247" s="24" t="n"/>
+      <c r="P247">
+        <f>IF(COUNTA($A247:$O247)=0,0,IF(OR($B247="",$D247="",$F247="",$G247=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q247">
         <f>IF(OR(AND($D247&lt;&gt;"",OR(LEN($D247)&lt;&gt;17,LEN($D247)-LEN(SUBSTITUTE($D247,":",""))&lt;&gt;5)),AND($E247&lt;&gt;"",OR(LEN($E247)&lt;&gt;17,LEN($E247)-LEN(SUBSTITUTE($E247,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7885,11 +8641,14 @@
       <c r="J248" s="24" t="n"/>
       <c r="K248" s="24" t="n"/>
       <c r="L248" s="24" t="n"/>
-      <c r="N248">
-        <f>IF(COUNTA($A248:$L248)=0,0,IF(OR($B248="",$D248="",$F248="",$G248=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O248">
+      <c r="M248" s="24" t="n"/>
+      <c r="N248" s="24" t="n"/>
+      <c r="O248" s="24" t="n"/>
+      <c r="P248">
+        <f>IF(COUNTA($A248:$O248)=0,0,IF(OR($B248="",$D248="",$F248="",$G248=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q248">
         <f>IF(OR(AND($D248&lt;&gt;"",OR(LEN($D248)&lt;&gt;17,LEN($D248)-LEN(SUBSTITUTE($D248,":",""))&lt;&gt;5)),AND($E248&lt;&gt;"",OR(LEN($E248)&lt;&gt;17,LEN($E248)-LEN(SUBSTITUTE($E248,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7907,11 +8666,14 @@
       <c r="J249" s="24" t="n"/>
       <c r="K249" s="24" t="n"/>
       <c r="L249" s="24" t="n"/>
-      <c r="N249">
-        <f>IF(COUNTA($A249:$L249)=0,0,IF(OR($B249="",$D249="",$F249="",$G249=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O249">
+      <c r="M249" s="24" t="n"/>
+      <c r="N249" s="24" t="n"/>
+      <c r="O249" s="24" t="n"/>
+      <c r="P249">
+        <f>IF(COUNTA($A249:$O249)=0,0,IF(OR($B249="",$D249="",$F249="",$G249=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q249">
         <f>IF(OR(AND($D249&lt;&gt;"",OR(LEN($D249)&lt;&gt;17,LEN($D249)-LEN(SUBSTITUTE($D249,":",""))&lt;&gt;5)),AND($E249&lt;&gt;"",OR(LEN($E249)&lt;&gt;17,LEN($E249)-LEN(SUBSTITUTE($E249,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7929,11 +8691,14 @@
       <c r="J250" s="24" t="n"/>
       <c r="K250" s="24" t="n"/>
       <c r="L250" s="24" t="n"/>
-      <c r="N250">
-        <f>IF(COUNTA($A250:$L250)=0,0,IF(OR($B250="",$D250="",$F250="",$G250=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O250">
+      <c r="M250" s="24" t="n"/>
+      <c r="N250" s="24" t="n"/>
+      <c r="O250" s="24" t="n"/>
+      <c r="P250">
+        <f>IF(COUNTA($A250:$O250)=0,0,IF(OR($B250="",$D250="",$F250="",$G250=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q250">
         <f>IF(OR(AND($D250&lt;&gt;"",OR(LEN($D250)&lt;&gt;17,LEN($D250)-LEN(SUBSTITUTE($D250,":",""))&lt;&gt;5)),AND($E250&lt;&gt;"",OR(LEN($E250)&lt;&gt;17,LEN($E250)-LEN(SUBSTITUTE($E250,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7951,11 +8716,14 @@
       <c r="J251" s="24" t="n"/>
       <c r="K251" s="24" t="n"/>
       <c r="L251" s="24" t="n"/>
-      <c r="N251">
-        <f>IF(COUNTA($A251:$L251)=0,0,IF(OR($B251="",$D251="",$F251="",$G251=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O251">
+      <c r="M251" s="24" t="n"/>
+      <c r="N251" s="24" t="n"/>
+      <c r="O251" s="24" t="n"/>
+      <c r="P251">
+        <f>IF(COUNTA($A251:$O251)=0,0,IF(OR($B251="",$D251="",$F251="",$G251=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q251">
         <f>IF(OR(AND($D251&lt;&gt;"",OR(LEN($D251)&lt;&gt;17,LEN($D251)-LEN(SUBSTITUTE($D251,":",""))&lt;&gt;5)),AND($E251&lt;&gt;"",OR(LEN($E251)&lt;&gt;17,LEN($E251)-LEN(SUBSTITUTE($E251,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7973,11 +8741,14 @@
       <c r="J252" s="24" t="n"/>
       <c r="K252" s="24" t="n"/>
       <c r="L252" s="24" t="n"/>
-      <c r="N252">
-        <f>IF(COUNTA($A252:$L252)=0,0,IF(OR($B252="",$D252="",$F252="",$G252=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O252">
+      <c r="M252" s="24" t="n"/>
+      <c r="N252" s="24" t="n"/>
+      <c r="O252" s="24" t="n"/>
+      <c r="P252">
+        <f>IF(COUNTA($A252:$O252)=0,0,IF(OR($B252="",$D252="",$F252="",$G252=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q252">
         <f>IF(OR(AND($D252&lt;&gt;"",OR(LEN($D252)&lt;&gt;17,LEN($D252)-LEN(SUBSTITUTE($D252,":",""))&lt;&gt;5)),AND($E252&lt;&gt;"",OR(LEN($E252)&lt;&gt;17,LEN($E252)-LEN(SUBSTITUTE($E252,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7995,11 +8766,14 @@
       <c r="J253" s="24" t="n"/>
       <c r="K253" s="24" t="n"/>
       <c r="L253" s="24" t="n"/>
-      <c r="N253">
-        <f>IF(COUNTA($A253:$L253)=0,0,IF(OR($B253="",$D253="",$F253="",$G253=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O253">
+      <c r="M253" s="24" t="n"/>
+      <c r="N253" s="24" t="n"/>
+      <c r="O253" s="24" t="n"/>
+      <c r="P253">
+        <f>IF(COUNTA($A253:$O253)=0,0,IF(OR($B253="",$D253="",$F253="",$G253=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q253">
         <f>IF(OR(AND($D253&lt;&gt;"",OR(LEN($D253)&lt;&gt;17,LEN($D253)-LEN(SUBSTITUTE($D253,":",""))&lt;&gt;5)),AND($E253&lt;&gt;"",OR(LEN($E253)&lt;&gt;17,LEN($E253)-LEN(SUBSTITUTE($E253,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8017,11 +8791,14 @@
       <c r="J254" s="24" t="n"/>
       <c r="K254" s="24" t="n"/>
       <c r="L254" s="24" t="n"/>
-      <c r="N254">
-        <f>IF(COUNTA($A254:$L254)=0,0,IF(OR($B254="",$D254="",$F254="",$G254=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O254">
+      <c r="M254" s="24" t="n"/>
+      <c r="N254" s="24" t="n"/>
+      <c r="O254" s="24" t="n"/>
+      <c r="P254">
+        <f>IF(COUNTA($A254:$O254)=0,0,IF(OR($B254="",$D254="",$F254="",$G254=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q254">
         <f>IF(OR(AND($D254&lt;&gt;"",OR(LEN($D254)&lt;&gt;17,LEN($D254)-LEN(SUBSTITUTE($D254,":",""))&lt;&gt;5)),AND($E254&lt;&gt;"",OR(LEN($E254)&lt;&gt;17,LEN($E254)-LEN(SUBSTITUTE($E254,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8039,11 +8816,14 @@
       <c r="J255" s="24" t="n"/>
       <c r="K255" s="24" t="n"/>
       <c r="L255" s="24" t="n"/>
-      <c r="N255">
-        <f>IF(COUNTA($A255:$L255)=0,0,IF(OR($B255="",$D255="",$F255="",$G255=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O255">
+      <c r="M255" s="24" t="n"/>
+      <c r="N255" s="24" t="n"/>
+      <c r="O255" s="24" t="n"/>
+      <c r="P255">
+        <f>IF(COUNTA($A255:$O255)=0,0,IF(OR($B255="",$D255="",$F255="",$G255=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q255">
         <f>IF(OR(AND($D255&lt;&gt;"",OR(LEN($D255)&lt;&gt;17,LEN($D255)-LEN(SUBSTITUTE($D255,":",""))&lt;&gt;5)),AND($E255&lt;&gt;"",OR(LEN($E255)&lt;&gt;17,LEN($E255)-LEN(SUBSTITUTE($E255,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8061,11 +8841,14 @@
       <c r="J256" s="24" t="n"/>
       <c r="K256" s="24" t="n"/>
       <c r="L256" s="24" t="n"/>
-      <c r="N256">
-        <f>IF(COUNTA($A256:$L256)=0,0,IF(OR($B256="",$D256="",$F256="",$G256=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O256">
+      <c r="M256" s="24" t="n"/>
+      <c r="N256" s="24" t="n"/>
+      <c r="O256" s="24" t="n"/>
+      <c r="P256">
+        <f>IF(COUNTA($A256:$O256)=0,0,IF(OR($B256="",$D256="",$F256="",$G256=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q256">
         <f>IF(OR(AND($D256&lt;&gt;"",OR(LEN($D256)&lt;&gt;17,LEN($D256)-LEN(SUBSTITUTE($D256,":",""))&lt;&gt;5)),AND($E256&lt;&gt;"",OR(LEN($E256)&lt;&gt;17,LEN($E256)-LEN(SUBSTITUTE($E256,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8083,11 +8866,14 @@
       <c r="J257" s="24" t="n"/>
       <c r="K257" s="24" t="n"/>
       <c r="L257" s="24" t="n"/>
-      <c r="N257">
-        <f>IF(COUNTA($A257:$L257)=0,0,IF(OR($B257="",$D257="",$F257="",$G257=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O257">
+      <c r="M257" s="24" t="n"/>
+      <c r="N257" s="24" t="n"/>
+      <c r="O257" s="24" t="n"/>
+      <c r="P257">
+        <f>IF(COUNTA($A257:$O257)=0,0,IF(OR($B257="",$D257="",$F257="",$G257=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q257">
         <f>IF(OR(AND($D257&lt;&gt;"",OR(LEN($D257)&lt;&gt;17,LEN($D257)-LEN(SUBSTITUTE($D257,":",""))&lt;&gt;5)),AND($E257&lt;&gt;"",OR(LEN($E257)&lt;&gt;17,LEN($E257)-LEN(SUBSTITUTE($E257,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8105,11 +8891,14 @@
       <c r="J258" s="24" t="n"/>
       <c r="K258" s="24" t="n"/>
       <c r="L258" s="24" t="n"/>
-      <c r="N258">
-        <f>IF(COUNTA($A258:$L258)=0,0,IF(OR($B258="",$D258="",$F258="",$G258=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O258">
+      <c r="M258" s="24" t="n"/>
+      <c r="N258" s="24" t="n"/>
+      <c r="O258" s="24" t="n"/>
+      <c r="P258">
+        <f>IF(COUNTA($A258:$O258)=0,0,IF(OR($B258="",$D258="",$F258="",$G258=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q258">
         <f>IF(OR(AND($D258&lt;&gt;"",OR(LEN($D258)&lt;&gt;17,LEN($D258)-LEN(SUBSTITUTE($D258,":",""))&lt;&gt;5)),AND($E258&lt;&gt;"",OR(LEN($E258)&lt;&gt;17,LEN($E258)-LEN(SUBSTITUTE($E258,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8127,11 +8916,14 @@
       <c r="J259" s="24" t="n"/>
       <c r="K259" s="24" t="n"/>
       <c r="L259" s="24" t="n"/>
-      <c r="N259">
-        <f>IF(COUNTA($A259:$L259)=0,0,IF(OR($B259="",$D259="",$F259="",$G259=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O259">
+      <c r="M259" s="24" t="n"/>
+      <c r="N259" s="24" t="n"/>
+      <c r="O259" s="24" t="n"/>
+      <c r="P259">
+        <f>IF(COUNTA($A259:$O259)=0,0,IF(OR($B259="",$D259="",$F259="",$G259=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q259">
         <f>IF(OR(AND($D259&lt;&gt;"",OR(LEN($D259)&lt;&gt;17,LEN($D259)-LEN(SUBSTITUTE($D259,":",""))&lt;&gt;5)),AND($E259&lt;&gt;"",OR(LEN($E259)&lt;&gt;17,LEN($E259)-LEN(SUBSTITUTE($E259,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8149,11 +8941,14 @@
       <c r="J260" s="24" t="n"/>
       <c r="K260" s="24" t="n"/>
       <c r="L260" s="24" t="n"/>
-      <c r="N260">
-        <f>IF(COUNTA($A260:$L260)=0,0,IF(OR($B260="",$D260="",$F260="",$G260=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O260">
+      <c r="M260" s="24" t="n"/>
+      <c r="N260" s="24" t="n"/>
+      <c r="O260" s="24" t="n"/>
+      <c r="P260">
+        <f>IF(COUNTA($A260:$O260)=0,0,IF(OR($B260="",$D260="",$F260="",$G260=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q260">
         <f>IF(OR(AND($D260&lt;&gt;"",OR(LEN($D260)&lt;&gt;17,LEN($D260)-LEN(SUBSTITUTE($D260,":",""))&lt;&gt;5)),AND($E260&lt;&gt;"",OR(LEN($E260)&lt;&gt;17,LEN($E260)-LEN(SUBSTITUTE($E260,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8171,11 +8966,14 @@
       <c r="J261" s="24" t="n"/>
       <c r="K261" s="24" t="n"/>
       <c r="L261" s="24" t="n"/>
-      <c r="N261">
-        <f>IF(COUNTA($A261:$L261)=0,0,IF(OR($B261="",$D261="",$F261="",$G261=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O261">
+      <c r="M261" s="24" t="n"/>
+      <c r="N261" s="24" t="n"/>
+      <c r="O261" s="24" t="n"/>
+      <c r="P261">
+        <f>IF(COUNTA($A261:$O261)=0,0,IF(OR($B261="",$D261="",$F261="",$G261=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q261">
         <f>IF(OR(AND($D261&lt;&gt;"",OR(LEN($D261)&lt;&gt;17,LEN($D261)-LEN(SUBSTITUTE($D261,":",""))&lt;&gt;5)),AND($E261&lt;&gt;"",OR(LEN($E261)&lt;&gt;17,LEN($E261)-LEN(SUBSTITUTE($E261,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8193,11 +8991,14 @@
       <c r="J262" s="24" t="n"/>
       <c r="K262" s="24" t="n"/>
       <c r="L262" s="24" t="n"/>
-      <c r="N262">
-        <f>IF(COUNTA($A262:$L262)=0,0,IF(OR($B262="",$D262="",$F262="",$G262=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O262">
+      <c r="M262" s="24" t="n"/>
+      <c r="N262" s="24" t="n"/>
+      <c r="O262" s="24" t="n"/>
+      <c r="P262">
+        <f>IF(COUNTA($A262:$O262)=0,0,IF(OR($B262="",$D262="",$F262="",$G262=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q262">
         <f>IF(OR(AND($D262&lt;&gt;"",OR(LEN($D262)&lt;&gt;17,LEN($D262)-LEN(SUBSTITUTE($D262,":",""))&lt;&gt;5)),AND($E262&lt;&gt;"",OR(LEN($E262)&lt;&gt;17,LEN($E262)-LEN(SUBSTITUTE($E262,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8215,11 +9016,14 @@
       <c r="J263" s="24" t="n"/>
       <c r="K263" s="24" t="n"/>
       <c r="L263" s="24" t="n"/>
-      <c r="N263">
-        <f>IF(COUNTA($A263:$L263)=0,0,IF(OR($B263="",$D263="",$F263="",$G263=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O263">
+      <c r="M263" s="24" t="n"/>
+      <c r="N263" s="24" t="n"/>
+      <c r="O263" s="24" t="n"/>
+      <c r="P263">
+        <f>IF(COUNTA($A263:$O263)=0,0,IF(OR($B263="",$D263="",$F263="",$G263=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q263">
         <f>IF(OR(AND($D263&lt;&gt;"",OR(LEN($D263)&lt;&gt;17,LEN($D263)-LEN(SUBSTITUTE($D263,":",""))&lt;&gt;5)),AND($E263&lt;&gt;"",OR(LEN($E263)&lt;&gt;17,LEN($E263)-LEN(SUBSTITUTE($E263,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8237,11 +9041,14 @@
       <c r="J264" s="24" t="n"/>
       <c r="K264" s="24" t="n"/>
       <c r="L264" s="24" t="n"/>
-      <c r="N264">
-        <f>IF(COUNTA($A264:$L264)=0,0,IF(OR($B264="",$D264="",$F264="",$G264=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O264">
+      <c r="M264" s="24" t="n"/>
+      <c r="N264" s="24" t="n"/>
+      <c r="O264" s="24" t="n"/>
+      <c r="P264">
+        <f>IF(COUNTA($A264:$O264)=0,0,IF(OR($B264="",$D264="",$F264="",$G264=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q264">
         <f>IF(OR(AND($D264&lt;&gt;"",OR(LEN($D264)&lt;&gt;17,LEN($D264)-LEN(SUBSTITUTE($D264,":",""))&lt;&gt;5)),AND($E264&lt;&gt;"",OR(LEN($E264)&lt;&gt;17,LEN($E264)-LEN(SUBSTITUTE($E264,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8259,11 +9066,14 @@
       <c r="J265" s="24" t="n"/>
       <c r="K265" s="24" t="n"/>
       <c r="L265" s="24" t="n"/>
-      <c r="N265">
-        <f>IF(COUNTA($A265:$L265)=0,0,IF(OR($B265="",$D265="",$F265="",$G265=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O265">
+      <c r="M265" s="24" t="n"/>
+      <c r="N265" s="24" t="n"/>
+      <c r="O265" s="24" t="n"/>
+      <c r="P265">
+        <f>IF(COUNTA($A265:$O265)=0,0,IF(OR($B265="",$D265="",$F265="",$G265=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q265">
         <f>IF(OR(AND($D265&lt;&gt;"",OR(LEN($D265)&lt;&gt;17,LEN($D265)-LEN(SUBSTITUTE($D265,":",""))&lt;&gt;5)),AND($E265&lt;&gt;"",OR(LEN($E265)&lt;&gt;17,LEN($E265)-LEN(SUBSTITUTE($E265,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8281,11 +9091,14 @@
       <c r="J266" s="24" t="n"/>
       <c r="K266" s="24" t="n"/>
       <c r="L266" s="24" t="n"/>
-      <c r="N266">
-        <f>IF(COUNTA($A266:$L266)=0,0,IF(OR($B266="",$D266="",$F266="",$G266=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O266">
+      <c r="M266" s="24" t="n"/>
+      <c r="N266" s="24" t="n"/>
+      <c r="O266" s="24" t="n"/>
+      <c r="P266">
+        <f>IF(COUNTA($A266:$O266)=0,0,IF(OR($B266="",$D266="",$F266="",$G266=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q266">
         <f>IF(OR(AND($D266&lt;&gt;"",OR(LEN($D266)&lt;&gt;17,LEN($D266)-LEN(SUBSTITUTE($D266,":",""))&lt;&gt;5)),AND($E266&lt;&gt;"",OR(LEN($E266)&lt;&gt;17,LEN($E266)-LEN(SUBSTITUTE($E266,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8303,11 +9116,14 @@
       <c r="J267" s="24" t="n"/>
       <c r="K267" s="24" t="n"/>
       <c r="L267" s="24" t="n"/>
-      <c r="N267">
-        <f>IF(COUNTA($A267:$L267)=0,0,IF(OR($B267="",$D267="",$F267="",$G267=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O267">
+      <c r="M267" s="24" t="n"/>
+      <c r="N267" s="24" t="n"/>
+      <c r="O267" s="24" t="n"/>
+      <c r="P267">
+        <f>IF(COUNTA($A267:$O267)=0,0,IF(OR($B267="",$D267="",$F267="",$G267=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q267">
         <f>IF(OR(AND($D267&lt;&gt;"",OR(LEN($D267)&lt;&gt;17,LEN($D267)-LEN(SUBSTITUTE($D267,":",""))&lt;&gt;5)),AND($E267&lt;&gt;"",OR(LEN($E267)&lt;&gt;17,LEN($E267)-LEN(SUBSTITUTE($E267,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8325,11 +9141,14 @@
       <c r="J268" s="24" t="n"/>
       <c r="K268" s="24" t="n"/>
       <c r="L268" s="24" t="n"/>
-      <c r="N268">
-        <f>IF(COUNTA($A268:$L268)=0,0,IF(OR($B268="",$D268="",$F268="",$G268=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O268">
+      <c r="M268" s="24" t="n"/>
+      <c r="N268" s="24" t="n"/>
+      <c r="O268" s="24" t="n"/>
+      <c r="P268">
+        <f>IF(COUNTA($A268:$O268)=0,0,IF(OR($B268="",$D268="",$F268="",$G268=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q268">
         <f>IF(OR(AND($D268&lt;&gt;"",OR(LEN($D268)&lt;&gt;17,LEN($D268)-LEN(SUBSTITUTE($D268,":",""))&lt;&gt;5)),AND($E268&lt;&gt;"",OR(LEN($E268)&lt;&gt;17,LEN($E268)-LEN(SUBSTITUTE($E268,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8347,11 +9166,14 @@
       <c r="J269" s="24" t="n"/>
       <c r="K269" s="24" t="n"/>
       <c r="L269" s="24" t="n"/>
-      <c r="N269">
-        <f>IF(COUNTA($A269:$L269)=0,0,IF(OR($B269="",$D269="",$F269="",$G269=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O269">
+      <c r="M269" s="24" t="n"/>
+      <c r="N269" s="24" t="n"/>
+      <c r="O269" s="24" t="n"/>
+      <c r="P269">
+        <f>IF(COUNTA($A269:$O269)=0,0,IF(OR($B269="",$D269="",$F269="",$G269=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q269">
         <f>IF(OR(AND($D269&lt;&gt;"",OR(LEN($D269)&lt;&gt;17,LEN($D269)-LEN(SUBSTITUTE($D269,":",""))&lt;&gt;5)),AND($E269&lt;&gt;"",OR(LEN($E269)&lt;&gt;17,LEN($E269)-LEN(SUBSTITUTE($E269,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8369,11 +9191,14 @@
       <c r="J270" s="24" t="n"/>
       <c r="K270" s="24" t="n"/>
       <c r="L270" s="24" t="n"/>
-      <c r="N270">
-        <f>IF(COUNTA($A270:$L270)=0,0,IF(OR($B270="",$D270="",$F270="",$G270=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O270">
+      <c r="M270" s="24" t="n"/>
+      <c r="N270" s="24" t="n"/>
+      <c r="O270" s="24" t="n"/>
+      <c r="P270">
+        <f>IF(COUNTA($A270:$O270)=0,0,IF(OR($B270="",$D270="",$F270="",$G270=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q270">
         <f>IF(OR(AND($D270&lt;&gt;"",OR(LEN($D270)&lt;&gt;17,LEN($D270)-LEN(SUBSTITUTE($D270,":",""))&lt;&gt;5)),AND($E270&lt;&gt;"",OR(LEN($E270)&lt;&gt;17,LEN($E270)-LEN(SUBSTITUTE($E270,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8391,11 +9216,14 @@
       <c r="J271" s="24" t="n"/>
       <c r="K271" s="24" t="n"/>
       <c r="L271" s="24" t="n"/>
-      <c r="N271">
-        <f>IF(COUNTA($A271:$L271)=0,0,IF(OR($B271="",$D271="",$F271="",$G271=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O271">
+      <c r="M271" s="24" t="n"/>
+      <c r="N271" s="24" t="n"/>
+      <c r="O271" s="24" t="n"/>
+      <c r="P271">
+        <f>IF(COUNTA($A271:$O271)=0,0,IF(OR($B271="",$D271="",$F271="",$G271=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q271">
         <f>IF(OR(AND($D271&lt;&gt;"",OR(LEN($D271)&lt;&gt;17,LEN($D271)-LEN(SUBSTITUTE($D271,":",""))&lt;&gt;5)),AND($E271&lt;&gt;"",OR(LEN($E271)&lt;&gt;17,LEN($E271)-LEN(SUBSTITUTE($E271,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8413,11 +9241,14 @@
       <c r="J272" s="24" t="n"/>
       <c r="K272" s="24" t="n"/>
       <c r="L272" s="24" t="n"/>
-      <c r="N272">
-        <f>IF(COUNTA($A272:$L272)=0,0,IF(OR($B272="",$D272="",$F272="",$G272=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O272">
+      <c r="M272" s="24" t="n"/>
+      <c r="N272" s="24" t="n"/>
+      <c r="O272" s="24" t="n"/>
+      <c r="P272">
+        <f>IF(COUNTA($A272:$O272)=0,0,IF(OR($B272="",$D272="",$F272="",$G272=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q272">
         <f>IF(OR(AND($D272&lt;&gt;"",OR(LEN($D272)&lt;&gt;17,LEN($D272)-LEN(SUBSTITUTE($D272,":",""))&lt;&gt;5)),AND($E272&lt;&gt;"",OR(LEN($E272)&lt;&gt;17,LEN($E272)-LEN(SUBSTITUTE($E272,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8435,11 +9266,14 @@
       <c r="J273" s="24" t="n"/>
       <c r="K273" s="24" t="n"/>
       <c r="L273" s="24" t="n"/>
-      <c r="N273">
-        <f>IF(COUNTA($A273:$L273)=0,0,IF(OR($B273="",$D273="",$F273="",$G273=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O273">
+      <c r="M273" s="24" t="n"/>
+      <c r="N273" s="24" t="n"/>
+      <c r="O273" s="24" t="n"/>
+      <c r="P273">
+        <f>IF(COUNTA($A273:$O273)=0,0,IF(OR($B273="",$D273="",$F273="",$G273=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q273">
         <f>IF(OR(AND($D273&lt;&gt;"",OR(LEN($D273)&lt;&gt;17,LEN($D273)-LEN(SUBSTITUTE($D273,":",""))&lt;&gt;5)),AND($E273&lt;&gt;"",OR(LEN($E273)&lt;&gt;17,LEN($E273)-LEN(SUBSTITUTE($E273,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8457,11 +9291,14 @@
       <c r="J274" s="24" t="n"/>
       <c r="K274" s="24" t="n"/>
       <c r="L274" s="24" t="n"/>
-      <c r="N274">
-        <f>IF(COUNTA($A274:$L274)=0,0,IF(OR($B274="",$D274="",$F274="",$G274=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O274">
+      <c r="M274" s="24" t="n"/>
+      <c r="N274" s="24" t="n"/>
+      <c r="O274" s="24" t="n"/>
+      <c r="P274">
+        <f>IF(COUNTA($A274:$O274)=0,0,IF(OR($B274="",$D274="",$F274="",$G274=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q274">
         <f>IF(OR(AND($D274&lt;&gt;"",OR(LEN($D274)&lt;&gt;17,LEN($D274)-LEN(SUBSTITUTE($D274,":",""))&lt;&gt;5)),AND($E274&lt;&gt;"",OR(LEN($E274)&lt;&gt;17,LEN($E274)-LEN(SUBSTITUTE($E274,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8479,11 +9316,14 @@
       <c r="J275" s="24" t="n"/>
       <c r="K275" s="24" t="n"/>
       <c r="L275" s="24" t="n"/>
-      <c r="N275">
-        <f>IF(COUNTA($A275:$L275)=0,0,IF(OR($B275="",$D275="",$F275="",$G275=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O275">
+      <c r="M275" s="24" t="n"/>
+      <c r="N275" s="24" t="n"/>
+      <c r="O275" s="24" t="n"/>
+      <c r="P275">
+        <f>IF(COUNTA($A275:$O275)=0,0,IF(OR($B275="",$D275="",$F275="",$G275=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q275">
         <f>IF(OR(AND($D275&lt;&gt;"",OR(LEN($D275)&lt;&gt;17,LEN($D275)-LEN(SUBSTITUTE($D275,":",""))&lt;&gt;5)),AND($E275&lt;&gt;"",OR(LEN($E275)&lt;&gt;17,LEN($E275)-LEN(SUBSTITUTE($E275,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8501,11 +9341,14 @@
       <c r="J276" s="24" t="n"/>
       <c r="K276" s="24" t="n"/>
       <c r="L276" s="24" t="n"/>
-      <c r="N276">
-        <f>IF(COUNTA($A276:$L276)=0,0,IF(OR($B276="",$D276="",$F276="",$G276=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O276">
+      <c r="M276" s="24" t="n"/>
+      <c r="N276" s="24" t="n"/>
+      <c r="O276" s="24" t="n"/>
+      <c r="P276">
+        <f>IF(COUNTA($A276:$O276)=0,0,IF(OR($B276="",$D276="",$F276="",$G276=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q276">
         <f>IF(OR(AND($D276&lt;&gt;"",OR(LEN($D276)&lt;&gt;17,LEN($D276)-LEN(SUBSTITUTE($D276,":",""))&lt;&gt;5)),AND($E276&lt;&gt;"",OR(LEN($E276)&lt;&gt;17,LEN($E276)-LEN(SUBSTITUTE($E276,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8523,11 +9366,14 @@
       <c r="J277" s="24" t="n"/>
       <c r="K277" s="24" t="n"/>
       <c r="L277" s="24" t="n"/>
-      <c r="N277">
-        <f>IF(COUNTA($A277:$L277)=0,0,IF(OR($B277="",$D277="",$F277="",$G277=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O277">
+      <c r="M277" s="24" t="n"/>
+      <c r="N277" s="24" t="n"/>
+      <c r="O277" s="24" t="n"/>
+      <c r="P277">
+        <f>IF(COUNTA($A277:$O277)=0,0,IF(OR($B277="",$D277="",$F277="",$G277=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q277">
         <f>IF(OR(AND($D277&lt;&gt;"",OR(LEN($D277)&lt;&gt;17,LEN($D277)-LEN(SUBSTITUTE($D277,":",""))&lt;&gt;5)),AND($E277&lt;&gt;"",OR(LEN($E277)&lt;&gt;17,LEN($E277)-LEN(SUBSTITUTE($E277,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8545,11 +9391,14 @@
       <c r="J278" s="24" t="n"/>
       <c r="K278" s="24" t="n"/>
       <c r="L278" s="24" t="n"/>
-      <c r="N278">
-        <f>IF(COUNTA($A278:$L278)=0,0,IF(OR($B278="",$D278="",$F278="",$G278=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O278">
+      <c r="M278" s="24" t="n"/>
+      <c r="N278" s="24" t="n"/>
+      <c r="O278" s="24" t="n"/>
+      <c r="P278">
+        <f>IF(COUNTA($A278:$O278)=0,0,IF(OR($B278="",$D278="",$F278="",$G278=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q278">
         <f>IF(OR(AND($D278&lt;&gt;"",OR(LEN($D278)&lt;&gt;17,LEN($D278)-LEN(SUBSTITUTE($D278,":",""))&lt;&gt;5)),AND($E278&lt;&gt;"",OR(LEN($E278)&lt;&gt;17,LEN($E278)-LEN(SUBSTITUTE($E278,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8567,11 +9416,14 @@
       <c r="J279" s="24" t="n"/>
       <c r="K279" s="24" t="n"/>
       <c r="L279" s="24" t="n"/>
-      <c r="N279">
-        <f>IF(COUNTA($A279:$L279)=0,0,IF(OR($B279="",$D279="",$F279="",$G279=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O279">
+      <c r="M279" s="24" t="n"/>
+      <c r="N279" s="24" t="n"/>
+      <c r="O279" s="24" t="n"/>
+      <c r="P279">
+        <f>IF(COUNTA($A279:$O279)=0,0,IF(OR($B279="",$D279="",$F279="",$G279=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q279">
         <f>IF(OR(AND($D279&lt;&gt;"",OR(LEN($D279)&lt;&gt;17,LEN($D279)-LEN(SUBSTITUTE($D279,":",""))&lt;&gt;5)),AND($E279&lt;&gt;"",OR(LEN($E279)&lt;&gt;17,LEN($E279)-LEN(SUBSTITUTE($E279,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8589,11 +9441,14 @@
       <c r="J280" s="24" t="n"/>
       <c r="K280" s="24" t="n"/>
       <c r="L280" s="24" t="n"/>
-      <c r="N280">
-        <f>IF(COUNTA($A280:$L280)=0,0,IF(OR($B280="",$D280="",$F280="",$G280=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O280">
+      <c r="M280" s="24" t="n"/>
+      <c r="N280" s="24" t="n"/>
+      <c r="O280" s="24" t="n"/>
+      <c r="P280">
+        <f>IF(COUNTA($A280:$O280)=0,0,IF(OR($B280="",$D280="",$F280="",$G280=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q280">
         <f>IF(OR(AND($D280&lt;&gt;"",OR(LEN($D280)&lt;&gt;17,LEN($D280)-LEN(SUBSTITUTE($D280,":",""))&lt;&gt;5)),AND($E280&lt;&gt;"",OR(LEN($E280)&lt;&gt;17,LEN($E280)-LEN(SUBSTITUTE($E280,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8611,11 +9466,14 @@
       <c r="J281" s="24" t="n"/>
       <c r="K281" s="24" t="n"/>
       <c r="L281" s="24" t="n"/>
-      <c r="N281">
-        <f>IF(COUNTA($A281:$L281)=0,0,IF(OR($B281="",$D281="",$F281="",$G281=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O281">
+      <c r="M281" s="24" t="n"/>
+      <c r="N281" s="24" t="n"/>
+      <c r="O281" s="24" t="n"/>
+      <c r="P281">
+        <f>IF(COUNTA($A281:$O281)=0,0,IF(OR($B281="",$D281="",$F281="",$G281=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q281">
         <f>IF(OR(AND($D281&lt;&gt;"",OR(LEN($D281)&lt;&gt;17,LEN($D281)-LEN(SUBSTITUTE($D281,":",""))&lt;&gt;5)),AND($E281&lt;&gt;"",OR(LEN($E281)&lt;&gt;17,LEN($E281)-LEN(SUBSTITUTE($E281,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8633,11 +9491,14 @@
       <c r="J282" s="24" t="n"/>
       <c r="K282" s="24" t="n"/>
       <c r="L282" s="24" t="n"/>
-      <c r="N282">
-        <f>IF(COUNTA($A282:$L282)=0,0,IF(OR($B282="",$D282="",$F282="",$G282=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O282">
+      <c r="M282" s="24" t="n"/>
+      <c r="N282" s="24" t="n"/>
+      <c r="O282" s="24" t="n"/>
+      <c r="P282">
+        <f>IF(COUNTA($A282:$O282)=0,0,IF(OR($B282="",$D282="",$F282="",$G282=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q282">
         <f>IF(OR(AND($D282&lt;&gt;"",OR(LEN($D282)&lt;&gt;17,LEN($D282)-LEN(SUBSTITUTE($D282,":",""))&lt;&gt;5)),AND($E282&lt;&gt;"",OR(LEN($E282)&lt;&gt;17,LEN($E282)-LEN(SUBSTITUTE($E282,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8655,11 +9516,14 @@
       <c r="J283" s="24" t="n"/>
       <c r="K283" s="24" t="n"/>
       <c r="L283" s="24" t="n"/>
-      <c r="N283">
-        <f>IF(COUNTA($A283:$L283)=0,0,IF(OR($B283="",$D283="",$F283="",$G283=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O283">
+      <c r="M283" s="24" t="n"/>
+      <c r="N283" s="24" t="n"/>
+      <c r="O283" s="24" t="n"/>
+      <c r="P283">
+        <f>IF(COUNTA($A283:$O283)=0,0,IF(OR($B283="",$D283="",$F283="",$G283=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q283">
         <f>IF(OR(AND($D283&lt;&gt;"",OR(LEN($D283)&lt;&gt;17,LEN($D283)-LEN(SUBSTITUTE($D283,":",""))&lt;&gt;5)),AND($E283&lt;&gt;"",OR(LEN($E283)&lt;&gt;17,LEN($E283)-LEN(SUBSTITUTE($E283,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8677,11 +9541,14 @@
       <c r="J284" s="24" t="n"/>
       <c r="K284" s="24" t="n"/>
       <c r="L284" s="24" t="n"/>
-      <c r="N284">
-        <f>IF(COUNTA($A284:$L284)=0,0,IF(OR($B284="",$D284="",$F284="",$G284=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O284">
+      <c r="M284" s="24" t="n"/>
+      <c r="N284" s="24" t="n"/>
+      <c r="O284" s="24" t="n"/>
+      <c r="P284">
+        <f>IF(COUNTA($A284:$O284)=0,0,IF(OR($B284="",$D284="",$F284="",$G284=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q284">
         <f>IF(OR(AND($D284&lt;&gt;"",OR(LEN($D284)&lt;&gt;17,LEN($D284)-LEN(SUBSTITUTE($D284,":",""))&lt;&gt;5)),AND($E284&lt;&gt;"",OR(LEN($E284)&lt;&gt;17,LEN($E284)-LEN(SUBSTITUTE($E284,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8699,11 +9566,14 @@
       <c r="J285" s="24" t="n"/>
       <c r="K285" s="24" t="n"/>
       <c r="L285" s="24" t="n"/>
-      <c r="N285">
-        <f>IF(COUNTA($A285:$L285)=0,0,IF(OR($B285="",$D285="",$F285="",$G285=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O285">
+      <c r="M285" s="24" t="n"/>
+      <c r="N285" s="24" t="n"/>
+      <c r="O285" s="24" t="n"/>
+      <c r="P285">
+        <f>IF(COUNTA($A285:$O285)=0,0,IF(OR($B285="",$D285="",$F285="",$G285=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q285">
         <f>IF(OR(AND($D285&lt;&gt;"",OR(LEN($D285)&lt;&gt;17,LEN($D285)-LEN(SUBSTITUTE($D285,":",""))&lt;&gt;5)),AND($E285&lt;&gt;"",OR(LEN($E285)&lt;&gt;17,LEN($E285)-LEN(SUBSTITUTE($E285,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8721,11 +9591,14 @@
       <c r="J286" s="24" t="n"/>
       <c r="K286" s="24" t="n"/>
       <c r="L286" s="24" t="n"/>
-      <c r="N286">
-        <f>IF(COUNTA($A286:$L286)=0,0,IF(OR($B286="",$D286="",$F286="",$G286=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O286">
+      <c r="M286" s="24" t="n"/>
+      <c r="N286" s="24" t="n"/>
+      <c r="O286" s="24" t="n"/>
+      <c r="P286">
+        <f>IF(COUNTA($A286:$O286)=0,0,IF(OR($B286="",$D286="",$F286="",$G286=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q286">
         <f>IF(OR(AND($D286&lt;&gt;"",OR(LEN($D286)&lt;&gt;17,LEN($D286)-LEN(SUBSTITUTE($D286,":",""))&lt;&gt;5)),AND($E286&lt;&gt;"",OR(LEN($E286)&lt;&gt;17,LEN($E286)-LEN(SUBSTITUTE($E286,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8743,11 +9616,14 @@
       <c r="J287" s="24" t="n"/>
       <c r="K287" s="24" t="n"/>
       <c r="L287" s="24" t="n"/>
-      <c r="N287">
-        <f>IF(COUNTA($A287:$L287)=0,0,IF(OR($B287="",$D287="",$F287="",$G287=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O287">
+      <c r="M287" s="24" t="n"/>
+      <c r="N287" s="24" t="n"/>
+      <c r="O287" s="24" t="n"/>
+      <c r="P287">
+        <f>IF(COUNTA($A287:$O287)=0,0,IF(OR($B287="",$D287="",$F287="",$G287=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q287">
         <f>IF(OR(AND($D287&lt;&gt;"",OR(LEN($D287)&lt;&gt;17,LEN($D287)-LEN(SUBSTITUTE($D287,":",""))&lt;&gt;5)),AND($E287&lt;&gt;"",OR(LEN($E287)&lt;&gt;17,LEN($E287)-LEN(SUBSTITUTE($E287,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8765,11 +9641,14 @@
       <c r="J288" s="24" t="n"/>
       <c r="K288" s="24" t="n"/>
       <c r="L288" s="24" t="n"/>
-      <c r="N288">
-        <f>IF(COUNTA($A288:$L288)=0,0,IF(OR($B288="",$D288="",$F288="",$G288=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O288">
+      <c r="M288" s="24" t="n"/>
+      <c r="N288" s="24" t="n"/>
+      <c r="O288" s="24" t="n"/>
+      <c r="P288">
+        <f>IF(COUNTA($A288:$O288)=0,0,IF(OR($B288="",$D288="",$F288="",$G288=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q288">
         <f>IF(OR(AND($D288&lt;&gt;"",OR(LEN($D288)&lt;&gt;17,LEN($D288)-LEN(SUBSTITUTE($D288,":",""))&lt;&gt;5)),AND($E288&lt;&gt;"",OR(LEN($E288)&lt;&gt;17,LEN($E288)-LEN(SUBSTITUTE($E288,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8787,11 +9666,14 @@
       <c r="J289" s="24" t="n"/>
       <c r="K289" s="24" t="n"/>
       <c r="L289" s="24" t="n"/>
-      <c r="N289">
-        <f>IF(COUNTA($A289:$L289)=0,0,IF(OR($B289="",$D289="",$F289="",$G289=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O289">
+      <c r="M289" s="24" t="n"/>
+      <c r="N289" s="24" t="n"/>
+      <c r="O289" s="24" t="n"/>
+      <c r="P289">
+        <f>IF(COUNTA($A289:$O289)=0,0,IF(OR($B289="",$D289="",$F289="",$G289=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q289">
         <f>IF(OR(AND($D289&lt;&gt;"",OR(LEN($D289)&lt;&gt;17,LEN($D289)-LEN(SUBSTITUTE($D289,":",""))&lt;&gt;5)),AND($E289&lt;&gt;"",OR(LEN($E289)&lt;&gt;17,LEN($E289)-LEN(SUBSTITUTE($E289,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8809,11 +9691,14 @@
       <c r="J290" s="24" t="n"/>
       <c r="K290" s="24" t="n"/>
       <c r="L290" s="24" t="n"/>
-      <c r="N290">
-        <f>IF(COUNTA($A290:$L290)=0,0,IF(OR($B290="",$D290="",$F290="",$G290=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O290">
+      <c r="M290" s="24" t="n"/>
+      <c r="N290" s="24" t="n"/>
+      <c r="O290" s="24" t="n"/>
+      <c r="P290">
+        <f>IF(COUNTA($A290:$O290)=0,0,IF(OR($B290="",$D290="",$F290="",$G290=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q290">
         <f>IF(OR(AND($D290&lt;&gt;"",OR(LEN($D290)&lt;&gt;17,LEN($D290)-LEN(SUBSTITUTE($D290,":",""))&lt;&gt;5)),AND($E290&lt;&gt;"",OR(LEN($E290)&lt;&gt;17,LEN($E290)-LEN(SUBSTITUTE($E290,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8831,11 +9716,14 @@
       <c r="J291" s="24" t="n"/>
       <c r="K291" s="24" t="n"/>
       <c r="L291" s="24" t="n"/>
-      <c r="N291">
-        <f>IF(COUNTA($A291:$L291)=0,0,IF(OR($B291="",$D291="",$F291="",$G291=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O291">
+      <c r="M291" s="24" t="n"/>
+      <c r="N291" s="24" t="n"/>
+      <c r="O291" s="24" t="n"/>
+      <c r="P291">
+        <f>IF(COUNTA($A291:$O291)=0,0,IF(OR($B291="",$D291="",$F291="",$G291=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q291">
         <f>IF(OR(AND($D291&lt;&gt;"",OR(LEN($D291)&lt;&gt;17,LEN($D291)-LEN(SUBSTITUTE($D291,":",""))&lt;&gt;5)),AND($E291&lt;&gt;"",OR(LEN($E291)&lt;&gt;17,LEN($E291)-LEN(SUBSTITUTE($E291,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8853,11 +9741,14 @@
       <c r="J292" s="24" t="n"/>
       <c r="K292" s="24" t="n"/>
       <c r="L292" s="24" t="n"/>
-      <c r="N292">
-        <f>IF(COUNTA($A292:$L292)=0,0,IF(OR($B292="",$D292="",$F292="",$G292=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O292">
+      <c r="M292" s="24" t="n"/>
+      <c r="N292" s="24" t="n"/>
+      <c r="O292" s="24" t="n"/>
+      <c r="P292">
+        <f>IF(COUNTA($A292:$O292)=0,0,IF(OR($B292="",$D292="",$F292="",$G292=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q292">
         <f>IF(OR(AND($D292&lt;&gt;"",OR(LEN($D292)&lt;&gt;17,LEN($D292)-LEN(SUBSTITUTE($D292,":",""))&lt;&gt;5)),AND($E292&lt;&gt;"",OR(LEN($E292)&lt;&gt;17,LEN($E292)-LEN(SUBSTITUTE($E292,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8875,11 +9766,14 @@
       <c r="J293" s="24" t="n"/>
       <c r="K293" s="24" t="n"/>
       <c r="L293" s="24" t="n"/>
-      <c r="N293">
-        <f>IF(COUNTA($A293:$L293)=0,0,IF(OR($B293="",$D293="",$F293="",$G293=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O293">
+      <c r="M293" s="24" t="n"/>
+      <c r="N293" s="24" t="n"/>
+      <c r="O293" s="24" t="n"/>
+      <c r="P293">
+        <f>IF(COUNTA($A293:$O293)=0,0,IF(OR($B293="",$D293="",$F293="",$G293=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q293">
         <f>IF(OR(AND($D293&lt;&gt;"",OR(LEN($D293)&lt;&gt;17,LEN($D293)-LEN(SUBSTITUTE($D293,":",""))&lt;&gt;5)),AND($E293&lt;&gt;"",OR(LEN($E293)&lt;&gt;17,LEN($E293)-LEN(SUBSTITUTE($E293,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8897,11 +9791,14 @@
       <c r="J294" s="24" t="n"/>
       <c r="K294" s="24" t="n"/>
       <c r="L294" s="24" t="n"/>
-      <c r="N294">
-        <f>IF(COUNTA($A294:$L294)=0,0,IF(OR($B294="",$D294="",$F294="",$G294=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O294">
+      <c r="M294" s="24" t="n"/>
+      <c r="N294" s="24" t="n"/>
+      <c r="O294" s="24" t="n"/>
+      <c r="P294">
+        <f>IF(COUNTA($A294:$O294)=0,0,IF(OR($B294="",$D294="",$F294="",$G294=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q294">
         <f>IF(OR(AND($D294&lt;&gt;"",OR(LEN($D294)&lt;&gt;17,LEN($D294)-LEN(SUBSTITUTE($D294,":",""))&lt;&gt;5)),AND($E294&lt;&gt;"",OR(LEN($E294)&lt;&gt;17,LEN($E294)-LEN(SUBSTITUTE($E294,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8919,11 +9816,14 @@
       <c r="J295" s="24" t="n"/>
       <c r="K295" s="24" t="n"/>
       <c r="L295" s="24" t="n"/>
-      <c r="N295">
-        <f>IF(COUNTA($A295:$L295)=0,0,IF(OR($B295="",$D295="",$F295="",$G295=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O295">
+      <c r="M295" s="24" t="n"/>
+      <c r="N295" s="24" t="n"/>
+      <c r="O295" s="24" t="n"/>
+      <c r="P295">
+        <f>IF(COUNTA($A295:$O295)=0,0,IF(OR($B295="",$D295="",$F295="",$G295=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q295">
         <f>IF(OR(AND($D295&lt;&gt;"",OR(LEN($D295)&lt;&gt;17,LEN($D295)-LEN(SUBSTITUTE($D295,":",""))&lt;&gt;5)),AND($E295&lt;&gt;"",OR(LEN($E295)&lt;&gt;17,LEN($E295)-LEN(SUBSTITUTE($E295,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8941,11 +9841,14 @@
       <c r="J296" s="24" t="n"/>
       <c r="K296" s="24" t="n"/>
       <c r="L296" s="24" t="n"/>
-      <c r="N296">
-        <f>IF(COUNTA($A296:$L296)=0,0,IF(OR($B296="",$D296="",$F296="",$G296=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O296">
+      <c r="M296" s="24" t="n"/>
+      <c r="N296" s="24" t="n"/>
+      <c r="O296" s="24" t="n"/>
+      <c r="P296">
+        <f>IF(COUNTA($A296:$O296)=0,0,IF(OR($B296="",$D296="",$F296="",$G296=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q296">
         <f>IF(OR(AND($D296&lt;&gt;"",OR(LEN($D296)&lt;&gt;17,LEN($D296)-LEN(SUBSTITUTE($D296,":",""))&lt;&gt;5)),AND($E296&lt;&gt;"",OR(LEN($E296)&lt;&gt;17,LEN($E296)-LEN(SUBSTITUTE($E296,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8963,11 +9866,14 @@
       <c r="J297" s="24" t="n"/>
       <c r="K297" s="24" t="n"/>
       <c r="L297" s="24" t="n"/>
-      <c r="N297">
-        <f>IF(COUNTA($A297:$L297)=0,0,IF(OR($B297="",$D297="",$F297="",$G297=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O297">
+      <c r="M297" s="24" t="n"/>
+      <c r="N297" s="24" t="n"/>
+      <c r="O297" s="24" t="n"/>
+      <c r="P297">
+        <f>IF(COUNTA($A297:$O297)=0,0,IF(OR($B297="",$D297="",$F297="",$G297=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q297">
         <f>IF(OR(AND($D297&lt;&gt;"",OR(LEN($D297)&lt;&gt;17,LEN($D297)-LEN(SUBSTITUTE($D297,":",""))&lt;&gt;5)),AND($E297&lt;&gt;"",OR(LEN($E297)&lt;&gt;17,LEN($E297)-LEN(SUBSTITUTE($E297,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8985,11 +9891,14 @@
       <c r="J298" s="24" t="n"/>
       <c r="K298" s="24" t="n"/>
       <c r="L298" s="24" t="n"/>
-      <c r="N298">
-        <f>IF(COUNTA($A298:$L298)=0,0,IF(OR($B298="",$D298="",$F298="",$G298=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O298">
+      <c r="M298" s="24" t="n"/>
+      <c r="N298" s="24" t="n"/>
+      <c r="O298" s="24" t="n"/>
+      <c r="P298">
+        <f>IF(COUNTA($A298:$O298)=0,0,IF(OR($B298="",$D298="",$F298="",$G298=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q298">
         <f>IF(OR(AND($D298&lt;&gt;"",OR(LEN($D298)&lt;&gt;17,LEN($D298)-LEN(SUBSTITUTE($D298,":",""))&lt;&gt;5)),AND($E298&lt;&gt;"",OR(LEN($E298)&lt;&gt;17,LEN($E298)-LEN(SUBSTITUTE($E298,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -9007,11 +9916,14 @@
       <c r="J299" s="24" t="n"/>
       <c r="K299" s="24" t="n"/>
       <c r="L299" s="24" t="n"/>
-      <c r="N299">
-        <f>IF(COUNTA($A299:$L299)=0,0,IF(OR($B299="",$D299="",$F299="",$G299=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O299">
+      <c r="M299" s="24" t="n"/>
+      <c r="N299" s="24" t="n"/>
+      <c r="O299" s="24" t="n"/>
+      <c r="P299">
+        <f>IF(COUNTA($A299:$O299)=0,0,IF(OR($B299="",$D299="",$F299="",$G299=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q299">
         <f>IF(OR(AND($D299&lt;&gt;"",OR(LEN($D299)&lt;&gt;17,LEN($D299)-LEN(SUBSTITUTE($D299,":",""))&lt;&gt;5)),AND($E299&lt;&gt;"",OR(LEN($E299)&lt;&gt;17,LEN($E299)-LEN(SUBSTITUTE($E299,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -9029,11 +9941,14 @@
       <c r="J300" s="24" t="n"/>
       <c r="K300" s="24" t="n"/>
       <c r="L300" s="24" t="n"/>
-      <c r="N300">
-        <f>IF(COUNTA($A300:$L300)=0,0,IF(OR($B300="",$D300="",$F300="",$G300=""),1,0))</f>
-        <v/>
-      </c>
-      <c r="O300">
+      <c r="M300" s="24" t="n"/>
+      <c r="N300" s="24" t="n"/>
+      <c r="O300" s="24" t="n"/>
+      <c r="P300">
+        <f>IF(COUNTA($A300:$O300)=0,0,IF(OR($B300="",$D300="",$F300="",$G300=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="Q300">
         <f>IF(OR(AND($D300&lt;&gt;"",OR(LEN($D300)&lt;&gt;17,LEN($D300)-LEN(SUBSTITUTE($D300,":",""))&lt;&gt;5)),AND($E300&lt;&gt;"",OR(LEN($E300)&lt;&gt;17,LEN($E300)-LEN(SUBSTITUTE($E300,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>

--- a/src/main/resources/canevas/canevas-vierge.xlsx
+++ b/src/main/resources/canevas/canevas-vierge.xlsx
@@ -2419,7 +2419,7 @@
       </c>
       <c r="F1" s="10" t="inlineStr">
         <is>
-          <t>Agent attributaire *</t>
+          <t>Affecté à *</t>
         </is>
       </c>
       <c r="G1" s="10" t="inlineStr">

--- a/src/main/resources/canevas/canevas-vierge.xlsx
+++ b/src/main/resources/canevas/canevas-vierge.xlsx
@@ -128,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -189,6 +189,9 @@
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
@@ -1026,6 +1029,10 @@
         </is>
       </c>
       <c r="B15" s="24" t="n"/>
+      <c r="C15" s="24" t="n"/>
+      <c r="D15" s="24" t="n"/>
+      <c r="E15" s="24" t="n"/>
+      <c r="F15" s="24" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
@@ -2512,11 +2519,11 @@
       <c r="J2" s="23" t="n"/>
       <c r="K2" s="23" t="n"/>
       <c r="L2" s="23" t="n"/>
-      <c r="M2" s="24" t="n"/>
-      <c r="N2" s="24" t="n"/>
-      <c r="O2" s="24" t="n"/>
-      <c r="P2" s="24" t="n"/>
-      <c r="Q2" s="24" t="n"/>
+      <c r="M2" s="25" t="n"/>
+      <c r="N2" s="25" t="n"/>
+      <c r="O2" s="25" t="n"/>
+      <c r="P2" s="25" t="n"/>
+      <c r="Q2" s="25" t="n"/>
       <c r="S2">
         <f>IF(COUNTA($A2:$Q2)=0,0,IF(OR($B2="",$D2="",$F2="",$G2=""),1,0))</f>
         <v/>
@@ -2539,11 +2546,11 @@
       <c r="J3" s="23" t="n"/>
       <c r="K3" s="23" t="n"/>
       <c r="L3" s="23" t="n"/>
-      <c r="M3" s="24" t="n"/>
-      <c r="N3" s="24" t="n"/>
-      <c r="O3" s="24" t="n"/>
-      <c r="P3" s="24" t="n"/>
-      <c r="Q3" s="24" t="n"/>
+      <c r="M3" s="25" t="n"/>
+      <c r="N3" s="25" t="n"/>
+      <c r="O3" s="25" t="n"/>
+      <c r="P3" s="25" t="n"/>
+      <c r="Q3" s="25" t="n"/>
       <c r="S3">
         <f>IF(COUNTA($A3:$Q3)=0,0,IF(OR($B3="",$D3="",$F3="",$G3=""),1,0))</f>
         <v/>
@@ -2566,11 +2573,11 @@
       <c r="J4" s="23" t="n"/>
       <c r="K4" s="23" t="n"/>
       <c r="L4" s="23" t="n"/>
-      <c r="M4" s="24" t="n"/>
-      <c r="N4" s="24" t="n"/>
-      <c r="O4" s="24" t="n"/>
-      <c r="P4" s="24" t="n"/>
-      <c r="Q4" s="24" t="n"/>
+      <c r="M4" s="25" t="n"/>
+      <c r="N4" s="25" t="n"/>
+      <c r="O4" s="25" t="n"/>
+      <c r="P4" s="25" t="n"/>
+      <c r="Q4" s="25" t="n"/>
       <c r="S4">
         <f>IF(COUNTA($A4:$Q4)=0,0,IF(OR($B4="",$D4="",$F4="",$G4=""),1,0))</f>
         <v/>
@@ -2593,11 +2600,11 @@
       <c r="J5" s="23" t="n"/>
       <c r="K5" s="23" t="n"/>
       <c r="L5" s="23" t="n"/>
-      <c r="M5" s="24" t="n"/>
-      <c r="N5" s="24" t="n"/>
-      <c r="O5" s="24" t="n"/>
-      <c r="P5" s="24" t="n"/>
-      <c r="Q5" s="24" t="n"/>
+      <c r="M5" s="25" t="n"/>
+      <c r="N5" s="25" t="n"/>
+      <c r="O5" s="25" t="n"/>
+      <c r="P5" s="25" t="n"/>
+      <c r="Q5" s="25" t="n"/>
       <c r="S5">
         <f>IF(COUNTA($A5:$Q5)=0,0,IF(OR($B5="",$D5="",$F5="",$G5=""),1,0))</f>
         <v/>
@@ -2620,11 +2627,11 @@
       <c r="J6" s="23" t="n"/>
       <c r="K6" s="23" t="n"/>
       <c r="L6" s="23" t="n"/>
-      <c r="M6" s="24" t="n"/>
-      <c r="N6" s="24" t="n"/>
-      <c r="O6" s="24" t="n"/>
-      <c r="P6" s="24" t="n"/>
-      <c r="Q6" s="24" t="n"/>
+      <c r="M6" s="25" t="n"/>
+      <c r="N6" s="25" t="n"/>
+      <c r="O6" s="25" t="n"/>
+      <c r="P6" s="25" t="n"/>
+      <c r="Q6" s="25" t="n"/>
       <c r="S6">
         <f>IF(COUNTA($A6:$Q6)=0,0,IF(OR($B6="",$D6="",$F6="",$G6=""),1,0))</f>
         <v/>
@@ -2647,11 +2654,11 @@
       <c r="J7" s="23" t="n"/>
       <c r="K7" s="23" t="n"/>
       <c r="L7" s="23" t="n"/>
-      <c r="M7" s="24" t="n"/>
-      <c r="N7" s="24" t="n"/>
-      <c r="O7" s="24" t="n"/>
-      <c r="P7" s="24" t="n"/>
-      <c r="Q7" s="24" t="n"/>
+      <c r="M7" s="25" t="n"/>
+      <c r="N7" s="25" t="n"/>
+      <c r="O7" s="25" t="n"/>
+      <c r="P7" s="25" t="n"/>
+      <c r="Q7" s="25" t="n"/>
       <c r="S7">
         <f>IF(COUNTA($A7:$Q7)=0,0,IF(OR($B7="",$D7="",$F7="",$G7=""),1,0))</f>
         <v/>
@@ -2674,11 +2681,11 @@
       <c r="J8" s="23" t="n"/>
       <c r="K8" s="23" t="n"/>
       <c r="L8" s="23" t="n"/>
-      <c r="M8" s="24" t="n"/>
-      <c r="N8" s="24" t="n"/>
-      <c r="O8" s="24" t="n"/>
-      <c r="P8" s="24" t="n"/>
-      <c r="Q8" s="24" t="n"/>
+      <c r="M8" s="25" t="n"/>
+      <c r="N8" s="25" t="n"/>
+      <c r="O8" s="25" t="n"/>
+      <c r="P8" s="25" t="n"/>
+      <c r="Q8" s="25" t="n"/>
       <c r="S8">
         <f>IF(COUNTA($A8:$Q8)=0,0,IF(OR($B8="",$D8="",$F8="",$G8=""),1,0))</f>
         <v/>
@@ -2701,11 +2708,11 @@
       <c r="J9" s="23" t="n"/>
       <c r="K9" s="23" t="n"/>
       <c r="L9" s="23" t="n"/>
-      <c r="M9" s="24" t="n"/>
-      <c r="N9" s="24" t="n"/>
-      <c r="O9" s="24" t="n"/>
-      <c r="P9" s="24" t="n"/>
-      <c r="Q9" s="24" t="n"/>
+      <c r="M9" s="25" t="n"/>
+      <c r="N9" s="25" t="n"/>
+      <c r="O9" s="25" t="n"/>
+      <c r="P9" s="25" t="n"/>
+      <c r="Q9" s="25" t="n"/>
       <c r="S9">
         <f>IF(COUNTA($A9:$Q9)=0,0,IF(OR($B9="",$D9="",$F9="",$G9=""),1,0))</f>
         <v/>
@@ -2728,11 +2735,11 @@
       <c r="J10" s="23" t="n"/>
       <c r="K10" s="23" t="n"/>
       <c r="L10" s="23" t="n"/>
-      <c r="M10" s="24" t="n"/>
-      <c r="N10" s="24" t="n"/>
-      <c r="O10" s="24" t="n"/>
-      <c r="P10" s="24" t="n"/>
-      <c r="Q10" s="24" t="n"/>
+      <c r="M10" s="25" t="n"/>
+      <c r="N10" s="25" t="n"/>
+      <c r="O10" s="25" t="n"/>
+      <c r="P10" s="25" t="n"/>
+      <c r="Q10" s="25" t="n"/>
       <c r="S10">
         <f>IF(COUNTA($A10:$Q10)=0,0,IF(OR($B10="",$D10="",$F10="",$G10=""),1,0))</f>
         <v/>
@@ -2755,11 +2762,11 @@
       <c r="J11" s="23" t="n"/>
       <c r="K11" s="23" t="n"/>
       <c r="L11" s="23" t="n"/>
-      <c r="M11" s="24" t="n"/>
-      <c r="N11" s="24" t="n"/>
-      <c r="O11" s="24" t="n"/>
-      <c r="P11" s="24" t="n"/>
-      <c r="Q11" s="24" t="n"/>
+      <c r="M11" s="25" t="n"/>
+      <c r="N11" s="25" t="n"/>
+      <c r="O11" s="25" t="n"/>
+      <c r="P11" s="25" t="n"/>
+      <c r="Q11" s="25" t="n"/>
       <c r="S11">
         <f>IF(COUNTA($A11:$Q11)=0,0,IF(OR($B11="",$D11="",$F11="",$G11=""),1,0))</f>
         <v/>
@@ -2782,11 +2789,11 @@
       <c r="J12" s="23" t="n"/>
       <c r="K12" s="23" t="n"/>
       <c r="L12" s="23" t="n"/>
-      <c r="M12" s="24" t="n"/>
-      <c r="N12" s="24" t="n"/>
-      <c r="O12" s="24" t="n"/>
-      <c r="P12" s="24" t="n"/>
-      <c r="Q12" s="24" t="n"/>
+      <c r="M12" s="25" t="n"/>
+      <c r="N12" s="25" t="n"/>
+      <c r="O12" s="25" t="n"/>
+      <c r="P12" s="25" t="n"/>
+      <c r="Q12" s="25" t="n"/>
       <c r="S12">
         <f>IF(COUNTA($A12:$Q12)=0,0,IF(OR($B12="",$D12="",$F12="",$G12=""),1,0))</f>
         <v/>
@@ -2809,11 +2816,11 @@
       <c r="J13" s="23" t="n"/>
       <c r="K13" s="23" t="n"/>
       <c r="L13" s="23" t="n"/>
-      <c r="M13" s="24" t="n"/>
-      <c r="N13" s="24" t="n"/>
-      <c r="O13" s="24" t="n"/>
-      <c r="P13" s="24" t="n"/>
-      <c r="Q13" s="24" t="n"/>
+      <c r="M13" s="25" t="n"/>
+      <c r="N13" s="25" t="n"/>
+      <c r="O13" s="25" t="n"/>
+      <c r="P13" s="25" t="n"/>
+      <c r="Q13" s="25" t="n"/>
       <c r="S13">
         <f>IF(COUNTA($A13:$Q13)=0,0,IF(OR($B13="",$D13="",$F13="",$G13=""),1,0))</f>
         <v/>
@@ -2836,11 +2843,11 @@
       <c r="J14" s="23" t="n"/>
       <c r="K14" s="23" t="n"/>
       <c r="L14" s="23" t="n"/>
-      <c r="M14" s="24" t="n"/>
-      <c r="N14" s="24" t="n"/>
-      <c r="O14" s="24" t="n"/>
-      <c r="P14" s="24" t="n"/>
-      <c r="Q14" s="24" t="n"/>
+      <c r="M14" s="25" t="n"/>
+      <c r="N14" s="25" t="n"/>
+      <c r="O14" s="25" t="n"/>
+      <c r="P14" s="25" t="n"/>
+      <c r="Q14" s="25" t="n"/>
       <c r="S14">
         <f>IF(COUNTA($A14:$Q14)=0,0,IF(OR($B14="",$D14="",$F14="",$G14=""),1,0))</f>
         <v/>
@@ -2863,11 +2870,11 @@
       <c r="J15" s="23" t="n"/>
       <c r="K15" s="23" t="n"/>
       <c r="L15" s="23" t="n"/>
-      <c r="M15" s="24" t="n"/>
-      <c r="N15" s="24" t="n"/>
-      <c r="O15" s="24" t="n"/>
-      <c r="P15" s="24" t="n"/>
-      <c r="Q15" s="24" t="n"/>
+      <c r="M15" s="25" t="n"/>
+      <c r="N15" s="25" t="n"/>
+      <c r="O15" s="25" t="n"/>
+      <c r="P15" s="25" t="n"/>
+      <c r="Q15" s="25" t="n"/>
       <c r="S15">
         <f>IF(COUNTA($A15:$Q15)=0,0,IF(OR($B15="",$D15="",$F15="",$G15=""),1,0))</f>
         <v/>
@@ -2890,11 +2897,11 @@
       <c r="J16" s="23" t="n"/>
       <c r="K16" s="23" t="n"/>
       <c r="L16" s="23" t="n"/>
-      <c r="M16" s="24" t="n"/>
-      <c r="N16" s="24" t="n"/>
-      <c r="O16" s="24" t="n"/>
-      <c r="P16" s="24" t="n"/>
-      <c r="Q16" s="24" t="n"/>
+      <c r="M16" s="25" t="n"/>
+      <c r="N16" s="25" t="n"/>
+      <c r="O16" s="25" t="n"/>
+      <c r="P16" s="25" t="n"/>
+      <c r="Q16" s="25" t="n"/>
       <c r="S16">
         <f>IF(COUNTA($A16:$Q16)=0,0,IF(OR($B16="",$D16="",$F16="",$G16=""),1,0))</f>
         <v/>
@@ -2917,11 +2924,11 @@
       <c r="J17" s="23" t="n"/>
       <c r="K17" s="23" t="n"/>
       <c r="L17" s="23" t="n"/>
-      <c r="M17" s="24" t="n"/>
-      <c r="N17" s="24" t="n"/>
-      <c r="O17" s="24" t="n"/>
-      <c r="P17" s="24" t="n"/>
-      <c r="Q17" s="24" t="n"/>
+      <c r="M17" s="25" t="n"/>
+      <c r="N17" s="25" t="n"/>
+      <c r="O17" s="25" t="n"/>
+      <c r="P17" s="25" t="n"/>
+      <c r="Q17" s="25" t="n"/>
       <c r="S17">
         <f>IF(COUNTA($A17:$Q17)=0,0,IF(OR($B17="",$D17="",$F17="",$G17=""),1,0))</f>
         <v/>
@@ -2944,11 +2951,11 @@
       <c r="J18" s="23" t="n"/>
       <c r="K18" s="23" t="n"/>
       <c r="L18" s="23" t="n"/>
-      <c r="M18" s="24" t="n"/>
-      <c r="N18" s="24" t="n"/>
-      <c r="O18" s="24" t="n"/>
-      <c r="P18" s="24" t="n"/>
-      <c r="Q18" s="24" t="n"/>
+      <c r="M18" s="25" t="n"/>
+      <c r="N18" s="25" t="n"/>
+      <c r="O18" s="25" t="n"/>
+      <c r="P18" s="25" t="n"/>
+      <c r="Q18" s="25" t="n"/>
       <c r="S18">
         <f>IF(COUNTA($A18:$Q18)=0,0,IF(OR($B18="",$D18="",$F18="",$G18=""),1,0))</f>
         <v/>
@@ -2971,11 +2978,11 @@
       <c r="J19" s="23" t="n"/>
       <c r="K19" s="23" t="n"/>
       <c r="L19" s="23" t="n"/>
-      <c r="M19" s="24" t="n"/>
-      <c r="N19" s="24" t="n"/>
-      <c r="O19" s="24" t="n"/>
-      <c r="P19" s="24" t="n"/>
-      <c r="Q19" s="24" t="n"/>
+      <c r="M19" s="25" t="n"/>
+      <c r="N19" s="25" t="n"/>
+      <c r="O19" s="25" t="n"/>
+      <c r="P19" s="25" t="n"/>
+      <c r="Q19" s="25" t="n"/>
       <c r="S19">
         <f>IF(COUNTA($A19:$Q19)=0,0,IF(OR($B19="",$D19="",$F19="",$G19=""),1,0))</f>
         <v/>
@@ -2998,11 +3005,11 @@
       <c r="J20" s="23" t="n"/>
       <c r="K20" s="23" t="n"/>
       <c r="L20" s="23" t="n"/>
-      <c r="M20" s="24" t="n"/>
-      <c r="N20" s="24" t="n"/>
-      <c r="O20" s="24" t="n"/>
-      <c r="P20" s="24" t="n"/>
-      <c r="Q20" s="24" t="n"/>
+      <c r="M20" s="25" t="n"/>
+      <c r="N20" s="25" t="n"/>
+      <c r="O20" s="25" t="n"/>
+      <c r="P20" s="25" t="n"/>
+      <c r="Q20" s="25" t="n"/>
       <c r="S20">
         <f>IF(COUNTA($A20:$Q20)=0,0,IF(OR($B20="",$D20="",$F20="",$G20=""),1,0))</f>
         <v/>
@@ -3025,11 +3032,11 @@
       <c r="J21" s="23" t="n"/>
       <c r="K21" s="23" t="n"/>
       <c r="L21" s="23" t="n"/>
-      <c r="M21" s="24" t="n"/>
-      <c r="N21" s="24" t="n"/>
-      <c r="O21" s="24" t="n"/>
-      <c r="P21" s="24" t="n"/>
-      <c r="Q21" s="24" t="n"/>
+      <c r="M21" s="25" t="n"/>
+      <c r="N21" s="25" t="n"/>
+      <c r="O21" s="25" t="n"/>
+      <c r="P21" s="25" t="n"/>
+      <c r="Q21" s="25" t="n"/>
       <c r="S21">
         <f>IF(COUNTA($A21:$Q21)=0,0,IF(OR($B21="",$D21="",$F21="",$G21=""),1,0))</f>
         <v/>
@@ -3052,11 +3059,11 @@
       <c r="J22" s="23" t="n"/>
       <c r="K22" s="23" t="n"/>
       <c r="L22" s="23" t="n"/>
-      <c r="M22" s="24" t="n"/>
-      <c r="N22" s="24" t="n"/>
-      <c r="O22" s="24" t="n"/>
-      <c r="P22" s="24" t="n"/>
-      <c r="Q22" s="24" t="n"/>
+      <c r="M22" s="25" t="n"/>
+      <c r="N22" s="25" t="n"/>
+      <c r="O22" s="25" t="n"/>
+      <c r="P22" s="25" t="n"/>
+      <c r="Q22" s="25" t="n"/>
       <c r="S22">
         <f>IF(COUNTA($A22:$Q22)=0,0,IF(OR($B22="",$D22="",$F22="",$G22=""),1,0))</f>
         <v/>
@@ -3079,11 +3086,11 @@
       <c r="J23" s="23" t="n"/>
       <c r="K23" s="23" t="n"/>
       <c r="L23" s="23" t="n"/>
-      <c r="M23" s="24" t="n"/>
-      <c r="N23" s="24" t="n"/>
-      <c r="O23" s="24" t="n"/>
-      <c r="P23" s="24" t="n"/>
-      <c r="Q23" s="24" t="n"/>
+      <c r="M23" s="25" t="n"/>
+      <c r="N23" s="25" t="n"/>
+      <c r="O23" s="25" t="n"/>
+      <c r="P23" s="25" t="n"/>
+      <c r="Q23" s="25" t="n"/>
       <c r="S23">
         <f>IF(COUNTA($A23:$Q23)=0,0,IF(OR($B23="",$D23="",$F23="",$G23=""),1,0))</f>
         <v/>
@@ -3106,11 +3113,11 @@
       <c r="J24" s="23" t="n"/>
       <c r="K24" s="23" t="n"/>
       <c r="L24" s="23" t="n"/>
-      <c r="M24" s="24" t="n"/>
-      <c r="N24" s="24" t="n"/>
-      <c r="O24" s="24" t="n"/>
-      <c r="P24" s="24" t="n"/>
-      <c r="Q24" s="24" t="n"/>
+      <c r="M24" s="25" t="n"/>
+      <c r="N24" s="25" t="n"/>
+      <c r="O24" s="25" t="n"/>
+      <c r="P24" s="25" t="n"/>
+      <c r="Q24" s="25" t="n"/>
       <c r="S24">
         <f>IF(COUNTA($A24:$Q24)=0,0,IF(OR($B24="",$D24="",$F24="",$G24=""),1,0))</f>
         <v/>
@@ -3133,11 +3140,11 @@
       <c r="J25" s="23" t="n"/>
       <c r="K25" s="23" t="n"/>
       <c r="L25" s="23" t="n"/>
-      <c r="M25" s="24" t="n"/>
-      <c r="N25" s="24" t="n"/>
-      <c r="O25" s="24" t="n"/>
-      <c r="P25" s="24" t="n"/>
-      <c r="Q25" s="24" t="n"/>
+      <c r="M25" s="25" t="n"/>
+      <c r="N25" s="25" t="n"/>
+      <c r="O25" s="25" t="n"/>
+      <c r="P25" s="25" t="n"/>
+      <c r="Q25" s="25" t="n"/>
       <c r="S25">
         <f>IF(COUNTA($A25:$Q25)=0,0,IF(OR($B25="",$D25="",$F25="",$G25=""),1,0))</f>
         <v/>
@@ -3160,11 +3167,11 @@
       <c r="J26" s="23" t="n"/>
       <c r="K26" s="23" t="n"/>
       <c r="L26" s="23" t="n"/>
-      <c r="M26" s="24" t="n"/>
-      <c r="N26" s="24" t="n"/>
-      <c r="O26" s="24" t="n"/>
-      <c r="P26" s="24" t="n"/>
-      <c r="Q26" s="24" t="n"/>
+      <c r="M26" s="25" t="n"/>
+      <c r="N26" s="25" t="n"/>
+      <c r="O26" s="25" t="n"/>
+      <c r="P26" s="25" t="n"/>
+      <c r="Q26" s="25" t="n"/>
       <c r="S26">
         <f>IF(COUNTA($A26:$Q26)=0,0,IF(OR($B26="",$D26="",$F26="",$G26=""),1,0))</f>
         <v/>
@@ -3187,11 +3194,11 @@
       <c r="J27" s="23" t="n"/>
       <c r="K27" s="23" t="n"/>
       <c r="L27" s="23" t="n"/>
-      <c r="M27" s="24" t="n"/>
-      <c r="N27" s="24" t="n"/>
-      <c r="O27" s="24" t="n"/>
-      <c r="P27" s="24" t="n"/>
-      <c r="Q27" s="24" t="n"/>
+      <c r="M27" s="25" t="n"/>
+      <c r="N27" s="25" t="n"/>
+      <c r="O27" s="25" t="n"/>
+      <c r="P27" s="25" t="n"/>
+      <c r="Q27" s="25" t="n"/>
       <c r="S27">
         <f>IF(COUNTA($A27:$Q27)=0,0,IF(OR($B27="",$D27="",$F27="",$G27=""),1,0))</f>
         <v/>
@@ -3214,11 +3221,11 @@
       <c r="J28" s="23" t="n"/>
       <c r="K28" s="23" t="n"/>
       <c r="L28" s="23" t="n"/>
-      <c r="M28" s="24" t="n"/>
-      <c r="N28" s="24" t="n"/>
-      <c r="O28" s="24" t="n"/>
-      <c r="P28" s="24" t="n"/>
-      <c r="Q28" s="24" t="n"/>
+      <c r="M28" s="25" t="n"/>
+      <c r="N28" s="25" t="n"/>
+      <c r="O28" s="25" t="n"/>
+      <c r="P28" s="25" t="n"/>
+      <c r="Q28" s="25" t="n"/>
       <c r="S28">
         <f>IF(COUNTA($A28:$Q28)=0,0,IF(OR($B28="",$D28="",$F28="",$G28=""),1,0))</f>
         <v/>
@@ -3241,11 +3248,11 @@
       <c r="J29" s="23" t="n"/>
       <c r="K29" s="23" t="n"/>
       <c r="L29" s="23" t="n"/>
-      <c r="M29" s="24" t="n"/>
-      <c r="N29" s="24" t="n"/>
-      <c r="O29" s="24" t="n"/>
-      <c r="P29" s="24" t="n"/>
-      <c r="Q29" s="24" t="n"/>
+      <c r="M29" s="25" t="n"/>
+      <c r="N29" s="25" t="n"/>
+      <c r="O29" s="25" t="n"/>
+      <c r="P29" s="25" t="n"/>
+      <c r="Q29" s="25" t="n"/>
       <c r="S29">
         <f>IF(COUNTA($A29:$Q29)=0,0,IF(OR($B29="",$D29="",$F29="",$G29=""),1,0))</f>
         <v/>
@@ -3268,11 +3275,11 @@
       <c r="J30" s="23" t="n"/>
       <c r="K30" s="23" t="n"/>
       <c r="L30" s="23" t="n"/>
-      <c r="M30" s="24" t="n"/>
-      <c r="N30" s="24" t="n"/>
-      <c r="O30" s="24" t="n"/>
-      <c r="P30" s="24" t="n"/>
-      <c r="Q30" s="24" t="n"/>
+      <c r="M30" s="25" t="n"/>
+      <c r="N30" s="25" t="n"/>
+      <c r="O30" s="25" t="n"/>
+      <c r="P30" s="25" t="n"/>
+      <c r="Q30" s="25" t="n"/>
       <c r="S30">
         <f>IF(COUNTA($A30:$Q30)=0,0,IF(OR($B30="",$D30="",$F30="",$G30=""),1,0))</f>
         <v/>
@@ -3295,11 +3302,11 @@
       <c r="J31" s="23" t="n"/>
       <c r="K31" s="23" t="n"/>
       <c r="L31" s="23" t="n"/>
-      <c r="M31" s="24" t="n"/>
-      <c r="N31" s="24" t="n"/>
-      <c r="O31" s="24" t="n"/>
-      <c r="P31" s="24" t="n"/>
-      <c r="Q31" s="24" t="n"/>
+      <c r="M31" s="25" t="n"/>
+      <c r="N31" s="25" t="n"/>
+      <c r="O31" s="25" t="n"/>
+      <c r="P31" s="25" t="n"/>
+      <c r="Q31" s="25" t="n"/>
       <c r="S31">
         <f>IF(COUNTA($A31:$Q31)=0,0,IF(OR($B31="",$D31="",$F31="",$G31=""),1,0))</f>
         <v/>
@@ -3322,11 +3329,11 @@
       <c r="J32" s="23" t="n"/>
       <c r="K32" s="23" t="n"/>
       <c r="L32" s="23" t="n"/>
-      <c r="M32" s="24" t="n"/>
-      <c r="N32" s="24" t="n"/>
-      <c r="O32" s="24" t="n"/>
-      <c r="P32" s="24" t="n"/>
-      <c r="Q32" s="24" t="n"/>
+      <c r="M32" s="25" t="n"/>
+      <c r="N32" s="25" t="n"/>
+      <c r="O32" s="25" t="n"/>
+      <c r="P32" s="25" t="n"/>
+      <c r="Q32" s="25" t="n"/>
       <c r="S32">
         <f>IF(COUNTA($A32:$Q32)=0,0,IF(OR($B32="",$D32="",$F32="",$G32=""),1,0))</f>
         <v/>
@@ -3349,11 +3356,11 @@
       <c r="J33" s="23" t="n"/>
       <c r="K33" s="23" t="n"/>
       <c r="L33" s="23" t="n"/>
-      <c r="M33" s="24" t="n"/>
-      <c r="N33" s="24" t="n"/>
-      <c r="O33" s="24" t="n"/>
-      <c r="P33" s="24" t="n"/>
-      <c r="Q33" s="24" t="n"/>
+      <c r="M33" s="25" t="n"/>
+      <c r="N33" s="25" t="n"/>
+      <c r="O33" s="25" t="n"/>
+      <c r="P33" s="25" t="n"/>
+      <c r="Q33" s="25" t="n"/>
       <c r="S33">
         <f>IF(COUNTA($A33:$Q33)=0,0,IF(OR($B33="",$D33="",$F33="",$G33=""),1,0))</f>
         <v/>
@@ -3376,11 +3383,11 @@
       <c r="J34" s="23" t="n"/>
       <c r="K34" s="23" t="n"/>
       <c r="L34" s="23" t="n"/>
-      <c r="M34" s="24" t="n"/>
-      <c r="N34" s="24" t="n"/>
-      <c r="O34" s="24" t="n"/>
-      <c r="P34" s="24" t="n"/>
-      <c r="Q34" s="24" t="n"/>
+      <c r="M34" s="25" t="n"/>
+      <c r="N34" s="25" t="n"/>
+      <c r="O34" s="25" t="n"/>
+      <c r="P34" s="25" t="n"/>
+      <c r="Q34" s="25" t="n"/>
       <c r="S34">
         <f>IF(COUNTA($A34:$Q34)=0,0,IF(OR($B34="",$D34="",$F34="",$G34=""),1,0))</f>
         <v/>
@@ -3403,11 +3410,11 @@
       <c r="J35" s="23" t="n"/>
       <c r="K35" s="23" t="n"/>
       <c r="L35" s="23" t="n"/>
-      <c r="M35" s="24" t="n"/>
-      <c r="N35" s="24" t="n"/>
-      <c r="O35" s="24" t="n"/>
-      <c r="P35" s="24" t="n"/>
-      <c r="Q35" s="24" t="n"/>
+      <c r="M35" s="25" t="n"/>
+      <c r="N35" s="25" t="n"/>
+      <c r="O35" s="25" t="n"/>
+      <c r="P35" s="25" t="n"/>
+      <c r="Q35" s="25" t="n"/>
       <c r="S35">
         <f>IF(COUNTA($A35:$Q35)=0,0,IF(OR($B35="",$D35="",$F35="",$G35=""),1,0))</f>
         <v/>
@@ -3430,11 +3437,11 @@
       <c r="J36" s="23" t="n"/>
       <c r="K36" s="23" t="n"/>
       <c r="L36" s="23" t="n"/>
-      <c r="M36" s="24" t="n"/>
-      <c r="N36" s="24" t="n"/>
-      <c r="O36" s="24" t="n"/>
-      <c r="P36" s="24" t="n"/>
-      <c r="Q36" s="24" t="n"/>
+      <c r="M36" s="25" t="n"/>
+      <c r="N36" s="25" t="n"/>
+      <c r="O36" s="25" t="n"/>
+      <c r="P36" s="25" t="n"/>
+      <c r="Q36" s="25" t="n"/>
       <c r="S36">
         <f>IF(COUNTA($A36:$Q36)=0,0,IF(OR($B36="",$D36="",$F36="",$G36=""),1,0))</f>
         <v/>
@@ -3457,11 +3464,11 @@
       <c r="J37" s="23" t="n"/>
       <c r="K37" s="23" t="n"/>
       <c r="L37" s="23" t="n"/>
-      <c r="M37" s="24" t="n"/>
-      <c r="N37" s="24" t="n"/>
-      <c r="O37" s="24" t="n"/>
-      <c r="P37" s="24" t="n"/>
-      <c r="Q37" s="24" t="n"/>
+      <c r="M37" s="25" t="n"/>
+      <c r="N37" s="25" t="n"/>
+      <c r="O37" s="25" t="n"/>
+      <c r="P37" s="25" t="n"/>
+      <c r="Q37" s="25" t="n"/>
       <c r="S37">
         <f>IF(COUNTA($A37:$Q37)=0,0,IF(OR($B37="",$D37="",$F37="",$G37=""),1,0))</f>
         <v/>
@@ -3484,11 +3491,11 @@
       <c r="J38" s="23" t="n"/>
       <c r="K38" s="23" t="n"/>
       <c r="L38" s="23" t="n"/>
-      <c r="M38" s="24" t="n"/>
-      <c r="N38" s="24" t="n"/>
-      <c r="O38" s="24" t="n"/>
-      <c r="P38" s="24" t="n"/>
-      <c r="Q38" s="24" t="n"/>
+      <c r="M38" s="25" t="n"/>
+      <c r="N38" s="25" t="n"/>
+      <c r="O38" s="25" t="n"/>
+      <c r="P38" s="25" t="n"/>
+      <c r="Q38" s="25" t="n"/>
       <c r="S38">
         <f>IF(COUNTA($A38:$Q38)=0,0,IF(OR($B38="",$D38="",$F38="",$G38=""),1,0))</f>
         <v/>
@@ -3511,11 +3518,11 @@
       <c r="J39" s="23" t="n"/>
       <c r="K39" s="23" t="n"/>
       <c r="L39" s="23" t="n"/>
-      <c r="M39" s="24" t="n"/>
-      <c r="N39" s="24" t="n"/>
-      <c r="O39" s="24" t="n"/>
-      <c r="P39" s="24" t="n"/>
-      <c r="Q39" s="24" t="n"/>
+      <c r="M39" s="25" t="n"/>
+      <c r="N39" s="25" t="n"/>
+      <c r="O39" s="25" t="n"/>
+      <c r="P39" s="25" t="n"/>
+      <c r="Q39" s="25" t="n"/>
       <c r="S39">
         <f>IF(COUNTA($A39:$Q39)=0,0,IF(OR($B39="",$D39="",$F39="",$G39=""),1,0))</f>
         <v/>
@@ -3538,11 +3545,11 @@
       <c r="J40" s="23" t="n"/>
       <c r="K40" s="23" t="n"/>
       <c r="L40" s="23" t="n"/>
-      <c r="M40" s="24" t="n"/>
-      <c r="N40" s="24" t="n"/>
-      <c r="O40" s="24" t="n"/>
-      <c r="P40" s="24" t="n"/>
-      <c r="Q40" s="24" t="n"/>
+      <c r="M40" s="25" t="n"/>
+      <c r="N40" s="25" t="n"/>
+      <c r="O40" s="25" t="n"/>
+      <c r="P40" s="25" t="n"/>
+      <c r="Q40" s="25" t="n"/>
       <c r="S40">
         <f>IF(COUNTA($A40:$Q40)=0,0,IF(OR($B40="",$D40="",$F40="",$G40=""),1,0))</f>
         <v/>
@@ -3565,11 +3572,11 @@
       <c r="J41" s="23" t="n"/>
       <c r="K41" s="23" t="n"/>
       <c r="L41" s="23" t="n"/>
-      <c r="M41" s="24" t="n"/>
-      <c r="N41" s="24" t="n"/>
-      <c r="O41" s="24" t="n"/>
-      <c r="P41" s="24" t="n"/>
-      <c r="Q41" s="24" t="n"/>
+      <c r="M41" s="25" t="n"/>
+      <c r="N41" s="25" t="n"/>
+      <c r="O41" s="25" t="n"/>
+      <c r="P41" s="25" t="n"/>
+      <c r="Q41" s="25" t="n"/>
       <c r="S41">
         <f>IF(COUNTA($A41:$Q41)=0,0,IF(OR($B41="",$D41="",$F41="",$G41=""),1,0))</f>
         <v/>
@@ -10707,8 +10714,8 @@
       <c r="D2" s="23" t="n"/>
       <c r="E2" s="23" t="n"/>
       <c r="F2" s="23" t="n"/>
-      <c r="G2" s="24" t="n"/>
-      <c r="H2" s="24" t="n"/>
+      <c r="G2" s="25" t="n"/>
+      <c r="H2" s="25" t="n"/>
       <c r="J2">
         <f>IF(COUNTA($A2:$H2)=0,0,IF(OR($B2="",$D2=""),1,0))</f>
         <v/>
@@ -10725,8 +10732,8 @@
       <c r="D3" s="23" t="n"/>
       <c r="E3" s="23" t="n"/>
       <c r="F3" s="23" t="n"/>
-      <c r="G3" s="24" t="n"/>
-      <c r="H3" s="24" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="25" t="n"/>
       <c r="J3">
         <f>IF(COUNTA($A3:$H3)=0,0,IF(OR($B3="",$D3=""),1,0))</f>
         <v/>
@@ -10743,8 +10750,8 @@
       <c r="D4" s="23" t="n"/>
       <c r="E4" s="23" t="n"/>
       <c r="F4" s="23" t="n"/>
-      <c r="G4" s="24" t="n"/>
-      <c r="H4" s="24" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="25" t="n"/>
       <c r="J4">
         <f>IF(COUNTA($A4:$H4)=0,0,IF(OR($B4="",$D4=""),1,0))</f>
         <v/>
@@ -10761,8 +10768,8 @@
       <c r="D5" s="23" t="n"/>
       <c r="E5" s="23" t="n"/>
       <c r="F5" s="23" t="n"/>
-      <c r="G5" s="24" t="n"/>
-      <c r="H5" s="24" t="n"/>
+      <c r="G5" s="25" t="n"/>
+      <c r="H5" s="25" t="n"/>
       <c r="J5">
         <f>IF(COUNTA($A5:$H5)=0,0,IF(OR($B5="",$D5=""),1,0))</f>
         <v/>
@@ -10779,8 +10786,8 @@
       <c r="D6" s="23" t="n"/>
       <c r="E6" s="23" t="n"/>
       <c r="F6" s="23" t="n"/>
-      <c r="G6" s="24" t="n"/>
-      <c r="H6" s="24" t="n"/>
+      <c r="G6" s="25" t="n"/>
+      <c r="H6" s="25" t="n"/>
       <c r="J6">
         <f>IF(COUNTA($A6:$H6)=0,0,IF(OR($B6="",$D6=""),1,0))</f>
         <v/>
@@ -10797,8 +10804,8 @@
       <c r="D7" s="23" t="n"/>
       <c r="E7" s="23" t="n"/>
       <c r="F7" s="23" t="n"/>
-      <c r="G7" s="24" t="n"/>
-      <c r="H7" s="24" t="n"/>
+      <c r="G7" s="25" t="n"/>
+      <c r="H7" s="25" t="n"/>
       <c r="J7">
         <f>IF(COUNTA($A7:$H7)=0,0,IF(OR($B7="",$D7=""),1,0))</f>
         <v/>
@@ -10815,8 +10822,8 @@
       <c r="D8" s="23" t="n"/>
       <c r="E8" s="23" t="n"/>
       <c r="F8" s="23" t="n"/>
-      <c r="G8" s="24" t="n"/>
-      <c r="H8" s="24" t="n"/>
+      <c r="G8" s="25" t="n"/>
+      <c r="H8" s="25" t="n"/>
       <c r="J8">
         <f>IF(COUNTA($A8:$H8)=0,0,IF(OR($B8="",$D8=""),1,0))</f>
         <v/>
@@ -10833,8 +10840,8 @@
       <c r="D9" s="23" t="n"/>
       <c r="E9" s="23" t="n"/>
       <c r="F9" s="23" t="n"/>
-      <c r="G9" s="24" t="n"/>
-      <c r="H9" s="24" t="n"/>
+      <c r="G9" s="25" t="n"/>
+      <c r="H9" s="25" t="n"/>
       <c r="J9">
         <f>IF(COUNTA($A9:$H9)=0,0,IF(OR($B9="",$D9=""),1,0))</f>
         <v/>
@@ -10851,8 +10858,8 @@
       <c r="D10" s="23" t="n"/>
       <c r="E10" s="23" t="n"/>
       <c r="F10" s="23" t="n"/>
-      <c r="G10" s="24" t="n"/>
-      <c r="H10" s="24" t="n"/>
+      <c r="G10" s="25" t="n"/>
+      <c r="H10" s="25" t="n"/>
       <c r="J10">
         <f>IF(COUNTA($A10:$H10)=0,0,IF(OR($B10="",$D10=""),1,0))</f>
         <v/>
@@ -10869,8 +10876,8 @@
       <c r="D11" s="23" t="n"/>
       <c r="E11" s="23" t="n"/>
       <c r="F11" s="23" t="n"/>
-      <c r="G11" s="24" t="n"/>
-      <c r="H11" s="24" t="n"/>
+      <c r="G11" s="25" t="n"/>
+      <c r="H11" s="25" t="n"/>
       <c r="J11">
         <f>IF(COUNTA($A11:$H11)=0,0,IF(OR($B11="",$D11=""),1,0))</f>
         <v/>
@@ -10887,8 +10894,8 @@
       <c r="D12" s="23" t="n"/>
       <c r="E12" s="23" t="n"/>
       <c r="F12" s="23" t="n"/>
-      <c r="G12" s="24" t="n"/>
-      <c r="H12" s="24" t="n"/>
+      <c r="G12" s="25" t="n"/>
+      <c r="H12" s="25" t="n"/>
       <c r="J12">
         <f>IF(COUNTA($A12:$H12)=0,0,IF(OR($B12="",$D12=""),1,0))</f>
         <v/>
@@ -10905,8 +10912,8 @@
       <c r="D13" s="23" t="n"/>
       <c r="E13" s="23" t="n"/>
       <c r="F13" s="23" t="n"/>
-      <c r="G13" s="24" t="n"/>
-      <c r="H13" s="24" t="n"/>
+      <c r="G13" s="25" t="n"/>
+      <c r="H13" s="25" t="n"/>
       <c r="J13">
         <f>IF(COUNTA($A13:$H13)=0,0,IF(OR($B13="",$D13=""),1,0))</f>
         <v/>
@@ -10923,8 +10930,8 @@
       <c r="D14" s="23" t="n"/>
       <c r="E14" s="23" t="n"/>
       <c r="F14" s="23" t="n"/>
-      <c r="G14" s="24" t="n"/>
-      <c r="H14" s="24" t="n"/>
+      <c r="G14" s="25" t="n"/>
+      <c r="H14" s="25" t="n"/>
       <c r="J14">
         <f>IF(COUNTA($A14:$H14)=0,0,IF(OR($B14="",$D14=""),1,0))</f>
         <v/>
@@ -10941,8 +10948,8 @@
       <c r="D15" s="23" t="n"/>
       <c r="E15" s="23" t="n"/>
       <c r="F15" s="23" t="n"/>
-      <c r="G15" s="24" t="n"/>
-      <c r="H15" s="24" t="n"/>
+      <c r="G15" s="25" t="n"/>
+      <c r="H15" s="25" t="n"/>
       <c r="J15">
         <f>IF(COUNTA($A15:$H15)=0,0,IF(OR($B15="",$D15=""),1,0))</f>
         <v/>
@@ -10959,8 +10966,8 @@
       <c r="D16" s="23" t="n"/>
       <c r="E16" s="23" t="n"/>
       <c r="F16" s="23" t="n"/>
-      <c r="G16" s="24" t="n"/>
-      <c r="H16" s="24" t="n"/>
+      <c r="G16" s="25" t="n"/>
+      <c r="H16" s="25" t="n"/>
       <c r="J16">
         <f>IF(COUNTA($A16:$H16)=0,0,IF(OR($B16="",$D16=""),1,0))</f>
         <v/>
@@ -10977,8 +10984,8 @@
       <c r="D17" s="23" t="n"/>
       <c r="E17" s="23" t="n"/>
       <c r="F17" s="23" t="n"/>
-      <c r="G17" s="24" t="n"/>
-      <c r="H17" s="24" t="n"/>
+      <c r="G17" s="25" t="n"/>
+      <c r="H17" s="25" t="n"/>
       <c r="J17">
         <f>IF(COUNTA($A17:$H17)=0,0,IF(OR($B17="",$D17=""),1,0))</f>
         <v/>
@@ -10995,8 +11002,8 @@
       <c r="D18" s="23" t="n"/>
       <c r="E18" s="23" t="n"/>
       <c r="F18" s="23" t="n"/>
-      <c r="G18" s="24" t="n"/>
-      <c r="H18" s="24" t="n"/>
+      <c r="G18" s="25" t="n"/>
+      <c r="H18" s="25" t="n"/>
       <c r="J18">
         <f>IF(COUNTA($A18:$H18)=0,0,IF(OR($B18="",$D18=""),1,0))</f>
         <v/>
@@ -11013,8 +11020,8 @@
       <c r="D19" s="23" t="n"/>
       <c r="E19" s="23" t="n"/>
       <c r="F19" s="23" t="n"/>
-      <c r="G19" s="24" t="n"/>
-      <c r="H19" s="24" t="n"/>
+      <c r="G19" s="25" t="n"/>
+      <c r="H19" s="25" t="n"/>
       <c r="J19">
         <f>IF(COUNTA($A19:$H19)=0,0,IF(OR($B19="",$D19=""),1,0))</f>
         <v/>
@@ -11031,8 +11038,8 @@
       <c r="D20" s="23" t="n"/>
       <c r="E20" s="23" t="n"/>
       <c r="F20" s="23" t="n"/>
-      <c r="G20" s="24" t="n"/>
-      <c r="H20" s="24" t="n"/>
+      <c r="G20" s="25" t="n"/>
+      <c r="H20" s="25" t="n"/>
       <c r="J20">
         <f>IF(COUNTA($A20:$H20)=0,0,IF(OR($B20="",$D20=""),1,0))</f>
         <v/>
@@ -11049,8 +11056,8 @@
       <c r="D21" s="23" t="n"/>
       <c r="E21" s="23" t="n"/>
       <c r="F21" s="23" t="n"/>
-      <c r="G21" s="24" t="n"/>
-      <c r="H21" s="24" t="n"/>
+      <c r="G21" s="25" t="n"/>
+      <c r="H21" s="25" t="n"/>
       <c r="J21">
         <f>IF(COUNTA($A21:$H21)=0,0,IF(OR($B21="",$D21=""),1,0))</f>
         <v/>
@@ -11067,8 +11074,8 @@
       <c r="D22" s="23" t="n"/>
       <c r="E22" s="23" t="n"/>
       <c r="F22" s="23" t="n"/>
-      <c r="G22" s="24" t="n"/>
-      <c r="H22" s="24" t="n"/>
+      <c r="G22" s="25" t="n"/>
+      <c r="H22" s="25" t="n"/>
       <c r="J22">
         <f>IF(COUNTA($A22:$H22)=0,0,IF(OR($B22="",$D22=""),1,0))</f>
         <v/>
@@ -11085,8 +11092,8 @@
       <c r="D23" s="23" t="n"/>
       <c r="E23" s="23" t="n"/>
       <c r="F23" s="23" t="n"/>
-      <c r="G23" s="24" t="n"/>
-      <c r="H23" s="24" t="n"/>
+      <c r="G23" s="25" t="n"/>
+      <c r="H23" s="25" t="n"/>
       <c r="J23">
         <f>IF(COUNTA($A23:$H23)=0,0,IF(OR($B23="",$D23=""),1,0))</f>
         <v/>
@@ -11103,8 +11110,8 @@
       <c r="D24" s="23" t="n"/>
       <c r="E24" s="23" t="n"/>
       <c r="F24" s="23" t="n"/>
-      <c r="G24" s="24" t="n"/>
-      <c r="H24" s="24" t="n"/>
+      <c r="G24" s="25" t="n"/>
+      <c r="H24" s="25" t="n"/>
       <c r="J24">
         <f>IF(COUNTA($A24:$H24)=0,0,IF(OR($B24="",$D24=""),1,0))</f>
         <v/>
@@ -11121,8 +11128,8 @@
       <c r="D25" s="23" t="n"/>
       <c r="E25" s="23" t="n"/>
       <c r="F25" s="23" t="n"/>
-      <c r="G25" s="24" t="n"/>
-      <c r="H25" s="24" t="n"/>
+      <c r="G25" s="25" t="n"/>
+      <c r="H25" s="25" t="n"/>
       <c r="J25">
         <f>IF(COUNTA($A25:$H25)=0,0,IF(OR($B25="",$D25=""),1,0))</f>
         <v/>
@@ -11139,8 +11146,8 @@
       <c r="D26" s="23" t="n"/>
       <c r="E26" s="23" t="n"/>
       <c r="F26" s="23" t="n"/>
-      <c r="G26" s="24" t="n"/>
-      <c r="H26" s="24" t="n"/>
+      <c r="G26" s="25" t="n"/>
+      <c r="H26" s="25" t="n"/>
       <c r="J26">
         <f>IF(COUNTA($A26:$H26)=0,0,IF(OR($B26="",$D26=""),1,0))</f>
         <v/>
@@ -11157,8 +11164,8 @@
       <c r="D27" s="23" t="n"/>
       <c r="E27" s="23" t="n"/>
       <c r="F27" s="23" t="n"/>
-      <c r="G27" s="24" t="n"/>
-      <c r="H27" s="24" t="n"/>
+      <c r="G27" s="25" t="n"/>
+      <c r="H27" s="25" t="n"/>
       <c r="J27">
         <f>IF(COUNTA($A27:$H27)=0,0,IF(OR($B27="",$D27=""),1,0))</f>
         <v/>
@@ -11175,8 +11182,8 @@
       <c r="D28" s="23" t="n"/>
       <c r="E28" s="23" t="n"/>
       <c r="F28" s="23" t="n"/>
-      <c r="G28" s="24" t="n"/>
-      <c r="H28" s="24" t="n"/>
+      <c r="G28" s="25" t="n"/>
+      <c r="H28" s="25" t="n"/>
       <c r="J28">
         <f>IF(COUNTA($A28:$H28)=0,0,IF(OR($B28="",$D28=""),1,0))</f>
         <v/>
@@ -11193,8 +11200,8 @@
       <c r="D29" s="23" t="n"/>
       <c r="E29" s="23" t="n"/>
       <c r="F29" s="23" t="n"/>
-      <c r="G29" s="24" t="n"/>
-      <c r="H29" s="24" t="n"/>
+      <c r="G29" s="25" t="n"/>
+      <c r="H29" s="25" t="n"/>
       <c r="J29">
         <f>IF(COUNTA($A29:$H29)=0,0,IF(OR($B29="",$D29=""),1,0))</f>
         <v/>
@@ -11211,8 +11218,8 @@
       <c r="D30" s="23" t="n"/>
       <c r="E30" s="23" t="n"/>
       <c r="F30" s="23" t="n"/>
-      <c r="G30" s="24" t="n"/>
-      <c r="H30" s="24" t="n"/>
+      <c r="G30" s="25" t="n"/>
+      <c r="H30" s="25" t="n"/>
       <c r="J30">
         <f>IF(COUNTA($A30:$H30)=0,0,IF(OR($B30="",$D30=""),1,0))</f>
         <v/>
@@ -11229,8 +11236,8 @@
       <c r="D31" s="23" t="n"/>
       <c r="E31" s="23" t="n"/>
       <c r="F31" s="23" t="n"/>
-      <c r="G31" s="24" t="n"/>
-      <c r="H31" s="24" t="n"/>
+      <c r="G31" s="25" t="n"/>
+      <c r="H31" s="25" t="n"/>
       <c r="J31">
         <f>IF(COUNTA($A31:$H31)=0,0,IF(OR($B31="",$D31=""),1,0))</f>
         <v/>
@@ -11247,8 +11254,8 @@
       <c r="D32" s="23" t="n"/>
       <c r="E32" s="23" t="n"/>
       <c r="F32" s="23" t="n"/>
-      <c r="G32" s="24" t="n"/>
-      <c r="H32" s="24" t="n"/>
+      <c r="G32" s="25" t="n"/>
+      <c r="H32" s="25" t="n"/>
       <c r="J32">
         <f>IF(COUNTA($A32:$H32)=0,0,IF(OR($B32="",$D32=""),1,0))</f>
         <v/>
@@ -11265,8 +11272,8 @@
       <c r="D33" s="23" t="n"/>
       <c r="E33" s="23" t="n"/>
       <c r="F33" s="23" t="n"/>
-      <c r="G33" s="24" t="n"/>
-      <c r="H33" s="24" t="n"/>
+      <c r="G33" s="25" t="n"/>
+      <c r="H33" s="25" t="n"/>
       <c r="J33">
         <f>IF(COUNTA($A33:$H33)=0,0,IF(OR($B33="",$D33=""),1,0))</f>
         <v/>
@@ -11283,8 +11290,8 @@
       <c r="D34" s="23" t="n"/>
       <c r="E34" s="23" t="n"/>
       <c r="F34" s="23" t="n"/>
-      <c r="G34" s="24" t="n"/>
-      <c r="H34" s="24" t="n"/>
+      <c r="G34" s="25" t="n"/>
+      <c r="H34" s="25" t="n"/>
       <c r="J34">
         <f>IF(COUNTA($A34:$H34)=0,0,IF(OR($B34="",$D34=""),1,0))</f>
         <v/>
@@ -11301,8 +11308,8 @@
       <c r="D35" s="23" t="n"/>
       <c r="E35" s="23" t="n"/>
       <c r="F35" s="23" t="n"/>
-      <c r="G35" s="24" t="n"/>
-      <c r="H35" s="24" t="n"/>
+      <c r="G35" s="25" t="n"/>
+      <c r="H35" s="25" t="n"/>
       <c r="J35">
         <f>IF(COUNTA($A35:$H35)=0,0,IF(OR($B35="",$D35=""),1,0))</f>
         <v/>
@@ -11319,8 +11326,8 @@
       <c r="D36" s="23" t="n"/>
       <c r="E36" s="23" t="n"/>
       <c r="F36" s="23" t="n"/>
-      <c r="G36" s="24" t="n"/>
-      <c r="H36" s="24" t="n"/>
+      <c r="G36" s="25" t="n"/>
+      <c r="H36" s="25" t="n"/>
       <c r="J36">
         <f>IF(COUNTA($A36:$H36)=0,0,IF(OR($B36="",$D36=""),1,0))</f>
         <v/>
@@ -11337,8 +11344,8 @@
       <c r="D37" s="23" t="n"/>
       <c r="E37" s="23" t="n"/>
       <c r="F37" s="23" t="n"/>
-      <c r="G37" s="24" t="n"/>
-      <c r="H37" s="24" t="n"/>
+      <c r="G37" s="25" t="n"/>
+      <c r="H37" s="25" t="n"/>
       <c r="J37">
         <f>IF(COUNTA($A37:$H37)=0,0,IF(OR($B37="",$D37=""),1,0))</f>
         <v/>
@@ -11355,8 +11362,8 @@
       <c r="D38" s="23" t="n"/>
       <c r="E38" s="23" t="n"/>
       <c r="F38" s="23" t="n"/>
-      <c r="G38" s="24" t="n"/>
-      <c r="H38" s="24" t="n"/>
+      <c r="G38" s="25" t="n"/>
+      <c r="H38" s="25" t="n"/>
       <c r="J38">
         <f>IF(COUNTA($A38:$H38)=0,0,IF(OR($B38="",$D38=""),1,0))</f>
         <v/>
@@ -11373,8 +11380,8 @@
       <c r="D39" s="23" t="n"/>
       <c r="E39" s="23" t="n"/>
       <c r="F39" s="23" t="n"/>
-      <c r="G39" s="24" t="n"/>
-      <c r="H39" s="24" t="n"/>
+      <c r="G39" s="25" t="n"/>
+      <c r="H39" s="25" t="n"/>
       <c r="J39">
         <f>IF(COUNTA($A39:$H39)=0,0,IF(OR($B39="",$D39=""),1,0))</f>
         <v/>
@@ -11391,8 +11398,8 @@
       <c r="D40" s="23" t="n"/>
       <c r="E40" s="23" t="n"/>
       <c r="F40" s="23" t="n"/>
-      <c r="G40" s="24" t="n"/>
-      <c r="H40" s="24" t="n"/>
+      <c r="G40" s="25" t="n"/>
+      <c r="H40" s="25" t="n"/>
       <c r="J40">
         <f>IF(COUNTA($A40:$H40)=0,0,IF(OR($B40="",$D40=""),1,0))</f>
         <v/>
@@ -11409,8 +11416,8 @@
       <c r="D41" s="23" t="n"/>
       <c r="E41" s="23" t="n"/>
       <c r="F41" s="23" t="n"/>
-      <c r="G41" s="24" t="n"/>
-      <c r="H41" s="24" t="n"/>
+      <c r="G41" s="25" t="n"/>
+      <c r="H41" s="25" t="n"/>
       <c r="J41">
         <f>IF(COUNTA($A41:$H41)=0,0,IF(OR($B41="",$D41=""),1,0))</f>
         <v/>
@@ -16198,8 +16205,8 @@
       <c r="D2" s="23" t="n"/>
       <c r="E2" s="23" t="n"/>
       <c r="F2" s="23" t="n"/>
-      <c r="G2" s="24" t="n"/>
-      <c r="H2" s="24" t="n"/>
+      <c r="G2" s="25" t="n"/>
+      <c r="H2" s="25" t="n"/>
       <c r="J2">
         <f>IF(COUNTA($A2:$H2)=0,0,IF(OR($B2="",$C2="",$E2=""),1,0))</f>
         <v/>
@@ -16216,8 +16223,8 @@
       <c r="D3" s="23" t="n"/>
       <c r="E3" s="23" t="n"/>
       <c r="F3" s="23" t="n"/>
-      <c r="G3" s="24" t="n"/>
-      <c r="H3" s="24" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="25" t="n"/>
       <c r="J3">
         <f>IF(COUNTA($A3:$H3)=0,0,IF(OR($B3="",$C3="",$E3=""),1,0))</f>
         <v/>
@@ -16234,8 +16241,8 @@
       <c r="D4" s="23" t="n"/>
       <c r="E4" s="23" t="n"/>
       <c r="F4" s="23" t="n"/>
-      <c r="G4" s="24" t="n"/>
-      <c r="H4" s="24" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="25" t="n"/>
       <c r="J4">
         <f>IF(COUNTA($A4:$H4)=0,0,IF(OR($B4="",$C4="",$E4=""),1,0))</f>
         <v/>
@@ -16252,8 +16259,8 @@
       <c r="D5" s="23" t="n"/>
       <c r="E5" s="23" t="n"/>
       <c r="F5" s="23" t="n"/>
-      <c r="G5" s="24" t="n"/>
-      <c r="H5" s="24" t="n"/>
+      <c r="G5" s="25" t="n"/>
+      <c r="H5" s="25" t="n"/>
       <c r="J5">
         <f>IF(COUNTA($A5:$H5)=0,0,IF(OR($B5="",$C5="",$E5=""),1,0))</f>
         <v/>
@@ -16270,8 +16277,8 @@
       <c r="D6" s="23" t="n"/>
       <c r="E6" s="23" t="n"/>
       <c r="F6" s="23" t="n"/>
-      <c r="G6" s="24" t="n"/>
-      <c r="H6" s="24" t="n"/>
+      <c r="G6" s="25" t="n"/>
+      <c r="H6" s="25" t="n"/>
       <c r="J6">
         <f>IF(COUNTA($A6:$H6)=0,0,IF(OR($B6="",$C6="",$E6=""),1,0))</f>
         <v/>
@@ -16288,8 +16295,8 @@
       <c r="D7" s="23" t="n"/>
       <c r="E7" s="23" t="n"/>
       <c r="F7" s="23" t="n"/>
-      <c r="G7" s="24" t="n"/>
-      <c r="H7" s="24" t="n"/>
+      <c r="G7" s="25" t="n"/>
+      <c r="H7" s="25" t="n"/>
       <c r="J7">
         <f>IF(COUNTA($A7:$H7)=0,0,IF(OR($B7="",$C7="",$E7=""),1,0))</f>
         <v/>
@@ -16306,8 +16313,8 @@
       <c r="D8" s="23" t="n"/>
       <c r="E8" s="23" t="n"/>
       <c r="F8" s="23" t="n"/>
-      <c r="G8" s="24" t="n"/>
-      <c r="H8" s="24" t="n"/>
+      <c r="G8" s="25" t="n"/>
+      <c r="H8" s="25" t="n"/>
       <c r="J8">
         <f>IF(COUNTA($A8:$H8)=0,0,IF(OR($B8="",$C8="",$E8=""),1,0))</f>
         <v/>
@@ -16324,8 +16331,8 @@
       <c r="D9" s="23" t="n"/>
       <c r="E9" s="23" t="n"/>
       <c r="F9" s="23" t="n"/>
-      <c r="G9" s="24" t="n"/>
-      <c r="H9" s="24" t="n"/>
+      <c r="G9" s="25" t="n"/>
+      <c r="H9" s="25" t="n"/>
       <c r="J9">
         <f>IF(COUNTA($A9:$H9)=0,0,IF(OR($B9="",$C9="",$E9=""),1,0))</f>
         <v/>
@@ -16342,8 +16349,8 @@
       <c r="D10" s="23" t="n"/>
       <c r="E10" s="23" t="n"/>
       <c r="F10" s="23" t="n"/>
-      <c r="G10" s="24" t="n"/>
-      <c r="H10" s="24" t="n"/>
+      <c r="G10" s="25" t="n"/>
+      <c r="H10" s="25" t="n"/>
       <c r="J10">
         <f>IF(COUNTA($A10:$H10)=0,0,IF(OR($B10="",$C10="",$E10=""),1,0))</f>
         <v/>
@@ -16360,8 +16367,8 @@
       <c r="D11" s="23" t="n"/>
       <c r="E11" s="23" t="n"/>
       <c r="F11" s="23" t="n"/>
-      <c r="G11" s="24" t="n"/>
-      <c r="H11" s="24" t="n"/>
+      <c r="G11" s="25" t="n"/>
+      <c r="H11" s="25" t="n"/>
       <c r="J11">
         <f>IF(COUNTA($A11:$H11)=0,0,IF(OR($B11="",$C11="",$E11=""),1,0))</f>
         <v/>
@@ -16378,8 +16385,8 @@
       <c r="D12" s="23" t="n"/>
       <c r="E12" s="23" t="n"/>
       <c r="F12" s="23" t="n"/>
-      <c r="G12" s="24" t="n"/>
-      <c r="H12" s="24" t="n"/>
+      <c r="G12" s="25" t="n"/>
+      <c r="H12" s="25" t="n"/>
       <c r="J12">
         <f>IF(COUNTA($A12:$H12)=0,0,IF(OR($B12="",$C12="",$E12=""),1,0))</f>
         <v/>
@@ -16396,8 +16403,8 @@
       <c r="D13" s="23" t="n"/>
       <c r="E13" s="23" t="n"/>
       <c r="F13" s="23" t="n"/>
-      <c r="G13" s="24" t="n"/>
-      <c r="H13" s="24" t="n"/>
+      <c r="G13" s="25" t="n"/>
+      <c r="H13" s="25" t="n"/>
       <c r="J13">
         <f>IF(COUNTA($A13:$H13)=0,0,IF(OR($B13="",$C13="",$E13=""),1,0))</f>
         <v/>
@@ -16414,8 +16421,8 @@
       <c r="D14" s="23" t="n"/>
       <c r="E14" s="23" t="n"/>
       <c r="F14" s="23" t="n"/>
-      <c r="G14" s="24" t="n"/>
-      <c r="H14" s="24" t="n"/>
+      <c r="G14" s="25" t="n"/>
+      <c r="H14" s="25" t="n"/>
       <c r="J14">
         <f>IF(COUNTA($A14:$H14)=0,0,IF(OR($B14="",$C14="",$E14=""),1,0))</f>
         <v/>
@@ -16432,8 +16439,8 @@
       <c r="D15" s="23" t="n"/>
       <c r="E15" s="23" t="n"/>
       <c r="F15" s="23" t="n"/>
-      <c r="G15" s="24" t="n"/>
-      <c r="H15" s="24" t="n"/>
+      <c r="G15" s="25" t="n"/>
+      <c r="H15" s="25" t="n"/>
       <c r="J15">
         <f>IF(COUNTA($A15:$H15)=0,0,IF(OR($B15="",$C15="",$E15=""),1,0))</f>
         <v/>
@@ -16450,8 +16457,8 @@
       <c r="D16" s="23" t="n"/>
       <c r="E16" s="23" t="n"/>
       <c r="F16" s="23" t="n"/>
-      <c r="G16" s="24" t="n"/>
-      <c r="H16" s="24" t="n"/>
+      <c r="G16" s="25" t="n"/>
+      <c r="H16" s="25" t="n"/>
       <c r="J16">
         <f>IF(COUNTA($A16:$H16)=0,0,IF(OR($B16="",$C16="",$E16=""),1,0))</f>
         <v/>
@@ -16468,8 +16475,8 @@
       <c r="D17" s="23" t="n"/>
       <c r="E17" s="23" t="n"/>
       <c r="F17" s="23" t="n"/>
-      <c r="G17" s="24" t="n"/>
-      <c r="H17" s="24" t="n"/>
+      <c r="G17" s="25" t="n"/>
+      <c r="H17" s="25" t="n"/>
       <c r="J17">
         <f>IF(COUNTA($A17:$H17)=0,0,IF(OR($B17="",$C17="",$E17=""),1,0))</f>
         <v/>
@@ -16486,8 +16493,8 @@
       <c r="D18" s="23" t="n"/>
       <c r="E18" s="23" t="n"/>
       <c r="F18" s="23" t="n"/>
-      <c r="G18" s="24" t="n"/>
-      <c r="H18" s="24" t="n"/>
+      <c r="G18" s="25" t="n"/>
+      <c r="H18" s="25" t="n"/>
       <c r="J18">
         <f>IF(COUNTA($A18:$H18)=0,0,IF(OR($B18="",$C18="",$E18=""),1,0))</f>
         <v/>
@@ -16504,8 +16511,8 @@
       <c r="D19" s="23" t="n"/>
       <c r="E19" s="23" t="n"/>
       <c r="F19" s="23" t="n"/>
-      <c r="G19" s="24" t="n"/>
-      <c r="H19" s="24" t="n"/>
+      <c r="G19" s="25" t="n"/>
+      <c r="H19" s="25" t="n"/>
       <c r="J19">
         <f>IF(COUNTA($A19:$H19)=0,0,IF(OR($B19="",$C19="",$E19=""),1,0))</f>
         <v/>
@@ -16522,8 +16529,8 @@
       <c r="D20" s="23" t="n"/>
       <c r="E20" s="23" t="n"/>
       <c r="F20" s="23" t="n"/>
-      <c r="G20" s="24" t="n"/>
-      <c r="H20" s="24" t="n"/>
+      <c r="G20" s="25" t="n"/>
+      <c r="H20" s="25" t="n"/>
       <c r="J20">
         <f>IF(COUNTA($A20:$H20)=0,0,IF(OR($B20="",$C20="",$E20=""),1,0))</f>
         <v/>
@@ -16540,8 +16547,8 @@
       <c r="D21" s="23" t="n"/>
       <c r="E21" s="23" t="n"/>
       <c r="F21" s="23" t="n"/>
-      <c r="G21" s="24" t="n"/>
-      <c r="H21" s="24" t="n"/>
+      <c r="G21" s="25" t="n"/>
+      <c r="H21" s="25" t="n"/>
       <c r="J21">
         <f>IF(COUNTA($A21:$H21)=0,0,IF(OR($B21="",$C21="",$E21=""),1,0))</f>
         <v/>
@@ -16558,8 +16565,8 @@
       <c r="D22" s="23" t="n"/>
       <c r="E22" s="23" t="n"/>
       <c r="F22" s="23" t="n"/>
-      <c r="G22" s="24" t="n"/>
-      <c r="H22" s="24" t="n"/>
+      <c r="G22" s="25" t="n"/>
+      <c r="H22" s="25" t="n"/>
       <c r="J22">
         <f>IF(COUNTA($A22:$H22)=0,0,IF(OR($B22="",$C22="",$E22=""),1,0))</f>
         <v/>
@@ -16576,8 +16583,8 @@
       <c r="D23" s="23" t="n"/>
       <c r="E23" s="23" t="n"/>
       <c r="F23" s="23" t="n"/>
-      <c r="G23" s="24" t="n"/>
-      <c r="H23" s="24" t="n"/>
+      <c r="G23" s="25" t="n"/>
+      <c r="H23" s="25" t="n"/>
       <c r="J23">
         <f>IF(COUNTA($A23:$H23)=0,0,IF(OR($B23="",$C23="",$E23=""),1,0))</f>
         <v/>
@@ -16594,8 +16601,8 @@
       <c r="D24" s="23" t="n"/>
       <c r="E24" s="23" t="n"/>
       <c r="F24" s="23" t="n"/>
-      <c r="G24" s="24" t="n"/>
-      <c r="H24" s="24" t="n"/>
+      <c r="G24" s="25" t="n"/>
+      <c r="H24" s="25" t="n"/>
       <c r="J24">
         <f>IF(COUNTA($A24:$H24)=0,0,IF(OR($B24="",$C24="",$E24=""),1,0))</f>
         <v/>
@@ -16612,8 +16619,8 @@
       <c r="D25" s="23" t="n"/>
       <c r="E25" s="23" t="n"/>
       <c r="F25" s="23" t="n"/>
-      <c r="G25" s="24" t="n"/>
-      <c r="H25" s="24" t="n"/>
+      <c r="G25" s="25" t="n"/>
+      <c r="H25" s="25" t="n"/>
       <c r="J25">
         <f>IF(COUNTA($A25:$H25)=0,0,IF(OR($B25="",$C25="",$E25=""),1,0))</f>
         <v/>
@@ -16630,8 +16637,8 @@
       <c r="D26" s="23" t="n"/>
       <c r="E26" s="23" t="n"/>
       <c r="F26" s="23" t="n"/>
-      <c r="G26" s="24" t="n"/>
-      <c r="H26" s="24" t="n"/>
+      <c r="G26" s="25" t="n"/>
+      <c r="H26" s="25" t="n"/>
       <c r="J26">
         <f>IF(COUNTA($A26:$H26)=0,0,IF(OR($B26="",$C26="",$E26=""),1,0))</f>
         <v/>
@@ -16648,8 +16655,8 @@
       <c r="D27" s="23" t="n"/>
       <c r="E27" s="23" t="n"/>
       <c r="F27" s="23" t="n"/>
-      <c r="G27" s="24" t="n"/>
-      <c r="H27" s="24" t="n"/>
+      <c r="G27" s="25" t="n"/>
+      <c r="H27" s="25" t="n"/>
       <c r="J27">
         <f>IF(COUNTA($A27:$H27)=0,0,IF(OR($B27="",$C27="",$E27=""),1,0))</f>
         <v/>
@@ -16666,8 +16673,8 @@
       <c r="D28" s="23" t="n"/>
       <c r="E28" s="23" t="n"/>
       <c r="F28" s="23" t="n"/>
-      <c r="G28" s="24" t="n"/>
-      <c r="H28" s="24" t="n"/>
+      <c r="G28" s="25" t="n"/>
+      <c r="H28" s="25" t="n"/>
       <c r="J28">
         <f>IF(COUNTA($A28:$H28)=0,0,IF(OR($B28="",$C28="",$E28=""),1,0))</f>
         <v/>
@@ -16684,8 +16691,8 @@
       <c r="D29" s="23" t="n"/>
       <c r="E29" s="23" t="n"/>
       <c r="F29" s="23" t="n"/>
-      <c r="G29" s="24" t="n"/>
-      <c r="H29" s="24" t="n"/>
+      <c r="G29" s="25" t="n"/>
+      <c r="H29" s="25" t="n"/>
       <c r="J29">
         <f>IF(COUNTA($A29:$H29)=0,0,IF(OR($B29="",$C29="",$E29=""),1,0))</f>
         <v/>
@@ -16702,8 +16709,8 @@
       <c r="D30" s="23" t="n"/>
       <c r="E30" s="23" t="n"/>
       <c r="F30" s="23" t="n"/>
-      <c r="G30" s="24" t="n"/>
-      <c r="H30" s="24" t="n"/>
+      <c r="G30" s="25" t="n"/>
+      <c r="H30" s="25" t="n"/>
       <c r="J30">
         <f>IF(COUNTA($A30:$H30)=0,0,IF(OR($B30="",$C30="",$E30=""),1,0))</f>
         <v/>
@@ -16720,8 +16727,8 @@
       <c r="D31" s="23" t="n"/>
       <c r="E31" s="23" t="n"/>
       <c r="F31" s="23" t="n"/>
-      <c r="G31" s="24" t="n"/>
-      <c r="H31" s="24" t="n"/>
+      <c r="G31" s="25" t="n"/>
+      <c r="H31" s="25" t="n"/>
       <c r="J31">
         <f>IF(COUNTA($A31:$H31)=0,0,IF(OR($B31="",$C31="",$E31=""),1,0))</f>
         <v/>
@@ -16738,8 +16745,8 @@
       <c r="D32" s="23" t="n"/>
       <c r="E32" s="23" t="n"/>
       <c r="F32" s="23" t="n"/>
-      <c r="G32" s="24" t="n"/>
-      <c r="H32" s="24" t="n"/>
+      <c r="G32" s="25" t="n"/>
+      <c r="H32" s="25" t="n"/>
       <c r="J32">
         <f>IF(COUNTA($A32:$H32)=0,0,IF(OR($B32="",$C32="",$E32=""),1,0))</f>
         <v/>
@@ -16756,8 +16763,8 @@
       <c r="D33" s="23" t="n"/>
       <c r="E33" s="23" t="n"/>
       <c r="F33" s="23" t="n"/>
-      <c r="G33" s="24" t="n"/>
-      <c r="H33" s="24" t="n"/>
+      <c r="G33" s="25" t="n"/>
+      <c r="H33" s="25" t="n"/>
       <c r="J33">
         <f>IF(COUNTA($A33:$H33)=0,0,IF(OR($B33="",$C33="",$E33=""),1,0))</f>
         <v/>
@@ -16774,8 +16781,8 @@
       <c r="D34" s="23" t="n"/>
       <c r="E34" s="23" t="n"/>
       <c r="F34" s="23" t="n"/>
-      <c r="G34" s="24" t="n"/>
-      <c r="H34" s="24" t="n"/>
+      <c r="G34" s="25" t="n"/>
+      <c r="H34" s="25" t="n"/>
       <c r="J34">
         <f>IF(COUNTA($A34:$H34)=0,0,IF(OR($B34="",$C34="",$E34=""),1,0))</f>
         <v/>
@@ -16792,8 +16799,8 @@
       <c r="D35" s="23" t="n"/>
       <c r="E35" s="23" t="n"/>
       <c r="F35" s="23" t="n"/>
-      <c r="G35" s="24" t="n"/>
-      <c r="H35" s="24" t="n"/>
+      <c r="G35" s="25" t="n"/>
+      <c r="H35" s="25" t="n"/>
       <c r="J35">
         <f>IF(COUNTA($A35:$H35)=0,0,IF(OR($B35="",$C35="",$E35=""),1,0))</f>
         <v/>
@@ -16810,8 +16817,8 @@
       <c r="D36" s="23" t="n"/>
       <c r="E36" s="23" t="n"/>
       <c r="F36" s="23" t="n"/>
-      <c r="G36" s="24" t="n"/>
-      <c r="H36" s="24" t="n"/>
+      <c r="G36" s="25" t="n"/>
+      <c r="H36" s="25" t="n"/>
       <c r="J36">
         <f>IF(COUNTA($A36:$H36)=0,0,IF(OR($B36="",$C36="",$E36=""),1,0))</f>
         <v/>
@@ -16828,8 +16835,8 @@
       <c r="D37" s="23" t="n"/>
       <c r="E37" s="23" t="n"/>
       <c r="F37" s="23" t="n"/>
-      <c r="G37" s="24" t="n"/>
-      <c r="H37" s="24" t="n"/>
+      <c r="G37" s="25" t="n"/>
+      <c r="H37" s="25" t="n"/>
       <c r="J37">
         <f>IF(COUNTA($A37:$H37)=0,0,IF(OR($B37="",$C37="",$E37=""),1,0))</f>
         <v/>
@@ -16846,8 +16853,8 @@
       <c r="D38" s="23" t="n"/>
       <c r="E38" s="23" t="n"/>
       <c r="F38" s="23" t="n"/>
-      <c r="G38" s="24" t="n"/>
-      <c r="H38" s="24" t="n"/>
+      <c r="G38" s="25" t="n"/>
+      <c r="H38" s="25" t="n"/>
       <c r="J38">
         <f>IF(COUNTA($A38:$H38)=0,0,IF(OR($B38="",$C38="",$E38=""),1,0))</f>
         <v/>
@@ -16864,8 +16871,8 @@
       <c r="D39" s="23" t="n"/>
       <c r="E39" s="23" t="n"/>
       <c r="F39" s="23" t="n"/>
-      <c r="G39" s="24" t="n"/>
-      <c r="H39" s="24" t="n"/>
+      <c r="G39" s="25" t="n"/>
+      <c r="H39" s="25" t="n"/>
       <c r="J39">
         <f>IF(COUNTA($A39:$H39)=0,0,IF(OR($B39="",$C39="",$E39=""),1,0))</f>
         <v/>
@@ -16882,8 +16889,8 @@
       <c r="D40" s="23" t="n"/>
       <c r="E40" s="23" t="n"/>
       <c r="F40" s="23" t="n"/>
-      <c r="G40" s="24" t="n"/>
-      <c r="H40" s="24" t="n"/>
+      <c r="G40" s="25" t="n"/>
+      <c r="H40" s="25" t="n"/>
       <c r="J40">
         <f>IF(COUNTA($A40:$H40)=0,0,IF(OR($B40="",$C40="",$E40=""),1,0))</f>
         <v/>
@@ -16900,8 +16907,8 @@
       <c r="D41" s="23" t="n"/>
       <c r="E41" s="23" t="n"/>
       <c r="F41" s="23" t="n"/>
-      <c r="G41" s="24" t="n"/>
-      <c r="H41" s="24" t="n"/>
+      <c r="G41" s="25" t="n"/>
+      <c r="H41" s="25" t="n"/>
       <c r="J41">
         <f>IF(COUNTA($A41:$H41)=0,0,IF(OR($B41="",$C41="",$E41=""),1,0))</f>
         <v/>
@@ -21669,8 +21676,8 @@
       <c r="B2" s="23" t="n"/>
       <c r="C2" s="23" t="n"/>
       <c r="D2" s="23" t="n"/>
-      <c r="E2" s="24" t="n"/>
-      <c r="F2" s="24" t="n"/>
+      <c r="E2" s="25" t="n"/>
+      <c r="F2" s="25" t="n"/>
       <c r="H2">
         <f>IF(COUNTA($A2:$F2)=0,0,IF($B2="",1,0))</f>
         <v/>
@@ -21681,8 +21688,8 @@
       <c r="B3" s="23" t="n"/>
       <c r="C3" s="23" t="n"/>
       <c r="D3" s="23" t="n"/>
-      <c r="E3" s="24" t="n"/>
-      <c r="F3" s="24" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
       <c r="H3">
         <f>IF(COUNTA($A3:$F3)=0,0,IF($B3="",1,0))</f>
         <v/>
@@ -21693,8 +21700,8 @@
       <c r="B4" s="23" t="n"/>
       <c r="C4" s="23" t="n"/>
       <c r="D4" s="23" t="n"/>
-      <c r="E4" s="24" t="n"/>
-      <c r="F4" s="24" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
       <c r="H4">
         <f>IF(COUNTA($A4:$F4)=0,0,IF($B4="",1,0))</f>
         <v/>
@@ -21705,8 +21712,8 @@
       <c r="B5" s="23" t="n"/>
       <c r="C5" s="23" t="n"/>
       <c r="D5" s="23" t="n"/>
-      <c r="E5" s="24" t="n"/>
-      <c r="F5" s="24" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
       <c r="H5">
         <f>IF(COUNTA($A5:$F5)=0,0,IF($B5="",1,0))</f>
         <v/>
@@ -21717,8 +21724,8 @@
       <c r="B6" s="23" t="n"/>
       <c r="C6" s="23" t="n"/>
       <c r="D6" s="23" t="n"/>
-      <c r="E6" s="24" t="n"/>
-      <c r="F6" s="24" t="n"/>
+      <c r="E6" s="25" t="n"/>
+      <c r="F6" s="25" t="n"/>
       <c r="H6">
         <f>IF(COUNTA($A6:$F6)=0,0,IF($B6="",1,0))</f>
         <v/>
@@ -21729,8 +21736,8 @@
       <c r="B7" s="23" t="n"/>
       <c r="C7" s="23" t="n"/>
       <c r="D7" s="23" t="n"/>
-      <c r="E7" s="24" t="n"/>
-      <c r="F7" s="24" t="n"/>
+      <c r="E7" s="25" t="n"/>
+      <c r="F7" s="25" t="n"/>
       <c r="H7">
         <f>IF(COUNTA($A7:$F7)=0,0,IF($B7="",1,0))</f>
         <v/>
@@ -21741,8 +21748,8 @@
       <c r="B8" s="23" t="n"/>
       <c r="C8" s="23" t="n"/>
       <c r="D8" s="23" t="n"/>
-      <c r="E8" s="24" t="n"/>
-      <c r="F8" s="24" t="n"/>
+      <c r="E8" s="25" t="n"/>
+      <c r="F8" s="25" t="n"/>
       <c r="H8">
         <f>IF(COUNTA($A8:$F8)=0,0,IF($B8="",1,0))</f>
         <v/>
@@ -21753,8 +21760,8 @@
       <c r="B9" s="23" t="n"/>
       <c r="C9" s="23" t="n"/>
       <c r="D9" s="23" t="n"/>
-      <c r="E9" s="24" t="n"/>
-      <c r="F9" s="24" t="n"/>
+      <c r="E9" s="25" t="n"/>
+      <c r="F9" s="25" t="n"/>
       <c r="H9">
         <f>IF(COUNTA($A9:$F9)=0,0,IF($B9="",1,0))</f>
         <v/>
@@ -21765,8 +21772,8 @@
       <c r="B10" s="23" t="n"/>
       <c r="C10" s="23" t="n"/>
       <c r="D10" s="23" t="n"/>
-      <c r="E10" s="24" t="n"/>
-      <c r="F10" s="24" t="n"/>
+      <c r="E10" s="25" t="n"/>
+      <c r="F10" s="25" t="n"/>
       <c r="H10">
         <f>IF(COUNTA($A10:$F10)=0,0,IF($B10="",1,0))</f>
         <v/>
@@ -21777,8 +21784,8 @@
       <c r="B11" s="23" t="n"/>
       <c r="C11" s="23" t="n"/>
       <c r="D11" s="23" t="n"/>
-      <c r="E11" s="24" t="n"/>
-      <c r="F11" s="24" t="n"/>
+      <c r="E11" s="25" t="n"/>
+      <c r="F11" s="25" t="n"/>
       <c r="H11">
         <f>IF(COUNTA($A11:$F11)=0,0,IF($B11="",1,0))</f>
         <v/>
@@ -21789,8 +21796,8 @@
       <c r="B12" s="23" t="n"/>
       <c r="C12" s="23" t="n"/>
       <c r="D12" s="23" t="n"/>
-      <c r="E12" s="24" t="n"/>
-      <c r="F12" s="24" t="n"/>
+      <c r="E12" s="25" t="n"/>
+      <c r="F12" s="25" t="n"/>
       <c r="H12">
         <f>IF(COUNTA($A12:$F12)=0,0,IF($B12="",1,0))</f>
         <v/>
@@ -21801,8 +21808,8 @@
       <c r="B13" s="23" t="n"/>
       <c r="C13" s="23" t="n"/>
       <c r="D13" s="23" t="n"/>
-      <c r="E13" s="24" t="n"/>
-      <c r="F13" s="24" t="n"/>
+      <c r="E13" s="25" t="n"/>
+      <c r="F13" s="25" t="n"/>
       <c r="H13">
         <f>IF(COUNTA($A13:$F13)=0,0,IF($B13="",1,0))</f>
         <v/>
@@ -21813,8 +21820,8 @@
       <c r="B14" s="23" t="n"/>
       <c r="C14" s="23" t="n"/>
       <c r="D14" s="23" t="n"/>
-      <c r="E14" s="24" t="n"/>
-      <c r="F14" s="24" t="n"/>
+      <c r="E14" s="25" t="n"/>
+      <c r="F14" s="25" t="n"/>
       <c r="H14">
         <f>IF(COUNTA($A14:$F14)=0,0,IF($B14="",1,0))</f>
         <v/>
@@ -21825,8 +21832,8 @@
       <c r="B15" s="23" t="n"/>
       <c r="C15" s="23" t="n"/>
       <c r="D15" s="23" t="n"/>
-      <c r="E15" s="24" t="n"/>
-      <c r="F15" s="24" t="n"/>
+      <c r="E15" s="25" t="n"/>
+      <c r="F15" s="25" t="n"/>
       <c r="H15">
         <f>IF(COUNTA($A15:$F15)=0,0,IF($B15="",1,0))</f>
         <v/>
@@ -21837,8 +21844,8 @@
       <c r="B16" s="23" t="n"/>
       <c r="C16" s="23" t="n"/>
       <c r="D16" s="23" t="n"/>
-      <c r="E16" s="24" t="n"/>
-      <c r="F16" s="24" t="n"/>
+      <c r="E16" s="25" t="n"/>
+      <c r="F16" s="25" t="n"/>
       <c r="H16">
         <f>IF(COUNTA($A16:$F16)=0,0,IF($B16="",1,0))</f>
         <v/>
@@ -21849,8 +21856,8 @@
       <c r="B17" s="23" t="n"/>
       <c r="C17" s="23" t="n"/>
       <c r="D17" s="23" t="n"/>
-      <c r="E17" s="24" t="n"/>
-      <c r="F17" s="24" t="n"/>
+      <c r="E17" s="25" t="n"/>
+      <c r="F17" s="25" t="n"/>
       <c r="H17">
         <f>IF(COUNTA($A17:$F17)=0,0,IF($B17="",1,0))</f>
         <v/>
@@ -21861,8 +21868,8 @@
       <c r="B18" s="23" t="n"/>
       <c r="C18" s="23" t="n"/>
       <c r="D18" s="23" t="n"/>
-      <c r="E18" s="24" t="n"/>
-      <c r="F18" s="24" t="n"/>
+      <c r="E18" s="25" t="n"/>
+      <c r="F18" s="25" t="n"/>
       <c r="H18">
         <f>IF(COUNTA($A18:$F18)=0,0,IF($B18="",1,0))</f>
         <v/>
@@ -21873,8 +21880,8 @@
       <c r="B19" s="23" t="n"/>
       <c r="C19" s="23" t="n"/>
       <c r="D19" s="23" t="n"/>
-      <c r="E19" s="24" t="n"/>
-      <c r="F19" s="24" t="n"/>
+      <c r="E19" s="25" t="n"/>
+      <c r="F19" s="25" t="n"/>
       <c r="H19">
         <f>IF(COUNTA($A19:$F19)=0,0,IF($B19="",1,0))</f>
         <v/>
@@ -21885,8 +21892,8 @@
       <c r="B20" s="23" t="n"/>
       <c r="C20" s="23" t="n"/>
       <c r="D20" s="23" t="n"/>
-      <c r="E20" s="24" t="n"/>
-      <c r="F20" s="24" t="n"/>
+      <c r="E20" s="25" t="n"/>
+      <c r="F20" s="25" t="n"/>
       <c r="H20">
         <f>IF(COUNTA($A20:$F20)=0,0,IF($B20="",1,0))</f>
         <v/>
@@ -21897,8 +21904,8 @@
       <c r="B21" s="23" t="n"/>
       <c r="C21" s="23" t="n"/>
       <c r="D21" s="23" t="n"/>
-      <c r="E21" s="24" t="n"/>
-      <c r="F21" s="24" t="n"/>
+      <c r="E21" s="25" t="n"/>
+      <c r="F21" s="25" t="n"/>
       <c r="H21">
         <f>IF(COUNTA($A21:$F21)=0,0,IF($B21="",1,0))</f>
         <v/>
@@ -21909,8 +21916,8 @@
       <c r="B22" s="23" t="n"/>
       <c r="C22" s="23" t="n"/>
       <c r="D22" s="23" t="n"/>
-      <c r="E22" s="24" t="n"/>
-      <c r="F22" s="24" t="n"/>
+      <c r="E22" s="25" t="n"/>
+      <c r="F22" s="25" t="n"/>
       <c r="H22">
         <f>IF(COUNTA($A22:$F22)=0,0,IF($B22="",1,0))</f>
         <v/>
@@ -21921,8 +21928,8 @@
       <c r="B23" s="23" t="n"/>
       <c r="C23" s="23" t="n"/>
       <c r="D23" s="23" t="n"/>
-      <c r="E23" s="24" t="n"/>
-      <c r="F23" s="24" t="n"/>
+      <c r="E23" s="25" t="n"/>
+      <c r="F23" s="25" t="n"/>
       <c r="H23">
         <f>IF(COUNTA($A23:$F23)=0,0,IF($B23="",1,0))</f>
         <v/>
@@ -21933,8 +21940,8 @@
       <c r="B24" s="23" t="n"/>
       <c r="C24" s="23" t="n"/>
       <c r="D24" s="23" t="n"/>
-      <c r="E24" s="24" t="n"/>
-      <c r="F24" s="24" t="n"/>
+      <c r="E24" s="25" t="n"/>
+      <c r="F24" s="25" t="n"/>
       <c r="H24">
         <f>IF(COUNTA($A24:$F24)=0,0,IF($B24="",1,0))</f>
         <v/>
@@ -21945,8 +21952,8 @@
       <c r="B25" s="23" t="n"/>
       <c r="C25" s="23" t="n"/>
       <c r="D25" s="23" t="n"/>
-      <c r="E25" s="24" t="n"/>
-      <c r="F25" s="24" t="n"/>
+      <c r="E25" s="25" t="n"/>
+      <c r="F25" s="25" t="n"/>
       <c r="H25">
         <f>IF(COUNTA($A25:$F25)=0,0,IF($B25="",1,0))</f>
         <v/>
@@ -21957,8 +21964,8 @@
       <c r="B26" s="23" t="n"/>
       <c r="C26" s="23" t="n"/>
       <c r="D26" s="23" t="n"/>
-      <c r="E26" s="24" t="n"/>
-      <c r="F26" s="24" t="n"/>
+      <c r="E26" s="25" t="n"/>
+      <c r="F26" s="25" t="n"/>
       <c r="H26">
         <f>IF(COUNTA($A26:$F26)=0,0,IF($B26="",1,0))</f>
         <v/>
@@ -21969,8 +21976,8 @@
       <c r="B27" s="23" t="n"/>
       <c r="C27" s="23" t="n"/>
       <c r="D27" s="23" t="n"/>
-      <c r="E27" s="24" t="n"/>
-      <c r="F27" s="24" t="n"/>
+      <c r="E27" s="25" t="n"/>
+      <c r="F27" s="25" t="n"/>
       <c r="H27">
         <f>IF(COUNTA($A27:$F27)=0,0,IF($B27="",1,0))</f>
         <v/>
@@ -21981,8 +21988,8 @@
       <c r="B28" s="23" t="n"/>
       <c r="C28" s="23" t="n"/>
       <c r="D28" s="23" t="n"/>
-      <c r="E28" s="24" t="n"/>
-      <c r="F28" s="24" t="n"/>
+      <c r="E28" s="25" t="n"/>
+      <c r="F28" s="25" t="n"/>
       <c r="H28">
         <f>IF(COUNTA($A28:$F28)=0,0,IF($B28="",1,0))</f>
         <v/>
@@ -21993,8 +22000,8 @@
       <c r="B29" s="23" t="n"/>
       <c r="C29" s="23" t="n"/>
       <c r="D29" s="23" t="n"/>
-      <c r="E29" s="24" t="n"/>
-      <c r="F29" s="24" t="n"/>
+      <c r="E29" s="25" t="n"/>
+      <c r="F29" s="25" t="n"/>
       <c r="H29">
         <f>IF(COUNTA($A29:$F29)=0,0,IF($B29="",1,0))</f>
         <v/>
@@ -22005,8 +22012,8 @@
       <c r="B30" s="23" t="n"/>
       <c r="C30" s="23" t="n"/>
       <c r="D30" s="23" t="n"/>
-      <c r="E30" s="24" t="n"/>
-      <c r="F30" s="24" t="n"/>
+      <c r="E30" s="25" t="n"/>
+      <c r="F30" s="25" t="n"/>
       <c r="H30">
         <f>IF(COUNTA($A30:$F30)=0,0,IF($B30="",1,0))</f>
         <v/>
@@ -22017,8 +22024,8 @@
       <c r="B31" s="23" t="n"/>
       <c r="C31" s="23" t="n"/>
       <c r="D31" s="23" t="n"/>
-      <c r="E31" s="24" t="n"/>
-      <c r="F31" s="24" t="n"/>
+      <c r="E31" s="25" t="n"/>
+      <c r="F31" s="25" t="n"/>
       <c r="H31">
         <f>IF(COUNTA($A31:$F31)=0,0,IF($B31="",1,0))</f>
         <v/>
@@ -22029,8 +22036,8 @@
       <c r="B32" s="23" t="n"/>
       <c r="C32" s="23" t="n"/>
       <c r="D32" s="23" t="n"/>
-      <c r="E32" s="24" t="n"/>
-      <c r="F32" s="24" t="n"/>
+      <c r="E32" s="25" t="n"/>
+      <c r="F32" s="25" t="n"/>
       <c r="H32">
         <f>IF(COUNTA($A32:$F32)=0,0,IF($B32="",1,0))</f>
         <v/>
@@ -22041,8 +22048,8 @@
       <c r="B33" s="23" t="n"/>
       <c r="C33" s="23" t="n"/>
       <c r="D33" s="23" t="n"/>
-      <c r="E33" s="24" t="n"/>
-      <c r="F33" s="24" t="n"/>
+      <c r="E33" s="25" t="n"/>
+      <c r="F33" s="25" t="n"/>
       <c r="H33">
         <f>IF(COUNTA($A33:$F33)=0,0,IF($B33="",1,0))</f>
         <v/>
@@ -22053,8 +22060,8 @@
       <c r="B34" s="23" t="n"/>
       <c r="C34" s="23" t="n"/>
       <c r="D34" s="23" t="n"/>
-      <c r="E34" s="24" t="n"/>
-      <c r="F34" s="24" t="n"/>
+      <c r="E34" s="25" t="n"/>
+      <c r="F34" s="25" t="n"/>
       <c r="H34">
         <f>IF(COUNTA($A34:$F34)=0,0,IF($B34="",1,0))</f>
         <v/>
@@ -22065,8 +22072,8 @@
       <c r="B35" s="23" t="n"/>
       <c r="C35" s="23" t="n"/>
       <c r="D35" s="23" t="n"/>
-      <c r="E35" s="24" t="n"/>
-      <c r="F35" s="24" t="n"/>
+      <c r="E35" s="25" t="n"/>
+      <c r="F35" s="25" t="n"/>
       <c r="H35">
         <f>IF(COUNTA($A35:$F35)=0,0,IF($B35="",1,0))</f>
         <v/>
@@ -22077,8 +22084,8 @@
       <c r="B36" s="23" t="n"/>
       <c r="C36" s="23" t="n"/>
       <c r="D36" s="23" t="n"/>
-      <c r="E36" s="24" t="n"/>
-      <c r="F36" s="24" t="n"/>
+      <c r="E36" s="25" t="n"/>
+      <c r="F36" s="25" t="n"/>
       <c r="H36">
         <f>IF(COUNTA($A36:$F36)=0,0,IF($B36="",1,0))</f>
         <v/>
@@ -22089,8 +22096,8 @@
       <c r="B37" s="23" t="n"/>
       <c r="C37" s="23" t="n"/>
       <c r="D37" s="23" t="n"/>
-      <c r="E37" s="24" t="n"/>
-      <c r="F37" s="24" t="n"/>
+      <c r="E37" s="25" t="n"/>
+      <c r="F37" s="25" t="n"/>
       <c r="H37">
         <f>IF(COUNTA($A37:$F37)=0,0,IF($B37="",1,0))</f>
         <v/>
@@ -22101,8 +22108,8 @@
       <c r="B38" s="23" t="n"/>
       <c r="C38" s="23" t="n"/>
       <c r="D38" s="23" t="n"/>
-      <c r="E38" s="24" t="n"/>
-      <c r="F38" s="24" t="n"/>
+      <c r="E38" s="25" t="n"/>
+      <c r="F38" s="25" t="n"/>
       <c r="H38">
         <f>IF(COUNTA($A38:$F38)=0,0,IF($B38="",1,0))</f>
         <v/>
@@ -22113,8 +22120,8 @@
       <c r="B39" s="23" t="n"/>
       <c r="C39" s="23" t="n"/>
       <c r="D39" s="23" t="n"/>
-      <c r="E39" s="24" t="n"/>
-      <c r="F39" s="24" t="n"/>
+      <c r="E39" s="25" t="n"/>
+      <c r="F39" s="25" t="n"/>
       <c r="H39">
         <f>IF(COUNTA($A39:$F39)=0,0,IF($B39="",1,0))</f>
         <v/>
@@ -22125,8 +22132,8 @@
       <c r="B40" s="23" t="n"/>
       <c r="C40" s="23" t="n"/>
       <c r="D40" s="23" t="n"/>
-      <c r="E40" s="24" t="n"/>
-      <c r="F40" s="24" t="n"/>
+      <c r="E40" s="25" t="n"/>
+      <c r="F40" s="25" t="n"/>
       <c r="H40">
         <f>IF(COUNTA($A40:$F40)=0,0,IF($B40="",1,0))</f>
         <v/>
@@ -22137,8 +22144,8 @@
       <c r="B41" s="23" t="n"/>
       <c r="C41" s="23" t="n"/>
       <c r="D41" s="23" t="n"/>
-      <c r="E41" s="24" t="n"/>
-      <c r="F41" s="24" t="n"/>
+      <c r="E41" s="25" t="n"/>
+      <c r="F41" s="25" t="n"/>
       <c r="H41">
         <f>IF(COUNTA($A41:$F41)=0,0,IF($B41="",1,0))</f>
         <v/>

--- a/src/main/resources/canevas/canevas-vierge.xlsx
+++ b/src/main/resources/canevas/canevas-vierge.xlsx
@@ -2385,7 +2385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T300"/>
+  <dimension ref="A1:U300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2400,13 +2400,15 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="15" customWidth="1" min="16" max="16"/>
-    <col width="40" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="40" customWidth="1" min="18" max="18"/>
     <col hidden="1" width="13" customWidth="1" min="19" max="19"/>
     <col hidden="1" width="13" customWidth="1" min="20" max="20"/>
+    <col hidden="1" width="13" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2472,35 +2474,40 @@
       </c>
       <c r="M1" s="10" t="inlineStr">
         <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="N1" s="10" t="inlineStr">
+        <is>
           <t>RAM</t>
         </is>
       </c>
-      <c r="N1" s="10" t="inlineStr">
+      <c r="O1" s="10" t="inlineStr">
         <is>
           <t>Processeur</t>
         </is>
       </c>
-      <c r="O1" s="10" t="inlineStr">
+      <c r="P1" s="10" t="inlineStr">
         <is>
           <t>Disque dur</t>
         </is>
       </c>
-      <c r="P1" s="10" t="inlineStr">
+      <c r="Q1" s="10" t="inlineStr">
         <is>
           <t>Statut</t>
         </is>
       </c>
-      <c r="Q1" s="10" t="inlineStr">
+      <c r="R1" s="10" t="inlineStr">
         <is>
           <t>Observations</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>ctrl</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>ctrlfmt</t>
         </is>
@@ -2519,16 +2526,16 @@
       <c r="J2" s="23" t="n"/>
       <c r="K2" s="23" t="n"/>
       <c r="L2" s="23" t="n"/>
-      <c r="M2" s="25" t="n"/>
       <c r="N2" s="25" t="n"/>
       <c r="O2" s="25" t="n"/>
       <c r="P2" s="25" t="n"/>
       <c r="Q2" s="25" t="n"/>
-      <c r="S2">
+      <c r="R2" s="25" t="n"/>
+      <c r="T2">
         <f>IF(COUNTA($A2:$Q2)=0,0,IF(OR($B2="",$D2="",$F2="",$G2=""),1,0))</f>
         <v/>
       </c>
-      <c r="T2">
+      <c r="U2">
         <f>IF(OR(AND($D2&lt;&gt;"",OR(LEN($D2)&lt;&gt;17,LEN($D2)-LEN(SUBSTITUTE($D2,":",""))&lt;&gt;5)),AND($E2&lt;&gt;"",OR(LEN($E2)&lt;&gt;17,LEN($E2)-LEN(SUBSTITUTE($E2,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -2546,16 +2553,16 @@
       <c r="J3" s="23" t="n"/>
       <c r="K3" s="23" t="n"/>
       <c r="L3" s="23" t="n"/>
-      <c r="M3" s="25" t="n"/>
       <c r="N3" s="25" t="n"/>
       <c r="O3" s="25" t="n"/>
       <c r="P3" s="25" t="n"/>
       <c r="Q3" s="25" t="n"/>
-      <c r="S3">
+      <c r="R3" s="25" t="n"/>
+      <c r="T3">
         <f>IF(COUNTA($A3:$Q3)=0,0,IF(OR($B3="",$D3="",$F3="",$G3=""),1,0))</f>
         <v/>
       </c>
-      <c r="T3">
+      <c r="U3">
         <f>IF(OR(AND($D3&lt;&gt;"",OR(LEN($D3)&lt;&gt;17,LEN($D3)-LEN(SUBSTITUTE($D3,":",""))&lt;&gt;5)),AND($E3&lt;&gt;"",OR(LEN($E3)&lt;&gt;17,LEN($E3)-LEN(SUBSTITUTE($E3,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -2573,16 +2580,16 @@
       <c r="J4" s="23" t="n"/>
       <c r="K4" s="23" t="n"/>
       <c r="L4" s="23" t="n"/>
-      <c r="M4" s="25" t="n"/>
       <c r="N4" s="25" t="n"/>
       <c r="O4" s="25" t="n"/>
       <c r="P4" s="25" t="n"/>
       <c r="Q4" s="25" t="n"/>
-      <c r="S4">
+      <c r="R4" s="25" t="n"/>
+      <c r="T4">
         <f>IF(COUNTA($A4:$Q4)=0,0,IF(OR($B4="",$D4="",$F4="",$G4=""),1,0))</f>
         <v/>
       </c>
-      <c r="T4">
+      <c r="U4">
         <f>IF(OR(AND($D4&lt;&gt;"",OR(LEN($D4)&lt;&gt;17,LEN($D4)-LEN(SUBSTITUTE($D4,":",""))&lt;&gt;5)),AND($E4&lt;&gt;"",OR(LEN($E4)&lt;&gt;17,LEN($E4)-LEN(SUBSTITUTE($E4,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -2600,16 +2607,16 @@
       <c r="J5" s="23" t="n"/>
       <c r="K5" s="23" t="n"/>
       <c r="L5" s="23" t="n"/>
-      <c r="M5" s="25" t="n"/>
       <c r="N5" s="25" t="n"/>
       <c r="O5" s="25" t="n"/>
       <c r="P5" s="25" t="n"/>
       <c r="Q5" s="25" t="n"/>
-      <c r="S5">
+      <c r="R5" s="25" t="n"/>
+      <c r="T5">
         <f>IF(COUNTA($A5:$Q5)=0,0,IF(OR($B5="",$D5="",$F5="",$G5=""),1,0))</f>
         <v/>
       </c>
-      <c r="T5">
+      <c r="U5">
         <f>IF(OR(AND($D5&lt;&gt;"",OR(LEN($D5)&lt;&gt;17,LEN($D5)-LEN(SUBSTITUTE($D5,":",""))&lt;&gt;5)),AND($E5&lt;&gt;"",OR(LEN($E5)&lt;&gt;17,LEN($E5)-LEN(SUBSTITUTE($E5,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -2627,16 +2634,16 @@
       <c r="J6" s="23" t="n"/>
       <c r="K6" s="23" t="n"/>
       <c r="L6" s="23" t="n"/>
-      <c r="M6" s="25" t="n"/>
       <c r="N6" s="25" t="n"/>
       <c r="O6" s="25" t="n"/>
       <c r="P6" s="25" t="n"/>
       <c r="Q6" s="25" t="n"/>
-      <c r="S6">
+      <c r="R6" s="25" t="n"/>
+      <c r="T6">
         <f>IF(COUNTA($A6:$Q6)=0,0,IF(OR($B6="",$D6="",$F6="",$G6=""),1,0))</f>
         <v/>
       </c>
-      <c r="T6">
+      <c r="U6">
         <f>IF(OR(AND($D6&lt;&gt;"",OR(LEN($D6)&lt;&gt;17,LEN($D6)-LEN(SUBSTITUTE($D6,":",""))&lt;&gt;5)),AND($E6&lt;&gt;"",OR(LEN($E6)&lt;&gt;17,LEN($E6)-LEN(SUBSTITUTE($E6,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -2654,16 +2661,16 @@
       <c r="J7" s="23" t="n"/>
       <c r="K7" s="23" t="n"/>
       <c r="L7" s="23" t="n"/>
-      <c r="M7" s="25" t="n"/>
       <c r="N7" s="25" t="n"/>
       <c r="O7" s="25" t="n"/>
       <c r="P7" s="25" t="n"/>
       <c r="Q7" s="25" t="n"/>
-      <c r="S7">
+      <c r="R7" s="25" t="n"/>
+      <c r="T7">
         <f>IF(COUNTA($A7:$Q7)=0,0,IF(OR($B7="",$D7="",$F7="",$G7=""),1,0))</f>
         <v/>
       </c>
-      <c r="T7">
+      <c r="U7">
         <f>IF(OR(AND($D7&lt;&gt;"",OR(LEN($D7)&lt;&gt;17,LEN($D7)-LEN(SUBSTITUTE($D7,":",""))&lt;&gt;5)),AND($E7&lt;&gt;"",OR(LEN($E7)&lt;&gt;17,LEN($E7)-LEN(SUBSTITUTE($E7,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -2681,16 +2688,16 @@
       <c r="J8" s="23" t="n"/>
       <c r="K8" s="23" t="n"/>
       <c r="L8" s="23" t="n"/>
-      <c r="M8" s="25" t="n"/>
       <c r="N8" s="25" t="n"/>
       <c r="O8" s="25" t="n"/>
       <c r="P8" s="25" t="n"/>
       <c r="Q8" s="25" t="n"/>
-      <c r="S8">
+      <c r="R8" s="25" t="n"/>
+      <c r="T8">
         <f>IF(COUNTA($A8:$Q8)=0,0,IF(OR($B8="",$D8="",$F8="",$G8=""),1,0))</f>
         <v/>
       </c>
-      <c r="T8">
+      <c r="U8">
         <f>IF(OR(AND($D8&lt;&gt;"",OR(LEN($D8)&lt;&gt;17,LEN($D8)-LEN(SUBSTITUTE($D8,":",""))&lt;&gt;5)),AND($E8&lt;&gt;"",OR(LEN($E8)&lt;&gt;17,LEN($E8)-LEN(SUBSTITUTE($E8,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -2708,16 +2715,16 @@
       <c r="J9" s="23" t="n"/>
       <c r="K9" s="23" t="n"/>
       <c r="L9" s="23" t="n"/>
-      <c r="M9" s="25" t="n"/>
       <c r="N9" s="25" t="n"/>
       <c r="O9" s="25" t="n"/>
       <c r="P9" s="25" t="n"/>
       <c r="Q9" s="25" t="n"/>
-      <c r="S9">
+      <c r="R9" s="25" t="n"/>
+      <c r="T9">
         <f>IF(COUNTA($A9:$Q9)=0,0,IF(OR($B9="",$D9="",$F9="",$G9=""),1,0))</f>
         <v/>
       </c>
-      <c r="T9">
+      <c r="U9">
         <f>IF(OR(AND($D9&lt;&gt;"",OR(LEN($D9)&lt;&gt;17,LEN($D9)-LEN(SUBSTITUTE($D9,":",""))&lt;&gt;5)),AND($E9&lt;&gt;"",OR(LEN($E9)&lt;&gt;17,LEN($E9)-LEN(SUBSTITUTE($E9,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -2735,16 +2742,16 @@
       <c r="J10" s="23" t="n"/>
       <c r="K10" s="23" t="n"/>
       <c r="L10" s="23" t="n"/>
-      <c r="M10" s="25" t="n"/>
       <c r="N10" s="25" t="n"/>
       <c r="O10" s="25" t="n"/>
       <c r="P10" s="25" t="n"/>
       <c r="Q10" s="25" t="n"/>
-      <c r="S10">
+      <c r="R10" s="25" t="n"/>
+      <c r="T10">
         <f>IF(COUNTA($A10:$Q10)=0,0,IF(OR($B10="",$D10="",$F10="",$G10=""),1,0))</f>
         <v/>
       </c>
-      <c r="T10">
+      <c r="U10">
         <f>IF(OR(AND($D10&lt;&gt;"",OR(LEN($D10)&lt;&gt;17,LEN($D10)-LEN(SUBSTITUTE($D10,":",""))&lt;&gt;5)),AND($E10&lt;&gt;"",OR(LEN($E10)&lt;&gt;17,LEN($E10)-LEN(SUBSTITUTE($E10,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -2762,16 +2769,16 @@
       <c r="J11" s="23" t="n"/>
       <c r="K11" s="23" t="n"/>
       <c r="L11" s="23" t="n"/>
-      <c r="M11" s="25" t="n"/>
       <c r="N11" s="25" t="n"/>
       <c r="O11" s="25" t="n"/>
       <c r="P11" s="25" t="n"/>
       <c r="Q11" s="25" t="n"/>
-      <c r="S11">
+      <c r="R11" s="25" t="n"/>
+      <c r="T11">
         <f>IF(COUNTA($A11:$Q11)=0,0,IF(OR($B11="",$D11="",$F11="",$G11=""),1,0))</f>
         <v/>
       </c>
-      <c r="T11">
+      <c r="U11">
         <f>IF(OR(AND($D11&lt;&gt;"",OR(LEN($D11)&lt;&gt;17,LEN($D11)-LEN(SUBSTITUTE($D11,":",""))&lt;&gt;5)),AND($E11&lt;&gt;"",OR(LEN($E11)&lt;&gt;17,LEN($E11)-LEN(SUBSTITUTE($E11,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -2789,16 +2796,16 @@
       <c r="J12" s="23" t="n"/>
       <c r="K12" s="23" t="n"/>
       <c r="L12" s="23" t="n"/>
-      <c r="M12" s="25" t="n"/>
       <c r="N12" s="25" t="n"/>
       <c r="O12" s="25" t="n"/>
       <c r="P12" s="25" t="n"/>
       <c r="Q12" s="25" t="n"/>
-      <c r="S12">
+      <c r="R12" s="25" t="n"/>
+      <c r="T12">
         <f>IF(COUNTA($A12:$Q12)=0,0,IF(OR($B12="",$D12="",$F12="",$G12=""),1,0))</f>
         <v/>
       </c>
-      <c r="T12">
+      <c r="U12">
         <f>IF(OR(AND($D12&lt;&gt;"",OR(LEN($D12)&lt;&gt;17,LEN($D12)-LEN(SUBSTITUTE($D12,":",""))&lt;&gt;5)),AND($E12&lt;&gt;"",OR(LEN($E12)&lt;&gt;17,LEN($E12)-LEN(SUBSTITUTE($E12,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -2816,16 +2823,16 @@
       <c r="J13" s="23" t="n"/>
       <c r="K13" s="23" t="n"/>
       <c r="L13" s="23" t="n"/>
-      <c r="M13" s="25" t="n"/>
       <c r="N13" s="25" t="n"/>
       <c r="O13" s="25" t="n"/>
       <c r="P13" s="25" t="n"/>
       <c r="Q13" s="25" t="n"/>
-      <c r="S13">
+      <c r="R13" s="25" t="n"/>
+      <c r="T13">
         <f>IF(COUNTA($A13:$Q13)=0,0,IF(OR($B13="",$D13="",$F13="",$G13=""),1,0))</f>
         <v/>
       </c>
-      <c r="T13">
+      <c r="U13">
         <f>IF(OR(AND($D13&lt;&gt;"",OR(LEN($D13)&lt;&gt;17,LEN($D13)-LEN(SUBSTITUTE($D13,":",""))&lt;&gt;5)),AND($E13&lt;&gt;"",OR(LEN($E13)&lt;&gt;17,LEN($E13)-LEN(SUBSTITUTE($E13,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -2843,16 +2850,16 @@
       <c r="J14" s="23" t="n"/>
       <c r="K14" s="23" t="n"/>
       <c r="L14" s="23" t="n"/>
-      <c r="M14" s="25" t="n"/>
       <c r="N14" s="25" t="n"/>
       <c r="O14" s="25" t="n"/>
       <c r="P14" s="25" t="n"/>
       <c r="Q14" s="25" t="n"/>
-      <c r="S14">
+      <c r="R14" s="25" t="n"/>
+      <c r="T14">
         <f>IF(COUNTA($A14:$Q14)=0,0,IF(OR($B14="",$D14="",$F14="",$G14=""),1,0))</f>
         <v/>
       </c>
-      <c r="T14">
+      <c r="U14">
         <f>IF(OR(AND($D14&lt;&gt;"",OR(LEN($D14)&lt;&gt;17,LEN($D14)-LEN(SUBSTITUTE($D14,":",""))&lt;&gt;5)),AND($E14&lt;&gt;"",OR(LEN($E14)&lt;&gt;17,LEN($E14)-LEN(SUBSTITUTE($E14,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -2870,16 +2877,16 @@
       <c r="J15" s="23" t="n"/>
       <c r="K15" s="23" t="n"/>
       <c r="L15" s="23" t="n"/>
-      <c r="M15" s="25" t="n"/>
       <c r="N15" s="25" t="n"/>
       <c r="O15" s="25" t="n"/>
       <c r="P15" s="25" t="n"/>
       <c r="Q15" s="25" t="n"/>
-      <c r="S15">
+      <c r="R15" s="25" t="n"/>
+      <c r="T15">
         <f>IF(COUNTA($A15:$Q15)=0,0,IF(OR($B15="",$D15="",$F15="",$G15=""),1,0))</f>
         <v/>
       </c>
-      <c r="T15">
+      <c r="U15">
         <f>IF(OR(AND($D15&lt;&gt;"",OR(LEN($D15)&lt;&gt;17,LEN($D15)-LEN(SUBSTITUTE($D15,":",""))&lt;&gt;5)),AND($E15&lt;&gt;"",OR(LEN($E15)&lt;&gt;17,LEN($E15)-LEN(SUBSTITUTE($E15,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -2897,16 +2904,16 @@
       <c r="J16" s="23" t="n"/>
       <c r="K16" s="23" t="n"/>
       <c r="L16" s="23" t="n"/>
-      <c r="M16" s="25" t="n"/>
       <c r="N16" s="25" t="n"/>
       <c r="O16" s="25" t="n"/>
       <c r="P16" s="25" t="n"/>
       <c r="Q16" s="25" t="n"/>
-      <c r="S16">
+      <c r="R16" s="25" t="n"/>
+      <c r="T16">
         <f>IF(COUNTA($A16:$Q16)=0,0,IF(OR($B16="",$D16="",$F16="",$G16=""),1,0))</f>
         <v/>
       </c>
-      <c r="T16">
+      <c r="U16">
         <f>IF(OR(AND($D16&lt;&gt;"",OR(LEN($D16)&lt;&gt;17,LEN($D16)-LEN(SUBSTITUTE($D16,":",""))&lt;&gt;5)),AND($E16&lt;&gt;"",OR(LEN($E16)&lt;&gt;17,LEN($E16)-LEN(SUBSTITUTE($E16,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -2924,16 +2931,16 @@
       <c r="J17" s="23" t="n"/>
       <c r="K17" s="23" t="n"/>
       <c r="L17" s="23" t="n"/>
-      <c r="M17" s="25" t="n"/>
       <c r="N17" s="25" t="n"/>
       <c r="O17" s="25" t="n"/>
       <c r="P17" s="25" t="n"/>
       <c r="Q17" s="25" t="n"/>
-      <c r="S17">
+      <c r="R17" s="25" t="n"/>
+      <c r="T17">
         <f>IF(COUNTA($A17:$Q17)=0,0,IF(OR($B17="",$D17="",$F17="",$G17=""),1,0))</f>
         <v/>
       </c>
-      <c r="T17">
+      <c r="U17">
         <f>IF(OR(AND($D17&lt;&gt;"",OR(LEN($D17)&lt;&gt;17,LEN($D17)-LEN(SUBSTITUTE($D17,":",""))&lt;&gt;5)),AND($E17&lt;&gt;"",OR(LEN($E17)&lt;&gt;17,LEN($E17)-LEN(SUBSTITUTE($E17,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -2951,16 +2958,16 @@
       <c r="J18" s="23" t="n"/>
       <c r="K18" s="23" t="n"/>
       <c r="L18" s="23" t="n"/>
-      <c r="M18" s="25" t="n"/>
       <c r="N18" s="25" t="n"/>
       <c r="O18" s="25" t="n"/>
       <c r="P18" s="25" t="n"/>
       <c r="Q18" s="25" t="n"/>
-      <c r="S18">
+      <c r="R18" s="25" t="n"/>
+      <c r="T18">
         <f>IF(COUNTA($A18:$Q18)=0,0,IF(OR($B18="",$D18="",$F18="",$G18=""),1,0))</f>
         <v/>
       </c>
-      <c r="T18">
+      <c r="U18">
         <f>IF(OR(AND($D18&lt;&gt;"",OR(LEN($D18)&lt;&gt;17,LEN($D18)-LEN(SUBSTITUTE($D18,":",""))&lt;&gt;5)),AND($E18&lt;&gt;"",OR(LEN($E18)&lt;&gt;17,LEN($E18)-LEN(SUBSTITUTE($E18,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -2978,16 +2985,16 @@
       <c r="J19" s="23" t="n"/>
       <c r="K19" s="23" t="n"/>
       <c r="L19" s="23" t="n"/>
-      <c r="M19" s="25" t="n"/>
       <c r="N19" s="25" t="n"/>
       <c r="O19" s="25" t="n"/>
       <c r="P19" s="25" t="n"/>
       <c r="Q19" s="25" t="n"/>
-      <c r="S19">
+      <c r="R19" s="25" t="n"/>
+      <c r="T19">
         <f>IF(COUNTA($A19:$Q19)=0,0,IF(OR($B19="",$D19="",$F19="",$G19=""),1,0))</f>
         <v/>
       </c>
-      <c r="T19">
+      <c r="U19">
         <f>IF(OR(AND($D19&lt;&gt;"",OR(LEN($D19)&lt;&gt;17,LEN($D19)-LEN(SUBSTITUTE($D19,":",""))&lt;&gt;5)),AND($E19&lt;&gt;"",OR(LEN($E19)&lt;&gt;17,LEN($E19)-LEN(SUBSTITUTE($E19,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3005,16 +3012,16 @@
       <c r="J20" s="23" t="n"/>
       <c r="K20" s="23" t="n"/>
       <c r="L20" s="23" t="n"/>
-      <c r="M20" s="25" t="n"/>
       <c r="N20" s="25" t="n"/>
       <c r="O20" s="25" t="n"/>
       <c r="P20" s="25" t="n"/>
       <c r="Q20" s="25" t="n"/>
-      <c r="S20">
+      <c r="R20" s="25" t="n"/>
+      <c r="T20">
         <f>IF(COUNTA($A20:$Q20)=0,0,IF(OR($B20="",$D20="",$F20="",$G20=""),1,0))</f>
         <v/>
       </c>
-      <c r="T20">
+      <c r="U20">
         <f>IF(OR(AND($D20&lt;&gt;"",OR(LEN($D20)&lt;&gt;17,LEN($D20)-LEN(SUBSTITUTE($D20,":",""))&lt;&gt;5)),AND($E20&lt;&gt;"",OR(LEN($E20)&lt;&gt;17,LEN($E20)-LEN(SUBSTITUTE($E20,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3032,16 +3039,16 @@
       <c r="J21" s="23" t="n"/>
       <c r="K21" s="23" t="n"/>
       <c r="L21" s="23" t="n"/>
-      <c r="M21" s="25" t="n"/>
       <c r="N21" s="25" t="n"/>
       <c r="O21" s="25" t="n"/>
       <c r="P21" s="25" t="n"/>
       <c r="Q21" s="25" t="n"/>
-      <c r="S21">
+      <c r="R21" s="25" t="n"/>
+      <c r="T21">
         <f>IF(COUNTA($A21:$Q21)=0,0,IF(OR($B21="",$D21="",$F21="",$G21=""),1,0))</f>
         <v/>
       </c>
-      <c r="T21">
+      <c r="U21">
         <f>IF(OR(AND($D21&lt;&gt;"",OR(LEN($D21)&lt;&gt;17,LEN($D21)-LEN(SUBSTITUTE($D21,":",""))&lt;&gt;5)),AND($E21&lt;&gt;"",OR(LEN($E21)&lt;&gt;17,LEN($E21)-LEN(SUBSTITUTE($E21,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3059,16 +3066,16 @@
       <c r="J22" s="23" t="n"/>
       <c r="K22" s="23" t="n"/>
       <c r="L22" s="23" t="n"/>
-      <c r="M22" s="25" t="n"/>
       <c r="N22" s="25" t="n"/>
       <c r="O22" s="25" t="n"/>
       <c r="P22" s="25" t="n"/>
       <c r="Q22" s="25" t="n"/>
-      <c r="S22">
+      <c r="R22" s="25" t="n"/>
+      <c r="T22">
         <f>IF(COUNTA($A22:$Q22)=0,0,IF(OR($B22="",$D22="",$F22="",$G22=""),1,0))</f>
         <v/>
       </c>
-      <c r="T22">
+      <c r="U22">
         <f>IF(OR(AND($D22&lt;&gt;"",OR(LEN($D22)&lt;&gt;17,LEN($D22)-LEN(SUBSTITUTE($D22,":",""))&lt;&gt;5)),AND($E22&lt;&gt;"",OR(LEN($E22)&lt;&gt;17,LEN($E22)-LEN(SUBSTITUTE($E22,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3086,16 +3093,16 @@
       <c r="J23" s="23" t="n"/>
       <c r="K23" s="23" t="n"/>
       <c r="L23" s="23" t="n"/>
-      <c r="M23" s="25" t="n"/>
       <c r="N23" s="25" t="n"/>
       <c r="O23" s="25" t="n"/>
       <c r="P23" s="25" t="n"/>
       <c r="Q23" s="25" t="n"/>
-      <c r="S23">
+      <c r="R23" s="25" t="n"/>
+      <c r="T23">
         <f>IF(COUNTA($A23:$Q23)=0,0,IF(OR($B23="",$D23="",$F23="",$G23=""),1,0))</f>
         <v/>
       </c>
-      <c r="T23">
+      <c r="U23">
         <f>IF(OR(AND($D23&lt;&gt;"",OR(LEN($D23)&lt;&gt;17,LEN($D23)-LEN(SUBSTITUTE($D23,":",""))&lt;&gt;5)),AND($E23&lt;&gt;"",OR(LEN($E23)&lt;&gt;17,LEN($E23)-LEN(SUBSTITUTE($E23,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3113,16 +3120,16 @@
       <c r="J24" s="23" t="n"/>
       <c r="K24" s="23" t="n"/>
       <c r="L24" s="23" t="n"/>
-      <c r="M24" s="25" t="n"/>
       <c r="N24" s="25" t="n"/>
       <c r="O24" s="25" t="n"/>
       <c r="P24" s="25" t="n"/>
       <c r="Q24" s="25" t="n"/>
-      <c r="S24">
+      <c r="R24" s="25" t="n"/>
+      <c r="T24">
         <f>IF(COUNTA($A24:$Q24)=0,0,IF(OR($B24="",$D24="",$F24="",$G24=""),1,0))</f>
         <v/>
       </c>
-      <c r="T24">
+      <c r="U24">
         <f>IF(OR(AND($D24&lt;&gt;"",OR(LEN($D24)&lt;&gt;17,LEN($D24)-LEN(SUBSTITUTE($D24,":",""))&lt;&gt;5)),AND($E24&lt;&gt;"",OR(LEN($E24)&lt;&gt;17,LEN($E24)-LEN(SUBSTITUTE($E24,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3140,16 +3147,16 @@
       <c r="J25" s="23" t="n"/>
       <c r="K25" s="23" t="n"/>
       <c r="L25" s="23" t="n"/>
-      <c r="M25" s="25" t="n"/>
       <c r="N25" s="25" t="n"/>
       <c r="O25" s="25" t="n"/>
       <c r="P25" s="25" t="n"/>
       <c r="Q25" s="25" t="n"/>
-      <c r="S25">
+      <c r="R25" s="25" t="n"/>
+      <c r="T25">
         <f>IF(COUNTA($A25:$Q25)=0,0,IF(OR($B25="",$D25="",$F25="",$G25=""),1,0))</f>
         <v/>
       </c>
-      <c r="T25">
+      <c r="U25">
         <f>IF(OR(AND($D25&lt;&gt;"",OR(LEN($D25)&lt;&gt;17,LEN($D25)-LEN(SUBSTITUTE($D25,":",""))&lt;&gt;5)),AND($E25&lt;&gt;"",OR(LEN($E25)&lt;&gt;17,LEN($E25)-LEN(SUBSTITUTE($E25,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3167,16 +3174,16 @@
       <c r="J26" s="23" t="n"/>
       <c r="K26" s="23" t="n"/>
       <c r="L26" s="23" t="n"/>
-      <c r="M26" s="25" t="n"/>
       <c r="N26" s="25" t="n"/>
       <c r="O26" s="25" t="n"/>
       <c r="P26" s="25" t="n"/>
       <c r="Q26" s="25" t="n"/>
-      <c r="S26">
+      <c r="R26" s="25" t="n"/>
+      <c r="T26">
         <f>IF(COUNTA($A26:$Q26)=0,0,IF(OR($B26="",$D26="",$F26="",$G26=""),1,0))</f>
         <v/>
       </c>
-      <c r="T26">
+      <c r="U26">
         <f>IF(OR(AND($D26&lt;&gt;"",OR(LEN($D26)&lt;&gt;17,LEN($D26)-LEN(SUBSTITUTE($D26,":",""))&lt;&gt;5)),AND($E26&lt;&gt;"",OR(LEN($E26)&lt;&gt;17,LEN($E26)-LEN(SUBSTITUTE($E26,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3194,16 +3201,16 @@
       <c r="J27" s="23" t="n"/>
       <c r="K27" s="23" t="n"/>
       <c r="L27" s="23" t="n"/>
-      <c r="M27" s="25" t="n"/>
       <c r="N27" s="25" t="n"/>
       <c r="O27" s="25" t="n"/>
       <c r="P27" s="25" t="n"/>
       <c r="Q27" s="25" t="n"/>
-      <c r="S27">
+      <c r="R27" s="25" t="n"/>
+      <c r="T27">
         <f>IF(COUNTA($A27:$Q27)=0,0,IF(OR($B27="",$D27="",$F27="",$G27=""),1,0))</f>
         <v/>
       </c>
-      <c r="T27">
+      <c r="U27">
         <f>IF(OR(AND($D27&lt;&gt;"",OR(LEN($D27)&lt;&gt;17,LEN($D27)-LEN(SUBSTITUTE($D27,":",""))&lt;&gt;5)),AND($E27&lt;&gt;"",OR(LEN($E27)&lt;&gt;17,LEN($E27)-LEN(SUBSTITUTE($E27,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3221,16 +3228,16 @@
       <c r="J28" s="23" t="n"/>
       <c r="K28" s="23" t="n"/>
       <c r="L28" s="23" t="n"/>
-      <c r="M28" s="25" t="n"/>
       <c r="N28" s="25" t="n"/>
       <c r="O28" s="25" t="n"/>
       <c r="P28" s="25" t="n"/>
       <c r="Q28" s="25" t="n"/>
-      <c r="S28">
+      <c r="R28" s="25" t="n"/>
+      <c r="T28">
         <f>IF(COUNTA($A28:$Q28)=0,0,IF(OR($B28="",$D28="",$F28="",$G28=""),1,0))</f>
         <v/>
       </c>
-      <c r="T28">
+      <c r="U28">
         <f>IF(OR(AND($D28&lt;&gt;"",OR(LEN($D28)&lt;&gt;17,LEN($D28)-LEN(SUBSTITUTE($D28,":",""))&lt;&gt;5)),AND($E28&lt;&gt;"",OR(LEN($E28)&lt;&gt;17,LEN($E28)-LEN(SUBSTITUTE($E28,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3248,16 +3255,16 @@
       <c r="J29" s="23" t="n"/>
       <c r="K29" s="23" t="n"/>
       <c r="L29" s="23" t="n"/>
-      <c r="M29" s="25" t="n"/>
       <c r="N29" s="25" t="n"/>
       <c r="O29" s="25" t="n"/>
       <c r="P29" s="25" t="n"/>
       <c r="Q29" s="25" t="n"/>
-      <c r="S29">
+      <c r="R29" s="25" t="n"/>
+      <c r="T29">
         <f>IF(COUNTA($A29:$Q29)=0,0,IF(OR($B29="",$D29="",$F29="",$G29=""),1,0))</f>
         <v/>
       </c>
-      <c r="T29">
+      <c r="U29">
         <f>IF(OR(AND($D29&lt;&gt;"",OR(LEN($D29)&lt;&gt;17,LEN($D29)-LEN(SUBSTITUTE($D29,":",""))&lt;&gt;5)),AND($E29&lt;&gt;"",OR(LEN($E29)&lt;&gt;17,LEN($E29)-LEN(SUBSTITUTE($E29,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3275,16 +3282,16 @@
       <c r="J30" s="23" t="n"/>
       <c r="K30" s="23" t="n"/>
       <c r="L30" s="23" t="n"/>
-      <c r="M30" s="25" t="n"/>
       <c r="N30" s="25" t="n"/>
       <c r="O30" s="25" t="n"/>
       <c r="P30" s="25" t="n"/>
       <c r="Q30" s="25" t="n"/>
-      <c r="S30">
+      <c r="R30" s="25" t="n"/>
+      <c r="T30">
         <f>IF(COUNTA($A30:$Q30)=0,0,IF(OR($B30="",$D30="",$F30="",$G30=""),1,0))</f>
         <v/>
       </c>
-      <c r="T30">
+      <c r="U30">
         <f>IF(OR(AND($D30&lt;&gt;"",OR(LEN($D30)&lt;&gt;17,LEN($D30)-LEN(SUBSTITUTE($D30,":",""))&lt;&gt;5)),AND($E30&lt;&gt;"",OR(LEN($E30)&lt;&gt;17,LEN($E30)-LEN(SUBSTITUTE($E30,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3302,16 +3309,16 @@
       <c r="J31" s="23" t="n"/>
       <c r="K31" s="23" t="n"/>
       <c r="L31" s="23" t="n"/>
-      <c r="M31" s="25" t="n"/>
       <c r="N31" s="25" t="n"/>
       <c r="O31" s="25" t="n"/>
       <c r="P31" s="25" t="n"/>
       <c r="Q31" s="25" t="n"/>
-      <c r="S31">
+      <c r="R31" s="25" t="n"/>
+      <c r="T31">
         <f>IF(COUNTA($A31:$Q31)=0,0,IF(OR($B31="",$D31="",$F31="",$G31=""),1,0))</f>
         <v/>
       </c>
-      <c r="T31">
+      <c r="U31">
         <f>IF(OR(AND($D31&lt;&gt;"",OR(LEN($D31)&lt;&gt;17,LEN($D31)-LEN(SUBSTITUTE($D31,":",""))&lt;&gt;5)),AND($E31&lt;&gt;"",OR(LEN($E31)&lt;&gt;17,LEN($E31)-LEN(SUBSTITUTE($E31,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3329,16 +3336,16 @@
       <c r="J32" s="23" t="n"/>
       <c r="K32" s="23" t="n"/>
       <c r="L32" s="23" t="n"/>
-      <c r="M32" s="25" t="n"/>
       <c r="N32" s="25" t="n"/>
       <c r="O32" s="25" t="n"/>
       <c r="P32" s="25" t="n"/>
       <c r="Q32" s="25" t="n"/>
-      <c r="S32">
+      <c r="R32" s="25" t="n"/>
+      <c r="T32">
         <f>IF(COUNTA($A32:$Q32)=0,0,IF(OR($B32="",$D32="",$F32="",$G32=""),1,0))</f>
         <v/>
       </c>
-      <c r="T32">
+      <c r="U32">
         <f>IF(OR(AND($D32&lt;&gt;"",OR(LEN($D32)&lt;&gt;17,LEN($D32)-LEN(SUBSTITUTE($D32,":",""))&lt;&gt;5)),AND($E32&lt;&gt;"",OR(LEN($E32)&lt;&gt;17,LEN($E32)-LEN(SUBSTITUTE($E32,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3356,16 +3363,16 @@
       <c r="J33" s="23" t="n"/>
       <c r="K33" s="23" t="n"/>
       <c r="L33" s="23" t="n"/>
-      <c r="M33" s="25" t="n"/>
       <c r="N33" s="25" t="n"/>
       <c r="O33" s="25" t="n"/>
       <c r="P33" s="25" t="n"/>
       <c r="Q33" s="25" t="n"/>
-      <c r="S33">
+      <c r="R33" s="25" t="n"/>
+      <c r="T33">
         <f>IF(COUNTA($A33:$Q33)=0,0,IF(OR($B33="",$D33="",$F33="",$G33=""),1,0))</f>
         <v/>
       </c>
-      <c r="T33">
+      <c r="U33">
         <f>IF(OR(AND($D33&lt;&gt;"",OR(LEN($D33)&lt;&gt;17,LEN($D33)-LEN(SUBSTITUTE($D33,":",""))&lt;&gt;5)),AND($E33&lt;&gt;"",OR(LEN($E33)&lt;&gt;17,LEN($E33)-LEN(SUBSTITUTE($E33,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3383,16 +3390,16 @@
       <c r="J34" s="23" t="n"/>
       <c r="K34" s="23" t="n"/>
       <c r="L34" s="23" t="n"/>
-      <c r="M34" s="25" t="n"/>
       <c r="N34" s="25" t="n"/>
       <c r="O34" s="25" t="n"/>
       <c r="P34" s="25" t="n"/>
       <c r="Q34" s="25" t="n"/>
-      <c r="S34">
+      <c r="R34" s="25" t="n"/>
+      <c r="T34">
         <f>IF(COUNTA($A34:$Q34)=0,0,IF(OR($B34="",$D34="",$F34="",$G34=""),1,0))</f>
         <v/>
       </c>
-      <c r="T34">
+      <c r="U34">
         <f>IF(OR(AND($D34&lt;&gt;"",OR(LEN($D34)&lt;&gt;17,LEN($D34)-LEN(SUBSTITUTE($D34,":",""))&lt;&gt;5)),AND($E34&lt;&gt;"",OR(LEN($E34)&lt;&gt;17,LEN($E34)-LEN(SUBSTITUTE($E34,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3410,16 +3417,16 @@
       <c r="J35" s="23" t="n"/>
       <c r="K35" s="23" t="n"/>
       <c r="L35" s="23" t="n"/>
-      <c r="M35" s="25" t="n"/>
       <c r="N35" s="25" t="n"/>
       <c r="O35" s="25" t="n"/>
       <c r="P35" s="25" t="n"/>
       <c r="Q35" s="25" t="n"/>
-      <c r="S35">
+      <c r="R35" s="25" t="n"/>
+      <c r="T35">
         <f>IF(COUNTA($A35:$Q35)=0,0,IF(OR($B35="",$D35="",$F35="",$G35=""),1,0))</f>
         <v/>
       </c>
-      <c r="T35">
+      <c r="U35">
         <f>IF(OR(AND($D35&lt;&gt;"",OR(LEN($D35)&lt;&gt;17,LEN($D35)-LEN(SUBSTITUTE($D35,":",""))&lt;&gt;5)),AND($E35&lt;&gt;"",OR(LEN($E35)&lt;&gt;17,LEN($E35)-LEN(SUBSTITUTE($E35,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3437,16 +3444,16 @@
       <c r="J36" s="23" t="n"/>
       <c r="K36" s="23" t="n"/>
       <c r="L36" s="23" t="n"/>
-      <c r="M36" s="25" t="n"/>
       <c r="N36" s="25" t="n"/>
       <c r="O36" s="25" t="n"/>
       <c r="P36" s="25" t="n"/>
       <c r="Q36" s="25" t="n"/>
-      <c r="S36">
+      <c r="R36" s="25" t="n"/>
+      <c r="T36">
         <f>IF(COUNTA($A36:$Q36)=0,0,IF(OR($B36="",$D36="",$F36="",$G36=""),1,0))</f>
         <v/>
       </c>
-      <c r="T36">
+      <c r="U36">
         <f>IF(OR(AND($D36&lt;&gt;"",OR(LEN($D36)&lt;&gt;17,LEN($D36)-LEN(SUBSTITUTE($D36,":",""))&lt;&gt;5)),AND($E36&lt;&gt;"",OR(LEN($E36)&lt;&gt;17,LEN($E36)-LEN(SUBSTITUTE($E36,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3464,16 +3471,16 @@
       <c r="J37" s="23" t="n"/>
       <c r="K37" s="23" t="n"/>
       <c r="L37" s="23" t="n"/>
-      <c r="M37" s="25" t="n"/>
       <c r="N37" s="25" t="n"/>
       <c r="O37" s="25" t="n"/>
       <c r="P37" s="25" t="n"/>
       <c r="Q37" s="25" t="n"/>
-      <c r="S37">
+      <c r="R37" s="25" t="n"/>
+      <c r="T37">
         <f>IF(COUNTA($A37:$Q37)=0,0,IF(OR($B37="",$D37="",$F37="",$G37=""),1,0))</f>
         <v/>
       </c>
-      <c r="T37">
+      <c r="U37">
         <f>IF(OR(AND($D37&lt;&gt;"",OR(LEN($D37)&lt;&gt;17,LEN($D37)-LEN(SUBSTITUTE($D37,":",""))&lt;&gt;5)),AND($E37&lt;&gt;"",OR(LEN($E37)&lt;&gt;17,LEN($E37)-LEN(SUBSTITUTE($E37,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3491,16 +3498,16 @@
       <c r="J38" s="23" t="n"/>
       <c r="K38" s="23" t="n"/>
       <c r="L38" s="23" t="n"/>
-      <c r="M38" s="25" t="n"/>
       <c r="N38" s="25" t="n"/>
       <c r="O38" s="25" t="n"/>
       <c r="P38" s="25" t="n"/>
       <c r="Q38" s="25" t="n"/>
-      <c r="S38">
+      <c r="R38" s="25" t="n"/>
+      <c r="T38">
         <f>IF(COUNTA($A38:$Q38)=0,0,IF(OR($B38="",$D38="",$F38="",$G38=""),1,0))</f>
         <v/>
       </c>
-      <c r="T38">
+      <c r="U38">
         <f>IF(OR(AND($D38&lt;&gt;"",OR(LEN($D38)&lt;&gt;17,LEN($D38)-LEN(SUBSTITUTE($D38,":",""))&lt;&gt;5)),AND($E38&lt;&gt;"",OR(LEN($E38)&lt;&gt;17,LEN($E38)-LEN(SUBSTITUTE($E38,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3518,16 +3525,16 @@
       <c r="J39" s="23" t="n"/>
       <c r="K39" s="23" t="n"/>
       <c r="L39" s="23" t="n"/>
-      <c r="M39" s="25" t="n"/>
       <c r="N39" s="25" t="n"/>
       <c r="O39" s="25" t="n"/>
       <c r="P39" s="25" t="n"/>
       <c r="Q39" s="25" t="n"/>
-      <c r="S39">
+      <c r="R39" s="25" t="n"/>
+      <c r="T39">
         <f>IF(COUNTA($A39:$Q39)=0,0,IF(OR($B39="",$D39="",$F39="",$G39=""),1,0))</f>
         <v/>
       </c>
-      <c r="T39">
+      <c r="U39">
         <f>IF(OR(AND($D39&lt;&gt;"",OR(LEN($D39)&lt;&gt;17,LEN($D39)-LEN(SUBSTITUTE($D39,":",""))&lt;&gt;5)),AND($E39&lt;&gt;"",OR(LEN($E39)&lt;&gt;17,LEN($E39)-LEN(SUBSTITUTE($E39,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3545,16 +3552,16 @@
       <c r="J40" s="23" t="n"/>
       <c r="K40" s="23" t="n"/>
       <c r="L40" s="23" t="n"/>
-      <c r="M40" s="25" t="n"/>
       <c r="N40" s="25" t="n"/>
       <c r="O40" s="25" t="n"/>
       <c r="P40" s="25" t="n"/>
       <c r="Q40" s="25" t="n"/>
-      <c r="S40">
+      <c r="R40" s="25" t="n"/>
+      <c r="T40">
         <f>IF(COUNTA($A40:$Q40)=0,0,IF(OR($B40="",$D40="",$F40="",$G40=""),1,0))</f>
         <v/>
       </c>
-      <c r="T40">
+      <c r="U40">
         <f>IF(OR(AND($D40&lt;&gt;"",OR(LEN($D40)&lt;&gt;17,LEN($D40)-LEN(SUBSTITUTE($D40,":",""))&lt;&gt;5)),AND($E40&lt;&gt;"",OR(LEN($E40)&lt;&gt;17,LEN($E40)-LEN(SUBSTITUTE($E40,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3572,16 +3579,16 @@
       <c r="J41" s="23" t="n"/>
       <c r="K41" s="23" t="n"/>
       <c r="L41" s="23" t="n"/>
-      <c r="M41" s="25" t="n"/>
       <c r="N41" s="25" t="n"/>
       <c r="O41" s="25" t="n"/>
       <c r="P41" s="25" t="n"/>
       <c r="Q41" s="25" t="n"/>
-      <c r="S41">
+      <c r="R41" s="25" t="n"/>
+      <c r="T41">
         <f>IF(COUNTA($A41:$Q41)=0,0,IF(OR($B41="",$D41="",$F41="",$G41=""),1,0))</f>
         <v/>
       </c>
-      <c r="T41">
+      <c r="U41">
         <f>IF(OR(AND($D41&lt;&gt;"",OR(LEN($D41)&lt;&gt;17,LEN($D41)-LEN(SUBSTITUTE($D41,":",""))&lt;&gt;5)),AND($E41&lt;&gt;"",OR(LEN($E41)&lt;&gt;17,LEN($E41)-LEN(SUBSTITUTE($E41,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3599,16 +3606,16 @@
       <c r="J42" s="24" t="n"/>
       <c r="K42" s="24" t="n"/>
       <c r="L42" s="24" t="n"/>
-      <c r="M42" s="24" t="n"/>
       <c r="N42" s="24" t="n"/>
       <c r="O42" s="24" t="n"/>
       <c r="P42" s="24" t="n"/>
       <c r="Q42" s="24" t="n"/>
-      <c r="S42">
+      <c r="R42" s="24" t="n"/>
+      <c r="T42">
         <f>IF(COUNTA($A42:$Q42)=0,0,IF(OR($B42="",$D42="",$F42="",$G42=""),1,0))</f>
         <v/>
       </c>
-      <c r="T42">
+      <c r="U42">
         <f>IF(OR(AND($D42&lt;&gt;"",OR(LEN($D42)&lt;&gt;17,LEN($D42)-LEN(SUBSTITUTE($D42,":",""))&lt;&gt;5)),AND($E42&lt;&gt;"",OR(LEN($E42)&lt;&gt;17,LEN($E42)-LEN(SUBSTITUTE($E42,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3626,16 +3633,16 @@
       <c r="J43" s="24" t="n"/>
       <c r="K43" s="24" t="n"/>
       <c r="L43" s="24" t="n"/>
-      <c r="M43" s="24" t="n"/>
       <c r="N43" s="24" t="n"/>
       <c r="O43" s="24" t="n"/>
       <c r="P43" s="24" t="n"/>
       <c r="Q43" s="24" t="n"/>
-      <c r="S43">
+      <c r="R43" s="24" t="n"/>
+      <c r="T43">
         <f>IF(COUNTA($A43:$Q43)=0,0,IF(OR($B43="",$D43="",$F43="",$G43=""),1,0))</f>
         <v/>
       </c>
-      <c r="T43">
+      <c r="U43">
         <f>IF(OR(AND($D43&lt;&gt;"",OR(LEN($D43)&lt;&gt;17,LEN($D43)-LEN(SUBSTITUTE($D43,":",""))&lt;&gt;5)),AND($E43&lt;&gt;"",OR(LEN($E43)&lt;&gt;17,LEN($E43)-LEN(SUBSTITUTE($E43,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3653,16 +3660,16 @@
       <c r="J44" s="24" t="n"/>
       <c r="K44" s="24" t="n"/>
       <c r="L44" s="24" t="n"/>
-      <c r="M44" s="24" t="n"/>
       <c r="N44" s="24" t="n"/>
       <c r="O44" s="24" t="n"/>
       <c r="P44" s="24" t="n"/>
       <c r="Q44" s="24" t="n"/>
-      <c r="S44">
+      <c r="R44" s="24" t="n"/>
+      <c r="T44">
         <f>IF(COUNTA($A44:$Q44)=0,0,IF(OR($B44="",$D44="",$F44="",$G44=""),1,0))</f>
         <v/>
       </c>
-      <c r="T44">
+      <c r="U44">
         <f>IF(OR(AND($D44&lt;&gt;"",OR(LEN($D44)&lt;&gt;17,LEN($D44)-LEN(SUBSTITUTE($D44,":",""))&lt;&gt;5)),AND($E44&lt;&gt;"",OR(LEN($E44)&lt;&gt;17,LEN($E44)-LEN(SUBSTITUTE($E44,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3680,16 +3687,16 @@
       <c r="J45" s="24" t="n"/>
       <c r="K45" s="24" t="n"/>
       <c r="L45" s="24" t="n"/>
-      <c r="M45" s="24" t="n"/>
       <c r="N45" s="24" t="n"/>
       <c r="O45" s="24" t="n"/>
       <c r="P45" s="24" t="n"/>
       <c r="Q45" s="24" t="n"/>
-      <c r="S45">
+      <c r="R45" s="24" t="n"/>
+      <c r="T45">
         <f>IF(COUNTA($A45:$Q45)=0,0,IF(OR($B45="",$D45="",$F45="",$G45=""),1,0))</f>
         <v/>
       </c>
-      <c r="T45">
+      <c r="U45">
         <f>IF(OR(AND($D45&lt;&gt;"",OR(LEN($D45)&lt;&gt;17,LEN($D45)-LEN(SUBSTITUTE($D45,":",""))&lt;&gt;5)),AND($E45&lt;&gt;"",OR(LEN($E45)&lt;&gt;17,LEN($E45)-LEN(SUBSTITUTE($E45,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3707,16 +3714,16 @@
       <c r="J46" s="24" t="n"/>
       <c r="K46" s="24" t="n"/>
       <c r="L46" s="24" t="n"/>
-      <c r="M46" s="24" t="n"/>
       <c r="N46" s="24" t="n"/>
       <c r="O46" s="24" t="n"/>
       <c r="P46" s="24" t="n"/>
       <c r="Q46" s="24" t="n"/>
-      <c r="S46">
+      <c r="R46" s="24" t="n"/>
+      <c r="T46">
         <f>IF(COUNTA($A46:$Q46)=0,0,IF(OR($B46="",$D46="",$F46="",$G46=""),1,0))</f>
         <v/>
       </c>
-      <c r="T46">
+      <c r="U46">
         <f>IF(OR(AND($D46&lt;&gt;"",OR(LEN($D46)&lt;&gt;17,LEN($D46)-LEN(SUBSTITUTE($D46,":",""))&lt;&gt;5)),AND($E46&lt;&gt;"",OR(LEN($E46)&lt;&gt;17,LEN($E46)-LEN(SUBSTITUTE($E46,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3734,16 +3741,16 @@
       <c r="J47" s="24" t="n"/>
       <c r="K47" s="24" t="n"/>
       <c r="L47" s="24" t="n"/>
-      <c r="M47" s="24" t="n"/>
       <c r="N47" s="24" t="n"/>
       <c r="O47" s="24" t="n"/>
       <c r="P47" s="24" t="n"/>
       <c r="Q47" s="24" t="n"/>
-      <c r="S47">
+      <c r="R47" s="24" t="n"/>
+      <c r="T47">
         <f>IF(COUNTA($A47:$Q47)=0,0,IF(OR($B47="",$D47="",$F47="",$G47=""),1,0))</f>
         <v/>
       </c>
-      <c r="T47">
+      <c r="U47">
         <f>IF(OR(AND($D47&lt;&gt;"",OR(LEN($D47)&lt;&gt;17,LEN($D47)-LEN(SUBSTITUTE($D47,":",""))&lt;&gt;5)),AND($E47&lt;&gt;"",OR(LEN($E47)&lt;&gt;17,LEN($E47)-LEN(SUBSTITUTE($E47,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3761,16 +3768,16 @@
       <c r="J48" s="24" t="n"/>
       <c r="K48" s="24" t="n"/>
       <c r="L48" s="24" t="n"/>
-      <c r="M48" s="24" t="n"/>
       <c r="N48" s="24" t="n"/>
       <c r="O48" s="24" t="n"/>
       <c r="P48" s="24" t="n"/>
       <c r="Q48" s="24" t="n"/>
-      <c r="S48">
+      <c r="R48" s="24" t="n"/>
+      <c r="T48">
         <f>IF(COUNTA($A48:$Q48)=0,0,IF(OR($B48="",$D48="",$F48="",$G48=""),1,0))</f>
         <v/>
       </c>
-      <c r="T48">
+      <c r="U48">
         <f>IF(OR(AND($D48&lt;&gt;"",OR(LEN($D48)&lt;&gt;17,LEN($D48)-LEN(SUBSTITUTE($D48,":",""))&lt;&gt;5)),AND($E48&lt;&gt;"",OR(LEN($E48)&lt;&gt;17,LEN($E48)-LEN(SUBSTITUTE($E48,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3788,16 +3795,16 @@
       <c r="J49" s="24" t="n"/>
       <c r="K49" s="24" t="n"/>
       <c r="L49" s="24" t="n"/>
-      <c r="M49" s="24" t="n"/>
       <c r="N49" s="24" t="n"/>
       <c r="O49" s="24" t="n"/>
       <c r="P49" s="24" t="n"/>
       <c r="Q49" s="24" t="n"/>
-      <c r="S49">
+      <c r="R49" s="24" t="n"/>
+      <c r="T49">
         <f>IF(COUNTA($A49:$Q49)=0,0,IF(OR($B49="",$D49="",$F49="",$G49=""),1,0))</f>
         <v/>
       </c>
-      <c r="T49">
+      <c r="U49">
         <f>IF(OR(AND($D49&lt;&gt;"",OR(LEN($D49)&lt;&gt;17,LEN($D49)-LEN(SUBSTITUTE($D49,":",""))&lt;&gt;5)),AND($E49&lt;&gt;"",OR(LEN($E49)&lt;&gt;17,LEN($E49)-LEN(SUBSTITUTE($E49,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3815,16 +3822,16 @@
       <c r="J50" s="24" t="n"/>
       <c r="K50" s="24" t="n"/>
       <c r="L50" s="24" t="n"/>
-      <c r="M50" s="24" t="n"/>
       <c r="N50" s="24" t="n"/>
       <c r="O50" s="24" t="n"/>
       <c r="P50" s="24" t="n"/>
       <c r="Q50" s="24" t="n"/>
-      <c r="S50">
+      <c r="R50" s="24" t="n"/>
+      <c r="T50">
         <f>IF(COUNTA($A50:$Q50)=0,0,IF(OR($B50="",$D50="",$F50="",$G50=""),1,0))</f>
         <v/>
       </c>
-      <c r="T50">
+      <c r="U50">
         <f>IF(OR(AND($D50&lt;&gt;"",OR(LEN($D50)&lt;&gt;17,LEN($D50)-LEN(SUBSTITUTE($D50,":",""))&lt;&gt;5)),AND($E50&lt;&gt;"",OR(LEN($E50)&lt;&gt;17,LEN($E50)-LEN(SUBSTITUTE($E50,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3842,16 +3849,16 @@
       <c r="J51" s="24" t="n"/>
       <c r="K51" s="24" t="n"/>
       <c r="L51" s="24" t="n"/>
-      <c r="M51" s="24" t="n"/>
       <c r="N51" s="24" t="n"/>
       <c r="O51" s="24" t="n"/>
       <c r="P51" s="24" t="n"/>
       <c r="Q51" s="24" t="n"/>
-      <c r="S51">
+      <c r="R51" s="24" t="n"/>
+      <c r="T51">
         <f>IF(COUNTA($A51:$Q51)=0,0,IF(OR($B51="",$D51="",$F51="",$G51=""),1,0))</f>
         <v/>
       </c>
-      <c r="T51">
+      <c r="U51">
         <f>IF(OR(AND($D51&lt;&gt;"",OR(LEN($D51)&lt;&gt;17,LEN($D51)-LEN(SUBSTITUTE($D51,":",""))&lt;&gt;5)),AND($E51&lt;&gt;"",OR(LEN($E51)&lt;&gt;17,LEN($E51)-LEN(SUBSTITUTE($E51,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3869,16 +3876,16 @@
       <c r="J52" s="24" t="n"/>
       <c r="K52" s="24" t="n"/>
       <c r="L52" s="24" t="n"/>
-      <c r="M52" s="24" t="n"/>
       <c r="N52" s="24" t="n"/>
       <c r="O52" s="24" t="n"/>
       <c r="P52" s="24" t="n"/>
       <c r="Q52" s="24" t="n"/>
-      <c r="S52">
+      <c r="R52" s="24" t="n"/>
+      <c r="T52">
         <f>IF(COUNTA($A52:$Q52)=0,0,IF(OR($B52="",$D52="",$F52="",$G52=""),1,0))</f>
         <v/>
       </c>
-      <c r="T52">
+      <c r="U52">
         <f>IF(OR(AND($D52&lt;&gt;"",OR(LEN($D52)&lt;&gt;17,LEN($D52)-LEN(SUBSTITUTE($D52,":",""))&lt;&gt;5)),AND($E52&lt;&gt;"",OR(LEN($E52)&lt;&gt;17,LEN($E52)-LEN(SUBSTITUTE($E52,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3896,16 +3903,16 @@
       <c r="J53" s="24" t="n"/>
       <c r="K53" s="24" t="n"/>
       <c r="L53" s="24" t="n"/>
-      <c r="M53" s="24" t="n"/>
       <c r="N53" s="24" t="n"/>
       <c r="O53" s="24" t="n"/>
       <c r="P53" s="24" t="n"/>
       <c r="Q53" s="24" t="n"/>
-      <c r="S53">
+      <c r="R53" s="24" t="n"/>
+      <c r="T53">
         <f>IF(COUNTA($A53:$Q53)=0,0,IF(OR($B53="",$D53="",$F53="",$G53=""),1,0))</f>
         <v/>
       </c>
-      <c r="T53">
+      <c r="U53">
         <f>IF(OR(AND($D53&lt;&gt;"",OR(LEN($D53)&lt;&gt;17,LEN($D53)-LEN(SUBSTITUTE($D53,":",""))&lt;&gt;5)),AND($E53&lt;&gt;"",OR(LEN($E53)&lt;&gt;17,LEN($E53)-LEN(SUBSTITUTE($E53,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3923,16 +3930,16 @@
       <c r="J54" s="24" t="n"/>
       <c r="K54" s="24" t="n"/>
       <c r="L54" s="24" t="n"/>
-      <c r="M54" s="24" t="n"/>
       <c r="N54" s="24" t="n"/>
       <c r="O54" s="24" t="n"/>
       <c r="P54" s="24" t="n"/>
       <c r="Q54" s="24" t="n"/>
-      <c r="S54">
+      <c r="R54" s="24" t="n"/>
+      <c r="T54">
         <f>IF(COUNTA($A54:$Q54)=0,0,IF(OR($B54="",$D54="",$F54="",$G54=""),1,0))</f>
         <v/>
       </c>
-      <c r="T54">
+      <c r="U54">
         <f>IF(OR(AND($D54&lt;&gt;"",OR(LEN($D54)&lt;&gt;17,LEN($D54)-LEN(SUBSTITUTE($D54,":",""))&lt;&gt;5)),AND($E54&lt;&gt;"",OR(LEN($E54)&lt;&gt;17,LEN($E54)-LEN(SUBSTITUTE($E54,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3950,16 +3957,16 @@
       <c r="J55" s="24" t="n"/>
       <c r="K55" s="24" t="n"/>
       <c r="L55" s="24" t="n"/>
-      <c r="M55" s="24" t="n"/>
       <c r="N55" s="24" t="n"/>
       <c r="O55" s="24" t="n"/>
       <c r="P55" s="24" t="n"/>
       <c r="Q55" s="24" t="n"/>
-      <c r="S55">
+      <c r="R55" s="24" t="n"/>
+      <c r="T55">
         <f>IF(COUNTA($A55:$Q55)=0,0,IF(OR($B55="",$D55="",$F55="",$G55=""),1,0))</f>
         <v/>
       </c>
-      <c r="T55">
+      <c r="U55">
         <f>IF(OR(AND($D55&lt;&gt;"",OR(LEN($D55)&lt;&gt;17,LEN($D55)-LEN(SUBSTITUTE($D55,":",""))&lt;&gt;5)),AND($E55&lt;&gt;"",OR(LEN($E55)&lt;&gt;17,LEN($E55)-LEN(SUBSTITUTE($E55,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -3977,16 +3984,16 @@
       <c r="J56" s="24" t="n"/>
       <c r="K56" s="24" t="n"/>
       <c r="L56" s="24" t="n"/>
-      <c r="M56" s="24" t="n"/>
       <c r="N56" s="24" t="n"/>
       <c r="O56" s="24" t="n"/>
       <c r="P56" s="24" t="n"/>
       <c r="Q56" s="24" t="n"/>
-      <c r="S56">
+      <c r="R56" s="24" t="n"/>
+      <c r="T56">
         <f>IF(COUNTA($A56:$Q56)=0,0,IF(OR($B56="",$D56="",$F56="",$G56=""),1,0))</f>
         <v/>
       </c>
-      <c r="T56">
+      <c r="U56">
         <f>IF(OR(AND($D56&lt;&gt;"",OR(LEN($D56)&lt;&gt;17,LEN($D56)-LEN(SUBSTITUTE($D56,":",""))&lt;&gt;5)),AND($E56&lt;&gt;"",OR(LEN($E56)&lt;&gt;17,LEN($E56)-LEN(SUBSTITUTE($E56,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4004,16 +4011,16 @@
       <c r="J57" s="24" t="n"/>
       <c r="K57" s="24" t="n"/>
       <c r="L57" s="24" t="n"/>
-      <c r="M57" s="24" t="n"/>
       <c r="N57" s="24" t="n"/>
       <c r="O57" s="24" t="n"/>
       <c r="P57" s="24" t="n"/>
       <c r="Q57" s="24" t="n"/>
-      <c r="S57">
+      <c r="R57" s="24" t="n"/>
+      <c r="T57">
         <f>IF(COUNTA($A57:$Q57)=0,0,IF(OR($B57="",$D57="",$F57="",$G57=""),1,0))</f>
         <v/>
       </c>
-      <c r="T57">
+      <c r="U57">
         <f>IF(OR(AND($D57&lt;&gt;"",OR(LEN($D57)&lt;&gt;17,LEN($D57)-LEN(SUBSTITUTE($D57,":",""))&lt;&gt;5)),AND($E57&lt;&gt;"",OR(LEN($E57)&lt;&gt;17,LEN($E57)-LEN(SUBSTITUTE($E57,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4031,16 +4038,16 @@
       <c r="J58" s="24" t="n"/>
       <c r="K58" s="24" t="n"/>
       <c r="L58" s="24" t="n"/>
-      <c r="M58" s="24" t="n"/>
       <c r="N58" s="24" t="n"/>
       <c r="O58" s="24" t="n"/>
       <c r="P58" s="24" t="n"/>
       <c r="Q58" s="24" t="n"/>
-      <c r="S58">
+      <c r="R58" s="24" t="n"/>
+      <c r="T58">
         <f>IF(COUNTA($A58:$Q58)=0,0,IF(OR($B58="",$D58="",$F58="",$G58=""),1,0))</f>
         <v/>
       </c>
-      <c r="T58">
+      <c r="U58">
         <f>IF(OR(AND($D58&lt;&gt;"",OR(LEN($D58)&lt;&gt;17,LEN($D58)-LEN(SUBSTITUTE($D58,":",""))&lt;&gt;5)),AND($E58&lt;&gt;"",OR(LEN($E58)&lt;&gt;17,LEN($E58)-LEN(SUBSTITUTE($E58,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4058,16 +4065,16 @@
       <c r="J59" s="24" t="n"/>
       <c r="K59" s="24" t="n"/>
       <c r="L59" s="24" t="n"/>
-      <c r="M59" s="24" t="n"/>
       <c r="N59" s="24" t="n"/>
       <c r="O59" s="24" t="n"/>
       <c r="P59" s="24" t="n"/>
       <c r="Q59" s="24" t="n"/>
-      <c r="S59">
+      <c r="R59" s="24" t="n"/>
+      <c r="T59">
         <f>IF(COUNTA($A59:$Q59)=0,0,IF(OR($B59="",$D59="",$F59="",$G59=""),1,0))</f>
         <v/>
       </c>
-      <c r="T59">
+      <c r="U59">
         <f>IF(OR(AND($D59&lt;&gt;"",OR(LEN($D59)&lt;&gt;17,LEN($D59)-LEN(SUBSTITUTE($D59,":",""))&lt;&gt;5)),AND($E59&lt;&gt;"",OR(LEN($E59)&lt;&gt;17,LEN($E59)-LEN(SUBSTITUTE($E59,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4085,16 +4092,16 @@
       <c r="J60" s="24" t="n"/>
       <c r="K60" s="24" t="n"/>
       <c r="L60" s="24" t="n"/>
-      <c r="M60" s="24" t="n"/>
       <c r="N60" s="24" t="n"/>
       <c r="O60" s="24" t="n"/>
       <c r="P60" s="24" t="n"/>
       <c r="Q60" s="24" t="n"/>
-      <c r="S60">
+      <c r="R60" s="24" t="n"/>
+      <c r="T60">
         <f>IF(COUNTA($A60:$Q60)=0,0,IF(OR($B60="",$D60="",$F60="",$G60=""),1,0))</f>
         <v/>
       </c>
-      <c r="T60">
+      <c r="U60">
         <f>IF(OR(AND($D60&lt;&gt;"",OR(LEN($D60)&lt;&gt;17,LEN($D60)-LEN(SUBSTITUTE($D60,":",""))&lt;&gt;5)),AND($E60&lt;&gt;"",OR(LEN($E60)&lt;&gt;17,LEN($E60)-LEN(SUBSTITUTE($E60,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4112,16 +4119,16 @@
       <c r="J61" s="24" t="n"/>
       <c r="K61" s="24" t="n"/>
       <c r="L61" s="24" t="n"/>
-      <c r="M61" s="24" t="n"/>
       <c r="N61" s="24" t="n"/>
       <c r="O61" s="24" t="n"/>
       <c r="P61" s="24" t="n"/>
       <c r="Q61" s="24" t="n"/>
-      <c r="S61">
+      <c r="R61" s="24" t="n"/>
+      <c r="T61">
         <f>IF(COUNTA($A61:$Q61)=0,0,IF(OR($B61="",$D61="",$F61="",$G61=""),1,0))</f>
         <v/>
       </c>
-      <c r="T61">
+      <c r="U61">
         <f>IF(OR(AND($D61&lt;&gt;"",OR(LEN($D61)&lt;&gt;17,LEN($D61)-LEN(SUBSTITUTE($D61,":",""))&lt;&gt;5)),AND($E61&lt;&gt;"",OR(LEN($E61)&lt;&gt;17,LEN($E61)-LEN(SUBSTITUTE($E61,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4139,16 +4146,16 @@
       <c r="J62" s="24" t="n"/>
       <c r="K62" s="24" t="n"/>
       <c r="L62" s="24" t="n"/>
-      <c r="M62" s="24" t="n"/>
       <c r="N62" s="24" t="n"/>
       <c r="O62" s="24" t="n"/>
       <c r="P62" s="24" t="n"/>
       <c r="Q62" s="24" t="n"/>
-      <c r="S62">
+      <c r="R62" s="24" t="n"/>
+      <c r="T62">
         <f>IF(COUNTA($A62:$Q62)=0,0,IF(OR($B62="",$D62="",$F62="",$G62=""),1,0))</f>
         <v/>
       </c>
-      <c r="T62">
+      <c r="U62">
         <f>IF(OR(AND($D62&lt;&gt;"",OR(LEN($D62)&lt;&gt;17,LEN($D62)-LEN(SUBSTITUTE($D62,":",""))&lt;&gt;5)),AND($E62&lt;&gt;"",OR(LEN($E62)&lt;&gt;17,LEN($E62)-LEN(SUBSTITUTE($E62,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4166,16 +4173,16 @@
       <c r="J63" s="24" t="n"/>
       <c r="K63" s="24" t="n"/>
       <c r="L63" s="24" t="n"/>
-      <c r="M63" s="24" t="n"/>
       <c r="N63" s="24" t="n"/>
       <c r="O63" s="24" t="n"/>
       <c r="P63" s="24" t="n"/>
       <c r="Q63" s="24" t="n"/>
-      <c r="S63">
+      <c r="R63" s="24" t="n"/>
+      <c r="T63">
         <f>IF(COUNTA($A63:$Q63)=0,0,IF(OR($B63="",$D63="",$F63="",$G63=""),1,0))</f>
         <v/>
       </c>
-      <c r="T63">
+      <c r="U63">
         <f>IF(OR(AND($D63&lt;&gt;"",OR(LEN($D63)&lt;&gt;17,LEN($D63)-LEN(SUBSTITUTE($D63,":",""))&lt;&gt;5)),AND($E63&lt;&gt;"",OR(LEN($E63)&lt;&gt;17,LEN($E63)-LEN(SUBSTITUTE($E63,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4193,16 +4200,16 @@
       <c r="J64" s="24" t="n"/>
       <c r="K64" s="24" t="n"/>
       <c r="L64" s="24" t="n"/>
-      <c r="M64" s="24" t="n"/>
       <c r="N64" s="24" t="n"/>
       <c r="O64" s="24" t="n"/>
       <c r="P64" s="24" t="n"/>
       <c r="Q64" s="24" t="n"/>
-      <c r="S64">
+      <c r="R64" s="24" t="n"/>
+      <c r="T64">
         <f>IF(COUNTA($A64:$Q64)=0,0,IF(OR($B64="",$D64="",$F64="",$G64=""),1,0))</f>
         <v/>
       </c>
-      <c r="T64">
+      <c r="U64">
         <f>IF(OR(AND($D64&lt;&gt;"",OR(LEN($D64)&lt;&gt;17,LEN($D64)-LEN(SUBSTITUTE($D64,":",""))&lt;&gt;5)),AND($E64&lt;&gt;"",OR(LEN($E64)&lt;&gt;17,LEN($E64)-LEN(SUBSTITUTE($E64,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4220,16 +4227,16 @@
       <c r="J65" s="24" t="n"/>
       <c r="K65" s="24" t="n"/>
       <c r="L65" s="24" t="n"/>
-      <c r="M65" s="24" t="n"/>
       <c r="N65" s="24" t="n"/>
       <c r="O65" s="24" t="n"/>
       <c r="P65" s="24" t="n"/>
       <c r="Q65" s="24" t="n"/>
-      <c r="S65">
+      <c r="R65" s="24" t="n"/>
+      <c r="T65">
         <f>IF(COUNTA($A65:$Q65)=0,0,IF(OR($B65="",$D65="",$F65="",$G65=""),1,0))</f>
         <v/>
       </c>
-      <c r="T65">
+      <c r="U65">
         <f>IF(OR(AND($D65&lt;&gt;"",OR(LEN($D65)&lt;&gt;17,LEN($D65)-LEN(SUBSTITUTE($D65,":",""))&lt;&gt;5)),AND($E65&lt;&gt;"",OR(LEN($E65)&lt;&gt;17,LEN($E65)-LEN(SUBSTITUTE($E65,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4247,16 +4254,16 @@
       <c r="J66" s="24" t="n"/>
       <c r="K66" s="24" t="n"/>
       <c r="L66" s="24" t="n"/>
-      <c r="M66" s="24" t="n"/>
       <c r="N66" s="24" t="n"/>
       <c r="O66" s="24" t="n"/>
       <c r="P66" s="24" t="n"/>
       <c r="Q66" s="24" t="n"/>
-      <c r="S66">
+      <c r="R66" s="24" t="n"/>
+      <c r="T66">
         <f>IF(COUNTA($A66:$Q66)=0,0,IF(OR($B66="",$D66="",$F66="",$G66=""),1,0))</f>
         <v/>
       </c>
-      <c r="T66">
+      <c r="U66">
         <f>IF(OR(AND($D66&lt;&gt;"",OR(LEN($D66)&lt;&gt;17,LEN($D66)-LEN(SUBSTITUTE($D66,":",""))&lt;&gt;5)),AND($E66&lt;&gt;"",OR(LEN($E66)&lt;&gt;17,LEN($E66)-LEN(SUBSTITUTE($E66,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4274,16 +4281,16 @@
       <c r="J67" s="24" t="n"/>
       <c r="K67" s="24" t="n"/>
       <c r="L67" s="24" t="n"/>
-      <c r="M67" s="24" t="n"/>
       <c r="N67" s="24" t="n"/>
       <c r="O67" s="24" t="n"/>
       <c r="P67" s="24" t="n"/>
       <c r="Q67" s="24" t="n"/>
-      <c r="S67">
+      <c r="R67" s="24" t="n"/>
+      <c r="T67">
         <f>IF(COUNTA($A67:$Q67)=0,0,IF(OR($B67="",$D67="",$F67="",$G67=""),1,0))</f>
         <v/>
       </c>
-      <c r="T67">
+      <c r="U67">
         <f>IF(OR(AND($D67&lt;&gt;"",OR(LEN($D67)&lt;&gt;17,LEN($D67)-LEN(SUBSTITUTE($D67,":",""))&lt;&gt;5)),AND($E67&lt;&gt;"",OR(LEN($E67)&lt;&gt;17,LEN($E67)-LEN(SUBSTITUTE($E67,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4301,16 +4308,16 @@
       <c r="J68" s="24" t="n"/>
       <c r="K68" s="24" t="n"/>
       <c r="L68" s="24" t="n"/>
-      <c r="M68" s="24" t="n"/>
       <c r="N68" s="24" t="n"/>
       <c r="O68" s="24" t="n"/>
       <c r="P68" s="24" t="n"/>
       <c r="Q68" s="24" t="n"/>
-      <c r="S68">
+      <c r="R68" s="24" t="n"/>
+      <c r="T68">
         <f>IF(COUNTA($A68:$Q68)=0,0,IF(OR($B68="",$D68="",$F68="",$G68=""),1,0))</f>
         <v/>
       </c>
-      <c r="T68">
+      <c r="U68">
         <f>IF(OR(AND($D68&lt;&gt;"",OR(LEN($D68)&lt;&gt;17,LEN($D68)-LEN(SUBSTITUTE($D68,":",""))&lt;&gt;5)),AND($E68&lt;&gt;"",OR(LEN($E68)&lt;&gt;17,LEN($E68)-LEN(SUBSTITUTE($E68,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4328,16 +4335,16 @@
       <c r="J69" s="24" t="n"/>
       <c r="K69" s="24" t="n"/>
       <c r="L69" s="24" t="n"/>
-      <c r="M69" s="24" t="n"/>
       <c r="N69" s="24" t="n"/>
       <c r="O69" s="24" t="n"/>
       <c r="P69" s="24" t="n"/>
       <c r="Q69" s="24" t="n"/>
-      <c r="S69">
+      <c r="R69" s="24" t="n"/>
+      <c r="T69">
         <f>IF(COUNTA($A69:$Q69)=0,0,IF(OR($B69="",$D69="",$F69="",$G69=""),1,0))</f>
         <v/>
       </c>
-      <c r="T69">
+      <c r="U69">
         <f>IF(OR(AND($D69&lt;&gt;"",OR(LEN($D69)&lt;&gt;17,LEN($D69)-LEN(SUBSTITUTE($D69,":",""))&lt;&gt;5)),AND($E69&lt;&gt;"",OR(LEN($E69)&lt;&gt;17,LEN($E69)-LEN(SUBSTITUTE($E69,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4355,16 +4362,16 @@
       <c r="J70" s="24" t="n"/>
       <c r="K70" s="24" t="n"/>
       <c r="L70" s="24" t="n"/>
-      <c r="M70" s="24" t="n"/>
       <c r="N70" s="24" t="n"/>
       <c r="O70" s="24" t="n"/>
       <c r="P70" s="24" t="n"/>
       <c r="Q70" s="24" t="n"/>
-      <c r="S70">
+      <c r="R70" s="24" t="n"/>
+      <c r="T70">
         <f>IF(COUNTA($A70:$Q70)=0,0,IF(OR($B70="",$D70="",$F70="",$G70=""),1,0))</f>
         <v/>
       </c>
-      <c r="T70">
+      <c r="U70">
         <f>IF(OR(AND($D70&lt;&gt;"",OR(LEN($D70)&lt;&gt;17,LEN($D70)-LEN(SUBSTITUTE($D70,":",""))&lt;&gt;5)),AND($E70&lt;&gt;"",OR(LEN($E70)&lt;&gt;17,LEN($E70)-LEN(SUBSTITUTE($E70,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4382,16 +4389,16 @@
       <c r="J71" s="24" t="n"/>
       <c r="K71" s="24" t="n"/>
       <c r="L71" s="24" t="n"/>
-      <c r="M71" s="24" t="n"/>
       <c r="N71" s="24" t="n"/>
       <c r="O71" s="24" t="n"/>
       <c r="P71" s="24" t="n"/>
       <c r="Q71" s="24" t="n"/>
-      <c r="S71">
+      <c r="R71" s="24" t="n"/>
+      <c r="T71">
         <f>IF(COUNTA($A71:$Q71)=0,0,IF(OR($B71="",$D71="",$F71="",$G71=""),1,0))</f>
         <v/>
       </c>
-      <c r="T71">
+      <c r="U71">
         <f>IF(OR(AND($D71&lt;&gt;"",OR(LEN($D71)&lt;&gt;17,LEN($D71)-LEN(SUBSTITUTE($D71,":",""))&lt;&gt;5)),AND($E71&lt;&gt;"",OR(LEN($E71)&lt;&gt;17,LEN($E71)-LEN(SUBSTITUTE($E71,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4409,16 +4416,16 @@
       <c r="J72" s="24" t="n"/>
       <c r="K72" s="24" t="n"/>
       <c r="L72" s="24" t="n"/>
-      <c r="M72" s="24" t="n"/>
       <c r="N72" s="24" t="n"/>
       <c r="O72" s="24" t="n"/>
       <c r="P72" s="24" t="n"/>
       <c r="Q72" s="24" t="n"/>
-      <c r="S72">
+      <c r="R72" s="24" t="n"/>
+      <c r="T72">
         <f>IF(COUNTA($A72:$Q72)=0,0,IF(OR($B72="",$D72="",$F72="",$G72=""),1,0))</f>
         <v/>
       </c>
-      <c r="T72">
+      <c r="U72">
         <f>IF(OR(AND($D72&lt;&gt;"",OR(LEN($D72)&lt;&gt;17,LEN($D72)-LEN(SUBSTITUTE($D72,":",""))&lt;&gt;5)),AND($E72&lt;&gt;"",OR(LEN($E72)&lt;&gt;17,LEN($E72)-LEN(SUBSTITUTE($E72,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4436,16 +4443,16 @@
       <c r="J73" s="24" t="n"/>
       <c r="K73" s="24" t="n"/>
       <c r="L73" s="24" t="n"/>
-      <c r="M73" s="24" t="n"/>
       <c r="N73" s="24" t="n"/>
       <c r="O73" s="24" t="n"/>
       <c r="P73" s="24" t="n"/>
       <c r="Q73" s="24" t="n"/>
-      <c r="S73">
+      <c r="R73" s="24" t="n"/>
+      <c r="T73">
         <f>IF(COUNTA($A73:$Q73)=0,0,IF(OR($B73="",$D73="",$F73="",$G73=""),1,0))</f>
         <v/>
       </c>
-      <c r="T73">
+      <c r="U73">
         <f>IF(OR(AND($D73&lt;&gt;"",OR(LEN($D73)&lt;&gt;17,LEN($D73)-LEN(SUBSTITUTE($D73,":",""))&lt;&gt;5)),AND($E73&lt;&gt;"",OR(LEN($E73)&lt;&gt;17,LEN($E73)-LEN(SUBSTITUTE($E73,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4463,16 +4470,16 @@
       <c r="J74" s="24" t="n"/>
       <c r="K74" s="24" t="n"/>
       <c r="L74" s="24" t="n"/>
-      <c r="M74" s="24" t="n"/>
       <c r="N74" s="24" t="n"/>
       <c r="O74" s="24" t="n"/>
       <c r="P74" s="24" t="n"/>
       <c r="Q74" s="24" t="n"/>
-      <c r="S74">
+      <c r="R74" s="24" t="n"/>
+      <c r="T74">
         <f>IF(COUNTA($A74:$Q74)=0,0,IF(OR($B74="",$D74="",$F74="",$G74=""),1,0))</f>
         <v/>
       </c>
-      <c r="T74">
+      <c r="U74">
         <f>IF(OR(AND($D74&lt;&gt;"",OR(LEN($D74)&lt;&gt;17,LEN($D74)-LEN(SUBSTITUTE($D74,":",""))&lt;&gt;5)),AND($E74&lt;&gt;"",OR(LEN($E74)&lt;&gt;17,LEN($E74)-LEN(SUBSTITUTE($E74,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4490,16 +4497,16 @@
       <c r="J75" s="24" t="n"/>
       <c r="K75" s="24" t="n"/>
       <c r="L75" s="24" t="n"/>
-      <c r="M75" s="24" t="n"/>
       <c r="N75" s="24" t="n"/>
       <c r="O75" s="24" t="n"/>
       <c r="P75" s="24" t="n"/>
       <c r="Q75" s="24" t="n"/>
-      <c r="S75">
+      <c r="R75" s="24" t="n"/>
+      <c r="T75">
         <f>IF(COUNTA($A75:$Q75)=0,0,IF(OR($B75="",$D75="",$F75="",$G75=""),1,0))</f>
         <v/>
       </c>
-      <c r="T75">
+      <c r="U75">
         <f>IF(OR(AND($D75&lt;&gt;"",OR(LEN($D75)&lt;&gt;17,LEN($D75)-LEN(SUBSTITUTE($D75,":",""))&lt;&gt;5)),AND($E75&lt;&gt;"",OR(LEN($E75)&lt;&gt;17,LEN($E75)-LEN(SUBSTITUTE($E75,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4517,16 +4524,16 @@
       <c r="J76" s="24" t="n"/>
       <c r="K76" s="24" t="n"/>
       <c r="L76" s="24" t="n"/>
-      <c r="M76" s="24" t="n"/>
       <c r="N76" s="24" t="n"/>
       <c r="O76" s="24" t="n"/>
       <c r="P76" s="24" t="n"/>
       <c r="Q76" s="24" t="n"/>
-      <c r="S76">
+      <c r="R76" s="24" t="n"/>
+      <c r="T76">
         <f>IF(COUNTA($A76:$Q76)=0,0,IF(OR($B76="",$D76="",$F76="",$G76=""),1,0))</f>
         <v/>
       </c>
-      <c r="T76">
+      <c r="U76">
         <f>IF(OR(AND($D76&lt;&gt;"",OR(LEN($D76)&lt;&gt;17,LEN($D76)-LEN(SUBSTITUTE($D76,":",""))&lt;&gt;5)),AND($E76&lt;&gt;"",OR(LEN($E76)&lt;&gt;17,LEN($E76)-LEN(SUBSTITUTE($E76,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4544,16 +4551,16 @@
       <c r="J77" s="24" t="n"/>
       <c r="K77" s="24" t="n"/>
       <c r="L77" s="24" t="n"/>
-      <c r="M77" s="24" t="n"/>
       <c r="N77" s="24" t="n"/>
       <c r="O77" s="24" t="n"/>
       <c r="P77" s="24" t="n"/>
       <c r="Q77" s="24" t="n"/>
-      <c r="S77">
+      <c r="R77" s="24" t="n"/>
+      <c r="T77">
         <f>IF(COUNTA($A77:$Q77)=0,0,IF(OR($B77="",$D77="",$F77="",$G77=""),1,0))</f>
         <v/>
       </c>
-      <c r="T77">
+      <c r="U77">
         <f>IF(OR(AND($D77&lt;&gt;"",OR(LEN($D77)&lt;&gt;17,LEN($D77)-LEN(SUBSTITUTE($D77,":",""))&lt;&gt;5)),AND($E77&lt;&gt;"",OR(LEN($E77)&lt;&gt;17,LEN($E77)-LEN(SUBSTITUTE($E77,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4571,16 +4578,16 @@
       <c r="J78" s="24" t="n"/>
       <c r="K78" s="24" t="n"/>
       <c r="L78" s="24" t="n"/>
-      <c r="M78" s="24" t="n"/>
       <c r="N78" s="24" t="n"/>
       <c r="O78" s="24" t="n"/>
       <c r="P78" s="24" t="n"/>
       <c r="Q78" s="24" t="n"/>
-      <c r="S78">
+      <c r="R78" s="24" t="n"/>
+      <c r="T78">
         <f>IF(COUNTA($A78:$Q78)=0,0,IF(OR($B78="",$D78="",$F78="",$G78=""),1,0))</f>
         <v/>
       </c>
-      <c r="T78">
+      <c r="U78">
         <f>IF(OR(AND($D78&lt;&gt;"",OR(LEN($D78)&lt;&gt;17,LEN($D78)-LEN(SUBSTITUTE($D78,":",""))&lt;&gt;5)),AND($E78&lt;&gt;"",OR(LEN($E78)&lt;&gt;17,LEN($E78)-LEN(SUBSTITUTE($E78,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4598,16 +4605,16 @@
       <c r="J79" s="24" t="n"/>
       <c r="K79" s="24" t="n"/>
       <c r="L79" s="24" t="n"/>
-      <c r="M79" s="24" t="n"/>
       <c r="N79" s="24" t="n"/>
       <c r="O79" s="24" t="n"/>
       <c r="P79" s="24" t="n"/>
       <c r="Q79" s="24" t="n"/>
-      <c r="S79">
+      <c r="R79" s="24" t="n"/>
+      <c r="T79">
         <f>IF(COUNTA($A79:$Q79)=0,0,IF(OR($B79="",$D79="",$F79="",$G79=""),1,0))</f>
         <v/>
       </c>
-      <c r="T79">
+      <c r="U79">
         <f>IF(OR(AND($D79&lt;&gt;"",OR(LEN($D79)&lt;&gt;17,LEN($D79)-LEN(SUBSTITUTE($D79,":",""))&lt;&gt;5)),AND($E79&lt;&gt;"",OR(LEN($E79)&lt;&gt;17,LEN($E79)-LEN(SUBSTITUTE($E79,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4625,16 +4632,16 @@
       <c r="J80" s="24" t="n"/>
       <c r="K80" s="24" t="n"/>
       <c r="L80" s="24" t="n"/>
-      <c r="M80" s="24" t="n"/>
       <c r="N80" s="24" t="n"/>
       <c r="O80" s="24" t="n"/>
       <c r="P80" s="24" t="n"/>
       <c r="Q80" s="24" t="n"/>
-      <c r="S80">
+      <c r="R80" s="24" t="n"/>
+      <c r="T80">
         <f>IF(COUNTA($A80:$Q80)=0,0,IF(OR($B80="",$D80="",$F80="",$G80=""),1,0))</f>
         <v/>
       </c>
-      <c r="T80">
+      <c r="U80">
         <f>IF(OR(AND($D80&lt;&gt;"",OR(LEN($D80)&lt;&gt;17,LEN($D80)-LEN(SUBSTITUTE($D80,":",""))&lt;&gt;5)),AND($E80&lt;&gt;"",OR(LEN($E80)&lt;&gt;17,LEN($E80)-LEN(SUBSTITUTE($E80,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4652,16 +4659,16 @@
       <c r="J81" s="24" t="n"/>
       <c r="K81" s="24" t="n"/>
       <c r="L81" s="24" t="n"/>
-      <c r="M81" s="24" t="n"/>
       <c r="N81" s="24" t="n"/>
       <c r="O81" s="24" t="n"/>
       <c r="P81" s="24" t="n"/>
       <c r="Q81" s="24" t="n"/>
-      <c r="S81">
+      <c r="R81" s="24" t="n"/>
+      <c r="T81">
         <f>IF(COUNTA($A81:$Q81)=0,0,IF(OR($B81="",$D81="",$F81="",$G81=""),1,0))</f>
         <v/>
       </c>
-      <c r="T81">
+      <c r="U81">
         <f>IF(OR(AND($D81&lt;&gt;"",OR(LEN($D81)&lt;&gt;17,LEN($D81)-LEN(SUBSTITUTE($D81,":",""))&lt;&gt;5)),AND($E81&lt;&gt;"",OR(LEN($E81)&lt;&gt;17,LEN($E81)-LEN(SUBSTITUTE($E81,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4679,16 +4686,16 @@
       <c r="J82" s="24" t="n"/>
       <c r="K82" s="24" t="n"/>
       <c r="L82" s="24" t="n"/>
-      <c r="M82" s="24" t="n"/>
       <c r="N82" s="24" t="n"/>
       <c r="O82" s="24" t="n"/>
       <c r="P82" s="24" t="n"/>
       <c r="Q82" s="24" t="n"/>
-      <c r="S82">
+      <c r="R82" s="24" t="n"/>
+      <c r="T82">
         <f>IF(COUNTA($A82:$Q82)=0,0,IF(OR($B82="",$D82="",$F82="",$G82=""),1,0))</f>
         <v/>
       </c>
-      <c r="T82">
+      <c r="U82">
         <f>IF(OR(AND($D82&lt;&gt;"",OR(LEN($D82)&lt;&gt;17,LEN($D82)-LEN(SUBSTITUTE($D82,":",""))&lt;&gt;5)),AND($E82&lt;&gt;"",OR(LEN($E82)&lt;&gt;17,LEN($E82)-LEN(SUBSTITUTE($E82,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4706,16 +4713,16 @@
       <c r="J83" s="24" t="n"/>
       <c r="K83" s="24" t="n"/>
       <c r="L83" s="24" t="n"/>
-      <c r="M83" s="24" t="n"/>
       <c r="N83" s="24" t="n"/>
       <c r="O83" s="24" t="n"/>
       <c r="P83" s="24" t="n"/>
       <c r="Q83" s="24" t="n"/>
-      <c r="S83">
+      <c r="R83" s="24" t="n"/>
+      <c r="T83">
         <f>IF(COUNTA($A83:$Q83)=0,0,IF(OR($B83="",$D83="",$F83="",$G83=""),1,0))</f>
         <v/>
       </c>
-      <c r="T83">
+      <c r="U83">
         <f>IF(OR(AND($D83&lt;&gt;"",OR(LEN($D83)&lt;&gt;17,LEN($D83)-LEN(SUBSTITUTE($D83,":",""))&lt;&gt;5)),AND($E83&lt;&gt;"",OR(LEN($E83)&lt;&gt;17,LEN($E83)-LEN(SUBSTITUTE($E83,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4733,16 +4740,16 @@
       <c r="J84" s="24" t="n"/>
       <c r="K84" s="24" t="n"/>
       <c r="L84" s="24" t="n"/>
-      <c r="M84" s="24" t="n"/>
       <c r="N84" s="24" t="n"/>
       <c r="O84" s="24" t="n"/>
       <c r="P84" s="24" t="n"/>
       <c r="Q84" s="24" t="n"/>
-      <c r="S84">
+      <c r="R84" s="24" t="n"/>
+      <c r="T84">
         <f>IF(COUNTA($A84:$Q84)=0,0,IF(OR($B84="",$D84="",$F84="",$G84=""),1,0))</f>
         <v/>
       </c>
-      <c r="T84">
+      <c r="U84">
         <f>IF(OR(AND($D84&lt;&gt;"",OR(LEN($D84)&lt;&gt;17,LEN($D84)-LEN(SUBSTITUTE($D84,":",""))&lt;&gt;5)),AND($E84&lt;&gt;"",OR(LEN($E84)&lt;&gt;17,LEN($E84)-LEN(SUBSTITUTE($E84,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4760,16 +4767,16 @@
       <c r="J85" s="24" t="n"/>
       <c r="K85" s="24" t="n"/>
       <c r="L85" s="24" t="n"/>
-      <c r="M85" s="24" t="n"/>
       <c r="N85" s="24" t="n"/>
       <c r="O85" s="24" t="n"/>
       <c r="P85" s="24" t="n"/>
       <c r="Q85" s="24" t="n"/>
-      <c r="S85">
+      <c r="R85" s="24" t="n"/>
+      <c r="T85">
         <f>IF(COUNTA($A85:$Q85)=0,0,IF(OR($B85="",$D85="",$F85="",$G85=""),1,0))</f>
         <v/>
       </c>
-      <c r="T85">
+      <c r="U85">
         <f>IF(OR(AND($D85&lt;&gt;"",OR(LEN($D85)&lt;&gt;17,LEN($D85)-LEN(SUBSTITUTE($D85,":",""))&lt;&gt;5)),AND($E85&lt;&gt;"",OR(LEN($E85)&lt;&gt;17,LEN($E85)-LEN(SUBSTITUTE($E85,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4787,16 +4794,16 @@
       <c r="J86" s="24" t="n"/>
       <c r="K86" s="24" t="n"/>
       <c r="L86" s="24" t="n"/>
-      <c r="M86" s="24" t="n"/>
       <c r="N86" s="24" t="n"/>
       <c r="O86" s="24" t="n"/>
       <c r="P86" s="24" t="n"/>
       <c r="Q86" s="24" t="n"/>
-      <c r="S86">
+      <c r="R86" s="24" t="n"/>
+      <c r="T86">
         <f>IF(COUNTA($A86:$Q86)=0,0,IF(OR($B86="",$D86="",$F86="",$G86=""),1,0))</f>
         <v/>
       </c>
-      <c r="T86">
+      <c r="U86">
         <f>IF(OR(AND($D86&lt;&gt;"",OR(LEN($D86)&lt;&gt;17,LEN($D86)-LEN(SUBSTITUTE($D86,":",""))&lt;&gt;5)),AND($E86&lt;&gt;"",OR(LEN($E86)&lt;&gt;17,LEN($E86)-LEN(SUBSTITUTE($E86,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4814,16 +4821,16 @@
       <c r="J87" s="24" t="n"/>
       <c r="K87" s="24" t="n"/>
       <c r="L87" s="24" t="n"/>
-      <c r="M87" s="24" t="n"/>
       <c r="N87" s="24" t="n"/>
       <c r="O87" s="24" t="n"/>
       <c r="P87" s="24" t="n"/>
       <c r="Q87" s="24" t="n"/>
-      <c r="S87">
+      <c r="R87" s="24" t="n"/>
+      <c r="T87">
         <f>IF(COUNTA($A87:$Q87)=0,0,IF(OR($B87="",$D87="",$F87="",$G87=""),1,0))</f>
         <v/>
       </c>
-      <c r="T87">
+      <c r="U87">
         <f>IF(OR(AND($D87&lt;&gt;"",OR(LEN($D87)&lt;&gt;17,LEN($D87)-LEN(SUBSTITUTE($D87,":",""))&lt;&gt;5)),AND($E87&lt;&gt;"",OR(LEN($E87)&lt;&gt;17,LEN($E87)-LEN(SUBSTITUTE($E87,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4841,16 +4848,16 @@
       <c r="J88" s="24" t="n"/>
       <c r="K88" s="24" t="n"/>
       <c r="L88" s="24" t="n"/>
-      <c r="M88" s="24" t="n"/>
       <c r="N88" s="24" t="n"/>
       <c r="O88" s="24" t="n"/>
       <c r="P88" s="24" t="n"/>
       <c r="Q88" s="24" t="n"/>
-      <c r="S88">
+      <c r="R88" s="24" t="n"/>
+      <c r="T88">
         <f>IF(COUNTA($A88:$Q88)=0,0,IF(OR($B88="",$D88="",$F88="",$G88=""),1,0))</f>
         <v/>
       </c>
-      <c r="T88">
+      <c r="U88">
         <f>IF(OR(AND($D88&lt;&gt;"",OR(LEN($D88)&lt;&gt;17,LEN($D88)-LEN(SUBSTITUTE($D88,":",""))&lt;&gt;5)),AND($E88&lt;&gt;"",OR(LEN($E88)&lt;&gt;17,LEN($E88)-LEN(SUBSTITUTE($E88,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4868,16 +4875,16 @@
       <c r="J89" s="24" t="n"/>
       <c r="K89" s="24" t="n"/>
       <c r="L89" s="24" t="n"/>
-      <c r="M89" s="24" t="n"/>
       <c r="N89" s="24" t="n"/>
       <c r="O89" s="24" t="n"/>
       <c r="P89" s="24" t="n"/>
       <c r="Q89" s="24" t="n"/>
-      <c r="S89">
+      <c r="R89" s="24" t="n"/>
+      <c r="T89">
         <f>IF(COUNTA($A89:$Q89)=0,0,IF(OR($B89="",$D89="",$F89="",$G89=""),1,0))</f>
         <v/>
       </c>
-      <c r="T89">
+      <c r="U89">
         <f>IF(OR(AND($D89&lt;&gt;"",OR(LEN($D89)&lt;&gt;17,LEN($D89)-LEN(SUBSTITUTE($D89,":",""))&lt;&gt;5)),AND($E89&lt;&gt;"",OR(LEN($E89)&lt;&gt;17,LEN($E89)-LEN(SUBSTITUTE($E89,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4895,16 +4902,16 @@
       <c r="J90" s="24" t="n"/>
       <c r="K90" s="24" t="n"/>
       <c r="L90" s="24" t="n"/>
-      <c r="M90" s="24" t="n"/>
       <c r="N90" s="24" t="n"/>
       <c r="O90" s="24" t="n"/>
       <c r="P90" s="24" t="n"/>
       <c r="Q90" s="24" t="n"/>
-      <c r="S90">
+      <c r="R90" s="24" t="n"/>
+      <c r="T90">
         <f>IF(COUNTA($A90:$Q90)=0,0,IF(OR($B90="",$D90="",$F90="",$G90=""),1,0))</f>
         <v/>
       </c>
-      <c r="T90">
+      <c r="U90">
         <f>IF(OR(AND($D90&lt;&gt;"",OR(LEN($D90)&lt;&gt;17,LEN($D90)-LEN(SUBSTITUTE($D90,":",""))&lt;&gt;5)),AND($E90&lt;&gt;"",OR(LEN($E90)&lt;&gt;17,LEN($E90)-LEN(SUBSTITUTE($E90,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4922,16 +4929,16 @@
       <c r="J91" s="24" t="n"/>
       <c r="K91" s="24" t="n"/>
       <c r="L91" s="24" t="n"/>
-      <c r="M91" s="24" t="n"/>
       <c r="N91" s="24" t="n"/>
       <c r="O91" s="24" t="n"/>
       <c r="P91" s="24" t="n"/>
       <c r="Q91" s="24" t="n"/>
-      <c r="S91">
+      <c r="R91" s="24" t="n"/>
+      <c r="T91">
         <f>IF(COUNTA($A91:$Q91)=0,0,IF(OR($B91="",$D91="",$F91="",$G91=""),1,0))</f>
         <v/>
       </c>
-      <c r="T91">
+      <c r="U91">
         <f>IF(OR(AND($D91&lt;&gt;"",OR(LEN($D91)&lt;&gt;17,LEN($D91)-LEN(SUBSTITUTE($D91,":",""))&lt;&gt;5)),AND($E91&lt;&gt;"",OR(LEN($E91)&lt;&gt;17,LEN($E91)-LEN(SUBSTITUTE($E91,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4949,16 +4956,16 @@
       <c r="J92" s="24" t="n"/>
       <c r="K92" s="24" t="n"/>
       <c r="L92" s="24" t="n"/>
-      <c r="M92" s="24" t="n"/>
       <c r="N92" s="24" t="n"/>
       <c r="O92" s="24" t="n"/>
       <c r="P92" s="24" t="n"/>
       <c r="Q92" s="24" t="n"/>
-      <c r="S92">
+      <c r="R92" s="24" t="n"/>
+      <c r="T92">
         <f>IF(COUNTA($A92:$Q92)=0,0,IF(OR($B92="",$D92="",$F92="",$G92=""),1,0))</f>
         <v/>
       </c>
-      <c r="T92">
+      <c r="U92">
         <f>IF(OR(AND($D92&lt;&gt;"",OR(LEN($D92)&lt;&gt;17,LEN($D92)-LEN(SUBSTITUTE($D92,":",""))&lt;&gt;5)),AND($E92&lt;&gt;"",OR(LEN($E92)&lt;&gt;17,LEN($E92)-LEN(SUBSTITUTE($E92,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -4976,16 +4983,16 @@
       <c r="J93" s="24" t="n"/>
       <c r="K93" s="24" t="n"/>
       <c r="L93" s="24" t="n"/>
-      <c r="M93" s="24" t="n"/>
       <c r="N93" s="24" t="n"/>
       <c r="O93" s="24" t="n"/>
       <c r="P93" s="24" t="n"/>
       <c r="Q93" s="24" t="n"/>
-      <c r="S93">
+      <c r="R93" s="24" t="n"/>
+      <c r="T93">
         <f>IF(COUNTA($A93:$Q93)=0,0,IF(OR($B93="",$D93="",$F93="",$G93=""),1,0))</f>
         <v/>
       </c>
-      <c r="T93">
+      <c r="U93">
         <f>IF(OR(AND($D93&lt;&gt;"",OR(LEN($D93)&lt;&gt;17,LEN($D93)-LEN(SUBSTITUTE($D93,":",""))&lt;&gt;5)),AND($E93&lt;&gt;"",OR(LEN($E93)&lt;&gt;17,LEN($E93)-LEN(SUBSTITUTE($E93,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5003,16 +5010,16 @@
       <c r="J94" s="24" t="n"/>
       <c r="K94" s="24" t="n"/>
       <c r="L94" s="24" t="n"/>
-      <c r="M94" s="24" t="n"/>
       <c r="N94" s="24" t="n"/>
       <c r="O94" s="24" t="n"/>
       <c r="P94" s="24" t="n"/>
       <c r="Q94" s="24" t="n"/>
-      <c r="S94">
+      <c r="R94" s="24" t="n"/>
+      <c r="T94">
         <f>IF(COUNTA($A94:$Q94)=0,0,IF(OR($B94="",$D94="",$F94="",$G94=""),1,0))</f>
         <v/>
       </c>
-      <c r="T94">
+      <c r="U94">
         <f>IF(OR(AND($D94&lt;&gt;"",OR(LEN($D94)&lt;&gt;17,LEN($D94)-LEN(SUBSTITUTE($D94,":",""))&lt;&gt;5)),AND($E94&lt;&gt;"",OR(LEN($E94)&lt;&gt;17,LEN($E94)-LEN(SUBSTITUTE($E94,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5030,16 +5037,16 @@
       <c r="J95" s="24" t="n"/>
       <c r="K95" s="24" t="n"/>
       <c r="L95" s="24" t="n"/>
-      <c r="M95" s="24" t="n"/>
       <c r="N95" s="24" t="n"/>
       <c r="O95" s="24" t="n"/>
       <c r="P95" s="24" t="n"/>
       <c r="Q95" s="24" t="n"/>
-      <c r="S95">
+      <c r="R95" s="24" t="n"/>
+      <c r="T95">
         <f>IF(COUNTA($A95:$Q95)=0,0,IF(OR($B95="",$D95="",$F95="",$G95=""),1,0))</f>
         <v/>
       </c>
-      <c r="T95">
+      <c r="U95">
         <f>IF(OR(AND($D95&lt;&gt;"",OR(LEN($D95)&lt;&gt;17,LEN($D95)-LEN(SUBSTITUTE($D95,":",""))&lt;&gt;5)),AND($E95&lt;&gt;"",OR(LEN($E95)&lt;&gt;17,LEN($E95)-LEN(SUBSTITUTE($E95,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5057,16 +5064,16 @@
       <c r="J96" s="24" t="n"/>
       <c r="K96" s="24" t="n"/>
       <c r="L96" s="24" t="n"/>
-      <c r="M96" s="24" t="n"/>
       <c r="N96" s="24" t="n"/>
       <c r="O96" s="24" t="n"/>
       <c r="P96" s="24" t="n"/>
       <c r="Q96" s="24" t="n"/>
-      <c r="S96">
+      <c r="R96" s="24" t="n"/>
+      <c r="T96">
         <f>IF(COUNTA($A96:$Q96)=0,0,IF(OR($B96="",$D96="",$F96="",$G96=""),1,0))</f>
         <v/>
       </c>
-      <c r="T96">
+      <c r="U96">
         <f>IF(OR(AND($D96&lt;&gt;"",OR(LEN($D96)&lt;&gt;17,LEN($D96)-LEN(SUBSTITUTE($D96,":",""))&lt;&gt;5)),AND($E96&lt;&gt;"",OR(LEN($E96)&lt;&gt;17,LEN($E96)-LEN(SUBSTITUTE($E96,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5084,16 +5091,16 @@
       <c r="J97" s="24" t="n"/>
       <c r="K97" s="24" t="n"/>
       <c r="L97" s="24" t="n"/>
-      <c r="M97" s="24" t="n"/>
       <c r="N97" s="24" t="n"/>
       <c r="O97" s="24" t="n"/>
       <c r="P97" s="24" t="n"/>
       <c r="Q97" s="24" t="n"/>
-      <c r="S97">
+      <c r="R97" s="24" t="n"/>
+      <c r="T97">
         <f>IF(COUNTA($A97:$Q97)=0,0,IF(OR($B97="",$D97="",$F97="",$G97=""),1,0))</f>
         <v/>
       </c>
-      <c r="T97">
+      <c r="U97">
         <f>IF(OR(AND($D97&lt;&gt;"",OR(LEN($D97)&lt;&gt;17,LEN($D97)-LEN(SUBSTITUTE($D97,":",""))&lt;&gt;5)),AND($E97&lt;&gt;"",OR(LEN($E97)&lt;&gt;17,LEN($E97)-LEN(SUBSTITUTE($E97,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5111,16 +5118,16 @@
       <c r="J98" s="24" t="n"/>
       <c r="K98" s="24" t="n"/>
       <c r="L98" s="24" t="n"/>
-      <c r="M98" s="24" t="n"/>
       <c r="N98" s="24" t="n"/>
       <c r="O98" s="24" t="n"/>
       <c r="P98" s="24" t="n"/>
       <c r="Q98" s="24" t="n"/>
-      <c r="S98">
+      <c r="R98" s="24" t="n"/>
+      <c r="T98">
         <f>IF(COUNTA($A98:$Q98)=0,0,IF(OR($B98="",$D98="",$F98="",$G98=""),1,0))</f>
         <v/>
       </c>
-      <c r="T98">
+      <c r="U98">
         <f>IF(OR(AND($D98&lt;&gt;"",OR(LEN($D98)&lt;&gt;17,LEN($D98)-LEN(SUBSTITUTE($D98,":",""))&lt;&gt;5)),AND($E98&lt;&gt;"",OR(LEN($E98)&lt;&gt;17,LEN($E98)-LEN(SUBSTITUTE($E98,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5138,16 +5145,16 @@
       <c r="J99" s="24" t="n"/>
       <c r="K99" s="24" t="n"/>
       <c r="L99" s="24" t="n"/>
-      <c r="M99" s="24" t="n"/>
       <c r="N99" s="24" t="n"/>
       <c r="O99" s="24" t="n"/>
       <c r="P99" s="24" t="n"/>
       <c r="Q99" s="24" t="n"/>
-      <c r="S99">
+      <c r="R99" s="24" t="n"/>
+      <c r="T99">
         <f>IF(COUNTA($A99:$Q99)=0,0,IF(OR($B99="",$D99="",$F99="",$G99=""),1,0))</f>
         <v/>
       </c>
-      <c r="T99">
+      <c r="U99">
         <f>IF(OR(AND($D99&lt;&gt;"",OR(LEN($D99)&lt;&gt;17,LEN($D99)-LEN(SUBSTITUTE($D99,":",""))&lt;&gt;5)),AND($E99&lt;&gt;"",OR(LEN($E99)&lt;&gt;17,LEN($E99)-LEN(SUBSTITUTE($E99,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5165,16 +5172,16 @@
       <c r="J100" s="24" t="n"/>
       <c r="K100" s="24" t="n"/>
       <c r="L100" s="24" t="n"/>
-      <c r="M100" s="24" t="n"/>
       <c r="N100" s="24" t="n"/>
       <c r="O100" s="24" t="n"/>
       <c r="P100" s="24" t="n"/>
       <c r="Q100" s="24" t="n"/>
-      <c r="S100">
+      <c r="R100" s="24" t="n"/>
+      <c r="T100">
         <f>IF(COUNTA($A100:$Q100)=0,0,IF(OR($B100="",$D100="",$F100="",$G100=""),1,0))</f>
         <v/>
       </c>
-      <c r="T100">
+      <c r="U100">
         <f>IF(OR(AND($D100&lt;&gt;"",OR(LEN($D100)&lt;&gt;17,LEN($D100)-LEN(SUBSTITUTE($D100,":",""))&lt;&gt;5)),AND($E100&lt;&gt;"",OR(LEN($E100)&lt;&gt;17,LEN($E100)-LEN(SUBSTITUTE($E100,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5192,16 +5199,16 @@
       <c r="J101" s="24" t="n"/>
       <c r="K101" s="24" t="n"/>
       <c r="L101" s="24" t="n"/>
-      <c r="M101" s="24" t="n"/>
       <c r="N101" s="24" t="n"/>
       <c r="O101" s="24" t="n"/>
       <c r="P101" s="24" t="n"/>
       <c r="Q101" s="24" t="n"/>
-      <c r="S101">
+      <c r="R101" s="24" t="n"/>
+      <c r="T101">
         <f>IF(COUNTA($A101:$Q101)=0,0,IF(OR($B101="",$D101="",$F101="",$G101=""),1,0))</f>
         <v/>
       </c>
-      <c r="T101">
+      <c r="U101">
         <f>IF(OR(AND($D101&lt;&gt;"",OR(LEN($D101)&lt;&gt;17,LEN($D101)-LEN(SUBSTITUTE($D101,":",""))&lt;&gt;5)),AND($E101&lt;&gt;"",OR(LEN($E101)&lt;&gt;17,LEN($E101)-LEN(SUBSTITUTE($E101,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5219,16 +5226,16 @@
       <c r="J102" s="24" t="n"/>
       <c r="K102" s="24" t="n"/>
       <c r="L102" s="24" t="n"/>
-      <c r="M102" s="24" t="n"/>
       <c r="N102" s="24" t="n"/>
       <c r="O102" s="24" t="n"/>
       <c r="P102" s="24" t="n"/>
       <c r="Q102" s="24" t="n"/>
-      <c r="S102">
+      <c r="R102" s="24" t="n"/>
+      <c r="T102">
         <f>IF(COUNTA($A102:$Q102)=0,0,IF(OR($B102="",$D102="",$F102="",$G102=""),1,0))</f>
         <v/>
       </c>
-      <c r="T102">
+      <c r="U102">
         <f>IF(OR(AND($D102&lt;&gt;"",OR(LEN($D102)&lt;&gt;17,LEN($D102)-LEN(SUBSTITUTE($D102,":",""))&lt;&gt;5)),AND($E102&lt;&gt;"",OR(LEN($E102)&lt;&gt;17,LEN($E102)-LEN(SUBSTITUTE($E102,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5246,16 +5253,16 @@
       <c r="J103" s="24" t="n"/>
       <c r="K103" s="24" t="n"/>
       <c r="L103" s="24" t="n"/>
-      <c r="M103" s="24" t="n"/>
       <c r="N103" s="24" t="n"/>
       <c r="O103" s="24" t="n"/>
       <c r="P103" s="24" t="n"/>
       <c r="Q103" s="24" t="n"/>
-      <c r="S103">
+      <c r="R103" s="24" t="n"/>
+      <c r="T103">
         <f>IF(COUNTA($A103:$Q103)=0,0,IF(OR($B103="",$D103="",$F103="",$G103=""),1,0))</f>
         <v/>
       </c>
-      <c r="T103">
+      <c r="U103">
         <f>IF(OR(AND($D103&lt;&gt;"",OR(LEN($D103)&lt;&gt;17,LEN($D103)-LEN(SUBSTITUTE($D103,":",""))&lt;&gt;5)),AND($E103&lt;&gt;"",OR(LEN($E103)&lt;&gt;17,LEN($E103)-LEN(SUBSTITUTE($E103,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5273,16 +5280,16 @@
       <c r="J104" s="24" t="n"/>
       <c r="K104" s="24" t="n"/>
       <c r="L104" s="24" t="n"/>
-      <c r="M104" s="24" t="n"/>
       <c r="N104" s="24" t="n"/>
       <c r="O104" s="24" t="n"/>
       <c r="P104" s="24" t="n"/>
       <c r="Q104" s="24" t="n"/>
-      <c r="S104">
+      <c r="R104" s="24" t="n"/>
+      <c r="T104">
         <f>IF(COUNTA($A104:$Q104)=0,0,IF(OR($B104="",$D104="",$F104="",$G104=""),1,0))</f>
         <v/>
       </c>
-      <c r="T104">
+      <c r="U104">
         <f>IF(OR(AND($D104&lt;&gt;"",OR(LEN($D104)&lt;&gt;17,LEN($D104)-LEN(SUBSTITUTE($D104,":",""))&lt;&gt;5)),AND($E104&lt;&gt;"",OR(LEN($E104)&lt;&gt;17,LEN($E104)-LEN(SUBSTITUTE($E104,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5300,16 +5307,16 @@
       <c r="J105" s="24" t="n"/>
       <c r="K105" s="24" t="n"/>
       <c r="L105" s="24" t="n"/>
-      <c r="M105" s="24" t="n"/>
       <c r="N105" s="24" t="n"/>
       <c r="O105" s="24" t="n"/>
       <c r="P105" s="24" t="n"/>
       <c r="Q105" s="24" t="n"/>
-      <c r="S105">
+      <c r="R105" s="24" t="n"/>
+      <c r="T105">
         <f>IF(COUNTA($A105:$Q105)=0,0,IF(OR($B105="",$D105="",$F105="",$G105=""),1,0))</f>
         <v/>
       </c>
-      <c r="T105">
+      <c r="U105">
         <f>IF(OR(AND($D105&lt;&gt;"",OR(LEN($D105)&lt;&gt;17,LEN($D105)-LEN(SUBSTITUTE($D105,":",""))&lt;&gt;5)),AND($E105&lt;&gt;"",OR(LEN($E105)&lt;&gt;17,LEN($E105)-LEN(SUBSTITUTE($E105,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5327,16 +5334,16 @@
       <c r="J106" s="24" t="n"/>
       <c r="K106" s="24" t="n"/>
       <c r="L106" s="24" t="n"/>
-      <c r="M106" s="24" t="n"/>
       <c r="N106" s="24" t="n"/>
       <c r="O106" s="24" t="n"/>
       <c r="P106" s="24" t="n"/>
       <c r="Q106" s="24" t="n"/>
-      <c r="S106">
+      <c r="R106" s="24" t="n"/>
+      <c r="T106">
         <f>IF(COUNTA($A106:$Q106)=0,0,IF(OR($B106="",$D106="",$F106="",$G106=""),1,0))</f>
         <v/>
       </c>
-      <c r="T106">
+      <c r="U106">
         <f>IF(OR(AND($D106&lt;&gt;"",OR(LEN($D106)&lt;&gt;17,LEN($D106)-LEN(SUBSTITUTE($D106,":",""))&lt;&gt;5)),AND($E106&lt;&gt;"",OR(LEN($E106)&lt;&gt;17,LEN($E106)-LEN(SUBSTITUTE($E106,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5354,16 +5361,16 @@
       <c r="J107" s="24" t="n"/>
       <c r="K107" s="24" t="n"/>
       <c r="L107" s="24" t="n"/>
-      <c r="M107" s="24" t="n"/>
       <c r="N107" s="24" t="n"/>
       <c r="O107" s="24" t="n"/>
       <c r="P107" s="24" t="n"/>
       <c r="Q107" s="24" t="n"/>
-      <c r="S107">
+      <c r="R107" s="24" t="n"/>
+      <c r="T107">
         <f>IF(COUNTA($A107:$Q107)=0,0,IF(OR($B107="",$D107="",$F107="",$G107=""),1,0))</f>
         <v/>
       </c>
-      <c r="T107">
+      <c r="U107">
         <f>IF(OR(AND($D107&lt;&gt;"",OR(LEN($D107)&lt;&gt;17,LEN($D107)-LEN(SUBSTITUTE($D107,":",""))&lt;&gt;5)),AND($E107&lt;&gt;"",OR(LEN($E107)&lt;&gt;17,LEN($E107)-LEN(SUBSTITUTE($E107,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5381,16 +5388,16 @@
       <c r="J108" s="24" t="n"/>
       <c r="K108" s="24" t="n"/>
       <c r="L108" s="24" t="n"/>
-      <c r="M108" s="24" t="n"/>
       <c r="N108" s="24" t="n"/>
       <c r="O108" s="24" t="n"/>
       <c r="P108" s="24" t="n"/>
       <c r="Q108" s="24" t="n"/>
-      <c r="S108">
+      <c r="R108" s="24" t="n"/>
+      <c r="T108">
         <f>IF(COUNTA($A108:$Q108)=0,0,IF(OR($B108="",$D108="",$F108="",$G108=""),1,0))</f>
         <v/>
       </c>
-      <c r="T108">
+      <c r="U108">
         <f>IF(OR(AND($D108&lt;&gt;"",OR(LEN($D108)&lt;&gt;17,LEN($D108)-LEN(SUBSTITUTE($D108,":",""))&lt;&gt;5)),AND($E108&lt;&gt;"",OR(LEN($E108)&lt;&gt;17,LEN($E108)-LEN(SUBSTITUTE($E108,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5408,16 +5415,16 @@
       <c r="J109" s="24" t="n"/>
       <c r="K109" s="24" t="n"/>
       <c r="L109" s="24" t="n"/>
-      <c r="M109" s="24" t="n"/>
       <c r="N109" s="24" t="n"/>
       <c r="O109" s="24" t="n"/>
       <c r="P109" s="24" t="n"/>
       <c r="Q109" s="24" t="n"/>
-      <c r="S109">
+      <c r="R109" s="24" t="n"/>
+      <c r="T109">
         <f>IF(COUNTA($A109:$Q109)=0,0,IF(OR($B109="",$D109="",$F109="",$G109=""),1,0))</f>
         <v/>
       </c>
-      <c r="T109">
+      <c r="U109">
         <f>IF(OR(AND($D109&lt;&gt;"",OR(LEN($D109)&lt;&gt;17,LEN($D109)-LEN(SUBSTITUTE($D109,":",""))&lt;&gt;5)),AND($E109&lt;&gt;"",OR(LEN($E109)&lt;&gt;17,LEN($E109)-LEN(SUBSTITUTE($E109,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5435,16 +5442,16 @@
       <c r="J110" s="24" t="n"/>
       <c r="K110" s="24" t="n"/>
       <c r="L110" s="24" t="n"/>
-      <c r="M110" s="24" t="n"/>
       <c r="N110" s="24" t="n"/>
       <c r="O110" s="24" t="n"/>
       <c r="P110" s="24" t="n"/>
       <c r="Q110" s="24" t="n"/>
-      <c r="S110">
+      <c r="R110" s="24" t="n"/>
+      <c r="T110">
         <f>IF(COUNTA($A110:$Q110)=0,0,IF(OR($B110="",$D110="",$F110="",$G110=""),1,0))</f>
         <v/>
       </c>
-      <c r="T110">
+      <c r="U110">
         <f>IF(OR(AND($D110&lt;&gt;"",OR(LEN($D110)&lt;&gt;17,LEN($D110)-LEN(SUBSTITUTE($D110,":",""))&lt;&gt;5)),AND($E110&lt;&gt;"",OR(LEN($E110)&lt;&gt;17,LEN($E110)-LEN(SUBSTITUTE($E110,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5462,16 +5469,16 @@
       <c r="J111" s="24" t="n"/>
       <c r="K111" s="24" t="n"/>
       <c r="L111" s="24" t="n"/>
-      <c r="M111" s="24" t="n"/>
       <c r="N111" s="24" t="n"/>
       <c r="O111" s="24" t="n"/>
       <c r="P111" s="24" t="n"/>
       <c r="Q111" s="24" t="n"/>
-      <c r="S111">
+      <c r="R111" s="24" t="n"/>
+      <c r="T111">
         <f>IF(COUNTA($A111:$Q111)=0,0,IF(OR($B111="",$D111="",$F111="",$G111=""),1,0))</f>
         <v/>
       </c>
-      <c r="T111">
+      <c r="U111">
         <f>IF(OR(AND($D111&lt;&gt;"",OR(LEN($D111)&lt;&gt;17,LEN($D111)-LEN(SUBSTITUTE($D111,":",""))&lt;&gt;5)),AND($E111&lt;&gt;"",OR(LEN($E111)&lt;&gt;17,LEN($E111)-LEN(SUBSTITUTE($E111,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5489,16 +5496,16 @@
       <c r="J112" s="24" t="n"/>
       <c r="K112" s="24" t="n"/>
       <c r="L112" s="24" t="n"/>
-      <c r="M112" s="24" t="n"/>
       <c r="N112" s="24" t="n"/>
       <c r="O112" s="24" t="n"/>
       <c r="P112" s="24" t="n"/>
       <c r="Q112" s="24" t="n"/>
-      <c r="S112">
+      <c r="R112" s="24" t="n"/>
+      <c r="T112">
         <f>IF(COUNTA($A112:$Q112)=0,0,IF(OR($B112="",$D112="",$F112="",$G112=""),1,0))</f>
         <v/>
       </c>
-      <c r="T112">
+      <c r="U112">
         <f>IF(OR(AND($D112&lt;&gt;"",OR(LEN($D112)&lt;&gt;17,LEN($D112)-LEN(SUBSTITUTE($D112,":",""))&lt;&gt;5)),AND($E112&lt;&gt;"",OR(LEN($E112)&lt;&gt;17,LEN($E112)-LEN(SUBSTITUTE($E112,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5516,16 +5523,16 @@
       <c r="J113" s="24" t="n"/>
       <c r="K113" s="24" t="n"/>
       <c r="L113" s="24" t="n"/>
-      <c r="M113" s="24" t="n"/>
       <c r="N113" s="24" t="n"/>
       <c r="O113" s="24" t="n"/>
       <c r="P113" s="24" t="n"/>
       <c r="Q113" s="24" t="n"/>
-      <c r="S113">
+      <c r="R113" s="24" t="n"/>
+      <c r="T113">
         <f>IF(COUNTA($A113:$Q113)=0,0,IF(OR($B113="",$D113="",$F113="",$G113=""),1,0))</f>
         <v/>
       </c>
-      <c r="T113">
+      <c r="U113">
         <f>IF(OR(AND($D113&lt;&gt;"",OR(LEN($D113)&lt;&gt;17,LEN($D113)-LEN(SUBSTITUTE($D113,":",""))&lt;&gt;5)),AND($E113&lt;&gt;"",OR(LEN($E113)&lt;&gt;17,LEN($E113)-LEN(SUBSTITUTE($E113,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5543,16 +5550,16 @@
       <c r="J114" s="24" t="n"/>
       <c r="K114" s="24" t="n"/>
       <c r="L114" s="24" t="n"/>
-      <c r="M114" s="24" t="n"/>
       <c r="N114" s="24" t="n"/>
       <c r="O114" s="24" t="n"/>
       <c r="P114" s="24" t="n"/>
       <c r="Q114" s="24" t="n"/>
-      <c r="S114">
+      <c r="R114" s="24" t="n"/>
+      <c r="T114">
         <f>IF(COUNTA($A114:$Q114)=0,0,IF(OR($B114="",$D114="",$F114="",$G114=""),1,0))</f>
         <v/>
       </c>
-      <c r="T114">
+      <c r="U114">
         <f>IF(OR(AND($D114&lt;&gt;"",OR(LEN($D114)&lt;&gt;17,LEN($D114)-LEN(SUBSTITUTE($D114,":",""))&lt;&gt;5)),AND($E114&lt;&gt;"",OR(LEN($E114)&lt;&gt;17,LEN($E114)-LEN(SUBSTITUTE($E114,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5570,16 +5577,16 @@
       <c r="J115" s="24" t="n"/>
       <c r="K115" s="24" t="n"/>
       <c r="L115" s="24" t="n"/>
-      <c r="M115" s="24" t="n"/>
       <c r="N115" s="24" t="n"/>
       <c r="O115" s="24" t="n"/>
       <c r="P115" s="24" t="n"/>
       <c r="Q115" s="24" t="n"/>
-      <c r="S115">
+      <c r="R115" s="24" t="n"/>
+      <c r="T115">
         <f>IF(COUNTA($A115:$Q115)=0,0,IF(OR($B115="",$D115="",$F115="",$G115=""),1,0))</f>
         <v/>
       </c>
-      <c r="T115">
+      <c r="U115">
         <f>IF(OR(AND($D115&lt;&gt;"",OR(LEN($D115)&lt;&gt;17,LEN($D115)-LEN(SUBSTITUTE($D115,":",""))&lt;&gt;5)),AND($E115&lt;&gt;"",OR(LEN($E115)&lt;&gt;17,LEN($E115)-LEN(SUBSTITUTE($E115,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5597,16 +5604,16 @@
       <c r="J116" s="24" t="n"/>
       <c r="K116" s="24" t="n"/>
       <c r="L116" s="24" t="n"/>
-      <c r="M116" s="24" t="n"/>
       <c r="N116" s="24" t="n"/>
       <c r="O116" s="24" t="n"/>
       <c r="P116" s="24" t="n"/>
       <c r="Q116" s="24" t="n"/>
-      <c r="S116">
+      <c r="R116" s="24" t="n"/>
+      <c r="T116">
         <f>IF(COUNTA($A116:$Q116)=0,0,IF(OR($B116="",$D116="",$F116="",$G116=""),1,0))</f>
         <v/>
       </c>
-      <c r="T116">
+      <c r="U116">
         <f>IF(OR(AND($D116&lt;&gt;"",OR(LEN($D116)&lt;&gt;17,LEN($D116)-LEN(SUBSTITUTE($D116,":",""))&lt;&gt;5)),AND($E116&lt;&gt;"",OR(LEN($E116)&lt;&gt;17,LEN($E116)-LEN(SUBSTITUTE($E116,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5624,16 +5631,16 @@
       <c r="J117" s="24" t="n"/>
       <c r="K117" s="24" t="n"/>
       <c r="L117" s="24" t="n"/>
-      <c r="M117" s="24" t="n"/>
       <c r="N117" s="24" t="n"/>
       <c r="O117" s="24" t="n"/>
       <c r="P117" s="24" t="n"/>
       <c r="Q117" s="24" t="n"/>
-      <c r="S117">
+      <c r="R117" s="24" t="n"/>
+      <c r="T117">
         <f>IF(COUNTA($A117:$Q117)=0,0,IF(OR($B117="",$D117="",$F117="",$G117=""),1,0))</f>
         <v/>
       </c>
-      <c r="T117">
+      <c r="U117">
         <f>IF(OR(AND($D117&lt;&gt;"",OR(LEN($D117)&lt;&gt;17,LEN($D117)-LEN(SUBSTITUTE($D117,":",""))&lt;&gt;5)),AND($E117&lt;&gt;"",OR(LEN($E117)&lt;&gt;17,LEN($E117)-LEN(SUBSTITUTE($E117,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5651,16 +5658,16 @@
       <c r="J118" s="24" t="n"/>
       <c r="K118" s="24" t="n"/>
       <c r="L118" s="24" t="n"/>
-      <c r="M118" s="24" t="n"/>
       <c r="N118" s="24" t="n"/>
       <c r="O118" s="24" t="n"/>
       <c r="P118" s="24" t="n"/>
       <c r="Q118" s="24" t="n"/>
-      <c r="S118">
+      <c r="R118" s="24" t="n"/>
+      <c r="T118">
         <f>IF(COUNTA($A118:$Q118)=0,0,IF(OR($B118="",$D118="",$F118="",$G118=""),1,0))</f>
         <v/>
       </c>
-      <c r="T118">
+      <c r="U118">
         <f>IF(OR(AND($D118&lt;&gt;"",OR(LEN($D118)&lt;&gt;17,LEN($D118)-LEN(SUBSTITUTE($D118,":",""))&lt;&gt;5)),AND($E118&lt;&gt;"",OR(LEN($E118)&lt;&gt;17,LEN($E118)-LEN(SUBSTITUTE($E118,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5678,16 +5685,16 @@
       <c r="J119" s="24" t="n"/>
       <c r="K119" s="24" t="n"/>
       <c r="L119" s="24" t="n"/>
-      <c r="M119" s="24" t="n"/>
       <c r="N119" s="24" t="n"/>
       <c r="O119" s="24" t="n"/>
       <c r="P119" s="24" t="n"/>
       <c r="Q119" s="24" t="n"/>
-      <c r="S119">
+      <c r="R119" s="24" t="n"/>
+      <c r="T119">
         <f>IF(COUNTA($A119:$Q119)=0,0,IF(OR($B119="",$D119="",$F119="",$G119=""),1,0))</f>
         <v/>
       </c>
-      <c r="T119">
+      <c r="U119">
         <f>IF(OR(AND($D119&lt;&gt;"",OR(LEN($D119)&lt;&gt;17,LEN($D119)-LEN(SUBSTITUTE($D119,":",""))&lt;&gt;5)),AND($E119&lt;&gt;"",OR(LEN($E119)&lt;&gt;17,LEN($E119)-LEN(SUBSTITUTE($E119,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5705,16 +5712,16 @@
       <c r="J120" s="24" t="n"/>
       <c r="K120" s="24" t="n"/>
       <c r="L120" s="24" t="n"/>
-      <c r="M120" s="24" t="n"/>
       <c r="N120" s="24" t="n"/>
       <c r="O120" s="24" t="n"/>
       <c r="P120" s="24" t="n"/>
       <c r="Q120" s="24" t="n"/>
-      <c r="S120">
+      <c r="R120" s="24" t="n"/>
+      <c r="T120">
         <f>IF(COUNTA($A120:$Q120)=0,0,IF(OR($B120="",$D120="",$F120="",$G120=""),1,0))</f>
         <v/>
       </c>
-      <c r="T120">
+      <c r="U120">
         <f>IF(OR(AND($D120&lt;&gt;"",OR(LEN($D120)&lt;&gt;17,LEN($D120)-LEN(SUBSTITUTE($D120,":",""))&lt;&gt;5)),AND($E120&lt;&gt;"",OR(LEN($E120)&lt;&gt;17,LEN($E120)-LEN(SUBSTITUTE($E120,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5732,16 +5739,16 @@
       <c r="J121" s="24" t="n"/>
       <c r="K121" s="24" t="n"/>
       <c r="L121" s="24" t="n"/>
-      <c r="M121" s="24" t="n"/>
       <c r="N121" s="24" t="n"/>
       <c r="O121" s="24" t="n"/>
       <c r="P121" s="24" t="n"/>
       <c r="Q121" s="24" t="n"/>
-      <c r="S121">
+      <c r="R121" s="24" t="n"/>
+      <c r="T121">
         <f>IF(COUNTA($A121:$Q121)=0,0,IF(OR($B121="",$D121="",$F121="",$G121=""),1,0))</f>
         <v/>
       </c>
-      <c r="T121">
+      <c r="U121">
         <f>IF(OR(AND($D121&lt;&gt;"",OR(LEN($D121)&lt;&gt;17,LEN($D121)-LEN(SUBSTITUTE($D121,":",""))&lt;&gt;5)),AND($E121&lt;&gt;"",OR(LEN($E121)&lt;&gt;17,LEN($E121)-LEN(SUBSTITUTE($E121,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5759,16 +5766,16 @@
       <c r="J122" s="24" t="n"/>
       <c r="K122" s="24" t="n"/>
       <c r="L122" s="24" t="n"/>
-      <c r="M122" s="24" t="n"/>
       <c r="N122" s="24" t="n"/>
       <c r="O122" s="24" t="n"/>
       <c r="P122" s="24" t="n"/>
       <c r="Q122" s="24" t="n"/>
-      <c r="S122">
+      <c r="R122" s="24" t="n"/>
+      <c r="T122">
         <f>IF(COUNTA($A122:$Q122)=0,0,IF(OR($B122="",$D122="",$F122="",$G122=""),1,0))</f>
         <v/>
       </c>
-      <c r="T122">
+      <c r="U122">
         <f>IF(OR(AND($D122&lt;&gt;"",OR(LEN($D122)&lt;&gt;17,LEN($D122)-LEN(SUBSTITUTE($D122,":",""))&lt;&gt;5)),AND($E122&lt;&gt;"",OR(LEN($E122)&lt;&gt;17,LEN($E122)-LEN(SUBSTITUTE($E122,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5786,16 +5793,16 @@
       <c r="J123" s="24" t="n"/>
       <c r="K123" s="24" t="n"/>
       <c r="L123" s="24" t="n"/>
-      <c r="M123" s="24" t="n"/>
       <c r="N123" s="24" t="n"/>
       <c r="O123" s="24" t="n"/>
       <c r="P123" s="24" t="n"/>
       <c r="Q123" s="24" t="n"/>
-      <c r="S123">
+      <c r="R123" s="24" t="n"/>
+      <c r="T123">
         <f>IF(COUNTA($A123:$Q123)=0,0,IF(OR($B123="",$D123="",$F123="",$G123=""),1,0))</f>
         <v/>
       </c>
-      <c r="T123">
+      <c r="U123">
         <f>IF(OR(AND($D123&lt;&gt;"",OR(LEN($D123)&lt;&gt;17,LEN($D123)-LEN(SUBSTITUTE($D123,":",""))&lt;&gt;5)),AND($E123&lt;&gt;"",OR(LEN($E123)&lt;&gt;17,LEN($E123)-LEN(SUBSTITUTE($E123,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5813,16 +5820,16 @@
       <c r="J124" s="24" t="n"/>
       <c r="K124" s="24" t="n"/>
       <c r="L124" s="24" t="n"/>
-      <c r="M124" s="24" t="n"/>
       <c r="N124" s="24" t="n"/>
       <c r="O124" s="24" t="n"/>
       <c r="P124" s="24" t="n"/>
       <c r="Q124" s="24" t="n"/>
-      <c r="S124">
+      <c r="R124" s="24" t="n"/>
+      <c r="T124">
         <f>IF(COUNTA($A124:$Q124)=0,0,IF(OR($B124="",$D124="",$F124="",$G124=""),1,0))</f>
         <v/>
       </c>
-      <c r="T124">
+      <c r="U124">
         <f>IF(OR(AND($D124&lt;&gt;"",OR(LEN($D124)&lt;&gt;17,LEN($D124)-LEN(SUBSTITUTE($D124,":",""))&lt;&gt;5)),AND($E124&lt;&gt;"",OR(LEN($E124)&lt;&gt;17,LEN($E124)-LEN(SUBSTITUTE($E124,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5840,16 +5847,16 @@
       <c r="J125" s="24" t="n"/>
       <c r="K125" s="24" t="n"/>
       <c r="L125" s="24" t="n"/>
-      <c r="M125" s="24" t="n"/>
       <c r="N125" s="24" t="n"/>
       <c r="O125" s="24" t="n"/>
       <c r="P125" s="24" t="n"/>
       <c r="Q125" s="24" t="n"/>
-      <c r="S125">
+      <c r="R125" s="24" t="n"/>
+      <c r="T125">
         <f>IF(COUNTA($A125:$Q125)=0,0,IF(OR($B125="",$D125="",$F125="",$G125=""),1,0))</f>
         <v/>
       </c>
-      <c r="T125">
+      <c r="U125">
         <f>IF(OR(AND($D125&lt;&gt;"",OR(LEN($D125)&lt;&gt;17,LEN($D125)-LEN(SUBSTITUTE($D125,":",""))&lt;&gt;5)),AND($E125&lt;&gt;"",OR(LEN($E125)&lt;&gt;17,LEN($E125)-LEN(SUBSTITUTE($E125,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5867,16 +5874,16 @@
       <c r="J126" s="24" t="n"/>
       <c r="K126" s="24" t="n"/>
       <c r="L126" s="24" t="n"/>
-      <c r="M126" s="24" t="n"/>
       <c r="N126" s="24" t="n"/>
       <c r="O126" s="24" t="n"/>
       <c r="P126" s="24" t="n"/>
       <c r="Q126" s="24" t="n"/>
-      <c r="S126">
+      <c r="R126" s="24" t="n"/>
+      <c r="T126">
         <f>IF(COUNTA($A126:$Q126)=0,0,IF(OR($B126="",$D126="",$F126="",$G126=""),1,0))</f>
         <v/>
       </c>
-      <c r="T126">
+      <c r="U126">
         <f>IF(OR(AND($D126&lt;&gt;"",OR(LEN($D126)&lt;&gt;17,LEN($D126)-LEN(SUBSTITUTE($D126,":",""))&lt;&gt;5)),AND($E126&lt;&gt;"",OR(LEN($E126)&lt;&gt;17,LEN($E126)-LEN(SUBSTITUTE($E126,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5894,16 +5901,16 @@
       <c r="J127" s="24" t="n"/>
       <c r="K127" s="24" t="n"/>
       <c r="L127" s="24" t="n"/>
-      <c r="M127" s="24" t="n"/>
       <c r="N127" s="24" t="n"/>
       <c r="O127" s="24" t="n"/>
       <c r="P127" s="24" t="n"/>
       <c r="Q127" s="24" t="n"/>
-      <c r="S127">
+      <c r="R127" s="24" t="n"/>
+      <c r="T127">
         <f>IF(COUNTA($A127:$Q127)=0,0,IF(OR($B127="",$D127="",$F127="",$G127=""),1,0))</f>
         <v/>
       </c>
-      <c r="T127">
+      <c r="U127">
         <f>IF(OR(AND($D127&lt;&gt;"",OR(LEN($D127)&lt;&gt;17,LEN($D127)-LEN(SUBSTITUTE($D127,":",""))&lt;&gt;5)),AND($E127&lt;&gt;"",OR(LEN($E127)&lt;&gt;17,LEN($E127)-LEN(SUBSTITUTE($E127,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5921,16 +5928,16 @@
       <c r="J128" s="24" t="n"/>
       <c r="K128" s="24" t="n"/>
       <c r="L128" s="24" t="n"/>
-      <c r="M128" s="24" t="n"/>
       <c r="N128" s="24" t="n"/>
       <c r="O128" s="24" t="n"/>
       <c r="P128" s="24" t="n"/>
       <c r="Q128" s="24" t="n"/>
-      <c r="S128">
+      <c r="R128" s="24" t="n"/>
+      <c r="T128">
         <f>IF(COUNTA($A128:$Q128)=0,0,IF(OR($B128="",$D128="",$F128="",$G128=""),1,0))</f>
         <v/>
       </c>
-      <c r="T128">
+      <c r="U128">
         <f>IF(OR(AND($D128&lt;&gt;"",OR(LEN($D128)&lt;&gt;17,LEN($D128)-LEN(SUBSTITUTE($D128,":",""))&lt;&gt;5)),AND($E128&lt;&gt;"",OR(LEN($E128)&lt;&gt;17,LEN($E128)-LEN(SUBSTITUTE($E128,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5948,16 +5955,16 @@
       <c r="J129" s="24" t="n"/>
       <c r="K129" s="24" t="n"/>
       <c r="L129" s="24" t="n"/>
-      <c r="M129" s="24" t="n"/>
       <c r="N129" s="24" t="n"/>
       <c r="O129" s="24" t="n"/>
       <c r="P129" s="24" t="n"/>
       <c r="Q129" s="24" t="n"/>
-      <c r="S129">
+      <c r="R129" s="24" t="n"/>
+      <c r="T129">
         <f>IF(COUNTA($A129:$Q129)=0,0,IF(OR($B129="",$D129="",$F129="",$G129=""),1,0))</f>
         <v/>
       </c>
-      <c r="T129">
+      <c r="U129">
         <f>IF(OR(AND($D129&lt;&gt;"",OR(LEN($D129)&lt;&gt;17,LEN($D129)-LEN(SUBSTITUTE($D129,":",""))&lt;&gt;5)),AND($E129&lt;&gt;"",OR(LEN($E129)&lt;&gt;17,LEN($E129)-LEN(SUBSTITUTE($E129,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -5975,16 +5982,16 @@
       <c r="J130" s="24" t="n"/>
       <c r="K130" s="24" t="n"/>
       <c r="L130" s="24" t="n"/>
-      <c r="M130" s="24" t="n"/>
       <c r="N130" s="24" t="n"/>
       <c r="O130" s="24" t="n"/>
       <c r="P130" s="24" t="n"/>
       <c r="Q130" s="24" t="n"/>
-      <c r="S130">
+      <c r="R130" s="24" t="n"/>
+      <c r="T130">
         <f>IF(COUNTA($A130:$Q130)=0,0,IF(OR($B130="",$D130="",$F130="",$G130=""),1,0))</f>
         <v/>
       </c>
-      <c r="T130">
+      <c r="U130">
         <f>IF(OR(AND($D130&lt;&gt;"",OR(LEN($D130)&lt;&gt;17,LEN($D130)-LEN(SUBSTITUTE($D130,":",""))&lt;&gt;5)),AND($E130&lt;&gt;"",OR(LEN($E130)&lt;&gt;17,LEN($E130)-LEN(SUBSTITUTE($E130,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6002,16 +6009,16 @@
       <c r="J131" s="24" t="n"/>
       <c r="K131" s="24" t="n"/>
       <c r="L131" s="24" t="n"/>
-      <c r="M131" s="24" t="n"/>
       <c r="N131" s="24" t="n"/>
       <c r="O131" s="24" t="n"/>
       <c r="P131" s="24" t="n"/>
       <c r="Q131" s="24" t="n"/>
-      <c r="S131">
+      <c r="R131" s="24" t="n"/>
+      <c r="T131">
         <f>IF(COUNTA($A131:$Q131)=0,0,IF(OR($B131="",$D131="",$F131="",$G131=""),1,0))</f>
         <v/>
       </c>
-      <c r="T131">
+      <c r="U131">
         <f>IF(OR(AND($D131&lt;&gt;"",OR(LEN($D131)&lt;&gt;17,LEN($D131)-LEN(SUBSTITUTE($D131,":",""))&lt;&gt;5)),AND($E131&lt;&gt;"",OR(LEN($E131)&lt;&gt;17,LEN($E131)-LEN(SUBSTITUTE($E131,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6029,16 +6036,16 @@
       <c r="J132" s="24" t="n"/>
       <c r="K132" s="24" t="n"/>
       <c r="L132" s="24" t="n"/>
-      <c r="M132" s="24" t="n"/>
       <c r="N132" s="24" t="n"/>
       <c r="O132" s="24" t="n"/>
       <c r="P132" s="24" t="n"/>
       <c r="Q132" s="24" t="n"/>
-      <c r="S132">
+      <c r="R132" s="24" t="n"/>
+      <c r="T132">
         <f>IF(COUNTA($A132:$Q132)=0,0,IF(OR($B132="",$D132="",$F132="",$G132=""),1,0))</f>
         <v/>
       </c>
-      <c r="T132">
+      <c r="U132">
         <f>IF(OR(AND($D132&lt;&gt;"",OR(LEN($D132)&lt;&gt;17,LEN($D132)-LEN(SUBSTITUTE($D132,":",""))&lt;&gt;5)),AND($E132&lt;&gt;"",OR(LEN($E132)&lt;&gt;17,LEN($E132)-LEN(SUBSTITUTE($E132,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6056,16 +6063,16 @@
       <c r="J133" s="24" t="n"/>
       <c r="K133" s="24" t="n"/>
       <c r="L133" s="24" t="n"/>
-      <c r="M133" s="24" t="n"/>
       <c r="N133" s="24" t="n"/>
       <c r="O133" s="24" t="n"/>
       <c r="P133" s="24" t="n"/>
       <c r="Q133" s="24" t="n"/>
-      <c r="S133">
+      <c r="R133" s="24" t="n"/>
+      <c r="T133">
         <f>IF(COUNTA($A133:$Q133)=0,0,IF(OR($B133="",$D133="",$F133="",$G133=""),1,0))</f>
         <v/>
       </c>
-      <c r="T133">
+      <c r="U133">
         <f>IF(OR(AND($D133&lt;&gt;"",OR(LEN($D133)&lt;&gt;17,LEN($D133)-LEN(SUBSTITUTE($D133,":",""))&lt;&gt;5)),AND($E133&lt;&gt;"",OR(LEN($E133)&lt;&gt;17,LEN($E133)-LEN(SUBSTITUTE($E133,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6083,16 +6090,16 @@
       <c r="J134" s="24" t="n"/>
       <c r="K134" s="24" t="n"/>
       <c r="L134" s="24" t="n"/>
-      <c r="M134" s="24" t="n"/>
       <c r="N134" s="24" t="n"/>
       <c r="O134" s="24" t="n"/>
       <c r="P134" s="24" t="n"/>
       <c r="Q134" s="24" t="n"/>
-      <c r="S134">
+      <c r="R134" s="24" t="n"/>
+      <c r="T134">
         <f>IF(COUNTA($A134:$Q134)=0,0,IF(OR($B134="",$D134="",$F134="",$G134=""),1,0))</f>
         <v/>
       </c>
-      <c r="T134">
+      <c r="U134">
         <f>IF(OR(AND($D134&lt;&gt;"",OR(LEN($D134)&lt;&gt;17,LEN($D134)-LEN(SUBSTITUTE($D134,":",""))&lt;&gt;5)),AND($E134&lt;&gt;"",OR(LEN($E134)&lt;&gt;17,LEN($E134)-LEN(SUBSTITUTE($E134,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6110,16 +6117,16 @@
       <c r="J135" s="24" t="n"/>
       <c r="K135" s="24" t="n"/>
       <c r="L135" s="24" t="n"/>
-      <c r="M135" s="24" t="n"/>
       <c r="N135" s="24" t="n"/>
       <c r="O135" s="24" t="n"/>
       <c r="P135" s="24" t="n"/>
       <c r="Q135" s="24" t="n"/>
-      <c r="S135">
+      <c r="R135" s="24" t="n"/>
+      <c r="T135">
         <f>IF(COUNTA($A135:$Q135)=0,0,IF(OR($B135="",$D135="",$F135="",$G135=""),1,0))</f>
         <v/>
       </c>
-      <c r="T135">
+      <c r="U135">
         <f>IF(OR(AND($D135&lt;&gt;"",OR(LEN($D135)&lt;&gt;17,LEN($D135)-LEN(SUBSTITUTE($D135,":",""))&lt;&gt;5)),AND($E135&lt;&gt;"",OR(LEN($E135)&lt;&gt;17,LEN($E135)-LEN(SUBSTITUTE($E135,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6137,16 +6144,16 @@
       <c r="J136" s="24" t="n"/>
       <c r="K136" s="24" t="n"/>
       <c r="L136" s="24" t="n"/>
-      <c r="M136" s="24" t="n"/>
       <c r="N136" s="24" t="n"/>
       <c r="O136" s="24" t="n"/>
       <c r="P136" s="24" t="n"/>
       <c r="Q136" s="24" t="n"/>
-      <c r="S136">
+      <c r="R136" s="24" t="n"/>
+      <c r="T136">
         <f>IF(COUNTA($A136:$Q136)=0,0,IF(OR($B136="",$D136="",$F136="",$G136=""),1,0))</f>
         <v/>
       </c>
-      <c r="T136">
+      <c r="U136">
         <f>IF(OR(AND($D136&lt;&gt;"",OR(LEN($D136)&lt;&gt;17,LEN($D136)-LEN(SUBSTITUTE($D136,":",""))&lt;&gt;5)),AND($E136&lt;&gt;"",OR(LEN($E136)&lt;&gt;17,LEN($E136)-LEN(SUBSTITUTE($E136,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6164,16 +6171,16 @@
       <c r="J137" s="24" t="n"/>
       <c r="K137" s="24" t="n"/>
       <c r="L137" s="24" t="n"/>
-      <c r="M137" s="24" t="n"/>
       <c r="N137" s="24" t="n"/>
       <c r="O137" s="24" t="n"/>
       <c r="P137" s="24" t="n"/>
       <c r="Q137" s="24" t="n"/>
-      <c r="S137">
+      <c r="R137" s="24" t="n"/>
+      <c r="T137">
         <f>IF(COUNTA($A137:$Q137)=0,0,IF(OR($B137="",$D137="",$F137="",$G137=""),1,0))</f>
         <v/>
       </c>
-      <c r="T137">
+      <c r="U137">
         <f>IF(OR(AND($D137&lt;&gt;"",OR(LEN($D137)&lt;&gt;17,LEN($D137)-LEN(SUBSTITUTE($D137,":",""))&lt;&gt;5)),AND($E137&lt;&gt;"",OR(LEN($E137)&lt;&gt;17,LEN($E137)-LEN(SUBSTITUTE($E137,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6191,16 +6198,16 @@
       <c r="J138" s="24" t="n"/>
       <c r="K138" s="24" t="n"/>
       <c r="L138" s="24" t="n"/>
-      <c r="M138" s="24" t="n"/>
       <c r="N138" s="24" t="n"/>
       <c r="O138" s="24" t="n"/>
       <c r="P138" s="24" t="n"/>
       <c r="Q138" s="24" t="n"/>
-      <c r="S138">
+      <c r="R138" s="24" t="n"/>
+      <c r="T138">
         <f>IF(COUNTA($A138:$Q138)=0,0,IF(OR($B138="",$D138="",$F138="",$G138=""),1,0))</f>
         <v/>
       </c>
-      <c r="T138">
+      <c r="U138">
         <f>IF(OR(AND($D138&lt;&gt;"",OR(LEN($D138)&lt;&gt;17,LEN($D138)-LEN(SUBSTITUTE($D138,":",""))&lt;&gt;5)),AND($E138&lt;&gt;"",OR(LEN($E138)&lt;&gt;17,LEN($E138)-LEN(SUBSTITUTE($E138,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6218,16 +6225,16 @@
       <c r="J139" s="24" t="n"/>
       <c r="K139" s="24" t="n"/>
       <c r="L139" s="24" t="n"/>
-      <c r="M139" s="24" t="n"/>
       <c r="N139" s="24" t="n"/>
       <c r="O139" s="24" t="n"/>
       <c r="P139" s="24" t="n"/>
       <c r="Q139" s="24" t="n"/>
-      <c r="S139">
+      <c r="R139" s="24" t="n"/>
+      <c r="T139">
         <f>IF(COUNTA($A139:$Q139)=0,0,IF(OR($B139="",$D139="",$F139="",$G139=""),1,0))</f>
         <v/>
       </c>
-      <c r="T139">
+      <c r="U139">
         <f>IF(OR(AND($D139&lt;&gt;"",OR(LEN($D139)&lt;&gt;17,LEN($D139)-LEN(SUBSTITUTE($D139,":",""))&lt;&gt;5)),AND($E139&lt;&gt;"",OR(LEN($E139)&lt;&gt;17,LEN($E139)-LEN(SUBSTITUTE($E139,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6245,16 +6252,16 @@
       <c r="J140" s="24" t="n"/>
       <c r="K140" s="24" t="n"/>
       <c r="L140" s="24" t="n"/>
-      <c r="M140" s="24" t="n"/>
       <c r="N140" s="24" t="n"/>
       <c r="O140" s="24" t="n"/>
       <c r="P140" s="24" t="n"/>
       <c r="Q140" s="24" t="n"/>
-      <c r="S140">
+      <c r="R140" s="24" t="n"/>
+      <c r="T140">
         <f>IF(COUNTA($A140:$Q140)=0,0,IF(OR($B140="",$D140="",$F140="",$G140=""),1,0))</f>
         <v/>
       </c>
-      <c r="T140">
+      <c r="U140">
         <f>IF(OR(AND($D140&lt;&gt;"",OR(LEN($D140)&lt;&gt;17,LEN($D140)-LEN(SUBSTITUTE($D140,":",""))&lt;&gt;5)),AND($E140&lt;&gt;"",OR(LEN($E140)&lt;&gt;17,LEN($E140)-LEN(SUBSTITUTE($E140,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6272,16 +6279,16 @@
       <c r="J141" s="24" t="n"/>
       <c r="K141" s="24" t="n"/>
       <c r="L141" s="24" t="n"/>
-      <c r="M141" s="24" t="n"/>
       <c r="N141" s="24" t="n"/>
       <c r="O141" s="24" t="n"/>
       <c r="P141" s="24" t="n"/>
       <c r="Q141" s="24" t="n"/>
-      <c r="S141">
+      <c r="R141" s="24" t="n"/>
+      <c r="T141">
         <f>IF(COUNTA($A141:$Q141)=0,0,IF(OR($B141="",$D141="",$F141="",$G141=""),1,0))</f>
         <v/>
       </c>
-      <c r="T141">
+      <c r="U141">
         <f>IF(OR(AND($D141&lt;&gt;"",OR(LEN($D141)&lt;&gt;17,LEN($D141)-LEN(SUBSTITUTE($D141,":",""))&lt;&gt;5)),AND($E141&lt;&gt;"",OR(LEN($E141)&lt;&gt;17,LEN($E141)-LEN(SUBSTITUTE($E141,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6299,16 +6306,16 @@
       <c r="J142" s="24" t="n"/>
       <c r="K142" s="24" t="n"/>
       <c r="L142" s="24" t="n"/>
-      <c r="M142" s="24" t="n"/>
       <c r="N142" s="24" t="n"/>
       <c r="O142" s="24" t="n"/>
       <c r="P142" s="24" t="n"/>
       <c r="Q142" s="24" t="n"/>
-      <c r="S142">
+      <c r="R142" s="24" t="n"/>
+      <c r="T142">
         <f>IF(COUNTA($A142:$Q142)=0,0,IF(OR($B142="",$D142="",$F142="",$G142=""),1,0))</f>
         <v/>
       </c>
-      <c r="T142">
+      <c r="U142">
         <f>IF(OR(AND($D142&lt;&gt;"",OR(LEN($D142)&lt;&gt;17,LEN($D142)-LEN(SUBSTITUTE($D142,":",""))&lt;&gt;5)),AND($E142&lt;&gt;"",OR(LEN($E142)&lt;&gt;17,LEN($E142)-LEN(SUBSTITUTE($E142,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6326,16 +6333,16 @@
       <c r="J143" s="24" t="n"/>
       <c r="K143" s="24" t="n"/>
       <c r="L143" s="24" t="n"/>
-      <c r="M143" s="24" t="n"/>
       <c r="N143" s="24" t="n"/>
       <c r="O143" s="24" t="n"/>
       <c r="P143" s="24" t="n"/>
       <c r="Q143" s="24" t="n"/>
-      <c r="S143">
+      <c r="R143" s="24" t="n"/>
+      <c r="T143">
         <f>IF(COUNTA($A143:$Q143)=0,0,IF(OR($B143="",$D143="",$F143="",$G143=""),1,0))</f>
         <v/>
       </c>
-      <c r="T143">
+      <c r="U143">
         <f>IF(OR(AND($D143&lt;&gt;"",OR(LEN($D143)&lt;&gt;17,LEN($D143)-LEN(SUBSTITUTE($D143,":",""))&lt;&gt;5)),AND($E143&lt;&gt;"",OR(LEN($E143)&lt;&gt;17,LEN($E143)-LEN(SUBSTITUTE($E143,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6353,16 +6360,16 @@
       <c r="J144" s="24" t="n"/>
       <c r="K144" s="24" t="n"/>
       <c r="L144" s="24" t="n"/>
-      <c r="M144" s="24" t="n"/>
       <c r="N144" s="24" t="n"/>
       <c r="O144" s="24" t="n"/>
       <c r="P144" s="24" t="n"/>
       <c r="Q144" s="24" t="n"/>
-      <c r="S144">
+      <c r="R144" s="24" t="n"/>
+      <c r="T144">
         <f>IF(COUNTA($A144:$Q144)=0,0,IF(OR($B144="",$D144="",$F144="",$G144=""),1,0))</f>
         <v/>
       </c>
-      <c r="T144">
+      <c r="U144">
         <f>IF(OR(AND($D144&lt;&gt;"",OR(LEN($D144)&lt;&gt;17,LEN($D144)-LEN(SUBSTITUTE($D144,":",""))&lt;&gt;5)),AND($E144&lt;&gt;"",OR(LEN($E144)&lt;&gt;17,LEN($E144)-LEN(SUBSTITUTE($E144,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6380,16 +6387,16 @@
       <c r="J145" s="24" t="n"/>
       <c r="K145" s="24" t="n"/>
       <c r="L145" s="24" t="n"/>
-      <c r="M145" s="24" t="n"/>
       <c r="N145" s="24" t="n"/>
       <c r="O145" s="24" t="n"/>
       <c r="P145" s="24" t="n"/>
       <c r="Q145" s="24" t="n"/>
-      <c r="S145">
+      <c r="R145" s="24" t="n"/>
+      <c r="T145">
         <f>IF(COUNTA($A145:$Q145)=0,0,IF(OR($B145="",$D145="",$F145="",$G145=""),1,0))</f>
         <v/>
       </c>
-      <c r="T145">
+      <c r="U145">
         <f>IF(OR(AND($D145&lt;&gt;"",OR(LEN($D145)&lt;&gt;17,LEN($D145)-LEN(SUBSTITUTE($D145,":",""))&lt;&gt;5)),AND($E145&lt;&gt;"",OR(LEN($E145)&lt;&gt;17,LEN($E145)-LEN(SUBSTITUTE($E145,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6407,16 +6414,16 @@
       <c r="J146" s="24" t="n"/>
       <c r="K146" s="24" t="n"/>
       <c r="L146" s="24" t="n"/>
-      <c r="M146" s="24" t="n"/>
       <c r="N146" s="24" t="n"/>
       <c r="O146" s="24" t="n"/>
       <c r="P146" s="24" t="n"/>
       <c r="Q146" s="24" t="n"/>
-      <c r="S146">
+      <c r="R146" s="24" t="n"/>
+      <c r="T146">
         <f>IF(COUNTA($A146:$Q146)=0,0,IF(OR($B146="",$D146="",$F146="",$G146=""),1,0))</f>
         <v/>
       </c>
-      <c r="T146">
+      <c r="U146">
         <f>IF(OR(AND($D146&lt;&gt;"",OR(LEN($D146)&lt;&gt;17,LEN($D146)-LEN(SUBSTITUTE($D146,":",""))&lt;&gt;5)),AND($E146&lt;&gt;"",OR(LEN($E146)&lt;&gt;17,LEN($E146)-LEN(SUBSTITUTE($E146,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6434,16 +6441,16 @@
       <c r="J147" s="24" t="n"/>
       <c r="K147" s="24" t="n"/>
       <c r="L147" s="24" t="n"/>
-      <c r="M147" s="24" t="n"/>
       <c r="N147" s="24" t="n"/>
       <c r="O147" s="24" t="n"/>
       <c r="P147" s="24" t="n"/>
       <c r="Q147" s="24" t="n"/>
-      <c r="S147">
+      <c r="R147" s="24" t="n"/>
+      <c r="T147">
         <f>IF(COUNTA($A147:$Q147)=0,0,IF(OR($B147="",$D147="",$F147="",$G147=""),1,0))</f>
         <v/>
       </c>
-      <c r="T147">
+      <c r="U147">
         <f>IF(OR(AND($D147&lt;&gt;"",OR(LEN($D147)&lt;&gt;17,LEN($D147)-LEN(SUBSTITUTE($D147,":",""))&lt;&gt;5)),AND($E147&lt;&gt;"",OR(LEN($E147)&lt;&gt;17,LEN($E147)-LEN(SUBSTITUTE($E147,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6461,16 +6468,16 @@
       <c r="J148" s="24" t="n"/>
       <c r="K148" s="24" t="n"/>
       <c r="L148" s="24" t="n"/>
-      <c r="M148" s="24" t="n"/>
       <c r="N148" s="24" t="n"/>
       <c r="O148" s="24" t="n"/>
       <c r="P148" s="24" t="n"/>
       <c r="Q148" s="24" t="n"/>
-      <c r="S148">
+      <c r="R148" s="24" t="n"/>
+      <c r="T148">
         <f>IF(COUNTA($A148:$Q148)=0,0,IF(OR($B148="",$D148="",$F148="",$G148=""),1,0))</f>
         <v/>
       </c>
-      <c r="T148">
+      <c r="U148">
         <f>IF(OR(AND($D148&lt;&gt;"",OR(LEN($D148)&lt;&gt;17,LEN($D148)-LEN(SUBSTITUTE($D148,":",""))&lt;&gt;5)),AND($E148&lt;&gt;"",OR(LEN($E148)&lt;&gt;17,LEN($E148)-LEN(SUBSTITUTE($E148,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6488,16 +6495,16 @@
       <c r="J149" s="24" t="n"/>
       <c r="K149" s="24" t="n"/>
       <c r="L149" s="24" t="n"/>
-      <c r="M149" s="24" t="n"/>
       <c r="N149" s="24" t="n"/>
       <c r="O149" s="24" t="n"/>
       <c r="P149" s="24" t="n"/>
       <c r="Q149" s="24" t="n"/>
-      <c r="S149">
+      <c r="R149" s="24" t="n"/>
+      <c r="T149">
         <f>IF(COUNTA($A149:$Q149)=0,0,IF(OR($B149="",$D149="",$F149="",$G149=""),1,0))</f>
         <v/>
       </c>
-      <c r="T149">
+      <c r="U149">
         <f>IF(OR(AND($D149&lt;&gt;"",OR(LEN($D149)&lt;&gt;17,LEN($D149)-LEN(SUBSTITUTE($D149,":",""))&lt;&gt;5)),AND($E149&lt;&gt;"",OR(LEN($E149)&lt;&gt;17,LEN($E149)-LEN(SUBSTITUTE($E149,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6515,16 +6522,16 @@
       <c r="J150" s="24" t="n"/>
       <c r="K150" s="24" t="n"/>
       <c r="L150" s="24" t="n"/>
-      <c r="M150" s="24" t="n"/>
       <c r="N150" s="24" t="n"/>
       <c r="O150" s="24" t="n"/>
       <c r="P150" s="24" t="n"/>
       <c r="Q150" s="24" t="n"/>
-      <c r="S150">
+      <c r="R150" s="24" t="n"/>
+      <c r="T150">
         <f>IF(COUNTA($A150:$Q150)=0,0,IF(OR($B150="",$D150="",$F150="",$G150=""),1,0))</f>
         <v/>
       </c>
-      <c r="T150">
+      <c r="U150">
         <f>IF(OR(AND($D150&lt;&gt;"",OR(LEN($D150)&lt;&gt;17,LEN($D150)-LEN(SUBSTITUTE($D150,":",""))&lt;&gt;5)),AND($E150&lt;&gt;"",OR(LEN($E150)&lt;&gt;17,LEN($E150)-LEN(SUBSTITUTE($E150,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6542,16 +6549,16 @@
       <c r="J151" s="24" t="n"/>
       <c r="K151" s="24" t="n"/>
       <c r="L151" s="24" t="n"/>
-      <c r="M151" s="24" t="n"/>
       <c r="N151" s="24" t="n"/>
       <c r="O151" s="24" t="n"/>
       <c r="P151" s="24" t="n"/>
       <c r="Q151" s="24" t="n"/>
-      <c r="S151">
+      <c r="R151" s="24" t="n"/>
+      <c r="T151">
         <f>IF(COUNTA($A151:$Q151)=0,0,IF(OR($B151="",$D151="",$F151="",$G151=""),1,0))</f>
         <v/>
       </c>
-      <c r="T151">
+      <c r="U151">
         <f>IF(OR(AND($D151&lt;&gt;"",OR(LEN($D151)&lt;&gt;17,LEN($D151)-LEN(SUBSTITUTE($D151,":",""))&lt;&gt;5)),AND($E151&lt;&gt;"",OR(LEN($E151)&lt;&gt;17,LEN($E151)-LEN(SUBSTITUTE($E151,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6569,16 +6576,16 @@
       <c r="J152" s="24" t="n"/>
       <c r="K152" s="24" t="n"/>
       <c r="L152" s="24" t="n"/>
-      <c r="M152" s="24" t="n"/>
       <c r="N152" s="24" t="n"/>
       <c r="O152" s="24" t="n"/>
       <c r="P152" s="24" t="n"/>
       <c r="Q152" s="24" t="n"/>
-      <c r="S152">
+      <c r="R152" s="24" t="n"/>
+      <c r="T152">
         <f>IF(COUNTA($A152:$Q152)=0,0,IF(OR($B152="",$D152="",$F152="",$G152=""),1,0))</f>
         <v/>
       </c>
-      <c r="T152">
+      <c r="U152">
         <f>IF(OR(AND($D152&lt;&gt;"",OR(LEN($D152)&lt;&gt;17,LEN($D152)-LEN(SUBSTITUTE($D152,":",""))&lt;&gt;5)),AND($E152&lt;&gt;"",OR(LEN($E152)&lt;&gt;17,LEN($E152)-LEN(SUBSTITUTE($E152,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6596,16 +6603,16 @@
       <c r="J153" s="24" t="n"/>
       <c r="K153" s="24" t="n"/>
       <c r="L153" s="24" t="n"/>
-      <c r="M153" s="24" t="n"/>
       <c r="N153" s="24" t="n"/>
       <c r="O153" s="24" t="n"/>
       <c r="P153" s="24" t="n"/>
       <c r="Q153" s="24" t="n"/>
-      <c r="S153">
+      <c r="R153" s="24" t="n"/>
+      <c r="T153">
         <f>IF(COUNTA($A153:$Q153)=0,0,IF(OR($B153="",$D153="",$F153="",$G153=""),1,0))</f>
         <v/>
       </c>
-      <c r="T153">
+      <c r="U153">
         <f>IF(OR(AND($D153&lt;&gt;"",OR(LEN($D153)&lt;&gt;17,LEN($D153)-LEN(SUBSTITUTE($D153,":",""))&lt;&gt;5)),AND($E153&lt;&gt;"",OR(LEN($E153)&lt;&gt;17,LEN($E153)-LEN(SUBSTITUTE($E153,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6623,16 +6630,16 @@
       <c r="J154" s="24" t="n"/>
       <c r="K154" s="24" t="n"/>
       <c r="L154" s="24" t="n"/>
-      <c r="M154" s="24" t="n"/>
       <c r="N154" s="24" t="n"/>
       <c r="O154" s="24" t="n"/>
       <c r="P154" s="24" t="n"/>
       <c r="Q154" s="24" t="n"/>
-      <c r="S154">
+      <c r="R154" s="24" t="n"/>
+      <c r="T154">
         <f>IF(COUNTA($A154:$Q154)=0,0,IF(OR($B154="",$D154="",$F154="",$G154=""),1,0))</f>
         <v/>
       </c>
-      <c r="T154">
+      <c r="U154">
         <f>IF(OR(AND($D154&lt;&gt;"",OR(LEN($D154)&lt;&gt;17,LEN($D154)-LEN(SUBSTITUTE($D154,":",""))&lt;&gt;5)),AND($E154&lt;&gt;"",OR(LEN($E154)&lt;&gt;17,LEN($E154)-LEN(SUBSTITUTE($E154,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6650,16 +6657,16 @@
       <c r="J155" s="24" t="n"/>
       <c r="K155" s="24" t="n"/>
       <c r="L155" s="24" t="n"/>
-      <c r="M155" s="24" t="n"/>
       <c r="N155" s="24" t="n"/>
       <c r="O155" s="24" t="n"/>
       <c r="P155" s="24" t="n"/>
       <c r="Q155" s="24" t="n"/>
-      <c r="S155">
+      <c r="R155" s="24" t="n"/>
+      <c r="T155">
         <f>IF(COUNTA($A155:$Q155)=0,0,IF(OR($B155="",$D155="",$F155="",$G155=""),1,0))</f>
         <v/>
       </c>
-      <c r="T155">
+      <c r="U155">
         <f>IF(OR(AND($D155&lt;&gt;"",OR(LEN($D155)&lt;&gt;17,LEN($D155)-LEN(SUBSTITUTE($D155,":",""))&lt;&gt;5)),AND($E155&lt;&gt;"",OR(LEN($E155)&lt;&gt;17,LEN($E155)-LEN(SUBSTITUTE($E155,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6677,16 +6684,16 @@
       <c r="J156" s="24" t="n"/>
       <c r="K156" s="24" t="n"/>
       <c r="L156" s="24" t="n"/>
-      <c r="M156" s="24" t="n"/>
       <c r="N156" s="24" t="n"/>
       <c r="O156" s="24" t="n"/>
       <c r="P156" s="24" t="n"/>
       <c r="Q156" s="24" t="n"/>
-      <c r="S156">
+      <c r="R156" s="24" t="n"/>
+      <c r="T156">
         <f>IF(COUNTA($A156:$Q156)=0,0,IF(OR($B156="",$D156="",$F156="",$G156=""),1,0))</f>
         <v/>
       </c>
-      <c r="T156">
+      <c r="U156">
         <f>IF(OR(AND($D156&lt;&gt;"",OR(LEN($D156)&lt;&gt;17,LEN($D156)-LEN(SUBSTITUTE($D156,":",""))&lt;&gt;5)),AND($E156&lt;&gt;"",OR(LEN($E156)&lt;&gt;17,LEN($E156)-LEN(SUBSTITUTE($E156,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6704,16 +6711,16 @@
       <c r="J157" s="24" t="n"/>
       <c r="K157" s="24" t="n"/>
       <c r="L157" s="24" t="n"/>
-      <c r="M157" s="24" t="n"/>
       <c r="N157" s="24" t="n"/>
       <c r="O157" s="24" t="n"/>
       <c r="P157" s="24" t="n"/>
       <c r="Q157" s="24" t="n"/>
-      <c r="S157">
+      <c r="R157" s="24" t="n"/>
+      <c r="T157">
         <f>IF(COUNTA($A157:$Q157)=0,0,IF(OR($B157="",$D157="",$F157="",$G157=""),1,0))</f>
         <v/>
       </c>
-      <c r="T157">
+      <c r="U157">
         <f>IF(OR(AND($D157&lt;&gt;"",OR(LEN($D157)&lt;&gt;17,LEN($D157)-LEN(SUBSTITUTE($D157,":",""))&lt;&gt;5)),AND($E157&lt;&gt;"",OR(LEN($E157)&lt;&gt;17,LEN($E157)-LEN(SUBSTITUTE($E157,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6731,16 +6738,16 @@
       <c r="J158" s="24" t="n"/>
       <c r="K158" s="24" t="n"/>
       <c r="L158" s="24" t="n"/>
-      <c r="M158" s="24" t="n"/>
       <c r="N158" s="24" t="n"/>
       <c r="O158" s="24" t="n"/>
       <c r="P158" s="24" t="n"/>
       <c r="Q158" s="24" t="n"/>
-      <c r="S158">
+      <c r="R158" s="24" t="n"/>
+      <c r="T158">
         <f>IF(COUNTA($A158:$Q158)=0,0,IF(OR($B158="",$D158="",$F158="",$G158=""),1,0))</f>
         <v/>
       </c>
-      <c r="T158">
+      <c r="U158">
         <f>IF(OR(AND($D158&lt;&gt;"",OR(LEN($D158)&lt;&gt;17,LEN($D158)-LEN(SUBSTITUTE($D158,":",""))&lt;&gt;5)),AND($E158&lt;&gt;"",OR(LEN($E158)&lt;&gt;17,LEN($E158)-LEN(SUBSTITUTE($E158,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6758,16 +6765,16 @@
       <c r="J159" s="24" t="n"/>
       <c r="K159" s="24" t="n"/>
       <c r="L159" s="24" t="n"/>
-      <c r="M159" s="24" t="n"/>
       <c r="N159" s="24" t="n"/>
       <c r="O159" s="24" t="n"/>
       <c r="P159" s="24" t="n"/>
       <c r="Q159" s="24" t="n"/>
-      <c r="S159">
+      <c r="R159" s="24" t="n"/>
+      <c r="T159">
         <f>IF(COUNTA($A159:$Q159)=0,0,IF(OR($B159="",$D159="",$F159="",$G159=""),1,0))</f>
         <v/>
       </c>
-      <c r="T159">
+      <c r="U159">
         <f>IF(OR(AND($D159&lt;&gt;"",OR(LEN($D159)&lt;&gt;17,LEN($D159)-LEN(SUBSTITUTE($D159,":",""))&lt;&gt;5)),AND($E159&lt;&gt;"",OR(LEN($E159)&lt;&gt;17,LEN($E159)-LEN(SUBSTITUTE($E159,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6785,16 +6792,16 @@
       <c r="J160" s="24" t="n"/>
       <c r="K160" s="24" t="n"/>
       <c r="L160" s="24" t="n"/>
-      <c r="M160" s="24" t="n"/>
       <c r="N160" s="24" t="n"/>
       <c r="O160" s="24" t="n"/>
       <c r="P160" s="24" t="n"/>
       <c r="Q160" s="24" t="n"/>
-      <c r="S160">
+      <c r="R160" s="24" t="n"/>
+      <c r="T160">
         <f>IF(COUNTA($A160:$Q160)=0,0,IF(OR($B160="",$D160="",$F160="",$G160=""),1,0))</f>
         <v/>
       </c>
-      <c r="T160">
+      <c r="U160">
         <f>IF(OR(AND($D160&lt;&gt;"",OR(LEN($D160)&lt;&gt;17,LEN($D160)-LEN(SUBSTITUTE($D160,":",""))&lt;&gt;5)),AND($E160&lt;&gt;"",OR(LEN($E160)&lt;&gt;17,LEN($E160)-LEN(SUBSTITUTE($E160,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6812,16 +6819,16 @@
       <c r="J161" s="24" t="n"/>
       <c r="K161" s="24" t="n"/>
       <c r="L161" s="24" t="n"/>
-      <c r="M161" s="24" t="n"/>
       <c r="N161" s="24" t="n"/>
       <c r="O161" s="24" t="n"/>
       <c r="P161" s="24" t="n"/>
       <c r="Q161" s="24" t="n"/>
-      <c r="S161">
+      <c r="R161" s="24" t="n"/>
+      <c r="T161">
         <f>IF(COUNTA($A161:$Q161)=0,0,IF(OR($B161="",$D161="",$F161="",$G161=""),1,0))</f>
         <v/>
       </c>
-      <c r="T161">
+      <c r="U161">
         <f>IF(OR(AND($D161&lt;&gt;"",OR(LEN($D161)&lt;&gt;17,LEN($D161)-LEN(SUBSTITUTE($D161,":",""))&lt;&gt;5)),AND($E161&lt;&gt;"",OR(LEN($E161)&lt;&gt;17,LEN($E161)-LEN(SUBSTITUTE($E161,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6839,16 +6846,16 @@
       <c r="J162" s="24" t="n"/>
       <c r="K162" s="24" t="n"/>
       <c r="L162" s="24" t="n"/>
-      <c r="M162" s="24" t="n"/>
       <c r="N162" s="24" t="n"/>
       <c r="O162" s="24" t="n"/>
       <c r="P162" s="24" t="n"/>
       <c r="Q162" s="24" t="n"/>
-      <c r="S162">
+      <c r="R162" s="24" t="n"/>
+      <c r="T162">
         <f>IF(COUNTA($A162:$Q162)=0,0,IF(OR($B162="",$D162="",$F162="",$G162=""),1,0))</f>
         <v/>
       </c>
-      <c r="T162">
+      <c r="U162">
         <f>IF(OR(AND($D162&lt;&gt;"",OR(LEN($D162)&lt;&gt;17,LEN($D162)-LEN(SUBSTITUTE($D162,":",""))&lt;&gt;5)),AND($E162&lt;&gt;"",OR(LEN($E162)&lt;&gt;17,LEN($E162)-LEN(SUBSTITUTE($E162,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6866,16 +6873,16 @@
       <c r="J163" s="24" t="n"/>
       <c r="K163" s="24" t="n"/>
       <c r="L163" s="24" t="n"/>
-      <c r="M163" s="24" t="n"/>
       <c r="N163" s="24" t="n"/>
       <c r="O163" s="24" t="n"/>
       <c r="P163" s="24" t="n"/>
       <c r="Q163" s="24" t="n"/>
-      <c r="S163">
+      <c r="R163" s="24" t="n"/>
+      <c r="T163">
         <f>IF(COUNTA($A163:$Q163)=0,0,IF(OR($B163="",$D163="",$F163="",$G163=""),1,0))</f>
         <v/>
       </c>
-      <c r="T163">
+      <c r="U163">
         <f>IF(OR(AND($D163&lt;&gt;"",OR(LEN($D163)&lt;&gt;17,LEN($D163)-LEN(SUBSTITUTE($D163,":",""))&lt;&gt;5)),AND($E163&lt;&gt;"",OR(LEN($E163)&lt;&gt;17,LEN($E163)-LEN(SUBSTITUTE($E163,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6893,16 +6900,16 @@
       <c r="J164" s="24" t="n"/>
       <c r="K164" s="24" t="n"/>
       <c r="L164" s="24" t="n"/>
-      <c r="M164" s="24" t="n"/>
       <c r="N164" s="24" t="n"/>
       <c r="O164" s="24" t="n"/>
       <c r="P164" s="24" t="n"/>
       <c r="Q164" s="24" t="n"/>
-      <c r="S164">
+      <c r="R164" s="24" t="n"/>
+      <c r="T164">
         <f>IF(COUNTA($A164:$Q164)=0,0,IF(OR($B164="",$D164="",$F164="",$G164=""),1,0))</f>
         <v/>
       </c>
-      <c r="T164">
+      <c r="U164">
         <f>IF(OR(AND($D164&lt;&gt;"",OR(LEN($D164)&lt;&gt;17,LEN($D164)-LEN(SUBSTITUTE($D164,":",""))&lt;&gt;5)),AND($E164&lt;&gt;"",OR(LEN($E164)&lt;&gt;17,LEN($E164)-LEN(SUBSTITUTE($E164,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6920,16 +6927,16 @@
       <c r="J165" s="24" t="n"/>
       <c r="K165" s="24" t="n"/>
       <c r="L165" s="24" t="n"/>
-      <c r="M165" s="24" t="n"/>
       <c r="N165" s="24" t="n"/>
       <c r="O165" s="24" t="n"/>
       <c r="P165" s="24" t="n"/>
       <c r="Q165" s="24" t="n"/>
-      <c r="S165">
+      <c r="R165" s="24" t="n"/>
+      <c r="T165">
         <f>IF(COUNTA($A165:$Q165)=0,0,IF(OR($B165="",$D165="",$F165="",$G165=""),1,0))</f>
         <v/>
       </c>
-      <c r="T165">
+      <c r="U165">
         <f>IF(OR(AND($D165&lt;&gt;"",OR(LEN($D165)&lt;&gt;17,LEN($D165)-LEN(SUBSTITUTE($D165,":",""))&lt;&gt;5)),AND($E165&lt;&gt;"",OR(LEN($E165)&lt;&gt;17,LEN($E165)-LEN(SUBSTITUTE($E165,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6947,16 +6954,16 @@
       <c r="J166" s="24" t="n"/>
       <c r="K166" s="24" t="n"/>
       <c r="L166" s="24" t="n"/>
-      <c r="M166" s="24" t="n"/>
       <c r="N166" s="24" t="n"/>
       <c r="O166" s="24" t="n"/>
       <c r="P166" s="24" t="n"/>
       <c r="Q166" s="24" t="n"/>
-      <c r="S166">
+      <c r="R166" s="24" t="n"/>
+      <c r="T166">
         <f>IF(COUNTA($A166:$Q166)=0,0,IF(OR($B166="",$D166="",$F166="",$G166=""),1,0))</f>
         <v/>
       </c>
-      <c r="T166">
+      <c r="U166">
         <f>IF(OR(AND($D166&lt;&gt;"",OR(LEN($D166)&lt;&gt;17,LEN($D166)-LEN(SUBSTITUTE($D166,":",""))&lt;&gt;5)),AND($E166&lt;&gt;"",OR(LEN($E166)&lt;&gt;17,LEN($E166)-LEN(SUBSTITUTE($E166,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -6974,16 +6981,16 @@
       <c r="J167" s="24" t="n"/>
       <c r="K167" s="24" t="n"/>
       <c r="L167" s="24" t="n"/>
-      <c r="M167" s="24" t="n"/>
       <c r="N167" s="24" t="n"/>
       <c r="O167" s="24" t="n"/>
       <c r="P167" s="24" t="n"/>
       <c r="Q167" s="24" t="n"/>
-      <c r="S167">
+      <c r="R167" s="24" t="n"/>
+      <c r="T167">
         <f>IF(COUNTA($A167:$Q167)=0,0,IF(OR($B167="",$D167="",$F167="",$G167=""),1,0))</f>
         <v/>
       </c>
-      <c r="T167">
+      <c r="U167">
         <f>IF(OR(AND($D167&lt;&gt;"",OR(LEN($D167)&lt;&gt;17,LEN($D167)-LEN(SUBSTITUTE($D167,":",""))&lt;&gt;5)),AND($E167&lt;&gt;"",OR(LEN($E167)&lt;&gt;17,LEN($E167)-LEN(SUBSTITUTE($E167,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7001,16 +7008,16 @@
       <c r="J168" s="24" t="n"/>
       <c r="K168" s="24" t="n"/>
       <c r="L168" s="24" t="n"/>
-      <c r="M168" s="24" t="n"/>
       <c r="N168" s="24" t="n"/>
       <c r="O168" s="24" t="n"/>
       <c r="P168" s="24" t="n"/>
       <c r="Q168" s="24" t="n"/>
-      <c r="S168">
+      <c r="R168" s="24" t="n"/>
+      <c r="T168">
         <f>IF(COUNTA($A168:$Q168)=0,0,IF(OR($B168="",$D168="",$F168="",$G168=""),1,0))</f>
         <v/>
       </c>
-      <c r="T168">
+      <c r="U168">
         <f>IF(OR(AND($D168&lt;&gt;"",OR(LEN($D168)&lt;&gt;17,LEN($D168)-LEN(SUBSTITUTE($D168,":",""))&lt;&gt;5)),AND($E168&lt;&gt;"",OR(LEN($E168)&lt;&gt;17,LEN($E168)-LEN(SUBSTITUTE($E168,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7028,16 +7035,16 @@
       <c r="J169" s="24" t="n"/>
       <c r="K169" s="24" t="n"/>
       <c r="L169" s="24" t="n"/>
-      <c r="M169" s="24" t="n"/>
       <c r="N169" s="24" t="n"/>
       <c r="O169" s="24" t="n"/>
       <c r="P169" s="24" t="n"/>
       <c r="Q169" s="24" t="n"/>
-      <c r="S169">
+      <c r="R169" s="24" t="n"/>
+      <c r="T169">
         <f>IF(COUNTA($A169:$Q169)=0,0,IF(OR($B169="",$D169="",$F169="",$G169=""),1,0))</f>
         <v/>
       </c>
-      <c r="T169">
+      <c r="U169">
         <f>IF(OR(AND($D169&lt;&gt;"",OR(LEN($D169)&lt;&gt;17,LEN($D169)-LEN(SUBSTITUTE($D169,":",""))&lt;&gt;5)),AND($E169&lt;&gt;"",OR(LEN($E169)&lt;&gt;17,LEN($E169)-LEN(SUBSTITUTE($E169,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7055,16 +7062,16 @@
       <c r="J170" s="24" t="n"/>
       <c r="K170" s="24" t="n"/>
       <c r="L170" s="24" t="n"/>
-      <c r="M170" s="24" t="n"/>
       <c r="N170" s="24" t="n"/>
       <c r="O170" s="24" t="n"/>
       <c r="P170" s="24" t="n"/>
       <c r="Q170" s="24" t="n"/>
-      <c r="S170">
+      <c r="R170" s="24" t="n"/>
+      <c r="T170">
         <f>IF(COUNTA($A170:$Q170)=0,0,IF(OR($B170="",$D170="",$F170="",$G170=""),1,0))</f>
         <v/>
       </c>
-      <c r="T170">
+      <c r="U170">
         <f>IF(OR(AND($D170&lt;&gt;"",OR(LEN($D170)&lt;&gt;17,LEN($D170)-LEN(SUBSTITUTE($D170,":",""))&lt;&gt;5)),AND($E170&lt;&gt;"",OR(LEN($E170)&lt;&gt;17,LEN($E170)-LEN(SUBSTITUTE($E170,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7082,16 +7089,16 @@
       <c r="J171" s="24" t="n"/>
       <c r="K171" s="24" t="n"/>
       <c r="L171" s="24" t="n"/>
-      <c r="M171" s="24" t="n"/>
       <c r="N171" s="24" t="n"/>
       <c r="O171" s="24" t="n"/>
       <c r="P171" s="24" t="n"/>
       <c r="Q171" s="24" t="n"/>
-      <c r="S171">
+      <c r="R171" s="24" t="n"/>
+      <c r="T171">
         <f>IF(COUNTA($A171:$Q171)=0,0,IF(OR($B171="",$D171="",$F171="",$G171=""),1,0))</f>
         <v/>
       </c>
-      <c r="T171">
+      <c r="U171">
         <f>IF(OR(AND($D171&lt;&gt;"",OR(LEN($D171)&lt;&gt;17,LEN($D171)-LEN(SUBSTITUTE($D171,":",""))&lt;&gt;5)),AND($E171&lt;&gt;"",OR(LEN($E171)&lt;&gt;17,LEN($E171)-LEN(SUBSTITUTE($E171,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7109,16 +7116,16 @@
       <c r="J172" s="24" t="n"/>
       <c r="K172" s="24" t="n"/>
       <c r="L172" s="24" t="n"/>
-      <c r="M172" s="24" t="n"/>
       <c r="N172" s="24" t="n"/>
       <c r="O172" s="24" t="n"/>
       <c r="P172" s="24" t="n"/>
       <c r="Q172" s="24" t="n"/>
-      <c r="S172">
+      <c r="R172" s="24" t="n"/>
+      <c r="T172">
         <f>IF(COUNTA($A172:$Q172)=0,0,IF(OR($B172="",$D172="",$F172="",$G172=""),1,0))</f>
         <v/>
       </c>
-      <c r="T172">
+      <c r="U172">
         <f>IF(OR(AND($D172&lt;&gt;"",OR(LEN($D172)&lt;&gt;17,LEN($D172)-LEN(SUBSTITUTE($D172,":",""))&lt;&gt;5)),AND($E172&lt;&gt;"",OR(LEN($E172)&lt;&gt;17,LEN($E172)-LEN(SUBSTITUTE($E172,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7136,16 +7143,16 @@
       <c r="J173" s="24" t="n"/>
       <c r="K173" s="24" t="n"/>
       <c r="L173" s="24" t="n"/>
-      <c r="M173" s="24" t="n"/>
       <c r="N173" s="24" t="n"/>
       <c r="O173" s="24" t="n"/>
       <c r="P173" s="24" t="n"/>
       <c r="Q173" s="24" t="n"/>
-      <c r="S173">
+      <c r="R173" s="24" t="n"/>
+      <c r="T173">
         <f>IF(COUNTA($A173:$Q173)=0,0,IF(OR($B173="",$D173="",$F173="",$G173=""),1,0))</f>
         <v/>
       </c>
-      <c r="T173">
+      <c r="U173">
         <f>IF(OR(AND($D173&lt;&gt;"",OR(LEN($D173)&lt;&gt;17,LEN($D173)-LEN(SUBSTITUTE($D173,":",""))&lt;&gt;5)),AND($E173&lt;&gt;"",OR(LEN($E173)&lt;&gt;17,LEN($E173)-LEN(SUBSTITUTE($E173,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7163,16 +7170,16 @@
       <c r="J174" s="24" t="n"/>
       <c r="K174" s="24" t="n"/>
       <c r="L174" s="24" t="n"/>
-      <c r="M174" s="24" t="n"/>
       <c r="N174" s="24" t="n"/>
       <c r="O174" s="24" t="n"/>
       <c r="P174" s="24" t="n"/>
       <c r="Q174" s="24" t="n"/>
-      <c r="S174">
+      <c r="R174" s="24" t="n"/>
+      <c r="T174">
         <f>IF(COUNTA($A174:$Q174)=0,0,IF(OR($B174="",$D174="",$F174="",$G174=""),1,0))</f>
         <v/>
       </c>
-      <c r="T174">
+      <c r="U174">
         <f>IF(OR(AND($D174&lt;&gt;"",OR(LEN($D174)&lt;&gt;17,LEN($D174)-LEN(SUBSTITUTE($D174,":",""))&lt;&gt;5)),AND($E174&lt;&gt;"",OR(LEN($E174)&lt;&gt;17,LEN($E174)-LEN(SUBSTITUTE($E174,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7190,16 +7197,16 @@
       <c r="J175" s="24" t="n"/>
       <c r="K175" s="24" t="n"/>
       <c r="L175" s="24" t="n"/>
-      <c r="M175" s="24" t="n"/>
       <c r="N175" s="24" t="n"/>
       <c r="O175" s="24" t="n"/>
       <c r="P175" s="24" t="n"/>
       <c r="Q175" s="24" t="n"/>
-      <c r="S175">
+      <c r="R175" s="24" t="n"/>
+      <c r="T175">
         <f>IF(COUNTA($A175:$Q175)=0,0,IF(OR($B175="",$D175="",$F175="",$G175=""),1,0))</f>
         <v/>
       </c>
-      <c r="T175">
+      <c r="U175">
         <f>IF(OR(AND($D175&lt;&gt;"",OR(LEN($D175)&lt;&gt;17,LEN($D175)-LEN(SUBSTITUTE($D175,":",""))&lt;&gt;5)),AND($E175&lt;&gt;"",OR(LEN($E175)&lt;&gt;17,LEN($E175)-LEN(SUBSTITUTE($E175,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7217,16 +7224,16 @@
       <c r="J176" s="24" t="n"/>
       <c r="K176" s="24" t="n"/>
       <c r="L176" s="24" t="n"/>
-      <c r="M176" s="24" t="n"/>
       <c r="N176" s="24" t="n"/>
       <c r="O176" s="24" t="n"/>
       <c r="P176" s="24" t="n"/>
       <c r="Q176" s="24" t="n"/>
-      <c r="S176">
+      <c r="R176" s="24" t="n"/>
+      <c r="T176">
         <f>IF(COUNTA($A176:$Q176)=0,0,IF(OR($B176="",$D176="",$F176="",$G176=""),1,0))</f>
         <v/>
       </c>
-      <c r="T176">
+      <c r="U176">
         <f>IF(OR(AND($D176&lt;&gt;"",OR(LEN($D176)&lt;&gt;17,LEN($D176)-LEN(SUBSTITUTE($D176,":",""))&lt;&gt;5)),AND($E176&lt;&gt;"",OR(LEN($E176)&lt;&gt;17,LEN($E176)-LEN(SUBSTITUTE($E176,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7244,16 +7251,16 @@
       <c r="J177" s="24" t="n"/>
       <c r="K177" s="24" t="n"/>
       <c r="L177" s="24" t="n"/>
-      <c r="M177" s="24" t="n"/>
       <c r="N177" s="24" t="n"/>
       <c r="O177" s="24" t="n"/>
       <c r="P177" s="24" t="n"/>
       <c r="Q177" s="24" t="n"/>
-      <c r="S177">
+      <c r="R177" s="24" t="n"/>
+      <c r="T177">
         <f>IF(COUNTA($A177:$Q177)=0,0,IF(OR($B177="",$D177="",$F177="",$G177=""),1,0))</f>
         <v/>
       </c>
-      <c r="T177">
+      <c r="U177">
         <f>IF(OR(AND($D177&lt;&gt;"",OR(LEN($D177)&lt;&gt;17,LEN($D177)-LEN(SUBSTITUTE($D177,":",""))&lt;&gt;5)),AND($E177&lt;&gt;"",OR(LEN($E177)&lt;&gt;17,LEN($E177)-LEN(SUBSTITUTE($E177,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7271,16 +7278,16 @@
       <c r="J178" s="24" t="n"/>
       <c r="K178" s="24" t="n"/>
       <c r="L178" s="24" t="n"/>
-      <c r="M178" s="24" t="n"/>
       <c r="N178" s="24" t="n"/>
       <c r="O178" s="24" t="n"/>
       <c r="P178" s="24" t="n"/>
       <c r="Q178" s="24" t="n"/>
-      <c r="S178">
+      <c r="R178" s="24" t="n"/>
+      <c r="T178">
         <f>IF(COUNTA($A178:$Q178)=0,0,IF(OR($B178="",$D178="",$F178="",$G178=""),1,0))</f>
         <v/>
       </c>
-      <c r="T178">
+      <c r="U178">
         <f>IF(OR(AND($D178&lt;&gt;"",OR(LEN($D178)&lt;&gt;17,LEN($D178)-LEN(SUBSTITUTE($D178,":",""))&lt;&gt;5)),AND($E178&lt;&gt;"",OR(LEN($E178)&lt;&gt;17,LEN($E178)-LEN(SUBSTITUTE($E178,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7298,16 +7305,16 @@
       <c r="J179" s="24" t="n"/>
       <c r="K179" s="24" t="n"/>
       <c r="L179" s="24" t="n"/>
-      <c r="M179" s="24" t="n"/>
       <c r="N179" s="24" t="n"/>
       <c r="O179" s="24" t="n"/>
       <c r="P179" s="24" t="n"/>
       <c r="Q179" s="24" t="n"/>
-      <c r="S179">
+      <c r="R179" s="24" t="n"/>
+      <c r="T179">
         <f>IF(COUNTA($A179:$Q179)=0,0,IF(OR($B179="",$D179="",$F179="",$G179=""),1,0))</f>
         <v/>
       </c>
-      <c r="T179">
+      <c r="U179">
         <f>IF(OR(AND($D179&lt;&gt;"",OR(LEN($D179)&lt;&gt;17,LEN($D179)-LEN(SUBSTITUTE($D179,":",""))&lt;&gt;5)),AND($E179&lt;&gt;"",OR(LEN($E179)&lt;&gt;17,LEN($E179)-LEN(SUBSTITUTE($E179,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7325,16 +7332,16 @@
       <c r="J180" s="24" t="n"/>
       <c r="K180" s="24" t="n"/>
       <c r="L180" s="24" t="n"/>
-      <c r="M180" s="24" t="n"/>
       <c r="N180" s="24" t="n"/>
       <c r="O180" s="24" t="n"/>
       <c r="P180" s="24" t="n"/>
       <c r="Q180" s="24" t="n"/>
-      <c r="S180">
+      <c r="R180" s="24" t="n"/>
+      <c r="T180">
         <f>IF(COUNTA($A180:$Q180)=0,0,IF(OR($B180="",$D180="",$F180="",$G180=""),1,0))</f>
         <v/>
       </c>
-      <c r="T180">
+      <c r="U180">
         <f>IF(OR(AND($D180&lt;&gt;"",OR(LEN($D180)&lt;&gt;17,LEN($D180)-LEN(SUBSTITUTE($D180,":",""))&lt;&gt;5)),AND($E180&lt;&gt;"",OR(LEN($E180)&lt;&gt;17,LEN($E180)-LEN(SUBSTITUTE($E180,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7352,16 +7359,16 @@
       <c r="J181" s="24" t="n"/>
       <c r="K181" s="24" t="n"/>
       <c r="L181" s="24" t="n"/>
-      <c r="M181" s="24" t="n"/>
       <c r="N181" s="24" t="n"/>
       <c r="O181" s="24" t="n"/>
       <c r="P181" s="24" t="n"/>
       <c r="Q181" s="24" t="n"/>
-      <c r="S181">
+      <c r="R181" s="24" t="n"/>
+      <c r="T181">
         <f>IF(COUNTA($A181:$Q181)=0,0,IF(OR($B181="",$D181="",$F181="",$G181=""),1,0))</f>
         <v/>
       </c>
-      <c r="T181">
+      <c r="U181">
         <f>IF(OR(AND($D181&lt;&gt;"",OR(LEN($D181)&lt;&gt;17,LEN($D181)-LEN(SUBSTITUTE($D181,":",""))&lt;&gt;5)),AND($E181&lt;&gt;"",OR(LEN($E181)&lt;&gt;17,LEN($E181)-LEN(SUBSTITUTE($E181,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7379,16 +7386,16 @@
       <c r="J182" s="24" t="n"/>
       <c r="K182" s="24" t="n"/>
       <c r="L182" s="24" t="n"/>
-      <c r="M182" s="24" t="n"/>
       <c r="N182" s="24" t="n"/>
       <c r="O182" s="24" t="n"/>
       <c r="P182" s="24" t="n"/>
       <c r="Q182" s="24" t="n"/>
-      <c r="S182">
+      <c r="R182" s="24" t="n"/>
+      <c r="T182">
         <f>IF(COUNTA($A182:$Q182)=0,0,IF(OR($B182="",$D182="",$F182="",$G182=""),1,0))</f>
         <v/>
       </c>
-      <c r="T182">
+      <c r="U182">
         <f>IF(OR(AND($D182&lt;&gt;"",OR(LEN($D182)&lt;&gt;17,LEN($D182)-LEN(SUBSTITUTE($D182,":",""))&lt;&gt;5)),AND($E182&lt;&gt;"",OR(LEN($E182)&lt;&gt;17,LEN($E182)-LEN(SUBSTITUTE($E182,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7406,16 +7413,16 @@
       <c r="J183" s="24" t="n"/>
       <c r="K183" s="24" t="n"/>
       <c r="L183" s="24" t="n"/>
-      <c r="M183" s="24" t="n"/>
       <c r="N183" s="24" t="n"/>
       <c r="O183" s="24" t="n"/>
       <c r="P183" s="24" t="n"/>
       <c r="Q183" s="24" t="n"/>
-      <c r="S183">
+      <c r="R183" s="24" t="n"/>
+      <c r="T183">
         <f>IF(COUNTA($A183:$Q183)=0,0,IF(OR($B183="",$D183="",$F183="",$G183=""),1,0))</f>
         <v/>
       </c>
-      <c r="T183">
+      <c r="U183">
         <f>IF(OR(AND($D183&lt;&gt;"",OR(LEN($D183)&lt;&gt;17,LEN($D183)-LEN(SUBSTITUTE($D183,":",""))&lt;&gt;5)),AND($E183&lt;&gt;"",OR(LEN($E183)&lt;&gt;17,LEN($E183)-LEN(SUBSTITUTE($E183,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7433,16 +7440,16 @@
       <c r="J184" s="24" t="n"/>
       <c r="K184" s="24" t="n"/>
       <c r="L184" s="24" t="n"/>
-      <c r="M184" s="24" t="n"/>
       <c r="N184" s="24" t="n"/>
       <c r="O184" s="24" t="n"/>
       <c r="P184" s="24" t="n"/>
       <c r="Q184" s="24" t="n"/>
-      <c r="S184">
+      <c r="R184" s="24" t="n"/>
+      <c r="T184">
         <f>IF(COUNTA($A184:$Q184)=0,0,IF(OR($B184="",$D184="",$F184="",$G184=""),1,0))</f>
         <v/>
       </c>
-      <c r="T184">
+      <c r="U184">
         <f>IF(OR(AND($D184&lt;&gt;"",OR(LEN($D184)&lt;&gt;17,LEN($D184)-LEN(SUBSTITUTE($D184,":",""))&lt;&gt;5)),AND($E184&lt;&gt;"",OR(LEN($E184)&lt;&gt;17,LEN($E184)-LEN(SUBSTITUTE($E184,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7460,16 +7467,16 @@
       <c r="J185" s="24" t="n"/>
       <c r="K185" s="24" t="n"/>
       <c r="L185" s="24" t="n"/>
-      <c r="M185" s="24" t="n"/>
       <c r="N185" s="24" t="n"/>
       <c r="O185" s="24" t="n"/>
       <c r="P185" s="24" t="n"/>
       <c r="Q185" s="24" t="n"/>
-      <c r="S185">
+      <c r="R185" s="24" t="n"/>
+      <c r="T185">
         <f>IF(COUNTA($A185:$Q185)=0,0,IF(OR($B185="",$D185="",$F185="",$G185=""),1,0))</f>
         <v/>
       </c>
-      <c r="T185">
+      <c r="U185">
         <f>IF(OR(AND($D185&lt;&gt;"",OR(LEN($D185)&lt;&gt;17,LEN($D185)-LEN(SUBSTITUTE($D185,":",""))&lt;&gt;5)),AND($E185&lt;&gt;"",OR(LEN($E185)&lt;&gt;17,LEN($E185)-LEN(SUBSTITUTE($E185,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7487,16 +7494,16 @@
       <c r="J186" s="24" t="n"/>
       <c r="K186" s="24" t="n"/>
       <c r="L186" s="24" t="n"/>
-      <c r="M186" s="24" t="n"/>
       <c r="N186" s="24" t="n"/>
       <c r="O186" s="24" t="n"/>
       <c r="P186" s="24" t="n"/>
       <c r="Q186" s="24" t="n"/>
-      <c r="S186">
+      <c r="R186" s="24" t="n"/>
+      <c r="T186">
         <f>IF(COUNTA($A186:$Q186)=0,0,IF(OR($B186="",$D186="",$F186="",$G186=""),1,0))</f>
         <v/>
       </c>
-      <c r="T186">
+      <c r="U186">
         <f>IF(OR(AND($D186&lt;&gt;"",OR(LEN($D186)&lt;&gt;17,LEN($D186)-LEN(SUBSTITUTE($D186,":",""))&lt;&gt;5)),AND($E186&lt;&gt;"",OR(LEN($E186)&lt;&gt;17,LEN($E186)-LEN(SUBSTITUTE($E186,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7514,16 +7521,16 @@
       <c r="J187" s="24" t="n"/>
       <c r="K187" s="24" t="n"/>
       <c r="L187" s="24" t="n"/>
-      <c r="M187" s="24" t="n"/>
       <c r="N187" s="24" t="n"/>
       <c r="O187" s="24" t="n"/>
       <c r="P187" s="24" t="n"/>
       <c r="Q187" s="24" t="n"/>
-      <c r="S187">
+      <c r="R187" s="24" t="n"/>
+      <c r="T187">
         <f>IF(COUNTA($A187:$Q187)=0,0,IF(OR($B187="",$D187="",$F187="",$G187=""),1,0))</f>
         <v/>
       </c>
-      <c r="T187">
+      <c r="U187">
         <f>IF(OR(AND($D187&lt;&gt;"",OR(LEN($D187)&lt;&gt;17,LEN($D187)-LEN(SUBSTITUTE($D187,":",""))&lt;&gt;5)),AND($E187&lt;&gt;"",OR(LEN($E187)&lt;&gt;17,LEN($E187)-LEN(SUBSTITUTE($E187,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7541,16 +7548,16 @@
       <c r="J188" s="24" t="n"/>
       <c r="K188" s="24" t="n"/>
       <c r="L188" s="24" t="n"/>
-      <c r="M188" s="24" t="n"/>
       <c r="N188" s="24" t="n"/>
       <c r="O188" s="24" t="n"/>
       <c r="P188" s="24" t="n"/>
       <c r="Q188" s="24" t="n"/>
-      <c r="S188">
+      <c r="R188" s="24" t="n"/>
+      <c r="T188">
         <f>IF(COUNTA($A188:$Q188)=0,0,IF(OR($B188="",$D188="",$F188="",$G188=""),1,0))</f>
         <v/>
       </c>
-      <c r="T188">
+      <c r="U188">
         <f>IF(OR(AND($D188&lt;&gt;"",OR(LEN($D188)&lt;&gt;17,LEN($D188)-LEN(SUBSTITUTE($D188,":",""))&lt;&gt;5)),AND($E188&lt;&gt;"",OR(LEN($E188)&lt;&gt;17,LEN($E188)-LEN(SUBSTITUTE($E188,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7568,16 +7575,16 @@
       <c r="J189" s="24" t="n"/>
       <c r="K189" s="24" t="n"/>
       <c r="L189" s="24" t="n"/>
-      <c r="M189" s="24" t="n"/>
       <c r="N189" s="24" t="n"/>
       <c r="O189" s="24" t="n"/>
       <c r="P189" s="24" t="n"/>
       <c r="Q189" s="24" t="n"/>
-      <c r="S189">
+      <c r="R189" s="24" t="n"/>
+      <c r="T189">
         <f>IF(COUNTA($A189:$Q189)=0,0,IF(OR($B189="",$D189="",$F189="",$G189=""),1,0))</f>
         <v/>
       </c>
-      <c r="T189">
+      <c r="U189">
         <f>IF(OR(AND($D189&lt;&gt;"",OR(LEN($D189)&lt;&gt;17,LEN($D189)-LEN(SUBSTITUTE($D189,":",""))&lt;&gt;5)),AND($E189&lt;&gt;"",OR(LEN($E189)&lt;&gt;17,LEN($E189)-LEN(SUBSTITUTE($E189,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7595,16 +7602,16 @@
       <c r="J190" s="24" t="n"/>
       <c r="K190" s="24" t="n"/>
       <c r="L190" s="24" t="n"/>
-      <c r="M190" s="24" t="n"/>
       <c r="N190" s="24" t="n"/>
       <c r="O190" s="24" t="n"/>
       <c r="P190" s="24" t="n"/>
       <c r="Q190" s="24" t="n"/>
-      <c r="S190">
+      <c r="R190" s="24" t="n"/>
+      <c r="T190">
         <f>IF(COUNTA($A190:$Q190)=0,0,IF(OR($B190="",$D190="",$F190="",$G190=""),1,0))</f>
         <v/>
       </c>
-      <c r="T190">
+      <c r="U190">
         <f>IF(OR(AND($D190&lt;&gt;"",OR(LEN($D190)&lt;&gt;17,LEN($D190)-LEN(SUBSTITUTE($D190,":",""))&lt;&gt;5)),AND($E190&lt;&gt;"",OR(LEN($E190)&lt;&gt;17,LEN($E190)-LEN(SUBSTITUTE($E190,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7622,16 +7629,16 @@
       <c r="J191" s="24" t="n"/>
       <c r="K191" s="24" t="n"/>
       <c r="L191" s="24" t="n"/>
-      <c r="M191" s="24" t="n"/>
       <c r="N191" s="24" t="n"/>
       <c r="O191" s="24" t="n"/>
       <c r="P191" s="24" t="n"/>
       <c r="Q191" s="24" t="n"/>
-      <c r="S191">
+      <c r="R191" s="24" t="n"/>
+      <c r="T191">
         <f>IF(COUNTA($A191:$Q191)=0,0,IF(OR($B191="",$D191="",$F191="",$G191=""),1,0))</f>
         <v/>
       </c>
-      <c r="T191">
+      <c r="U191">
         <f>IF(OR(AND($D191&lt;&gt;"",OR(LEN($D191)&lt;&gt;17,LEN($D191)-LEN(SUBSTITUTE($D191,":",""))&lt;&gt;5)),AND($E191&lt;&gt;"",OR(LEN($E191)&lt;&gt;17,LEN($E191)-LEN(SUBSTITUTE($E191,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7649,16 +7656,16 @@
       <c r="J192" s="24" t="n"/>
       <c r="K192" s="24" t="n"/>
       <c r="L192" s="24" t="n"/>
-      <c r="M192" s="24" t="n"/>
       <c r="N192" s="24" t="n"/>
       <c r="O192" s="24" t="n"/>
       <c r="P192" s="24" t="n"/>
       <c r="Q192" s="24" t="n"/>
-      <c r="S192">
+      <c r="R192" s="24" t="n"/>
+      <c r="T192">
         <f>IF(COUNTA($A192:$Q192)=0,0,IF(OR($B192="",$D192="",$F192="",$G192=""),1,0))</f>
         <v/>
       </c>
-      <c r="T192">
+      <c r="U192">
         <f>IF(OR(AND($D192&lt;&gt;"",OR(LEN($D192)&lt;&gt;17,LEN($D192)-LEN(SUBSTITUTE($D192,":",""))&lt;&gt;5)),AND($E192&lt;&gt;"",OR(LEN($E192)&lt;&gt;17,LEN($E192)-LEN(SUBSTITUTE($E192,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7676,16 +7683,16 @@
       <c r="J193" s="24" t="n"/>
       <c r="K193" s="24" t="n"/>
       <c r="L193" s="24" t="n"/>
-      <c r="M193" s="24" t="n"/>
       <c r="N193" s="24" t="n"/>
       <c r="O193" s="24" t="n"/>
       <c r="P193" s="24" t="n"/>
       <c r="Q193" s="24" t="n"/>
-      <c r="S193">
+      <c r="R193" s="24" t="n"/>
+      <c r="T193">
         <f>IF(COUNTA($A193:$Q193)=0,0,IF(OR($B193="",$D193="",$F193="",$G193=""),1,0))</f>
         <v/>
       </c>
-      <c r="T193">
+      <c r="U193">
         <f>IF(OR(AND($D193&lt;&gt;"",OR(LEN($D193)&lt;&gt;17,LEN($D193)-LEN(SUBSTITUTE($D193,":",""))&lt;&gt;5)),AND($E193&lt;&gt;"",OR(LEN($E193)&lt;&gt;17,LEN($E193)-LEN(SUBSTITUTE($E193,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7703,16 +7710,16 @@
       <c r="J194" s="24" t="n"/>
       <c r="K194" s="24" t="n"/>
       <c r="L194" s="24" t="n"/>
-      <c r="M194" s="24" t="n"/>
       <c r="N194" s="24" t="n"/>
       <c r="O194" s="24" t="n"/>
       <c r="P194" s="24" t="n"/>
       <c r="Q194" s="24" t="n"/>
-      <c r="S194">
+      <c r="R194" s="24" t="n"/>
+      <c r="T194">
         <f>IF(COUNTA($A194:$Q194)=0,0,IF(OR($B194="",$D194="",$F194="",$G194=""),1,0))</f>
         <v/>
       </c>
-      <c r="T194">
+      <c r="U194">
         <f>IF(OR(AND($D194&lt;&gt;"",OR(LEN($D194)&lt;&gt;17,LEN($D194)-LEN(SUBSTITUTE($D194,":",""))&lt;&gt;5)),AND($E194&lt;&gt;"",OR(LEN($E194)&lt;&gt;17,LEN($E194)-LEN(SUBSTITUTE($E194,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7730,16 +7737,16 @@
       <c r="J195" s="24" t="n"/>
       <c r="K195" s="24" t="n"/>
       <c r="L195" s="24" t="n"/>
-      <c r="M195" s="24" t="n"/>
       <c r="N195" s="24" t="n"/>
       <c r="O195" s="24" t="n"/>
       <c r="P195" s="24" t="n"/>
       <c r="Q195" s="24" t="n"/>
-      <c r="S195">
+      <c r="R195" s="24" t="n"/>
+      <c r="T195">
         <f>IF(COUNTA($A195:$Q195)=0,0,IF(OR($B195="",$D195="",$F195="",$G195=""),1,0))</f>
         <v/>
       </c>
-      <c r="T195">
+      <c r="U195">
         <f>IF(OR(AND($D195&lt;&gt;"",OR(LEN($D195)&lt;&gt;17,LEN($D195)-LEN(SUBSTITUTE($D195,":",""))&lt;&gt;5)),AND($E195&lt;&gt;"",OR(LEN($E195)&lt;&gt;17,LEN($E195)-LEN(SUBSTITUTE($E195,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7757,16 +7764,16 @@
       <c r="J196" s="24" t="n"/>
       <c r="K196" s="24" t="n"/>
       <c r="L196" s="24" t="n"/>
-      <c r="M196" s="24" t="n"/>
       <c r="N196" s="24" t="n"/>
       <c r="O196" s="24" t="n"/>
       <c r="P196" s="24" t="n"/>
       <c r="Q196" s="24" t="n"/>
-      <c r="S196">
+      <c r="R196" s="24" t="n"/>
+      <c r="T196">
         <f>IF(COUNTA($A196:$Q196)=0,0,IF(OR($B196="",$D196="",$F196="",$G196=""),1,0))</f>
         <v/>
       </c>
-      <c r="T196">
+      <c r="U196">
         <f>IF(OR(AND($D196&lt;&gt;"",OR(LEN($D196)&lt;&gt;17,LEN($D196)-LEN(SUBSTITUTE($D196,":",""))&lt;&gt;5)),AND($E196&lt;&gt;"",OR(LEN($E196)&lt;&gt;17,LEN($E196)-LEN(SUBSTITUTE($E196,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7784,16 +7791,16 @@
       <c r="J197" s="24" t="n"/>
       <c r="K197" s="24" t="n"/>
       <c r="L197" s="24" t="n"/>
-      <c r="M197" s="24" t="n"/>
       <c r="N197" s="24" t="n"/>
       <c r="O197" s="24" t="n"/>
       <c r="P197" s="24" t="n"/>
       <c r="Q197" s="24" t="n"/>
-      <c r="S197">
+      <c r="R197" s="24" t="n"/>
+      <c r="T197">
         <f>IF(COUNTA($A197:$Q197)=0,0,IF(OR($B197="",$D197="",$F197="",$G197=""),1,0))</f>
         <v/>
       </c>
-      <c r="T197">
+      <c r="U197">
         <f>IF(OR(AND($D197&lt;&gt;"",OR(LEN($D197)&lt;&gt;17,LEN($D197)-LEN(SUBSTITUTE($D197,":",""))&lt;&gt;5)),AND($E197&lt;&gt;"",OR(LEN($E197)&lt;&gt;17,LEN($E197)-LEN(SUBSTITUTE($E197,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7811,16 +7818,16 @@
       <c r="J198" s="24" t="n"/>
       <c r="K198" s="24" t="n"/>
       <c r="L198" s="24" t="n"/>
-      <c r="M198" s="24" t="n"/>
       <c r="N198" s="24" t="n"/>
       <c r="O198" s="24" t="n"/>
       <c r="P198" s="24" t="n"/>
       <c r="Q198" s="24" t="n"/>
-      <c r="S198">
+      <c r="R198" s="24" t="n"/>
+      <c r="T198">
         <f>IF(COUNTA($A198:$Q198)=0,0,IF(OR($B198="",$D198="",$F198="",$G198=""),1,0))</f>
         <v/>
       </c>
-      <c r="T198">
+      <c r="U198">
         <f>IF(OR(AND($D198&lt;&gt;"",OR(LEN($D198)&lt;&gt;17,LEN($D198)-LEN(SUBSTITUTE($D198,":",""))&lt;&gt;5)),AND($E198&lt;&gt;"",OR(LEN($E198)&lt;&gt;17,LEN($E198)-LEN(SUBSTITUTE($E198,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7838,16 +7845,16 @@
       <c r="J199" s="24" t="n"/>
       <c r="K199" s="24" t="n"/>
       <c r="L199" s="24" t="n"/>
-      <c r="M199" s="24" t="n"/>
       <c r="N199" s="24" t="n"/>
       <c r="O199" s="24" t="n"/>
       <c r="P199" s="24" t="n"/>
       <c r="Q199" s="24" t="n"/>
-      <c r="S199">
+      <c r="R199" s="24" t="n"/>
+      <c r="T199">
         <f>IF(COUNTA($A199:$Q199)=0,0,IF(OR($B199="",$D199="",$F199="",$G199=""),1,0))</f>
         <v/>
       </c>
-      <c r="T199">
+      <c r="U199">
         <f>IF(OR(AND($D199&lt;&gt;"",OR(LEN($D199)&lt;&gt;17,LEN($D199)-LEN(SUBSTITUTE($D199,":",""))&lt;&gt;5)),AND($E199&lt;&gt;"",OR(LEN($E199)&lt;&gt;17,LEN($E199)-LEN(SUBSTITUTE($E199,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7865,16 +7872,16 @@
       <c r="J200" s="24" t="n"/>
       <c r="K200" s="24" t="n"/>
       <c r="L200" s="24" t="n"/>
-      <c r="M200" s="24" t="n"/>
       <c r="N200" s="24" t="n"/>
       <c r="O200" s="24" t="n"/>
       <c r="P200" s="24" t="n"/>
       <c r="Q200" s="24" t="n"/>
-      <c r="S200">
+      <c r="R200" s="24" t="n"/>
+      <c r="T200">
         <f>IF(COUNTA($A200:$Q200)=0,0,IF(OR($B200="",$D200="",$F200="",$G200=""),1,0))</f>
         <v/>
       </c>
-      <c r="T200">
+      <c r="U200">
         <f>IF(OR(AND($D200&lt;&gt;"",OR(LEN($D200)&lt;&gt;17,LEN($D200)-LEN(SUBSTITUTE($D200,":",""))&lt;&gt;5)),AND($E200&lt;&gt;"",OR(LEN($E200)&lt;&gt;17,LEN($E200)-LEN(SUBSTITUTE($E200,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7892,16 +7899,16 @@
       <c r="J201" s="24" t="n"/>
       <c r="K201" s="24" t="n"/>
       <c r="L201" s="24" t="n"/>
-      <c r="M201" s="24" t="n"/>
       <c r="N201" s="24" t="n"/>
       <c r="O201" s="24" t="n"/>
       <c r="P201" s="24" t="n"/>
       <c r="Q201" s="24" t="n"/>
-      <c r="S201">
+      <c r="R201" s="24" t="n"/>
+      <c r="T201">
         <f>IF(COUNTA($A201:$Q201)=0,0,IF(OR($B201="",$D201="",$F201="",$G201=""),1,0))</f>
         <v/>
       </c>
-      <c r="T201">
+      <c r="U201">
         <f>IF(OR(AND($D201&lt;&gt;"",OR(LEN($D201)&lt;&gt;17,LEN($D201)-LEN(SUBSTITUTE($D201,":",""))&lt;&gt;5)),AND($E201&lt;&gt;"",OR(LEN($E201)&lt;&gt;17,LEN($E201)-LEN(SUBSTITUTE($E201,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7919,16 +7926,16 @@
       <c r="J202" s="24" t="n"/>
       <c r="K202" s="24" t="n"/>
       <c r="L202" s="24" t="n"/>
-      <c r="M202" s="24" t="n"/>
       <c r="N202" s="24" t="n"/>
       <c r="O202" s="24" t="n"/>
       <c r="P202" s="24" t="n"/>
       <c r="Q202" s="24" t="n"/>
-      <c r="S202">
+      <c r="R202" s="24" t="n"/>
+      <c r="T202">
         <f>IF(COUNTA($A202:$Q202)=0,0,IF(OR($B202="",$D202="",$F202="",$G202=""),1,0))</f>
         <v/>
       </c>
-      <c r="T202">
+      <c r="U202">
         <f>IF(OR(AND($D202&lt;&gt;"",OR(LEN($D202)&lt;&gt;17,LEN($D202)-LEN(SUBSTITUTE($D202,":",""))&lt;&gt;5)),AND($E202&lt;&gt;"",OR(LEN($E202)&lt;&gt;17,LEN($E202)-LEN(SUBSTITUTE($E202,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7946,16 +7953,16 @@
       <c r="J203" s="24" t="n"/>
       <c r="K203" s="24" t="n"/>
       <c r="L203" s="24" t="n"/>
-      <c r="M203" s="24" t="n"/>
       <c r="N203" s="24" t="n"/>
       <c r="O203" s="24" t="n"/>
       <c r="P203" s="24" t="n"/>
       <c r="Q203" s="24" t="n"/>
-      <c r="S203">
+      <c r="R203" s="24" t="n"/>
+      <c r="T203">
         <f>IF(COUNTA($A203:$Q203)=0,0,IF(OR($B203="",$D203="",$F203="",$G203=""),1,0))</f>
         <v/>
       </c>
-      <c r="T203">
+      <c r="U203">
         <f>IF(OR(AND($D203&lt;&gt;"",OR(LEN($D203)&lt;&gt;17,LEN($D203)-LEN(SUBSTITUTE($D203,":",""))&lt;&gt;5)),AND($E203&lt;&gt;"",OR(LEN($E203)&lt;&gt;17,LEN($E203)-LEN(SUBSTITUTE($E203,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -7973,16 +7980,16 @@
       <c r="J204" s="24" t="n"/>
       <c r="K204" s="24" t="n"/>
       <c r="L204" s="24" t="n"/>
-      <c r="M204" s="24" t="n"/>
       <c r="N204" s="24" t="n"/>
       <c r="O204" s="24" t="n"/>
       <c r="P204" s="24" t="n"/>
       <c r="Q204" s="24" t="n"/>
-      <c r="S204">
+      <c r="R204" s="24" t="n"/>
+      <c r="T204">
         <f>IF(COUNTA($A204:$Q204)=0,0,IF(OR($B204="",$D204="",$F204="",$G204=""),1,0))</f>
         <v/>
       </c>
-      <c r="T204">
+      <c r="U204">
         <f>IF(OR(AND($D204&lt;&gt;"",OR(LEN($D204)&lt;&gt;17,LEN($D204)-LEN(SUBSTITUTE($D204,":",""))&lt;&gt;5)),AND($E204&lt;&gt;"",OR(LEN($E204)&lt;&gt;17,LEN($E204)-LEN(SUBSTITUTE($E204,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8000,16 +8007,16 @@
       <c r="J205" s="24" t="n"/>
       <c r="K205" s="24" t="n"/>
       <c r="L205" s="24" t="n"/>
-      <c r="M205" s="24" t="n"/>
       <c r="N205" s="24" t="n"/>
       <c r="O205" s="24" t="n"/>
       <c r="P205" s="24" t="n"/>
       <c r="Q205" s="24" t="n"/>
-      <c r="S205">
+      <c r="R205" s="24" t="n"/>
+      <c r="T205">
         <f>IF(COUNTA($A205:$Q205)=0,0,IF(OR($B205="",$D205="",$F205="",$G205=""),1,0))</f>
         <v/>
       </c>
-      <c r="T205">
+      <c r="U205">
         <f>IF(OR(AND($D205&lt;&gt;"",OR(LEN($D205)&lt;&gt;17,LEN($D205)-LEN(SUBSTITUTE($D205,":",""))&lt;&gt;5)),AND($E205&lt;&gt;"",OR(LEN($E205)&lt;&gt;17,LEN($E205)-LEN(SUBSTITUTE($E205,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8027,16 +8034,16 @@
       <c r="J206" s="24" t="n"/>
       <c r="K206" s="24" t="n"/>
       <c r="L206" s="24" t="n"/>
-      <c r="M206" s="24" t="n"/>
       <c r="N206" s="24" t="n"/>
       <c r="O206" s="24" t="n"/>
       <c r="P206" s="24" t="n"/>
       <c r="Q206" s="24" t="n"/>
-      <c r="S206">
+      <c r="R206" s="24" t="n"/>
+      <c r="T206">
         <f>IF(COUNTA($A206:$Q206)=0,0,IF(OR($B206="",$D206="",$F206="",$G206=""),1,0))</f>
         <v/>
       </c>
-      <c r="T206">
+      <c r="U206">
         <f>IF(OR(AND($D206&lt;&gt;"",OR(LEN($D206)&lt;&gt;17,LEN($D206)-LEN(SUBSTITUTE($D206,":",""))&lt;&gt;5)),AND($E206&lt;&gt;"",OR(LEN($E206)&lt;&gt;17,LEN($E206)-LEN(SUBSTITUTE($E206,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8054,16 +8061,16 @@
       <c r="J207" s="24" t="n"/>
       <c r="K207" s="24" t="n"/>
       <c r="L207" s="24" t="n"/>
-      <c r="M207" s="24" t="n"/>
       <c r="N207" s="24" t="n"/>
       <c r="O207" s="24" t="n"/>
       <c r="P207" s="24" t="n"/>
       <c r="Q207" s="24" t="n"/>
-      <c r="S207">
+      <c r="R207" s="24" t="n"/>
+      <c r="T207">
         <f>IF(COUNTA($A207:$Q207)=0,0,IF(OR($B207="",$D207="",$F207="",$G207=""),1,0))</f>
         <v/>
       </c>
-      <c r="T207">
+      <c r="U207">
         <f>IF(OR(AND($D207&lt;&gt;"",OR(LEN($D207)&lt;&gt;17,LEN($D207)-LEN(SUBSTITUTE($D207,":",""))&lt;&gt;5)),AND($E207&lt;&gt;"",OR(LEN($E207)&lt;&gt;17,LEN($E207)-LEN(SUBSTITUTE($E207,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8081,16 +8088,16 @@
       <c r="J208" s="24" t="n"/>
       <c r="K208" s="24" t="n"/>
       <c r="L208" s="24" t="n"/>
-      <c r="M208" s="24" t="n"/>
       <c r="N208" s="24" t="n"/>
       <c r="O208" s="24" t="n"/>
       <c r="P208" s="24" t="n"/>
       <c r="Q208" s="24" t="n"/>
-      <c r="S208">
+      <c r="R208" s="24" t="n"/>
+      <c r="T208">
         <f>IF(COUNTA($A208:$Q208)=0,0,IF(OR($B208="",$D208="",$F208="",$G208=""),1,0))</f>
         <v/>
       </c>
-      <c r="T208">
+      <c r="U208">
         <f>IF(OR(AND($D208&lt;&gt;"",OR(LEN($D208)&lt;&gt;17,LEN($D208)-LEN(SUBSTITUTE($D208,":",""))&lt;&gt;5)),AND($E208&lt;&gt;"",OR(LEN($E208)&lt;&gt;17,LEN($E208)-LEN(SUBSTITUTE($E208,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8108,16 +8115,16 @@
       <c r="J209" s="24" t="n"/>
       <c r="K209" s="24" t="n"/>
       <c r="L209" s="24" t="n"/>
-      <c r="M209" s="24" t="n"/>
       <c r="N209" s="24" t="n"/>
       <c r="O209" s="24" t="n"/>
       <c r="P209" s="24" t="n"/>
       <c r="Q209" s="24" t="n"/>
-      <c r="S209">
+      <c r="R209" s="24" t="n"/>
+      <c r="T209">
         <f>IF(COUNTA($A209:$Q209)=0,0,IF(OR($B209="",$D209="",$F209="",$G209=""),1,0))</f>
         <v/>
       </c>
-      <c r="T209">
+      <c r="U209">
         <f>IF(OR(AND($D209&lt;&gt;"",OR(LEN($D209)&lt;&gt;17,LEN($D209)-LEN(SUBSTITUTE($D209,":",""))&lt;&gt;5)),AND($E209&lt;&gt;"",OR(LEN($E209)&lt;&gt;17,LEN($E209)-LEN(SUBSTITUTE($E209,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8135,16 +8142,16 @@
       <c r="J210" s="24" t="n"/>
       <c r="K210" s="24" t="n"/>
       <c r="L210" s="24" t="n"/>
-      <c r="M210" s="24" t="n"/>
       <c r="N210" s="24" t="n"/>
       <c r="O210" s="24" t="n"/>
       <c r="P210" s="24" t="n"/>
       <c r="Q210" s="24" t="n"/>
-      <c r="S210">
+      <c r="R210" s="24" t="n"/>
+      <c r="T210">
         <f>IF(COUNTA($A210:$Q210)=0,0,IF(OR($B210="",$D210="",$F210="",$G210=""),1,0))</f>
         <v/>
       </c>
-      <c r="T210">
+      <c r="U210">
         <f>IF(OR(AND($D210&lt;&gt;"",OR(LEN($D210)&lt;&gt;17,LEN($D210)-LEN(SUBSTITUTE($D210,":",""))&lt;&gt;5)),AND($E210&lt;&gt;"",OR(LEN($E210)&lt;&gt;17,LEN($E210)-LEN(SUBSTITUTE($E210,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8162,16 +8169,16 @@
       <c r="J211" s="24" t="n"/>
       <c r="K211" s="24" t="n"/>
       <c r="L211" s="24" t="n"/>
-      <c r="M211" s="24" t="n"/>
       <c r="N211" s="24" t="n"/>
       <c r="O211" s="24" t="n"/>
       <c r="P211" s="24" t="n"/>
       <c r="Q211" s="24" t="n"/>
-      <c r="S211">
+      <c r="R211" s="24" t="n"/>
+      <c r="T211">
         <f>IF(COUNTA($A211:$Q211)=0,0,IF(OR($B211="",$D211="",$F211="",$G211=""),1,0))</f>
         <v/>
       </c>
-      <c r="T211">
+      <c r="U211">
         <f>IF(OR(AND($D211&lt;&gt;"",OR(LEN($D211)&lt;&gt;17,LEN($D211)-LEN(SUBSTITUTE($D211,":",""))&lt;&gt;5)),AND($E211&lt;&gt;"",OR(LEN($E211)&lt;&gt;17,LEN($E211)-LEN(SUBSTITUTE($E211,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8189,16 +8196,16 @@
       <c r="J212" s="24" t="n"/>
       <c r="K212" s="24" t="n"/>
       <c r="L212" s="24" t="n"/>
-      <c r="M212" s="24" t="n"/>
       <c r="N212" s="24" t="n"/>
       <c r="O212" s="24" t="n"/>
       <c r="P212" s="24" t="n"/>
       <c r="Q212" s="24" t="n"/>
-      <c r="S212">
+      <c r="R212" s="24" t="n"/>
+      <c r="T212">
         <f>IF(COUNTA($A212:$Q212)=0,0,IF(OR($B212="",$D212="",$F212="",$G212=""),1,0))</f>
         <v/>
       </c>
-      <c r="T212">
+      <c r="U212">
         <f>IF(OR(AND($D212&lt;&gt;"",OR(LEN($D212)&lt;&gt;17,LEN($D212)-LEN(SUBSTITUTE($D212,":",""))&lt;&gt;5)),AND($E212&lt;&gt;"",OR(LEN($E212)&lt;&gt;17,LEN($E212)-LEN(SUBSTITUTE($E212,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8216,16 +8223,16 @@
       <c r="J213" s="24" t="n"/>
       <c r="K213" s="24" t="n"/>
       <c r="L213" s="24" t="n"/>
-      <c r="M213" s="24" t="n"/>
       <c r="N213" s="24" t="n"/>
       <c r="O213" s="24" t="n"/>
       <c r="P213" s="24" t="n"/>
       <c r="Q213" s="24" t="n"/>
-      <c r="S213">
+      <c r="R213" s="24" t="n"/>
+      <c r="T213">
         <f>IF(COUNTA($A213:$Q213)=0,0,IF(OR($B213="",$D213="",$F213="",$G213=""),1,0))</f>
         <v/>
       </c>
-      <c r="T213">
+      <c r="U213">
         <f>IF(OR(AND($D213&lt;&gt;"",OR(LEN($D213)&lt;&gt;17,LEN($D213)-LEN(SUBSTITUTE($D213,":",""))&lt;&gt;5)),AND($E213&lt;&gt;"",OR(LEN($E213)&lt;&gt;17,LEN($E213)-LEN(SUBSTITUTE($E213,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8243,16 +8250,16 @@
       <c r="J214" s="24" t="n"/>
       <c r="K214" s="24" t="n"/>
       <c r="L214" s="24" t="n"/>
-      <c r="M214" s="24" t="n"/>
       <c r="N214" s="24" t="n"/>
       <c r="O214" s="24" t="n"/>
       <c r="P214" s="24" t="n"/>
       <c r="Q214" s="24" t="n"/>
-      <c r="S214">
+      <c r="R214" s="24" t="n"/>
+      <c r="T214">
         <f>IF(COUNTA($A214:$Q214)=0,0,IF(OR($B214="",$D214="",$F214="",$G214=""),1,0))</f>
         <v/>
       </c>
-      <c r="T214">
+      <c r="U214">
         <f>IF(OR(AND($D214&lt;&gt;"",OR(LEN($D214)&lt;&gt;17,LEN($D214)-LEN(SUBSTITUTE($D214,":",""))&lt;&gt;5)),AND($E214&lt;&gt;"",OR(LEN($E214)&lt;&gt;17,LEN($E214)-LEN(SUBSTITUTE($E214,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8270,16 +8277,16 @@
       <c r="J215" s="24" t="n"/>
       <c r="K215" s="24" t="n"/>
       <c r="L215" s="24" t="n"/>
-      <c r="M215" s="24" t="n"/>
       <c r="N215" s="24" t="n"/>
       <c r="O215" s="24" t="n"/>
       <c r="P215" s="24" t="n"/>
       <c r="Q215" s="24" t="n"/>
-      <c r="S215">
+      <c r="R215" s="24" t="n"/>
+      <c r="T215">
         <f>IF(COUNTA($A215:$Q215)=0,0,IF(OR($B215="",$D215="",$F215="",$G215=""),1,0))</f>
         <v/>
       </c>
-      <c r="T215">
+      <c r="U215">
         <f>IF(OR(AND($D215&lt;&gt;"",OR(LEN($D215)&lt;&gt;17,LEN($D215)-LEN(SUBSTITUTE($D215,":",""))&lt;&gt;5)),AND($E215&lt;&gt;"",OR(LEN($E215)&lt;&gt;17,LEN($E215)-LEN(SUBSTITUTE($E215,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8297,16 +8304,16 @@
       <c r="J216" s="24" t="n"/>
       <c r="K216" s="24" t="n"/>
       <c r="L216" s="24" t="n"/>
-      <c r="M216" s="24" t="n"/>
       <c r="N216" s="24" t="n"/>
       <c r="O216" s="24" t="n"/>
       <c r="P216" s="24" t="n"/>
       <c r="Q216" s="24" t="n"/>
-      <c r="S216">
+      <c r="R216" s="24" t="n"/>
+      <c r="T216">
         <f>IF(COUNTA($A216:$Q216)=0,0,IF(OR($B216="",$D216="",$F216="",$G216=""),1,0))</f>
         <v/>
       </c>
-      <c r="T216">
+      <c r="U216">
         <f>IF(OR(AND($D216&lt;&gt;"",OR(LEN($D216)&lt;&gt;17,LEN($D216)-LEN(SUBSTITUTE($D216,":",""))&lt;&gt;5)),AND($E216&lt;&gt;"",OR(LEN($E216)&lt;&gt;17,LEN($E216)-LEN(SUBSTITUTE($E216,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8324,16 +8331,16 @@
       <c r="J217" s="24" t="n"/>
       <c r="K217" s="24" t="n"/>
       <c r="L217" s="24" t="n"/>
-      <c r="M217" s="24" t="n"/>
       <c r="N217" s="24" t="n"/>
       <c r="O217" s="24" t="n"/>
       <c r="P217" s="24" t="n"/>
       <c r="Q217" s="24" t="n"/>
-      <c r="S217">
+      <c r="R217" s="24" t="n"/>
+      <c r="T217">
         <f>IF(COUNTA($A217:$Q217)=0,0,IF(OR($B217="",$D217="",$F217="",$G217=""),1,0))</f>
         <v/>
       </c>
-      <c r="T217">
+      <c r="U217">
         <f>IF(OR(AND($D217&lt;&gt;"",OR(LEN($D217)&lt;&gt;17,LEN($D217)-LEN(SUBSTITUTE($D217,":",""))&lt;&gt;5)),AND($E217&lt;&gt;"",OR(LEN($E217)&lt;&gt;17,LEN($E217)-LEN(SUBSTITUTE($E217,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8351,16 +8358,16 @@
       <c r="J218" s="24" t="n"/>
       <c r="K218" s="24" t="n"/>
       <c r="L218" s="24" t="n"/>
-      <c r="M218" s="24" t="n"/>
       <c r="N218" s="24" t="n"/>
       <c r="O218" s="24" t="n"/>
       <c r="P218" s="24" t="n"/>
       <c r="Q218" s="24" t="n"/>
-      <c r="S218">
+      <c r="R218" s="24" t="n"/>
+      <c r="T218">
         <f>IF(COUNTA($A218:$Q218)=0,0,IF(OR($B218="",$D218="",$F218="",$G218=""),1,0))</f>
         <v/>
       </c>
-      <c r="T218">
+      <c r="U218">
         <f>IF(OR(AND($D218&lt;&gt;"",OR(LEN($D218)&lt;&gt;17,LEN($D218)-LEN(SUBSTITUTE($D218,":",""))&lt;&gt;5)),AND($E218&lt;&gt;"",OR(LEN($E218)&lt;&gt;17,LEN($E218)-LEN(SUBSTITUTE($E218,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8378,16 +8385,16 @@
       <c r="J219" s="24" t="n"/>
       <c r="K219" s="24" t="n"/>
       <c r="L219" s="24" t="n"/>
-      <c r="M219" s="24" t="n"/>
       <c r="N219" s="24" t="n"/>
       <c r="O219" s="24" t="n"/>
       <c r="P219" s="24" t="n"/>
       <c r="Q219" s="24" t="n"/>
-      <c r="S219">
+      <c r="R219" s="24" t="n"/>
+      <c r="T219">
         <f>IF(COUNTA($A219:$Q219)=0,0,IF(OR($B219="",$D219="",$F219="",$G219=""),1,0))</f>
         <v/>
       </c>
-      <c r="T219">
+      <c r="U219">
         <f>IF(OR(AND($D219&lt;&gt;"",OR(LEN($D219)&lt;&gt;17,LEN($D219)-LEN(SUBSTITUTE($D219,":",""))&lt;&gt;5)),AND($E219&lt;&gt;"",OR(LEN($E219)&lt;&gt;17,LEN($E219)-LEN(SUBSTITUTE($E219,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8405,16 +8412,16 @@
       <c r="J220" s="24" t="n"/>
       <c r="K220" s="24" t="n"/>
       <c r="L220" s="24" t="n"/>
-      <c r="M220" s="24" t="n"/>
       <c r="N220" s="24" t="n"/>
       <c r="O220" s="24" t="n"/>
       <c r="P220" s="24" t="n"/>
       <c r="Q220" s="24" t="n"/>
-      <c r="S220">
+      <c r="R220" s="24" t="n"/>
+      <c r="T220">
         <f>IF(COUNTA($A220:$Q220)=0,0,IF(OR($B220="",$D220="",$F220="",$G220=""),1,0))</f>
         <v/>
       </c>
-      <c r="T220">
+      <c r="U220">
         <f>IF(OR(AND($D220&lt;&gt;"",OR(LEN($D220)&lt;&gt;17,LEN($D220)-LEN(SUBSTITUTE($D220,":",""))&lt;&gt;5)),AND($E220&lt;&gt;"",OR(LEN($E220)&lt;&gt;17,LEN($E220)-LEN(SUBSTITUTE($E220,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8432,16 +8439,16 @@
       <c r="J221" s="24" t="n"/>
       <c r="K221" s="24" t="n"/>
       <c r="L221" s="24" t="n"/>
-      <c r="M221" s="24" t="n"/>
       <c r="N221" s="24" t="n"/>
       <c r="O221" s="24" t="n"/>
       <c r="P221" s="24" t="n"/>
       <c r="Q221" s="24" t="n"/>
-      <c r="S221">
+      <c r="R221" s="24" t="n"/>
+      <c r="T221">
         <f>IF(COUNTA($A221:$Q221)=0,0,IF(OR($B221="",$D221="",$F221="",$G221=""),1,0))</f>
         <v/>
       </c>
-      <c r="T221">
+      <c r="U221">
         <f>IF(OR(AND($D221&lt;&gt;"",OR(LEN($D221)&lt;&gt;17,LEN($D221)-LEN(SUBSTITUTE($D221,":",""))&lt;&gt;5)),AND($E221&lt;&gt;"",OR(LEN($E221)&lt;&gt;17,LEN($E221)-LEN(SUBSTITUTE($E221,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8459,16 +8466,16 @@
       <c r="J222" s="24" t="n"/>
       <c r="K222" s="24" t="n"/>
       <c r="L222" s="24" t="n"/>
-      <c r="M222" s="24" t="n"/>
       <c r="N222" s="24" t="n"/>
       <c r="O222" s="24" t="n"/>
       <c r="P222" s="24" t="n"/>
       <c r="Q222" s="24" t="n"/>
-      <c r="S222">
+      <c r="R222" s="24" t="n"/>
+      <c r="T222">
         <f>IF(COUNTA($A222:$Q222)=0,0,IF(OR($B222="",$D222="",$F222="",$G222=""),1,0))</f>
         <v/>
       </c>
-      <c r="T222">
+      <c r="U222">
         <f>IF(OR(AND($D222&lt;&gt;"",OR(LEN($D222)&lt;&gt;17,LEN($D222)-LEN(SUBSTITUTE($D222,":",""))&lt;&gt;5)),AND($E222&lt;&gt;"",OR(LEN($E222)&lt;&gt;17,LEN($E222)-LEN(SUBSTITUTE($E222,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8486,16 +8493,16 @@
       <c r="J223" s="24" t="n"/>
       <c r="K223" s="24" t="n"/>
       <c r="L223" s="24" t="n"/>
-      <c r="M223" s="24" t="n"/>
       <c r="N223" s="24" t="n"/>
       <c r="O223" s="24" t="n"/>
       <c r="P223" s="24" t="n"/>
       <c r="Q223" s="24" t="n"/>
-      <c r="S223">
+      <c r="R223" s="24" t="n"/>
+      <c r="T223">
         <f>IF(COUNTA($A223:$Q223)=0,0,IF(OR($B223="",$D223="",$F223="",$G223=""),1,0))</f>
         <v/>
       </c>
-      <c r="T223">
+      <c r="U223">
         <f>IF(OR(AND($D223&lt;&gt;"",OR(LEN($D223)&lt;&gt;17,LEN($D223)-LEN(SUBSTITUTE($D223,":",""))&lt;&gt;5)),AND($E223&lt;&gt;"",OR(LEN($E223)&lt;&gt;17,LEN($E223)-LEN(SUBSTITUTE($E223,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8513,16 +8520,16 @@
       <c r="J224" s="24" t="n"/>
       <c r="K224" s="24" t="n"/>
       <c r="L224" s="24" t="n"/>
-      <c r="M224" s="24" t="n"/>
       <c r="N224" s="24" t="n"/>
       <c r="O224" s="24" t="n"/>
       <c r="P224" s="24" t="n"/>
       <c r="Q224" s="24" t="n"/>
-      <c r="S224">
+      <c r="R224" s="24" t="n"/>
+      <c r="T224">
         <f>IF(COUNTA($A224:$Q224)=0,0,IF(OR($B224="",$D224="",$F224="",$G224=""),1,0))</f>
         <v/>
       </c>
-      <c r="T224">
+      <c r="U224">
         <f>IF(OR(AND($D224&lt;&gt;"",OR(LEN($D224)&lt;&gt;17,LEN($D224)-LEN(SUBSTITUTE($D224,":",""))&lt;&gt;5)),AND($E224&lt;&gt;"",OR(LEN($E224)&lt;&gt;17,LEN($E224)-LEN(SUBSTITUTE($E224,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8540,16 +8547,16 @@
       <c r="J225" s="24" t="n"/>
       <c r="K225" s="24" t="n"/>
       <c r="L225" s="24" t="n"/>
-      <c r="M225" s="24" t="n"/>
       <c r="N225" s="24" t="n"/>
       <c r="O225" s="24" t="n"/>
       <c r="P225" s="24" t="n"/>
       <c r="Q225" s="24" t="n"/>
-      <c r="S225">
+      <c r="R225" s="24" t="n"/>
+      <c r="T225">
         <f>IF(COUNTA($A225:$Q225)=0,0,IF(OR($B225="",$D225="",$F225="",$G225=""),1,0))</f>
         <v/>
       </c>
-      <c r="T225">
+      <c r="U225">
         <f>IF(OR(AND($D225&lt;&gt;"",OR(LEN($D225)&lt;&gt;17,LEN($D225)-LEN(SUBSTITUTE($D225,":",""))&lt;&gt;5)),AND($E225&lt;&gt;"",OR(LEN($E225)&lt;&gt;17,LEN($E225)-LEN(SUBSTITUTE($E225,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8567,16 +8574,16 @@
       <c r="J226" s="24" t="n"/>
       <c r="K226" s="24" t="n"/>
       <c r="L226" s="24" t="n"/>
-      <c r="M226" s="24" t="n"/>
       <c r="N226" s="24" t="n"/>
       <c r="O226" s="24" t="n"/>
       <c r="P226" s="24" t="n"/>
       <c r="Q226" s="24" t="n"/>
-      <c r="S226">
+      <c r="R226" s="24" t="n"/>
+      <c r="T226">
         <f>IF(COUNTA($A226:$Q226)=0,0,IF(OR($B226="",$D226="",$F226="",$G226=""),1,0))</f>
         <v/>
       </c>
-      <c r="T226">
+      <c r="U226">
         <f>IF(OR(AND($D226&lt;&gt;"",OR(LEN($D226)&lt;&gt;17,LEN($D226)-LEN(SUBSTITUTE($D226,":",""))&lt;&gt;5)),AND($E226&lt;&gt;"",OR(LEN($E226)&lt;&gt;17,LEN($E226)-LEN(SUBSTITUTE($E226,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8594,16 +8601,16 @@
       <c r="J227" s="24" t="n"/>
       <c r="K227" s="24" t="n"/>
       <c r="L227" s="24" t="n"/>
-      <c r="M227" s="24" t="n"/>
       <c r="N227" s="24" t="n"/>
       <c r="O227" s="24" t="n"/>
       <c r="P227" s="24" t="n"/>
       <c r="Q227" s="24" t="n"/>
-      <c r="S227">
+      <c r="R227" s="24" t="n"/>
+      <c r="T227">
         <f>IF(COUNTA($A227:$Q227)=0,0,IF(OR($B227="",$D227="",$F227="",$G227=""),1,0))</f>
         <v/>
       </c>
-      <c r="T227">
+      <c r="U227">
         <f>IF(OR(AND($D227&lt;&gt;"",OR(LEN($D227)&lt;&gt;17,LEN($D227)-LEN(SUBSTITUTE($D227,":",""))&lt;&gt;5)),AND($E227&lt;&gt;"",OR(LEN($E227)&lt;&gt;17,LEN($E227)-LEN(SUBSTITUTE($E227,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8621,16 +8628,16 @@
       <c r="J228" s="24" t="n"/>
       <c r="K228" s="24" t="n"/>
       <c r="L228" s="24" t="n"/>
-      <c r="M228" s="24" t="n"/>
       <c r="N228" s="24" t="n"/>
       <c r="O228" s="24" t="n"/>
       <c r="P228" s="24" t="n"/>
       <c r="Q228" s="24" t="n"/>
-      <c r="S228">
+      <c r="R228" s="24" t="n"/>
+      <c r="T228">
         <f>IF(COUNTA($A228:$Q228)=0,0,IF(OR($B228="",$D228="",$F228="",$G228=""),1,0))</f>
         <v/>
       </c>
-      <c r="T228">
+      <c r="U228">
         <f>IF(OR(AND($D228&lt;&gt;"",OR(LEN($D228)&lt;&gt;17,LEN($D228)-LEN(SUBSTITUTE($D228,":",""))&lt;&gt;5)),AND($E228&lt;&gt;"",OR(LEN($E228)&lt;&gt;17,LEN($E228)-LEN(SUBSTITUTE($E228,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8648,16 +8655,16 @@
       <c r="J229" s="24" t="n"/>
       <c r="K229" s="24" t="n"/>
       <c r="L229" s="24" t="n"/>
-      <c r="M229" s="24" t="n"/>
       <c r="N229" s="24" t="n"/>
       <c r="O229" s="24" t="n"/>
       <c r="P229" s="24" t="n"/>
       <c r="Q229" s="24" t="n"/>
-      <c r="S229">
+      <c r="R229" s="24" t="n"/>
+      <c r="T229">
         <f>IF(COUNTA($A229:$Q229)=0,0,IF(OR($B229="",$D229="",$F229="",$G229=""),1,0))</f>
         <v/>
       </c>
-      <c r="T229">
+      <c r="U229">
         <f>IF(OR(AND($D229&lt;&gt;"",OR(LEN($D229)&lt;&gt;17,LEN($D229)-LEN(SUBSTITUTE($D229,":",""))&lt;&gt;5)),AND($E229&lt;&gt;"",OR(LEN($E229)&lt;&gt;17,LEN($E229)-LEN(SUBSTITUTE($E229,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8675,16 +8682,16 @@
       <c r="J230" s="24" t="n"/>
       <c r="K230" s="24" t="n"/>
       <c r="L230" s="24" t="n"/>
-      <c r="M230" s="24" t="n"/>
       <c r="N230" s="24" t="n"/>
       <c r="O230" s="24" t="n"/>
       <c r="P230" s="24" t="n"/>
       <c r="Q230" s="24" t="n"/>
-      <c r="S230">
+      <c r="R230" s="24" t="n"/>
+      <c r="T230">
         <f>IF(COUNTA($A230:$Q230)=0,0,IF(OR($B230="",$D230="",$F230="",$G230=""),1,0))</f>
         <v/>
       </c>
-      <c r="T230">
+      <c r="U230">
         <f>IF(OR(AND($D230&lt;&gt;"",OR(LEN($D230)&lt;&gt;17,LEN($D230)-LEN(SUBSTITUTE($D230,":",""))&lt;&gt;5)),AND($E230&lt;&gt;"",OR(LEN($E230)&lt;&gt;17,LEN($E230)-LEN(SUBSTITUTE($E230,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8702,16 +8709,16 @@
       <c r="J231" s="24" t="n"/>
       <c r="K231" s="24" t="n"/>
       <c r="L231" s="24" t="n"/>
-      <c r="M231" s="24" t="n"/>
       <c r="N231" s="24" t="n"/>
       <c r="O231" s="24" t="n"/>
       <c r="P231" s="24" t="n"/>
       <c r="Q231" s="24" t="n"/>
-      <c r="S231">
+      <c r="R231" s="24" t="n"/>
+      <c r="T231">
         <f>IF(COUNTA($A231:$Q231)=0,0,IF(OR($B231="",$D231="",$F231="",$G231=""),1,0))</f>
         <v/>
       </c>
-      <c r="T231">
+      <c r="U231">
         <f>IF(OR(AND($D231&lt;&gt;"",OR(LEN($D231)&lt;&gt;17,LEN($D231)-LEN(SUBSTITUTE($D231,":",""))&lt;&gt;5)),AND($E231&lt;&gt;"",OR(LEN($E231)&lt;&gt;17,LEN($E231)-LEN(SUBSTITUTE($E231,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8729,16 +8736,16 @@
       <c r="J232" s="24" t="n"/>
       <c r="K232" s="24" t="n"/>
       <c r="L232" s="24" t="n"/>
-      <c r="M232" s="24" t="n"/>
       <c r="N232" s="24" t="n"/>
       <c r="O232" s="24" t="n"/>
       <c r="P232" s="24" t="n"/>
       <c r="Q232" s="24" t="n"/>
-      <c r="S232">
+      <c r="R232" s="24" t="n"/>
+      <c r="T232">
         <f>IF(COUNTA($A232:$Q232)=0,0,IF(OR($B232="",$D232="",$F232="",$G232=""),1,0))</f>
         <v/>
       </c>
-      <c r="T232">
+      <c r="U232">
         <f>IF(OR(AND($D232&lt;&gt;"",OR(LEN($D232)&lt;&gt;17,LEN($D232)-LEN(SUBSTITUTE($D232,":",""))&lt;&gt;5)),AND($E232&lt;&gt;"",OR(LEN($E232)&lt;&gt;17,LEN($E232)-LEN(SUBSTITUTE($E232,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8756,16 +8763,16 @@
       <c r="J233" s="24" t="n"/>
       <c r="K233" s="24" t="n"/>
       <c r="L233" s="24" t="n"/>
-      <c r="M233" s="24" t="n"/>
       <c r="N233" s="24" t="n"/>
       <c r="O233" s="24" t="n"/>
       <c r="P233" s="24" t="n"/>
       <c r="Q233" s="24" t="n"/>
-      <c r="S233">
+      <c r="R233" s="24" t="n"/>
+      <c r="T233">
         <f>IF(COUNTA($A233:$Q233)=0,0,IF(OR($B233="",$D233="",$F233="",$G233=""),1,0))</f>
         <v/>
       </c>
-      <c r="T233">
+      <c r="U233">
         <f>IF(OR(AND($D233&lt;&gt;"",OR(LEN($D233)&lt;&gt;17,LEN($D233)-LEN(SUBSTITUTE($D233,":",""))&lt;&gt;5)),AND($E233&lt;&gt;"",OR(LEN($E233)&lt;&gt;17,LEN($E233)-LEN(SUBSTITUTE($E233,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8783,16 +8790,16 @@
       <c r="J234" s="24" t="n"/>
       <c r="K234" s="24" t="n"/>
       <c r="L234" s="24" t="n"/>
-      <c r="M234" s="24" t="n"/>
       <c r="N234" s="24" t="n"/>
       <c r="O234" s="24" t="n"/>
       <c r="P234" s="24" t="n"/>
       <c r="Q234" s="24" t="n"/>
-      <c r="S234">
+      <c r="R234" s="24" t="n"/>
+      <c r="T234">
         <f>IF(COUNTA($A234:$Q234)=0,0,IF(OR($B234="",$D234="",$F234="",$G234=""),1,0))</f>
         <v/>
       </c>
-      <c r="T234">
+      <c r="U234">
         <f>IF(OR(AND($D234&lt;&gt;"",OR(LEN($D234)&lt;&gt;17,LEN($D234)-LEN(SUBSTITUTE($D234,":",""))&lt;&gt;5)),AND($E234&lt;&gt;"",OR(LEN($E234)&lt;&gt;17,LEN($E234)-LEN(SUBSTITUTE($E234,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8810,16 +8817,16 @@
       <c r="J235" s="24" t="n"/>
       <c r="K235" s="24" t="n"/>
       <c r="L235" s="24" t="n"/>
-      <c r="M235" s="24" t="n"/>
       <c r="N235" s="24" t="n"/>
       <c r="O235" s="24" t="n"/>
       <c r="P235" s="24" t="n"/>
       <c r="Q235" s="24" t="n"/>
-      <c r="S235">
+      <c r="R235" s="24" t="n"/>
+      <c r="T235">
         <f>IF(COUNTA($A235:$Q235)=0,0,IF(OR($B235="",$D235="",$F235="",$G235=""),1,0))</f>
         <v/>
       </c>
-      <c r="T235">
+      <c r="U235">
         <f>IF(OR(AND($D235&lt;&gt;"",OR(LEN($D235)&lt;&gt;17,LEN($D235)-LEN(SUBSTITUTE($D235,":",""))&lt;&gt;5)),AND($E235&lt;&gt;"",OR(LEN($E235)&lt;&gt;17,LEN($E235)-LEN(SUBSTITUTE($E235,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8837,16 +8844,16 @@
       <c r="J236" s="24" t="n"/>
       <c r="K236" s="24" t="n"/>
       <c r="L236" s="24" t="n"/>
-      <c r="M236" s="24" t="n"/>
       <c r="N236" s="24" t="n"/>
       <c r="O236" s="24" t="n"/>
       <c r="P236" s="24" t="n"/>
       <c r="Q236" s="24" t="n"/>
-      <c r="S236">
+      <c r="R236" s="24" t="n"/>
+      <c r="T236">
         <f>IF(COUNTA($A236:$Q236)=0,0,IF(OR($B236="",$D236="",$F236="",$G236=""),1,0))</f>
         <v/>
       </c>
-      <c r="T236">
+      <c r="U236">
         <f>IF(OR(AND($D236&lt;&gt;"",OR(LEN($D236)&lt;&gt;17,LEN($D236)-LEN(SUBSTITUTE($D236,":",""))&lt;&gt;5)),AND($E236&lt;&gt;"",OR(LEN($E236)&lt;&gt;17,LEN($E236)-LEN(SUBSTITUTE($E236,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8864,16 +8871,16 @@
       <c r="J237" s="24" t="n"/>
       <c r="K237" s="24" t="n"/>
       <c r="L237" s="24" t="n"/>
-      <c r="M237" s="24" t="n"/>
       <c r="N237" s="24" t="n"/>
       <c r="O237" s="24" t="n"/>
       <c r="P237" s="24" t="n"/>
       <c r="Q237" s="24" t="n"/>
-      <c r="S237">
+      <c r="R237" s="24" t="n"/>
+      <c r="T237">
         <f>IF(COUNTA($A237:$Q237)=0,0,IF(OR($B237="",$D237="",$F237="",$G237=""),1,0))</f>
         <v/>
       </c>
-      <c r="T237">
+      <c r="U237">
         <f>IF(OR(AND($D237&lt;&gt;"",OR(LEN($D237)&lt;&gt;17,LEN($D237)-LEN(SUBSTITUTE($D237,":",""))&lt;&gt;5)),AND($E237&lt;&gt;"",OR(LEN($E237)&lt;&gt;17,LEN($E237)-LEN(SUBSTITUTE($E237,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8891,16 +8898,16 @@
       <c r="J238" s="24" t="n"/>
       <c r="K238" s="24" t="n"/>
       <c r="L238" s="24" t="n"/>
-      <c r="M238" s="24" t="n"/>
       <c r="N238" s="24" t="n"/>
       <c r="O238" s="24" t="n"/>
       <c r="P238" s="24" t="n"/>
       <c r="Q238" s="24" t="n"/>
-      <c r="S238">
+      <c r="R238" s="24" t="n"/>
+      <c r="T238">
         <f>IF(COUNTA($A238:$Q238)=0,0,IF(OR($B238="",$D238="",$F238="",$G238=""),1,0))</f>
         <v/>
       </c>
-      <c r="T238">
+      <c r="U238">
         <f>IF(OR(AND($D238&lt;&gt;"",OR(LEN($D238)&lt;&gt;17,LEN($D238)-LEN(SUBSTITUTE($D238,":",""))&lt;&gt;5)),AND($E238&lt;&gt;"",OR(LEN($E238)&lt;&gt;17,LEN($E238)-LEN(SUBSTITUTE($E238,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8918,16 +8925,16 @@
       <c r="J239" s="24" t="n"/>
       <c r="K239" s="24" t="n"/>
       <c r="L239" s="24" t="n"/>
-      <c r="M239" s="24" t="n"/>
       <c r="N239" s="24" t="n"/>
       <c r="O239" s="24" t="n"/>
       <c r="P239" s="24" t="n"/>
       <c r="Q239" s="24" t="n"/>
-      <c r="S239">
+      <c r="R239" s="24" t="n"/>
+      <c r="T239">
         <f>IF(COUNTA($A239:$Q239)=0,0,IF(OR($B239="",$D239="",$F239="",$G239=""),1,0))</f>
         <v/>
       </c>
-      <c r="T239">
+      <c r="U239">
         <f>IF(OR(AND($D239&lt;&gt;"",OR(LEN($D239)&lt;&gt;17,LEN($D239)-LEN(SUBSTITUTE($D239,":",""))&lt;&gt;5)),AND($E239&lt;&gt;"",OR(LEN($E239)&lt;&gt;17,LEN($E239)-LEN(SUBSTITUTE($E239,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8945,16 +8952,16 @@
       <c r="J240" s="24" t="n"/>
       <c r="K240" s="24" t="n"/>
       <c r="L240" s="24" t="n"/>
-      <c r="M240" s="24" t="n"/>
       <c r="N240" s="24" t="n"/>
       <c r="O240" s="24" t="n"/>
       <c r="P240" s="24" t="n"/>
       <c r="Q240" s="24" t="n"/>
-      <c r="S240">
+      <c r="R240" s="24" t="n"/>
+      <c r="T240">
         <f>IF(COUNTA($A240:$Q240)=0,0,IF(OR($B240="",$D240="",$F240="",$G240=""),1,0))</f>
         <v/>
       </c>
-      <c r="T240">
+      <c r="U240">
         <f>IF(OR(AND($D240&lt;&gt;"",OR(LEN($D240)&lt;&gt;17,LEN($D240)-LEN(SUBSTITUTE($D240,":",""))&lt;&gt;5)),AND($E240&lt;&gt;"",OR(LEN($E240)&lt;&gt;17,LEN($E240)-LEN(SUBSTITUTE($E240,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8972,16 +8979,16 @@
       <c r="J241" s="24" t="n"/>
       <c r="K241" s="24" t="n"/>
       <c r="L241" s="24" t="n"/>
-      <c r="M241" s="24" t="n"/>
       <c r="N241" s="24" t="n"/>
       <c r="O241" s="24" t="n"/>
       <c r="P241" s="24" t="n"/>
       <c r="Q241" s="24" t="n"/>
-      <c r="S241">
+      <c r="R241" s="24" t="n"/>
+      <c r="T241">
         <f>IF(COUNTA($A241:$Q241)=0,0,IF(OR($B241="",$D241="",$F241="",$G241=""),1,0))</f>
         <v/>
       </c>
-      <c r="T241">
+      <c r="U241">
         <f>IF(OR(AND($D241&lt;&gt;"",OR(LEN($D241)&lt;&gt;17,LEN($D241)-LEN(SUBSTITUTE($D241,":",""))&lt;&gt;5)),AND($E241&lt;&gt;"",OR(LEN($E241)&lt;&gt;17,LEN($E241)-LEN(SUBSTITUTE($E241,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -8999,16 +9006,16 @@
       <c r="J242" s="24" t="n"/>
       <c r="K242" s="24" t="n"/>
       <c r="L242" s="24" t="n"/>
-      <c r="M242" s="24" t="n"/>
       <c r="N242" s="24" t="n"/>
       <c r="O242" s="24" t="n"/>
       <c r="P242" s="24" t="n"/>
       <c r="Q242" s="24" t="n"/>
-      <c r="S242">
+      <c r="R242" s="24" t="n"/>
+      <c r="T242">
         <f>IF(COUNTA($A242:$Q242)=0,0,IF(OR($B242="",$D242="",$F242="",$G242=""),1,0))</f>
         <v/>
       </c>
-      <c r="T242">
+      <c r="U242">
         <f>IF(OR(AND($D242&lt;&gt;"",OR(LEN($D242)&lt;&gt;17,LEN($D242)-LEN(SUBSTITUTE($D242,":",""))&lt;&gt;5)),AND($E242&lt;&gt;"",OR(LEN($E242)&lt;&gt;17,LEN($E242)-LEN(SUBSTITUTE($E242,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -9026,16 +9033,16 @@
       <c r="J243" s="24" t="n"/>
       <c r="K243" s="24" t="n"/>
       <c r="L243" s="24" t="n"/>
-      <c r="M243" s="24" t="n"/>
       <c r="N243" s="24" t="n"/>
       <c r="O243" s="24" t="n"/>
       <c r="P243" s="24" t="n"/>
       <c r="Q243" s="24" t="n"/>
-      <c r="S243">
+      <c r="R243" s="24" t="n"/>
+      <c r="T243">
         <f>IF(COUNTA($A243:$Q243)=0,0,IF(OR($B243="",$D243="",$F243="",$G243=""),1,0))</f>
         <v/>
       </c>
-      <c r="T243">
+      <c r="U243">
         <f>IF(OR(AND($D243&lt;&gt;"",OR(LEN($D243)&lt;&gt;17,LEN($D243)-LEN(SUBSTITUTE($D243,":",""))&lt;&gt;5)),AND($E243&lt;&gt;"",OR(LEN($E243)&lt;&gt;17,LEN($E243)-LEN(SUBSTITUTE($E243,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -9053,16 +9060,16 @@
       <c r="J244" s="24" t="n"/>
       <c r="K244" s="24" t="n"/>
       <c r="L244" s="24" t="n"/>
-      <c r="M244" s="24" t="n"/>
       <c r="N244" s="24" t="n"/>
       <c r="O244" s="24" t="n"/>
       <c r="P244" s="24" t="n"/>
       <c r="Q244" s="24" t="n"/>
-      <c r="S244">
+      <c r="R244" s="24" t="n"/>
+      <c r="T244">
         <f>IF(COUNTA($A244:$Q244)=0,0,IF(OR($B244="",$D244="",$F244="",$G244=""),1,0))</f>
         <v/>
       </c>
-      <c r="T244">
+      <c r="U244">
         <f>IF(OR(AND($D244&lt;&gt;"",OR(LEN($D244)&lt;&gt;17,LEN($D244)-LEN(SUBSTITUTE($D244,":",""))&lt;&gt;5)),AND($E244&lt;&gt;"",OR(LEN($E244)&lt;&gt;17,LEN($E244)-LEN(SUBSTITUTE($E244,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -9080,16 +9087,16 @@
       <c r="J245" s="24" t="n"/>
       <c r="K245" s="24" t="n"/>
       <c r="L245" s="24" t="n"/>
-      <c r="M245" s="24" t="n"/>
       <c r="N245" s="24" t="n"/>
       <c r="O245" s="24" t="n"/>
       <c r="P245" s="24" t="n"/>
       <c r="Q245" s="24" t="n"/>
-      <c r="S245">
+      <c r="R245" s="24" t="n"/>
+      <c r="T245">
         <f>IF(COUNTA($A245:$Q245)=0,0,IF(OR($B245="",$D245="",$F245="",$G245=""),1,0))</f>
         <v/>
       </c>
-      <c r="T245">
+      <c r="U245">
         <f>IF(OR(AND($D245&lt;&gt;"",OR(LEN($D245)&lt;&gt;17,LEN($D245)-LEN(SUBSTITUTE($D245,":",""))&lt;&gt;5)),AND($E245&lt;&gt;"",OR(LEN($E245)&lt;&gt;17,LEN($E245)-LEN(SUBSTITUTE($E245,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -9107,16 +9114,16 @@
       <c r="J246" s="24" t="n"/>
       <c r="K246" s="24" t="n"/>
       <c r="L246" s="24" t="n"/>
-      <c r="M246" s="24" t="n"/>
       <c r="N246" s="24" t="n"/>
       <c r="O246" s="24" t="n"/>
       <c r="P246" s="24" t="n"/>
       <c r="Q246" s="24" t="n"/>
-      <c r="S246">
+      <c r="R246" s="24" t="n"/>
+      <c r="T246">
         <f>IF(COUNTA($A246:$Q246)=0,0,IF(OR($B246="",$D246="",$F246="",$G246=""),1,0))</f>
         <v/>
       </c>
-      <c r="T246">
+      <c r="U246">
         <f>IF(OR(AND($D246&lt;&gt;"",OR(LEN($D246)&lt;&gt;17,LEN($D246)-LEN(SUBSTITUTE($D246,":",""))&lt;&gt;5)),AND($E246&lt;&gt;"",OR(LEN($E246)&lt;&gt;17,LEN($E246)-LEN(SUBSTITUTE($E246,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -9134,16 +9141,16 @@
       <c r="J247" s="24" t="n"/>
       <c r="K247" s="24" t="n"/>
       <c r="L247" s="24" t="n"/>
-      <c r="M247" s="24" t="n"/>
       <c r="N247" s="24" t="n"/>
       <c r="O247" s="24" t="n"/>
       <c r="P247" s="24" t="n"/>
       <c r="Q247" s="24" t="n"/>
-      <c r="S247">
+      <c r="R247" s="24" t="n"/>
+      <c r="T247">
         <f>IF(COUNTA($A247:$Q247)=0,0,IF(OR($B247="",$D247="",$F247="",$G247=""),1,0))</f>
         <v/>
       </c>
-      <c r="T247">
+      <c r="U247">
         <f>IF(OR(AND($D247&lt;&gt;"",OR(LEN($D247)&lt;&gt;17,LEN($D247)-LEN(SUBSTITUTE($D247,":",""))&lt;&gt;5)),AND($E247&lt;&gt;"",OR(LEN($E247)&lt;&gt;17,LEN($E247)-LEN(SUBSTITUTE($E247,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -9161,16 +9168,16 @@
       <c r="J248" s="24" t="n"/>
       <c r="K248" s="24" t="n"/>
       <c r="L248" s="24" t="n"/>
-      <c r="M248" s="24" t="n"/>
       <c r="N248" s="24" t="n"/>
       <c r="O248" s="24" t="n"/>
       <c r="P248" s="24" t="n"/>
       <c r="Q248" s="24" t="n"/>
-      <c r="S248">
+      <c r="R248" s="24" t="n"/>
+      <c r="T248">
         <f>IF(COUNTA($A248:$Q248)=0,0,IF(OR($B248="",$D248="",$F248="",$G248=""),1,0))</f>
         <v/>
       </c>
-      <c r="T248">
+      <c r="U248">
         <f>IF(OR(AND($D248&lt;&gt;"",OR(LEN($D248)&lt;&gt;17,LEN($D248)-LEN(SUBSTITUTE($D248,":",""))&lt;&gt;5)),AND($E248&lt;&gt;"",OR(LEN($E248)&lt;&gt;17,LEN($E248)-LEN(SUBSTITUTE($E248,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -9188,16 +9195,16 @@
       <c r="J249" s="24" t="n"/>
       <c r="K249" s="24" t="n"/>
       <c r="L249" s="24" t="n"/>
-      <c r="M249" s="24" t="n"/>
       <c r="N249" s="24" t="n"/>
       <c r="O249" s="24" t="n"/>
       <c r="P249" s="24" t="n"/>
       <c r="Q249" s="24" t="n"/>
-      <c r="S249">
+      <c r="R249" s="24" t="n"/>
+      <c r="T249">
         <f>IF(COUNTA($A249:$Q249)=0,0,IF(OR($B249="",$D249="",$F249="",$G249=""),1,0))</f>
         <v/>
       </c>
-      <c r="T249">
+      <c r="U249">
         <f>IF(OR(AND($D249&lt;&gt;"",OR(LEN($D249)&lt;&gt;17,LEN($D249)-LEN(SUBSTITUTE($D249,":",""))&lt;&gt;5)),AND($E249&lt;&gt;"",OR(LEN($E249)&lt;&gt;17,LEN($E249)-LEN(SUBSTITUTE($E249,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -9215,16 +9222,16 @@
       <c r="J250" s="24" t="n"/>
       <c r="K250" s="24" t="n"/>
       <c r="L250" s="24" t="n"/>
-      <c r="M250" s="24" t="n"/>
       <c r="N250" s="24" t="n"/>
       <c r="O250" s="24" t="n"/>
       <c r="P250" s="24" t="n"/>
       <c r="Q250" s="24" t="n"/>
-      <c r="S250">
+      <c r="R250" s="24" t="n"/>
+      <c r="T250">
         <f>IF(COUNTA($A250:$Q250)=0,0,IF(OR($B250="",$D250="",$F250="",$G250=""),1,0))</f>
         <v/>
       </c>
-      <c r="T250">
+      <c r="U250">
         <f>IF(OR(AND($D250&lt;&gt;"",OR(LEN($D250)&lt;&gt;17,LEN($D250)-LEN(SUBSTITUTE($D250,":",""))&lt;&gt;5)),AND($E250&lt;&gt;"",OR(LEN($E250)&lt;&gt;17,LEN($E250)-LEN(SUBSTITUTE($E250,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -9242,16 +9249,16 @@
       <c r="J251" s="24" t="n"/>
       <c r="K251" s="24" t="n"/>
       <c r="L251" s="24" t="n"/>
-      <c r="M251" s="24" t="n"/>
       <c r="N251" s="24" t="n"/>
       <c r="O251" s="24" t="n"/>
       <c r="P251" s="24" t="n"/>
       <c r="Q251" s="24" t="n"/>
-      <c r="S251">
+      <c r="R251" s="24" t="n"/>
+      <c r="T251">
         <f>IF(COUNTA($A251:$Q251)=0,0,IF(OR($B251="",$D251="",$F251="",$G251=""),1,0))</f>
         <v/>
       </c>
-      <c r="T251">
+      <c r="U251">
         <f>IF(OR(AND($D251&lt;&gt;"",OR(LEN($D251)&lt;&gt;17,LEN($D251)-LEN(SUBSTITUTE($D251,":",""))&lt;&gt;5)),AND($E251&lt;&gt;"",OR(LEN($E251)&lt;&gt;17,LEN($E251)-LEN(SUBSTITUTE($E251,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -9269,16 +9276,16 @@
       <c r="J252" s="24" t="n"/>
       <c r="K252" s="24" t="n"/>
       <c r="L252" s="24" t="n"/>
-      <c r="M252" s="24" t="n"/>
       <c r="N252" s="24" t="n"/>
       <c r="O252" s="24" t="n"/>
       <c r="P252" s="24" t="n"/>
       <c r="Q252" s="24" t="n"/>
-      <c r="S252">
+      <c r="R252" s="24" t="n"/>
+      <c r="T252">
         <f>IF(COUNTA($A252:$Q252)=0,0,IF(OR($B252="",$D252="",$F252="",$G252=""),1,0))</f>
         <v/>
       </c>
-      <c r="T252">
+      <c r="U252">
         <f>IF(OR(AND($D252&lt;&gt;"",OR(LEN($D252)&lt;&gt;17,LEN($D252)-LEN(SUBSTITUTE($D252,":",""))&lt;&gt;5)),AND($E252&lt;&gt;"",OR(LEN($E252)&lt;&gt;17,LEN($E252)-LEN(SUBSTITUTE($E252,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -9296,16 +9303,16 @@
       <c r="J253" s="24" t="n"/>
       <c r="K253" s="24" t="n"/>
       <c r="L253" s="24" t="n"/>
-      <c r="M253" s="24" t="n"/>
       <c r="N253" s="24" t="n"/>
       <c r="O253" s="24" t="n"/>
       <c r="P253" s="24" t="n"/>
       <c r="Q253" s="24" t="n"/>
-      <c r="S253">
+      <c r="R253" s="24" t="n"/>
+      <c r="T253">
         <f>IF(COUNTA($A253:$Q253)=0,0,IF(OR($B253="",$D253="",$F253="",$G253=""),1,0))</f>
         <v/>
       </c>
-      <c r="T253">
+      <c r="U253">
         <f>IF(OR(AND($D253&lt;&gt;"",OR(LEN($D253)&lt;&gt;17,LEN($D253)-LEN(SUBSTITUTE($D253,":",""))&lt;&gt;5)),AND($E253&lt;&gt;"",OR(LEN($E253)&lt;&gt;17,LEN($E253)-LEN(SUBSTITUTE($E253,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -9323,16 +9330,16 @@
       <c r="J254" s="24" t="n"/>
       <c r="K254" s="24" t="n"/>
       <c r="L254" s="24" t="n"/>
-      <c r="M254" s="24" t="n"/>
       <c r="N254" s="24" t="n"/>
       <c r="O254" s="24" t="n"/>
       <c r="P254" s="24" t="n"/>
       <c r="Q254" s="24" t="n"/>
-      <c r="S254">
+      <c r="R254" s="24" t="n"/>
+      <c r="T254">
         <f>IF(COUNTA($A254:$Q254)=0,0,IF(OR($B254="",$D254="",$F254="",$G254=""),1,0))</f>
         <v/>
       </c>
-      <c r="T254">
+      <c r="U254">
         <f>IF(OR(AND($D254&lt;&gt;"",OR(LEN($D254)&lt;&gt;17,LEN($D254)-LEN(SUBSTITUTE($D254,":",""))&lt;&gt;5)),AND($E254&lt;&gt;"",OR(LEN($E254)&lt;&gt;17,LEN($E254)-LEN(SUBSTITUTE($E254,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -9350,16 +9357,16 @@
       <c r="J255" s="24" t="n"/>
       <c r="K255" s="24" t="n"/>
       <c r="L255" s="24" t="n"/>
-      <c r="M255" s="24" t="n"/>
       <c r="N255" s="24" t="n"/>
       <c r="O255" s="24" t="n"/>
       <c r="P255" s="24" t="n"/>
       <c r="Q255" s="24" t="n"/>
-      <c r="S255">
+      <c r="R255" s="24" t="n"/>
+      <c r="T255">
         <f>IF(COUNTA($A255:$Q255)=0,0,IF(OR($B255="",$D255="",$F255="",$G255=""),1,0))</f>
         <v/>
       </c>
-      <c r="T255">
+      <c r="U255">
         <f>IF(OR(AND($D255&lt;&gt;"",OR(LEN($D255)&lt;&gt;17,LEN($D255)-LEN(SUBSTITUTE($D255,":",""))&lt;&gt;5)),AND($E255&lt;&gt;"",OR(LEN($E255)&lt;&gt;17,LEN($E255)-LEN(SUBSTITUTE($E255,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -9377,16 +9384,16 @@
       <c r="J256" s="24" t="n"/>
       <c r="K256" s="24" t="n"/>
       <c r="L256" s="24" t="n"/>
-      <c r="M256" s="24" t="n"/>
       <c r="N256" s="24" t="n"/>
       <c r="O256" s="24" t="n"/>
       <c r="P256" s="24" t="n"/>
       <c r="Q256" s="24" t="n"/>
-      <c r="S256">
+      <c r="R256" s="24" t="n"/>
+      <c r="T256">
         <f>IF(COUNTA($A256:$Q256)=0,0,IF(OR($B256="",$D256="",$F256="",$G256=""),1,0))</f>
         <v/>
       </c>
-      <c r="T256">
+      <c r="U256">
         <f>IF(OR(AND($D256&lt;&gt;"",OR(LEN($D256)&lt;&gt;17,LEN($D256)-LEN(SUBSTITUTE($D256,":",""))&lt;&gt;5)),AND($E256&lt;&gt;"",OR(LEN($E256)&lt;&gt;17,LEN($E256)-LEN(SUBSTITUTE($E256,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -9404,16 +9411,16 @@
       <c r="J257" s="24" t="n"/>
       <c r="K257" s="24" t="n"/>
       <c r="L257" s="24" t="n"/>
-      <c r="M257" s="24" t="n"/>
       <c r="N257" s="24" t="n"/>
       <c r="O257" s="24" t="n"/>
       <c r="P257" s="24" t="n"/>
       <c r="Q257" s="24" t="n"/>
-      <c r="S257">
+      <c r="R257" s="24" t="n"/>
+      <c r="T257">
         <f>IF(COUNTA($A257:$Q257)=0,0,IF(OR($B257="",$D257="",$F257="",$G257=""),1,0))</f>
         <v/>
       </c>
-      <c r="T257">
+      <c r="U257">
         <f>IF(OR(AND($D257&lt;&gt;"",OR(LEN($D257)&lt;&gt;17,LEN($D257)-LEN(SUBSTITUTE($D257,":",""))&lt;&gt;5)),AND($E257&lt;&gt;"",OR(LEN($E257)&lt;&gt;17,LEN($E257)-LEN(SUBSTITUTE($E257,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -9431,16 +9438,16 @@
       <c r="J258" s="24" t="n"/>
       <c r="K258" s="24" t="n"/>
       <c r="L258" s="24" t="n"/>
-      <c r="M258" s="24" t="n"/>
       <c r="N258" s="24" t="n"/>
       <c r="O258" s="24" t="n"/>
       <c r="P258" s="24" t="n"/>
       <c r="Q258" s="24" t="n"/>
-      <c r="S258">
+      <c r="R258" s="24" t="n"/>
+      <c r="T258">
         <f>IF(COUNTA($A258:$Q258)=0,0,IF(OR($B258="",$D258="",$F258="",$G258=""),1,0))</f>
         <v/>
       </c>
-      <c r="T258">
+      <c r="U258">
         <f>IF(OR(AND($D258&lt;&gt;"",OR(LEN($D258)&lt;&gt;17,LEN($D258)-LEN(SUBSTITUTE($D258,":",""))&lt;&gt;5)),AND($E258&lt;&gt;"",OR(LEN($E258)&lt;&gt;17,LEN($E258)-LEN(SUBSTITUTE($E258,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -9458,16 +9465,16 @@
       <c r="J259" s="24" t="n"/>
       <c r="K259" s="24" t="n"/>
       <c r="L259" s="24" t="n"/>
-      <c r="M259" s="24" t="n"/>
       <c r="N259" s="24" t="n"/>
       <c r="O259" s="24" t="n"/>
       <c r="P259" s="24" t="n"/>
       <c r="Q259" s="24" t="n"/>
-      <c r="S259">
+      <c r="R259" s="24" t="n"/>
+      <c r="T259">
         <f>IF(COUNTA($A259:$Q259)=0,0,IF(OR($B259="",$D259="",$F259="",$G259=""),1,0))</f>
         <v/>
       </c>
-      <c r="T259">
+      <c r="U259">
         <f>IF(OR(AND($D259&lt;&gt;"",OR(LEN($D259)&lt;&gt;17,LEN($D259)-LEN(SUBSTITUTE($D259,":",""))&lt;&gt;5)),AND($E259&lt;&gt;"",OR(LEN($E259)&lt;&gt;17,LEN($E259)-LEN(SUBSTITUTE($E259,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -9485,16 +9492,16 @@
       <c r="J260" s="24" t="n"/>
       <c r="K260" s="24" t="n"/>
       <c r="L260" s="24" t="n"/>
-      <c r="M260" s="24" t="n"/>
       <c r="N260" s="24" t="n"/>
       <c r="O260" s="24" t="n"/>
       <c r="P260" s="24" t="n"/>
       <c r="Q260" s="24" t="n"/>
-      <c r="S260">
+      <c r="R260" s="24" t="n"/>
+      <c r="T260">
         <f>IF(COUNTA($A260:$Q260)=0,0,IF(OR($B260="",$D260="",$F260="",$G260=""),1,0))</f>
         <v/>
       </c>
-      <c r="T260">
+      <c r="U260">
         <f>IF(OR(AND($D260&lt;&gt;"",OR(LEN($D260)&lt;&gt;17,LEN($D260)-LEN(SUBSTITUTE($D260,":",""))&lt;&gt;5)),AND($E260&lt;&gt;"",OR(LEN($E260)&lt;&gt;17,LEN($E260)-LEN(SUBSTITUTE($E260,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -9512,16 +9519,16 @@
       <c r="J261" s="24" t="n"/>
       <c r="K261" s="24" t="n"/>
       <c r="L261" s="24" t="n"/>
-      <c r="M261" s="24" t="n"/>
       <c r="N261" s="24" t="n"/>
       <c r="O261" s="24" t="n"/>
       <c r="P261" s="24" t="n"/>
       <c r="Q261" s="24" t="n"/>
-      <c r="S261">
+      <c r="R261" s="24" t="n"/>
+      <c r="T261">
         <f>IF(COUNTA($A261:$Q261)=0,0,IF(OR($B261="",$D261="",$F261="",$G261=""),1,0))</f>
         <v/>
       </c>
-      <c r="T261">
+      <c r="U261">
         <f>IF(OR(AND($D261&lt;&gt;"",OR(LEN($D261)&lt;&gt;17,LEN($D261)-LEN(SUBSTITUTE($D261,":",""))&lt;&gt;5)),AND($E261&lt;&gt;"",OR(LEN($E261)&lt;&gt;17,LEN($E261)-LEN(SUBSTITUTE($E261,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -9539,16 +9546,16 @@
       <c r="J262" s="24" t="n"/>
       <c r="K262" s="24" t="n"/>
       <c r="L262" s="24" t="n"/>
-      <c r="M262" s="24" t="n"/>
       <c r="N262" s="24" t="n"/>
       <c r="O262" s="24" t="n"/>
       <c r="P262" s="24" t="n"/>
       <c r="Q262" s="24" t="n"/>
-      <c r="S262">
+      <c r="R262" s="24" t="n"/>
+      <c r="T262">
         <f>IF(COUNTA($A262:$Q262)=0,0,IF(OR($B262="",$D262="",$F262="",$G262=""),1,0))</f>
         <v/>
       </c>
-      <c r="T262">
+      <c r="U262">
         <f>IF(OR(AND($D262&lt;&gt;"",OR(LEN($D262)&lt;&gt;17,LEN($D262)-LEN(SUBSTITUTE($D262,":",""))&lt;&gt;5)),AND($E262&lt;&gt;"",OR(LEN($E262)&lt;&gt;17,LEN($E262)-LEN(SUBSTITUTE($E262,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -9566,16 +9573,16 @@
       <c r="J263" s="24" t="n"/>
       <c r="K263" s="24" t="n"/>
       <c r="L263" s="24" t="n"/>
-      <c r="M263" s="24" t="n"/>
       <c r="N263" s="24" t="n"/>
       <c r="O263" s="24" t="n"/>
       <c r="P263" s="24" t="n"/>
       <c r="Q263" s="24" t="n"/>
-      <c r="S263">
+      <c r="R263" s="24" t="n"/>
+      <c r="T263">
         <f>IF(COUNTA($A263:$Q263)=0,0,IF(OR($B263="",$D263="",$F263="",$G263=""),1,0))</f>
         <v/>
       </c>
-      <c r="T263">
+      <c r="U263">
         <f>IF(OR(AND($D263&lt;&gt;"",OR(LEN($D263)&lt;&gt;17,LEN($D263)-LEN(SUBSTITUTE($D263,":",""))&lt;&gt;5)),AND($E263&lt;&gt;"",OR(LEN($E263)&lt;&gt;17,LEN($E263)-LEN(SUBSTITUTE($E263,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -9593,16 +9600,16 @@
       <c r="J264" s="24" t="n"/>
       <c r="K264" s="24" t="n"/>
       <c r="L264" s="24" t="n"/>
-      <c r="M264" s="24" t="n"/>
       <c r="N264" s="24" t="n"/>
       <c r="O264" s="24" t="n"/>
       <c r="P264" s="24" t="n"/>
       <c r="Q264" s="24" t="n"/>
-      <c r="S264">
+      <c r="R264" s="24" t="n"/>
+      <c r="T264">
         <f>IF(COUNTA($A264:$Q264)=0,0,IF(OR($B264="",$D264="",$F264="",$G264=""),1,0))</f>
         <v/>
       </c>
-      <c r="T264">
+      <c r="U264">
         <f>IF(OR(AND($D264&lt;&gt;"",OR(LEN($D264)&lt;&gt;17,LEN($D264)-LEN(SUBSTITUTE($D264,":",""))&lt;&gt;5)),AND($E264&lt;&gt;"",OR(LEN($E264)&lt;&gt;17,LEN($E264)-LEN(SUBSTITUTE($E264,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -9620,16 +9627,16 @@
       <c r="J265" s="24" t="n"/>
       <c r="K265" s="24" t="n"/>
       <c r="L265" s="24" t="n"/>
-      <c r="M265" s="24" t="n"/>
       <c r="N265" s="24" t="n"/>
       <c r="O265" s="24" t="n"/>
       <c r="P265" s="24" t="n"/>
       <c r="Q265" s="24" t="n"/>
-      <c r="S265">
+      <c r="R265" s="24" t="n"/>
+      <c r="T265">
         <f>IF(COUNTA($A265:$Q265)=0,0,IF(OR($B265="",$D265="",$F265="",$G265=""),1,0))</f>
         <v/>
       </c>
-      <c r="T265">
+      <c r="U265">
         <f>IF(OR(AND($D265&lt;&gt;"",OR(LEN($D265)&lt;&gt;17,LEN($D265)-LEN(SUBSTITUTE($D265,":",""))&lt;&gt;5)),AND($E265&lt;&gt;"",OR(LEN($E265)&lt;&gt;17,LEN($E265)-LEN(SUBSTITUTE($E265,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -9647,16 +9654,16 @@
       <c r="J266" s="24" t="n"/>
       <c r="K266" s="24" t="n"/>
       <c r="L266" s="24" t="n"/>
-      <c r="M266" s="24" t="n"/>
       <c r="N266" s="24" t="n"/>
       <c r="O266" s="24" t="n"/>
       <c r="P266" s="24" t="n"/>
       <c r="Q266" s="24" t="n"/>
-      <c r="S266">
+      <c r="R266" s="24" t="n"/>
+      <c r="T266">
         <f>IF(COUNTA($A266:$Q266)=0,0,IF(OR($B266="",$D266="",$F266="",$G266=""),1,0))</f>
         <v/>
       </c>
-      <c r="T266">
+      <c r="U266">
         <f>IF(OR(AND($D266&lt;&gt;"",OR(LEN($D266)&lt;&gt;17,LEN($D266)-LEN(SUBSTITUTE($D266,":",""))&lt;&gt;5)),AND($E266&lt;&gt;"",OR(LEN($E266)&lt;&gt;17,LEN($E266)-LEN(SUBSTITUTE($E266,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -9674,16 +9681,16 @@
       <c r="J267" s="24" t="n"/>
       <c r="K267" s="24" t="n"/>
       <c r="L267" s="24" t="n"/>
-      <c r="M267" s="24" t="n"/>
       <c r="N267" s="24" t="n"/>
       <c r="O267" s="24" t="n"/>
       <c r="P267" s="24" t="n"/>
       <c r="Q267" s="24" t="n"/>
-      <c r="S267">
+      <c r="R267" s="24" t="n"/>
+      <c r="T267">
         <f>IF(COUNTA($A267:$Q267)=0,0,IF(OR($B267="",$D267="",$F267="",$G267=""),1,0))</f>
         <v/>
       </c>
-      <c r="T267">
+      <c r="U267">
         <f>IF(OR(AND($D267&lt;&gt;"",OR(LEN($D267)&lt;&gt;17,LEN($D267)-LEN(SUBSTITUTE($D267,":",""))&lt;&gt;5)),AND($E267&lt;&gt;"",OR(LEN($E267)&lt;&gt;17,LEN($E267)-LEN(SUBSTITUTE($E267,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -9701,16 +9708,16 @@
       <c r="J268" s="24" t="n"/>
       <c r="K268" s="24" t="n"/>
       <c r="L268" s="24" t="n"/>
-      <c r="M268" s="24" t="n"/>
       <c r="N268" s="24" t="n"/>
       <c r="O268" s="24" t="n"/>
       <c r="P268" s="24" t="n"/>
       <c r="Q268" s="24" t="n"/>
-      <c r="S268">
+      <c r="R268" s="24" t="n"/>
+      <c r="T268">
         <f>IF(COUNTA($A268:$Q268)=0,0,IF(OR($B268="",$D268="",$F268="",$G268=""),1,0))</f>
         <v/>
       </c>
-      <c r="T268">
+      <c r="U268">
         <f>IF(OR(AND($D268&lt;&gt;"",OR(LEN($D268)&lt;&gt;17,LEN($D268)-LEN(SUBSTITUTE($D268,":",""))&lt;&gt;5)),AND($E268&lt;&gt;"",OR(LEN($E268)&lt;&gt;17,LEN($E268)-LEN(SUBSTITUTE($E268,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -9728,16 +9735,16 @@
       <c r="J269" s="24" t="n"/>
       <c r="K269" s="24" t="n"/>
       <c r="L269" s="24" t="n"/>
-      <c r="M269" s="24" t="n"/>
       <c r="N269" s="24" t="n"/>
       <c r="O269" s="24" t="n"/>
       <c r="P269" s="24" t="n"/>
       <c r="Q269" s="24" t="n"/>
-      <c r="S269">
+      <c r="R269" s="24" t="n"/>
+      <c r="T269">
         <f>IF(COUNTA($A269:$Q269)=0,0,IF(OR($B269="",$D269="",$F269="",$G269=""),1,0))</f>
         <v/>
       </c>
-      <c r="T269">
+      <c r="U269">
         <f>IF(OR(AND($D269&lt;&gt;"",OR(LEN($D269)&lt;&gt;17,LEN($D269)-LEN(SUBSTITUTE($D269,":",""))&lt;&gt;5)),AND($E269&lt;&gt;"",OR(LEN($E269)&lt;&gt;17,LEN($E269)-LEN(SUBSTITUTE($E269,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -9755,16 +9762,16 @@
       <c r="J270" s="24" t="n"/>
       <c r="K270" s="24" t="n"/>
       <c r="L270" s="24" t="n"/>
-      <c r="M270" s="24" t="n"/>
       <c r="N270" s="24" t="n"/>
       <c r="O270" s="24" t="n"/>
       <c r="P270" s="24" t="n"/>
       <c r="Q270" s="24" t="n"/>
-      <c r="S270">
+      <c r="R270" s="24" t="n"/>
+      <c r="T270">
         <f>IF(COUNTA($A270:$Q270)=0,0,IF(OR($B270="",$D270="",$F270="",$G270=""),1,0))</f>
         <v/>
       </c>
-      <c r="T270">
+      <c r="U270">
         <f>IF(OR(AND($D270&lt;&gt;"",OR(LEN($D270)&lt;&gt;17,LEN($D270)-LEN(SUBSTITUTE($D270,":",""))&lt;&gt;5)),AND($E270&lt;&gt;"",OR(LEN($E270)&lt;&gt;17,LEN($E270)-LEN(SUBSTITUTE($E270,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -9782,16 +9789,16 @@
       <c r="J271" s="24" t="n"/>
       <c r="K271" s="24" t="n"/>
       <c r="L271" s="24" t="n"/>
-      <c r="M271" s="24" t="n"/>
       <c r="N271" s="24" t="n"/>
       <c r="O271" s="24" t="n"/>
       <c r="P271" s="24" t="n"/>
       <c r="Q271" s="24" t="n"/>
-      <c r="S271">
+      <c r="R271" s="24" t="n"/>
+      <c r="T271">
         <f>IF(COUNTA($A271:$Q271)=0,0,IF(OR($B271="",$D271="",$F271="",$G271=""),1,0))</f>
         <v/>
       </c>
-      <c r="T271">
+      <c r="U271">
         <f>IF(OR(AND($D271&lt;&gt;"",OR(LEN($D271)&lt;&gt;17,LEN($D271)-LEN(SUBSTITUTE($D271,":",""))&lt;&gt;5)),AND($E271&lt;&gt;"",OR(LEN($E271)&lt;&gt;17,LEN($E271)-LEN(SUBSTITUTE($E271,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -9809,16 +9816,16 @@
       <c r="J272" s="24" t="n"/>
       <c r="K272" s="24" t="n"/>
       <c r="L272" s="24" t="n"/>
-      <c r="M272" s="24" t="n"/>
       <c r="N272" s="24" t="n"/>
       <c r="O272" s="24" t="n"/>
       <c r="P272" s="24" t="n"/>
       <c r="Q272" s="24" t="n"/>
-      <c r="S272">
+      <c r="R272" s="24" t="n"/>
+      <c r="T272">
         <f>IF(COUNTA($A272:$Q272)=0,0,IF(OR($B272="",$D272="",$F272="",$G272=""),1,0))</f>
         <v/>
       </c>
-      <c r="T272">
+      <c r="U272">
         <f>IF(OR(AND($D272&lt;&gt;"",OR(LEN($D272)&lt;&gt;17,LEN($D272)-LEN(SUBSTITUTE($D272,":",""))&lt;&gt;5)),AND($E272&lt;&gt;"",OR(LEN($E272)&lt;&gt;17,LEN($E272)-LEN(SUBSTITUTE($E272,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -9836,16 +9843,16 @@
       <c r="J273" s="24" t="n"/>
       <c r="K273" s="24" t="n"/>
       <c r="L273" s="24" t="n"/>
-      <c r="M273" s="24" t="n"/>
       <c r="N273" s="24" t="n"/>
       <c r="O273" s="24" t="n"/>
       <c r="P273" s="24" t="n"/>
       <c r="Q273" s="24" t="n"/>
-      <c r="S273">
+      <c r="R273" s="24" t="n"/>
+      <c r="T273">
         <f>IF(COUNTA($A273:$Q273)=0,0,IF(OR($B273="",$D273="",$F273="",$G273=""),1,0))</f>
         <v/>
       </c>
-      <c r="T273">
+      <c r="U273">
         <f>IF(OR(AND($D273&lt;&gt;"",OR(LEN($D273)&lt;&gt;17,LEN($D273)-LEN(SUBSTITUTE($D273,":",""))&lt;&gt;5)),AND($E273&lt;&gt;"",OR(LEN($E273)&lt;&gt;17,LEN($E273)-LEN(SUBSTITUTE($E273,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -9863,16 +9870,16 @@
       <c r="J274" s="24" t="n"/>
       <c r="K274" s="24" t="n"/>
       <c r="L274" s="24" t="n"/>
-      <c r="M274" s="24" t="n"/>
       <c r="N274" s="24" t="n"/>
       <c r="O274" s="24" t="n"/>
       <c r="P274" s="24" t="n"/>
       <c r="Q274" s="24" t="n"/>
-      <c r="S274">
+      <c r="R274" s="24" t="n"/>
+      <c r="T274">
         <f>IF(COUNTA($A274:$Q274)=0,0,IF(OR($B274="",$D274="",$F274="",$G274=""),1,0))</f>
         <v/>
       </c>
-      <c r="T274">
+      <c r="U274">
         <f>IF(OR(AND($D274&lt;&gt;"",OR(LEN($D274)&lt;&gt;17,LEN($D274)-LEN(SUBSTITUTE($D274,":",""))&lt;&gt;5)),AND($E274&lt;&gt;"",OR(LEN($E274)&lt;&gt;17,LEN($E274)-LEN(SUBSTITUTE($E274,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -9890,16 +9897,16 @@
       <c r="J275" s="24" t="n"/>
       <c r="K275" s="24" t="n"/>
       <c r="L275" s="24" t="n"/>
-      <c r="M275" s="24" t="n"/>
       <c r="N275" s="24" t="n"/>
       <c r="O275" s="24" t="n"/>
       <c r="P275" s="24" t="n"/>
       <c r="Q275" s="24" t="n"/>
-      <c r="S275">
+      <c r="R275" s="24" t="n"/>
+      <c r="T275">
         <f>IF(COUNTA($A275:$Q275)=0,0,IF(OR($B275="",$D275="",$F275="",$G275=""),1,0))</f>
         <v/>
       </c>
-      <c r="T275">
+      <c r="U275">
         <f>IF(OR(AND($D275&lt;&gt;"",OR(LEN($D275)&lt;&gt;17,LEN($D275)-LEN(SUBSTITUTE($D275,":",""))&lt;&gt;5)),AND($E275&lt;&gt;"",OR(LEN($E275)&lt;&gt;17,LEN($E275)-LEN(SUBSTITUTE($E275,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -9917,16 +9924,16 @@
       <c r="J276" s="24" t="n"/>
       <c r="K276" s="24" t="n"/>
       <c r="L276" s="24" t="n"/>
-      <c r="M276" s="24" t="n"/>
       <c r="N276" s="24" t="n"/>
       <c r="O276" s="24" t="n"/>
       <c r="P276" s="24" t="n"/>
       <c r="Q276" s="24" t="n"/>
-      <c r="S276">
+      <c r="R276" s="24" t="n"/>
+      <c r="T276">
         <f>IF(COUNTA($A276:$Q276)=0,0,IF(OR($B276="",$D276="",$F276="",$G276=""),1,0))</f>
         <v/>
       </c>
-      <c r="T276">
+      <c r="U276">
         <f>IF(OR(AND($D276&lt;&gt;"",OR(LEN($D276)&lt;&gt;17,LEN($D276)-LEN(SUBSTITUTE($D276,":",""))&lt;&gt;5)),AND($E276&lt;&gt;"",OR(LEN($E276)&lt;&gt;17,LEN($E276)-LEN(SUBSTITUTE($E276,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -9944,16 +9951,16 @@
       <c r="J277" s="24" t="n"/>
       <c r="K277" s="24" t="n"/>
       <c r="L277" s="24" t="n"/>
-      <c r="M277" s="24" t="n"/>
       <c r="N277" s="24" t="n"/>
       <c r="O277" s="24" t="n"/>
       <c r="P277" s="24" t="n"/>
       <c r="Q277" s="24" t="n"/>
-      <c r="S277">
+      <c r="R277" s="24" t="n"/>
+      <c r="T277">
         <f>IF(COUNTA($A277:$Q277)=0,0,IF(OR($B277="",$D277="",$F277="",$G277=""),1,0))</f>
         <v/>
       </c>
-      <c r="T277">
+      <c r="U277">
         <f>IF(OR(AND($D277&lt;&gt;"",OR(LEN($D277)&lt;&gt;17,LEN($D277)-LEN(SUBSTITUTE($D277,":",""))&lt;&gt;5)),AND($E277&lt;&gt;"",OR(LEN($E277)&lt;&gt;17,LEN($E277)-LEN(SUBSTITUTE($E277,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -9971,16 +9978,16 @@
       <c r="J278" s="24" t="n"/>
       <c r="K278" s="24" t="n"/>
       <c r="L278" s="24" t="n"/>
-      <c r="M278" s="24" t="n"/>
       <c r="N278" s="24" t="n"/>
       <c r="O278" s="24" t="n"/>
       <c r="P278" s="24" t="n"/>
       <c r="Q278" s="24" t="n"/>
-      <c r="S278">
+      <c r="R278" s="24" t="n"/>
+      <c r="T278">
         <f>IF(COUNTA($A278:$Q278)=0,0,IF(OR($B278="",$D278="",$F278="",$G278=""),1,0))</f>
         <v/>
       </c>
-      <c r="T278">
+      <c r="U278">
         <f>IF(OR(AND($D278&lt;&gt;"",OR(LEN($D278)&lt;&gt;17,LEN($D278)-LEN(SUBSTITUTE($D278,":",""))&lt;&gt;5)),AND($E278&lt;&gt;"",OR(LEN($E278)&lt;&gt;17,LEN($E278)-LEN(SUBSTITUTE($E278,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -9998,16 +10005,16 @@
       <c r="J279" s="24" t="n"/>
       <c r="K279" s="24" t="n"/>
       <c r="L279" s="24" t="n"/>
-      <c r="M279" s="24" t="n"/>
       <c r="N279" s="24" t="n"/>
       <c r="O279" s="24" t="n"/>
       <c r="P279" s="24" t="n"/>
       <c r="Q279" s="24" t="n"/>
-      <c r="S279">
+      <c r="R279" s="24" t="n"/>
+      <c r="T279">
         <f>IF(COUNTA($A279:$Q279)=0,0,IF(OR($B279="",$D279="",$F279="",$G279=""),1,0))</f>
         <v/>
       </c>
-      <c r="T279">
+      <c r="U279">
         <f>IF(OR(AND($D279&lt;&gt;"",OR(LEN($D279)&lt;&gt;17,LEN($D279)-LEN(SUBSTITUTE($D279,":",""))&lt;&gt;5)),AND($E279&lt;&gt;"",OR(LEN($E279)&lt;&gt;17,LEN($E279)-LEN(SUBSTITUTE($E279,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -10025,16 +10032,16 @@
       <c r="J280" s="24" t="n"/>
       <c r="K280" s="24" t="n"/>
       <c r="L280" s="24" t="n"/>
-      <c r="M280" s="24" t="n"/>
       <c r="N280" s="24" t="n"/>
       <c r="O280" s="24" t="n"/>
       <c r="P280" s="24" t="n"/>
       <c r="Q280" s="24" t="n"/>
-      <c r="S280">
+      <c r="R280" s="24" t="n"/>
+      <c r="T280">
         <f>IF(COUNTA($A280:$Q280)=0,0,IF(OR($B280="",$D280="",$F280="",$G280=""),1,0))</f>
         <v/>
       </c>
-      <c r="T280">
+      <c r="U280">
         <f>IF(OR(AND($D280&lt;&gt;"",OR(LEN($D280)&lt;&gt;17,LEN($D280)-LEN(SUBSTITUTE($D280,":",""))&lt;&gt;5)),AND($E280&lt;&gt;"",OR(LEN($E280)&lt;&gt;17,LEN($E280)-LEN(SUBSTITUTE($E280,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -10052,16 +10059,16 @@
       <c r="J281" s="24" t="n"/>
       <c r="K281" s="24" t="n"/>
       <c r="L281" s="24" t="n"/>
-      <c r="M281" s="24" t="n"/>
       <c r="N281" s="24" t="n"/>
       <c r="O281" s="24" t="n"/>
       <c r="P281" s="24" t="n"/>
       <c r="Q281" s="24" t="n"/>
-      <c r="S281">
+      <c r="R281" s="24" t="n"/>
+      <c r="T281">
         <f>IF(COUNTA($A281:$Q281)=0,0,IF(OR($B281="",$D281="",$F281="",$G281=""),1,0))</f>
         <v/>
       </c>
-      <c r="T281">
+      <c r="U281">
         <f>IF(OR(AND($D281&lt;&gt;"",OR(LEN($D281)&lt;&gt;17,LEN($D281)-LEN(SUBSTITUTE($D281,":",""))&lt;&gt;5)),AND($E281&lt;&gt;"",OR(LEN($E281)&lt;&gt;17,LEN($E281)-LEN(SUBSTITUTE($E281,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -10079,16 +10086,16 @@
       <c r="J282" s="24" t="n"/>
       <c r="K282" s="24" t="n"/>
       <c r="L282" s="24" t="n"/>
-      <c r="M282" s="24" t="n"/>
       <c r="N282" s="24" t="n"/>
       <c r="O282" s="24" t="n"/>
       <c r="P282" s="24" t="n"/>
       <c r="Q282" s="24" t="n"/>
-      <c r="S282">
+      <c r="R282" s="24" t="n"/>
+      <c r="T282">
         <f>IF(COUNTA($A282:$Q282)=0,0,IF(OR($B282="",$D282="",$F282="",$G282=""),1,0))</f>
         <v/>
       </c>
-      <c r="T282">
+      <c r="U282">
         <f>IF(OR(AND($D282&lt;&gt;"",OR(LEN($D282)&lt;&gt;17,LEN($D282)-LEN(SUBSTITUTE($D282,":",""))&lt;&gt;5)),AND($E282&lt;&gt;"",OR(LEN($E282)&lt;&gt;17,LEN($E282)-LEN(SUBSTITUTE($E282,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -10106,16 +10113,16 @@
       <c r="J283" s="24" t="n"/>
       <c r="K283" s="24" t="n"/>
       <c r="L283" s="24" t="n"/>
-      <c r="M283" s="24" t="n"/>
       <c r="N283" s="24" t="n"/>
       <c r="O283" s="24" t="n"/>
       <c r="P283" s="24" t="n"/>
       <c r="Q283" s="24" t="n"/>
-      <c r="S283">
+      <c r="R283" s="24" t="n"/>
+      <c r="T283">
         <f>IF(COUNTA($A283:$Q283)=0,0,IF(OR($B283="",$D283="",$F283="",$G283=""),1,0))</f>
         <v/>
       </c>
-      <c r="T283">
+      <c r="U283">
         <f>IF(OR(AND($D283&lt;&gt;"",OR(LEN($D283)&lt;&gt;17,LEN($D283)-LEN(SUBSTITUTE($D283,":",""))&lt;&gt;5)),AND($E283&lt;&gt;"",OR(LEN($E283)&lt;&gt;17,LEN($E283)-LEN(SUBSTITUTE($E283,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -10133,16 +10140,16 @@
       <c r="J284" s="24" t="n"/>
       <c r="K284" s="24" t="n"/>
       <c r="L284" s="24" t="n"/>
-      <c r="M284" s="24" t="n"/>
       <c r="N284" s="24" t="n"/>
       <c r="O284" s="24" t="n"/>
       <c r="P284" s="24" t="n"/>
       <c r="Q284" s="24" t="n"/>
-      <c r="S284">
+      <c r="R284" s="24" t="n"/>
+      <c r="T284">
         <f>IF(COUNTA($A284:$Q284)=0,0,IF(OR($B284="",$D284="",$F284="",$G284=""),1,0))</f>
         <v/>
       </c>
-      <c r="T284">
+      <c r="U284">
         <f>IF(OR(AND($D284&lt;&gt;"",OR(LEN($D284)&lt;&gt;17,LEN($D284)-LEN(SUBSTITUTE($D284,":",""))&lt;&gt;5)),AND($E284&lt;&gt;"",OR(LEN($E284)&lt;&gt;17,LEN($E284)-LEN(SUBSTITUTE($E284,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -10160,16 +10167,16 @@
       <c r="J285" s="24" t="n"/>
       <c r="K285" s="24" t="n"/>
       <c r="L285" s="24" t="n"/>
-      <c r="M285" s="24" t="n"/>
       <c r="N285" s="24" t="n"/>
       <c r="O285" s="24" t="n"/>
       <c r="P285" s="24" t="n"/>
       <c r="Q285" s="24" t="n"/>
-      <c r="S285">
+      <c r="R285" s="24" t="n"/>
+      <c r="T285">
         <f>IF(COUNTA($A285:$Q285)=0,0,IF(OR($B285="",$D285="",$F285="",$G285=""),1,0))</f>
         <v/>
       </c>
-      <c r="T285">
+      <c r="U285">
         <f>IF(OR(AND($D285&lt;&gt;"",OR(LEN($D285)&lt;&gt;17,LEN($D285)-LEN(SUBSTITUTE($D285,":",""))&lt;&gt;5)),AND($E285&lt;&gt;"",OR(LEN($E285)&lt;&gt;17,LEN($E285)-LEN(SUBSTITUTE($E285,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -10187,16 +10194,16 @@
       <c r="J286" s="24" t="n"/>
       <c r="K286" s="24" t="n"/>
       <c r="L286" s="24" t="n"/>
-      <c r="M286" s="24" t="n"/>
       <c r="N286" s="24" t="n"/>
       <c r="O286" s="24" t="n"/>
       <c r="P286" s="24" t="n"/>
       <c r="Q286" s="24" t="n"/>
-      <c r="S286">
+      <c r="R286" s="24" t="n"/>
+      <c r="T286">
         <f>IF(COUNTA($A286:$Q286)=0,0,IF(OR($B286="",$D286="",$F286="",$G286=""),1,0))</f>
         <v/>
       </c>
-      <c r="T286">
+      <c r="U286">
         <f>IF(OR(AND($D286&lt;&gt;"",OR(LEN($D286)&lt;&gt;17,LEN($D286)-LEN(SUBSTITUTE($D286,":",""))&lt;&gt;5)),AND($E286&lt;&gt;"",OR(LEN($E286)&lt;&gt;17,LEN($E286)-LEN(SUBSTITUTE($E286,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -10214,16 +10221,16 @@
       <c r="J287" s="24" t="n"/>
       <c r="K287" s="24" t="n"/>
       <c r="L287" s="24" t="n"/>
-      <c r="M287" s="24" t="n"/>
       <c r="N287" s="24" t="n"/>
       <c r="O287" s="24" t="n"/>
       <c r="P287" s="24" t="n"/>
       <c r="Q287" s="24" t="n"/>
-      <c r="S287">
+      <c r="R287" s="24" t="n"/>
+      <c r="T287">
         <f>IF(COUNTA($A287:$Q287)=0,0,IF(OR($B287="",$D287="",$F287="",$G287=""),1,0))</f>
         <v/>
       </c>
-      <c r="T287">
+      <c r="U287">
         <f>IF(OR(AND($D287&lt;&gt;"",OR(LEN($D287)&lt;&gt;17,LEN($D287)-LEN(SUBSTITUTE($D287,":",""))&lt;&gt;5)),AND($E287&lt;&gt;"",OR(LEN($E287)&lt;&gt;17,LEN($E287)-LEN(SUBSTITUTE($E287,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -10241,16 +10248,16 @@
       <c r="J288" s="24" t="n"/>
       <c r="K288" s="24" t="n"/>
       <c r="L288" s="24" t="n"/>
-      <c r="M288" s="24" t="n"/>
       <c r="N288" s="24" t="n"/>
       <c r="O288" s="24" t="n"/>
       <c r="P288" s="24" t="n"/>
       <c r="Q288" s="24" t="n"/>
-      <c r="S288">
+      <c r="R288" s="24" t="n"/>
+      <c r="T288">
         <f>IF(COUNTA($A288:$Q288)=0,0,IF(OR($B288="",$D288="",$F288="",$G288=""),1,0))</f>
         <v/>
       </c>
-      <c r="T288">
+      <c r="U288">
         <f>IF(OR(AND($D288&lt;&gt;"",OR(LEN($D288)&lt;&gt;17,LEN($D288)-LEN(SUBSTITUTE($D288,":",""))&lt;&gt;5)),AND($E288&lt;&gt;"",OR(LEN($E288)&lt;&gt;17,LEN($E288)-LEN(SUBSTITUTE($E288,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -10268,16 +10275,16 @@
       <c r="J289" s="24" t="n"/>
       <c r="K289" s="24" t="n"/>
       <c r="L289" s="24" t="n"/>
-      <c r="M289" s="24" t="n"/>
       <c r="N289" s="24" t="n"/>
       <c r="O289" s="24" t="n"/>
       <c r="P289" s="24" t="n"/>
       <c r="Q289" s="24" t="n"/>
-      <c r="S289">
+      <c r="R289" s="24" t="n"/>
+      <c r="T289">
         <f>IF(COUNTA($A289:$Q289)=0,0,IF(OR($B289="",$D289="",$F289="",$G289=""),1,0))</f>
         <v/>
       </c>
-      <c r="T289">
+      <c r="U289">
         <f>IF(OR(AND($D289&lt;&gt;"",OR(LEN($D289)&lt;&gt;17,LEN($D289)-LEN(SUBSTITUTE($D289,":",""))&lt;&gt;5)),AND($E289&lt;&gt;"",OR(LEN($E289)&lt;&gt;17,LEN($E289)-LEN(SUBSTITUTE($E289,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -10295,16 +10302,16 @@
       <c r="J290" s="24" t="n"/>
       <c r="K290" s="24" t="n"/>
       <c r="L290" s="24" t="n"/>
-      <c r="M290" s="24" t="n"/>
       <c r="N290" s="24" t="n"/>
       <c r="O290" s="24" t="n"/>
       <c r="P290" s="24" t="n"/>
       <c r="Q290" s="24" t="n"/>
-      <c r="S290">
+      <c r="R290" s="24" t="n"/>
+      <c r="T290">
         <f>IF(COUNTA($A290:$Q290)=0,0,IF(OR($B290="",$D290="",$F290="",$G290=""),1,0))</f>
         <v/>
       </c>
-      <c r="T290">
+      <c r="U290">
         <f>IF(OR(AND($D290&lt;&gt;"",OR(LEN($D290)&lt;&gt;17,LEN($D290)-LEN(SUBSTITUTE($D290,":",""))&lt;&gt;5)),AND($E290&lt;&gt;"",OR(LEN($E290)&lt;&gt;17,LEN($E290)-LEN(SUBSTITUTE($E290,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -10322,16 +10329,16 @@
       <c r="J291" s="24" t="n"/>
       <c r="K291" s="24" t="n"/>
       <c r="L291" s="24" t="n"/>
-      <c r="M291" s="24" t="n"/>
       <c r="N291" s="24" t="n"/>
       <c r="O291" s="24" t="n"/>
       <c r="P291" s="24" t="n"/>
       <c r="Q291" s="24" t="n"/>
-      <c r="S291">
+      <c r="R291" s="24" t="n"/>
+      <c r="T291">
         <f>IF(COUNTA($A291:$Q291)=0,0,IF(OR($B291="",$D291="",$F291="",$G291=""),1,0))</f>
         <v/>
       </c>
-      <c r="T291">
+      <c r="U291">
         <f>IF(OR(AND($D291&lt;&gt;"",OR(LEN($D291)&lt;&gt;17,LEN($D291)-LEN(SUBSTITUTE($D291,":",""))&lt;&gt;5)),AND($E291&lt;&gt;"",OR(LEN($E291)&lt;&gt;17,LEN($E291)-LEN(SUBSTITUTE($E291,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -10349,16 +10356,16 @@
       <c r="J292" s="24" t="n"/>
       <c r="K292" s="24" t="n"/>
       <c r="L292" s="24" t="n"/>
-      <c r="M292" s="24" t="n"/>
       <c r="N292" s="24" t="n"/>
       <c r="O292" s="24" t="n"/>
       <c r="P292" s="24" t="n"/>
       <c r="Q292" s="24" t="n"/>
-      <c r="S292">
+      <c r="R292" s="24" t="n"/>
+      <c r="T292">
         <f>IF(COUNTA($A292:$Q292)=0,0,IF(OR($B292="",$D292="",$F292="",$G292=""),1,0))</f>
         <v/>
       </c>
-      <c r="T292">
+      <c r="U292">
         <f>IF(OR(AND($D292&lt;&gt;"",OR(LEN($D292)&lt;&gt;17,LEN($D292)-LEN(SUBSTITUTE($D292,":",""))&lt;&gt;5)),AND($E292&lt;&gt;"",OR(LEN($E292)&lt;&gt;17,LEN($E292)-LEN(SUBSTITUTE($E292,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -10376,16 +10383,16 @@
       <c r="J293" s="24" t="n"/>
       <c r="K293" s="24" t="n"/>
       <c r="L293" s="24" t="n"/>
-      <c r="M293" s="24" t="n"/>
       <c r="N293" s="24" t="n"/>
       <c r="O293" s="24" t="n"/>
       <c r="P293" s="24" t="n"/>
       <c r="Q293" s="24" t="n"/>
-      <c r="S293">
+      <c r="R293" s="24" t="n"/>
+      <c r="T293">
         <f>IF(COUNTA($A293:$Q293)=0,0,IF(OR($B293="",$D293="",$F293="",$G293=""),1,0))</f>
         <v/>
       </c>
-      <c r="T293">
+      <c r="U293">
         <f>IF(OR(AND($D293&lt;&gt;"",OR(LEN($D293)&lt;&gt;17,LEN($D293)-LEN(SUBSTITUTE($D293,":",""))&lt;&gt;5)),AND($E293&lt;&gt;"",OR(LEN($E293)&lt;&gt;17,LEN($E293)-LEN(SUBSTITUTE($E293,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -10403,16 +10410,16 @@
       <c r="J294" s="24" t="n"/>
       <c r="K294" s="24" t="n"/>
       <c r="L294" s="24" t="n"/>
-      <c r="M294" s="24" t="n"/>
       <c r="N294" s="24" t="n"/>
       <c r="O294" s="24" t="n"/>
       <c r="P294" s="24" t="n"/>
       <c r="Q294" s="24" t="n"/>
-      <c r="S294">
+      <c r="R294" s="24" t="n"/>
+      <c r="T294">
         <f>IF(COUNTA($A294:$Q294)=0,0,IF(OR($B294="",$D294="",$F294="",$G294=""),1,0))</f>
         <v/>
       </c>
-      <c r="T294">
+      <c r="U294">
         <f>IF(OR(AND($D294&lt;&gt;"",OR(LEN($D294)&lt;&gt;17,LEN($D294)-LEN(SUBSTITUTE($D294,":",""))&lt;&gt;5)),AND($E294&lt;&gt;"",OR(LEN($E294)&lt;&gt;17,LEN($E294)-LEN(SUBSTITUTE($E294,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -10430,16 +10437,16 @@
       <c r="J295" s="24" t="n"/>
       <c r="K295" s="24" t="n"/>
       <c r="L295" s="24" t="n"/>
-      <c r="M295" s="24" t="n"/>
       <c r="N295" s="24" t="n"/>
       <c r="O295" s="24" t="n"/>
       <c r="P295" s="24" t="n"/>
       <c r="Q295" s="24" t="n"/>
-      <c r="S295">
+      <c r="R295" s="24" t="n"/>
+      <c r="T295">
         <f>IF(COUNTA($A295:$Q295)=0,0,IF(OR($B295="",$D295="",$F295="",$G295=""),1,0))</f>
         <v/>
       </c>
-      <c r="T295">
+      <c r="U295">
         <f>IF(OR(AND($D295&lt;&gt;"",OR(LEN($D295)&lt;&gt;17,LEN($D295)-LEN(SUBSTITUTE($D295,":",""))&lt;&gt;5)),AND($E295&lt;&gt;"",OR(LEN($E295)&lt;&gt;17,LEN($E295)-LEN(SUBSTITUTE($E295,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -10457,16 +10464,16 @@
       <c r="J296" s="24" t="n"/>
       <c r="K296" s="24" t="n"/>
       <c r="L296" s="24" t="n"/>
-      <c r="M296" s="24" t="n"/>
       <c r="N296" s="24" t="n"/>
       <c r="O296" s="24" t="n"/>
       <c r="P296" s="24" t="n"/>
       <c r="Q296" s="24" t="n"/>
-      <c r="S296">
+      <c r="R296" s="24" t="n"/>
+      <c r="T296">
         <f>IF(COUNTA($A296:$Q296)=0,0,IF(OR($B296="",$D296="",$F296="",$G296=""),1,0))</f>
         <v/>
       </c>
-      <c r="T296">
+      <c r="U296">
         <f>IF(OR(AND($D296&lt;&gt;"",OR(LEN($D296)&lt;&gt;17,LEN($D296)-LEN(SUBSTITUTE($D296,":",""))&lt;&gt;5)),AND($E296&lt;&gt;"",OR(LEN($E296)&lt;&gt;17,LEN($E296)-LEN(SUBSTITUTE($E296,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -10484,16 +10491,16 @@
       <c r="J297" s="24" t="n"/>
       <c r="K297" s="24" t="n"/>
       <c r="L297" s="24" t="n"/>
-      <c r="M297" s="24" t="n"/>
       <c r="N297" s="24" t="n"/>
       <c r="O297" s="24" t="n"/>
       <c r="P297" s="24" t="n"/>
       <c r="Q297" s="24" t="n"/>
-      <c r="S297">
+      <c r="R297" s="24" t="n"/>
+      <c r="T297">
         <f>IF(COUNTA($A297:$Q297)=0,0,IF(OR($B297="",$D297="",$F297="",$G297=""),1,0))</f>
         <v/>
       </c>
-      <c r="T297">
+      <c r="U297">
         <f>IF(OR(AND($D297&lt;&gt;"",OR(LEN($D297)&lt;&gt;17,LEN($D297)-LEN(SUBSTITUTE($D297,":",""))&lt;&gt;5)),AND($E297&lt;&gt;"",OR(LEN($E297)&lt;&gt;17,LEN($E297)-LEN(SUBSTITUTE($E297,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -10511,16 +10518,16 @@
       <c r="J298" s="24" t="n"/>
       <c r="K298" s="24" t="n"/>
       <c r="L298" s="24" t="n"/>
-      <c r="M298" s="24" t="n"/>
       <c r="N298" s="24" t="n"/>
       <c r="O298" s="24" t="n"/>
       <c r="P298" s="24" t="n"/>
       <c r="Q298" s="24" t="n"/>
-      <c r="S298">
+      <c r="R298" s="24" t="n"/>
+      <c r="T298">
         <f>IF(COUNTA($A298:$Q298)=0,0,IF(OR($B298="",$D298="",$F298="",$G298=""),1,0))</f>
         <v/>
       </c>
-      <c r="T298">
+      <c r="U298">
         <f>IF(OR(AND($D298&lt;&gt;"",OR(LEN($D298)&lt;&gt;17,LEN($D298)-LEN(SUBSTITUTE($D298,":",""))&lt;&gt;5)),AND($E298&lt;&gt;"",OR(LEN($E298)&lt;&gt;17,LEN($E298)-LEN(SUBSTITUTE($E298,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -10538,16 +10545,16 @@
       <c r="J299" s="24" t="n"/>
       <c r="K299" s="24" t="n"/>
       <c r="L299" s="24" t="n"/>
-      <c r="M299" s="24" t="n"/>
       <c r="N299" s="24" t="n"/>
       <c r="O299" s="24" t="n"/>
       <c r="P299" s="24" t="n"/>
       <c r="Q299" s="24" t="n"/>
-      <c r="S299">
+      <c r="R299" s="24" t="n"/>
+      <c r="T299">
         <f>IF(COUNTA($A299:$Q299)=0,0,IF(OR($B299="",$D299="",$F299="",$G299=""),1,0))</f>
         <v/>
       </c>
-      <c r="T299">
+      <c r="U299">
         <f>IF(OR(AND($D299&lt;&gt;"",OR(LEN($D299)&lt;&gt;17,LEN($D299)-LEN(SUBSTITUTE($D299,":",""))&lt;&gt;5)),AND($E299&lt;&gt;"",OR(LEN($E299)&lt;&gt;17,LEN($E299)-LEN(SUBSTITUTE($E299,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -10565,16 +10572,16 @@
       <c r="J300" s="24" t="n"/>
       <c r="K300" s="24" t="n"/>
       <c r="L300" s="24" t="n"/>
-      <c r="M300" s="24" t="n"/>
       <c r="N300" s="24" t="n"/>
       <c r="O300" s="24" t="n"/>
       <c r="P300" s="24" t="n"/>
       <c r="Q300" s="24" t="n"/>
-      <c r="S300">
+      <c r="R300" s="24" t="n"/>
+      <c r="T300">
         <f>IF(COUNTA($A300:$Q300)=0,0,IF(OR($B300="",$D300="",$F300="",$G300=""),1,0))</f>
         <v/>
       </c>
-      <c r="T300">
+      <c r="U300">
         <f>IF(OR(AND($D300&lt;&gt;"",OR(LEN($D300)&lt;&gt;17,LEN($D300)-LEN(SUBSTITUTE($D300,":",""))&lt;&gt;5)),AND($E300&lt;&gt;"",OR(LEN($E300)&lt;&gt;17,LEN($E300)-LEN(SUBSTITUTE($E300,":",""))&lt;&gt;5))),1,0)</f>
         <v/>
       </c>
@@ -10616,7 +10623,7 @@
     <dataValidation sqref="G2:G300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Referentiels!$A$4:$A$203</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H300 I2:I300 J2:J300 K2:K300 L2:L300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:M300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Oui,Non"</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D300" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Adresse MAC invalide" error="Format attendu : AA:BB:CC:DD:EE:FF — 6 paires hexadécimales (0-9, A-F) séparées par « : »." promptTitle="Format adresse MAC" prompt="6 paires hexadécimales séparées par « : », ex. 00:1A:2B:3C:4D:5E" type="custom" errorStyle="stop">
@@ -10625,7 +10632,7 @@
     <dataValidation sqref="E2:E300" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Adresse MAC invalide" error="Format attendu : AA:BB:CC:DD:EE:FF — 6 paires hexadécimales (0-9, A-F) séparées par « : »." promptTitle="Format adresse MAC" prompt="6 paires hexadécimales séparées par « : », ex. 00:1A:2B:3C:4D:5E" type="custom" errorStyle="stop">
       <formula1>AND(LEN(E2)=17,LEN(SUBSTITUTE(E2,":",""))=12,MID(E2,3,1)=":",MID(E2,6,1)=":",MID(E2,9,1)=":",MID(E2,12,1)=":",MID(E2,15,1)=":",ISNUMBER(HEX2DEC(LEFT(SUBSTITUTE(E2,":",""),6))),ISNUMBER(HEX2DEC(MID(SUBSTITUTE(E2,":",""),7,6))))</formula1>
     </dataValidation>
-    <dataValidation sqref="P2:P300" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Statut du matériel" prompt="En service / En panne / À changer" type="list">
+    <dataValidation sqref="Q2:Q300" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Statut du matériel" prompt="En service / En panne / À changer" type="list">
       <formula1>"En service,En panne,À changer"</formula1>
     </dataValidation>
   </dataValidations>
